--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="2085">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048797607422</t>
+    <t xml:space="preserve">5.32048845291138</t>
   </si>
   <si>
     <t xml:space="preserve">5.17209386825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13951921463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26257848739624</t>
+    <t xml:space="preserve">5.13951969146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26257944107056</t>
   </si>
   <si>
     <t xml:space="preserve">5.1322808265686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26619720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31325006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959499359131</t>
+    <t xml:space="preserve">5.26619815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3132495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19381093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0454158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959547042847</t>
   </si>
   <si>
     <t xml:space="preserve">5.07437133789062</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">4.65814208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82101345062256</t>
+    <t xml:space="preserve">4.8210129737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">5.05265474319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21190690994263</t>
+    <t xml:space="preserve">5.21190738677979</t>
   </si>
   <si>
     <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485500335693</t>
+    <t xml:space="preserve">5.14675855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485548019409</t>
   </si>
   <si>
     <t xml:space="preserve">5.12504196166992</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">4.74138784408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56765794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34325551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45545721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441171646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213472366333</t>
+    <t xml:space="preserve">4.56765747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34325647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45545768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4844126701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213520050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.78482055664062</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">4.73414897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81377601623535</t>
+    <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.7667236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71243238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187246322632</t>
+    <t xml:space="preserve">4.71243286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187294006348</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88616418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00922203063965</t>
+    <t xml:space="preserve">4.88616323471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00922250747681</t>
   </si>
   <si>
     <t xml:space="preserve">5.09246778488159</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">5.10332632064819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16847515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95493125915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84272956848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120088577271</t>
+    <t xml:space="preserve">5.16847467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95493173599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8427300453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120040893555</t>
   </si>
   <si>
     <t xml:space="preserve">5.06713199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08884859085083</t>
+    <t xml:space="preserve">5.08884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">5.00560188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99112462997437</t>
+    <t xml:space="preserve">4.99112510681152</t>
   </si>
   <si>
     <t xml:space="preserve">5.19019079208374</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">5.23362350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35668277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12866115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02007961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94769191741943</t>
+    <t xml:space="preserve">5.35668230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12866163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02008056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94769239425659</t>
   </si>
   <si>
     <t xml:space="preserve">4.9730281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02370023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11418294906616</t>
+    <t xml:space="preserve">4.90787982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369928359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11418390274048</t>
   </si>
   <si>
     <t xml:space="preserve">5.121422290802</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">5.23406362533569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.282874584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27161073684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23030948638916</t>
+    <t xml:space="preserve">5.28287506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27161026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.230309009552</t>
   </si>
   <si>
     <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168601989746</t>
+    <t xml:space="preserve">5.33168649673462</t>
   </si>
   <si>
     <t xml:space="preserve">5.30164813995361</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">5.09889459609985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96747875213623</t>
+    <t xml:space="preserve">4.96747970581055</t>
   </si>
   <si>
     <t xml:space="preserve">4.88863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78725385665894</t>
+    <t xml:space="preserve">4.78725337982178</t>
   </si>
   <si>
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472520828247</t>
+    <t xml:space="preserve">4.76472473144531</t>
   </si>
   <si>
     <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96372556686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90364980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90740442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77598905563354</t>
+    <t xml:space="preserve">4.96372509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90364933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7759895324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.73844242095947</t>
@@ -296,43 +296,43 @@
     <t xml:space="preserve">4.84357404708862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91866827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.986252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97874307632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01629114151001</t>
+    <t xml:space="preserve">4.91866874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98625326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97874355316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01629018783569</t>
   </si>
   <si>
     <t xml:space="preserve">4.92617797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95246028900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9712347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483837127686</t>
+    <t xml:space="preserve">4.95246076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97123432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8548378944397</t>
   </si>
   <si>
     <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80227184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62204742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44182062149048</t>
+    <t xml:space="preserve">4.8022723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62204647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197118759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44182014465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.4493293762207</t>
@@ -347,46 +347,46 @@
     <t xml:space="preserve">4.7534613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73093318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80602693557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97498941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1301794052124</t>
+    <t xml:space="preserve">4.73093271255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80602741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97498893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13017892837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39676380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33668899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39300870895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17523622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10014247894287</t>
+    <t xml:space="preserve">4.33668851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39300966262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17523574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10014152526855</t>
   </si>
   <si>
     <t xml:space="preserve">3.87485909461975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94244432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26534938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31791496276855</t>
+    <t xml:space="preserve">3.94244384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2653489112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31791543960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.1902551651001</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">4.23531150817871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31040573120117</t>
+    <t xml:space="preserve">4.31040525436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.25032997131348</t>
@@ -413,49 +413,49 @@
     <t xml:space="preserve">4.09638690948486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93118071556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8373122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93868947029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623682022095</t>
+    <t xml:space="preserve">3.9311797618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98750066757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83731174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9386899471283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623634338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493485450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97248196601868</t>
+    <t xml:space="preserve">3.97248148918152</t>
   </si>
   <si>
     <t xml:space="preserve">3.95746302604675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9461989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99876475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980275154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604765892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348208427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133104324341</t>
+    <t xml:space="preserve">3.94619846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99876427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8298032283783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604813575745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.07010412216187</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01378393173218</t>
+    <t xml:space="preserve">4.01378345489502</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09263229370117</t>
+    <t xml:space="preserve">4.09263181686401</t>
   </si>
   <si>
     <t xml:space="preserve">4.1376895904541</t>
@@ -479,64 +479,64 @@
     <t xml:space="preserve">4.12267017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05508613586426</t>
+    <t xml:space="preserve">4.0550856590271</t>
   </si>
   <si>
     <t xml:space="preserve">4.07385921478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03255653381348</t>
+    <t xml:space="preserve">4.03255701065063</t>
   </si>
   <si>
     <t xml:space="preserve">3.91240644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82229351997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478381156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90489745140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114235877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987827301025</t>
+    <t xml:space="preserve">3.82229375839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9048969745636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114188194275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987731933594</t>
   </si>
   <si>
     <t xml:space="preserve">3.81102919578552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88612413406372</t>
+    <t xml:space="preserve">3.88612365722656</t>
   </si>
   <si>
     <t xml:space="preserve">3.89738774299622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88236856460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110447883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850054740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61202931404114</t>
+    <t xml:space="preserve">3.88236904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221871376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6120297908783</t>
   </si>
   <si>
     <t xml:space="preserve">3.59550881385803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79601073265076</t>
+    <t xml:space="preserve">3.79600977897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.96121764183044</t>
@@ -545,88 +545,88 @@
     <t xml:space="preserve">3.97999143600464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02504825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96497225761414</t>
+    <t xml:space="preserve">4.02504777908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96497273445129</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08887767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14519882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99501061439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474593162537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727505683899</t>
+    <t xml:space="preserve">4.08887815475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14519834518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99501013755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742514610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474640846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727529525757</t>
   </si>
   <si>
     <t xml:space="preserve">3.79225564002991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.751704454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518443107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60452055931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54444456100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843808174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54144144058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55645990371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47085285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799982070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66459536552429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64507174491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66910171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748627662659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968958854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857654571533</t>
+    <t xml:space="preserve">3.75170516967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64056539535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60452008247375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5444450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843760490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54144191741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55645942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4708526134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799910545349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66459584236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64507126808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66910147666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748603820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73968982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857606887817</t>
   </si>
   <si>
     <t xml:space="preserve">4.14144325256348</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">4.1038966178894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01002883911133</t>
+    <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
     <t xml:space="preserve">4.04006624221802</t>
@@ -644,28 +644,28 @@
     <t xml:space="preserve">4.11516046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00251960754395</t>
+    <t xml:space="preserve">4.00251913070679</t>
   </si>
   <si>
     <t xml:space="preserve">4.07761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16772651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270805358887</t>
+    <t xml:space="preserve">4.16772699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270757675171</t>
   </si>
   <si>
     <t xml:space="preserve">4.14895343780518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512353897095</t>
+    <t xml:space="preserve">4.08512306213379</t>
   </si>
   <si>
     <t xml:space="preserve">4.18274593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22029256820679</t>
+    <t xml:space="preserve">4.22029209136963</t>
   </si>
   <si>
     <t xml:space="preserve">4.23906660079956</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06259489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03631162643433</t>
+    <t xml:space="preserve">4.12642526626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06259441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03631210327148</t>
   </si>
   <si>
     <t xml:space="preserve">4.13393449783325</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">4.28787708282471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30289697647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293390274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706493377686</t>
+    <t xml:space="preserve">4.30289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706541061401</t>
   </si>
   <si>
     <t xml:space="preserve">4.6933856010437</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">4.72342348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085742950439</t>
+    <t xml:space="preserve">4.67085790634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.80978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83981943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81353664398193</t>
+    <t xml:space="preserve">4.83982038497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81353616714478</t>
   </si>
   <si>
     <t xml:space="preserve">4.79851770401001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72717761993408</t>
+    <t xml:space="preserve">4.72717809677124</t>
   </si>
   <si>
     <t xml:space="preserve">4.85108375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82104587554932</t>
+    <t xml:space="preserve">4.82104539871216</t>
   </si>
   <si>
     <t xml:space="preserve">4.83606433868408</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.07056140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13733100891113</t>
+    <t xml:space="preserve">5.13733053207397</t>
   </si>
   <si>
     <t xml:space="preserve">5.10198211669922</t>
@@ -749,37 +749,37 @@
     <t xml:space="preserve">5.0744891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12947559356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16875123977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371210098267</t>
+    <t xml:space="preserve">5.12947511672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16875171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552131652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371257781982</t>
   </si>
   <si>
     <t xml:space="preserve">5.3415675163269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3769154548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20410060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28265190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20017337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092334747314</t>
+    <t xml:space="preserve">5.37691593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20410013198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28265237808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20017290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373819351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0509238243103</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
@@ -788,40 +788,40 @@
     <t xml:space="preserve">5.29050779342651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26694297790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36906099319458</t>
+    <t xml:space="preserve">5.26694250106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36906051635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.34942197799683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3847713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588277816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21981191635132</t>
+    <t xml:space="preserve">5.38477182388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21981143951416</t>
   </si>
   <si>
     <t xml:space="preserve">5.25515937805176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32978391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32585716247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512321472168</t>
+    <t xml:space="preserve">5.32978487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32585668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25123167037964</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975782394409</t>
+    <t xml:space="preserve">5.43975830078125</t>
   </si>
   <si>
     <t xml:space="preserve">5.61650133132935</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">5.57722473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5418758392334</t>
+    <t xml:space="preserve">5.54187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">5.63221120834351</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">5.5065279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53794860839844</t>
+    <t xml:space="preserve">5.53794813156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55365896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50260019302368</t>
+    <t xml:space="preserve">5.55365943908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50259971618652</t>
   </si>
   <si>
     <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52223825454712</t>
+    <t xml:space="preserve">5.52223873138428</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257266998291</t>
@@ -875,40 +875,40 @@
     <t xml:space="preserve">5.71076440811157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73432922363281</t>
+    <t xml:space="preserve">5.73432970046997</t>
   </si>
   <si>
     <t xml:space="preserve">5.64006614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65970420837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72647428512573</t>
+    <t xml:space="preserve">5.65970468521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72647380828857</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67148780822754</t>
+    <t xml:space="preserve">5.67148733139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.65577697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77753353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77360582351685</t>
+    <t xml:space="preserve">5.77753305435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77360534667969</t>
   </si>
   <si>
     <t xml:space="preserve">5.86786842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83644723892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82466506958008</t>
+    <t xml:space="preserve">5.83644771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82466459274292</t>
   </si>
   <si>
     <t xml:space="preserve">5.8403754234314</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">5.82859230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87179613113403</t>
+    <t xml:space="preserve">5.87179708480835</t>
   </si>
   <si>
     <t xml:space="preserve">5.93463802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95034837722778</t>
+    <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
     <t xml:space="preserve">5.90714502334595</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">5.7971715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70290899276733</t>
+    <t xml:space="preserve">5.70290851593018</t>
   </si>
   <si>
     <t xml:space="preserve">5.78931617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89143419265747</t>
+    <t xml:space="preserve">5.89143466949463</t>
   </si>
   <si>
     <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68719720840454</t>
+    <t xml:space="preserve">5.79324340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70683670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68719816207886</t>
   </si>
   <si>
     <t xml:space="preserve">5.56936979293823</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">5.59293460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66755962371826</t>
+    <t xml:space="preserve">5.66756010055542</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903394699097</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">5.39262628555298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45939588546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75004005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182270050049</t>
+    <t xml:space="preserve">5.45939540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75004053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7618236541748</t>
   </si>
   <si>
     <t xml:space="preserve">5.73040199279785</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8089542388916</t>
+    <t xml:space="preserve">5.80895471572876</t>
   </si>
   <si>
     <t xml:space="preserve">5.91499996185303</t>
@@ -1001,46 +1001,46 @@
     <t xml:space="preserve">5.87965154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8521580696106</t>
+    <t xml:space="preserve">5.85215854644775</t>
   </si>
   <si>
     <t xml:space="preserve">5.84430313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86001300811768</t>
+    <t xml:space="preserve">5.86001348495483</t>
   </si>
   <si>
     <t xml:space="preserve">5.84823083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72254657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69505310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6636323928833</t>
+    <t xml:space="preserve">5.72254610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6950535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363286972046</t>
   </si>
   <si>
     <t xml:space="preserve">5.64792156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71861886978149</t>
+    <t xml:space="preserve">5.71861934661865</t>
   </si>
   <si>
     <t xml:space="preserve">5.83252000808716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76575040817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11530876159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08388757705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26063013076782</t>
+    <t xml:space="preserve">5.76575088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11530828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08388805389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2606315612793</t>
   </si>
   <si>
     <t xml:space="preserve">6.24492025375366</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">6.30776262283325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29990768432617</t>
+    <t xml:space="preserve">6.29990720748901</t>
   </si>
   <si>
     <t xml:space="preserve">6.29205226898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25670337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25277614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20171689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2331371307373</t>
+    <t xml:space="preserve">6.25670289993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2527756690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26455879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20171642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23313808441162</t>
   </si>
   <si>
     <t xml:space="preserve">6.06032228469849</t>
@@ -1085,73 +1085,73 @@
     <t xml:space="preserve">6.12709188461304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528314590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28026962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37060356140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37453269958496</t>
+    <t xml:space="preserve">6.22528266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37060403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3745322227478</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39809799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45308446884155</t>
+    <t xml:space="preserve">6.39809846878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45308494567871</t>
   </si>
   <si>
     <t xml:space="preserve">6.58662366867065</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65339326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53949165344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60626125335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63768291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56305742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83013582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874216079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79086065292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409105300903</t>
+    <t xml:space="preserve">6.65339279174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60626173019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63768243789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5630578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230840682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8301362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79086017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088579177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.77907752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336622238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85763025283813</t>
+    <t xml:space="preserve">6.75551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336717605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762977600098</t>
   </si>
   <si>
     <t xml:space="preserve">6.86155700683594</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">6.81049823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70445251464844</t>
+    <t xml:space="preserve">6.7044529914856</t>
   </si>
   <si>
     <t xml:space="preserve">6.63375473022461</t>
@@ -1169,58 +1169,58 @@
     <t xml:space="preserve">6.64553737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91261720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99902391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116945266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40356922149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5803108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54103660583496</t>
+    <t xml:space="preserve">6.91261672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40356969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54103565216064</t>
   </si>
   <si>
     <t xml:space="preserve">7.55281782150269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46641111373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66671943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80418586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75705480575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8866662979126</t>
+    <t xml:space="preserve">7.46641254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66672039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8041877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75705575942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88666725158691</t>
   </si>
   <si>
     <t xml:space="preserve">7.93379831314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91808748245239</t>
+    <t xml:space="preserve">7.91808843612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.78454828262329</t>
@@ -1232,37 +1232,37 @@
     <t xml:space="preserve">7.87488317489624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74056100845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886449813843</t>
+    <t xml:space="preserve">7.74056005477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886497497559</t>
   </si>
   <si>
     <t xml:space="preserve">7.31951808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50804281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53161001205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23782348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610231399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410820007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076318740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59131002426147</t>
+    <t xml:space="preserve">7.50804424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53161096572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23782300949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410772323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59130907058716</t>
   </si>
   <si>
     <t xml:space="preserve">7.69656991958618</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">7.77355051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80025911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826452255249</t>
+    <t xml:space="preserve">7.80025959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826547622681</t>
   </si>
   <si>
     <t xml:space="preserve">7.833251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94950771331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52061367034912</t>
+    <t xml:space="preserve">7.94950866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5206127166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.83010911941528</t>
@@ -1301,43 +1301,43 @@
     <t xml:space="preserve">8.09090423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94165372848511</t>
+    <t xml:space="preserve">7.94165229797363</t>
   </si>
   <si>
     <t xml:space="preserve">7.95343589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04377174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11054134368896</t>
+    <t xml:space="preserve">8.0437707901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11054229736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07126617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86702871322632</t>
+    <t xml:space="preserve">8.07126426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86702966690063</t>
   </si>
   <si>
     <t xml:space="preserve">7.83953523635864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69499826431274</t>
+    <t xml:space="preserve">7.69499921798706</t>
   </si>
   <si>
     <t xml:space="preserve">7.7107105255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64158248901367</t>
+    <t xml:space="preserve">7.64158344268799</t>
   </si>
   <si>
     <t xml:space="preserve">7.67300367355347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61487674713135</t>
+    <t xml:space="preserve">7.61487531661987</t>
   </si>
   <si>
     <t xml:space="preserve">7.65572309494019</t>
@@ -1346,37 +1346,37 @@
     <t xml:space="preserve">7.85524654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59445190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56145858764648</t>
+    <t xml:space="preserve">7.59445142745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415239334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602403640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56146001815796</t>
   </si>
   <si>
     <t xml:space="preserve">7.7531270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83168029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7955470085144</t>
+    <t xml:space="preserve">7.83167934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554510116577</t>
   </si>
   <si>
     <t xml:space="preserve">8.03897953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08750629425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01633358001709</t>
+    <t xml:space="preserve">8.08750534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
     <t xml:space="preserve">7.96942806243896</t>
@@ -1388,22 +1388,22 @@
     <t xml:space="preserve">8.00986480712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07456588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560094833374</t>
+    <t xml:space="preserve">8.07456493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560190200806</t>
   </si>
   <si>
     <t xml:space="preserve">8.14816188812256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21690368652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93222427368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105442047119</t>
+    <t xml:space="preserve">8.21690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93222522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105537414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.85943794250488</t>
@@ -1412,46 +1412,46 @@
     <t xml:space="preserve">7.87884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86752367019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4194769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626140594482</t>
+    <t xml:space="preserve">7.86752462387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41947746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626235961914</t>
   </si>
   <si>
     <t xml:space="preserve">7.43079948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40491962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42594623565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43441867828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84850025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10729885101318</t>
+    <t xml:space="preserve">7.40491914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42594718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59293413162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43441915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8484992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805219650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10729932785034</t>
   </si>
   <si>
     <t xml:space="preserve">6.92613935470581</t>
@@ -1463,46 +1463,46 @@
     <t xml:space="preserve">7.2221417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20111465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1477370262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681222915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58607959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70415782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63783979415894</t>
+    <t xml:space="preserve">7.20111417770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14773654937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26419687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5860800743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70415592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63783884048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.78179597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70739269256592</t>
+    <t xml:space="preserve">7.7073917388916</t>
   </si>
   <si>
     <t xml:space="preserve">7.80282497406006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62975168228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69445133209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886688232422</t>
+    <t xml:space="preserve">7.62975215911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6944522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886735916138</t>
   </si>
   <si>
     <t xml:space="preserve">7.69768714904785</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">7.82223510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83032178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9516339302063</t>
+    <t xml:space="preserve">7.83032131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95163536071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.05353832244873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03089237213135</t>
+    <t xml:space="preserve">8.03089332580566</t>
   </si>
   <si>
     <t xml:space="preserve">7.95001792907715</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19264316558838</t>
+    <t xml:space="preserve">8.19264125823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969192504883</t>
+    <t xml:space="preserve">8.28969097137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.29778099060059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31395530700684</t>
+    <t xml:space="preserve">8.31395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.27756118774414</t>
@@ -1559,46 +1559,46 @@
     <t xml:space="preserve">8.21286010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28564739227295</t>
+    <t xml:space="preserve">8.28564834594727</t>
   </si>
   <si>
     <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794303894043</t>
+    <t xml:space="preserve">8.12794208526611</t>
   </si>
   <si>
     <t xml:space="preserve">8.24521160125732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13198661804199</t>
+    <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
     <t xml:space="preserve">8.06647682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1764669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07941722869873</t>
+    <t xml:space="preserve">8.17646598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07941627502441</t>
   </si>
   <si>
     <t xml:space="preserve">8.14007377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08588790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12389945983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20881748199463</t>
+    <t xml:space="preserve">8.08588600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12389850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20881652832031</t>
   </si>
   <si>
     <t xml:space="preserve">8.2249927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30991172790527</t>
+    <t xml:space="preserve">8.30991077423096</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903633117676</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">8.1885986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33417415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182456970215</t>
+    <t xml:space="preserve">8.33417510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182361602783</t>
   </si>
   <si>
     <t xml:space="preserve">8.3179988861084</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77089977264404</t>
+    <t xml:space="preserve">8.77089881896973</t>
   </si>
   <si>
     <t xml:space="preserve">8.89625549316406</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.95691108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03778743743896</t>
+    <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.04183006286621</t>
@@ -1640,25 +1640,25 @@
     <t xml:space="preserve">9.11866188049316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22379875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32084941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41790008544922</t>
+    <t xml:space="preserve">9.22380065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32085037231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2278413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4178991317749</t>
   </si>
   <si>
     <t xml:space="preserve">9.44620609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61604404449463</t>
+    <t xml:space="preserve">9.61604309082031</t>
   </si>
   <si>
     <t xml:space="preserve">9.48259925842285</t>
@@ -1670,28 +1670,28 @@
     <t xml:space="preserve">9.39768123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30063056945801</t>
+    <t xml:space="preserve">9.30063152313232</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19549369812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1146183013916</t>
+    <t xml:space="preserve">9.1954927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11461925506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.67789268493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05192089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89987325668335</t>
+    <t xml:space="preserve">8.65362930297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05191993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89987421035767</t>
   </si>
   <si>
     <t xml:space="preserve">7.88531732559204</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287532806396</t>
+    <t xml:space="preserve">7.83355665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287485122681</t>
   </si>
   <si>
     <t xml:space="preserve">7.24155235290527</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">7.05715608596802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080936431885</t>
+    <t xml:space="preserve">7.32080984115601</t>
   </si>
   <si>
     <t xml:space="preserve">7.09597682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31595659255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860158920288</t>
+    <t xml:space="preserve">7.31595611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3386025428772</t>
   </si>
   <si>
     <t xml:space="preserve">7.47770690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59093189239502</t>
+    <t xml:space="preserve">7.59093141555786</t>
   </si>
   <si>
     <t xml:space="preserve">7.92251873016357</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">7.76562213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78503131866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98721933364868</t>
+    <t xml:space="preserve">7.78503227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.987220287323</t>
   </si>
   <si>
     <t xml:space="preserve">8.00824737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94516468048096</t>
+    <t xml:space="preserve">7.94516563415527</t>
   </si>
   <si>
     <t xml:space="preserve">7.96619272232056</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">7.88369941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78017997741699</t>
+    <t xml:space="preserve">7.78017902374268</t>
   </si>
   <si>
     <t xml:space="preserve">7.78988456726074</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">7.76238584518433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74297857284546</t>
+    <t xml:space="preserve">7.74297761917114</t>
   </si>
   <si>
     <t xml:space="preserve">7.84164428710938</t>
@@ -1781,55 +1781,55 @@
     <t xml:space="preserve">7.9807505607605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91119623184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474721908569</t>
+    <t xml:space="preserve">7.91119718551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474626541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.85134983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74944734573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889652252197</t>
+    <t xml:space="preserve">7.74944639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889795303345</t>
   </si>
   <si>
     <t xml:space="preserve">7.39036178588867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22537612915039</t>
+    <t xml:space="preserve">7.22537660598755</t>
   </si>
   <si>
     <t xml:space="preserve">7.24963903427124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4421215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49388122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26581478118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890687942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35477685928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01833772659302</t>
+    <t xml:space="preserve">7.44212198257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938817024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26581430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890640258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35477733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01833629608154</t>
   </si>
   <si>
     <t xml:space="preserve">7.05230474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93099164962769</t>
+    <t xml:space="preserve">6.93099069595337</t>
   </si>
   <si>
     <t xml:space="preserve">7.09921169281006</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">7.07980155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99245643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831701278687</t>
+    <t xml:space="preserve">6.99245691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831748962402</t>
   </si>
   <si>
     <t xml:space="preserve">7.27875423431396</t>
@@ -1850,46 +1850,46 @@
     <t xml:space="preserve">7.58446216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62328100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54079008102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92898893356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78826808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88046503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781812667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67342472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57152271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83193874359131</t>
+    <t xml:space="preserve">7.62328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828737258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54078912734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9370756149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92898988723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78826713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88046550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781908035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.673424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57152223587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83193969726562</t>
   </si>
   <si>
     <t xml:space="preserve">7.92575454711914</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80767726898193</t>
+    <t xml:space="preserve">7.80767822265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.00339412689209</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">8.3988733291626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23712348937988</t>
+    <t xml:space="preserve">8.2371244430542</t>
   </si>
   <si>
     <t xml:space="preserve">8.45144176483154</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">8.38674259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18051147460938</t>
+    <t xml:space="preserve">8.26947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18051052093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.26138687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034847259521</t>
+    <t xml:space="preserve">8.35034942626953</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559989929199</t>
@@ -1937,49 +1937,49 @@
     <t xml:space="preserve">8.92051792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08226680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15909862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18740463256836</t>
+    <t xml:space="preserve">9.08226776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15909957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18740558624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07418060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445434570312</t>
+    <t xml:space="preserve">9.07418155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17931747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23188591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34915542602539</t>
+    <t xml:space="preserve">9.2318868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34915637969971</t>
   </si>
   <si>
     <t xml:space="preserve">9.38150691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32489395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828193664551</t>
+    <t xml:space="preserve">9.3248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828098297119</t>
   </si>
   <si>
     <t xml:space="preserve">9.36533069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5917797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40576839447021</t>
+    <t xml:space="preserve">9.59178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4057674407959</t>
   </si>
   <si>
     <t xml:space="preserve">9.59582424163818</t>
@@ -1988,43 +1988,43 @@
     <t xml:space="preserve">9.65647983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56751918792725</t>
+    <t xml:space="preserve">9.56751823425293</t>
   </si>
   <si>
     <t xml:space="preserve">9.45833683013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46642398834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47451114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81014251708984</t>
+    <t xml:space="preserve">9.46642303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47451210021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">10.0163745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83036136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84943866729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79552745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629379272461</t>
+    <t xml:space="preserve">9.83036231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.036060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84943962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7955265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629474639893</t>
   </si>
   <si>
     <t xml:space="preserve">9.79967308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73331832885742</t>
+    <t xml:space="preserve">9.73331928253174</t>
   </si>
   <si>
     <t xml:space="preserve">9.47619724273682</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">9.40569686889648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18589687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50162029266357</t>
+    <t xml:space="preserve">9.18589782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50161933898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.44356155395508</t>
@@ -2054,22 +2054,22 @@
     <t xml:space="preserve">8.12506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03050708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22625255584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23620510101318</t>
+    <t xml:space="preserve">8.0305061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22625064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2362060546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.11842632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2113208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09520149230957</t>
+    <t xml:space="preserve">8.21132183074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
     <t xml:space="preserve">8.00728321075439</t>
@@ -2078,25 +2078,25 @@
     <t xml:space="preserve">8.0869083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0388011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67385339736938</t>
+    <t xml:space="preserve">8.03880214691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385292053223</t>
   </si>
   <si>
     <t xml:space="preserve">7.69376087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670240402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77172660827637</t>
+    <t xml:space="preserve">7.59091138839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670335769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77172565460205</t>
   </si>
   <si>
     <t xml:space="preserve">7.70868921279907</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70039510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73357248306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58925199508667</t>
+    <t xml:space="preserve">7.7003960609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73357200622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58925104141235</t>
   </si>
   <si>
     <t xml:space="preserve">7.62574672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50299167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109834671021</t>
+    <t xml:space="preserve">7.50299119949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109786987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.72859573364258</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">7.82978534698486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9193639755249</t>
+    <t xml:space="preserve">7.91936302185059</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17814350128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2196159362793</t>
+    <t xml:space="preserve">7.96249389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17814445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21961688995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.60529899597168</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">8.87901020050049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86656951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54723930358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38550090789795</t>
+    <t xml:space="preserve">8.86656856536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54724025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38549995422363</t>
   </si>
   <si>
     <t xml:space="preserve">8.55553340911865</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">8.29094696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3232946395874</t>
+    <t xml:space="preserve">8.32329368591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.05704879760742</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">7.86462116241455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45820236206055</t>
+    <t xml:space="preserve">7.36530733108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45820188522339</t>
   </si>
   <si>
     <t xml:space="preserve">7.5726637840271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39184808731079</t>
+    <t xml:space="preserve">7.39184856414795</t>
   </si>
   <si>
     <t xml:space="preserve">7.22098684310913</t>
@@ -2225,28 +2225,28 @@
     <t xml:space="preserve">7.38355445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38853120803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191165924072</t>
+    <t xml:space="preserve">7.38853073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73191261291504</t>
   </si>
   <si>
     <t xml:space="preserve">7.41839027404785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25084590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42502593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06173706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388282775879</t>
+    <t xml:space="preserve">7.25084543228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42502546310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06173658370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17951583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388187408447</t>
   </si>
   <si>
     <t xml:space="preserve">7.25914001464844</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">7.94258737564087</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15989780426025</t>
+    <t xml:space="preserve">8.15989875793457</t>
   </si>
   <si>
     <t xml:space="preserve">8.18975639343262</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">8.09852027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76343154907227</t>
+    <t xml:space="preserve">7.76343202590942</t>
   </si>
   <si>
     <t xml:space="preserve">7.79660797119141</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">8.03216648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98903608322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84969186782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86130332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581172943115</t>
+    <t xml:space="preserve">7.98903512954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84969091415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86130380630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581077575684</t>
   </si>
   <si>
     <t xml:space="preserve">7.76840829849243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90443468093872</t>
+    <t xml:space="preserve">7.9044337272644</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
@@ -2339,73 +2339,73 @@
     <t xml:space="preserve">7.65394735336304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72361850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89614057540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1267204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95917510986328</t>
+    <t xml:space="preserve">7.72361946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89613962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12671947479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
     <t xml:space="preserve">8.17482662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33988380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34402942657471</t>
+    <t xml:space="preserve">8.33988285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.5596809387207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46014881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44770812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6260347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47673892974854</t>
+    <t xml:space="preserve">8.46014976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44770908355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62603569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47673797607422</t>
   </si>
   <si>
     <t xml:space="preserve">8.37720775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60944652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95780658721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99927711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1651611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13198471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23566436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48449325561523</t>
+    <t xml:space="preserve">8.60944747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95780563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16516208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13198566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23566246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48449230194092</t>
   </si>
   <si>
     <t xml:space="preserve">9.54255199432373</t>
@@ -2417,19 +2417,19 @@
     <t xml:space="preserve">9.50937461853027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42643165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31445789337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057918548584</t>
+    <t xml:space="preserve">9.42643070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3144588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
     <t xml:space="preserve">9.38496017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51766967773438</t>
+    <t xml:space="preserve">9.51766872406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.73746681213379</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">9.70014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57158184051514</t>
+    <t xml:space="preserve">9.57158088684082</t>
   </si>
   <si>
     <t xml:space="preserve">9.33934116363525</t>
@@ -2453,28 +2453,28 @@
     <t xml:space="preserve">9.35178279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38910675048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19833946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31031322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078109741211</t>
+    <t xml:space="preserve">9.3891077041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19834041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31031227111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
     <t xml:space="preserve">9.26884078979492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11539649963379</t>
+    <t xml:space="preserve">9.11539745330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.12369060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04074954986572</t>
+    <t xml:space="preserve">9.04074764251709</t>
   </si>
   <si>
     <t xml:space="preserve">9.06148433685303</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">9.01586532592773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05318927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93292331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12783813476562</t>
+    <t xml:space="preserve">9.05319023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93292427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12783908843994</t>
   </si>
   <si>
     <t xml:space="preserve">8.88315773010254</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">8.82509803771973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09880828857422</t>
+    <t xml:space="preserve">9.09880924224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24395751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58817005157471</t>
+    <t xml:space="preserve">9.58817100524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.29372406005859</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">9.15686702728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21492767333984</t>
+    <t xml:space="preserve">9.21492862701416</t>
   </si>
   <si>
     <t xml:space="preserve">9.11954402923584</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">9.08221912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09466171264648</t>
+    <t xml:space="preserve">9.09466075897217</t>
   </si>
   <si>
     <t xml:space="preserve">9.11124992370605</t>
@@ -2546,34 +2546,34 @@
     <t xml:space="preserve">8.77118396759033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97024631500244</t>
+    <t xml:space="preserve">8.97024726867676</t>
   </si>
   <si>
     <t xml:space="preserve">9.27713584899902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68770122528076</t>
+    <t xml:space="preserve">9.68770217895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.1444263458252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08636569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05733776092529</t>
+    <t xml:space="preserve">9.08636665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05733680725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.99098205566406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28128051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89559841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25279331207275</t>
+    <t xml:space="preserve">9.28128147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25279426574707</t>
   </si>
   <si>
     <t xml:space="preserve">8.14994430541992</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">7.34042501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35867118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73328399658203</t>
+    <t xml:space="preserve">7.35867166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327211380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73328447341919</t>
   </si>
   <si>
     <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53256225585938</t>
+    <t xml:space="preserve">6.53256273269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.73797225952148</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">6.2024507522583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1908392906189</t>
+    <t xml:space="preserve">6.19083976745605</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">6.71503639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33047103881836</t>
+    <t xml:space="preserve">7.3304705619812</t>
   </si>
   <si>
     <t xml:space="preserve">6.85769748687744</t>
@@ -2642,34 +2642,34 @@
     <t xml:space="preserve">6.87594556808472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09159660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4233660697937</t>
+    <t xml:space="preserve">6.87096881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0915961265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42336702346802</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8331036567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144378662109</t>
+    <t xml:space="preserve">7.83310270309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144474029541</t>
   </si>
   <si>
     <t xml:space="preserve">7.92931747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32715320587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21601009368896</t>
+    <t xml:space="preserve">7.32715368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21600961685181</t>
   </si>
   <si>
     <t xml:space="preserve">7.24255228042603</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">6.76977825164795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26411724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067649841309</t>
+    <t xml:space="preserve">7.26411771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067602157593</t>
   </si>
   <si>
     <t xml:space="preserve">7.88286828994751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07363700866699</t>
+    <t xml:space="preserve">8.07363796234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.46844387054443</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897769927979</t>
+    <t xml:space="preserve">8.7089786529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22956848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48503112792969</t>
+    <t xml:space="preserve">8.22956943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
     <t xml:space="preserve">8.294264793396</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">8.75874423980713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91218662261963</t>
+    <t xml:space="preserve">8.91218566894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.0034236907959</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.34763622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34348964691162</t>
+    <t xml:space="preserve">9.34349060058594</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">10.0402059555054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973299026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94897079467773</t>
+    <t xml:space="preserve">10.2973289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94897174835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0443544387817</t>
@@ -2771,28 +2771,28 @@
     <t xml:space="preserve">10.2848873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87432193756104</t>
+    <t xml:space="preserve">9.87432098388672</t>
   </si>
   <si>
     <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065089225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9655590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95311737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3595361709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3512420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7286310195923</t>
+    <t xml:space="preserve">10.0650901794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96555995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95311641693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3595371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3512411117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7286319732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.6996011734009</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">10.4093017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4632148742676</t>
+    <t xml:space="preserve">10.4632139205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.4010076522827</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">10.6415405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8323097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659540176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9318408966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.778395652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6332473754883</t>
+    <t xml:space="preserve">10.8323106765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7659559249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9318399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7783966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.633246421814</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042175292969</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">10.1812086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.53786277771</t>
+    <t xml:space="preserve">10.5378637313843</t>
   </si>
   <si>
     <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553886413574</t>
+    <t xml:space="preserve">10.3553895950317</t>
   </si>
   <si>
     <t xml:space="preserve">10.230975151062</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">11.064549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8654870986938</t>
+    <t xml:space="preserve">10.8654880523682</t>
   </si>
   <si>
     <t xml:space="preserve">10.8240156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.612512588501</t>
+    <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
     <t xml:space="preserve">10.6000699996948</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">10.7949857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6664237976074</t>
+    <t xml:space="preserve">10.6664257049561</t>
   </si>
   <si>
     <t xml:space="preserve">10.5337162017822</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">10.0733842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4341840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2392692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3180637359619</t>
+    <t xml:space="preserve">10.4341850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2392702102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180646896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1936502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0319128036499</t>
+    <t xml:space="preserve">10.1936511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0319137573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.81626224517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83285045623779</t>
+    <t xml:space="preserve">9.83285140991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.46790313720703</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">9.82040977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0277671813965</t>
+    <t xml:space="preserve">10.0277662277222</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335178375244</t>
+    <t xml:space="preserve">9.90335083007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.1604738235474</t>
@@ -2978,46 +2978,46 @@
     <t xml:space="preserve">10.1521787643433</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99044227600098</t>
+    <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1065616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59646320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53425693511963</t>
+    <t xml:space="preserve">9.96141147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59646415710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53425598144531</t>
   </si>
   <si>
     <t xml:space="preserve">9.67111206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74576091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970653533936</t>
+    <t xml:space="preserve">9.74575996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970558166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3844194412231</t>
+    <t xml:space="preserve">10.3844203948975</t>
   </si>
   <si>
     <t xml:space="preserve">10.347095489502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3346529006958</t>
+    <t xml:space="preserve">10.3346538543701</t>
   </si>
   <si>
     <t xml:space="preserve">9.94482231140137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272964477539</t>
+    <t xml:space="preserve">10.1272974014282</t>
   </si>
   <si>
     <t xml:space="preserve">10.2682991027832</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">10.9733114242554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.898663520813</t>
+    <t xml:space="preserve">10.8986644744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.8364553451538</t>
@@ -3065,64 +3065,64 @@
     <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8447504043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9774580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350498199463</t>
+    <t xml:space="preserve">10.8447513580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9774589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350507736206</t>
   </si>
   <si>
     <t xml:space="preserve">11.1018733978271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1143131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35484790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1474914550781</t>
+    <t xml:space="preserve">11.1143140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1474905014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3921728134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2843465805054</t>
+    <t xml:space="preserve">11.3921718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2843456268311</t>
   </si>
   <si>
     <t xml:space="preserve">11.6119699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.520733833313</t>
+    <t xml:space="preserve">11.5207328796387</t>
   </si>
   <si>
     <t xml:space="preserve">11.4792623519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.350700378418</t>
+    <t xml:space="preserve">11.3507013320923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1889629364014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1682262420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1226091384888</t>
+    <t xml:space="preserve">11.1682271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1226081848145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0355186462402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452192306519</t>
+    <t xml:space="preserve">10.9442825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452201843262</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">12.1096258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3999242782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1303615570068</t>
+    <t xml:space="preserve">12.3999261856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1303625106812</t>
   </si>
   <si>
     <t xml:space="preserve">12.4455442428589</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.358452796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1718339920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3169822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1842746734619</t>
+    <t xml:space="preserve">12.3584537506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1718330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3169832229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1842737197876</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3377180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.192569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0847434997559</t>
+    <t xml:space="preserve">12.3377170562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1925687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0847425460815</t>
   </si>
   <si>
     <t xml:space="preserve">12.2879524230957</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">12.0349779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9230051040649</t>
+    <t xml:space="preserve">11.9230060577393</t>
   </si>
   <si>
     <t xml:space="preserve">11.9810638427734</t>
@@ -3206,16 +3206,16 @@
     <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3543071746826</t>
+    <t xml:space="preserve">12.3543062210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.1759805679321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.972770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9769191741943</t>
+    <t xml:space="preserve">11.9727716445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.97691822052</t>
   </si>
   <si>
     <t xml:space="preserve">11.9437408447266</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">12.1179208755493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.78200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5580587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5539112091064</t>
+    <t xml:space="preserve">11.7820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5580577850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5539102554321</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5746469497681</t>
+    <t xml:space="preserve">11.5746459960938</t>
   </si>
   <si>
     <t xml:space="preserve">11.4834089279175</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7405309677124</t>
+    <t xml:space="preserve">11.7405319213867</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981227874756</t>
+    <t xml:space="preserve">11.7985916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981237411499</t>
   </si>
   <si>
     <t xml:space="preserve">11.9520349502563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.545615196228</t>
+    <t xml:space="preserve">11.5456161499023</t>
   </si>
   <si>
     <t xml:space="preserve">11.5331745147705</t>
@@ -3284,28 +3284,28 @@
     <t xml:space="preserve">11.4751148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6783237457275</t>
+    <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
     <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064159393311</t>
+    <t xml:space="preserve">11.9064168930054</t>
   </si>
   <si>
     <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142412185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6949138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8732385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6617364883423</t>
+    <t xml:space="preserve">12.0142421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6949129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8732395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6617374420166</t>
   </si>
   <si>
     <t xml:space="preserve">11.7322378158569</t>
@@ -3323,25 +3323,25 @@
     <t xml:space="preserve">11.7654142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1640815734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2055511474609</t>
+    <t xml:space="preserve">11.5787935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.164080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2055521011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.3050832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4129085540771</t>
+    <t xml:space="preserve">11.4129076004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.4336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3299646377563</t>
+    <t xml:space="preserve">11.3299655914307</t>
   </si>
   <si>
     <t xml:space="preserve">11.3631420135498</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">11.3382596969604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3880243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3714370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4917030334473</t>
+    <t xml:space="preserve">11.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714380264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4917020797729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5124397277832</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">11.6451473236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5622034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248804092407</t>
+    <t xml:space="preserve">11.5622043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.524881362915</t>
   </si>
   <si>
     <t xml:space="preserve">11.5953807830811</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">11.9312992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8607988357544</t>
+    <t xml:space="preserve">11.8607997894287</t>
   </si>
   <si>
     <t xml:space="preserve">11.6410007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.026683807373</t>
+    <t xml:space="preserve">11.8068857192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0266828536987</t>
   </si>
   <si>
     <t xml:space="preserve">12.1013317108154</t>
@@ -3416,16 +3416,16 @@
     <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391254425049</t>
+    <t xml:space="preserve">12.0391263961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690929412842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220664978027</t>
+    <t xml:space="preserve">11.7778558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220674514771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2215986251831</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7773151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8975820541382</t>
+    <t xml:space="preserve">12.7773132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8975811004639</t>
   </si>
   <si>
     <t xml:space="preserve">13.2293519973755</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">13.3827962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532957077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5942993164062</t>
+    <t xml:space="preserve">13.453296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5942983627319</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698848724365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201202392578</t>
+    <t xml:space="preserve">13.4201211929321</t>
   </si>
   <si>
     <t xml:space="preserve">13.3496179580688</t>
@@ -3476,46 +3476,46 @@
     <t xml:space="preserve">13.4781799316406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2169103622437</t>
+    <t xml:space="preserve">13.216911315918</t>
   </si>
   <si>
     <t xml:space="preserve">13.051025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1588497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1837339401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625303268433</t>
+    <t xml:space="preserve">13.1588487625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1837348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625293731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8644046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8685512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607269287109</t>
+    <t xml:space="preserve">12.8644037246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8685522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9349050521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312273025513</t>
+    <t xml:space="preserve">12.9349060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312282562256</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482833862305</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">13.237645149231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1215267181396</t>
+    <t xml:space="preserve">13.1215257644653</t>
   </si>
   <si>
     <t xml:space="preserve">13.0095539093018</t>
@@ -3545,19 +3545,19 @@
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9431991577148</t>
+    <t xml:space="preserve">12.9431982040405</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9971132278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7690210342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.644606590271</t>
+    <t xml:space="preserve">12.9971122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7690200805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6446056365967</t>
   </si>
   <si>
     <t xml:space="preserve">12.9722309112549</t>
@@ -3575,16 +3575,16 @@
     <t xml:space="preserve">12.9929647445679</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2044696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1173782348633</t>
+    <t xml:space="preserve">13.2044687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1173791885376</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850685119629</t>
+    <t xml:space="preserve">13.7850694656372</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523590087891</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">13.7975091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9219226837158</t>
+    <t xml:space="preserve">13.9219236373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.9799823760986</t>
@@ -3608,10 +3608,10 @@
     <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7270059585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6979780197144</t>
+    <t xml:space="preserve">13.7270069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69797706604</t>
   </si>
   <si>
     <t xml:space="preserve">14.0048656463623</t>
@@ -3620,22 +3620,22 @@
     <t xml:space="preserve">13.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173072814941</t>
+    <t xml:space="preserve">14.0878076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173063278198</t>
   </si>
   <si>
     <t xml:space="preserve">14.224663734436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3324909210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583089828491</t>
+    <t xml:space="preserve">14.3324899673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583099365234</t>
   </si>
   <si>
     <t xml:space="preserve">14.2951650619507</t>
@@ -3644,13 +3644,13 @@
     <t xml:space="preserve">14.3532257080078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2619867324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3076066970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163686752319</t>
+    <t xml:space="preserve">14.2619876861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3076057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163677215576</t>
   </si>
   <si>
     <t xml:space="preserve">14.12513256073</t>
@@ -3668,43 +3668,43 @@
     <t xml:space="preserve">13.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819042205811</t>
+    <t xml:space="preserve">13.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4359970092773</t>
+    <t xml:space="preserve">13.2605028152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.435996055603</t>
   </si>
   <si>
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5515661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6457328796387</t>
+    <t xml:space="preserve">13.1834564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5515670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9068365097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6457347869873</t>
   </si>
   <si>
     <t xml:space="preserve">13.4488382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4188756942749</t>
+    <t xml:space="preserve">13.4188766479492</t>
   </si>
   <si>
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445571899414</t>
+    <t xml:space="preserve">13.4445581436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258846282959</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">12.9523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2433815002441</t>
+    <t xml:space="preserve">12.9095144271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2433824539185</t>
   </si>
   <si>
     <t xml:space="preserve">13.2519416809082</t>
@@ -3737,25 +3737,25 @@
     <t xml:space="preserve">13.4531183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.487361907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6842565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3589506149292</t>
+    <t xml:space="preserve">13.4873609542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6842575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3589496612549</t>
   </si>
   <si>
     <t xml:space="preserve">13.0122423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8511905670166</t>
+    <t xml:space="preserve">13.7741451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8511915206909</t>
   </si>
   <si>
     <t xml:space="preserve">13.5301647186279</t>
@@ -3767,19 +3767,19 @@
     <t xml:space="preserve">13.2861862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0293655395508</t>
+    <t xml:space="preserve">13.0293645858765</t>
   </si>
   <si>
     <t xml:space="preserve">13.1920175552368</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1320934295654</t>
+    <t xml:space="preserve">13.1320924758911</t>
   </si>
   <si>
     <t xml:space="preserve">12.7597026824951</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3616313934326</t>
+    <t xml:space="preserve">12.3616304397583</t>
   </si>
   <si>
     <t xml:space="preserve">12.5499658584595</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.85387134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009532928467</t>
+    <t xml:space="preserve">12.6740961074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8538703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.900954246521</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254600524902</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">12.7682638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8495903015137</t>
+    <t xml:space="preserve">12.849591255188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0550470352173</t>
@@ -3830,28 +3830,28 @@
     <t xml:space="preserve">13.4103155136108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2776250839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4301166534424</t>
+    <t xml:space="preserve">13.277624130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4301156997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768249511719</t>
+    <t xml:space="preserve">12.7768239974976</t>
   </si>
   <si>
     <t xml:space="preserve">12.0234842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0363254547119</t>
+    <t xml:space="preserve">12.0363264083862</t>
   </si>
   <si>
     <t xml:space="preserve">11.8351488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576778411865</t>
+    <t xml:space="preserve">10.9576787948608</t>
   </si>
   <si>
     <t xml:space="preserve">10.8720712661743</t>
@@ -3869,19 +3869,19 @@
     <t xml:space="preserve">11.5954494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8265886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950729370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157232284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9892406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106430053711</t>
+    <t xml:space="preserve">11.826587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9892416000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0106420516968</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277652740479</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">11.9849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8479909896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9507179260254</t>
+    <t xml:space="preserve">11.8479900360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9507188796997</t>
   </si>
   <si>
     <t xml:space="preserve">12.3145475387573</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102674484253</t>
+    <t xml:space="preserve">12.310266494751</t>
   </si>
   <si>
     <t xml:space="preserve">12.2631826400757</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188276290894</t>
+    <t xml:space="preserve">12.1262121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188285827637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203798294067</t>
@@ -3935,19 +3935,19 @@
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834093093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0705680847168</t>
+    <t xml:space="preserve">12.0834083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0705671310425</t>
   </si>
   <si>
     <t xml:space="preserve">11.8651113510132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4798812866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2444620132446</t>
+    <t xml:space="preserve">11.4798803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2444610595703</t>
   </si>
   <si>
     <t xml:space="preserve">11.2530221939087</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">11.0775270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090368270874</t>
+    <t xml:space="preserve">11.0903692245483</t>
   </si>
   <si>
     <t xml:space="preserve">10.5724487304688</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4868402481079</t>
+    <t xml:space="preserve">10.4868412017822</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771043777466</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">10.6109714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8292675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035860061646</t>
+    <t xml:space="preserve">10.8292684555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035850524902</t>
   </si>
   <si>
     <t xml:space="preserve">10.7693433761597</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">11.1668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1403951644897</t>
+    <t xml:space="preserve">11.1403942108154</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158653259277</t>
+    <t xml:space="preserve">11.5158643722534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368246078491</t>
+    <t xml:space="preserve">10.6368255615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.62968254089355</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.13053035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74453163146973</t>
+    <t xml:space="preserve">9.74453258514404</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">10.1818447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4645509719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191568374634</t>
+    <t xml:space="preserve">10.4645500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191558837891</t>
   </si>
   <si>
     <t xml:space="preserve">10.4689674377441</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">10.2171812057495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7384214401245</t>
+    <t xml:space="preserve">10.7384223937988</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3585367202759</t>
+    <t xml:space="preserve">10.3585357666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.83287906646729</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758285522461</t>
+    <t xml:space="preserve">10.0758295059204</t>
   </si>
   <si>
     <t xml:space="preserve">10.0007352828979</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">10.999041557312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8841915130615</t>
+    <t xml:space="preserve">10.8841924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.8267679214478</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">10.5573139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9062786102295</t>
+    <t xml:space="preserve">10.9062795639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902067184448</t>
+    <t xml:space="preserve">10.9902076721191</t>
   </si>
   <si>
     <t xml:space="preserve">10.7781772613525</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">10.6544942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1465063095093</t>
+    <t xml:space="preserve">10.146505355835</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
@@ -4181,10 +4181,10 @@
     <t xml:space="preserve">10.0051527023315</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93447685241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45299053192139</t>
+    <t xml:space="preserve">9.93447589874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4529914855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.58109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59876155853271</t>
+    <t xml:space="preserve">9.59876251220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797750473022</t>
+    <t xml:space="preserve">10.8797740936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.919529914856</t>
@@ -4238,10 +4238,10 @@
     <t xml:space="preserve">10.8046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215036392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9372005462646</t>
+    <t xml:space="preserve">11.3215045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9371995925903</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259210586548</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.188985824585</t>
+    <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
     <t xml:space="preserve">11.8471603393555</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">10.9239473342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.246410369873</t>
+    <t xml:space="preserve">11.2464094161987</t>
   </si>
   <si>
     <t xml:space="preserve">11.2331581115723</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">12.1961269378662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3949041366577</t>
+    <t xml:space="preserve">12.3949031829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.1607885360718</t>
@@ -4325,16 +4325,16 @@
     <t xml:space="preserve">12.6246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908617019653</t>
+    <t xml:space="preserve">12.6908626556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.7527046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8277988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.920560836792</t>
+    <t xml:space="preserve">12.8277978897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9205617904663</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514827728271</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">13.0354108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2518577575684</t>
+    <t xml:space="preserve">13.2518587112427</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2827796936035</t>
+    <t xml:space="preserve">13.2827787399292</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
@@ -4370,19 +4370,19 @@
     <t xml:space="preserve">13.6405782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9144506454468</t>
+    <t xml:space="preserve">13.6494131088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9144515991211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5522336959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6008243560791</t>
+    <t xml:space="preserve">13.5522327423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6008234024048</t>
   </si>
   <si>
     <t xml:space="preserve">13.7465934753418</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188690185547</t>
+    <t xml:space="preserve">13.9188680648804</t>
   </si>
   <si>
     <t xml:space="preserve">13.1414251327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3534545898438</t>
+    <t xml:space="preserve">13.3534555435181</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">13.5345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5831537246704</t>
+    <t xml:space="preserve">13.5831546783447</t>
   </si>
   <si>
     <t xml:space="preserve">13.834939956665</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">14.1883230209351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5947132110596</t>
+    <t xml:space="preserve">14.5947122573853</t>
   </si>
   <si>
     <t xml:space="preserve">14.4710273742676</t>
@@ -4439,19 +4439,19 @@
     <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8685836791992</t>
+    <t xml:space="preserve">14.8685846328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7669868469238</t>
+    <t xml:space="preserve">14.7669878005981</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095623016357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7934913635254</t>
+    <t xml:space="preserve">14.7934904098511</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">14.5814609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9790163040161</t>
+    <t xml:space="preserve">14.9790172576904</t>
   </si>
   <si>
     <t xml:space="preserve">14.9392614364624</t>
@@ -4499,13 +4499,13 @@
     <t xml:space="preserve">14.8553333282471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0099382400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6918926239014</t>
+    <t xml:space="preserve">15.009937286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6609725952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6918916702271</t>
   </si>
   <si>
     <t xml:space="preserve">14.568208694458</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">14.9701814651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7714033126831</t>
+    <t xml:space="preserve">14.7714042663574</t>
   </si>
   <si>
     <t xml:space="preserve">14.6433038711548</t>
@@ -4559,10 +4559,10 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402992248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4523296356201</t>
+    <t xml:space="preserve">12.2402982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4523286819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.502613067627</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500919342041</t>
+    <t xml:space="preserve">12.5009183883667</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">12.5141706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0795841217041</t>
+    <t xml:space="preserve">13.0795831680298</t>
   </si>
   <si>
     <t xml:space="preserve">12.5848474502563</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">12.5406742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1298666000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7588148117065</t>
+    <t xml:space="preserve">12.1298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7588157653809</t>
   </si>
   <si>
     <t xml:space="preserve">12.1121988296509</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343809127808</t>
+    <t xml:space="preserve">11.0343799591064</t>
   </si>
   <si>
     <t xml:space="preserve">11.2199058532715</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.0653009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2950000762939</t>
+    <t xml:space="preserve">11.2949991226196</t>
   </si>
   <si>
     <t xml:space="preserve">11.0873880386353</t>
@@ -6264,6 +6264,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.2099990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3649997711182</t>
   </si>
 </sst>
 </file>
@@ -71238,7 +71241,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.652337963</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>1158608</v>
@@ -71259,6 +71262,32 @@
         <v>2083</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6497800926</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>848562</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>18.4300003051758</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>18.2649993896484</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>18.2900009155273</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>18.3649997711182</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2084</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="2085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="2086">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,28 +44,28 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048845291138</t>
+    <t xml:space="preserve">5.32048797607422</t>
   </si>
   <si>
     <t xml:space="preserve">5.17209386825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13951969146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26257944107056</t>
+    <t xml:space="preserve">5.13951921463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2625789642334</t>
   </si>
   <si>
     <t xml:space="preserve">5.1322808265686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26619815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3132495880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381093978882</t>
+    <t xml:space="preserve">5.266197681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31325006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">5.0454158782959</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">5.07437133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8210129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96578931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05265474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21190738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04903507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14675855636597</t>
+    <t xml:space="preserve">4.65814113616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101345062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96578979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05265378952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21190643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0490345954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14675807952881</t>
   </si>
   <si>
     <t xml:space="preserve">5.16485548019409</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138784408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56765747070312</t>
+    <t xml:space="preserve">4.74138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56765794754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.34325647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4844126701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213520050049</t>
+    <t xml:space="preserve">4.45545673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441171646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213472366333</t>
   </si>
   <si>
     <t xml:space="preserve">4.78482055664062</t>
@@ -137,58 +137,58 @@
     <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71243286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187294006348</t>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71243238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88616323471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00922250747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09246778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332632064819</t>
+    <t xml:space="preserve">4.88616275787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00922155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09246730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332489013672</t>
   </si>
   <si>
     <t xml:space="preserve">5.16847467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95493173599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8427300453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713199615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08884906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00560188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99112510681152</t>
+    <t xml:space="preserve">4.95493030548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84273052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120088577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713247299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00560235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99112558364868</t>
   </si>
   <si>
     <t xml:space="preserve">5.19019079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362350463867</t>
+    <t xml:space="preserve">5.23362302780151</t>
   </si>
   <si>
     <t xml:space="preserve">5.35668230056763</t>
@@ -203,64 +203,64 @@
     <t xml:space="preserve">4.98026752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94769239425659</t>
+    <t xml:space="preserve">4.94769287109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.9730281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90787982940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369928359985</t>
+    <t xml:space="preserve">4.90787935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369976043701</t>
   </si>
   <si>
     <t xml:space="preserve">5.11418390274048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.121422290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406362533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28287506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27161026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.230309009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16647911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33168649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.391761302948</t>
+    <t xml:space="preserve">5.12142324447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544111251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.282874584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27161073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23030948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16647958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33168601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39176177978516</t>
   </si>
   <si>
     <t xml:space="preserve">5.2641019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25659227371216</t>
+    <t xml:space="preserve">5.25659275054932</t>
   </si>
   <si>
     <t xml:space="preserve">5.05759239196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09889459609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96747970581055</t>
+    <t xml:space="preserve">5.0988941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96747922897339</t>
   </si>
   <si>
     <t xml:space="preserve">4.88863039016724</t>
@@ -272,46 +272,46 @@
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70089530944824</t>
+    <t xml:space="preserve">4.76472520828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7008957862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.96372509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90364933013916</t>
+    <t xml:space="preserve">4.903648853302</t>
   </si>
   <si>
     <t xml:space="preserve">4.90740394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7759895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73844242095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84357404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91866874694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98625326156616</t>
+    <t xml:space="preserve">4.77598905563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73844289779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84357452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9186692237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98625230789185</t>
   </si>
   <si>
     <t xml:space="preserve">4.97874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01629018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92617797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95246076583862</t>
+    <t xml:space="preserve">5.01629066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92617750167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95246028900146</t>
   </si>
   <si>
     <t xml:space="preserve">4.97123432159424</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">4.62204647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56197118759155</t>
+    <t xml:space="preserve">4.56197071075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.44182014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4493293762207</t>
+    <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.45683908462524</t>
@@ -344,52 +344,52 @@
     <t xml:space="preserve">4.56948041915894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7534613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093271255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97498893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063205718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13017892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39676380157471</t>
+    <t xml:space="preserve">4.75346088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093318939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80602693557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97498941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39676427841187</t>
   </si>
   <si>
     <t xml:space="preserve">4.33668851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39300966262817</t>
+    <t xml:space="preserve">4.39300870895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.17523574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10014152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87485909461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2653489112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31791543960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1902551651001</t>
+    <t xml:space="preserve">4.10014200210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87485861778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244360923767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31791496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19025421142578</t>
   </si>
   <si>
     <t xml:space="preserve">4.20151853561401</t>
@@ -407,55 +407,55 @@
     <t xml:space="preserve">4.24657583236694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27661371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638690948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9311797618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750066757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83731174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9386899471283</t>
+    <t xml:space="preserve">4.27661323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638738632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93118047714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9875009059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8373122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93868899345398</t>
   </si>
   <si>
     <t xml:space="preserve">3.97623634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93493485450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97248148918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746302604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619846343994</t>
+    <t xml:space="preserve">3.93493437767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9724817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619917869568</t>
   </si>
   <si>
     <t xml:space="preserve">3.99876427650452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8298032283783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604813575745</t>
+    <t xml:space="preserve">3.82980298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604837417603</t>
   </si>
   <si>
     <t xml:space="preserve">3.77348232269287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75470876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133008956909</t>
+    <t xml:space="preserve">3.7547082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.07010412216187</t>
@@ -470,28 +470,28 @@
     <t xml:space="preserve">4.05884027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09263181686401</t>
+    <t xml:space="preserve">4.09263277053833</t>
   </si>
   <si>
     <t xml:space="preserve">4.1376895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12267017364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0550856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91240644454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229375839233</t>
+    <t xml:space="preserve">4.12266969680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05508518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229399681091</t>
   </si>
   <si>
     <t xml:space="preserve">3.81478404998779</t>
@@ -500,61 +500,61 @@
     <t xml:space="preserve">3.9048969745636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90114188194275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81102919578552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88612365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738774299622</t>
+    <t xml:space="preserve">3.90114235877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987851142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81102895736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88612389564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738726615906</t>
   </si>
   <si>
     <t xml:space="preserve">3.88236904144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87110495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233163833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6120297908783</t>
+    <t xml:space="preserve">3.8711051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233092308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850150108337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221823692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61203026771545</t>
   </si>
   <si>
     <t xml:space="preserve">3.59550881385803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79600977897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96121764183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999143600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02504777908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96497273445129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01753807067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08887815475464</t>
+    <t xml:space="preserve">3.79601001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96121835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999119758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02504825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96497201919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01753759384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08887767791748</t>
   </si>
   <si>
     <t xml:space="preserve">4.14519834518433</t>
@@ -563,52 +563,52 @@
     <t xml:space="preserve">3.99501013755798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92742514610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355736732483</t>
+    <t xml:space="preserve">3.92742586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355760574341</t>
   </si>
   <si>
     <t xml:space="preserve">3.78474640846252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80727529525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225564002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056539535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60452008247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5444450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843760490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54144191741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4708526134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799910545349</t>
+    <t xml:space="preserve">3.80727481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225635528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6405656337738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60452079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54444479942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843712806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54144167900085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47085285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799958229065</t>
   </si>
   <si>
     <t xml:space="preserve">3.66459584236145</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910147666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857606887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144325256348</t>
+    <t xml:space="preserve">3.66910195350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748651504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73968935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857654571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144420623779</t>
   </si>
   <si>
     <t xml:space="preserve">4.1038966178894</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006624221802</t>
+    <t xml:space="preserve">4.04006671905518</t>
   </si>
   <si>
     <t xml:space="preserve">4.11516046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00251913070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07761383056641</t>
+    <t xml:space="preserve">4.0025200843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07761287689209</t>
   </si>
   <si>
     <t xml:space="preserve">4.16772699356079</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">4.15270757675171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14895343780518</t>
+    <t xml:space="preserve">4.14895296096802</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512306213379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18274593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22029209136963</t>
+    <t xml:space="preserve">4.18274545669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22029256820679</t>
   </si>
   <si>
     <t xml:space="preserve">4.23906660079956</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06259441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03631210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13393449783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28787708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706541061401</t>
+    <t xml:space="preserve">4.12642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06259489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03631162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13393402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28787755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30289602279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706588745117</t>
   </si>
   <si>
     <t xml:space="preserve">4.6933856010437</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">4.72342348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085790634155</t>
+    <t xml:space="preserve">4.67085742950439</t>
   </si>
   <si>
     <t xml:space="preserve">4.80978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83982038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81353616714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79851770401001</t>
+    <t xml:space="preserve">4.83981990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81353664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79851722717285</t>
   </si>
   <si>
     <t xml:space="preserve">4.72717809677124</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.85108375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82104539871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83606433868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07056140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733053207397</t>
+    <t xml:space="preserve">4.82104635238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07056045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733100891113</t>
   </si>
   <si>
     <t xml:space="preserve">5.10198211669922</t>
@@ -749,25 +749,25 @@
     <t xml:space="preserve">5.0744891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12947511672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16875171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371257781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3415675163269</t>
+    <t xml:space="preserve">5.12947559356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16875219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552083969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34156656265259</t>
   </si>
   <si>
     <t xml:space="preserve">5.37691593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20410013198853</t>
+    <t xml:space="preserve">5.20410060882568</t>
   </si>
   <si>
     <t xml:space="preserve">5.28265237808228</t>
@@ -779,55 +779,55 @@
     <t xml:space="preserve">5.22373819351196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0509238243103</t>
+    <t xml:space="preserve">5.05092287063599</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29050779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26694250106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34942197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38477182388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21981143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25515937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978487014771</t>
+    <t xml:space="preserve">5.29050827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26694202423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36906099319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38477087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.219810962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25515985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978391647339</t>
   </si>
   <si>
     <t xml:space="preserve">5.32585668563843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25123167037964</t>
+    <t xml:space="preserve">5.2512321472168</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975830078125</t>
+    <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
     <t xml:space="preserve">5.61650133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57722473144531</t>
+    <t xml:space="preserve">5.57722425460815</t>
   </si>
   <si>
     <t xml:space="preserve">5.54187631607056</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">5.62435626983643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065279006958</t>
+    <t xml:space="preserve">5.50652742385864</t>
   </si>
   <si>
     <t xml:space="preserve">5.53794813156128</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55365943908691</t>
+    <t xml:space="preserve">5.5536584854126</t>
   </si>
   <si>
     <t xml:space="preserve">5.50259971618652</t>
@@ -857,34 +857,34 @@
     <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52223873138428</t>
+    <t xml:space="preserve">5.52223777770996</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257266998291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69112586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789546966553</t>
+    <t xml:space="preserve">5.69112539291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789499282837</t>
   </si>
   <si>
     <t xml:space="preserve">5.87572383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71076440811157</t>
+    <t xml:space="preserve">5.71076393127441</t>
   </si>
   <si>
     <t xml:space="preserve">5.73432970046997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64006614685059</t>
+    <t xml:space="preserve">5.64006662368774</t>
   </si>
   <si>
     <t xml:space="preserve">5.65970468521118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72647380828857</t>
+    <t xml:space="preserve">5.72647476196289</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">5.67148733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65577697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77753305435181</t>
+    <t xml:space="preserve">5.6557765007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
     <t xml:space="preserve">5.77360534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86786842346191</t>
+    <t xml:space="preserve">5.86786890029907</t>
   </si>
   <si>
     <t xml:space="preserve">5.83644771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82466459274292</t>
+    <t xml:space="preserve">5.82466506958008</t>
   </si>
   <si>
     <t xml:space="preserve">5.8403754234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82859230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93463802337646</t>
+    <t xml:space="preserve">5.8285927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93463850021362</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90714502334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7971715927124</t>
+    <t xml:space="preserve">5.90714550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79717111587524</t>
   </si>
   <si>
     <t xml:space="preserve">5.70290851593018</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78931617736816</t>
+    <t xml:space="preserve">5.78931665420532</t>
   </si>
   <si>
     <t xml:space="preserve">5.89143466949463</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70683670043945</t>
+    <t xml:space="preserve">5.79324388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70683622360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.68719816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936979293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46725082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293460845947</t>
+    <t xml:space="preserve">5.56936931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46725130081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293508529663</t>
   </si>
   <si>
     <t xml:space="preserve">5.66756010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47903394699097</t>
+    <t xml:space="preserve">5.47903442382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">5.39262628555298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45939540863037</t>
+    <t xml:space="preserve">5.45939588546753</t>
   </si>
   <si>
     <t xml:space="preserve">5.75004053115845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7618236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040199279785</t>
+    <t xml:space="preserve">5.76182270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040151596069</t>
   </si>
   <si>
     <t xml:space="preserve">5.75396776199341</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">5.80895471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91499996185303</t>
+    <t xml:space="preserve">5.91500043869019</t>
   </si>
   <si>
     <t xml:space="preserve">5.87965154647827</t>
@@ -1016,208 +1016,208 @@
     <t xml:space="preserve">5.72254610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6950535774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66363286972046</t>
+    <t xml:space="preserve">5.69505310058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6636323928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.64792156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71861934661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83252000808716</t>
+    <t xml:space="preserve">5.71861886978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83252048492432</t>
   </si>
   <si>
     <t xml:space="preserve">5.76575088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11530828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08388805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2606315612793</t>
+    <t xml:space="preserve">6.11530923843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08388757705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26063108444214</t>
   </si>
   <si>
     <t xml:space="preserve">6.24492025375366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31168985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776262283325</t>
+    <t xml:space="preserve">6.31169033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776214599609</t>
   </si>
   <si>
     <t xml:space="preserve">6.29990720748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29205226898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670289993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2527756690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26455879211426</t>
+    <t xml:space="preserve">6.29205179214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25277614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2645583152771</t>
   </si>
   <si>
     <t xml:space="preserve">6.20171642303467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23313808441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032228469849</t>
+    <t xml:space="preserve">6.2331371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032276153564</t>
   </si>
   <si>
     <t xml:space="preserve">6.00926303863525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12709188461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22528266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28026914596558</t>
+    <t xml:space="preserve">6.12709140777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22528314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28026866912842</t>
   </si>
   <si>
     <t xml:space="preserve">6.37060403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3745322227478</t>
+    <t xml:space="preserve">6.37453126907349</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39809846878052</t>
+    <t xml:space="preserve">6.3980975151062</t>
   </si>
   <si>
     <t xml:space="preserve">6.45308494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58662366867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339279174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5394926071167</t>
+    <t xml:space="preserve">6.58662414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53949213027954</t>
   </si>
   <si>
     <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63768243789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5630578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230840682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8301362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79086017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088579177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409057617188</t>
+    <t xml:space="preserve">6.63768291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56305742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83013534545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79086065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6808876991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409105300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.77907752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75551223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336717605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85762977600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81049823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7044529914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261672973633</t>
+    <t xml:space="preserve">6.75551271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86155652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81049871444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375520706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261625289917</t>
   </si>
   <si>
     <t xml:space="preserve">6.9990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99116802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40356969833374</t>
+    <t xml:space="preserve">6.99116897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40356922149658</t>
   </si>
   <si>
     <t xml:space="preserve">7.58031225204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54103565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55281782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66672039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8041877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75705575942993</t>
+    <t xml:space="preserve">7.54103708267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66671991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80418872833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75705528259277</t>
   </si>
   <si>
     <t xml:space="preserve">7.88666725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93379831314087</t>
+    <t xml:space="preserve">7.93379926681519</t>
   </si>
   <si>
     <t xml:space="preserve">7.91808843612671</t>
@@ -1226,211 +1226,211 @@
     <t xml:space="preserve">7.78454828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86310148239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488317489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74056005477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50804424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53161096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23782300949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410772323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59130907058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69656991958618</t>
+    <t xml:space="preserve">7.86310243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8748836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74055862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50804376602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53160953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23782396316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610231399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410820007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3006649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076318740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59131002426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69657039642334</t>
   </si>
   <si>
     <t xml:space="preserve">7.77355051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80025959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826547622681</t>
+    <t xml:space="preserve">7.80026006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826452255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.833251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94950866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914625167847</t>
+    <t xml:space="preserve">7.94950914382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914768218994</t>
   </si>
   <si>
     <t xml:space="preserve">7.5206127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83010911941528</t>
+    <t xml:space="preserve">7.83010864257812</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08304786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090423583984</t>
+    <t xml:space="preserve">8.08304882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090328216553</t>
   </si>
   <si>
     <t xml:space="preserve">7.94165229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95343589782715</t>
+    <t xml:space="preserve">7.95343685150146</t>
   </si>
   <si>
     <t xml:space="preserve">8.0437707901001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11054229736328</t>
+    <t xml:space="preserve">8.11054134368896</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07126426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86702966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83953523635864</t>
+    <t xml:space="preserve">8.07126522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.867027759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8395357131958</t>
   </si>
   <si>
     <t xml:space="preserve">7.69499921798706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7107105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300367355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487531661987</t>
+    <t xml:space="preserve">7.71070957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158391952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300271987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487627029419</t>
   </si>
   <si>
     <t xml:space="preserve">7.65572309494019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85524654388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59445142745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415239334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602403640747</t>
+    <t xml:space="preserve">7.85524463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59445238113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602355957031</t>
   </si>
   <si>
     <t xml:space="preserve">7.56146001815796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7531270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83167934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554510116577</t>
+    <t xml:space="preserve">7.75312757492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83168077468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554605484009</t>
   </si>
   <si>
     <t xml:space="preserve">8.03897953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08750534057617</t>
+    <t xml:space="preserve">8.08750343322754</t>
   </si>
   <si>
     <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97427940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14816188812256</t>
+    <t xml:space="preserve">7.96942663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97427988052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14815998077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.21690559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93222522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85943794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86752462387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726968765259</t>
+    <t xml:space="preserve">7.93222284317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85943746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87884616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86752510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726921081543</t>
   </si>
   <si>
     <t xml:space="preserve">7.41947746276855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25125551223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626235961914</t>
+    <t xml:space="preserve">7.25125598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626188278198</t>
   </si>
   <si>
     <t xml:space="preserve">7.43079948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40491914749146</t>
+    <t xml:space="preserve">7.40491962432861</t>
   </si>
   <si>
     <t xml:space="preserve">7.42594718933105</t>
@@ -1439,64 +1439,64 @@
     <t xml:space="preserve">7.10568237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59293413162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43441915512085</t>
+    <t xml:space="preserve">6.59293460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43441867828369</t>
   </si>
   <si>
     <t xml:space="preserve">6.8484992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91805219650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92613935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81776714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2221417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20111417770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14773654937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26419687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681318283081</t>
+    <t xml:space="preserve">6.91805171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92613887786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81776666641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22214269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20111513137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1477370262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2641978263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681175231934</t>
   </si>
   <si>
     <t xml:space="preserve">7.5860800743103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63783884048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78179597854614</t>
+    <t xml:space="preserve">7.70415687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857194900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7817964553833</t>
   </si>
   <si>
     <t xml:space="preserve">7.7073917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80282497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62975215911865</t>
+    <t xml:space="preserve">7.8028244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62975168228149</t>
   </si>
   <si>
     <t xml:space="preserve">7.6944522857666</t>
@@ -1505,43 +1505,43 @@
     <t xml:space="preserve">7.65886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69768714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223510742188</t>
+    <t xml:space="preserve">7.69768619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223463058472</t>
   </si>
   <si>
     <t xml:space="preserve">7.83032131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95163536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05353832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001792907715</t>
+    <t xml:space="preserve">7.95163297653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0535364151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001745223999</t>
   </si>
   <si>
     <t xml:space="preserve">8.07294750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06809425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19264125823975</t>
+    <t xml:space="preserve">8.06809329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19264316558838</t>
   </si>
   <si>
     <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29778099060059</t>
+    <t xml:space="preserve">8.28969287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29778003692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.31395435333252</t>
@@ -1553,19 +1553,19 @@
     <t xml:space="preserve">8.18455505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23307991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21286010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28564834594727</t>
+    <t xml:space="preserve">8.23308086395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21286106109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28564929962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794208526611</t>
+    <t xml:space="preserve">8.12794303894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.24521160125732</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06647682189941</t>
+    <t xml:space="preserve">8.06647777557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.17646598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07941627502441</t>
+    <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
     <t xml:space="preserve">8.14007377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08588600158691</t>
+    <t xml:space="preserve">8.08588695526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.12389850616455</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">8.20881652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2249927520752</t>
+    <t xml:space="preserve">8.22499179840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.30991077423096</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">8.1885986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33417510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182361602783</t>
+    <t xml:space="preserve">8.33417415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182266235352</t>
   </si>
   <si>
     <t xml:space="preserve">8.3179988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60510635375977</t>
+    <t xml:space="preserve">8.60510540008545</t>
   </si>
   <si>
     <t xml:space="preserve">8.77898597717285</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04183006286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11866188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22380065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32085037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2278413772583</t>
+    <t xml:space="preserve">9.04183101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32084941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22784328460693</t>
   </si>
   <si>
     <t xml:space="preserve">9.4178991317749</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">9.44620609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61604309082031</t>
+    <t xml:space="preserve">9.61604404449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.48259925842285</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">9.31276226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39768123626709</t>
+    <t xml:space="preserve">9.39768028259277</t>
   </si>
   <si>
     <t xml:space="preserve">9.30063152313232</t>
@@ -1679,97 +1679,97 @@
     <t xml:space="preserve">9.1954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11461925506592</t>
+    <t xml:space="preserve">9.1146183013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.67789268493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65362930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05191993713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89987421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531732559204</t>
+    <t xml:space="preserve">8.65363025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05192089080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89987373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531684875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287485122681</t>
+    <t xml:space="preserve">7.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4680027961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287389755249</t>
   </si>
   <si>
     <t xml:space="preserve">7.24155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1606764793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05715608596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080984115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3386025428772</t>
+    <t xml:space="preserve">7.16067743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05715703964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080888748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595659255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860158920288</t>
   </si>
   <si>
     <t xml:space="preserve">7.47770690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59093141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92251873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.987220287323</t>
+    <t xml:space="preserve">7.59093284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92251968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98721933364868</t>
   </si>
   <si>
     <t xml:space="preserve">8.00824737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94516563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96619272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78017902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78988456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76238584518433</t>
+    <t xml:space="preserve">7.9451642036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9661922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88369989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78018093109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78988409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76238632202148</t>
   </si>
   <si>
     <t xml:space="preserve">7.74297761917114</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">7.84164428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9807505607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91119718551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474626541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85134983062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74944639205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889795303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39036178588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24963903427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4938817024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521503448486</t>
+    <t xml:space="preserve">7.98074960708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9111967086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8513503074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74944686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889699935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39036130905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2496395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212102890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49388217926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521408081055</t>
   </si>
   <si>
     <t xml:space="preserve">7.26581430435181</t>
@@ -1820,19 +1820,19 @@
     <t xml:space="preserve">7.21890640258789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35477733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01833629608154</t>
+    <t xml:space="preserve">7.35477685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
     <t xml:space="preserve">7.05230474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93099069595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09921169281006</t>
+    <t xml:space="preserve">6.93099164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09921216964722</t>
   </si>
   <si>
     <t xml:space="preserve">7.07980155944824</t>
@@ -1841,94 +1841,94 @@
     <t xml:space="preserve">6.99245691299438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23831748962402</t>
+    <t xml:space="preserve">7.23831605911255</t>
   </si>
   <si>
     <t xml:space="preserve">7.27875423431396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58446216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62328147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828737258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54078912734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9370756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92898988723755</t>
+    <t xml:space="preserve">7.5844612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62328195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534791946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54078960418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92899036407471</t>
   </si>
   <si>
     <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046550750732</t>
+    <t xml:space="preserve">7.88046455383301</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781908035278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.673424243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57152223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83193969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92575454711914</t>
+    <t xml:space="preserve">7.67342329025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57152271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83194065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9257550239563</t>
   </si>
   <si>
     <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80767822265625</t>
+    <t xml:space="preserve">7.80767774581909</t>
   </si>
   <si>
     <t xml:space="preserve">8.00339412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3988733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2371244430542</t>
+    <t xml:space="preserve">8.39887428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23712348937988</t>
   </si>
   <si>
     <t xml:space="preserve">8.45144176483154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57679843902588</t>
+    <t xml:space="preserve">8.5767993927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.38674259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26947402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18051052093506</t>
+    <t xml:space="preserve">8.2694730758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18050956726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.26138687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034942626953</t>
+    <t xml:space="preserve">8.35034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559989929199</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">8.92051792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15909957885742</t>
+    <t xml:space="preserve">9.08226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15909862518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.18740558624268</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07418155670166</t>
+    <t xml:space="preserve">9.07418060302734</t>
   </si>
   <si>
     <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17931747436523</t>
+    <t xml:space="preserve">9.17931938171387</t>
   </si>
   <si>
     <t xml:space="preserve">9.2318868637085</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">9.34915637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38150691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36533069610596</t>
+    <t xml:space="preserve">9.38150596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32489204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36533164978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4057674407959</t>
+    <t xml:space="preserve">9.40576934814453</t>
   </si>
   <si>
     <t xml:space="preserve">9.59582424163818</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">9.65647983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56751823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46642303466797</t>
+    <t xml:space="preserve">9.56751728057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45833587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4664249420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.47451210021973</t>
@@ -2003,13 +2003,13 @@
     <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83036231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.036060333252</t>
+    <t xml:space="preserve">10.0163736343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83036327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0360612869263</t>
   </si>
   <si>
     <t xml:space="preserve">9.84943962097168</t>
@@ -2018,25 +2018,25 @@
     <t xml:space="preserve">9.7955265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98629474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79967308044434</t>
+    <t xml:space="preserve">9.98629570007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79967212677002</t>
   </si>
   <si>
     <t xml:space="preserve">9.73331928253174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47619724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569686889648</t>
+    <t xml:space="preserve">9.4761962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569496154785</t>
   </si>
   <si>
     <t xml:space="preserve">9.18589782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50161933898926</t>
+    <t xml:space="preserve">8.50162220001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.44356155395508</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">8.0305061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22625064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2362060546875</t>
+    <t xml:space="preserve">8.22625160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23620510101318</t>
   </si>
   <si>
     <t xml:space="preserve">8.11842632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21132183074951</t>
+    <t xml:space="preserve">8.2113208770752</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
@@ -2075,43 +2075,43 @@
     <t xml:space="preserve">8.00728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0869083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03880214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955045700073</t>
+    <t xml:space="preserve">8.08690738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0388011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955141067505</t>
   </si>
   <si>
     <t xml:space="preserve">7.67385292053223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69376087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091138839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670335769653</t>
+    <t xml:space="preserve">7.69376039505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670288085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77172565460205</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70868921279907</t>
+    <t xml:space="preserve">7.70868825912476</t>
   </si>
   <si>
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7003960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73357200622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58925104141235</t>
+    <t xml:space="preserve">7.70039558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7335729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58925247192383</t>
   </si>
   <si>
     <t xml:space="preserve">7.62574672698975</t>
@@ -2120,46 +2120,46 @@
     <t xml:space="preserve">7.50299119949341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55109786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72859573364258</t>
+    <t xml:space="preserve">7.55109882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72859621047974</t>
   </si>
   <si>
     <t xml:space="preserve">7.82978534698486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91936302185059</t>
+    <t xml:space="preserve">7.9193639755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12837886810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08359050750732</t>
+    <t xml:space="preserve">8.12837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08359146118164</t>
   </si>
   <si>
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667488098145</t>
+    <t xml:space="preserve">7.96249485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667392730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.17814445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21961688995361</t>
+    <t xml:space="preserve">8.2196159362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.60529899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87901020050049</t>
+    <t xml:space="preserve">8.87900924682617</t>
   </si>
   <si>
     <t xml:space="preserve">8.86656856536865</t>
@@ -2174,28 +2174,28 @@
     <t xml:space="preserve">8.55553340911865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51406288146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45600318908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30670642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48088645935059</t>
+    <t xml:space="preserve">8.51406192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4560022354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30670547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48088455200195</t>
   </si>
   <si>
     <t xml:space="preserve">8.29094696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32329368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06700134277344</t>
+    <t xml:space="preserve">8.3232946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704784393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06700038909912</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283981323242</t>
@@ -2204,91 +2204,91 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462116241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36530733108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45820188522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5726637840271</t>
+    <t xml:space="preserve">7.86462163925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45820140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57266426086426</t>
   </si>
   <si>
     <t xml:space="preserve">7.39184856414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22098684310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38355445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38853073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41839027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25084543228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42502546310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06173658370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17951583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25914001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.564368724823</t>
+    <t xml:space="preserve">7.22098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38852977752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7319130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41839075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25084590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42502593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06173610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17951536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388235092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2591404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436824798584</t>
   </si>
   <si>
     <t xml:space="preserve">7.4449315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76509046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73854875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92765712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77836132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989875793457</t>
+    <t xml:space="preserve">7.76509141921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73854827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92765760421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77836036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030115127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989780426025</t>
   </si>
   <si>
     <t xml:space="preserve">8.18975639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651544570923</t>
+    <t xml:space="preserve">7.89116382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651449203491</t>
   </si>
   <si>
     <t xml:space="preserve">8.16985034942627</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">8.09852027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76343202590942</t>
+    <t xml:space="preserve">7.76343059539795</t>
   </si>
   <si>
     <t xml:space="preserve">7.79660797119141</t>
@@ -2315,43 +2315,43 @@
     <t xml:space="preserve">7.86130380630493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97742319107056</t>
+    <t xml:space="preserve">7.97742366790771</t>
   </si>
   <si>
     <t xml:space="preserve">8.05539035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96581077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9044337272644</t>
+    <t xml:space="preserve">7.96581220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840782165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90443420410156</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02718925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65394735336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89613962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12671947479248</t>
+    <t xml:space="preserve">8.02719020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65394639968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361898422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89614105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12672138214111</t>
   </si>
   <si>
     <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17482662200928</t>
+    <t xml:space="preserve">8.17482757568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.33988285064697</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5596809387207</t>
+    <t xml:space="preserve">8.55967998504639</t>
   </si>
   <si>
     <t xml:space="preserve">8.46014976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44770908355713</t>
+    <t xml:space="preserve">8.44770812988281</t>
   </si>
   <si>
     <t xml:space="preserve">8.42697334289551</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">8.37720775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60944747924805</t>
+    <t xml:space="preserve">8.60944557189941</t>
   </si>
   <si>
     <t xml:space="preserve">8.85412788391113</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">9.16516208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13198566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23566246032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48449230194092</t>
+    <t xml:space="preserve">9.13198471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23566341400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4844913482666</t>
   </si>
   <si>
     <t xml:space="preserve">9.54255199432373</t>
@@ -2417,34 +2417,34 @@
     <t xml:space="preserve">9.50937461853027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42643070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3144588470459</t>
+    <t xml:space="preserve">9.42643165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31445789337158</t>
   </si>
   <si>
     <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38496017456055</t>
+    <t xml:space="preserve">9.38496112823486</t>
   </si>
   <si>
     <t xml:space="preserve">9.51766872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73746681213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33934116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23151683807373</t>
+    <t xml:space="preserve">9.73746585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70014095306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57158184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23151588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.28957653045654</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">9.35178279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3891077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19834041595459</t>
+    <t xml:space="preserve">9.38910675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19833946228027</t>
   </si>
   <si>
     <t xml:space="preserve">9.31031227111816</t>
@@ -2465,82 +2465,82 @@
     <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26884078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11539745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12369060516357</t>
+    <t xml:space="preserve">9.26883983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11539649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
     <t xml:space="preserve">9.04074764251709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06148433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01586532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05319023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93292427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12783908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88315773010254</t>
+    <t xml:space="preserve">9.06148529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01586627960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05318927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93292331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12783718109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88315677642822</t>
   </si>
   <si>
     <t xml:space="preserve">8.82509803771973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09880924224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24395751953125</t>
+    <t xml:space="preserve">9.09880828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24395847320557</t>
   </si>
   <si>
     <t xml:space="preserve">9.58817100524902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29372406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1527214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25639915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15686702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21492862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11954402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08221912384033</t>
+    <t xml:space="preserve">9.29372501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25639820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15686798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21492767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11954498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08221817016602</t>
   </si>
   <si>
     <t xml:space="preserve">9.09466075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11124992370605</t>
+    <t xml:space="preserve">9.11124897003174</t>
   </si>
   <si>
     <t xml:space="preserve">8.77533149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27298736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10710144042969</t>
+    <t xml:space="preserve">9.27298831939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.107102394104</t>
   </si>
   <si>
     <t xml:space="preserve">8.77118396759033</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">8.97024726867676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27713584899902</t>
+    <t xml:space="preserve">9.27713489532471</t>
   </si>
   <si>
     <t xml:space="preserve">9.68770217895508</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">9.05733680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99098205566406</t>
+    <t xml:space="preserve">8.99098300933838</t>
   </si>
   <si>
     <t xml:space="preserve">9.28128147125244</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">8.89559936523438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25279426574707</t>
+    <t xml:space="preserve">8.25279331207275</t>
   </si>
   <si>
     <t xml:space="preserve">8.14994430541992</t>
@@ -2582,58 +2582,58 @@
     <t xml:space="preserve">7.87457513809204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74186611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042501449585</t>
+    <t xml:space="preserve">7.74186658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042406082153</t>
   </si>
   <si>
     <t xml:space="preserve">7.35867166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44327211380005</t>
+    <t xml:space="preserve">7.44327306747437</t>
   </si>
   <si>
     <t xml:space="preserve">6.73328447341919</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25055742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53256273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73797225952148</t>
+    <t xml:space="preserve">6.2505578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53256225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73797178268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.38990116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30861759185791</t>
+    <t xml:space="preserve">6.30861711502075</t>
   </si>
   <si>
     <t xml:space="preserve">6.12946128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24060487747192</t>
+    <t xml:space="preserve">6.24060440063477</t>
   </si>
   <si>
     <t xml:space="preserve">6.2024507522583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19083976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8178858757019</t>
+    <t xml:space="preserve">6.19083881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81788539886475</t>
   </si>
   <si>
     <t xml:space="preserve">6.71503639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3304705619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85769748687744</t>
+    <t xml:space="preserve">7.33047151565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8576979637146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98542928695679</t>
@@ -2642,31 +2642,31 @@
     <t xml:space="preserve">6.87594556808472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096881866455</t>
+    <t xml:space="preserve">6.87096929550171</t>
   </si>
   <si>
     <t xml:space="preserve">7.0915961265564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42336702346802</t>
+    <t xml:space="preserve">7.4233660697937</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83310270309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92931747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32715368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264575958252</t>
+    <t xml:space="preserve">7.8331036567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92931842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32715225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264528274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.21600961685181</t>
@@ -2678,25 +2678,25 @@
     <t xml:space="preserve">6.76977825164795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26411771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067602157593</t>
+    <t xml:space="preserve">7.2641167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66224145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067649841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.88286828994751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07363796234131</t>
+    <t xml:space="preserve">8.07363700866699</t>
   </si>
   <si>
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41038513183594</t>
+    <t xml:space="preserve">8.41038417816162</t>
   </si>
   <si>
     <t xml:space="preserve">8.05207252502441</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7089786529541</t>
+    <t xml:space="preserve">8.70897674560547</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232353210449</t>
@@ -2717,52 +2717,52 @@
     <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.294264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20800304412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43111991882324</t>
+    <t xml:space="preserve">8.29426383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20800399780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43111896514893</t>
   </si>
   <si>
     <t xml:space="preserve">8.4725923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78777408599854</t>
+    <t xml:space="preserve">8.78777313232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.71312427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91218566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0034236907959</t>
+    <t xml:space="preserve">8.75874328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91218662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00342273712158</t>
   </si>
   <si>
     <t xml:space="preserve">9.34763622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34349060058594</t>
+    <t xml:space="preserve">9.3434886932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60475826263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402059555054</t>
+    <t xml:space="preserve">9.60475921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402069091797</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94897174835205</t>
+    <t xml:space="preserve">9.94896984100342</t>
   </si>
   <si>
     <t xml:space="preserve">10.0443544387817</t>
@@ -2780,16 +2780,16 @@
     <t xml:space="preserve">10.0650901794434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96555995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95311641693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3595371246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3512411117554</t>
+    <t xml:space="preserve">9.9655590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95311832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3595361709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3512401580811</t>
   </si>
   <si>
     <t xml:space="preserve">10.7286319732666</t>
@@ -2798,34 +2798,34 @@
     <t xml:space="preserve">10.6996011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6747188568115</t>
+    <t xml:space="preserve">10.6747179031372</t>
   </si>
   <si>
     <t xml:space="preserve">10.3388013839722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4093017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4632139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4010076522827</t>
+    <t xml:space="preserve">10.4093027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4010066986084</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8323106765747</t>
+    <t xml:space="preserve">10.6415424346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8323097229004</t>
   </si>
   <si>
     <t xml:space="preserve">10.7659559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9318399429321</t>
+    <t xml:space="preserve">10.9318408966064</t>
   </si>
   <si>
     <t xml:space="preserve">10.7783966064453</t>
@@ -2840,22 +2840,22 @@
     <t xml:space="preserve">10.4300374984741</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5295677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024150848389</t>
+    <t xml:space="preserve">10.5295686721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024141311646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5378637313843</t>
+    <t xml:space="preserve">10.53786277771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553895950317</t>
+    <t xml:space="preserve">10.3553876876831</t>
   </si>
   <si>
     <t xml:space="preserve">10.230975151062</t>
@@ -2882,25 +2882,25 @@
     <t xml:space="preserve">10.7493667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.687159538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6913080215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7949857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6664257049561</t>
+    <t xml:space="preserve">10.6871604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6913070678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7949848175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6664237976074</t>
   </si>
   <si>
     <t xml:space="preserve">10.5337162017822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6249523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751876831055</t>
+    <t xml:space="preserve">10.6249532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751867294312</t>
   </si>
   <si>
     <t xml:space="preserve">10.0733842849731</t>
@@ -2912,31 +2912,31 @@
     <t xml:space="preserve">10.2392702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180646896362</t>
+    <t xml:space="preserve">10.3180637359619</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1936511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0319137573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81626224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83285140991211</t>
+    <t xml:space="preserve">10.1936502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0319128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81626319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83284950256348</t>
   </si>
   <si>
     <t xml:space="preserve">9.46790313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44716739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72087860107422</t>
+    <t xml:space="preserve">9.44716835021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72087955474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.5591402053833</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">9.74990749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82040977478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0277662277222</t>
+    <t xml:space="preserve">9.82041072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
@@ -2963,28 +2963,28 @@
     <t xml:space="preserve">9.90335083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1604738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1729154586792</t>
+    <t xml:space="preserve">10.1604747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1729164123535</t>
   </si>
   <si>
     <t xml:space="preserve">10.2102403640747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0775318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1521787643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99044132232666</t>
+    <t xml:space="preserve">10.0775308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1521797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99044227600098</t>
   </si>
   <si>
     <t xml:space="preserve">10.1065616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96141147613525</t>
+    <t xml:space="preserve">9.96141052246094</t>
   </si>
   <si>
     <t xml:space="preserve">9.59646415710449</t>
@@ -2996,43 +2996,43 @@
     <t xml:space="preserve">9.67111206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74575996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970558166504</t>
+    <t xml:space="preserve">9.74576091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970653533936</t>
   </si>
   <si>
     <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3844203948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.347095489502</t>
+    <t xml:space="preserve">10.3844194412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3470964431763</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94482231140137</t>
+    <t xml:space="preserve">9.94482421875</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2682991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5088329315186</t>
+    <t xml:space="preserve">10.2683000564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5088338851929</t>
   </si>
   <si>
     <t xml:space="preserve">10.4134492874146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5212755203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8074264526367</t>
+    <t xml:space="preserve">10.5212745666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.807427406311</t>
   </si>
   <si>
     <t xml:space="preserve">10.7576608657837</t>
@@ -3041,37 +3041,37 @@
     <t xml:space="preserve">10.8779268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8945169448853</t>
+    <t xml:space="preserve">10.8945159912109</t>
   </si>
   <si>
     <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8157215118408</t>
+    <t xml:space="preserve">10.8157205581665</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733114242554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8364553451538</t>
+    <t xml:space="preserve">10.898663520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8364562988281</t>
   </si>
   <si>
     <t xml:space="preserve">10.9857530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8737802505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8447513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9774589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350507736206</t>
+    <t xml:space="preserve">10.8737812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8447494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350517272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.1018733978271</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">11.1143140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3548488616943</t>
+    <t xml:space="preserve">11.35484790802</t>
   </si>
   <si>
     <t xml:space="preserve">11.1474905014038</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">11.3921718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2843456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6119699478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5207328796387</t>
+    <t xml:space="preserve">11.2843465805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6119709014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.520733833313</t>
   </si>
   <si>
     <t xml:space="preserve">11.4792623519897</t>
@@ -3110,37 +3110,37 @@
     <t xml:space="preserve">11.1889629364014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1682271957397</t>
+    <t xml:space="preserve">11.1682281494141</t>
   </si>
   <si>
     <t xml:space="preserve">11.1226081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0355186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9442825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452201843262</t>
+    <t xml:space="preserve">11.0355195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9442806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452182769775</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926406860352</t>
+    <t xml:space="preserve">11.2926416397095</t>
   </si>
   <si>
     <t xml:space="preserve">11.9935064315796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1096258163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3999261856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1303625106812</t>
+    <t xml:space="preserve">12.1096267700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3999252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1303615570068</t>
   </si>
   <si>
     <t xml:space="preserve">12.4455442428589</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.594841003418</t>
+    <t xml:space="preserve">12.5948400497437</t>
   </si>
   <si>
     <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584537506104</t>
+    <t xml:space="preserve">12.3584547042847</t>
   </si>
   <si>
     <t xml:space="preserve">12.1718330383301</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">12.3169832229614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1842737197876</t>
+    <t xml:space="preserve">12.1842756271362</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3377170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1925687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0847425460815</t>
+    <t xml:space="preserve">12.3377180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1925678253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0847434997559</t>
   </si>
   <si>
     <t xml:space="preserve">12.2879524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0640077590942</t>
+    <t xml:space="preserve">12.0640068054199</t>
   </si>
   <si>
     <t xml:space="preserve">12.0349779129028</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">11.9230060577393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9810638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2755117416382</t>
+    <t xml:space="preserve">11.9810647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2755107879639</t>
   </si>
   <si>
     <t xml:space="preserve">12.163537979126</t>
@@ -3206,34 +3206,34 @@
     <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3543062210083</t>
+    <t xml:space="preserve">12.3543081283569</t>
   </si>
   <si>
     <t xml:space="preserve">12.1759805679321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9727716445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.97691822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9437408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1179208755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244125366211</t>
+    <t xml:space="preserve">11.972770690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9769172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9437398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.117919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.78200340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244115829468</t>
   </si>
   <si>
     <t xml:space="preserve">11.5580577850342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5539102554321</t>
+    <t xml:space="preserve">11.5539112091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626731872559</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">11.5746459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834089279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5912351608276</t>
+    <t xml:space="preserve">11.4834098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5912342071533</t>
   </si>
   <si>
     <t xml:space="preserve">11.5995292663574</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7405319213867</t>
+    <t xml:space="preserve">11.7405309677124</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985916137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9520349502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5456161499023</t>
+    <t xml:space="preserve">11.7985906600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9520359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.545615196228</t>
   </si>
   <si>
     <t xml:space="preserve">11.5331745147705</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8193273544312</t>
+    <t xml:space="preserve">11.8193264007568</t>
   </si>
   <si>
     <t xml:space="preserve">11.9064168930054</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142421722412</t>
+    <t xml:space="preserve">12.0142412185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6949129104614</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">11.8732395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6617374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322378158569</t>
+    <t xml:space="preserve">11.6617364883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322368621826</t>
   </si>
   <si>
     <t xml:space="preserve">11.7446784973145</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">11.711501121521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7654142379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5787935256958</t>
+    <t xml:space="preserve">11.7654132843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5787925720215</t>
   </si>
   <si>
     <t xml:space="preserve">11.164080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2055521011353</t>
+    <t xml:space="preserve">11.2055511474609</t>
   </si>
   <si>
     <t xml:space="preserve">11.3050832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4129076004028</t>
+    <t xml:space="preserve">11.4129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">11.4336442947388</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">11.3299655914307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631420135498</t>
+    <t xml:space="preserve">11.3631429672241</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382596969604</t>
@@ -3353,31 +3353,31 @@
     <t xml:space="preserve">11.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714380264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4917020797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5124397277832</t>
+    <t xml:space="preserve">11.3714351654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4917030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5124387741089</t>
   </si>
   <si>
     <t xml:space="preserve">11.6451473236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5622043609619</t>
+    <t xml:space="preserve">11.5622053146362</t>
   </si>
   <si>
     <t xml:space="preserve">11.524881362915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5953807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5497646331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.66588306427</t>
+    <t xml:space="preserve">11.5953817367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5497636795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">11.9312992095947</t>
@@ -3386,43 +3386,43 @@
     <t xml:space="preserve">11.8607997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6410007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8068857192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0266828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1013317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2133054733276</t>
+    <t xml:space="preserve">11.6409997940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.026683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1013307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2133045196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.2423343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1967163085938</t>
+    <t xml:space="preserve">12.1967153549194</t>
   </si>
   <si>
     <t xml:space="preserve">12.3086891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1510982513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.478720664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8690929412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778558731079</t>
+    <t xml:space="preserve">12.1510972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4787216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391244888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8690919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778549194336</t>
   </si>
   <si>
     <t xml:space="preserve">12.1220674514771</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">12.333571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7151069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5367813110352</t>
+    <t xml:space="preserve">12.7151079177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5367803573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7773132324219</t>
+    <t xml:space="preserve">12.7773151397705</t>
   </si>
   <si>
     <t xml:space="preserve">12.8975811004639</t>
@@ -3452,52 +3452,52 @@
     <t xml:space="preserve">13.2293519973755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3827962875366</t>
+    <t xml:space="preserve">13.382794380188</t>
   </si>
   <si>
     <t xml:space="preserve">13.453296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5942983627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698848724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4201211929321</t>
+    <t xml:space="preserve">13.5942993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4201192855835</t>
   </si>
   <si>
     <t xml:space="preserve">13.3496179580688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2252044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4781799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.216911315918</t>
+    <t xml:space="preserve">13.2252054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4781789779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2169103622437</t>
   </si>
   <si>
     <t xml:space="preserve">13.051025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1588487625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1837348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625293731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9514942169189</t>
+    <t xml:space="preserve">13.1588506698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1837329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9514932632446</t>
   </si>
   <si>
     <t xml:space="preserve">12.8644037246704</t>
@@ -3509,34 +3509,34 @@
     <t xml:space="preserve">12.7607250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7939033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9349060058594</t>
+    <t xml:space="preserve">12.7939023971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9349050521851</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312282562256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7482833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.574104309082</t>
+    <t xml:space="preserve">12.7482843399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5741052627563</t>
   </si>
   <si>
     <t xml:space="preserve">12.6611948013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9763765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.237645149231</t>
+    <t xml:space="preserve">12.9763774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2376470565796</t>
   </si>
   <si>
     <t xml:space="preserve">13.1215257644653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0095539093018</t>
+    <t xml:space="preserve">13.0095548629761</t>
   </si>
   <si>
     <t xml:space="preserve">13.2417936325073</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9431982040405</t>
+    <t xml:space="preserve">12.9431991577148</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">12.9722309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9888181686401</t>
+    <t xml:space="preserve">12.9888172149658</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302896499634</t>
@@ -3572,28 +3572,28 @@
     <t xml:space="preserve">13.1090850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9929647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2044687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1173791885376</t>
+    <t xml:space="preserve">12.9929656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2044696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1173782348633</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850694656372</t>
+    <t xml:space="preserve">13.7850675582886</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523590087891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8016548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7726259231567</t>
+    <t xml:space="preserve">13.8016557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">13.7975091934204</t>
@@ -3602,55 +3602,55 @@
     <t xml:space="preserve">13.9219236373901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9799823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6274766921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7270069122314</t>
+    <t xml:space="preserve">13.9799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.627477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7270059585571</t>
   </si>
   <si>
     <t xml:space="preserve">13.69797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0048656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.764331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878076553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.224663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3324899673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583099365234</t>
+    <t xml:space="preserve">14.004864692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7643308639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878095626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3324880599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583089828491</t>
   </si>
   <si>
     <t xml:space="preserve">14.2951650619507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3532257080078</t>
+    <t xml:space="preserve">14.3532247543335</t>
   </si>
   <si>
     <t xml:space="preserve">14.2619876861572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163677215576</t>
+    <t xml:space="preserve">14.3076076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163696289062</t>
   </si>
   <si>
     <t xml:space="preserve">14.12513256073</t>
@@ -3659,55 +3659,55 @@
     <t xml:space="preserve">14.3006258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.859751701355</t>
+    <t xml:space="preserve">13.8255071640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8597526550293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819051742554</t>
+    <t xml:space="preserve">13.2819042205811</t>
   </si>
   <si>
     <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605028152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.435996055603</t>
+    <t xml:space="preserve">13.2605037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4359970092773</t>
   </si>
   <si>
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5515670776367</t>
+    <t xml:space="preserve">13.1834573745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5515661239624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9068365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6457347869873</t>
+    <t xml:space="preserve">13.645733833313</t>
   </si>
   <si>
     <t xml:space="preserve">13.4488382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4188766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3974733352661</t>
+    <t xml:space="preserve">13.4188756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3974742889404</t>
   </si>
   <si>
     <t xml:space="preserve">13.4445581436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258846282959</t>
+    <t xml:space="preserve">13.5258836746216</t>
   </si>
   <si>
     <t xml:space="preserve">12.9951219558716</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">12.7639837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.965160369873</t>
+    <t xml:space="preserve">12.9651594161987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9095144271851</t>
+    <t xml:space="preserve">12.9095153808594</t>
   </si>
   <si>
     <t xml:space="preserve">13.2433824539185</t>
@@ -3740,10 +3740,10 @@
     <t xml:space="preserve">13.4873609542847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6842575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562217712402</t>
+    <t xml:space="preserve">13.6842565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562227249146</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589496612549</t>
@@ -3761,16 +3761,16 @@
     <t xml:space="preserve">13.5301647186279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6114912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2861862182617</t>
+    <t xml:space="preserve">13.6114902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2861852645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.0293645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1920175552368</t>
+    <t xml:space="preserve">13.1920166015625</t>
   </si>
   <si>
     <t xml:space="preserve">13.1320924758911</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">12.3616304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5499658584595</t>
+    <t xml:space="preserve">12.5499668121338</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900417327881</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740961074829</t>
+    <t xml:space="preserve">12.6740951538086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538703918457</t>
@@ -3803,22 +3803,22 @@
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682638168335</t>
+    <t xml:space="preserve">12.7682628631592</t>
   </si>
   <si>
     <t xml:space="preserve">12.849591255188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0550470352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6157712936401</t>
+    <t xml:space="preserve">13.055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6157722473145</t>
   </si>
   <si>
     <t xml:space="preserve">13.6286125183105</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7784242630005</t>
+    <t xml:space="preserve">13.7784233093262</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799764633179</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">13.4103155136108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.277624130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4301156997681</t>
+    <t xml:space="preserve">13.2776260375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4301166534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">10.8720712661743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5339250564575</t>
+    <t xml:space="preserve">10.5339241027832</t>
   </si>
   <si>
     <t xml:space="preserve">11.783784866333</t>
@@ -3878,13 +3878,13 @@
     <t xml:space="preserve">12.5157222747803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9892416000366</t>
+    <t xml:space="preserve">11.9892425537109</t>
   </si>
   <si>
     <t xml:space="preserve">12.0106420516968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277652740479</t>
+    <t xml:space="preserve">12.0277643203735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9849605560303</t>
@@ -3893,31 +3893,31 @@
     <t xml:space="preserve">11.8479900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9507188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3145475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1989784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2332210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.310266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2631826400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9549989700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1262121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188285827637</t>
+    <t xml:space="preserve">11.9507179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.314546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1989774703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2332220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3102674484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.26318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9549980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1262130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188276290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203798294067</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834083557129</t>
+    <t xml:space="preserve">12.0834093093872</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705671310425</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">11.2444610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2530221939087</t>
+    <t xml:space="preserve">11.253023147583</t>
   </si>
   <si>
     <t xml:space="preserve">11.2787046432495</t>
@@ -3974,22 +3974,22 @@
     <t xml:space="preserve">10.5724487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0545263290405</t>
+    <t xml:space="preserve">10.0545272827148</t>
   </si>
   <si>
     <t xml:space="preserve">10.080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4868412017822</t>
+    <t xml:space="preserve">10.4868402481079</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6109714508057</t>
+    <t xml:space="preserve">10.5938501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6109704971313</t>
   </si>
   <si>
     <t xml:space="preserve">10.8292684555054</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">11.5423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969738006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6351318359375</t>
+    <t xml:space="preserve">11.6969728469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6351308822632</t>
   </si>
   <si>
     <t xml:space="preserve">11.560037612915</t>
@@ -4028,19 +4028,19 @@
     <t xml:space="preserve">11.1580648422241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4893608093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3745107650757</t>
+    <t xml:space="preserve">11.4893598556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37451171875</t>
   </si>
   <si>
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62968254089355</t>
+    <t xml:space="preserve">10.6368246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62968349456787</t>
   </si>
   <si>
     <t xml:space="preserve">9.14378261566162</t>
@@ -4052,31 +4052,31 @@
     <t xml:space="preserve">9.74453258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44415664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57667636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89030361175537</t>
+    <t xml:space="preserve">9.44415760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57667541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89030265808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.92122364044189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1818447113037</t>
+    <t xml:space="preserve">10.1818437576294</t>
   </si>
   <si>
     <t xml:space="preserve">10.4645500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6191558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4689674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4778022766113</t>
+    <t xml:space="preserve">10.6191549301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4689683914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477801322937</t>
   </si>
   <si>
     <t xml:space="preserve">10.3894567489624</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">10.1244201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.226016998291</t>
+    <t xml:space="preserve">10.2260160446167</t>
   </si>
   <si>
     <t xml:space="preserve">9.9786491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2171812057495</t>
+    <t xml:space="preserve">10.2171821594238</t>
   </si>
   <si>
     <t xml:space="preserve">10.7384223937988</t>
@@ -4115,13 +4115,13 @@
     <t xml:space="preserve">10.0449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5661478042603</t>
+    <t xml:space="preserve">10.5661487579346</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0934982299805</t>
+    <t xml:space="preserve">10.0934991836548</t>
   </si>
   <si>
     <t xml:space="preserve">9.92564105987549</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">10.0007352828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6809978485107</t>
+    <t xml:space="preserve">10.6809968948364</t>
   </si>
   <si>
     <t xml:space="preserve">10.6500759124756</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">10.8267679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5573139190674</t>
+    <t xml:space="preserve">10.707501411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5573129653931</t>
   </si>
   <si>
     <t xml:space="preserve">10.9062795639038</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">10.959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902076721191</t>
+    <t xml:space="preserve">10.9902067184448</t>
   </si>
   <si>
     <t xml:space="preserve">10.7781772613525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5308094024658</t>
+    <t xml:space="preserve">10.5308103561401</t>
   </si>
   <si>
     <t xml:space="preserve">10.6544942855835</t>
@@ -4190,19 +4190,19 @@
     <t xml:space="preserve">9.46624374389648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54133796691895</t>
+    <t xml:space="preserve">9.54133701324463</t>
   </si>
   <si>
     <t xml:space="preserve">9.55458927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42648792266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84613037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55017185211182</t>
+    <t xml:space="preserve">9.42648887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84613132476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55017280578613</t>
   </si>
   <si>
     <t xml:space="preserve">9.58109378814697</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">9.59876251220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86379909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8797740936279</t>
+    <t xml:space="preserve">9.86380004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8797750473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.919529914856</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">10.8046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215045928955</t>
+    <t xml:space="preserve">11.3215036392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.9371995925903</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">11.02112865448</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8488550186157</t>
+    <t xml:space="preserve">10.8488540649414</t>
   </si>
   <si>
     <t xml:space="preserve">11.2508268356323</t>
@@ -4259,13 +4259,13 @@
     <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8471603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5379514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9460344314575</t>
+    <t xml:space="preserve">11.8471612930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5379505157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9460353851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.9548692703247</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">10.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239473342896</t>
+    <t xml:space="preserve">10.9239482879639</t>
   </si>
   <si>
     <t xml:space="preserve">11.2464094161987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2331581115723</t>
+    <t xml:space="preserve">11.2331590652466</t>
   </si>
   <si>
     <t xml:space="preserve">11.2110710144043</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">11.6572179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9620094299316</t>
+    <t xml:space="preserve">11.962010383606</t>
   </si>
   <si>
     <t xml:space="preserve">12.0591897964478</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">12.1431188583374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0503568649292</t>
+    <t xml:space="preserve">12.0503559112549</t>
   </si>
   <si>
     <t xml:space="preserve">12.1961269378662</t>
@@ -4319,10 +4319,10 @@
     <t xml:space="preserve">12.6201858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6246032714844</t>
+    <t xml:space="preserve">12.3772354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6246042251587</t>
   </si>
   <si>
     <t xml:space="preserve">12.6908626556396</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">12.7527046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8277978897095</t>
+    <t xml:space="preserve">12.8277988433838</t>
   </si>
   <si>
     <t xml:space="preserve">12.9205617904663</t>
@@ -4343,22 +4343,22 @@
     <t xml:space="preserve">13.0354108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2518587112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1811809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2827787399292</t>
+    <t xml:space="preserve">13.2518577575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1811819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2827777862549</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4418020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743188858032</t>
+    <t xml:space="preserve">13.441801071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743198394775</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285488128662</t>
@@ -4367,13 +4367,13 @@
     <t xml:space="preserve">13.3578729629517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6405782699585</t>
+    <t xml:space="preserve">13.6405792236328</t>
   </si>
   <si>
     <t xml:space="preserve">13.6494131088257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9144515991211</t>
+    <t xml:space="preserve">13.9144506454468</t>
   </si>
   <si>
     <t xml:space="preserve">13.8835296630859</t>
@@ -4385,10 +4385,10 @@
     <t xml:space="preserve">13.6008234024048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6759176254272</t>
+    <t xml:space="preserve">13.7465944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6759166717529</t>
   </si>
   <si>
     <t xml:space="preserve">13.7730979919434</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">13.9188680648804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1414251327515</t>
+    <t xml:space="preserve">13.1414260864258</t>
   </si>
   <si>
     <t xml:space="preserve">13.3534555435181</t>
@@ -4412,10 +4412,10 @@
     <t xml:space="preserve">13.5345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5831546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.834939956665</t>
+    <t xml:space="preserve">13.5831537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8349390029907</t>
   </si>
   <si>
     <t xml:space="preserve">13.7112560272217</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">13.8658599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1883230209351</t>
+    <t xml:space="preserve">14.1883220672607</t>
   </si>
   <si>
     <t xml:space="preserve">14.5947122573853</t>
@@ -4433,49 +4433,49 @@
     <t xml:space="preserve">14.4710273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5726270675659</t>
+    <t xml:space="preserve">14.5726280212402</t>
   </si>
   <si>
     <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8685846328735</t>
+    <t xml:space="preserve">14.8685855865479</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7669878005981</t>
+    <t xml:space="preserve">14.7669868469238</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095623016357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7934904098511</t>
+    <t xml:space="preserve">14.7934913635254</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3429279327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5196189880371</t>
+    <t xml:space="preserve">14.3429269790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5196180343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.3385095596313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.148567199707</t>
+    <t xml:space="preserve">14.1485662460327</t>
   </si>
   <si>
     <t xml:space="preserve">14.0955591201782</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4489421844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5107831954956</t>
+    <t xml:space="preserve">14.4489431381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5107841491699</t>
   </si>
   <si>
     <t xml:space="preserve">14.4312725067139</t>
@@ -4484,10 +4484,10 @@
     <t xml:space="preserve">14.5328712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.52845287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5814609527588</t>
+    <t xml:space="preserve">14.5284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5814599990845</t>
   </si>
   <si>
     <t xml:space="preserve">14.9790172576904</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">15.009937286377</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6609725952148</t>
+    <t xml:space="preserve">14.6609716415405</t>
   </si>
   <si>
     <t xml:space="preserve">14.6918916702271</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">14.7714042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6433038711548</t>
+    <t xml:space="preserve">14.6433029174805</t>
   </si>
   <si>
     <t xml:space="preserve">13.9453716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1397314071655</t>
+    <t xml:space="preserve">14.1397323608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.963041305542</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">14.444525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2236604690552</t>
+    <t xml:space="preserve">14.2236614227295</t>
   </si>
   <si>
     <t xml:space="preserve">14.3473443984985</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">14.2810859680176</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2501640319824</t>
+    <t xml:space="preserve">14.2501630783081</t>
   </si>
   <si>
     <t xml:space="preserve">14.3650140762329</t>
@@ -4562,10 +4562,10 @@
     <t xml:space="preserve">12.2402982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4523286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.502613067627</t>
+    <t xml:space="preserve">12.4523296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5026140213013</t>
   </si>
   <si>
     <t xml:space="preserve">11.7455635070801</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">12.3153924942017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4169902801514</t>
+    <t xml:space="preserve">12.4169912338257</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0238513946533</t>
+    <t xml:space="preserve">12.0238523483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5009183883667</t>
+    <t xml:space="preserve">12.500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
@@ -4604,25 +4604,25 @@
     <t xml:space="preserve">12.4920845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.293306350708</t>
+    <t xml:space="preserve">12.2933073043823</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579689025879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0636072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3728179931641</t>
+    <t xml:space="preserve">12.0636081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3728189468384</t>
   </si>
   <si>
     <t xml:space="preserve">12.6025171279907</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7306175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141706466675</t>
+    <t xml:space="preserve">12.7306184768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5141716003418</t>
   </si>
   <si>
     <t xml:space="preserve">13.0795831680298</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">12.5892648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5362577438354</t>
+    <t xml:space="preserve">12.5362567901611</t>
   </si>
   <si>
     <t xml:space="preserve">12.3065595626831</t>
@@ -4649,19 +4649,19 @@
     <t xml:space="preserve">12.5406742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7588157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1121988296509</t>
+    <t xml:space="preserve">12.1298666000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7588148117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1121978759766</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9399242401123</t>
+    <t xml:space="preserve">11.9399251937866</t>
   </si>
   <si>
     <t xml:space="preserve">11.8824987411499</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.0653009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949991226196</t>
+    <t xml:space="preserve">11.2950000762939</t>
   </si>
   <si>
     <t xml:space="preserve">11.0873880386353</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.30748462677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638675689697</t>
+    <t xml:space="preserve">11.0638666152954</t>
   </si>
   <si>
     <t xml:space="preserve">11.2753086090088</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">11.3856248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.436185836792</t>
+    <t xml:space="preserve">11.4361867904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.6522245407104</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">11.5832767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913454055786</t>
+    <t xml:space="preserve">11.4913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">11.4959421157837</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">11.4499769210815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4591703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7533483505249</t>
+    <t xml:space="preserve">11.4591693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7533473968506</t>
   </si>
   <si>
     <t xml:space="preserve">11.6935930252075</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">11.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0041122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9949197769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.096043586731</t>
+    <t xml:space="preserve">11.0041131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9949188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0960426330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.1833772659302</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">11.2890977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0868501663208</t>
+    <t xml:space="preserve">11.0868511199951</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4683637619019</t>
+    <t xml:space="preserve">11.4683628082275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8131036758423</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">12.1486501693726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3279151916504</t>
+    <t xml:space="preserve">12.3187227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3279161453247</t>
   </si>
   <si>
     <t xml:space="preserve">12.5117769241333</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.3784770965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5301628112793</t>
+    <t xml:space="preserve">12.5301637649536</t>
   </si>
   <si>
     <t xml:space="preserve">12.6358833312988</t>
@@ -4832,19 +4832,19 @@
     <t xml:space="preserve">12.9760274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645864486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4428291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255670547485</t>
+    <t xml:space="preserve">12.7645874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4428281784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255661010742</t>
   </si>
   <si>
     <t xml:space="preserve">12.4750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2385358810425</t>
+    <t xml:space="preserve">11.2385368347168</t>
   </si>
   <si>
     <t xml:space="preserve">12.0383338928223</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">11.964789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9555969238281</t>
+    <t xml:space="preserve">11.9555959701538</t>
   </si>
   <si>
     <t xml:space="preserve">11.5005388259888</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">11.6016626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.551100730896</t>
+    <t xml:space="preserve">11.5510997772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143280029297</t>
@@ -4877,19 +4877,19 @@
     <t xml:space="preserve">11.5786800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7073822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625417709351</t>
+    <t xml:space="preserve">11.7073831558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625408172607</t>
   </si>
   <si>
     <t xml:space="preserve">11.7441549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6384344100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
+    <t xml:space="preserve">11.6384353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465040206909</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855243682861</t>
@@ -4898,19 +4898,19 @@
     <t xml:space="preserve">11.7487516403198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6154527664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.94895362854</t>
+    <t xml:space="preserve">11.6154518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9489545822144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7558994293213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8708124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570241928101</t>
+    <t xml:space="preserve">10.870813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570232391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.8478298187256</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">10.889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7283201217651</t>
+    <t xml:space="preserve">10.7283210754395</t>
   </si>
   <si>
     <t xml:space="preserve">10.8294439315796</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">10.6915483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6547756195068</t>
+    <t xml:space="preserve">10.6547765731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7329168319702</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">10.6271963119507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858278274536</t>
+    <t xml:space="preserve">10.5858287811279</t>
   </si>
   <si>
     <t xml:space="preserve">10.287052154541</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">10.1445598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1215782165527</t>
+    <t xml:space="preserve">10.1215772628784</t>
   </si>
   <si>
     <t xml:space="preserve">9.91932964324951</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">9.99747085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79522323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399621963501</t>
+    <t xml:space="preserve">9.79522228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399631500244</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721391677856</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">9.90094375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96989250183105</t>
+    <t xml:space="preserve">9.96989154815674</t>
   </si>
   <si>
     <t xml:space="preserve">10.1951217651367</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">10.043436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0848054885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.03883934021</t>
+    <t xml:space="preserve">10.0848045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0388402938843</t>
   </si>
   <si>
     <t xml:space="preserve">10.057225227356</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">10.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629467010498</t>
+    <t xml:space="preserve">10.1629457473755</t>
   </si>
   <si>
     <t xml:space="preserve">10.2181043624878</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">11.0454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3948192596436</t>
+    <t xml:space="preserve">11.3948183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.5097322463989</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">11.0592708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9995155334473</t>
+    <t xml:space="preserve">10.9995164871216</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9903230667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477293014526</t>
+    <t xml:space="preserve">10.9903221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477283477783</t>
   </si>
   <si>
     <t xml:space="preserve">11.3672389984131</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">11.5970659255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.776330947876</t>
+    <t xml:space="preserve">11.7763319015503</t>
   </si>
   <si>
     <t xml:space="preserve">11.8866481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3646869659424</t>
+    <t xml:space="preserve">12.3646879196167</t>
   </si>
   <si>
     <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4290390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4014596939087</t>
+    <t xml:space="preserve">12.4290399551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.401460647583</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3692846298218</t>
+    <t xml:space="preserve">12.3692836761475</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554944992065</t>
@@ -5099,7 +5099,7 @@
     <t xml:space="preserve">12.5485486984253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.249773979187</t>
+    <t xml:space="preserve">12.2497749328613</t>
   </si>
   <si>
     <t xml:space="preserve">12.5393571853638</t>
@@ -5111,25 +5111,25 @@
     <t xml:space="preserve">12.6404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4566192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7507963180542</t>
+    <t xml:space="preserve">12.456618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7507972717285</t>
   </si>
   <si>
     <t xml:space="preserve">12.6680593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8473253250122</t>
+    <t xml:space="preserve">12.8473243713379</t>
   </si>
   <si>
     <t xml:space="preserve">12.870306968689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9024820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7783765792847</t>
+    <t xml:space="preserve">12.9024829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7783756256104</t>
   </si>
   <si>
     <t xml:space="preserve">12.8105525970459</t>
@@ -5138,16 +5138,16 @@
     <t xml:space="preserve">12.7094278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6174974441528</t>
+    <t xml:space="preserve">12.6174983978271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5577421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8381309509277</t>
+    <t xml:space="preserve">12.6588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8381319046021</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819499969482</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">11.8544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8452787399292</t>
+    <t xml:space="preserve">11.8452796936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705099105835</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">12.1348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0888957977295</t>
+    <t xml:space="preserve">12.0888948440552</t>
   </si>
   <si>
     <t xml:space="preserve">11.9326124191284</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">11.8085069656372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8958406448364</t>
+    <t xml:space="preserve">11.8958396911621</t>
   </si>
   <si>
     <t xml:space="preserve">12.0107536315918</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">12.194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.153247833252</t>
+    <t xml:space="preserve">12.1532468795776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1854228973389</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">12.0934915542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.157844543457</t>
+    <t xml:space="preserve">12.1808271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1578435897827</t>
   </si>
   <si>
     <t xml:space="preserve">12.2957391738892</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">12.3922672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.626690864563</t>
+    <t xml:space="preserve">12.6266899108887</t>
   </si>
   <si>
     <t xml:space="preserve">12.6220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8335342407227</t>
+    <t xml:space="preserve">12.833535194397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9162721633911</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">12.4796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2242403030396</t>
+    <t xml:space="preserve">13.2242412567139</t>
   </si>
   <si>
     <t xml:space="preserve">13.136905670166</t>
@@ -5270,7 +5270,7 @@
     <t xml:space="preserve">13.2012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2702054977417</t>
+    <t xml:space="preserve">13.270206451416</t>
   </si>
   <si>
     <t xml:space="preserve">13.1736783981323</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">12.6726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.681848526001</t>
+    <t xml:space="preserve">12.6818494796753</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9990110397339</t>
+    <t xml:space="preserve">12.9990100860596</t>
   </si>
   <si>
     <t xml:space="preserve">13.0265893936157</t>
@@ -5309,16 +5309,16 @@
     <t xml:space="preserve">12.8611135482788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0541677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058765411377</t>
+    <t xml:space="preserve">13.0541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587644577026</t>
   </si>
   <si>
     <t xml:space="preserve">13.2748022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1461000442505</t>
+    <t xml:space="preserve">13.1460990905762</t>
   </si>
   <si>
     <t xml:space="preserve">13.233434677124</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.780421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9275102615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9045286178589</t>
+    <t xml:space="preserve">13.7804222106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.92751121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9045276641846</t>
   </si>
   <si>
     <t xml:space="preserve">14.0102481842041</t>
@@ -6267,6 +6267,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.3649997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7549991607666</t>
   </si>
 </sst>
 </file>
@@ -71267,7 +71270,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6497800926</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>848562</v>
@@ -71288,6 +71291,32 @@
         <v>2084</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494444444</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>2306108</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>18.8700008392334</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>18.1450004577637</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>18.7549991607666</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="2086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="2087">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35306358337402</t>
+    <t xml:space="preserve">5.35306262969971</t>
   </si>
   <si>
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209386825562</t>
+    <t xml:space="preserve">5.32048892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209434509277</t>
   </si>
   <si>
     <t xml:space="preserve">5.13951921463013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2625789642334</t>
+    <t xml:space="preserve">5.26257848739624</t>
   </si>
   <si>
     <t xml:space="preserve">5.1322808265686</t>
@@ -68,64 +68,64 @@
     <t xml:space="preserve">5.19381046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0454158782959</t>
+    <t xml:space="preserve">5.04541540145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.92959547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07437133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65814113616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101345062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96578979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05265378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21190643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0490345954895</t>
+    <t xml:space="preserve">5.07437086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65814161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101392745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96578884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05265474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21190690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
     <t xml:space="preserve">5.14675807952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16485548019409</t>
+    <t xml:space="preserve">5.16485500335693</t>
   </si>
   <si>
     <t xml:space="preserve">5.12504196166992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88978242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79205894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74138879776001</t>
+    <t xml:space="preserve">4.88978290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79205846786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74138784408569</t>
   </si>
   <si>
     <t xml:space="preserve">4.56765794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34325647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45545673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441171646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213472366333</t>
+    <t xml:space="preserve">4.3432559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45545721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441123962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213520050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.78482055664062</t>
@@ -140,40 +140,40 @@
     <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71243238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84996891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88616275787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00922155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09246730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16847467422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95493030548096</t>
+    <t xml:space="preserve">4.71243286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84996938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88616323471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00922203063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09246683120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16847515106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95493078231812</t>
   </si>
   <si>
     <t xml:space="preserve">4.84273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78120088577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713247299194</t>
+    <t xml:space="preserve">4.78120183944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713199615479</t>
   </si>
   <si>
     <t xml:space="preserve">5.08884811401367</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">5.00560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99112558364868</t>
+    <t xml:space="preserve">4.99112510681152</t>
   </si>
   <si>
     <t xml:space="preserve">5.19019079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362302780151</t>
+    <t xml:space="preserve">5.23362350463867</t>
   </si>
   <si>
     <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02008056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026752471924</t>
+    <t xml:space="preserve">5.128662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02008008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026657104492</t>
   </si>
   <si>
     <t xml:space="preserve">4.94769287109375</t>
@@ -218,121 +218,121 @@
     <t xml:space="preserve">5.11418390274048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12142324447632</t>
+    <t xml:space="preserve">5.12142276763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.33544111251831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23406410217285</t>
+    <t xml:space="preserve">5.23406314849854</t>
   </si>
   <si>
     <t xml:space="preserve">5.282874584198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27161073684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23030948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16647958755493</t>
+    <t xml:space="preserve">5.27161121368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23030853271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
     <t xml:space="preserve">5.33168601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30164861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39176177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2641019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25659275054932</t>
+    <t xml:space="preserve">5.30164813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.391761302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26410150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25659227371216</t>
   </si>
   <si>
     <t xml:space="preserve">5.05759239196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0988941192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96747922897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88863039016724</t>
+    <t xml:space="preserve">5.09889459609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96748018264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">4.78725337982178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79100799560547</t>
+    <t xml:space="preserve">4.79100847244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.76472520828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7008957862854</t>
+    <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
     <t xml:space="preserve">4.96372509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.903648853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90740394592285</t>
+    <t xml:space="preserve">4.90364980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90740442276001</t>
   </si>
   <si>
     <t xml:space="preserve">4.77598905563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73844289779663</t>
+    <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9186692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98625230789185</t>
+    <t xml:space="preserve">4.91866827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.986252784729</t>
   </si>
   <si>
     <t xml:space="preserve">4.97874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01629066467285</t>
+    <t xml:space="preserve">5.01629018783569</t>
   </si>
   <si>
     <t xml:space="preserve">4.92617750167847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95246028900146</t>
+    <t xml:space="preserve">4.95246076583862</t>
   </si>
   <si>
     <t xml:space="preserve">4.97123432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8548378944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87736654281616</t>
+    <t xml:space="preserve">4.85483837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.877366065979</t>
   </si>
   <si>
     <t xml:space="preserve">4.8022723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204647064209</t>
+    <t xml:space="preserve">4.62204742431641</t>
   </si>
   <si>
     <t xml:space="preserve">4.56197071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44182014465332</t>
+    <t xml:space="preserve">4.44182062149048</t>
   </si>
   <si>
     <t xml:space="preserve">4.44932985305786</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">4.56948041915894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75346088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093318939209</t>
+    <t xml:space="preserve">4.7534613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093271255493</t>
   </si>
   <si>
     <t xml:space="preserve">4.80602693557739</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">4.97498941421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49063158035278</t>
+    <t xml:space="preserve">4.49063110351562</t>
   </si>
   <si>
     <t xml:space="preserve">4.1301794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39676427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33668851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39300870895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17523574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10014200210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87485861778259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244360923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26534938812256</t>
+    <t xml:space="preserve">4.39676380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33668899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3930082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17523622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10014152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87485957145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2653489112854</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19025421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20151853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23531150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31040525436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25032997131348</t>
+    <t xml:space="preserve">4.1902551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20151901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23531103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31040573120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25032949447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.24657583236694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27661323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93118047714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9875009059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8373122215271</t>
+    <t xml:space="preserve">4.27661275863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9311797618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98750114440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83731198310852</t>
   </si>
   <si>
     <t xml:space="preserve">3.93868899345398</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">3.93493437767029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9724817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619917869568</t>
+    <t xml:space="preserve">3.97248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619846343994</t>
   </si>
   <si>
     <t xml:space="preserve">3.99876427650452</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">3.82980298995972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82604837417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348232269287</t>
+    <t xml:space="preserve">3.82604742050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348184585571</t>
   </si>
   <si>
     <t xml:space="preserve">3.7547082901001</t>
@@ -458,37 +458,37 @@
     <t xml:space="preserve">4.05133056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07010412216187</t>
+    <t xml:space="preserve">4.07010459899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01378345489502</t>
+    <t xml:space="preserve">4.01378393173218</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09263277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1376895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12266969680786</t>
+    <t xml:space="preserve">4.09263181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13768863677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12267017364502</t>
   </si>
   <si>
     <t xml:space="preserve">4.05508518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07385873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255653381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124059677124</t>
+    <t xml:space="preserve">4.07385921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255605697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91240644454956</t>
   </si>
   <si>
     <t xml:space="preserve">3.82229399681091</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.81478404998779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9048969745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114235877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987851142883</t>
+    <t xml:space="preserve">3.90489649772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114283561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8898777961731</t>
   </si>
   <si>
     <t xml:space="preserve">3.81102895736694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88612389564514</t>
+    <t xml:space="preserve">3.8861231803894</t>
   </si>
   <si>
     <t xml:space="preserve">3.89738726615906</t>
@@ -518,76 +518,76 @@
     <t xml:space="preserve">3.88236904144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8711051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233092308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850150108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221823692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61203026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550881385803</t>
+    <t xml:space="preserve">3.87110543251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233068466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850102424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6120297908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550929069519</t>
   </si>
   <si>
     <t xml:space="preserve">3.79601001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96121835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999119758606</t>
+    <t xml:space="preserve">3.96121764183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999143600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96497201919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01753759384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08887767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14519834518433</t>
+    <t xml:space="preserve">3.96497273445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01753902435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0888786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14519786834717</t>
   </si>
   <si>
     <t xml:space="preserve">3.99501013755798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92742586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474640846252</t>
+    <t xml:space="preserve">3.92742466926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355689048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474593162537</t>
   </si>
   <si>
     <t xml:space="preserve">3.80727481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79225635528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170469284058</t>
+    <t xml:space="preserve">3.79225587844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170493125916</t>
   </si>
   <si>
     <t xml:space="preserve">3.73518419265747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6405656337738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60452079772949</t>
+    <t xml:space="preserve">3.64056587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60452055931091</t>
   </si>
   <si>
     <t xml:space="preserve">3.54444479942322</t>
@@ -596,115 +596,115 @@
     <t xml:space="preserve">3.53843712806702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54144167900085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47085285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799958229065</t>
+    <t xml:space="preserve">3.5414412021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55645990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001492500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4708526134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">3.66459584236145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64507126808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66910195350647</t>
+    <t xml:space="preserve">3.64507150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66910123825073</t>
   </si>
   <si>
     <t xml:space="preserve">3.57748651504517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73968935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144420623779</t>
+    <t xml:space="preserve">3.73968982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144325256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.1038966178894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01002931594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04006671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11516046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0025200843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07761287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16772699356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270757675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895296096802</t>
+    <t xml:space="preserve">4.01002883911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04006624221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11516094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00251913070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07761335372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16772651672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895343780518</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512306213379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18274545669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22029256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23906660079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16021728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06259489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03631162643433</t>
+    <t xml:space="preserve">4.18274593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22029209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23906564712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16021776199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642431259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06259441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03631114959717</t>
   </si>
   <si>
     <t xml:space="preserve">4.13393402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28787755966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30289602279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6933856010437</t>
+    <t xml:space="preserve">4.28787708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69338607788086</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342348098755</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">4.80978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83981990814209</t>
+    <t xml:space="preserve">4.83981943130493</t>
   </si>
   <si>
     <t xml:space="preserve">4.81353664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79851722717285</t>
+    <t xml:space="preserve">4.79851770401001</t>
   </si>
   <si>
     <t xml:space="preserve">4.72717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85108375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82104635238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83606481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07056045532227</t>
+    <t xml:space="preserve">4.85108327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82104539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83606433868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07056093215942</t>
   </si>
   <si>
     <t xml:space="preserve">5.13733100891113</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10198211669922</t>
+    <t xml:space="preserve">5.10198163986206</t>
   </si>
   <si>
     <t xml:space="preserve">5.0744891166687</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">5.16875219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23552083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34156656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37691593170166</t>
+    <t xml:space="preserve">5.23552131652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371257781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34156799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3769154548645</t>
   </si>
   <si>
     <t xml:space="preserve">5.20410060882568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28265237808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20017290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373819351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092287063599</t>
+    <t xml:space="preserve">5.28265285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20017337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092334747314</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
@@ -794,22 +794,22 @@
     <t xml:space="preserve">5.36906099319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34942245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38477087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588277816772</t>
+    <t xml:space="preserve">5.34942197799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38477039337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588325500488</t>
   </si>
   <si>
     <t xml:space="preserve">5.219810962677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25515985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978391647339</t>
+    <t xml:space="preserve">5.25515937805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978439331055</t>
   </si>
   <si>
     <t xml:space="preserve">5.32585668563843</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975782394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57722425460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54187631607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63221120834351</t>
+    <t xml:space="preserve">5.43975830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57722473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5418758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63221073150635</t>
   </si>
   <si>
     <t xml:space="preserve">5.62435626983643</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">5.53794813156128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62042856216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5536584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50259971618652</t>
+    <t xml:space="preserve">5.62042808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55365896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50260019302368</t>
   </si>
   <si>
     <t xml:space="preserve">5.41226434707642</t>
@@ -860,49 +860,49 @@
     <t xml:space="preserve">5.52223777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61257266998291</t>
+    <t xml:space="preserve">5.61257362365723</t>
   </si>
   <si>
     <t xml:space="preserve">5.69112539291382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75789499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87572383880615</t>
+    <t xml:space="preserve">5.75789546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87572431564331</t>
   </si>
   <si>
     <t xml:space="preserve">5.71076393127441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73432970046997</t>
+    <t xml:space="preserve">5.73433017730713</t>
   </si>
   <si>
     <t xml:space="preserve">5.64006662368774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65970468521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72647476196289</t>
+    <t xml:space="preserve">5.65970420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72647380828857</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67148733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6557765007019</t>
+    <t xml:space="preserve">5.67148780822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65577697753906</t>
   </si>
   <si>
     <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77360534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86786890029907</t>
+    <t xml:space="preserve">5.77360486984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86786842346191</t>
   </si>
   <si>
     <t xml:space="preserve">5.83644771575928</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">5.8403754234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8285927772522</t>
+    <t xml:space="preserve">5.82859230041504</t>
   </si>
   <si>
     <t xml:space="preserve">5.87179660797119</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90714550018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79717111587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70290851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78931665420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89143466949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78538846969604</t>
+    <t xml:space="preserve">5.90714502334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7971715927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70290899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78931617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89143419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538799285889</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324388504028</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">5.68719816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46725130081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66756010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903442382812</t>
+    <t xml:space="preserve">5.56936979293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46725082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66755962371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903347015381</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">5.39262628555298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45939588546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75004053115845</t>
+    <t xml:space="preserve">5.45939636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75004005432129</t>
   </si>
   <si>
     <t xml:space="preserve">5.76182270050049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75396776199341</t>
+    <t xml:space="preserve">5.73040199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75396728515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80895471572876</t>
+    <t xml:space="preserve">5.80895376205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.91500043869019</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">5.85215854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84430313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001348495483</t>
+    <t xml:space="preserve">5.84430265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001300811768</t>
   </si>
   <si>
     <t xml:space="preserve">5.84823083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72254610061646</t>
+    <t xml:space="preserve">5.72254657745361</t>
   </si>
   <si>
     <t xml:space="preserve">5.69505310058594</t>
@@ -1022,46 +1022,46 @@
     <t xml:space="preserve">5.6636323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64792156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71861886978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83252048492432</t>
+    <t xml:space="preserve">5.64792203903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71861934661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83252000808716</t>
   </si>
   <si>
     <t xml:space="preserve">5.76575088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11530923843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08388757705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26063108444214</t>
+    <t xml:space="preserve">6.11530876159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08388805389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26063060760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.24492025375366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31169033050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29990720748901</t>
+    <t xml:space="preserve">6.31168937683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29990816116333</t>
   </si>
   <si>
     <t xml:space="preserve">6.29205179214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25670337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706579208374</t>
+    <t xml:space="preserve">6.25670289993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706531524658</t>
   </si>
   <si>
     <t xml:space="preserve">6.25277614593506</t>
@@ -1073,40 +1073,40 @@
     <t xml:space="preserve">6.20171642303467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2331371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032276153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00926303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12709140777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22528314590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28026866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37060403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37453126907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33132839202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3980975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45308494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58662414550781</t>
+    <t xml:space="preserve">6.23313760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032228469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1270923614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22528266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37060356140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37453174591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33132886886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39809799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45308446884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58662462234497</t>
   </si>
   <si>
     <t xml:space="preserve">6.65339326858521</t>
@@ -1118,25 +1118,25 @@
     <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63768291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56305742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83013534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874216079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79086065292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6808876991272</t>
+    <t xml:space="preserve">6.63768339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5630578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83013582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79086017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088722229004</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409105300903</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">6.75551271438599</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76336669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85762929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86155652999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81049871444702</t>
+    <t xml:space="preserve">6.76336574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86155700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81049776077271</t>
   </si>
   <si>
     <t xml:space="preserve">6.70445203781128</t>
@@ -1166,58 +1166,58 @@
     <t xml:space="preserve">6.63375520706177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64553785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261625289917</t>
+    <t xml:space="preserve">6.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261768341064</t>
   </si>
   <si>
     <t xml:space="preserve">6.9990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99116897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287239074707</t>
+    <t xml:space="preserve">6.99116945266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287143707275</t>
   </si>
   <si>
     <t xml:space="preserve">7.40356922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58031225204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54103708267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55281925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351655960083</t>
+    <t xml:space="preserve">7.58031272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5410361289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.552818775177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641111373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351703643799</t>
   </si>
   <si>
     <t xml:space="preserve">7.66671991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80418872833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75705528259277</t>
+    <t xml:space="preserve">7.80418682098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75705575942993</t>
   </si>
   <si>
     <t xml:space="preserve">7.88666725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93379926681519</t>
+    <t xml:space="preserve">7.93379831314087</t>
   </si>
   <si>
     <t xml:space="preserve">7.91808843612671</t>
@@ -1226,52 +1226,52 @@
     <t xml:space="preserve">7.78454828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86310243606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8748836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74055862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50804376602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53160953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23782396316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610231399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410820007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3006649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076318740845</t>
+    <t xml:space="preserve">7.86310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87488317489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951761245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50804328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53161096572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23782348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410772323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076271057129</t>
   </si>
   <si>
     <t xml:space="preserve">7.59131002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69657039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355051040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80026006698608</t>
+    <t xml:space="preserve">7.69656991958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355146408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025959014893</t>
   </si>
   <si>
     <t xml:space="preserve">7.77826452255249</t>
@@ -1280,37 +1280,37 @@
     <t xml:space="preserve">7.833251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94950914382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914768218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5206127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83010864257812</t>
+    <t xml:space="preserve">7.94950866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914720535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52061367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8301100730896</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08304882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165229797363</t>
+    <t xml:space="preserve">8.08304786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165277481079</t>
   </si>
   <si>
     <t xml:space="preserve">7.95343685150146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0437707901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11054134368896</t>
+    <t xml:space="preserve">8.04377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11054039001465</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
@@ -1319,112 +1319,112 @@
     <t xml:space="preserve">8.07126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.867027759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8395357131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69499921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71070957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158391952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487627029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65572309494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85524463653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59445238113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415143966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56146001815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75312757492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83168077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554605484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08750343322754</t>
+    <t xml:space="preserve">7.86702966690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83953523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499826431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71070861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158296585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300367355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65572357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85524654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59445142745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56146097183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75312805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83168029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554510116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03898048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08750534057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97427988052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14815998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21690559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93222284317017</t>
+    <t xml:space="preserve">7.96942710876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97427940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14816093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21690464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93222332000732</t>
   </si>
   <si>
     <t xml:space="preserve">7.86105442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85943746566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87884616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86752510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41947746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626188278198</t>
+    <t xml:space="preserve">7.85943698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87884712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86752462387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41947650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125646591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626140594482</t>
   </si>
   <si>
     <t xml:space="preserve">7.43079948425293</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">7.40491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42594718933105</t>
+    <t xml:space="preserve">7.4259467124939</t>
   </si>
   <si>
     <t xml:space="preserve">7.10568237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59293460845947</t>
+    <t xml:space="preserve">6.59293413162231</t>
   </si>
   <si>
     <t xml:space="preserve">6.43441867828369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8484992980957</t>
+    <t xml:space="preserve">6.84849977493286</t>
   </si>
   <si>
     <t xml:space="preserve">6.91805171966553</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">6.81776666641235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22214269638062</t>
+    <t xml:space="preserve">7.22214221954346</t>
   </si>
   <si>
     <t xml:space="preserve">7.20111513137817</t>
@@ -1469,37 +1469,37 @@
     <t xml:space="preserve">7.1477370262146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2641978263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5860800743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70415687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63784027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7817964553833</t>
+    <t xml:space="preserve">7.26419687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58607959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70415592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63783979415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179693222046</t>
   </si>
   <si>
     <t xml:space="preserve">7.7073917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8028244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62975168228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6944522857666</t>
+    <t xml:space="preserve">7.80282402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62975263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69445323944092</t>
   </si>
   <si>
     <t xml:space="preserve">7.65886735916138</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">7.69768619537354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82223463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95163297653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0535364151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06809329986572</t>
+    <t xml:space="preserve">7.82223415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032274246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95163440704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05353736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001697540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
     <t xml:space="preserve">8.19264316558838</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969287872314</t>
+    <t xml:space="preserve">8.28969192504883</t>
   </si>
   <si>
     <t xml:space="preserve">8.29778003692627</t>
@@ -1550,76 +1550,76 @@
     <t xml:space="preserve">8.27756118774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18455505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23308086395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28564929962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24925518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12794303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24521160125732</t>
+    <t xml:space="preserve">8.18455410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23307991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21286201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28564834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24925422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12794208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24521064758301</t>
   </si>
   <si>
     <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06647777557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17646598815918</t>
+    <t xml:space="preserve">8.0664758682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1764669418335</t>
   </si>
   <si>
     <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14007377624512</t>
+    <t xml:space="preserve">8.14007472991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.08588695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12389850616455</t>
+    <t xml:space="preserve">8.12389755249023</t>
   </si>
   <si>
     <t xml:space="preserve">8.20881652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22499179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30991077423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22903633117676</t>
+    <t xml:space="preserve">8.2249927520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30991172790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22903537750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.1885986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33417415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182266235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3179988861084</t>
+    <t xml:space="preserve">8.33417510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31799793243408</t>
   </si>
   <si>
     <t xml:space="preserve">8.60510540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77898597717285</t>
+    <t xml:space="preserve">8.77898502349854</t>
   </si>
   <si>
     <t xml:space="preserve">8.77089881896973</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95691108703613</t>
+    <t xml:space="preserve">8.95691204071045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03778648376465</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">9.11866092681885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22379875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298206329346</t>
+    <t xml:space="preserve">9.22379970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298110961914</t>
   </si>
   <si>
     <t xml:space="preserve">9.32084941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22784328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4178991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44620609283447</t>
+    <t xml:space="preserve">9.22784233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41790008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44620418548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.61604404449463</t>
@@ -1664,22 +1664,22 @@
     <t xml:space="preserve">9.48259925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31276226043701</t>
+    <t xml:space="preserve">9.3127613067627</t>
   </si>
   <si>
     <t xml:space="preserve">9.39768028259277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30063152313232</t>
+    <t xml:space="preserve">9.30063056945801</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1146183013916</t>
+    <t xml:space="preserve">9.19549369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11461925506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.67789268493652</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">8.65363025665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05192089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89987373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531684875488</t>
+    <t xml:space="preserve">8.05191993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89987421035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531732559204</t>
   </si>
   <si>
     <t xml:space="preserve">8.11985492706299</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">7.83355760574341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4680027961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287389755249</t>
+    <t xml:space="preserve">7.46800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287485122681</t>
   </si>
   <si>
     <t xml:space="preserve">7.24155235290527</t>
@@ -1715,37 +1715,37 @@
     <t xml:space="preserve">7.16067743301392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05715703964233</t>
+    <t xml:space="preserve">7.05715656280518</t>
   </si>
   <si>
     <t xml:space="preserve">7.32080888748169</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09597635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595659255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860158920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59093284606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503274917603</t>
+    <t xml:space="preserve">7.09597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3386025428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47770643234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59093236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92251873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562213897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503322601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.98721933364868</t>
@@ -1754,25 +1754,25 @@
     <t xml:space="preserve">8.00824737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9451642036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9661922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78018093109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78988409042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76238632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74297761917114</t>
+    <t xml:space="preserve">7.94516468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96619319915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88369941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78017902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78988456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76238584518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74297857284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.84164428710938</t>
@@ -1781,163 +1781,163 @@
     <t xml:space="preserve">7.98074960708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9111967086792</t>
+    <t xml:space="preserve">7.91119623184204</t>
   </si>
   <si>
     <t xml:space="preserve">7.68474721908569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8513503074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74944686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889699935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39036130905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2496395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212102890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49388217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521408081055</t>
+    <t xml:space="preserve">7.85134983062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74944639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39036178588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24963855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4421215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49388313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521455764771</t>
   </si>
   <si>
     <t xml:space="preserve">7.26581430435181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21890640258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35477685928345</t>
+    <t xml:space="preserve">7.21890592575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35477733612061</t>
   </si>
   <si>
     <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05230474472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09921216964722</t>
+    <t xml:space="preserve">7.0523042678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09921169281006</t>
   </si>
   <si>
     <t xml:space="preserve">7.07980155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99245691299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5844612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62328195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534791946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54078960418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707799911499</t>
+    <t xml:space="preserve">6.99245643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62328100204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828546524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54079008102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707847595215</t>
   </si>
   <si>
     <t xml:space="preserve">7.90634489059448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92899036407471</t>
+    <t xml:space="preserve">7.92898988723755</t>
   </si>
   <si>
     <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046455383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67342329025269</t>
+    <t xml:space="preserve">7.88046503067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8578200340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.673424243927</t>
   </si>
   <si>
     <t xml:space="preserve">7.57152271270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83194065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9257550239563</t>
+    <t xml:space="preserve">7.83193874359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92575550079346</t>
   </si>
   <si>
     <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80767774581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00339412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39887428283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23712348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45144176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5767993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38674259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18050956726074</t>
+    <t xml:space="preserve">7.80767726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00339508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3988733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2371244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45144271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57679843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38674354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18051052093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.26138687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83559989929199</t>
+    <t xml:space="preserve">8.3503475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83559894561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.92051792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08226680755615</t>
+    <t xml:space="preserve">9.08226776123047</t>
   </si>
   <si>
     <t xml:space="preserve">9.15909862518311</t>
@@ -1955,37 +1955,37 @@
     <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17931938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2318868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34915637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38150596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32489204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36533164978027</t>
+    <t xml:space="preserve">9.17931747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23188591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34915542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38150691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36532974243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40576934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59582424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65647983551025</t>
+    <t xml:space="preserve">9.40576839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65648078918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.56751728057861</t>
@@ -2003,127 +2003,127 @@
     <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163736343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83036327362061</t>
+    <t xml:space="preserve">10.0163745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83036231994629</t>
   </si>
   <si>
     <t xml:space="preserve">10.0360612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84943962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7955265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629570007324</t>
+    <t xml:space="preserve">9.84943866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79552745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629379272461</t>
   </si>
   <si>
     <t xml:space="preserve">9.79967212677002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73331928253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4761962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569496154785</t>
+    <t xml:space="preserve">9.73331832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47619724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569591522217</t>
   </si>
   <si>
     <t xml:space="preserve">9.18589782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50162220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44356155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27767562866211</t>
+    <t xml:space="preserve">8.50162124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44356250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27767658233643</t>
   </si>
   <si>
     <t xml:space="preserve">8.17150974273682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96912908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12506103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0305061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22625160217285</t>
+    <t xml:space="preserve">7.96912813186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12506198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03050708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22625255584717</t>
   </si>
   <si>
     <t xml:space="preserve">8.23620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11842632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2113208770752</t>
+    <t xml:space="preserve">8.1184253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08690738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0388011932373</t>
+    <t xml:space="preserve">8.00728225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0869083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03880214691162</t>
   </si>
   <si>
     <t xml:space="preserve">7.87955141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67385292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69376039505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70868825912476</t>
+    <t xml:space="preserve">7.6738543510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69375991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091138839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7767014503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77172660827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70868921279907</t>
   </si>
   <si>
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70039558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7335729598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58925247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62574672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50299119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72859621047974</t>
+    <t xml:space="preserve">7.70039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73357248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58925104141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6257472038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50299072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109834671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72859573364258</t>
   </si>
   <si>
     <t xml:space="preserve">7.82978534698486</t>
@@ -2138,16 +2138,16 @@
     <t xml:space="preserve">8.12837982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08359146118164</t>
+    <t xml:space="preserve">8.08359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667392730713</t>
+    <t xml:space="preserve">7.96249389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667488098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.17814445495605</t>
@@ -2156,34 +2156,34 @@
     <t xml:space="preserve">8.2196159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60529899597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87900924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86656856536865</t>
+    <t xml:space="preserve">8.60529804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87901020050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86656951904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.54724025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38549995422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55553340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51406192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4560022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30670547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48088455200195</t>
+    <t xml:space="preserve">8.38550090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55553245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51406288146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45600318908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30670642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">8.29094696044922</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">8.3232946395874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05704784393311</t>
+    <t xml:space="preserve">8.05704879760742</t>
   </si>
   <si>
     <t xml:space="preserve">8.06700038909912</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462163925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36530685424805</t>
+    <t xml:space="preserve">7.86462211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36530733108521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45820140838623</t>
@@ -2219,28 +2219,28 @@
     <t xml:space="preserve">7.39184856414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22098636627197</t>
+    <t xml:space="preserve">7.22098588943481</t>
   </si>
   <si>
     <t xml:space="preserve">7.38355398178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38852977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7319130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41839075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25084590911865</t>
+    <t xml:space="preserve">7.38853073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73191261291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41839122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25084543228149</t>
   </si>
   <si>
     <t xml:space="preserve">7.42502593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06173610687256</t>
+    <t xml:space="preserve">7.06173658370972</t>
   </si>
   <si>
     <t xml:space="preserve">7.17951536178589</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">7.31388235092163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56436824798584</t>
+    <t xml:space="preserve">7.25914001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.564368724823</t>
   </si>
   <si>
     <t xml:space="preserve">7.4449315071106</t>
@@ -2261,37 +2261,37 @@
     <t xml:space="preserve">7.76509141921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73854827880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92765760421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77836036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030115127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18975639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116382598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16985034942627</t>
+    <t xml:space="preserve">7.73854875564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92765712738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77836227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18975734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16985130310059</t>
   </si>
   <si>
     <t xml:space="preserve">8.09852027893066</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">7.79660797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03216648101807</t>
+    <t xml:space="preserve">8.03216552734375</t>
   </si>
   <si>
     <t xml:space="preserve">7.98903512954712</t>
@@ -2312,22 +2312,22 @@
     <t xml:space="preserve">7.84969091415405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86130380630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05539035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581220626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840782165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90443420410156</t>
+    <t xml:space="preserve">7.86130332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05538845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9044337272644</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
@@ -2336,22 +2336,22 @@
     <t xml:space="preserve">8.02719020843506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65394639968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361898422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89614105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12672138214111</t>
+    <t xml:space="preserve">7.65394735336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89614057540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1267204284668</t>
   </si>
   <si>
     <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17482757568359</t>
+    <t xml:space="preserve">8.17482662200928</t>
   </si>
   <si>
     <t xml:space="preserve">8.33988285064697</t>
@@ -2360,31 +2360,31 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55967998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46014976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44770812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62603569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47673797607422</t>
+    <t xml:space="preserve">8.5596809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46014881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44770908355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6260347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47673892974854</t>
   </si>
   <si>
     <t xml:space="preserve">8.37720775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60944557189941</t>
+    <t xml:space="preserve">8.60944652557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.85412788391113</t>
@@ -2396,67 +2396,67 @@
     <t xml:space="preserve">8.99927806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16516208648682</t>
+    <t xml:space="preserve">9.16516304016113</t>
   </si>
   <si>
     <t xml:space="preserve">9.13198471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23566341400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4844913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52596282958984</t>
+    <t xml:space="preserve">9.23566246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52596187591553</t>
   </si>
   <si>
     <t xml:space="preserve">9.50937461853027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42643165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31445789337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38496112823486</t>
+    <t xml:space="preserve">9.42643070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3144588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057918548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38496017456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.51766872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73746585845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70014095306396</t>
+    <t xml:space="preserve">9.73746681213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70014190673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.57158184051514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33934307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23151588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28957653045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35178279876709</t>
+    <t xml:space="preserve">9.33934116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23151683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28957557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35178184509277</t>
   </si>
   <si>
     <t xml:space="preserve">9.38910675048828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19833946228027</t>
+    <t xml:space="preserve">9.19834041595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.31031227111816</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26883983612061</t>
+    <t xml:space="preserve">9.26884078979492</t>
   </si>
   <si>
     <t xml:space="preserve">9.11539649963379</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04074764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06148529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01586627960205</t>
+    <t xml:space="preserve">9.04074859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06148433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01586437225342</t>
   </si>
   <si>
     <t xml:space="preserve">9.05318927764893</t>
@@ -2489,25 +2489,25 @@
     <t xml:space="preserve">8.93292331695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12783718109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88315677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82509803771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09880828857422</t>
+    <t xml:space="preserve">9.12783813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88315773010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82509708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09880924224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24395847320557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58817100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29372501373291</t>
+    <t xml:space="preserve">9.58817005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29372406005859</t>
   </si>
   <si>
     <t xml:space="preserve">9.15272045135498</t>
@@ -2516,22 +2516,22 @@
     <t xml:space="preserve">9.25639820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15686798095703</t>
+    <t xml:space="preserve">9.15686702728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.21492767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11954498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08221817016602</t>
+    <t xml:space="preserve">9.11954402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08221912384033</t>
   </si>
   <si>
     <t xml:space="preserve">9.09466075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11124897003174</t>
+    <t xml:space="preserve">9.11124992370605</t>
   </si>
   <si>
     <t xml:space="preserve">8.77533149719238</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">9.27298831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.107102394104</t>
+    <t xml:space="preserve">9.10710144042969</t>
   </si>
   <si>
     <t xml:space="preserve">8.77118396759033</t>
@@ -2549,22 +2549,22 @@
     <t xml:space="preserve">8.97024726867676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27713489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68770217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1444263458252</t>
+    <t xml:space="preserve">9.27713584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68770122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14442729949951</t>
   </si>
   <si>
     <t xml:space="preserve">9.08636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05733680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99098300933838</t>
+    <t xml:space="preserve">9.05733585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99098205566406</t>
   </si>
   <si>
     <t xml:space="preserve">9.28128147125244</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">8.89559936523438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25279331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14994430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87457513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74186658859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042406082153</t>
+    <t xml:space="preserve">8.25279426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14994525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87457418441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042453765869</t>
   </si>
   <si>
     <t xml:space="preserve">7.35867166519165</t>
@@ -2597,46 +2597,46 @@
     <t xml:space="preserve">6.73328447341919</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2505578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53256225585938</t>
+    <t xml:space="preserve">6.25055742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53256320953369</t>
   </si>
   <si>
     <t xml:space="preserve">5.73797178268433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38990116119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30861711502075</t>
+    <t xml:space="preserve">6.38990163803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30861759185791</t>
   </si>
   <si>
     <t xml:space="preserve">6.12946128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24060440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2024507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19083881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81788539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71503639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33047151565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8576979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98542928695679</t>
+    <t xml:space="preserve">6.24060487747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20245122909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19083976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8178858757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71503591537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33047103881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85769748687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98542881011963</t>
   </si>
   <si>
     <t xml:space="preserve">6.87594556808472</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">7.0915961265564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4233660697937</t>
+    <t xml:space="preserve">7.42336702346802</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">7.8331036567688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83144426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92931842803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32715225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21600961685181</t>
+    <t xml:space="preserve">7.83144521713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92931747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32715272903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21601009368896</t>
   </si>
   <si>
     <t xml:space="preserve">7.24255228042603</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">7.2641167640686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067649841309</t>
+    <t xml:space="preserve">7.66224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067697525024</t>
   </si>
   <si>
     <t xml:space="preserve">7.88286828994751</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41038417816162</t>
+    <t xml:space="preserve">8.41038513183594</t>
   </si>
   <si>
     <t xml:space="preserve">8.05207252502441</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897674560547</t>
+    <t xml:space="preserve">8.70897769927979</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232353210449</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29426383972168</t>
+    <t xml:space="preserve">8.294264793396</t>
   </si>
   <si>
     <t xml:space="preserve">8.20800399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43111896514893</t>
+    <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
     <t xml:space="preserve">8.4725923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78777313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71312427520752</t>
+    <t xml:space="preserve">8.78777408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71312522888184</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874328613281</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">9.34763622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3434886932373</t>
+    <t xml:space="preserve">9.34349060058594</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60475921630859</t>
+    <t xml:space="preserve">9.60475730895996</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973289489746</t>
+    <t xml:space="preserve">10.2973279953003</t>
   </si>
   <si>
     <t xml:space="preserve">9.94896984100342</t>
@@ -2777,22 +2777,22 @@
     <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0650901794434</t>
+    <t xml:space="preserve">10.065089225769</t>
   </si>
   <si>
     <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95311832427979</t>
+    <t xml:space="preserve">9.95311641693115</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595361709595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3512401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7286319732666</t>
+    <t xml:space="preserve">10.351243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7286310195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.6996011734009</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">10.3388013839722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4093027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4632148742676</t>
+    <t xml:space="preserve">10.4093017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4632139205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.4010066986084</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415424346924</t>
+    <t xml:space="preserve">10.6415405273438</t>
   </si>
   <si>
     <t xml:space="preserve">10.8323097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7659559249878</t>
+    <t xml:space="preserve">10.7659549713135</t>
   </si>
   <si>
     <t xml:space="preserve">10.9318408966064</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">10.4300374984741</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5295686721802</t>
+    <t xml:space="preserve">10.5295677185059</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024141311646</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553876876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.230975151062</t>
+    <t xml:space="preserve">10.3553886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2309741973877</t>
   </si>
   <si>
     <t xml:space="preserve">10.4175968170166</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6000699996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7493667602539</t>
+    <t xml:space="preserve">10.6000690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7493677139282</t>
   </si>
   <si>
     <t xml:space="preserve">10.6871604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6913070678711</t>
+    <t xml:space="preserve">10.6913080215454</t>
   </si>
   <si>
     <t xml:space="preserve">10.7949848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6664237976074</t>
+    <t xml:space="preserve">10.6664247512817</t>
   </si>
   <si>
     <t xml:space="preserve">10.5337162017822</t>
@@ -2906,19 +2906,19 @@
     <t xml:space="preserve">10.0733842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4341850280762</t>
+    <t xml:space="preserve">10.4341840744019</t>
   </si>
   <si>
     <t xml:space="preserve">10.2392702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180637359619</t>
+    <t xml:space="preserve">10.3180646896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1936502456665</t>
+    <t xml:space="preserve">10.1936521530151</t>
   </si>
   <si>
     <t xml:space="preserve">10.0319128036499</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">9.46790313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44716835021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72087955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5591402053833</t>
+    <t xml:space="preserve">9.44716739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7208776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55913925170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.71258449554443</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">9.74990749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82041072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0277652740479</t>
+    <t xml:space="preserve">9.82040882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0277662277222</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1604747772217</t>
+    <t xml:space="preserve">9.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1604738235474</t>
   </si>
   <si>
     <t xml:space="preserve">10.1729164123535</t>
@@ -2975,22 +2975,22 @@
     <t xml:space="preserve">10.0775308609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1521797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99044227600098</t>
+    <t xml:space="preserve">10.1521787643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1065616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96141052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59646415710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53425598144531</t>
+    <t xml:space="preserve">9.96141147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59646511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53425693511963</t>
   </si>
   <si>
     <t xml:space="preserve">9.67111206054688</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">10.3844194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3470964431763</t>
+    <t xml:space="preserve">10.3470945358276</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1272974014282</t>
+    <t xml:space="preserve">9.94482326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1272964477539</t>
   </si>
   <si>
     <t xml:space="preserve">10.2683000564575</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">10.5212745666504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.807427406311</t>
+    <t xml:space="preserve">10.8074254989624</t>
   </si>
   <si>
     <t xml:space="preserve">10.7576608657837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8779268264771</t>
+    <t xml:space="preserve">10.8779277801514</t>
   </si>
   <si>
     <t xml:space="preserve">10.8945159912109</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8157205581665</t>
+    <t xml:space="preserve">10.8157215118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733114242554</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">10.9857530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8737812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8447494506836</t>
+    <t xml:space="preserve">10.873779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8447504043579</t>
   </si>
   <si>
     <t xml:space="preserve">10.9774580001831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1350517272949</t>
+    <t xml:space="preserve">11.1350507736206</t>
   </si>
   <si>
     <t xml:space="preserve">11.1018733978271</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">11.35484790802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1474905014038</t>
+    <t xml:space="preserve">11.1474924087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">11.520733833313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4792623519897</t>
+    <t xml:space="preserve">11.4792633056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3507013320923</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">11.1889629364014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1682281494141</t>
+    <t xml:space="preserve">11.1682262420654</t>
   </si>
   <si>
     <t xml:space="preserve">11.1226081848145</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">11.0355195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9442806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452182769775</t>
+    <t xml:space="preserve">10.944281578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452192306519</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926416397095</t>
+    <t xml:space="preserve">11.2926397323608</t>
   </si>
   <si>
     <t xml:space="preserve">11.9935064315796</t>
@@ -3143,22 +3143,22 @@
     <t xml:space="preserve">12.1303615570068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4455442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.263069152832</t>
+    <t xml:space="preserve">12.4455432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2630701065063</t>
   </si>
   <si>
     <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5948400497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4870157241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584547042847</t>
+    <t xml:space="preserve">12.594841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4870138168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584537506104</t>
   </si>
   <si>
     <t xml:space="preserve">12.1718330383301</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">12.3169832229614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1842756271362</t>
+    <t xml:space="preserve">12.1842746734619</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
@@ -3185,28 +3185,28 @@
     <t xml:space="preserve">12.2879524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0640068054199</t>
+    <t xml:space="preserve">12.0640077590942</t>
   </si>
   <si>
     <t xml:space="preserve">12.0349779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9230060577393</t>
+    <t xml:space="preserve">11.9230041503906</t>
   </si>
   <si>
     <t xml:space="preserve">11.9810647964478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2755107879639</t>
+    <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
     <t xml:space="preserve">12.163537979126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2174510955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3543081283569</t>
+    <t xml:space="preserve">12.2174501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3543062210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.1759805679321</t>
@@ -3215,25 +3215,25 @@
     <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9769172668457</t>
+    <t xml:space="preserve">11.9769191741943</t>
   </si>
   <si>
     <t xml:space="preserve">11.9437398910522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.117919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.78200340271</t>
+    <t xml:space="preserve">12.1179208755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820024490356</t>
   </si>
   <si>
     <t xml:space="preserve">11.6244115829468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5580577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5539112091064</t>
+    <t xml:space="preserve">11.5580587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5539102554321</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626731872559</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">11.5746459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834098815918</t>
+    <t xml:space="preserve">11.4834089279175</t>
   </si>
   <si>
     <t xml:space="preserve">11.5912342071533</t>
@@ -3263,22 +3263,22 @@
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981218338013</t>
+    <t xml:space="preserve">11.7985925674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981227874756</t>
   </si>
   <si>
     <t xml:space="preserve">11.9520359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.545615196228</t>
+    <t xml:space="preserve">11.5456161499023</t>
   </si>
   <si>
     <t xml:space="preserve">11.5331745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4543790817261</t>
+    <t xml:space="preserve">11.4543800354004</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751148223877</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8193264007568</t>
+    <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
     <t xml:space="preserve">11.9064168930054</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142412185669</t>
+    <t xml:space="preserve">12.0142402648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6949129104614</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">11.6617364883423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7322368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7446784973145</t>
+    <t xml:space="preserve">11.7322378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7446775436401</t>
   </si>
   <si>
     <t xml:space="preserve">11.6534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.711501121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7654132843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5787925720215</t>
+    <t xml:space="preserve">11.7115020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7654142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5787935256958</t>
   </si>
   <si>
     <t xml:space="preserve">11.164080619812</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">11.2055511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3050832748413</t>
+    <t xml:space="preserve">11.305082321167</t>
   </si>
   <si>
     <t xml:space="preserve">11.4129085540771</t>
@@ -3347,31 +3347,31 @@
     <t xml:space="preserve">11.3631429672241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3382596969604</t>
+    <t xml:space="preserve">11.3382606506348</t>
   </si>
   <si>
     <t xml:space="preserve">11.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4917030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5124387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5622053146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.524881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5953817367554</t>
+    <t xml:space="preserve">11.3714361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4917020797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5124397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6451482772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5622043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5953807830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5497636795044</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">11.6658821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9312992095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8607997894287</t>
+    <t xml:space="preserve">11.931300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8607978820801</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409997940063</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">11.806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.026683807373</t>
+    <t xml:space="preserve">12.0266828536987</t>
   </si>
   <si>
     <t xml:space="preserve">12.1013307571411</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">12.2423343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1967153549194</t>
+    <t xml:space="preserve">12.1967163085938</t>
   </si>
   <si>
     <t xml:space="preserve">12.3086891174316</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">12.1510972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4787216186523</t>
+    <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0391244888306</t>
@@ -3422,10 +3422,10 @@
     <t xml:space="preserve">11.8690919876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220674514771</t>
+    <t xml:space="preserve">11.7778558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.2215986251831</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">12.333571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7151079177856</t>
+    <t xml:space="preserve">12.7151069641113</t>
   </si>
   <si>
     <t xml:space="preserve">12.5367803573608</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7773151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8975811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2293519973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.382794380188</t>
+    <t xml:space="preserve">12.7773141860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8975801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2293510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3827962875366</t>
   </si>
   <si>
     <t xml:space="preserve">13.453296661377</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">13.4698858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201192855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3496179580688</t>
+    <t xml:space="preserve">13.4201202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3496189117432</t>
   </si>
   <si>
     <t xml:space="preserve">13.2252054214478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4781789779663</t>
+    <t xml:space="preserve">13.4781808853149</t>
   </si>
   <si>
     <t xml:space="preserve">13.2169103622437</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">13.1588506698608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1837329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583808898926</t>
+    <t xml:space="preserve">13.1837339401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583827972412</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629972457886</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">13.2625284194946</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9514932632446</t>
+    <t xml:space="preserve">12.9514942169189</t>
   </si>
   <si>
     <t xml:space="preserve">12.8644037246704</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">12.8685522079468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7607250213623</t>
+    <t xml:space="preserve">12.7607259750366</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939023971558</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">12.9349050521851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312282562256</t>
+    <t xml:space="preserve">12.8312273025513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482843399048</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5741052627563</t>
+    <t xml:space="preserve">12.574104309082</t>
   </si>
   <si>
     <t xml:space="preserve">12.6611948013306</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">12.9763774871826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2376470565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1215257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0095548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2417936325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3081474304199</t>
+    <t xml:space="preserve">13.2376461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1215267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.241792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3081464767456</t>
   </si>
   <si>
     <t xml:space="preserve">12.9431991577148</t>
@@ -3560,52 +3560,52 @@
     <t xml:space="preserve">12.6446056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9722309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888172149658</t>
+    <t xml:space="preserve">12.9722299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888181686401</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9929656982422</t>
+    <t xml:space="preserve">13.1090841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9929647445679</t>
   </si>
   <si>
     <t xml:space="preserve">13.2044696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1173782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.602593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7850675582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523590087891</t>
+    <t xml:space="preserve">13.1173791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6025943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7850685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523580551147</t>
   </si>
   <si>
     <t xml:space="preserve">13.8016557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7726249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7975091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9219236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9799833297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.627477645874</t>
+    <t xml:space="preserve">13.7726259231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7975082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9219226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9799823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.7270059585571</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">13.69797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004864692688</t>
+    <t xml:space="preserve">14.0048656463623</t>
   </si>
   <si>
     <t xml:space="preserve">13.7643308639526</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">14.2246627807617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3324880599976</t>
+    <t xml:space="preserve">14.3324890136719</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712194442749</t>
@@ -3638,58 +3638,58 @@
     <t xml:space="preserve">14.1583089828491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2951650619507</t>
+    <t xml:space="preserve">14.2951641082764</t>
   </si>
   <si>
     <t xml:space="preserve">14.3532247543335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2619876861572</t>
+    <t xml:space="preserve">14.2619867324829</t>
   </si>
   <si>
     <t xml:space="preserve">14.3076076507568</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2163696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.12513256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3006258010864</t>
+    <t xml:space="preserve">14.2163686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3006267547607</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255071640015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8597526550293</t>
+    <t xml:space="preserve">13.859751701355</t>
   </si>
   <si>
     <t xml:space="preserve">13.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819042205811</t>
+    <t xml:space="preserve">13.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4359970092773</t>
+    <t xml:space="preserve">13.2605028152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.435996055603</t>
   </si>
   <si>
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834573745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5515661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9068365097046</t>
+    <t xml:space="preserve">13.1834554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5515670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9068355560303</t>
   </si>
   <si>
     <t xml:space="preserve">13.645733833313</t>
@@ -3698,16 +3698,16 @@
     <t xml:space="preserve">13.4488382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4188756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3974742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4445581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258836746216</t>
+    <t xml:space="preserve">13.4188766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3974733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4445571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258846282959</t>
   </si>
   <si>
     <t xml:space="preserve">12.9951219558716</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">12.7639837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9651594161987</t>
+    <t xml:space="preserve">12.965160369873</t>
   </si>
   <si>
     <t xml:space="preserve">12.9523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2433824539185</t>
+    <t xml:space="preserve">12.9095144271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2433815002441</t>
   </si>
   <si>
     <t xml:space="preserve">13.2519416809082</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">13.4531183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4873609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6842565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562227249146</t>
+    <t xml:space="preserve">13.487361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6842575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562217712402</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589496612549</t>
@@ -3761,28 +3761,28 @@
     <t xml:space="preserve">13.5301647186279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6114902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2861852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0293645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1920166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1320924758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7597026824951</t>
+    <t xml:space="preserve">13.6114912033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2861862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0293655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1920175552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1320934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7597017288208</t>
   </si>
   <si>
     <t xml:space="preserve">12.3616304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5499668121338</t>
+    <t xml:space="preserve">12.5499658584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900417327881</t>
@@ -3791,34 +3791,34 @@
     <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740951538086</t>
+    <t xml:space="preserve">12.6740970611572</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.900954246521</t>
+    <t xml:space="preserve">12.9009532928467</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682628631592</t>
+    <t xml:space="preserve">12.7682647705078</t>
   </si>
   <si>
     <t xml:space="preserve">12.849591255188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.055046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6157722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7784233093262</t>
+    <t xml:space="preserve">13.0550470352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6157712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7784252166748</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799764633179</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">13.4103155136108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2776260375977</t>
+    <t xml:space="preserve">13.277624130249</t>
   </si>
   <si>
     <t xml:space="preserve">12.4301166534424</t>
@@ -3839,16 +3839,16 @@
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768239974976</t>
+    <t xml:space="preserve">12.7768249511719</t>
   </si>
   <si>
     <t xml:space="preserve">12.0234842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0363264083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8351488113403</t>
+    <t xml:space="preserve">12.0363254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.835147857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.9576787948608</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">10.8720712661743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5339241027832</t>
+    <t xml:space="preserve">10.5339250564575</t>
   </si>
   <si>
     <t xml:space="preserve">11.783784866333</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">11.826587677002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8950748443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9892425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106420516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0277643203735</t>
+    <t xml:space="preserve">11.895073890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157232284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9892416000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0106430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">11.9849605560303</t>
@@ -3893,16 +3893,16 @@
     <t xml:space="preserve">11.8479900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9507179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.314546585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1989774703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2332220077515</t>
+    <t xml:space="preserve">11.9507188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3145475387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1989784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
     <t xml:space="preserve">12.3102674484253</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">12.26318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9549980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1262130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188276290894</t>
+    <t xml:space="preserve">11.9549989700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1262121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188285827637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203798294067</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">11.9464378356934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9079141616821</t>
+    <t xml:space="preserve">11.9079151153564</t>
   </si>
   <si>
     <t xml:space="preserve">11.9036340713501</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834093093872</t>
+    <t xml:space="preserve">12.0834083557129</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705671310425</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">11.2444610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.253023147583</t>
+    <t xml:space="preserve">11.2530221939087</t>
   </si>
   <si>
     <t xml:space="preserve">11.2787046432495</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">11.407114982605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1716957092285</t>
+    <t xml:space="preserve">11.1716947555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.3771524429321</t>
@@ -3974,28 +3974,28 @@
     <t xml:space="preserve">10.5724487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0545272827148</t>
+    <t xml:space="preserve">10.0545263290405</t>
   </si>
   <si>
     <t xml:space="preserve">10.080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4868402481079</t>
+    <t xml:space="preserve">10.4868412017822</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6109704971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8292684555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035850524902</t>
+    <t xml:space="preserve">10.5938491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6109714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8292675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035860061646</t>
   </si>
   <si>
     <t xml:space="preserve">10.7693433761597</t>
@@ -4004,22 +4004,22 @@
     <t xml:space="preserve">11.1668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1403942108154</t>
+    <t xml:space="preserve">11.1403951644897</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158643722534</t>
+    <t xml:space="preserve">11.5158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969728469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6351308822632</t>
+    <t xml:space="preserve">11.6969738006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6351318359375</t>
   </si>
   <si>
     <t xml:space="preserve">11.560037612915</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">11.1580648422241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4893598556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.37451171875</t>
+    <t xml:space="preserve">11.4893608093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3745107650757</t>
   </si>
   <si>
     <t xml:space="preserve">11.1050567626953</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">10.6368246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62968349456787</t>
+    <t xml:space="preserve">9.62968254089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.14378261566162</t>
@@ -4049,34 +4049,34 @@
     <t xml:space="preserve">9.13053035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74453258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44415760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57667541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89030265808105</t>
+    <t xml:space="preserve">9.74453163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44415664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.92122364044189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1818437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4645500183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4689683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.477801322937</t>
+    <t xml:space="preserve">10.1818447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4645509719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191568374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4689674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4778022766113</t>
   </si>
   <si>
     <t xml:space="preserve">10.3894567489624</t>
@@ -4088,22 +4088,22 @@
     <t xml:space="preserve">10.1244201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260160446167</t>
+    <t xml:space="preserve">10.226016998291</t>
   </si>
   <si>
     <t xml:space="preserve">9.9786491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2171821594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7384223937988</t>
+    <t xml:space="preserve">10.2171812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7384214401245</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3585357666016</t>
+    <t xml:space="preserve">10.3585367202759</t>
   </si>
   <si>
     <t xml:space="preserve">9.83287906646729</t>
@@ -4115,25 +4115,25 @@
     <t xml:space="preserve">10.0449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5661487579346</t>
+    <t xml:space="preserve">10.5661478042603</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0934991836548</t>
+    <t xml:space="preserve">10.0934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758295059204</t>
+    <t xml:space="preserve">10.0758285522461</t>
   </si>
   <si>
     <t xml:space="preserve">10.0007352828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6809968948364</t>
+    <t xml:space="preserve">10.6809978485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.6500759124756</t>
@@ -4142,19 +4142,19 @@
     <t xml:space="preserve">10.999041557312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8841924667358</t>
+    <t xml:space="preserve">10.8841915130615</t>
   </si>
   <si>
     <t xml:space="preserve">10.8267679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.707501411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5573129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062795639038</t>
+    <t xml:space="preserve">10.7075004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5573139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062786102295</t>
   </si>
   <si>
     <t xml:space="preserve">10.959285736084</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">10.7781772613525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5308103561401</t>
+    <t xml:space="preserve">10.5308094024658</t>
   </si>
   <si>
     <t xml:space="preserve">10.6544942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.146505355835</t>
+    <t xml:space="preserve">10.1465063095093</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
@@ -4181,37 +4181,37 @@
     <t xml:space="preserve">10.0051527023315</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93447589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4529914855957</t>
+    <t xml:space="preserve">9.93447685241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45299053192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54133701324463</t>
+    <t xml:space="preserve">9.54133796691895</t>
   </si>
   <si>
     <t xml:space="preserve">9.55458927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42648887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84613132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55017280578613</t>
+    <t xml:space="preserve">9.42648792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55017185211182</t>
   </si>
   <si>
     <t xml:space="preserve">9.58109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59876251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86380004882812</t>
+    <t xml:space="preserve">9.59876155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
     <t xml:space="preserve">10.8797750473022</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">11.3215036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371995925903</t>
+    <t xml:space="preserve">10.9372005462646</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259210586548</t>
@@ -4250,22 +4250,22 @@
     <t xml:space="preserve">11.02112865448</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8488540649414</t>
+    <t xml:space="preserve">10.8488550186157</t>
   </si>
   <si>
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1889848709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8471612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5379505157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9460353851318</t>
+    <t xml:space="preserve">11.188985824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8471603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5379514694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9460344314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.9548692703247</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">10.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239482879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2464094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2331590652466</t>
+    <t xml:space="preserve">10.9239473342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.246410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2331581115723</t>
   </si>
   <si>
     <t xml:space="preserve">11.2110710144043</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">11.6572179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.962010383606</t>
+    <t xml:space="preserve">11.9620094299316</t>
   </si>
   <si>
     <t xml:space="preserve">12.0591897964478</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">12.1431188583374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0503559112549</t>
+    <t xml:space="preserve">12.0503568649292</t>
   </si>
   <si>
     <t xml:space="preserve">12.1961269378662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3949031829834</t>
+    <t xml:space="preserve">12.3949041366577</t>
   </si>
   <si>
     <t xml:space="preserve">12.1607885360718</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">12.6201858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6246042251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6908626556396</t>
+    <t xml:space="preserve">12.3772344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6246032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6908617019653</t>
   </si>
   <si>
     <t xml:space="preserve">12.7527046203613</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">12.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9205617904663</t>
+    <t xml:space="preserve">12.920560836792</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514827728271</t>
@@ -4346,19 +4346,19 @@
     <t xml:space="preserve">13.2518577575684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1811819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2827777862549</t>
+    <t xml:space="preserve">13.1811809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2827796936035</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.441801071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743198394775</t>
+    <t xml:space="preserve">13.4418020248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743188858032</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285488128662</t>
@@ -4367,10 +4367,10 @@
     <t xml:space="preserve">13.3578729629517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6405792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6494131088257</t>
+    <t xml:space="preserve">13.6405782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6494140625</t>
   </si>
   <si>
     <t xml:space="preserve">13.9144506454468</t>
@@ -4379,16 +4379,16 @@
     <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5522327423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6008234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7465944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6759166717529</t>
+    <t xml:space="preserve">13.5522336959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6008243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6759176254272</t>
   </si>
   <si>
     <t xml:space="preserve">13.7730979919434</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188680648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1414260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3534555435181</t>
+    <t xml:space="preserve">13.9188690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1414251327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3534545898438</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">13.5831537246704</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8349390029907</t>
+    <t xml:space="preserve">13.834939956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.7112560272217</t>
@@ -4424,22 +4424,22 @@
     <t xml:space="preserve">13.8658599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1883220672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5947122573853</t>
+    <t xml:space="preserve">14.1883230209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5947132110596</t>
   </si>
   <si>
     <t xml:space="preserve">14.4710273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5726280212402</t>
+    <t xml:space="preserve">14.5726270675659</t>
   </si>
   <si>
     <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8685855865479</t>
+    <t xml:space="preserve">14.8685836791992</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
@@ -4457,25 +4457,25 @@
     <t xml:space="preserve">14.6653900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3429269790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5196180343628</t>
+    <t xml:space="preserve">14.3429279327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5196189880371</t>
   </si>
   <si>
     <t xml:space="preserve">14.3385095596313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1485662460327</t>
+    <t xml:space="preserve">14.148567199707</t>
   </si>
   <si>
     <t xml:space="preserve">14.0955591201782</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4489431381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5107841491699</t>
+    <t xml:space="preserve">14.4489421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5107831954956</t>
   </si>
   <si>
     <t xml:space="preserve">14.4312725067139</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">14.5328712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5814599990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9790172576904</t>
+    <t xml:space="preserve">14.52845287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5814609527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9790163040161</t>
   </si>
   <si>
     <t xml:space="preserve">14.9392614364624</t>
@@ -4499,13 +4499,13 @@
     <t xml:space="preserve">14.8553333282471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.009937286377</t>
+    <t xml:space="preserve">15.0099382400513</t>
   </si>
   <si>
     <t xml:space="preserve">14.6609716415405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6918916702271</t>
+    <t xml:space="preserve">14.6918926239014</t>
   </si>
   <si>
     <t xml:space="preserve">14.568208694458</t>
@@ -4514,16 +4514,16 @@
     <t xml:space="preserve">14.9701814651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7714042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6433029174805</t>
+    <t xml:space="preserve">14.7714033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6433038711548</t>
   </si>
   <si>
     <t xml:space="preserve">13.9453716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1397323608398</t>
+    <t xml:space="preserve">14.1397314071655</t>
   </si>
   <si>
     <t xml:space="preserve">13.963041305542</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">14.444525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2236614227295</t>
+    <t xml:space="preserve">14.2236604690552</t>
   </si>
   <si>
     <t xml:space="preserve">14.3473443984985</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">14.2810859680176</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2501630783081</t>
+    <t xml:space="preserve">14.2501640319824</t>
   </si>
   <si>
     <t xml:space="preserve">14.3650140762329</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402982711792</t>
+    <t xml:space="preserve">12.2402992248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.4523296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5026140213013</t>
+    <t xml:space="preserve">11.502613067627</t>
   </si>
   <si>
     <t xml:space="preserve">11.7455635070801</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">12.3153924942017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4169912338257</t>
+    <t xml:space="preserve">12.4169902801514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0238523483276</t>
+    <t xml:space="preserve">12.0238513946533</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4604,28 +4604,28 @@
     <t xml:space="preserve">12.4920845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2933073043823</t>
+    <t xml:space="preserve">12.293306350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579689025879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0636081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3728189468384</t>
+    <t xml:space="preserve">12.0636072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3728179931641</t>
   </si>
   <si>
     <t xml:space="preserve">12.6025171279907</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7306184768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0795831680298</t>
+    <t xml:space="preserve">12.7306175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5141706466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0795841217041</t>
   </si>
   <si>
     <t xml:space="preserve">12.5848474502563</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">12.5892648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5362567901611</t>
+    <t xml:space="preserve">12.5362577438354</t>
   </si>
   <si>
     <t xml:space="preserve">12.3065595626831</t>
@@ -4655,13 +4655,13 @@
     <t xml:space="preserve">11.7588148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1121978759766</t>
+    <t xml:space="preserve">12.1121988296509</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9399251937866</t>
+    <t xml:space="preserve">11.9399242401123</t>
   </si>
   <si>
     <t xml:space="preserve">11.8824987411499</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343799591064</t>
+    <t xml:space="preserve">11.0343809127808</t>
   </si>
   <si>
     <t xml:space="preserve">11.2199058532715</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.30748462677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638666152954</t>
+    <t xml:space="preserve">11.0638675689697</t>
   </si>
   <si>
     <t xml:space="preserve">11.2753086090088</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">11.3856248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4361867904663</t>
+    <t xml:space="preserve">11.436185836792</t>
   </si>
   <si>
     <t xml:space="preserve">11.6522245407104</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">11.5832767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913463592529</t>
+    <t xml:space="preserve">11.4913454055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.4959421157837</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">11.4499769210815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4591693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7533473968506</t>
+    <t xml:space="preserve">11.4591703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7533483505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6935930252075</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">11.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0041131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9949188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0960426330566</t>
+    <t xml:space="preserve">11.0041122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9949197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.096043586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.1833772659302</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">11.2890977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0868511199951</t>
+    <t xml:space="preserve">11.0868501663208</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4683628082275</t>
+    <t xml:space="preserve">11.4683637619019</t>
   </si>
   <si>
     <t xml:space="preserve">11.8131036758423</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">12.1486501693726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3279161453247</t>
+    <t xml:space="preserve">12.3187217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3279151916504</t>
   </si>
   <si>
     <t xml:space="preserve">12.5117769241333</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.3784770965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5301637649536</t>
+    <t xml:space="preserve">12.5301628112793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6358833312988</t>
@@ -4832,19 +4832,19 @@
     <t xml:space="preserve">12.9760274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4428281784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255661010742</t>
+    <t xml:space="preserve">12.7645864486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4428291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255670547485</t>
   </si>
   <si>
     <t xml:space="preserve">12.4750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2385368347168</t>
+    <t xml:space="preserve">11.2385358810425</t>
   </si>
   <si>
     <t xml:space="preserve">12.0383338928223</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">11.964789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9555959701538</t>
+    <t xml:space="preserve">11.9555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5005388259888</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">11.6016626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5510997772217</t>
+    <t xml:space="preserve">11.551100730896</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143280029297</t>
@@ -4877,19 +4877,19 @@
     <t xml:space="preserve">11.5786800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7073831558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625408172607</t>
+    <t xml:space="preserve">11.7073822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625417709351</t>
   </si>
   <si>
     <t xml:space="preserve">11.7441549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6384353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465040206909</t>
+    <t xml:space="preserve">11.6384344100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465049743652</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855243682861</t>
@@ -4898,19 +4898,19 @@
     <t xml:space="preserve">11.7487516403198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6154518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9489545822144</t>
+    <t xml:space="preserve">11.6154527664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.94895362854</t>
   </si>
   <si>
     <t xml:space="preserve">10.7558994293213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.870813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570232391357</t>
+    <t xml:space="preserve">10.8708124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570241928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.8478298187256</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">10.889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7283210754395</t>
+    <t xml:space="preserve">10.7283201217651</t>
   </si>
   <si>
     <t xml:space="preserve">10.8294439315796</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">10.6915483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6547765731812</t>
+    <t xml:space="preserve">10.6547756195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7329168319702</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">10.6271963119507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858287811279</t>
+    <t xml:space="preserve">10.5858278274536</t>
   </si>
   <si>
     <t xml:space="preserve">10.287052154541</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">10.1445598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1215772628784</t>
+    <t xml:space="preserve">10.1215782165527</t>
   </si>
   <si>
     <t xml:space="preserve">9.91932964324951</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">9.99747085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79522228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399631500244</t>
+    <t xml:space="preserve">9.79522323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399621963501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721391677856</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">9.90094375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96989154815674</t>
+    <t xml:space="preserve">9.96989250183105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1951217651367</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">10.043436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0848045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0388402938843</t>
+    <t xml:space="preserve">10.0848054885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.03883934021</t>
   </si>
   <si>
     <t xml:space="preserve">10.057225227356</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">10.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629457473755</t>
+    <t xml:space="preserve">10.1629467010498</t>
   </si>
   <si>
     <t xml:space="preserve">10.2181043624878</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">11.0454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3948183059692</t>
+    <t xml:space="preserve">11.3948192596436</t>
   </si>
   <si>
     <t xml:space="preserve">11.5097322463989</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">11.0592708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9995164871216</t>
+    <t xml:space="preserve">10.9995155334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9903221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477283477783</t>
+    <t xml:space="preserve">10.9903230667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477293014526</t>
   </si>
   <si>
     <t xml:space="preserve">11.3672389984131</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">11.5970659255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7763319015503</t>
+    <t xml:space="preserve">11.776330947876</t>
   </si>
   <si>
     <t xml:space="preserve">11.8866481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3646879196167</t>
+    <t xml:space="preserve">12.3646869659424</t>
   </si>
   <si>
     <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4290399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.401460647583</t>
+    <t xml:space="preserve">12.4290390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4014596939087</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3692836761475</t>
+    <t xml:space="preserve">12.3692846298218</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554944992065</t>
@@ -5099,7 +5099,7 @@
     <t xml:space="preserve">12.5485486984253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2497749328613</t>
+    <t xml:space="preserve">12.249773979187</t>
   </si>
   <si>
     <t xml:space="preserve">12.5393571853638</t>
@@ -5111,25 +5111,25 @@
     <t xml:space="preserve">12.6404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.456618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7507972717285</t>
+    <t xml:space="preserve">12.4566192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7507963180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.6680593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8473243713379</t>
+    <t xml:space="preserve">12.8473253250122</t>
   </si>
   <si>
     <t xml:space="preserve">12.870306968689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9024829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7783756256104</t>
+    <t xml:space="preserve">12.9024820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7783765792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.8105525970459</t>
@@ -5138,16 +5138,16 @@
     <t xml:space="preserve">12.7094278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6174983978271</t>
+    <t xml:space="preserve">12.6174974441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.5577421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8381319046021</t>
+    <t xml:space="preserve">12.6588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8381309509277</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819499969482</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">11.8544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8452796936035</t>
+    <t xml:space="preserve">11.8452787399292</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705099105835</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">12.1348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0888948440552</t>
+    <t xml:space="preserve">12.0888957977295</t>
   </si>
   <si>
     <t xml:space="preserve">11.9326124191284</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">11.8085069656372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8958396911621</t>
+    <t xml:space="preserve">11.8958406448364</t>
   </si>
   <si>
     <t xml:space="preserve">12.0107536315918</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">12.194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1532468795776</t>
+    <t xml:space="preserve">12.153247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.1854228973389</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">12.0934915542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808271408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1578435897827</t>
+    <t xml:space="preserve">12.1808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.157844543457</t>
   </si>
   <si>
     <t xml:space="preserve">12.2957391738892</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">12.3922672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6266899108887</t>
+    <t xml:space="preserve">12.626690864563</t>
   </si>
   <si>
     <t xml:space="preserve">12.6220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.833535194397</t>
+    <t xml:space="preserve">12.8335342407227</t>
   </si>
   <si>
     <t xml:space="preserve">12.9162721633911</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">12.4796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2242412567139</t>
+    <t xml:space="preserve">13.2242403030396</t>
   </si>
   <si>
     <t xml:space="preserve">13.136905670166</t>
@@ -5270,7 +5270,7 @@
     <t xml:space="preserve">13.2012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.270206451416</t>
+    <t xml:space="preserve">13.2702054977417</t>
   </si>
   <si>
     <t xml:space="preserve">13.1736783981323</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">12.6726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6818494796753</t>
+    <t xml:space="preserve">12.681848526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9990100860596</t>
+    <t xml:space="preserve">12.9990110397339</t>
   </si>
   <si>
     <t xml:space="preserve">13.0265893936157</t>
@@ -5309,16 +5309,16 @@
     <t xml:space="preserve">12.8611135482788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0541687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587644577026</t>
+    <t xml:space="preserve">13.0541677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.058765411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2748022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460990905762</t>
+    <t xml:space="preserve">13.1461000442505</t>
   </si>
   <si>
     <t xml:space="preserve">13.233434677124</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7804222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.92751121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9045276641846</t>
+    <t xml:space="preserve">13.780421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9275102615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9045286178589</t>
   </si>
   <si>
     <t xml:space="preserve">14.0102481842041</t>
@@ -6270,6 +6270,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.7549991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7800006866455</t>
   </si>
 </sst>
 </file>
@@ -71296,7 +71299,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494444444</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>2306108</v>
@@ -71317,6 +71320,32 @@
         <v>2085</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6510648148</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>2259464</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>18.9500007629395</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>18.6499996185303</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>18.7800006866455</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048892974854</t>
+    <t xml:space="preserve">5.32048845291138</t>
   </si>
   <si>
     <t xml:space="preserve">5.17209434509277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13951921463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26257848739624</t>
+    <t xml:space="preserve">5.13951969146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26257753372192</t>
   </si>
   <si>
     <t xml:space="preserve">5.1322808265686</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">5.266197681427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31325006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381046295166</t>
+    <t xml:space="preserve">5.31325054168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1938099861145</t>
   </si>
   <si>
     <t xml:space="preserve">5.04541540145874</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">4.92959547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07437086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65814161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101392745972</t>
+    <t xml:space="preserve">5.07437038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101440429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578884124756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05265474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21190690994263</t>
+    <t xml:space="preserve">5.05265426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21190643310547</t>
   </si>
   <si>
     <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12504196166992</t>
+    <t xml:space="preserve">5.14675855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12504243850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.88978290557861</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">4.79205846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138784408569</t>
+    <t xml:space="preserve">4.74138832092285</t>
   </si>
   <si>
     <t xml:space="preserve">4.56765794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3432559967041</t>
+    <t xml:space="preserve">4.34325551986694</t>
   </si>
   <si>
     <t xml:space="preserve">4.45545721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48441123962402</t>
+    <t xml:space="preserve">4.48441171646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.58213520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78482055664062</t>
+    <t xml:space="preserve">4.78482007980347</t>
   </si>
   <si>
     <t xml:space="preserve">4.73414897918701</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71243286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187294006348</t>
+    <t xml:space="preserve">4.7667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71243333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187198638916</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996938705444</t>
@@ -152,67 +152,67 @@
     <t xml:space="preserve">4.88616323471069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00922203063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09246683120728</t>
+    <t xml:space="preserve">5.00922155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09246730804443</t>
   </si>
   <si>
     <t xml:space="preserve">5.10332584381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16847515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95493078231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84273052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120183944702</t>
+    <t xml:space="preserve">5.16847467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95493125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8427300453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120136260986</t>
   </si>
   <si>
     <t xml:space="preserve">5.06713199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08884811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00560235977173</t>
+    <t xml:space="preserve">5.08884906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00560188293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.99112510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19019079208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23362350463867</t>
+    <t xml:space="preserve">5.1901912689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23362398147583</t>
   </si>
   <si>
     <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.128662109375</t>
+    <t xml:space="preserve">5.12866163253784</t>
   </si>
   <si>
     <t xml:space="preserve">5.02008008956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98026657104492</t>
+    <t xml:space="preserve">4.98026752471924</t>
   </si>
   <si>
     <t xml:space="preserve">4.94769287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9730281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369976043701</t>
+    <t xml:space="preserve">4.97302770614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369928359985</t>
   </si>
   <si>
     <t xml:space="preserve">5.11418390274048</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">5.12142276763916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544111251831</t>
+    <t xml:space="preserve">5.33544158935547</t>
   </si>
   <si>
     <t xml:space="preserve">5.23406314849854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.282874584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27161121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23030853271484</t>
+    <t xml:space="preserve">5.28287506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27161073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.230309009552</t>
   </si>
   <si>
     <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.391761302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26410150527954</t>
+    <t xml:space="preserve">5.33168649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39176177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26410102844238</t>
   </si>
   <si>
     <t xml:space="preserve">5.25659227371216</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">5.09889459609985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96748018264771</t>
+    <t xml:space="preserve">4.96747922897339</t>
   </si>
   <si>
     <t xml:space="preserve">4.88863086700439</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">4.79100847244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472520828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70089530944824</t>
+    <t xml:space="preserve">4.76472473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7008957862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.96372509002686</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">4.90740442276001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77598905563354</t>
+    <t xml:space="preserve">4.7759895324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84357452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91866827011108</t>
+    <t xml:space="preserve">4.84357404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91866874694824</t>
   </si>
   <si>
     <t xml:space="preserve">4.986252784729</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">5.01629018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92617750167847</t>
+    <t xml:space="preserve">4.92617845535278</t>
   </si>
   <si>
     <t xml:space="preserve">4.95246076583862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97123432159424</t>
+    <t xml:space="preserve">4.97123384475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.85483837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.877366065979</t>
+    <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
     <t xml:space="preserve">4.8022723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44182062149048</t>
+    <t xml:space="preserve">4.62204647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197118759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44182014465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.44932985305786</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">4.7534613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73093271255493</t>
+    <t xml:space="preserve">4.73093318939209</t>
   </si>
   <si>
     <t xml:space="preserve">4.80602693557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97498941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1301794052124</t>
+    <t xml:space="preserve">4.97498846054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13017988204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.39676380157471</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">4.33668899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3930082321167</t>
+    <t xml:space="preserve">4.39300918579102</t>
   </si>
   <si>
     <t xml:space="preserve">4.17523622512817</t>
@@ -383,43 +383,43 @@
     <t xml:space="preserve">3.94244384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2653489112854</t>
+    <t xml:space="preserve">4.26534986495972</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1902551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20151901245117</t>
+    <t xml:space="preserve">4.19025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20151805877686</t>
   </si>
   <si>
     <t xml:space="preserve">4.23531103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31040573120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25032949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24657583236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27661275863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638690948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9311797618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83731198310852</t>
+    <t xml:space="preserve">4.31040525436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25032997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2465763092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27661371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638643264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93118023872375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98750066757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8373122215271</t>
   </si>
   <si>
     <t xml:space="preserve">3.93868899345398</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.93493437767029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97248220443726</t>
+    <t xml:space="preserve">3.97248196601868</t>
   </si>
   <si>
     <t xml:space="preserve">3.95746278762817</t>
@@ -440,31 +440,31 @@
     <t xml:space="preserve">3.94619846343994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99876427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604742050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348184585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7547082901001</t>
+    <t xml:space="preserve">3.99876475334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8298032283783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604813575745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348208427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470876693726</t>
   </si>
   <si>
     <t xml:space="preserve">4.05133056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07010459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04382133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01378393173218</t>
+    <t xml:space="preserve">4.07010412216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04382181167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01378345489502</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
@@ -473,46 +473,46 @@
     <t xml:space="preserve">4.09263181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13768863677979</t>
+    <t xml:space="preserve">4.13768911361694</t>
   </si>
   <si>
     <t xml:space="preserve">4.12267017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05508518218994</t>
+    <t xml:space="preserve">4.0550856590271</t>
   </si>
   <si>
     <t xml:space="preserve">4.07385921478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03255605697632</t>
+    <t xml:space="preserve">4.03255653381348</t>
   </si>
   <si>
     <t xml:space="preserve">3.91240644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82229399681091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478404998779</t>
+    <t xml:space="preserve">3.82229351997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478357315063</t>
   </si>
   <si>
     <t xml:space="preserve">3.90489649772644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90114283561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8898777961731</t>
+    <t xml:space="preserve">3.90114235877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987874984741</t>
   </si>
   <si>
     <t xml:space="preserve">3.81102895736694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8861231803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738726615906</t>
+    <t xml:space="preserve">3.88612413406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738774299622</t>
   </si>
   <si>
     <t xml:space="preserve">3.88236904144287</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">3.87110543251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85233068466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850102424622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7622184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6120297908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601001739502</t>
+    <t xml:space="preserve">3.85233163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221799850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61202955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79601049423218</t>
   </si>
   <si>
     <t xml:space="preserve">3.96121764183044</t>
@@ -545,100 +545,100 @@
     <t xml:space="preserve">3.97999143600464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02504825592041</t>
+    <t xml:space="preserve">4.02504777908325</t>
   </si>
   <si>
     <t xml:space="preserve">3.96497273445129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01753902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0888786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14519786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99501013755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355689048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474593162537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727481842041</t>
+    <t xml:space="preserve">4.01753807067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08887767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14519834518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99500966072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742514610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727434158325</t>
   </si>
   <si>
     <t xml:space="preserve">3.79225587844849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75170493125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056587219238</t>
+    <t xml:space="preserve">3.75170469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518443107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6405656337738</t>
   </si>
   <si>
     <t xml:space="preserve">3.60452055931091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54444479942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843712806702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5414412021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55645990371704</t>
+    <t xml:space="preserve">3.54444456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843760490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54144167900085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55645966529846</t>
   </si>
   <si>
     <t xml:space="preserve">3.60001492500305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4708526134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66459584236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64507150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66910123825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748651504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968982696533</t>
+    <t xml:space="preserve">3.47085237503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799982070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66459608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64507174491882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66910171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748627662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73969006538391</t>
   </si>
   <si>
     <t xml:space="preserve">3.84857702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14144325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1038966178894</t>
+    <t xml:space="preserve">4.14144372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10389614105225</t>
   </si>
   <si>
     <t xml:space="preserve">4.01002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006624221802</t>
+    <t xml:space="preserve">4.04006719589233</t>
   </si>
   <si>
     <t xml:space="preserve">4.11516094207764</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.00251913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07761335372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16772651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895343780518</t>
+    <t xml:space="preserve">4.07761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16772699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270853042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895391464233</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512306213379</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.18274593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22029209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23906564712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16021776199341</t>
+    <t xml:space="preserve">4.22029161453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2390661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16021680831909</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642431259155</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">4.06259441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631114959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13393402099609</t>
+    <t xml:space="preserve">4.03631210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13393449783325</t>
   </si>
   <si>
     <t xml:space="preserve">4.28787708282471</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">4.30289649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33293390274048</t>
+    <t xml:space="preserve">4.33293342590332</t>
   </si>
   <si>
     <t xml:space="preserve">4.46810340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69338607788086</t>
+    <t xml:space="preserve">4.44557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6370644569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6933856010437</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342348098755</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">4.81353664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79851770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72717809677124</t>
+    <t xml:space="preserve">4.79851722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72717761993408</t>
   </si>
   <si>
     <t xml:space="preserve">4.85108327865601</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">4.82104539871216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83606433868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07056093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198163986206</t>
+    <t xml:space="preserve">4.83606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07056140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198211669922</t>
   </si>
   <si>
     <t xml:space="preserve">5.0744891166687</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">5.12947559356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16875219345093</t>
+    <t xml:space="preserve">5.16875171661377</t>
   </si>
   <si>
     <t xml:space="preserve">5.23552131652832</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">5.33371257781982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34156799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3769154548645</t>
+    <t xml:space="preserve">5.3415675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37691593170166</t>
   </si>
   <si>
     <t xml:space="preserve">5.20410060882568</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">5.28265285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20017337799072</t>
+    <t xml:space="preserve">5.20017290115356</t>
   </si>
   <si>
     <t xml:space="preserve">5.22373867034912</t>
@@ -788,76 +788,76 @@
     <t xml:space="preserve">5.29050827026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26694202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36906099319458</t>
+    <t xml:space="preserve">5.26694250106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36906051635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.34942197799683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38477039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.219810962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25515937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32585668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512321472168</t>
+    <t xml:space="preserve">5.3847713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21981048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25515985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32585716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25123167037964</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650085449219</t>
+    <t xml:space="preserve">5.43975782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650133132935</t>
   </si>
   <si>
     <t xml:space="preserve">5.57722473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5418758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63221073150635</t>
+    <t xml:space="preserve">5.54187536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63221120834351</t>
   </si>
   <si>
     <t xml:space="preserve">5.62435626983643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50652742385864</t>
+    <t xml:space="preserve">5.5065279006958</t>
   </si>
   <si>
     <t xml:space="preserve">5.53794813156128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62042808532715</t>
+    <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
     <t xml:space="preserve">5.55365896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50260019302368</t>
+    <t xml:space="preserve">5.50260066986084</t>
   </si>
   <si>
     <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52223777770996</t>
+    <t xml:space="preserve">5.52223825454712</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257362365723</t>
@@ -869,37 +869,37 @@
     <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572431564331</t>
+    <t xml:space="preserve">5.87572383880615</t>
   </si>
   <si>
     <t xml:space="preserve">5.71076393127441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73433017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64006662368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65970420837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72647380828857</t>
+    <t xml:space="preserve">5.73432970046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64006614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65970468521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72647428512573</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67148780822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65577697753906</t>
+    <t xml:space="preserve">5.67148733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65577745437622</t>
   </si>
   <si>
     <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77360486984253</t>
+    <t xml:space="preserve">5.77360534667969</t>
   </si>
   <si>
     <t xml:space="preserve">5.86786842346191</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">5.8403754234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82859230041504</t>
+    <t xml:space="preserve">5.8285927772522</t>
   </si>
   <si>
     <t xml:space="preserve">5.87179660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93463850021362</t>
+    <t xml:space="preserve">5.93463802337646</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90714502334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7971715927124</t>
+    <t xml:space="preserve">5.90714454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79717206954956</t>
   </si>
   <si>
     <t xml:space="preserve">5.70290899276733</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">5.78931617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89143419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78538799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324388504028</t>
+    <t xml:space="preserve">5.89143466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538846969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324340820312</t>
   </si>
   <si>
     <t xml:space="preserve">5.70683622360229</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">5.56936979293823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46725082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66755962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903347015381</t>
+    <t xml:space="preserve">5.46725130081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66756010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903394699097</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">5.39262628555298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45939636230469</t>
+    <t xml:space="preserve">5.45939540863037</t>
   </si>
   <si>
     <t xml:space="preserve">5.75004005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76182270050049</t>
+    <t xml:space="preserve">5.76182222366333</t>
   </si>
   <si>
     <t xml:space="preserve">5.73040199279785</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80895376205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91500043869019</t>
+    <t xml:space="preserve">5.80895471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91499996185303</t>
   </si>
   <si>
     <t xml:space="preserve">5.87965154647827</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">5.85215854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84430265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001300811768</t>
+    <t xml:space="preserve">5.84430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001348495483</t>
   </si>
   <si>
     <t xml:space="preserve">5.84823083877563</t>
@@ -1016,49 +1016,49 @@
     <t xml:space="preserve">5.72254657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69505310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6636323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64792203903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71861934661865</t>
+    <t xml:space="preserve">5.6950535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363286972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64792156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71861886978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.83252000808716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76575088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11530876159668</t>
+    <t xml:space="preserve">5.76575040817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11530828475952</t>
   </si>
   <si>
     <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26063060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24492025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31168937683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776262283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29990816116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29205179214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670289993286</t>
+    <t xml:space="preserve">6.26063108444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24492073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31168985366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29990720748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29205226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670337677002</t>
   </si>
   <si>
     <t xml:space="preserve">6.23706531524658</t>
@@ -1067,193 +1067,193 @@
     <t xml:space="preserve">6.25277614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2645583152771</t>
+    <t xml:space="preserve">6.26455879211426</t>
   </si>
   <si>
     <t xml:space="preserve">6.20171642303467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23313760757446</t>
+    <t xml:space="preserve">6.23313808441162</t>
   </si>
   <si>
     <t xml:space="preserve">6.06032228469849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00926351547241</t>
+    <t xml:space="preserve">6.00926303863525</t>
   </si>
   <si>
     <t xml:space="preserve">6.1270923614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28026914596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37060356140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37453174591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33132886886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39809799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58662462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53949213027954</t>
+    <t xml:space="preserve">6.22528314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28026866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37060403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37453269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33132839202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3980975151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58662414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339279174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53949165344238</t>
   </si>
   <si>
     <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63768339157104</t>
+    <t xml:space="preserve">6.63768243789673</t>
   </si>
   <si>
     <t xml:space="preserve">6.5630578994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71230745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83013582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79086017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77907752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75551271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85762882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81049776077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70445203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375520706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116945266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40356922149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58031272888184</t>
+    <t xml:space="preserve">6.71230792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8301362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79086065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088626861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77907800674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86155652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81049823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99902391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287286758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40356874465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031177520752</t>
   </si>
   <si>
     <t xml:space="preserve">7.5410361289978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.552818775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641111373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351703643799</t>
+    <t xml:space="preserve">7.55281972885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351608276367</t>
   </si>
   <si>
     <t xml:space="preserve">7.66671991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80418682098389</t>
+    <t xml:space="preserve">7.8041877746582</t>
   </si>
   <si>
     <t xml:space="preserve">7.75705575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88666725158691</t>
+    <t xml:space="preserve">7.88666820526123</t>
   </si>
   <si>
     <t xml:space="preserve">7.93379831314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91808843612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310148239136</t>
+    <t xml:space="preserve">7.91808748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454923629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310052871704</t>
   </si>
   <si>
     <t xml:space="preserve">7.87488317489624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951761245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50804328918457</t>
+    <t xml:space="preserve">7.74056005477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50804376602173</t>
   </si>
   <si>
     <t xml:space="preserve">7.53161096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23782348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610326766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410772323608</t>
+    <t xml:space="preserve">7.23782253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2661018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410820007324</t>
   </si>
   <si>
     <t xml:space="preserve">7.30066537857056</t>
@@ -1262,37 +1262,37 @@
     <t xml:space="preserve">7.49076271057129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59131002426147</t>
+    <t xml:space="preserve">7.59130907058716</t>
   </si>
   <si>
     <t xml:space="preserve">7.69656991958618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77355146408081</t>
+    <t xml:space="preserve">7.77355051040649</t>
   </si>
   <si>
     <t xml:space="preserve">7.80025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77826452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.833251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94950866699219</t>
+    <t xml:space="preserve">7.77826547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83325099945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94950771331787</t>
   </si>
   <si>
     <t xml:space="preserve">7.96914720535278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52061367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8301100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96129179000854</t>
+    <t xml:space="preserve">7.52061223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83010911941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9612922668457</t>
   </si>
   <si>
     <t xml:space="preserve">8.08304786682129</t>
@@ -1310,28 +1310,28 @@
     <t xml:space="preserve">8.04377174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11054039001465</t>
+    <t xml:space="preserve">8.11054134368896</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07126522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86702966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83953523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69499826431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71070861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158296585083</t>
+    <t xml:space="preserve">8.07126426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86702871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83953428268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71070957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158201217651</t>
   </si>
   <si>
     <t xml:space="preserve">7.67300367355347</t>
@@ -1343,19 +1343,19 @@
     <t xml:space="preserve">7.65572357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85524654388428</t>
+    <t xml:space="preserve">7.85524463653564</t>
   </si>
   <si>
     <t xml:space="preserve">7.59445142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65415191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602212905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56146097183228</t>
+    <t xml:space="preserve">7.65415239334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602355957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56146001815796</t>
   </si>
   <si>
     <t xml:space="preserve">7.75312805175781</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">7.83168029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82696723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554510116577</t>
+    <t xml:space="preserve">7.82696628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554605484009</t>
   </si>
   <si>
     <t xml:space="preserve">8.03898048400879</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942710876465</t>
+    <t xml:space="preserve">7.96942806243896</t>
   </si>
   <si>
     <t xml:space="preserve">7.97427940368652</t>
@@ -1388,52 +1388,52 @@
     <t xml:space="preserve">8.00986480712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07456398010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560285568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14816093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21690464019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93222332000732</t>
+    <t xml:space="preserve">8.07456493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93222522735596</t>
   </si>
   <si>
     <t xml:space="preserve">7.86105442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85943698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87884712219238</t>
+    <t xml:space="preserve">7.85943794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">7.86752462387085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43726968765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41947650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125646591187</t>
+    <t xml:space="preserve">7.43726921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41947746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125598907471</t>
   </si>
   <si>
     <t xml:space="preserve">7.19626140594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43079948425293</t>
+    <t xml:space="preserve">7.43079900741577</t>
   </si>
   <si>
     <t xml:space="preserve">7.40491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4259467124939</t>
+    <t xml:space="preserve">7.42594718933105</t>
   </si>
   <si>
     <t xml:space="preserve">7.10568237304688</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">6.43441867828369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84849977493286</t>
+    <t xml:space="preserve">6.84849882125854</t>
   </si>
   <si>
     <t xml:space="preserve">6.91805171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10729885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92613887786865</t>
+    <t xml:space="preserve">7.10729932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92613935470581</t>
   </si>
   <si>
     <t xml:space="preserve">6.81776666641235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22214221954346</t>
+    <t xml:space="preserve">7.2221417427063</t>
   </si>
   <si>
     <t xml:space="preserve">7.20111513137817</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1477370262146</t>
+    <t xml:space="preserve">7.14773654937744</t>
   </si>
   <si>
     <t xml:space="preserve">7.26419687271118</t>
@@ -1478,37 +1478,37 @@
     <t xml:space="preserve">7.58607959747314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415592193604</t>
+    <t xml:space="preserve">7.70415687561035</t>
   </si>
   <si>
     <t xml:space="preserve">7.66857242584229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78179693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7073917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62975263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69445323944092</t>
+    <t xml:space="preserve">7.63784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179597854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70739078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62975168228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6944522857666</t>
   </si>
   <si>
     <t xml:space="preserve">7.65886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69768619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223415374756</t>
+    <t xml:space="preserve">7.69768714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223510742188</t>
   </si>
   <si>
     <t xml:space="preserve">7.83032274246216</t>
@@ -1517,28 +1517,28 @@
     <t xml:space="preserve">7.95163440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05353736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089332580566</t>
+    <t xml:space="preserve">8.05353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089237213135</t>
   </si>
   <si>
     <t xml:space="preserve">7.95001697540283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07294845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06809425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19264316558838</t>
+    <t xml:space="preserve">8.07294750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06809520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19264221191406</t>
   </si>
   <si>
     <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969192504883</t>
+    <t xml:space="preserve">8.28969097137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.29778003692627</t>
@@ -1556,19 +1556,19 @@
     <t xml:space="preserve">8.23307991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21286201477051</t>
+    <t xml:space="preserve">8.21286010742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.28564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24925422668457</t>
+    <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.12794208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24521064758301</t>
+    <t xml:space="preserve">8.24521160125732</t>
   </si>
   <si>
     <t xml:space="preserve">8.13198566436768</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14007472991943</t>
+    <t xml:space="preserve">8.14007377624512</t>
   </si>
   <si>
     <t xml:space="preserve">8.08588695526123</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">8.12389755249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20881652832031</t>
+    <t xml:space="preserve">8.20881748199463</t>
   </si>
   <si>
     <t xml:space="preserve">8.2249927520752</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">8.30991172790527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22903537750244</t>
+    <t xml:space="preserve">8.22903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">8.1885986328125</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">8.60510540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77898502349854</t>
+    <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
     <t xml:space="preserve">8.77089881896973</t>
@@ -1628,43 +1628,43 @@
     <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95691204071045</t>
+    <t xml:space="preserve">8.95691108703613</t>
   </si>
   <si>
     <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04183101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11866092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22379970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32084941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784233093262</t>
+    <t xml:space="preserve">9.04182910919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11866188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33297920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32085037231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2278413772583</t>
   </si>
   <si>
     <t xml:space="preserve">9.41790008544922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44620418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61604404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3127613067627</t>
+    <t xml:space="preserve">9.44620513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61604309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48260021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31276226043701</t>
   </si>
   <si>
     <t xml:space="preserve">9.39768028259277</t>
@@ -1682,85 +1682,85 @@
     <t xml:space="preserve">9.11461925506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67789268493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05191993713379</t>
+    <t xml:space="preserve">8.67789363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65362930297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05192089080811</t>
   </si>
   <si>
     <t xml:space="preserve">7.89987421035767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88531732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11985492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287485122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24155235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067743301392</t>
+    <t xml:space="preserve">7.88531637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1198558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83355665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24155187606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1606764793396</t>
   </si>
   <si>
     <t xml:space="preserve">7.05715656280518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080888748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3386025428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770643234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59093236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92251873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106334686279</t>
+    <t xml:space="preserve">7.32080984115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595659255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47770738601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59093141555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92251968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106430053711</t>
   </si>
   <si>
     <t xml:space="preserve">7.76562213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78503322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98721933364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00824737548828</t>
+    <t xml:space="preserve">7.78503227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.987220287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0082483291626</t>
   </si>
   <si>
     <t xml:space="preserve">7.94516468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96619319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369941711426</t>
+    <t xml:space="preserve">7.96619272232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88370037078857</t>
   </si>
   <si>
     <t xml:space="preserve">7.78017902374268</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">7.78988456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238584518433</t>
+    <t xml:space="preserve">7.76238775253296</t>
   </si>
   <si>
     <t xml:space="preserve">7.74297857284546</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">7.68474721908569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85134983062744</t>
+    <t xml:space="preserve">7.85134887695312</t>
   </si>
   <si>
     <t xml:space="preserve">7.74944639205933</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">7.22537660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24963855743408</t>
+    <t xml:space="preserve">7.2496395111084</t>
   </si>
   <si>
     <t xml:space="preserve">7.4421215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49388313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26581430435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890592575073</t>
+    <t xml:space="preserve">7.49388217926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26581382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890640258789</t>
   </si>
   <si>
     <t xml:space="preserve">7.35477733612061</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0523042678833</t>
+    <t xml:space="preserve">7.05230474472046</t>
   </si>
   <si>
     <t xml:space="preserve">6.93099117279053</t>
@@ -1835,25 +1835,25 @@
     <t xml:space="preserve">7.09921169281006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07980155944824</t>
+    <t xml:space="preserve">7.07980060577393</t>
   </si>
   <si>
     <t xml:space="preserve">6.99245643615723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23831748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875375747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58446311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62328100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828546524048</t>
+    <t xml:space="preserve">7.23831701278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62328195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828737258911</t>
   </si>
   <si>
     <t xml:space="preserve">7.55534696578979</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">7.64430952072144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93707847595215</t>
+    <t xml:space="preserve">7.93707752227783</t>
   </si>
   <si>
     <t xml:space="preserve">7.90634489059448</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046503067017</t>
+    <t xml:space="preserve">7.88046550750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.8578200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.673424243927</t>
+    <t xml:space="preserve">7.67342472076416</t>
   </si>
   <si>
     <t xml:space="preserve">7.57152271270752</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80767726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00339508056641</t>
+    <t xml:space="preserve">7.80767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00339412689209</t>
   </si>
   <si>
     <t xml:space="preserve">8.3988733291626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2371244430542</t>
+    <t xml:space="preserve">8.23712253570557</t>
   </si>
   <si>
     <t xml:space="preserve">8.45144271850586</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">8.38674354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26947402954102</t>
+    <t xml:space="preserve">8.26947498321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.18051052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26138687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3503475189209</t>
+    <t xml:space="preserve">8.26138591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559894561768</t>
@@ -1943,25 +1943,25 @@
     <t xml:space="preserve">9.15909862518311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18740558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02161121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07418060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17931747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23188591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34915542602539</t>
+    <t xml:space="preserve">9.18740463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0216121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07418155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17931842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2318868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34915637969971</t>
   </si>
   <si>
     <t xml:space="preserve">9.38150691986084</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">9.26828098297119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36532974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59178066253662</t>
+    <t xml:space="preserve">9.36533069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5917797088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.40576839447021</t>
@@ -1991,31 +1991,31 @@
     <t xml:space="preserve">9.56751728057861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45833587646484</t>
+    <t xml:space="preserve">9.45833683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.4664249420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47451210021973</t>
+    <t xml:space="preserve">9.47451114654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163745880127</t>
+    <t xml:space="preserve">10.016375541687</t>
   </si>
   <si>
     <t xml:space="preserve">9.83036231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84943866729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79552745819092</t>
+    <t xml:space="preserve">10.036060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84943962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7955265045166</t>
   </si>
   <si>
     <t xml:space="preserve">9.98629379272461</t>
@@ -2030,22 +2030,22 @@
     <t xml:space="preserve">9.47619724273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40569591522217</t>
+    <t xml:space="preserve">9.40569686889648</t>
   </si>
   <si>
     <t xml:space="preserve">9.18589782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50162124633789</t>
+    <t xml:space="preserve">8.50162029266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.44356250762939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27767658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17150974273682</t>
+    <t xml:space="preserve">8.27767562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1715087890625</t>
   </si>
   <si>
     <t xml:space="preserve">7.96912813186646</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">8.0869083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03880214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6738543510437</t>
+    <t xml:space="preserve">8.0388011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385339736938</t>
   </si>
   <si>
     <t xml:space="preserve">7.69375991821289</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">7.59091138839722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7767014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77172660827637</t>
+    <t xml:space="preserve">7.77670240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77172565460205</t>
   </si>
   <si>
     <t xml:space="preserve">7.70868921279907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7136664390564</t>
+    <t xml:space="preserve">7.71366548538208</t>
   </si>
   <si>
     <t xml:space="preserve">7.70039510726929</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">7.73357248306274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58925104141235</t>
+    <t xml:space="preserve">7.58925199508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.6257472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50299072265625</t>
+    <t xml:space="preserve">7.50299167633057</t>
   </si>
   <si>
     <t xml:space="preserve">7.55109834671021</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">7.72859573364258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82978534698486</t>
+    <t xml:space="preserve">7.82978630065918</t>
   </si>
   <si>
     <t xml:space="preserve">7.9193639755249</t>
@@ -2147,22 +2147,22 @@
     <t xml:space="preserve">7.96249389648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17814445495605</t>
+    <t xml:space="preserve">8.13667392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17814350128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.2196159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60529804229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87901020050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86656951904297</t>
+    <t xml:space="preserve">8.60529899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8790111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86656856536865</t>
   </si>
   <si>
     <t xml:space="preserve">8.54724025726318</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">8.38550090789795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55553245544434</t>
+    <t xml:space="preserve">8.55553340911865</t>
   </si>
   <si>
     <t xml:space="preserve">8.51406288146973</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">8.45600318908691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30670642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48088550567627</t>
+    <t xml:space="preserve">8.30670738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48088645935059</t>
   </si>
   <si>
     <t xml:space="preserve">8.29094696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3232946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06700038909912</t>
+    <t xml:space="preserve">8.32329368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704784393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06700134277344</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283981323242</t>
@@ -2210,40 +2210,40 @@
     <t xml:space="preserve">7.36530733108521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45820140838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57266426086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39184856414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22098588943481</t>
+    <t xml:space="preserve">7.45820236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57266330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39184761047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22098684310913</t>
   </si>
   <si>
     <t xml:space="preserve">7.38355398178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38853073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41839122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25084543228149</t>
+    <t xml:space="preserve">7.38853120803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73191356658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41839075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25084590911865</t>
   </si>
   <si>
     <t xml:space="preserve">7.42502593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06173658370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17951536178589</t>
+    <t xml:space="preserve">7.06173610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17951631546021</t>
   </si>
   <si>
     <t xml:space="preserve">7.31388235092163</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">7.564368724823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4449315071106</t>
+    <t xml:space="preserve">7.44493103027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.76509141921997</t>
@@ -2264,40 +2264,40 @@
     <t xml:space="preserve">7.73854875564575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92765712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77836227416992</t>
+    <t xml:space="preserve">7.92765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77836132049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.82646751403809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989685058594</t>
+    <t xml:space="preserve">7.72030162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258737564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989780426025</t>
   </si>
   <si>
     <t xml:space="preserve">8.18975734710693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89116334915161</t>
+    <t xml:space="preserve">7.89116287231445</t>
   </si>
   <si>
     <t xml:space="preserve">7.81651544570923</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16985130310059</t>
+    <t xml:space="preserve">8.16985034942627</t>
   </si>
   <si>
     <t xml:space="preserve">8.09852027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76343059539795</t>
+    <t xml:space="preserve">7.76343154907227</t>
   </si>
   <si>
     <t xml:space="preserve">7.79660797119141</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">7.97742414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05538845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840829849243</t>
+    <t xml:space="preserve">8.05538940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840925216675</t>
   </si>
   <si>
     <t xml:space="preserve">7.9044337272644</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">8.00064754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02719020843506</t>
+    <t xml:space="preserve">8.02718925476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.65394735336304</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">7.72361946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89614057540894</t>
+    <t xml:space="preserve">7.89613962173462</t>
   </si>
   <si>
     <t xml:space="preserve">8.1267204284668</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17482662200928</t>
+    <t xml:space="preserve">8.17482757568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.33988285064697</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5596809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46014881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44770908355713</t>
+    <t xml:space="preserve">8.55968189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46014976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44770812988281</t>
   </si>
   <si>
     <t xml:space="preserve">8.42697238922119</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">8.63018226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6260347366333</t>
+    <t xml:space="preserve">8.62603569030762</t>
   </si>
   <si>
     <t xml:space="preserve">8.47673892974854</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">8.95780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16516304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13198471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23566246032715</t>
+    <t xml:space="preserve">8.99927711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16516208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13198566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23566341400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.48449230194092</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">9.38496017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51766872406006</t>
+    <t xml:space="preserve">9.51766777038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.73746681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57158184051514</t>
+    <t xml:space="preserve">9.7001428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57158088684082</t>
   </si>
   <si>
     <t xml:space="preserve">9.33934116363525</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">9.23151683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28957557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35178184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38910675048828</t>
+    <t xml:space="preserve">9.28957653045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35178279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">9.19834041595459</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">9.31031227111816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21078014373779</t>
+    <t xml:space="preserve">9.21077919006348</t>
   </si>
   <si>
     <t xml:space="preserve">9.26884078979492</t>
@@ -2474,16 +2474,16 @@
     <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04074859619141</t>
+    <t xml:space="preserve">9.04074764251709</t>
   </si>
   <si>
     <t xml:space="preserve">9.06148433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01586437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05318927764893</t>
+    <t xml:space="preserve">9.01586532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05319023132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.93292331695557</t>
@@ -2507,25 +2507,25 @@
     <t xml:space="preserve">9.58817005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29372406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15272045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25639820098877</t>
+    <t xml:space="preserve">9.29372310638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1527214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25639915466309</t>
   </si>
   <si>
     <t xml:space="preserve">9.15686702728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21492767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11954402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08221912384033</t>
+    <t xml:space="preserve">9.21492862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11954307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08221817016602</t>
   </si>
   <si>
     <t xml:space="preserve">9.09466075897217</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">8.77533149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27298831939697</t>
+    <t xml:space="preserve">9.27298736572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.10710144042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77118396759033</t>
+    <t xml:space="preserve">8.77118492126465</t>
   </si>
   <si>
     <t xml:space="preserve">8.97024726867676</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">9.27713584899902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68770122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14442729949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08636665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05733585357666</t>
+    <t xml:space="preserve">9.68770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1444263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08636569976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05733680725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.99098205566406</t>
@@ -2570,22 +2570,22 @@
     <t xml:space="preserve">9.28128147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89559936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25279426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14994525909424</t>
+    <t xml:space="preserve">8.89559841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25279331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14994430541992</t>
   </si>
   <si>
     <t xml:space="preserve">7.87457418441772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74186706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042453765869</t>
+    <t xml:space="preserve">7.74186611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042501449585</t>
   </si>
   <si>
     <t xml:space="preserve">7.35867166519165</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53256320953369</t>
+    <t xml:space="preserve">6.53256273269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.73797178268433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38990163803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30861759185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12946128845215</t>
+    <t xml:space="preserve">6.38990116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30861806869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12946176528931</t>
   </si>
   <si>
     <t xml:space="preserve">6.24060487747192</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">6.20245122909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19083976745605</t>
+    <t xml:space="preserve">6.1908392906189</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">6.71503591537476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33047103881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85769748687744</t>
+    <t xml:space="preserve">7.3304705619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85769701004028</t>
   </si>
   <si>
     <t xml:space="preserve">6.98542881011963</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">7.59257030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8331036567688</t>
+    <t xml:space="preserve">7.83310461044312</t>
   </si>
   <si>
     <t xml:space="preserve">7.83144521713257</t>
@@ -2663,37 +2663,37 @@
     <t xml:space="preserve">7.92931747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32715272903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21601009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24255228042603</t>
+    <t xml:space="preserve">7.32715368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264528274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21600961685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24255132675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.76977825164795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2641167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067697525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88286828994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07363700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46844387054443</t>
+    <t xml:space="preserve">7.26411771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66224193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88286924362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07363796234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46844291687012</t>
   </si>
   <si>
     <t xml:space="preserve">8.41038513183594</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897769927979</t>
+    <t xml:space="preserve">8.7089786529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232353210449</t>
@@ -2717,19 +2717,19 @@
     <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.294264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20800399780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43111991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4725923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78777408599854</t>
+    <t xml:space="preserve">8.29426383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20800304412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43111896514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47259140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78777313232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.71312522888184</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">8.91218662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00342273712158</t>
+    <t xml:space="preserve">9.0034236907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.34763622283936</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">9.36007690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60475730895996</t>
+    <t xml:space="preserve">9.60475826263428</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973279953003</t>
+    <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
     <t xml:space="preserve">9.94896984100342</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065089225769</t>
+    <t xml:space="preserve">10.0650901794434</t>
   </si>
   <si>
     <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95311641693115</t>
+    <t xml:space="preserve">9.95311737060547</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595361709595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.351243019104</t>
+    <t xml:space="preserve">10.3512420654297</t>
   </si>
   <si>
     <t xml:space="preserve">10.7286310195923</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">10.6996011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6747179031372</t>
+    <t xml:space="preserve">10.6747198104858</t>
   </si>
   <si>
     <t xml:space="preserve">10.3388013839722</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">10.4093017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4632139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4010066986084</t>
+    <t xml:space="preserve">10.4632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498355865479</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">10.633246421814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024141311646</t>
+    <t xml:space="preserve">10.6042165756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295686721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024150848389</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812086105347</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2309741973877</t>
+    <t xml:space="preserve">10.3553895950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4175968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.064549446106</t>
+    <t xml:space="preserve">11.0645484924316</t>
   </si>
   <si>
     <t xml:space="preserve">10.8654880523682</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6000690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7493677139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6871604919434</t>
+    <t xml:space="preserve">10.6000699996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7493667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.687159538269</t>
   </si>
   <si>
     <t xml:space="preserve">10.6913080215454</t>
@@ -2891,16 +2891,16 @@
     <t xml:space="preserve">10.7949848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6664247512817</t>
+    <t xml:space="preserve">10.6664237976074</t>
   </si>
   <si>
     <t xml:space="preserve">10.5337162017822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6249532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751867294312</t>
+    <t xml:space="preserve">10.6249523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751876831055</t>
   </si>
   <si>
     <t xml:space="preserve">10.0733842849731</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">10.4341840744019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2392702102661</t>
+    <t xml:space="preserve">10.2392692565918</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180646896362</t>
@@ -2918,28 +2918,28 @@
     <t xml:space="preserve">10.1895036697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1936521530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0319128036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81626319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83284950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46790313720703</t>
+    <t xml:space="preserve">10.1936511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0319137573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83285045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46790409088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.44716739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7208776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55913925170898</t>
+    <t xml:space="preserve">9.72087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5591402053833</t>
   </si>
   <si>
     <t xml:space="preserve">9.71258449554443</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">9.67940711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74990749359131</t>
+    <t xml:space="preserve">9.74990844726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.82040882110596</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">9.74576091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96970653533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2600049972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3844194412231</t>
+    <t xml:space="preserve">9.96970558166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2600040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3844203948975</t>
   </si>
   <si>
     <t xml:space="preserve">10.3470945358276</t>
@@ -3014,19 +3014,19 @@
     <t xml:space="preserve">10.3346538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94482326507568</t>
+    <t xml:space="preserve">9.94482231140137</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272964477539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2683000564575</t>
+    <t xml:space="preserve">10.2682981491089</t>
   </si>
   <si>
     <t xml:space="preserve">10.5088338851929</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4134492874146</t>
+    <t xml:space="preserve">10.4134483337402</t>
   </si>
   <si>
     <t xml:space="preserve">10.5212745666504</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">10.7576608657837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8779277801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8945159912109</t>
+    <t xml:space="preserve">10.8779268264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8945169448853</t>
   </si>
   <si>
     <t xml:space="preserve">10.9359884262085</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">10.898663520813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8364562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9857530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.873779296875</t>
+    <t xml:space="preserve">10.8364553451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9857521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
     <t xml:space="preserve">10.8447504043579</t>
@@ -3074,28 +3074,28 @@
     <t xml:space="preserve">11.1350507736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1018733978271</t>
+    <t xml:space="preserve">11.1018724441528</t>
   </si>
   <si>
     <t xml:space="preserve">11.1143140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35484790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1474924087524</t>
+    <t xml:space="preserve">11.3548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3921718597412</t>
+    <t xml:space="preserve">11.3921728134155</t>
   </si>
   <si>
     <t xml:space="preserve">11.2843465805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6119709014893</t>
+    <t xml:space="preserve">11.6119699478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.520733833313</t>
@@ -3119,22 +3119,22 @@
     <t xml:space="preserve">11.0355195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452192306519</t>
+    <t xml:space="preserve">10.9442825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452201843262</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926397323608</t>
+    <t xml:space="preserve">11.2926406860352</t>
   </si>
   <si>
     <t xml:space="preserve">11.9935064315796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1096267700195</t>
+    <t xml:space="preserve">12.1096258163452</t>
   </si>
   <si>
     <t xml:space="preserve">12.3999252319336</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">12.1303615570068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4455432891846</t>
+    <t xml:space="preserve">12.4455442428589</t>
   </si>
   <si>
     <t xml:space="preserve">12.2630701065063</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.594841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4870138168335</t>
+    <t xml:space="preserve">12.5948419570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
     <t xml:space="preserve">12.3584537506104</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3377180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1925678253174</t>
+    <t xml:space="preserve">12.337718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1925687789917</t>
   </si>
   <si>
     <t xml:space="preserve">12.0847434997559</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">12.0640077590942</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0349779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230041503906</t>
+    <t xml:space="preserve">12.0349769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9230051040649</t>
   </si>
   <si>
     <t xml:space="preserve">11.9810647964478</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">12.163537979126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2174501419067</t>
+    <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3543062210083</t>
@@ -3215,19 +3215,19 @@
     <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9769191741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9437398910522</t>
+    <t xml:space="preserve">11.97691822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9437408447266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1179208755493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244115829468</t>
+    <t xml:space="preserve">11.7820014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244125366211</t>
   </si>
   <si>
     <t xml:space="preserve">11.5580587387085</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">11.7985925674438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8981227874756</t>
+    <t xml:space="preserve">11.8981237411499</t>
   </si>
   <si>
     <t xml:space="preserve">11.9520359039307</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">11.5456161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5331745147705</t>
+    <t xml:space="preserve">11.5331735610962</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543800354004</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8193273544312</t>
+    <t xml:space="preserve">11.8193264007568</t>
   </si>
   <si>
     <t xml:space="preserve">11.9064168930054</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142402648926</t>
+    <t xml:space="preserve">12.0142412185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6949129104614</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">11.7322378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7446775436401</t>
+    <t xml:space="preserve">11.7446765899658</t>
   </si>
   <si>
     <t xml:space="preserve">11.6534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7115020751953</t>
+    <t xml:space="preserve">11.711501121521</t>
   </si>
   <si>
     <t xml:space="preserve">11.7654142379761</t>
@@ -3332,10 +3332,10 @@
     <t xml:space="preserve">11.2055511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4129085540771</t>
+    <t xml:space="preserve">11.3050832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4129076004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.4336442947388</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">11.3631429672241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3382606506348</t>
+    <t xml:space="preserve">11.3382596969604</t>
   </si>
   <si>
     <t xml:space="preserve">11.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714361190796</t>
+    <t xml:space="preserve">11.3714370727539</t>
   </si>
   <si>
     <t xml:space="preserve">11.4917020797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5124397277832</t>
+    <t xml:space="preserve">11.5124387741089</t>
   </si>
   <si>
     <t xml:space="preserve">11.6451482772827</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">11.5622043609619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248794555664</t>
+    <t xml:space="preserve">11.5248804092407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5953807830811</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">11.931300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8607978820801</t>
+    <t xml:space="preserve">11.8607988357544</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409997940063</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">12.1013307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2133045196533</t>
+    <t xml:space="preserve">12.2133054733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.2423343658447</t>
@@ -3407,34 +3407,34 @@
     <t xml:space="preserve">12.1967163085938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3086891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1510972976685</t>
+    <t xml:space="preserve">12.3086881637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1510982513428</t>
   </si>
   <si>
     <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391244888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8690919876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2215986251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.333571434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7151069641113</t>
+    <t xml:space="preserve">12.0391254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8690929412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2215995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3335704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.715106010437</t>
   </si>
   <si>
     <t xml:space="preserve">12.5367803573608</t>
@@ -3443,13 +3443,13 @@
     <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7773141860962</t>
+    <t xml:space="preserve">12.7773132324219</t>
   </si>
   <si>
     <t xml:space="preserve">12.8975801467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2293510437012</t>
+    <t xml:space="preserve">13.2293519973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.3827962875366</t>
@@ -3461,40 +3461,40 @@
     <t xml:space="preserve">13.5942993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4201202392578</t>
+    <t xml:space="preserve">13.4698848724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4201211929321</t>
   </si>
   <si>
     <t xml:space="preserve">13.3496189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2252054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4781808853149</t>
+    <t xml:space="preserve">13.2252044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4781799316406</t>
   </si>
   <si>
     <t xml:space="preserve">13.2169103622437</t>
   </si>
   <si>
-    <t xml:space="preserve">13.051025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1588506698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1837339401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625284194946</t>
+    <t xml:space="preserve">13.0510244369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1588497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1837348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625293731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514942169189</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">12.8685522079468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7607259750366</t>
+    <t xml:space="preserve">12.7607269287109</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939023971558</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">13.241792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3081464767456</t>
+    <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
     <t xml:space="preserve">12.9431991577148</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8768453598022</t>
+    <t xml:space="preserve">12.8768463134766</t>
   </si>
   <si>
     <t xml:space="preserve">12.9971122741699</t>
@@ -3569,19 +3569,19 @@
     <t xml:space="preserve">13.0302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9929647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2044696807861</t>
+    <t xml:space="preserve">13.1090850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9929656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2044687271118</t>
   </si>
   <si>
     <t xml:space="preserve">13.1173791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6025943756104</t>
+    <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
     <t xml:space="preserve">13.7850685119629</t>
@@ -3593,52 +3593,52 @@
     <t xml:space="preserve">13.8016557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7726259231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7975082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9219226837158</t>
+    <t xml:space="preserve">13.7726268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7975091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9219236373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.9799823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6274766921997</t>
+    <t xml:space="preserve">13.627477645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.7270059585571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.69797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0048656463623</t>
+    <t xml:space="preserve">13.6979780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0048666000366</t>
   </si>
   <si>
     <t xml:space="preserve">13.7643308639526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878095626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2246627807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3324890136719</t>
+    <t xml:space="preserve">14.0878067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.224663734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3324899673462</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712194442749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1583089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2951641082764</t>
+    <t xml:space="preserve">14.1583099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2951650619507</t>
   </si>
   <si>
     <t xml:space="preserve">14.3532247543335</t>
@@ -3647,19 +3647,19 @@
     <t xml:space="preserve">14.2619867324829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163686752319</t>
+    <t xml:space="preserve">14.3076066970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163677215576</t>
   </si>
   <si>
     <t xml:space="preserve">14.1251316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3006267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8255071640015</t>
+    <t xml:space="preserve">14.3006258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8255081176758</t>
   </si>
   <si>
     <t xml:space="preserve">13.859751701355</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834554672241</t>
+    <t xml:space="preserve">13.1834564208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.5515670776367</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9068355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.645733833313</t>
+    <t xml:space="preserve">13.9068365097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6457347869873</t>
   </si>
   <si>
     <t xml:space="preserve">13.4488382339478</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445571899414</t>
+    <t xml:space="preserve">13.4445581436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258846282959</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">12.9095144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433815002441</t>
+    <t xml:space="preserve">13.2433824539185</t>
   </si>
   <si>
     <t xml:space="preserve">13.2519416809082</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">13.4531183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.487361907959</t>
+    <t xml:space="preserve">13.4873609542847</t>
   </si>
   <si>
     <t xml:space="preserve">13.6842575073242</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">13.2861862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0293655395508</t>
+    <t xml:space="preserve">13.0293645858765</t>
   </si>
   <si>
     <t xml:space="preserve">13.1920175552368</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1320934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7597017288208</t>
+    <t xml:space="preserve">13.1320924758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7597026824951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3616304397583</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740970611572</t>
+    <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9009532928467</t>
+    <t xml:space="preserve">12.900954246521</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682647705078</t>
+    <t xml:space="preserve">12.7682638168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.849591255188</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">13.6157712936401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6286134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7784252166748</t>
+    <t xml:space="preserve">13.6286125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7784242630005</t>
   </si>
   <si>
     <t xml:space="preserve">13.6799764633179</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">13.277624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4301166534424</t>
+    <t xml:space="preserve">12.4301156997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768249511719</t>
+    <t xml:space="preserve">12.7768239974976</t>
   </si>
   <si>
     <t xml:space="preserve">12.0234842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0363254547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.835147857666</t>
+    <t xml:space="preserve">12.0363264083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8351488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.9576787948608</t>
@@ -3872,16 +3872,16 @@
     <t xml:space="preserve">11.826587677002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.895073890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157232284546</t>
+    <t xml:space="preserve">11.8950748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157222747803</t>
   </si>
   <si>
     <t xml:space="preserve">11.9892416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0106430053711</t>
+    <t xml:space="preserve">12.0106420516968</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277652740479</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102674484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.26318359375</t>
+    <t xml:space="preserve">12.310266494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2631826400757</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549989700317</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">11.9464378356934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9079151153564</t>
+    <t xml:space="preserve">11.9079141616821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9036340713501</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">11.407114982605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1716947555542</t>
+    <t xml:space="preserve">11.1716957092285</t>
   </si>
   <si>
     <t xml:space="preserve">11.3771524429321</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">10.6109714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8292675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035860061646</t>
+    <t xml:space="preserve">10.8292684555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035850524902</t>
   </si>
   <si>
     <t xml:space="preserve">10.7693433761597</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">11.1668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1403951644897</t>
+    <t xml:space="preserve">11.1403942108154</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158653259277</t>
+    <t xml:space="preserve">11.5158643722534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368246078491</t>
+    <t xml:space="preserve">10.6368255615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.62968254089355</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.13053035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74453163146973</t>
+    <t xml:space="preserve">9.74453258514404</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">10.1818447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4645509719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191568374634</t>
+    <t xml:space="preserve">10.4645500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191558837891</t>
   </si>
   <si>
     <t xml:space="preserve">10.4689674377441</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">10.2171812057495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7384214401245</t>
+    <t xml:space="preserve">10.7384223937988</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3585367202759</t>
+    <t xml:space="preserve">10.3585357666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.83287906646729</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758285522461</t>
+    <t xml:space="preserve">10.0758295059204</t>
   </si>
   <si>
     <t xml:space="preserve">10.0007352828979</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">10.999041557312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8841915130615</t>
+    <t xml:space="preserve">10.8841924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.8267679214478</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">10.5573139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9062786102295</t>
+    <t xml:space="preserve">10.9062795639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902067184448</t>
+    <t xml:space="preserve">10.9902076721191</t>
   </si>
   <si>
     <t xml:space="preserve">10.7781772613525</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">10.6544942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1465063095093</t>
+    <t xml:space="preserve">10.146505355835</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
@@ -4181,10 +4181,10 @@
     <t xml:space="preserve">10.0051527023315</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93447685241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45299053192139</t>
+    <t xml:space="preserve">9.93447589874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4529914855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.58109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59876155853271</t>
+    <t xml:space="preserve">9.59876251220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797750473022</t>
+    <t xml:space="preserve">10.8797740936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.919529914856</t>
@@ -4238,10 +4238,10 @@
     <t xml:space="preserve">10.8046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215036392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9372005462646</t>
+    <t xml:space="preserve">11.3215045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9371995925903</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259210586548</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.188985824585</t>
+    <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
     <t xml:space="preserve">11.8471603393555</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">10.9239473342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.246410369873</t>
+    <t xml:space="preserve">11.2464094161987</t>
   </si>
   <si>
     <t xml:space="preserve">11.2331581115723</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">12.1961269378662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3949041366577</t>
+    <t xml:space="preserve">12.3949031829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.1607885360718</t>
@@ -4325,16 +4325,16 @@
     <t xml:space="preserve">12.6246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908617019653</t>
+    <t xml:space="preserve">12.6908626556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.7527046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8277988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.920560836792</t>
+    <t xml:space="preserve">12.8277978897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9205617904663</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514827728271</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">13.0354108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2518577575684</t>
+    <t xml:space="preserve">13.2518587112427</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2827796936035</t>
+    <t xml:space="preserve">13.2827787399292</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
@@ -4370,19 +4370,19 @@
     <t xml:space="preserve">13.6405782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9144506454468</t>
+    <t xml:space="preserve">13.6494131088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9144515991211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5522336959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6008243560791</t>
+    <t xml:space="preserve">13.5522327423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6008234024048</t>
   </si>
   <si>
     <t xml:space="preserve">13.7465934753418</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188690185547</t>
+    <t xml:space="preserve">13.9188680648804</t>
   </si>
   <si>
     <t xml:space="preserve">13.1414251327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3534545898438</t>
+    <t xml:space="preserve">13.3534555435181</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">13.5345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5831537246704</t>
+    <t xml:space="preserve">13.5831546783447</t>
   </si>
   <si>
     <t xml:space="preserve">13.834939956665</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">14.1883230209351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5947132110596</t>
+    <t xml:space="preserve">14.5947122573853</t>
   </si>
   <si>
     <t xml:space="preserve">14.4710273742676</t>
@@ -4439,19 +4439,19 @@
     <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8685836791992</t>
+    <t xml:space="preserve">14.8685846328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7669868469238</t>
+    <t xml:space="preserve">14.7669878005981</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095623016357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7934913635254</t>
+    <t xml:space="preserve">14.7934904098511</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">14.5814609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9790163040161</t>
+    <t xml:space="preserve">14.9790172576904</t>
   </si>
   <si>
     <t xml:space="preserve">14.9392614364624</t>
@@ -4499,13 +4499,13 @@
     <t xml:space="preserve">14.8553333282471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0099382400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6918926239014</t>
+    <t xml:space="preserve">15.009937286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6609725952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6918916702271</t>
   </si>
   <si>
     <t xml:space="preserve">14.568208694458</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">14.9701814651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7714033126831</t>
+    <t xml:space="preserve">14.7714042663574</t>
   </si>
   <si>
     <t xml:space="preserve">14.6433038711548</t>
@@ -4559,10 +4559,10 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402992248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4523296356201</t>
+    <t xml:space="preserve">12.2402982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4523286819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.502613067627</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500919342041</t>
+    <t xml:space="preserve">12.5009183883667</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">12.5141706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0795841217041</t>
+    <t xml:space="preserve">13.0795831680298</t>
   </si>
   <si>
     <t xml:space="preserve">12.5848474502563</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">12.5406742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1298666000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7588148117065</t>
+    <t xml:space="preserve">12.1298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7588157653809</t>
   </si>
   <si>
     <t xml:space="preserve">12.1121988296509</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343809127808</t>
+    <t xml:space="preserve">11.0343799591064</t>
   </si>
   <si>
     <t xml:space="preserve">11.2199058532715</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.0653009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2950000762939</t>
+    <t xml:space="preserve">11.2949991226196</t>
   </si>
   <si>
     <t xml:space="preserve">11.0873880386353</t>
@@ -71325,7 +71325,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6510648148</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>2259464</v>
@@ -71346,6 +71346,32 @@
         <v>2086</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494444444</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>1895438</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>19.0400009155273</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>18.7450008392334</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>18.8150005340576</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>19.0300006866455</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>2024</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="2088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="2089">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35306310653687</t>
+    <t xml:space="preserve">5.35306262969971</t>
   </si>
   <si>
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13951921463013</t>
+    <t xml:space="preserve">5.32048845291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209339141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951969146729</t>
   </si>
   <si>
     <t xml:space="preserve">5.26257848739624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1322808265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26619863510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31324911117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1938099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959499359131</t>
+    <t xml:space="preserve">5.13228130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.266197681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31325006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0454158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959594726562</t>
   </si>
   <si>
     <t xml:space="preserve">5.07437086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101440429688</t>
+    <t xml:space="preserve">4.65814256668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101345062256</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05265474319458</t>
+    <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.21190738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04903507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14675903320312</t>
+    <t xml:space="preserve">5.0490345954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14675855636597</t>
   </si>
   <si>
     <t xml:space="preserve">5.16485548019409</t>
@@ -110,40 +110,40 @@
     <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138784408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56765842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34325551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45545625686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441171646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213472366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78482103347778</t>
+    <t xml:space="preserve">4.74138689041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56765699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34325647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45545673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213520050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78482007980347</t>
   </si>
   <si>
     <t xml:space="preserve">4.73414945602417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81377458572388</t>
+    <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.7667236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71243190765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187198638916</t>
+    <t xml:space="preserve">4.71243333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996891021729</t>
@@ -152,49 +152,49 @@
     <t xml:space="preserve">4.88616275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00922155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09246778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332536697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16847515106201</t>
+    <t xml:space="preserve">5.00922203063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09246730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1684741973877</t>
   </si>
   <si>
     <t xml:space="preserve">4.95493078231812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84273052215576</t>
+    <t xml:space="preserve">4.8427300453186</t>
   </si>
   <si>
     <t xml:space="preserve">4.78120136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06713151931763</t>
+    <t xml:space="preserve">5.06713199615479</t>
   </si>
   <si>
     <t xml:space="preserve">5.08884859085083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00560235977173</t>
+    <t xml:space="preserve">5.00560283660889</t>
   </si>
   <si>
     <t xml:space="preserve">4.99112510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19019079208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23362350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35668230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.128662109375</t>
+    <t xml:space="preserve">5.19019031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23362398147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35668277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12866163253784</t>
   </si>
   <si>
     <t xml:space="preserve">5.02008008956909</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">4.94769239425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97302865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787982940674</t>
+    <t xml:space="preserve">4.9730281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787887573242</t>
   </si>
   <si>
     <t xml:space="preserve">5.02369976043701</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">5.33544111251831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23406362533569</t>
+    <t xml:space="preserve">5.23406410217285</t>
   </si>
   <si>
     <t xml:space="preserve">5.28287506103516</t>
@@ -233,25 +233,25 @@
     <t xml:space="preserve">5.27161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23030948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16647911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33168601989746</t>
+    <t xml:space="preserve">5.230309009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16647958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33168649673462</t>
   </si>
   <si>
     <t xml:space="preserve">5.30164861679077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.391761302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26410150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.256591796875</t>
+    <t xml:space="preserve">5.39176177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2641019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25659227371216</t>
   </si>
   <si>
     <t xml:space="preserve">5.05759239196777</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">4.96747922897339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88862991333008</t>
+    <t xml:space="preserve">4.88863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">4.78725385665894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79100847244263</t>
+    <t xml:space="preserve">4.79100894927979</t>
   </si>
   <si>
     <t xml:space="preserve">4.76472520828247</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96372509002686</t>
+    <t xml:space="preserve">4.9637246131897</t>
   </si>
   <si>
     <t xml:space="preserve">4.90364980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90740394592285</t>
+    <t xml:space="preserve">4.90740442276001</t>
   </si>
   <si>
     <t xml:space="preserve">4.7759895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73844289779663</t>
+    <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357404708862</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">4.91866827011108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.986252784729</t>
+    <t xml:space="preserve">4.98625326156616</t>
   </si>
   <si>
     <t xml:space="preserve">4.97874402999878</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">5.01629066467285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92617797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95246076583862</t>
+    <t xml:space="preserve">4.92617750167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95246124267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.97123384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85483837127686</t>
+    <t xml:space="preserve">4.85483884811401</t>
   </si>
   <si>
     <t xml:space="preserve">4.877366065979</t>
@@ -326,64 +326,64 @@
     <t xml:space="preserve">4.8022723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197023391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44181966781616</t>
+    <t xml:space="preserve">4.62204647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44182109832764</t>
   </si>
   <si>
     <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4568395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56948041915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093366622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80602693557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97498846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13017892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39676380157471</t>
+    <t xml:space="preserve">4.45683908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56947994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7534613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093318939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80602741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97498893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39676427841187</t>
   </si>
   <si>
     <t xml:space="preserve">4.33668851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39300918579102</t>
+    <t xml:space="preserve">4.39300966262817</t>
   </si>
   <si>
     <t xml:space="preserve">4.17523574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10014200210571</t>
+    <t xml:space="preserve">4.10014152526855</t>
   </si>
   <si>
     <t xml:space="preserve">3.87485933303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94244384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26534843444824</t>
+    <t xml:space="preserve">3.94244360923767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534938812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791543960571</t>
@@ -401,55 +401,55 @@
     <t xml:space="preserve">4.31040477752686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25032949447632</t>
+    <t xml:space="preserve">4.25032997131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.24657535552979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27661371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9311797618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750042915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83731198310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9386887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623658180237</t>
+    <t xml:space="preserve">4.27661418914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93118000030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98749995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83731174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93868851661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623610496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97248196601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9461989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9987645149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980275154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604813575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348279953003</t>
+    <t xml:space="preserve">3.9724817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99876403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604789733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348232269287</t>
   </si>
   <si>
     <t xml:space="preserve">3.75470876693726</t>
@@ -458,127 +458,127 @@
     <t xml:space="preserve">4.05133008956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07010412216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04382133483887</t>
+    <t xml:space="preserve">4.07010459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04382085800171</t>
   </si>
   <si>
     <t xml:space="preserve">4.01378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05884027481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09263277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1376895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0550856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385921478271</t>
+    <t xml:space="preserve">4.05883979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09263181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13768863677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12266969680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05508470535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385873794556</t>
   </si>
   <si>
     <t xml:space="preserve">4.03255653381348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91240668296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478333473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90489721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81102871894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88612365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738798141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236880302429</t>
+    <t xml:space="preserve">3.91240644454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9048969745636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114235877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987755775452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81102895736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8861231803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738774299622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236832618713</t>
   </si>
   <si>
     <t xml:space="preserve">3.87110471725464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85233092308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850150108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221823692322</t>
+    <t xml:space="preserve">3.85233068466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221799850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.61202955245972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59550881385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601049423218</t>
+    <t xml:space="preserve">3.59550857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79601001739502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96121788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97999119758606</t>
+    <t xml:space="preserve">3.97999143600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504777908325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96497297286987</t>
+    <t xml:space="preserve">3.96497273445129</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0888786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14519882202148</t>
+    <t xml:space="preserve">4.08887720108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14519834518433</t>
   </si>
   <si>
     <t xml:space="preserve">3.9950098991394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92742514610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474640846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727434158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225564002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170516967773</t>
+    <t xml:space="preserve">3.92742466926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474569320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727505683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225516319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170469284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.73518419265747</t>
@@ -587,82 +587,82 @@
     <t xml:space="preserve">3.64056539535522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60452055931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54444456100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843760490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54144144058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646061897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4708526134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799958229065</t>
+    <t xml:space="preserve">3.60452032089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5444450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5384373664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5414412021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55645990371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47085285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799910545349</t>
   </si>
   <si>
     <t xml:space="preserve">3.66459560394287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64507150650024</t>
+    <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
     <t xml:space="preserve">3.66910099983215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57748603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968958854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1038966178894</t>
+    <t xml:space="preserve">3.57748627662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73968982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857630729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10389566421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006671905518</t>
+    <t xml:space="preserve">4.04006624221802</t>
   </si>
   <si>
     <t xml:space="preserve">4.11516094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00251960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07761335372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16772651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270805358887</t>
+    <t xml:space="preserve">4.00251913070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07761287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16772699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270709991455</t>
   </si>
   <si>
     <t xml:space="preserve">4.14895296096802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18274545669556</t>
+    <t xml:space="preserve">4.08512353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18274593353271</t>
   </si>
   <si>
     <t xml:space="preserve">4.22029256820679</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.2390661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16021776199341</t>
+    <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642431259155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06259441375732</t>
+    <t xml:space="preserve">4.06259489059448</t>
   </si>
   <si>
     <t xml:space="preserve">4.03631162643433</t>
@@ -686,34 +686,34 @@
     <t xml:space="preserve">4.13393449783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28787755966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557428359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6933856010437</t>
+    <t xml:space="preserve">4.28787708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30289602279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69338607788086</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085695266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80978155136108</t>
+    <t xml:space="preserve">4.67085790634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80978202819824</t>
   </si>
   <si>
     <t xml:space="preserve">4.83981990814209</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">4.72717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85108327865601</t>
+    <t xml:space="preserve">4.85108375549316</t>
   </si>
   <si>
     <t xml:space="preserve">4.82104635238647</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">4.83606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07056140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198211669922</t>
+    <t xml:space="preserve">5.07056093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198163986206</t>
   </si>
   <si>
     <t xml:space="preserve">5.07448863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12947559356689</t>
+    <t xml:space="preserve">5.12947511672974</t>
   </si>
   <si>
     <t xml:space="preserve">5.16875171661377</t>
@@ -764,37 +764,37 @@
     <t xml:space="preserve">5.3415675163269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37691497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20410108566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28265237808228</t>
+    <t xml:space="preserve">5.3769154548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20410060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28265285491943</t>
   </si>
   <si>
     <t xml:space="preserve">5.20017242431641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22373819351196</t>
+    <t xml:space="preserve">5.22373867034912</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092287063599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15696859359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29050874710083</t>
+    <t xml:space="preserve">5.15696907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29050827026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.26694250106812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36906099319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34942245483398</t>
+    <t xml:space="preserve">5.36906051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34942197799683</t>
   </si>
   <si>
     <t xml:space="preserve">5.38477087020874</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">5.21588325500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21981143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25515985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32585763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37298822402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43975830078125</t>
+    <t xml:space="preserve">5.219810962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25515937805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978487014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32585716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25123167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3729887008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
     <t xml:space="preserve">5.61650085449219</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">5.50652742385864</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53794813156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62042856216431</t>
+    <t xml:space="preserve">5.53794860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62042903900146</t>
   </si>
   <si>
     <t xml:space="preserve">5.55365896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50259923934937</t>
+    <t xml:space="preserve">5.50259971618652</t>
   </si>
   <si>
     <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52223777770996</t>
+    <t xml:space="preserve">5.52223825454712</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257314682007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69112491607666</t>
+    <t xml:space="preserve">5.69112539291382</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789499282837</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">5.87572383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71076345443726</t>
+    <t xml:space="preserve">5.71076393127441</t>
   </si>
   <si>
     <t xml:space="preserve">5.73432970046997</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">5.64006662368774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65970468521118</t>
+    <t xml:space="preserve">5.65970420837402</t>
   </si>
   <si>
     <t xml:space="preserve">5.72647428512573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68327045440674</t>
+    <t xml:space="preserve">5.6832709312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.67148780822754</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77360582351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86786794662476</t>
+    <t xml:space="preserve">5.773606300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86786890029907</t>
   </si>
   <si>
     <t xml:space="preserve">5.83644771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82466506958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8403754234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82859230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179660797119</t>
+    <t xml:space="preserve">5.82466459274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82859182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179613113403</t>
   </si>
   <si>
     <t xml:space="preserve">5.93463850021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95034837722778</t>
+    <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
     <t xml:space="preserve">5.90714502334595</t>
@@ -932,64 +932,64 @@
     <t xml:space="preserve">5.7971715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70290899276733</t>
+    <t xml:space="preserve">5.70290851593018</t>
   </si>
   <si>
     <t xml:space="preserve">5.78931617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89143419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78538846969604</t>
+    <t xml:space="preserve">5.89143371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538799285889</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324388504028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70683526992798</t>
+    <t xml:space="preserve">5.70683622360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46725082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66756057739258</t>
+    <t xml:space="preserve">5.56936931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46725130081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66756010055542</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41619205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39262580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45939540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75004053115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040199279785</t>
+    <t xml:space="preserve">5.41619157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39262628555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45939588546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75004005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76182222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040246963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.75396776199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80109882354736</t>
+    <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
     <t xml:space="preserve">5.80895471572876</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">5.8521580696106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84430313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001348495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84823036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6950535774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66363191604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64792203903198</t>
+    <t xml:space="preserve">5.84430265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84823083877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69505310058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363286972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64792251586914</t>
   </si>
   <si>
     <t xml:space="preserve">5.71861886978149</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">5.83252048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76574993133545</t>
+    <t xml:space="preserve">5.76575040817261</t>
   </si>
   <si>
     <t xml:space="preserve">6.11530876159668</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26063060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24492120742798</t>
+    <t xml:space="preserve">6.26063108444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24492025375366</t>
   </si>
   <si>
     <t xml:space="preserve">6.31168985366821</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">6.30776214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29990768432617</t>
+    <t xml:space="preserve">6.29990720748901</t>
   </si>
   <si>
     <t xml:space="preserve">6.29205179214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25670337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25277614593506</t>
+    <t xml:space="preserve">6.25670433044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2527756690979</t>
   </si>
   <si>
     <t xml:space="preserve">6.2645583152771</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">6.23313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06032180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00926351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12709188461304</t>
+    <t xml:space="preserve">6.06032228469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926303863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1270923614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.22528219223022</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">6.28026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37060403823853</t>
+    <t xml:space="preserve">6.37060451507568</t>
   </si>
   <si>
     <t xml:space="preserve">6.37453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33132791519165</t>
+    <t xml:space="preserve">6.33132839202881</t>
   </si>
   <si>
     <t xml:space="preserve">6.39809799194336</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">6.45308446884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58662414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339374542236</t>
+    <t xml:space="preserve">6.58662366867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339326858521</t>
   </si>
   <si>
     <t xml:space="preserve">6.53949213027954</t>
@@ -1121,64 +1121,64 @@
     <t xml:space="preserve">6.63768243789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5630578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83013677597046</t>
+    <t xml:space="preserve">6.56305837631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8301362991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.68874168395996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79086017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77907800674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75551080703735</t>
+    <t xml:space="preserve">6.79085969924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77907752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75551176071167</t>
   </si>
   <si>
     <t xml:space="preserve">6.76336669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85762929916382</t>
+    <t xml:space="preserve">6.85762882232666</t>
   </si>
   <si>
     <t xml:space="preserve">6.86155700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70445251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287143707275</t>
+    <t xml:space="preserve">6.81049823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375520706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99902391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.40356922149658</t>
@@ -1190,67 +1190,67 @@
     <t xml:space="preserve">7.54103660583496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55281782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387849807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66671943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8041877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75705575942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8866662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93379926681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91808748245239</t>
+    <t xml:space="preserve">7.552818775177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641111373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66672039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80418729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75705528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88666772842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93379783630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91808843612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.78454828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86310243606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488460540771</t>
+    <t xml:space="preserve">7.86310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87488317489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.74055957794189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65886497497559</t>
+    <t xml:space="preserve">7.65886449813843</t>
   </si>
   <si>
     <t xml:space="preserve">7.31951808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50804424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5316104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23782396316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610279083252</t>
+    <t xml:space="preserve">7.50804281234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53161096572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23782300949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610326766968</t>
   </si>
   <si>
     <t xml:space="preserve">7.24410772323608</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.3006649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49076175689697</t>
+    <t xml:space="preserve">7.49076271057129</t>
   </si>
   <si>
     <t xml:space="preserve">7.59131002426147</t>
@@ -1268,46 +1268,46 @@
     <t xml:space="preserve">7.69656991958618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77355098724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80025911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.833251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94950914382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914768218994</t>
+    <t xml:space="preserve">7.77355146408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826404571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83325052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9495096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914720535278</t>
   </si>
   <si>
     <t xml:space="preserve">7.5206127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83010864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96129179000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08304882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95343685150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04377174377441</t>
+    <t xml:space="preserve">7.83010959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96129035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08304786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165277481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95343732833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0437707901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.11054134368896</t>
@@ -1316,70 +1316,70 @@
     <t xml:space="preserve">8.14589023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07126331329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86702871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83953523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69499778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71070909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158296585083</t>
+    <t xml:space="preserve">8.07126522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86702919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83953475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499826431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71070861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158153533936</t>
   </si>
   <si>
     <t xml:space="preserve">7.67300415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61487579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65572261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85524606704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59445142745972</t>
+    <t xml:space="preserve">7.61487483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65572309494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85524654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59445190429688</t>
   </si>
   <si>
     <t xml:space="preserve">7.65415239334106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59602308273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5614595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7531270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83168125152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554557800293</t>
+    <t xml:space="preserve">7.59602165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56146001815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75312805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83168077468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554605484009</t>
   </si>
   <si>
     <t xml:space="preserve">8.03897953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08750438690186</t>
+    <t xml:space="preserve">8.08750534057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.01633548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942758560181</t>
+    <t xml:space="preserve">7.96942710876465</t>
   </si>
   <si>
     <t xml:space="preserve">7.97427940368652</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">8.00986385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07456398010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560094833374</t>
+    <t xml:space="preserve">8.07456493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560190200806</t>
   </si>
   <si>
     <t xml:space="preserve">8.14816093444824</t>
@@ -1400,37 +1400,37 @@
     <t xml:space="preserve">8.21690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93222379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85943698883057</t>
+    <t xml:space="preserve">7.9322247505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85943651199341</t>
   </si>
   <si>
     <t xml:space="preserve">7.87884664535522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86752367019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41947650909424</t>
+    <t xml:space="preserve">7.86752319335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4194769859314</t>
   </si>
   <si>
     <t xml:space="preserve">7.25125694274902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19626188278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43079948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40491962432861</t>
+    <t xml:space="preserve">7.19626140594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43079900741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40492010116577</t>
   </si>
   <si>
     <t xml:space="preserve">7.4259467124939</t>
@@ -1439,25 +1439,25 @@
     <t xml:space="preserve">7.10568141937256</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59293413162231</t>
+    <t xml:space="preserve">6.59293365478516</t>
   </si>
   <si>
     <t xml:space="preserve">6.43441915512085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84849977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92613887786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81776666641235</t>
+    <t xml:space="preserve">6.8484992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92613840103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81776714324951</t>
   </si>
   <si>
     <t xml:space="preserve">7.22214221954346</t>
@@ -1466,34 +1466,34 @@
     <t xml:space="preserve">7.20111465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1477370262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26419687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681175231934</t>
+    <t xml:space="preserve">7.14773797988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26419734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681318283081</t>
   </si>
   <si>
     <t xml:space="preserve">7.5860800743103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415735244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63783931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7817964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70739269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282402038574</t>
+    <t xml:space="preserve">7.70415687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7073917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282306671143</t>
   </si>
   <si>
     <t xml:space="preserve">7.62975215911865</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">7.69445133209229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768667221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032274246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95163440704346</t>
+    <t xml:space="preserve">7.65886783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95163536071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.05353736877441</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">8.03089237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95001697540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294845581055</t>
+    <t xml:space="preserve">7.95001649856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294654846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19264316558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25329971313477</t>
+    <t xml:space="preserve">8.19264221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25329780578613</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969287872314</t>
@@ -1544,28 +1544,28 @@
     <t xml:space="preserve">8.29777908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31395530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27756023406982</t>
+    <t xml:space="preserve">8.31395435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27756214141846</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23307991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21286010742188</t>
+    <t xml:space="preserve">8.233078956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21286106109619</t>
   </si>
   <si>
     <t xml:space="preserve">8.28564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24925422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12794208526611</t>
+    <t xml:space="preserve">8.24925518035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12794303894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.24521064758301</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06647872924805</t>
+    <t xml:space="preserve">8.06647777557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.1764669418335</t>
@@ -1583,46 +1583,46 @@
     <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1400728225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08588790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12389945983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20881652832031</t>
+    <t xml:space="preserve">8.14007377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08588695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12389850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20881748199463</t>
   </si>
   <si>
     <t xml:space="preserve">8.2249927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30990982055664</t>
+    <t xml:space="preserve">8.30991172790527</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33417415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31799793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60510635375977</t>
+    <t xml:space="preserve">8.18859958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33417320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60510540008545</t>
   </si>
   <si>
     <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77089786529541</t>
+    <t xml:space="preserve">8.77089881896973</t>
   </si>
   <si>
     <t xml:space="preserve">8.89625549316406</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">8.95691204071045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03778648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04183006286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11866092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22379875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32084941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41790008544922</t>
+    <t xml:space="preserve">9.03778553009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04183101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11866188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32084846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22784233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4178991317749</t>
   </si>
   <si>
     <t xml:space="preserve">9.44620609283447</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">9.48259925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31276226043701</t>
+    <t xml:space="preserve">9.31276321411133</t>
   </si>
   <si>
     <t xml:space="preserve">9.39768028259277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30063056945801</t>
+    <t xml:space="preserve">9.30062961578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
@@ -1682,109 +1682,109 @@
     <t xml:space="preserve">9.11461925506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67789173126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65362930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05191993713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89987373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531732559204</t>
+    <t xml:space="preserve">8.67789077758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65363025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05192089080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89987421035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531684875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.1198558807373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800136566162</t>
+    <t xml:space="preserve">7.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800184249878</t>
   </si>
   <si>
     <t xml:space="preserve">7.25287389755249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24155235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1606764793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05715608596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595659255981</t>
+    <t xml:space="preserve">7.24155330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05715703964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080888748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595754623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.33860206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.477707862854</t>
+    <t xml:space="preserve">7.47770643234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.59093189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92252016067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562404632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98721885681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0082483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516515731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96619272232056</t>
+    <t xml:space="preserve">7.92251920700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98721981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00824642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96619319915771</t>
   </si>
   <si>
     <t xml:space="preserve">7.88370037078857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78017950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78988409042358</t>
+    <t xml:space="preserve">7.78017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78988456726074</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74297761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84164381027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98075008392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91119718551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474721908569</t>
+    <t xml:space="preserve">7.74297714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84164476394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9807505607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9111967086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474626541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.85134935379028</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">7.32889699935913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39036130905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537612915039</t>
+    <t xml:space="preserve">7.3903603553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537708282471</t>
   </si>
   <si>
     <t xml:space="preserve">7.24963903427124</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">7.44212198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49388217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521551132202</t>
+    <t xml:space="preserve">7.49388122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521408081055</t>
   </si>
   <si>
     <t xml:space="preserve">7.26581430435181</t>
@@ -1820,19 +1820,19 @@
     <t xml:space="preserve">7.21890640258789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35477733612061</t>
+    <t xml:space="preserve">7.35477685928345</t>
   </si>
   <si>
     <t xml:space="preserve">7.01833772659302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05230379104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09921169281006</t>
+    <t xml:space="preserve">7.05230474472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0992112159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07980155944824</t>
@@ -1841,46 +1841,46 @@
     <t xml:space="preserve">6.99245691299438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23831653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875471115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58446168899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62328052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54078912734985</t>
+    <t xml:space="preserve">7.23831558227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828737258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54078960418701</t>
   </si>
   <si>
     <t xml:space="preserve">7.64430904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93707752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92898893356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7882661819458</t>
+    <t xml:space="preserve">7.93707799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92898941040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78826761245728</t>
   </si>
   <si>
     <t xml:space="preserve">7.88046550750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8578200340271</t>
+    <t xml:space="preserve">7.85781955718994</t>
   </si>
   <si>
     <t xml:space="preserve">7.67342376708984</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">7.83193922042847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9257550239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01795196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80767679214478</t>
+    <t xml:space="preserve">7.92575550079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01795101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80767822265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.00339412689209</t>
@@ -1907,121 +1907,121 @@
     <t xml:space="preserve">8.39887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23712348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45144176483154</t>
+    <t xml:space="preserve">8.2371244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45144271850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.57679843902588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38674354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18051052093506</t>
+    <t xml:space="preserve">8.38674259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18051147460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034847259521</t>
+    <t xml:space="preserve">8.35034942626953</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92051887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08226680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15909862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18740463256836</t>
+    <t xml:space="preserve">8.92051792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08226776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15909767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18740558624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07418060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17931747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2318868637085</t>
+    <t xml:space="preserve">9.07417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17931842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23188591003418</t>
   </si>
   <si>
     <t xml:space="preserve">9.34915542602539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38150596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32489204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828098297119</t>
+    <t xml:space="preserve">9.38150501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828002929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.36533069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40576934814453</t>
+    <t xml:space="preserve">9.5917797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40576839447021</t>
   </si>
   <si>
     <t xml:space="preserve">9.59582424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65648078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56751728057861</t>
+    <t xml:space="preserve">9.65647983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56751918792725</t>
   </si>
   <si>
     <t xml:space="preserve">9.45833683013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4664249420166</t>
+    <t xml:space="preserve">9.46642398834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.47451114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81014251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0163745880127</t>
+    <t xml:space="preserve">9.81014347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0163736343384</t>
   </si>
   <si>
     <t xml:space="preserve">9.83036136627197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.036060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84943962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79552745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79967308044434</t>
+    <t xml:space="preserve">10.0360612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84943771362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7955265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79967212677002</t>
   </si>
   <si>
     <t xml:space="preserve">9.73331928253174</t>
@@ -2039,22 +2039,22 @@
     <t xml:space="preserve">8.50162124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44356155395508</t>
+    <t xml:space="preserve">8.44356060028076</t>
   </si>
   <si>
     <t xml:space="preserve">8.27767562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1715087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96912908554077</t>
+    <t xml:space="preserve">8.17150974273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96912860870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.12506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03050708770752</t>
+    <t xml:space="preserve">8.03050804138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.22625160217285</t>
@@ -2063,37 +2063,37 @@
     <t xml:space="preserve">8.23620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11842727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21131992340088</t>
+    <t xml:space="preserve">8.11842632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2113208770752</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0869083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03880214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67385339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670240402222</t>
+    <t xml:space="preserve">8.00728416442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08690738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0388011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69375944137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091138839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670288085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77172613143921</t>
@@ -2105,34 +2105,34 @@
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70039510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73357200622559</t>
+    <t xml:space="preserve">7.7003960609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73357248306274</t>
   </si>
   <si>
     <t xml:space="preserve">7.58925151824951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62574672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50299119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109834671021</t>
+    <t xml:space="preserve">7.62574625015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50299215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109882354736</t>
   </si>
   <si>
     <t xml:space="preserve">7.72859525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82978534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91936445236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12340259552002</t>
+    <t xml:space="preserve">7.82978439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9193639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12340068817139</t>
   </si>
   <si>
     <t xml:space="preserve">8.12837982177734</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667297363281</t>
+    <t xml:space="preserve">7.96249437332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667488098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.17814445495605</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">8.60529899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87901020050049</t>
+    <t xml:space="preserve">8.87900924682617</t>
   </si>
   <si>
     <t xml:space="preserve">8.86656761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54724025726318</t>
+    <t xml:space="preserve">8.54723930358887</t>
   </si>
   <si>
     <t xml:space="preserve">8.38550090789795</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">8.4560022354126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30670547485352</t>
+    <t xml:space="preserve">8.30670642852783</t>
   </si>
   <si>
     <t xml:space="preserve">8.48088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2909460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3232946395874</t>
+    <t xml:space="preserve">8.29094696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32329368591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.05704784393311</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462259292603</t>
+    <t xml:space="preserve">7.86462211608887</t>
   </si>
   <si>
     <t xml:space="preserve">7.36530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45820283889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57266330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39184761047363</t>
+    <t xml:space="preserve">7.45820188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57266283035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39184856414795</t>
   </si>
   <si>
     <t xml:space="preserve">7.22098636627197</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">7.38355445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38853120803833</t>
+    <t xml:space="preserve">7.38853073120117</t>
   </si>
   <si>
     <t xml:space="preserve">7.7319130897522</t>
@@ -2234,43 +2234,43 @@
     <t xml:space="preserve">7.41839027404785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25084543228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42502593994141</t>
+    <t xml:space="preserve">7.25084495544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42502546310425</t>
   </si>
   <si>
     <t xml:space="preserve">7.06173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17951583862305</t>
+    <t xml:space="preserve">7.17951536178589</t>
   </si>
   <si>
     <t xml:space="preserve">7.31388187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25914001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56436920166016</t>
+    <t xml:space="preserve">7.2591404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436824798584</t>
   </si>
   <si>
     <t xml:space="preserve">7.44493246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76509189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73854875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92765760421753</t>
+    <t xml:space="preserve">7.76509141921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73854827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92765665054321</t>
   </si>
   <si>
     <t xml:space="preserve">7.77836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82646799087524</t>
+    <t xml:space="preserve">7.82646751403809</t>
   </si>
   <si>
     <t xml:space="preserve">7.72030162811279</t>
@@ -2282,40 +2282,40 @@
     <t xml:space="preserve">8.15989685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1897554397583</t>
+    <t xml:space="preserve">8.18975639343262</t>
   </si>
   <si>
     <t xml:space="preserve">7.89116239547729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81651496887207</t>
+    <t xml:space="preserve">7.81651449203491</t>
   </si>
   <si>
     <t xml:space="preserve">8.16985130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09851932525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76343107223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79660844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03216457366943</t>
+    <t xml:space="preserve">8.09852027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76343154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79660797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03216552734375</t>
   </si>
   <si>
     <t xml:space="preserve">7.98903560638428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84969186782837</t>
+    <t xml:space="preserve">7.84969139099121</t>
   </si>
   <si>
     <t xml:space="preserve">7.86130428314209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9774227142334</t>
+    <t xml:space="preserve">7.97742319107056</t>
   </si>
   <si>
     <t xml:space="preserve">8.05538940429688</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">7.96581172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76840782165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90443468093872</t>
+    <t xml:space="preserve">7.76840829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9044337272644</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">8.1267204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95917654037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17482662200928</t>
+    <t xml:space="preserve">7.95917558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17482757568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.33988285064697</t>
@@ -2360,61 +2360,61 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5596809387207</t>
+    <t xml:space="preserve">8.55968189239502</t>
   </si>
   <si>
     <t xml:space="preserve">8.46014976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44770812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62603569030762</t>
+    <t xml:space="preserve">8.44770908355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6260347366333</t>
   </si>
   <si>
     <t xml:space="preserve">8.47673797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37720775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60944557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412693023682</t>
+    <t xml:space="preserve">8.37720680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60944747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412788391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.95780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16516208648682</t>
+    <t xml:space="preserve">8.99927711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1651611328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.13198471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23566436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48449325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52596282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50937557220459</t>
+    <t xml:space="preserve">9.23566341400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52596187591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50937461853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.42643070220947</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38496112823486</t>
+    <t xml:space="preserve">9.38496017456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.51766872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73746585845947</t>
+    <t xml:space="preserve">9.73746681213379</t>
   </si>
   <si>
     <t xml:space="preserve">9.70014190673828</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">9.33934211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2315149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28957748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35178279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38910675048828</t>
+    <t xml:space="preserve">9.23151588439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28957653045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35178375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">9.19833946228027</t>
@@ -2465,22 +2465,22 @@
     <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26884078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11539554595947</t>
+    <t xml:space="preserve">9.26883983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11539745330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04074859619141</t>
+    <t xml:space="preserve">9.04074668884277</t>
   </si>
   <si>
     <t xml:space="preserve">9.06148338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01586532592773</t>
+    <t xml:space="preserve">9.01586627960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.05319023132324</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">8.93292236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12783813476562</t>
+    <t xml:space="preserve">9.12783718109131</t>
   </si>
   <si>
     <t xml:space="preserve">8.88315773010254</t>
@@ -2501,25 +2501,25 @@
     <t xml:space="preserve">9.09880828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24395751953125</t>
+    <t xml:space="preserve">9.24395847320557</t>
   </si>
   <si>
     <t xml:space="preserve">9.58817005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29372215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15272045135498</t>
+    <t xml:space="preserve">9.29372310638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1527214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.25639915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15686798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21492767333984</t>
+    <t xml:space="preserve">9.15686893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21492671966553</t>
   </si>
   <si>
     <t xml:space="preserve">9.11954402923584</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">9.11124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77533149719238</t>
+    <t xml:space="preserve">8.77533054351807</t>
   </si>
   <si>
     <t xml:space="preserve">9.27298831939697</t>
@@ -2543,52 +2543,52 @@
     <t xml:space="preserve">9.107102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77118301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97024536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27713489532471</t>
+    <t xml:space="preserve">8.77118492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97024631500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27713584899902</t>
   </si>
   <si>
     <t xml:space="preserve">9.68770122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1444263458252</t>
+    <t xml:space="preserve">9.14442539215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.0863676071167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05733680725098</t>
+    <t xml:space="preserve">9.05733776092529</t>
   </si>
   <si>
     <t xml:space="preserve">8.99098300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28128147125244</t>
+    <t xml:space="preserve">9.28128242492676</t>
   </si>
   <si>
     <t xml:space="preserve">8.89559936523438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25279235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14994335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87457466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74186611175537</t>
+    <t xml:space="preserve">8.25279331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14994430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87457609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74186706542969</t>
   </si>
   <si>
     <t xml:space="preserve">7.34042406082153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35867071151733</t>
+    <t xml:space="preserve">7.35867166519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.44327259063721</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">6.73328399658203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25055694580078</t>
+    <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.53256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73797273635864</t>
+    <t xml:space="preserve">5.73797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">6.38990116119385</t>
@@ -2621,82 +2621,82 @@
     <t xml:space="preserve">6.20245122909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1908392906189</t>
+    <t xml:space="preserve">6.19083976745605</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71503686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33047151565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85769748687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98542881011963</t>
+    <t xml:space="preserve">6.71503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33047199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8576979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98542928695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.87594509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096834182739</t>
+    <t xml:space="preserve">6.87096881866455</t>
   </si>
   <si>
     <t xml:space="preserve">7.09159660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4233660697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59256887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310317993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144474029541</t>
+    <t xml:space="preserve">7.42336559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59256982803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144569396973</t>
   </si>
   <si>
     <t xml:space="preserve">7.92931699752808</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32715368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21601009368896</t>
+    <t xml:space="preserve">7.32715272903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21600961685181</t>
   </si>
   <si>
     <t xml:space="preserve">7.24255228042603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76977872848511</t>
+    <t xml:space="preserve">6.76977825164795</t>
   </si>
   <si>
     <t xml:space="preserve">7.26411724090576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66224193572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067697525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88286876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07363796234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46844387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4103832244873</t>
+    <t xml:space="preserve">7.66224145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88286972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07363700866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46844482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41038417816162</t>
   </si>
   <si>
     <t xml:space="preserve">8.0520715713501</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">8.70897674560547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35232448577881</t>
+    <t xml:space="preserve">8.35232353210449</t>
   </si>
   <si>
     <t xml:space="preserve">8.22956848144531</t>
@@ -2717,16 +2717,16 @@
     <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29426383972168</t>
+    <t xml:space="preserve">8.294264793396</t>
   </si>
   <si>
     <t xml:space="preserve">8.20800399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43111991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47259044647217</t>
+    <t xml:space="preserve">8.43112087249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47259140014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.78777408599854</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">8.75874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91218757629395</t>
+    <t xml:space="preserve">8.91218662261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.0034236907959</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.34763717651367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34348964691162</t>
+    <t xml:space="preserve">9.3434886932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
@@ -2756,16 +2756,16 @@
     <t xml:space="preserve">9.60475826263428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402059555054</t>
+    <t xml:space="preserve">10.040207862854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94896984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0443544387817</t>
+    <t xml:space="preserve">9.94897079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0443525314331</t>
   </si>
   <si>
     <t xml:space="preserve">10.2848873138428</t>
@@ -2774,34 +2774,34 @@
     <t xml:space="preserve">9.87432193756104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98214721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0650901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9655590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95311641693115</t>
+    <t xml:space="preserve">9.98214626312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065089225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96555995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95311737060547</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595361709595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3512411117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7286310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6996002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6747169494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387994766235</t>
+    <t xml:space="preserve">10.3512420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7286319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6995992660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6747188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3388004302979</t>
   </si>
   <si>
     <t xml:space="preserve">10.4093027114868</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">10.4632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4010076522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498355865479</t>
+    <t xml:space="preserve">10.401008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498346328735</t>
   </si>
   <si>
     <t xml:space="preserve">10.6415414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8323097229004</t>
+    <t xml:space="preserve">10.8323087692261</t>
   </si>
   <si>
     <t xml:space="preserve">10.7659549713135</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">10.6332473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295696258545</t>
+    <t xml:space="preserve">10.6042165756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295686721802</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024141311646</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">10.181209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.53786277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3305072784424</t>
+    <t xml:space="preserve">10.5378618240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
     <t xml:space="preserve">10.3553895950317</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">10.2309761047363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4175968170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0645484924316</t>
+    <t xml:space="preserve">10.4175958633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.064549446106</t>
   </si>
   <si>
     <t xml:space="preserve">10.8654870986938</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.8240156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6125116348267</t>
+    <t xml:space="preserve">10.6125106811523</t>
   </si>
   <si>
     <t xml:space="preserve">10.6000699996948</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">10.6913070678711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7949857711792</t>
+    <t xml:space="preserve">10.7949867248535</t>
   </si>
   <si>
     <t xml:space="preserve">10.6664237976074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5337152481079</t>
+    <t xml:space="preserve">10.5337171554565</t>
   </si>
   <si>
     <t xml:space="preserve">10.6249532699585</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">10.5751867294312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0733852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341850280762</t>
+    <t xml:space="preserve">10.0733842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4341840744019</t>
   </si>
   <si>
     <t xml:space="preserve">10.2392702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180646896362</t>
+    <t xml:space="preserve">10.3180656433105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
@@ -2921,25 +2921,25 @@
     <t xml:space="preserve">10.1936511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0319137573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81626129150391</t>
+    <t xml:space="preserve">10.0319128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81626224517822</t>
   </si>
   <si>
     <t xml:space="preserve">9.83285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46790313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44716835021973</t>
+    <t xml:space="preserve">9.46790218353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44716644287109</t>
   </si>
   <si>
     <t xml:space="preserve">9.72087860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5591402053833</t>
+    <t xml:space="preserve">9.55913925170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.71258354187012</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">9.74990749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82040977478027</t>
+    <t xml:space="preserve">9.82040882110596</t>
   </si>
   <si>
     <t xml:space="preserve">10.0277652740479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1107082366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90335178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1604747772217</t>
+    <t xml:space="preserve">10.11070728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90335083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1604738235474</t>
   </si>
   <si>
     <t xml:space="preserve">10.1729164123535</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">10.2102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0775299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1521797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99044227600098</t>
+    <t xml:space="preserve">10.0775318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1521787643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1065626144409</t>
@@ -2987,28 +2987,28 @@
     <t xml:space="preserve">9.96141147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59646320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53425693511963</t>
+    <t xml:space="preserve">9.59646415710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53425598144531</t>
   </si>
   <si>
     <t xml:space="preserve">9.67111301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970748901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2600049972534</t>
+    <t xml:space="preserve">9.74576091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970653533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2600059509277</t>
   </si>
   <si>
     <t xml:space="preserve">10.3844194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.347095489502</t>
+    <t xml:space="preserve">10.3470945358276</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346538543701</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">9.94482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272974014282</t>
+    <t xml:space="preserve">10.1272983551025</t>
   </si>
   <si>
     <t xml:space="preserve">10.2683010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5088329315186</t>
+    <t xml:space="preserve">10.5088319778442</t>
   </si>
   <si>
     <t xml:space="preserve">10.4134483337402</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">10.8074264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7576608657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8779277801514</t>
+    <t xml:space="preserve">10.757661819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8779268264771</t>
   </si>
   <si>
     <t xml:space="preserve">10.8945169448853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9359874725342</t>
+    <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
     <t xml:space="preserve">10.8157215118408</t>
@@ -3053,40 +3053,40 @@
     <t xml:space="preserve">10.9733114242554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986625671387</t>
+    <t xml:space="preserve">10.898663520813</t>
   </si>
   <si>
     <t xml:space="preserve">10.8364562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9857530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8737802505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8447504043579</t>
+    <t xml:space="preserve">10.9857540130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.873779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8447513580322</t>
   </si>
   <si>
     <t xml:space="preserve">10.9774589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.135048866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1018733978271</t>
+    <t xml:space="preserve">11.1350498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1018724441528</t>
   </si>
   <si>
     <t xml:space="preserve">11.1143140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35484790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1474905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1599321365356</t>
+    <t xml:space="preserve">11.3548469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1474914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
     <t xml:space="preserve">11.3921718597412</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">11.2843465805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6119709014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5207328796387</t>
+    <t xml:space="preserve">11.6119699478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.520733833313</t>
   </si>
   <si>
     <t xml:space="preserve">11.4792623519897</t>
@@ -3110,22 +3110,22 @@
     <t xml:space="preserve">11.1889629364014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1682271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1226081848145</t>
+    <t xml:space="preserve">11.1682281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1226091384888</t>
   </si>
   <si>
     <t xml:space="preserve">11.0355186462402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9442825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6788654327393</t>
+    <t xml:space="preserve">10.9442806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452192306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6788644790649</t>
   </si>
   <si>
     <t xml:space="preserve">11.2926416397095</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">12.3999252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303625106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4455432891846</t>
+    <t xml:space="preserve">12.1303615570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4455442428589</t>
   </si>
   <si>
     <t xml:space="preserve">12.2630701065063</t>
@@ -3152,28 +3152,28 @@
     <t xml:space="preserve">12.4953098297119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.594841003418</t>
+    <t xml:space="preserve">12.5948419570923</t>
   </si>
   <si>
     <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.358452796936</t>
+    <t xml:space="preserve">12.3584537506104</t>
   </si>
   <si>
     <t xml:space="preserve">12.1718339920044</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3169822692871</t>
+    <t xml:space="preserve">12.3169832229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.1842737197876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0557136535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3377180099487</t>
+    <t xml:space="preserve">12.0557126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3377170562744</t>
   </si>
   <si>
     <t xml:space="preserve">12.192569732666</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">12.2879524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0640087127686</t>
+    <t xml:space="preserve">12.0640077590942</t>
   </si>
   <si>
     <t xml:space="preserve">12.0349779129028</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.9230051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9810638427734</t>
+    <t xml:space="preserve">11.9810647964478</t>
   </si>
   <si>
     <t xml:space="preserve">12.2755117416382</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">12.1635389328003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2174510955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3543081283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1759805679321</t>
+    <t xml:space="preserve">12.2174501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3543071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1759796142578</t>
   </si>
   <si>
     <t xml:space="preserve">11.9727716445923</t>
@@ -3221,55 +3221,55 @@
     <t xml:space="preserve">11.9437408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.117919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5580577850342</t>
+    <t xml:space="preserve">12.1179208755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5580587387085</t>
   </si>
   <si>
     <t xml:space="preserve">11.5539112091064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4626731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5746459960938</t>
+    <t xml:space="preserve">11.4626741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5746469497681</t>
   </si>
   <si>
     <t xml:space="preserve">11.4834098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5912351608276</t>
+    <t xml:space="preserve">11.5912342071533</t>
   </si>
   <si>
     <t xml:space="preserve">11.5995283126831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5870866775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6824703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7405319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9603290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7985906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9520349502563</t>
+    <t xml:space="preserve">11.5870876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9603300094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7985916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.952033996582</t>
   </si>
   <si>
     <t xml:space="preserve">11.5456161499023</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">11.5331745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4543800354004</t>
+    <t xml:space="preserve">11.4543790817261</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751148223877</t>
@@ -3287,37 +3287,37 @@
     <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8193264007568</t>
+    <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
     <t xml:space="preserve">11.9064168930054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8773860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0142421722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6949129104614</t>
+    <t xml:space="preserve">11.877387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0142412185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6949138641357</t>
   </si>
   <si>
     <t xml:space="preserve">11.8732395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.661735534668</t>
+    <t xml:space="preserve">11.6617364883423</t>
   </si>
   <si>
     <t xml:space="preserve">11.7322378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7446784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6534414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7115020751953</t>
+    <t xml:space="preserve">11.7446794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6534423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.711501121521</t>
   </si>
   <si>
     <t xml:space="preserve">11.7654151916504</t>
@@ -3338,58 +3338,58 @@
     <t xml:space="preserve">11.4129085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4336433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3299646377563</t>
+    <t xml:space="preserve">11.4336442947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3299655914307</t>
   </si>
   <si>
     <t xml:space="preserve">11.3631420135498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3382587432861</t>
+    <t xml:space="preserve">11.3382596969604</t>
   </si>
   <si>
     <t xml:space="preserve">11.3880243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714370727539</t>
+    <t xml:space="preserve">11.3714361190796</t>
   </si>
   <si>
     <t xml:space="preserve">11.4917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5124387741089</t>
+    <t xml:space="preserve">11.5124397277832</t>
   </si>
   <si>
     <t xml:space="preserve">11.6451482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5622034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248794555664</t>
+    <t xml:space="preserve">11.5622043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248804092407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5953817367554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5497636795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.66588306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.931300163269</t>
+    <t xml:space="preserve">11.5497627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9312992095947</t>
   </si>
   <si>
     <t xml:space="preserve">11.8607978820801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6409997940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8068857192993</t>
+    <t xml:space="preserve">11.6410007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">12.026683807373</t>
@@ -3398,49 +3398,49 @@
     <t xml:space="preserve">12.1013326644897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2133045196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2423334121704</t>
+    <t xml:space="preserve">12.213303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2423343658447</t>
   </si>
   <si>
     <t xml:space="preserve">12.1967153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3086881637573</t>
+    <t xml:space="preserve">12.308687210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.1510972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.478720664978</t>
+    <t xml:space="preserve">12.4787197113037</t>
   </si>
   <si>
     <t xml:space="preserve">12.0391254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690929412842</t>
+    <t xml:space="preserve">11.8690938949585</t>
   </si>
   <si>
     <t xml:space="preserve">11.7778558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1220664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2215976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.333571434021</t>
+    <t xml:space="preserve">12.1220674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2215995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3335723876953</t>
   </si>
   <si>
     <t xml:space="preserve">12.7151079177856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5367813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3708944320679</t>
+    <t xml:space="preserve">12.5367803573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
     <t xml:space="preserve">12.7773141860962</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">13.3827962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532957077026</t>
+    <t xml:space="preserve">13.453296661377</t>
   </si>
   <si>
     <t xml:space="preserve">13.5942993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4201202392578</t>
+    <t xml:space="preserve">13.4698848724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4201192855835</t>
   </si>
   <si>
     <t xml:space="preserve">13.3496179580688</t>
@@ -3473,28 +3473,28 @@
     <t xml:space="preserve">13.2252044677734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4781799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.216911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0510244369507</t>
+    <t xml:space="preserve">13.4781808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2169103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.051025390625</t>
   </si>
   <si>
     <t xml:space="preserve">13.1588506698608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1837348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625284194946</t>
+    <t xml:space="preserve">13.1837339401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625293731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514942169189</t>
@@ -3503,49 +3503,49 @@
     <t xml:space="preserve">12.8644037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8685503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7939033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9349069595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312273025513</t>
+    <t xml:space="preserve">12.8685512542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7939023971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9349050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.831226348877</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482843399048</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5741052627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6611957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9763774871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2376470565796</t>
+    <t xml:space="preserve">12.574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6611948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9763765335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.237645149231</t>
   </si>
   <si>
     <t xml:space="preserve">13.1215267181396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0095548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.241792678833</t>
+    <t xml:space="preserve">13.0095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2417936325073</t>
   </si>
   <si>
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9431982040405</t>
+    <t xml:space="preserve">12.9431991577148</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">12.9971122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7690200805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6446056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722299575806</t>
+    <t xml:space="preserve">12.7690210342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.644606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722290039062</t>
   </si>
   <si>
     <t xml:space="preserve">12.9888191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302886962891</t>
+    <t xml:space="preserve">13.0302896499634</t>
   </si>
   <si>
     <t xml:space="preserve">13.1090860366821</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">13.2044687271118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1173801422119</t>
+    <t xml:space="preserve">13.1173791885376</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850685119629</t>
+    <t xml:space="preserve">13.7850666046143</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523580551147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8016538619995</t>
+    <t xml:space="preserve">13.8016548156738</t>
   </si>
   <si>
     <t xml:space="preserve">13.7726259231567</t>
@@ -3599,37 +3599,37 @@
     <t xml:space="preserve">13.7975101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9219217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9799833297729</t>
+    <t xml:space="preserve">13.9219226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9799823760986</t>
   </si>
   <si>
     <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7270059585571</t>
+    <t xml:space="preserve">13.7270078659058</t>
   </si>
   <si>
     <t xml:space="preserve">13.6979780197144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0048666000366</t>
+    <t xml:space="preserve">14.0048656463623</t>
   </si>
   <si>
     <t xml:space="preserve">13.7643308639526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878095626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.224663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3324899673462</t>
+    <t xml:space="preserve">14.0878086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3324890136719</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712203979492</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">14.1583089828491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2951650619507</t>
+    <t xml:space="preserve">14.2951641082764</t>
   </si>
   <si>
     <t xml:space="preserve">14.3532238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2619867324829</t>
+    <t xml:space="preserve">14.2619876861572</t>
   </si>
   <si>
     <t xml:space="preserve">14.3076066970825</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2163696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251316070557</t>
+    <t xml:space="preserve">14.2163686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.12513256073</t>
   </si>
   <si>
     <t xml:space="preserve">14.3006267547607</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">13.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3161468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605028152466</t>
+    <t xml:space="preserve">13.3161478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605037689209</t>
   </si>
   <si>
     <t xml:space="preserve">13.4359970092773</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834573745728</t>
+    <t xml:space="preserve">13.1834564208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.5515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9068365097046</t>
+    <t xml:space="preserve">13.9068355560303</t>
   </si>
   <si>
     <t xml:space="preserve">13.645733833313</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258836746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9951229095459</t>
+    <t xml:space="preserve">13.4445581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9951219558716</t>
   </si>
   <si>
     <t xml:space="preserve">12.7639837265015</t>
@@ -3719,10 +3719,10 @@
     <t xml:space="preserve">12.965160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9523191452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9095144271851</t>
+    <t xml:space="preserve">12.9523181915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9095134735107</t>
   </si>
   <si>
     <t xml:space="preserve">13.2433815002441</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">13.2519416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2134189605713</t>
+    <t xml:space="preserve">13.2134199142456</t>
   </si>
   <si>
     <t xml:space="preserve">13.4531192779541</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">13.2562217712402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589496612549</t>
+    <t xml:space="preserve">13.3589506149292</t>
   </si>
   <si>
     <t xml:space="preserve">13.0122423171997</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">13.1320934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7597026824951</t>
+    <t xml:space="preserve">12.7597036361694</t>
   </si>
   <si>
     <t xml:space="preserve">12.3616313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5499649047852</t>
+    <t xml:space="preserve">12.5499658584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900417327881</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.85387134552</t>
+    <t xml:space="preserve">12.8538703918457</t>
   </si>
   <si>
     <t xml:space="preserve">12.900954246521</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">12.7682628631592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8495903015137</t>
+    <t xml:space="preserve">12.849591255188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0550470352173</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">13.6799764633179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5430059432983</t>
+    <t xml:space="preserve">13.5430068969727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4103145599365</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768239974976</t>
+    <t xml:space="preserve">12.7768249511719</t>
   </si>
   <si>
     <t xml:space="preserve">12.0234832763672</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">10.9576787948608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8720712661743</t>
+    <t xml:space="preserve">10.8720722198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.5339260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.783784866333</t>
+    <t xml:space="preserve">11.7837858200073</t>
   </si>
   <si>
     <t xml:space="preserve">11.3172273635864</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">11.5954494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8265867233276</t>
+    <t xml:space="preserve">11.826587677002</t>
   </si>
   <si>
     <t xml:space="preserve">11.8950729370117</t>
@@ -3893,16 +3893,16 @@
     <t xml:space="preserve">11.8479900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9507179260254</t>
+    <t xml:space="preserve">11.9507188796997</t>
   </si>
   <si>
     <t xml:space="preserve">12.3145475387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1989774703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2332210540771</t>
+    <t xml:space="preserve">12.1989784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2332201004028</t>
   </si>
   <si>
     <t xml:space="preserve">12.3102674484253</t>
@@ -3923,19 +3923,19 @@
     <t xml:space="preserve">12.2203798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9464378356934</t>
+    <t xml:space="preserve">11.946436882019</t>
   </si>
   <si>
     <t xml:space="preserve">11.9079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9036340713501</t>
+    <t xml:space="preserve">11.9036331176758</t>
   </si>
   <si>
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834083557129</t>
+    <t xml:space="preserve">12.0834093093872</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705680847168</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4868412017822</t>
+    <t xml:space="preserve">10.4868402481079</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771043777466</t>
@@ -6276,6 +6276,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.6599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9150009155273</t>
   </si>
 </sst>
 </file>
@@ -71406,7 +71409,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6494791667</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>1409310</v>
@@ -71427,6 +71430,32 @@
         <v>2027</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6496296296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>1110327</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>18.9899997711182</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>18.8600006103516</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>18.9150009155273</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2088</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="2090">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,43 +44,43 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048845291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209339141846</t>
+    <t xml:space="preserve">5.32048797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209386825562</t>
   </si>
   <si>
     <t xml:space="preserve">5.13951969146729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26257848739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13228130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.266197681427</t>
+    <t xml:space="preserve">5.2625789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1322808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26619815826416</t>
   </si>
   <si>
     <t xml:space="preserve">5.31325006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19381046295166</t>
+    <t xml:space="preserve">5.19381093978882</t>
   </si>
   <si>
     <t xml:space="preserve">5.0454158782959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92959594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07437086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65814256668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101345062256</t>
+    <t xml:space="preserve">4.92959547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07437181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65814161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101392745972</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
@@ -89,34 +89,34 @@
     <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21190738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0490345954895</t>
+    <t xml:space="preserve">5.21190690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
     <t xml:space="preserve">5.14675855636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12504196166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8897819519043</t>
+    <t xml:space="preserve">5.16485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12504148483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88978290557861</t>
   </si>
   <si>
     <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138689041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56765699386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34325647354126</t>
+    <t xml:space="preserve">4.74138736724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56765747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3432559967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.45545673370361</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">4.58213520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78482007980347</t>
+    <t xml:space="preserve">4.78482103347778</t>
   </si>
   <si>
     <t xml:space="preserve">4.73414945602417</t>
@@ -137,25 +137,25 @@
     <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71243333816528</t>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71243238449097</t>
   </si>
   <si>
     <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84996891021729</t>
+    <t xml:space="preserve">4.84996938705444</t>
   </si>
   <si>
     <t xml:space="preserve">4.88616275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00922203063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09246730804443</t>
+    <t xml:space="preserve">5.00922155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09246778488159</t>
   </si>
   <si>
     <t xml:space="preserve">5.10332584381104</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">4.95493078231812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8427300453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120136260986</t>
+    <t xml:space="preserve">4.84273052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120183944702</t>
   </si>
   <si>
     <t xml:space="preserve">5.06713199615479</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">5.08884859085083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00560283660889</t>
+    <t xml:space="preserve">5.00560235977173</t>
   </si>
   <si>
     <t xml:space="preserve">4.99112510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19019031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23362398147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35668277740479</t>
+    <t xml:space="preserve">5.1901912689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23362302780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
     <t xml:space="preserve">5.12866163253784</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">5.33544111251831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23406410217285</t>
+    <t xml:space="preserve">5.23406314849854</t>
   </si>
   <si>
     <t xml:space="preserve">5.28287506103516</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">5.27161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.230309009552</t>
+    <t xml:space="preserve">5.23030948638916</t>
   </si>
   <si>
     <t xml:space="preserve">5.16647958755493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164861679077</t>
+    <t xml:space="preserve">5.3316855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164909362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.39176177978516</t>
@@ -254,46 +254,46 @@
     <t xml:space="preserve">5.25659227371216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05759239196777</t>
+    <t xml:space="preserve">5.05759191513062</t>
   </si>
   <si>
     <t xml:space="preserve">5.0988941192627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96747922897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88863086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78725385665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79100894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76472520828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70089530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9637246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90364980697632</t>
+    <t xml:space="preserve">4.96747875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88863039016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78725433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79100799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76472473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96372509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90364933013916</t>
   </si>
   <si>
     <t xml:space="preserve">4.90740442276001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7759895324707</t>
+    <t xml:space="preserve">4.77598905563354</t>
   </si>
   <si>
     <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84357404708862</t>
+    <t xml:space="preserve">4.84357452392578</t>
   </si>
   <si>
     <t xml:space="preserve">4.91866827011108</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">4.92617750167847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95246124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97123384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483884811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.877366065979</t>
+    <t xml:space="preserve">4.95245981216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9712347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85483837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
     <t xml:space="preserve">4.8022723197937</t>
@@ -332,136 +332,136 @@
     <t xml:space="preserve">4.56197071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44182109832764</t>
+    <t xml:space="preserve">4.44182062149048</t>
   </si>
   <si>
     <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45683908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56947994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7534613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97498893737793</t>
+    <t xml:space="preserve">4.4568395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56948089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093271255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80602693557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97498941421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.49063205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39676427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33668851852417</t>
+    <t xml:space="preserve">4.13017892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39676332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33668899536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.39300966262817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17523574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10014152526855</t>
+    <t xml:space="preserve">4.17523622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10014200210571</t>
   </si>
   <si>
     <t xml:space="preserve">3.87485933303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94244360923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26534938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31791543960571</t>
+    <t xml:space="preserve">3.94244408607483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2653489112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3179144859314</t>
   </si>
   <si>
     <t xml:space="preserve">4.1902551651001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20151901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23531103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31040477752686</t>
+    <t xml:space="preserve">4.20151853561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23531150817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31040525436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.25032997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24657535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27661418914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638690948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93118000030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98749995231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83731174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93868851661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623610496521</t>
+    <t xml:space="preserve">4.24657583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27661323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638738632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9311797618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98750042915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8373122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9386887550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623682022095</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9724817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746278762817</t>
+    <t xml:space="preserve">3.97248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746350288391</t>
   </si>
   <si>
     <t xml:space="preserve">3.94619846343994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99876403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604789733887</t>
+    <t xml:space="preserve">3.99876475334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980275154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604765892029</t>
   </si>
   <si>
     <t xml:space="preserve">3.77348232269287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75470876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133008956909</t>
+    <t xml:space="preserve">3.75470852851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.07010459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04382085800171</t>
+    <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
     <t xml:space="preserve">4.01378345489502</t>
@@ -473,112 +473,112 @@
     <t xml:space="preserve">4.09263181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13768863677979</t>
+    <t xml:space="preserve">4.13768911361694</t>
   </si>
   <si>
     <t xml:space="preserve">4.12266969680786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05508470535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255653381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91240644454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9048969745636</t>
+    <t xml:space="preserve">4.05508613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255701065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91240692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229351997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90489721298218</t>
   </si>
   <si>
     <t xml:space="preserve">3.90114235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88987755775452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81102895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8861231803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738774299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236832618713</t>
+    <t xml:space="preserve">3.88987827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81102919578552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88612389564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738750457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236856460571</t>
   </si>
   <si>
     <t xml:space="preserve">3.87110471725464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85233068466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221799850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61202955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96121788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999143600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02504777908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96497273445129</t>
+    <t xml:space="preserve">3.8523313999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850102424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61202931404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550881385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79601049423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96121740341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999119758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02504730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96497225761414</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08887720108032</t>
+    <t xml:space="preserve">4.08887815475464</t>
   </si>
   <si>
     <t xml:space="preserve">4.14519834518433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9950098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727505683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225516319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170469284058</t>
+    <t xml:space="preserve">3.99500942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742490768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474640846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727458000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225564002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170516967773</t>
   </si>
   <si>
     <t xml:space="preserve">3.73518419265747</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">3.64056539535522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60452032089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5444450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5384373664856</t>
+    <t xml:space="preserve">3.60452055931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54444456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843712806702</t>
   </si>
   <si>
     <t xml:space="preserve">3.5414412021637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55645990371704</t>
+    <t xml:space="preserve">3.55646014213562</t>
   </si>
   <si>
     <t xml:space="preserve">3.60001468658447</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">3.47085285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58799910545349</t>
+    <t xml:space="preserve">3.58799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">3.66459560394287</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910099983215</t>
+    <t xml:space="preserve">3.66910123825073</t>
   </si>
   <si>
     <t xml:space="preserve">3.57748627662659</t>
@@ -626,112 +626,112 @@
     <t xml:space="preserve">3.73968982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84857630729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10389566421509</t>
+    <t xml:space="preserve">3.84857606887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10389709472656</t>
   </si>
   <si>
     <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11516094207764</t>
+    <t xml:space="preserve">4.04006671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11516046524048</t>
   </si>
   <si>
     <t xml:space="preserve">4.00251913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07761287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16772699356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512353897095</t>
+    <t xml:space="preserve">4.07761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16772651672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512306213379</t>
   </si>
   <si>
     <t xml:space="preserve">4.18274593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22029256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2390661239624</t>
+    <t xml:space="preserve">4.22029209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23906707763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642431259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06259489059448</t>
+    <t xml:space="preserve">4.12642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06259536743164</t>
   </si>
   <si>
     <t xml:space="preserve">4.03631162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13393449783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28787708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30289602279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293390274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706588745117</t>
+    <t xml:space="preserve">4.13393402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28787755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706493377686</t>
   </si>
   <si>
     <t xml:space="preserve">4.69338607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72342395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67085790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80978202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83981990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81353664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79851770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72717809677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85108375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82104635238647</t>
+    <t xml:space="preserve">4.72342348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67085647583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8097825050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83981943130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81353616714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79851722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72717761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85108423233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82104587554932</t>
   </si>
   <si>
     <t xml:space="preserve">4.83606481552124</t>
@@ -740,22 +740,22 @@
     <t xml:space="preserve">5.07056093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13733053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198163986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07448863983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12947511672974</t>
+    <t xml:space="preserve">5.13733148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198259353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07448959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12947559356689</t>
   </si>
   <si>
     <t xml:space="preserve">5.16875171661377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23552179336548</t>
+    <t xml:space="preserve">5.23552131652832</t>
   </si>
   <si>
     <t xml:space="preserve">5.33371162414551</t>
@@ -770,34 +770,34 @@
     <t xml:space="preserve">5.20410060882568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28265285491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20017242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373867034912</t>
+    <t xml:space="preserve">5.28265190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20017337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373819351196</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092287063599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29050827026367</t>
+    <t xml:space="preserve">5.15696859359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29050779342651</t>
   </si>
   <si>
     <t xml:space="preserve">5.26694250106812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34942197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38477087020874</t>
+    <t xml:space="preserve">5.36906099319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3847713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.21588325500488</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">5.25515937805176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32978487014771</t>
+    <t xml:space="preserve">5.32978391647339</t>
   </si>
   <si>
     <t xml:space="preserve">5.32585716247559</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">5.25123167037964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3729887008667</t>
+    <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
     <t xml:space="preserve">5.43975782394409</t>
@@ -827,52 +827,52 @@
     <t xml:space="preserve">5.61650085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57722473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5418758392334</t>
+    <t xml:space="preserve">5.577223777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">5.63221120834351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62435626983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50652742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53794860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62042903900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55365896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50259971618652</t>
+    <t xml:space="preserve">5.62435579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5065279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5379490852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62042856216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55365943908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50260019302368</t>
   </si>
   <si>
     <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52223825454712</t>
+    <t xml:space="preserve">5.52223777770996</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257314682007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69112539291382</t>
+    <t xml:space="preserve">5.69112586975098</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789499282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076393127441</t>
+    <t xml:space="preserve">5.87572431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076345443726</t>
   </si>
   <si>
     <t xml:space="preserve">5.73432970046997</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">5.65970420837402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72647428512573</t>
+    <t xml:space="preserve">5.72647380828857</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
@@ -899,28 +899,28 @@
     <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.773606300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86786890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83644771575928</t>
+    <t xml:space="preserve">5.77360534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86786794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83644723892212</t>
   </si>
   <si>
     <t xml:space="preserve">5.82466459274292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82859182357788</t>
+    <t xml:space="preserve">5.8403754234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8285927772522</t>
   </si>
   <si>
     <t xml:space="preserve">5.87179613113403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93463850021362</t>
+    <t xml:space="preserve">5.93463802337646</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034885406494</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">5.7971715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70290851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78931617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89143371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78538799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324388504028</t>
+    <t xml:space="preserve">5.70290899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78931570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89143419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538846969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324340820312</t>
   </si>
   <si>
     <t xml:space="preserve">5.70683622360229</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">5.59293460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66756010055542</t>
+    <t xml:space="preserve">5.66755962371826</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41619157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39262628555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45939588546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75004005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182222366333</t>
+    <t xml:space="preserve">5.41619205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39262580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45939540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75004053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76182270050049</t>
   </si>
   <si>
     <t xml:space="preserve">5.73040246963501</t>
@@ -992,49 +992,49 @@
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80895471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91500043869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87965154647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8521580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84430265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84823083877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254610061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69505310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66363286972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64792251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71861886978149</t>
+    <t xml:space="preserve">5.8089542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87965202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85215759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001348495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84823131561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69505262374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6636323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64792203903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71861934661865</t>
   </si>
   <si>
     <t xml:space="preserve">5.83252048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76575040817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11530876159668</t>
+    <t xml:space="preserve">5.76575088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11530923843384</t>
   </si>
   <si>
     <t xml:space="preserve">6.08388805389404</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">6.26063108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24492025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31168985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776214599609</t>
+    <t xml:space="preserve">6.24492073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31169033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776309967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.29990720748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29205179214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670433044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706579208374</t>
+    <t xml:space="preserve">6.29205226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706483840942</t>
   </si>
   <si>
     <t xml:space="preserve">6.2527756690979</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">6.2645583152771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20171642303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23313760757446</t>
+    <t xml:space="preserve">6.20171594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23313665390015</t>
   </si>
   <si>
     <t xml:space="preserve">6.06032228469849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00926303863525</t>
+    <t xml:space="preserve">6.00926351547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.1270923614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528219223022</t>
+    <t xml:space="preserve">6.22528266906738</t>
   </si>
   <si>
     <t xml:space="preserve">6.28026914596558</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">6.37060451507568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37453174591064</t>
+    <t xml:space="preserve">6.3745322227478</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">6.45308446884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58662366867065</t>
+    <t xml:space="preserve">6.58662414550781</t>
   </si>
   <si>
     <t xml:space="preserve">6.65339326858521</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">6.53949213027954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60626125335693</t>
+    <t xml:space="preserve">6.60626220703125</t>
   </si>
   <si>
     <t xml:space="preserve">6.63768243789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56305837631226</t>
+    <t xml:space="preserve">6.5630578994751</t>
   </si>
   <si>
     <t xml:space="preserve">6.71230792999268</t>
@@ -1133,25 +1133,25 @@
     <t xml:space="preserve">6.68874168395996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79085969924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088674545288</t>
+    <t xml:space="preserve">6.79086065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088626861572</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77907752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85762882232666</t>
+    <t xml:space="preserve">6.77907705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75551128387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336622238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762929916382</t>
   </si>
   <si>
     <t xml:space="preserve">6.86155700683594</t>
@@ -1163,28 +1163,28 @@
     <t xml:space="preserve">6.70445203781128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63375520706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99902391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116897583008</t>
+    <t xml:space="preserve">6.63375425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116849899292</t>
   </si>
   <si>
     <t xml:space="preserve">7.33287239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40356922149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58031225204468</t>
+    <t xml:space="preserve">7.40356969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031272888184</t>
   </si>
   <si>
     <t xml:space="preserve">7.54103660583496</t>
@@ -1193,121 +1193,121 @@
     <t xml:space="preserve">7.552818775177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46641111373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66672039031982</t>
+    <t xml:space="preserve">7.46641159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351560592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66671991348267</t>
   </si>
   <si>
     <t xml:space="preserve">7.80418729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75705528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88666772842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93379783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91808843612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310148239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488317489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74055957794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886449813843</t>
+    <t xml:space="preserve">7.75705432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8866662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93379831314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91808795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87488412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74055862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886497497559</t>
   </si>
   <si>
     <t xml:space="preserve">7.31951808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50804281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53161096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23782300949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610326766968</t>
+    <t xml:space="preserve">7.50804376602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53161001205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23782348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610279083252</t>
   </si>
   <si>
     <t xml:space="preserve">7.24410772323608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3006649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076271057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59131002426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69656991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355146408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80025959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826404571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83325052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9495096206665</t>
+    <t xml:space="preserve">7.30066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076223373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59130954742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355098724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025911331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83325099945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94950866699219</t>
   </si>
   <si>
     <t xml:space="preserve">7.96914720535278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5206127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83010959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96129035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08304786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165277481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95343732833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0437707901001</t>
+    <t xml:space="preserve">7.52061367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83010911941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96129179000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08304882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090328216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95343589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04377269744873</t>
   </si>
   <si>
     <t xml:space="preserve">8.11054134368896</t>
@@ -1316,55 +1316,55 @@
     <t xml:space="preserve">8.14589023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07126522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86702919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83953475952148</t>
+    <t xml:space="preserve">8.07126426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86702871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83953523635864</t>
   </si>
   <si>
     <t xml:space="preserve">7.69499826431274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71070861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487483978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65572309494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85524654388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59445190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415239334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56146001815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75312805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83168077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696628570557</t>
+    <t xml:space="preserve">7.7107105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300271987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487674713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65572357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85524559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59445285797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602308273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5614595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7531270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83167934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696580886841</t>
   </si>
   <si>
     <t xml:space="preserve">7.79554605484009</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">8.08750534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01633548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96942710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97427940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560190200806</t>
+    <t xml:space="preserve">8.01633453369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96942663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97428035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560094833374</t>
   </si>
   <si>
     <t xml:space="preserve">8.14816093444824</t>
@@ -1412,109 +1412,109 @@
     <t xml:space="preserve">7.87884664535522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86752319335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726873397827</t>
+    <t xml:space="preserve">7.86752367019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726921081543</t>
   </si>
   <si>
     <t xml:space="preserve">7.4194769859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25125694274902</t>
+    <t xml:space="preserve">7.25125646591187</t>
   </si>
   <si>
     <t xml:space="preserve">7.19626140594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43079900741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40492010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4259467124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59293365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43441915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8484992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1072998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92613840103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81776714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22214221954346</t>
+    <t xml:space="preserve">7.43079853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40491962432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42594575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59293413162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43441867828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84849977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10729932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92613983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81776666641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22214126586914</t>
   </si>
   <si>
     <t xml:space="preserve">7.20111465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14773797988892</t>
+    <t xml:space="preserve">7.1477370262146</t>
   </si>
   <si>
     <t xml:space="preserve">7.26419734954834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61681318283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5860800743103</t>
+    <t xml:space="preserve">7.61681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58607959747314</t>
   </si>
   <si>
     <t xml:space="preserve">7.70415687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63784027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78179693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7073917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62975215911865</t>
+    <t xml:space="preserve">7.66857290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63783979415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179597854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70739221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282545089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62975168228149</t>
   </si>
   <si>
     <t xml:space="preserve">7.69445133209229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65886783599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95163536071777</t>
+    <t xml:space="preserve">7.65886688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768667221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8222336769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032178878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95163488388062</t>
   </si>
   <si>
     <t xml:space="preserve">8.05353736877441</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">8.03089237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95001649856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06809425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19264221191406</t>
+    <t xml:space="preserve">7.95001745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06809520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19264125823975</t>
   </si>
   <si>
     <t xml:space="preserve">8.25329780578613</t>
@@ -1541,19 +1541,19 @@
     <t xml:space="preserve">8.28969287872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29777908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27756214141846</t>
+    <t xml:space="preserve">8.29778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31395530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27756118774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.233078956604</t>
+    <t xml:space="preserve">8.23307991027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.21286106109619</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794303894043</t>
+    <t xml:space="preserve">8.12794208526611</t>
   </si>
   <si>
     <t xml:space="preserve">8.24521064758301</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06647777557373</t>
+    <t xml:space="preserve">8.06647682189941</t>
   </si>
   <si>
     <t xml:space="preserve">8.1764669418335</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14007377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08588695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12389850616455</t>
+    <t xml:space="preserve">8.1400728225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08588790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12389945983887</t>
   </si>
   <si>
     <t xml:space="preserve">8.20881748199463</t>
@@ -1598,22 +1598,22 @@
     <t xml:space="preserve">8.2249927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30991172790527</t>
+    <t xml:space="preserve">8.30991077423096</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18859958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33417320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3179988861084</t>
+    <t xml:space="preserve">8.1885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33417415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31799793243408</t>
   </si>
   <si>
     <t xml:space="preserve">8.60510540008545</t>
@@ -1622,67 +1622,67 @@
     <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77089881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95691204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03778553009033</t>
+    <t xml:space="preserve">8.77089977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89625453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95691108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03778743743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.04183101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11866188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22379970550537</t>
+    <t xml:space="preserve">9.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379875183105</t>
   </si>
   <si>
     <t xml:space="preserve">9.33298015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32084846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4178991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44620609283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61604404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31276321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39768028259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30062961578369</t>
+    <t xml:space="preserve">9.32084941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22784423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41790103912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44620513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61604309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48260116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3127613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39768123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30063056945801</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11461925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67789077758789</t>
+    <t xml:space="preserve">9.19549369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1146183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67789268493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.65363025665283</t>
@@ -1691,46 +1691,46 @@
     <t xml:space="preserve">8.05192089080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89987421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1198558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24155330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067743301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05715703964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080888748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595754623413</t>
+    <t xml:space="preserve">7.89987373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531732559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11985492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83355617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4680027961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24155235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1606764793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05715656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595611572266</t>
   </si>
   <si>
     <t xml:space="preserve">7.33860206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47770643234253</t>
+    <t xml:space="preserve">7.47770690917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.59093189239502</t>
@@ -1742,70 +1742,70 @@
     <t xml:space="preserve">7.75106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76562309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98721981048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00824642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96619319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88370037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78017997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78988456726074</t>
+    <t xml:space="preserve">7.76562070846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.987220287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0082483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9661922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88369941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78017902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78988361358643</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74297714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84164476394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9807505607605</t>
+    <t xml:space="preserve">7.7429780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84164381027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98074865341187</t>
   </si>
   <si>
     <t xml:space="preserve">7.9111967086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68474626541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85134935379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74944639205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889699935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3903603553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24963903427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212198257446</t>
+    <t xml:space="preserve">7.68474721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85134983062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74944686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889652252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39036178588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2496395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212102890015</t>
   </si>
   <si>
     <t xml:space="preserve">7.49388122558594</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">7.39521408081055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26581430435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890640258789</t>
+    <t xml:space="preserve">7.26581478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890735626221</t>
   </si>
   <si>
     <t xml:space="preserve">7.35477685928345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01833772659302</t>
+    <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
     <t xml:space="preserve">7.05230474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93099117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0992112159729</t>
+    <t xml:space="preserve">6.93099164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09921169281006</t>
   </si>
   <si>
     <t xml:space="preserve">7.07980155944824</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">6.99245691299438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23831558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875423431396</t>
+    <t xml:space="preserve">7.23831701278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875375747681</t>
   </si>
   <si>
     <t xml:space="preserve">7.58446216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62328147888184</t>
+    <t xml:space="preserve">7.62328195571899</t>
   </si>
   <si>
     <t xml:space="preserve">7.56828737258911</t>
@@ -1862,55 +1862,55 @@
     <t xml:space="preserve">7.54078960418701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64430904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92898941040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78826761245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88046550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67342376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57152318954468</t>
+    <t xml:space="preserve">7.64430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92898845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78826713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88046646118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67342472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57152223587036</t>
   </si>
   <si>
     <t xml:space="preserve">7.83193922042847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92575550079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01795101165771</t>
+    <t xml:space="preserve">7.92575454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
     <t xml:space="preserve">7.80767822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00339412689209</t>
+    <t xml:space="preserve">8.00339508056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.39887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2371244430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45144271850586</t>
+    <t xml:space="preserve">8.23712348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45144176483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.57679843902588</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">8.38674259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26947402954102</t>
+    <t xml:space="preserve">8.2694730758667</t>
   </si>
   <si>
     <t xml:space="preserve">8.18051147460938</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034942626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83559799194336</t>
+    <t xml:space="preserve">8.35034847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83559989929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.92051792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15909767150879</t>
+    <t xml:space="preserve">9.08226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15909862518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.18740558624268</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07417964935303</t>
+    <t xml:space="preserve">9.07418060302734</t>
   </si>
   <si>
     <t xml:space="preserve">9.28445529937744</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">9.17931842803955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23188591003418</t>
+    <t xml:space="preserve">9.2318868637085</t>
   </si>
   <si>
     <t xml:space="preserve">9.34915542602539</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">9.3248929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26828002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36533069610596</t>
+    <t xml:space="preserve">9.26828098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36532974243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.5917797088623</t>
@@ -1988,58 +1988,58 @@
     <t xml:space="preserve">9.65647983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56751918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46642398834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47451114654541</t>
+    <t xml:space="preserve">9.56751823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45833778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4664249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47451305389404</t>
   </si>
   <si>
     <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163736343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83036136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84943771362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7955265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79967212677002</t>
+    <t xml:space="preserve">10.0163745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83036231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.036060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84943866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79552745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79967308044434</t>
   </si>
   <si>
     <t xml:space="preserve">9.73331928253174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47619724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50162124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44356060028076</t>
+    <t xml:space="preserve">9.4761962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50162029266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44356155395508</t>
   </si>
   <si>
     <t xml:space="preserve">8.27767562866211</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">8.12506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03050804138184</t>
+    <t xml:space="preserve">8.03050708770752</t>
   </si>
   <si>
     <t xml:space="preserve">8.22625160217285</t>
@@ -2072,85 +2072,85 @@
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728416442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08690738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0388011932373</t>
+    <t xml:space="preserve">8.00728321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08690929412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03880214691162</t>
   </si>
   <si>
     <t xml:space="preserve">7.87955093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67385292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091138839722</t>
+    <t xml:space="preserve">7.67385339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69376039505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5909104347229</t>
   </si>
   <si>
     <t xml:space="preserve">7.77670288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77172613143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70868873596191</t>
+    <t xml:space="preserve">7.77172660827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70868968963623</t>
   </si>
   <si>
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7003960609436</t>
+    <t xml:space="preserve">7.70039558410645</t>
   </si>
   <si>
     <t xml:space="preserve">7.73357248306274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58925151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62574625015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50299215316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72859525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82978439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9193639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12340068817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08359050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01557731628418</t>
+    <t xml:space="preserve">7.58925247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6257472038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50299119949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109834671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72859573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82978582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91936349868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12340259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12837886810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08359146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01557636260986</t>
   </si>
   <si>
     <t xml:space="preserve">7.96249437332153</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17814445495605</t>
+    <t xml:space="preserve">8.13667392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17814350128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.2196159362793</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">8.60529899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87900924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86656761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54723930358887</t>
+    <t xml:space="preserve">8.87901020050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86656856536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54724025726318</t>
   </si>
   <si>
     <t xml:space="preserve">8.38550090789795</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">8.4560022354126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30670642852783</t>
+    <t xml:space="preserve">8.30670547485352</t>
   </si>
   <si>
     <t xml:space="preserve">8.48088550567627</t>
@@ -2204,37 +2204,37 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462211608887</t>
+    <t xml:space="preserve">7.86462116241455</t>
   </si>
   <si>
     <t xml:space="preserve">7.36530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45820188522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57266283035278</t>
+    <t xml:space="preserve">7.45820236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5726637840271</t>
   </si>
   <si>
     <t xml:space="preserve">7.39184856414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22098636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38355445861816</t>
+    <t xml:space="preserve">7.22098731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38355493545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.38853073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7319130897522</t>
+    <t xml:space="preserve">7.73191261291504</t>
   </si>
   <si>
     <t xml:space="preserve">7.41839027404785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25084495544434</t>
+    <t xml:space="preserve">7.25084590911865</t>
   </si>
   <si>
     <t xml:space="preserve">7.42502546310425</t>
@@ -2243,58 +2243,58 @@
     <t xml:space="preserve">7.06173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17951536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56436824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44493246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76509141921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73854827880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92765665054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77836132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18975639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116239547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16985130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09852027893066</t>
+    <t xml:space="preserve">7.17951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25914001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.564368724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44493103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76509094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73854875564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92765712738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77836179733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16985034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09851932525635</t>
   </si>
   <si>
     <t xml:space="preserve">7.76343154907227</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">8.03216552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98903560638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84969139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742319107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9044337272644</t>
+    <t xml:space="preserve">7.98903656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84969186782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86130332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840782165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90443420410156</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">8.02718925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65394687652588</t>
+    <t xml:space="preserve">7.6539478302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.72361946105957</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">8.1267204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95917558670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17482757568359</t>
+    <t xml:space="preserve">7.95917463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17482662200928</t>
   </si>
   <si>
     <t xml:space="preserve">8.33988285064697</t>
@@ -2360,49 +2360,49 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55968189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46014976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44770908355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018321990967</t>
+    <t xml:space="preserve">8.5596809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46014881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44770812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018226623535</t>
   </si>
   <si>
     <t xml:space="preserve">8.6260347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47673797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37720680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60944747924805</t>
+    <t xml:space="preserve">8.47673892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37720775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60944652557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.85412788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95780563354492</t>
+    <t xml:space="preserve">8.95780658721924</t>
   </si>
   <si>
     <t xml:space="preserve">8.99927711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1651611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13198471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23566341400146</t>
+    <t xml:space="preserve">9.16516208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13198566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23566436767578</t>
   </si>
   <si>
     <t xml:space="preserve">9.48449230194092</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">9.52596187591553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50937461853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42643070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3144588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057823181152</t>
+    <t xml:space="preserve">9.50937366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42643260955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31445789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057918548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.38496017456055</t>
@@ -2435,64 +2435,64 @@
     <t xml:space="preserve">9.73746681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23151588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28957653045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35178375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3891077041626</t>
+    <t xml:space="preserve">9.7001428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57158184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33934116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23151683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28957748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35178279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38910675048828</t>
   </si>
   <si>
     <t xml:space="preserve">9.19833946228027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31031227111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26883983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11539745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12369155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04074668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06148338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01586627960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05319023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93292236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12783718109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88315773010254</t>
+    <t xml:space="preserve">9.31031322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21078109741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26884078979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11539649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12369060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04074859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06148433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01586532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05318927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93292331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12783813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88315677642822</t>
   </si>
   <si>
     <t xml:space="preserve">8.82509803771973</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">9.09880828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24395847320557</t>
+    <t xml:space="preserve">9.24395751953125</t>
   </si>
   <si>
     <t xml:space="preserve">9.58817005157471</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">9.1527214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25639915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15686893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21492671966553</t>
+    <t xml:space="preserve">9.2564001083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15686798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21492767333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.11954402923584</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">9.08221912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09466075897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11124897003174</t>
+    <t xml:space="preserve">9.0946626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11124992370605</t>
   </si>
   <si>
     <t xml:space="preserve">8.77533054351807</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">9.27298831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.107102394104</t>
+    <t xml:space="preserve">9.10710144042969</t>
   </si>
   <si>
     <t xml:space="preserve">8.77118492126465</t>
@@ -2549,28 +2549,28 @@
     <t xml:space="preserve">8.97024631500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68770122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14442539215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0863676071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05733776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99098300933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28128242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89559936523438</t>
+    <t xml:space="preserve">9.27713489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68770027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1444263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08636665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05733680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99098205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28128147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89559841156006</t>
   </si>
   <si>
     <t xml:space="preserve">8.25279331207275</t>
@@ -2579,19 +2579,19 @@
     <t xml:space="preserve">8.14994430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87457609176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74186706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042406082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35867166519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327259063721</t>
+    <t xml:space="preserve">7.87457513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74186563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327306747437</t>
   </si>
   <si>
     <t xml:space="preserve">6.73328399658203</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">6.53256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73797225952148</t>
+    <t xml:space="preserve">5.73797273635864</t>
   </si>
   <si>
     <t xml:space="preserve">6.38990116119385</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">6.12946128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24060440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20245122909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19083976745605</t>
+    <t xml:space="preserve">6.24060487747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2024507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19083881378174</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">6.71503639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33047199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8576979637146</t>
+    <t xml:space="preserve">7.33047103881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85769748687744</t>
   </si>
   <si>
     <t xml:space="preserve">6.98542928695679</t>
@@ -2642,31 +2642,31 @@
     <t xml:space="preserve">6.87594509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096881866455</t>
+    <t xml:space="preserve">6.87096977233887</t>
   </si>
   <si>
     <t xml:space="preserve">7.09159660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42336559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59256982803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310413360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92931699752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32715272903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264575958252</t>
+    <t xml:space="preserve">7.42336654663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59257030487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310317993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92931652069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32715320587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264528274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.21600961685181</t>
@@ -2681,40 +2681,40 @@
     <t xml:space="preserve">7.26411724090576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88286972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07363700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46844482421875</t>
+    <t xml:space="preserve">7.66224193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88286828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07363605499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
     <t xml:space="preserve">8.41038417816162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0520715713501</t>
+    <t xml:space="preserve">8.05207252502441</t>
   </si>
   <si>
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35232353210449</t>
+    <t xml:space="preserve">8.70897769927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35232448577881</t>
   </si>
   <si>
     <t xml:space="preserve">8.22956848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.485032081604</t>
+    <t xml:space="preserve">8.48503112792969</t>
   </si>
   <si>
     <t xml:space="preserve">8.294264793396</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">8.20800399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43112087249756</t>
+    <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
     <t xml:space="preserve">8.47259140014648</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">8.78777408599854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71312522888184</t>
+    <t xml:space="preserve">8.71312427520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874328613281</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">9.0034236907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34763717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3434886932373</t>
+    <t xml:space="preserve">9.34763622283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34348964691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
@@ -2756,16 +2756,16 @@
     <t xml:space="preserve">9.60475826263428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.040207862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2973289489746</t>
+    <t xml:space="preserve">10.0402069091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2973299026489</t>
   </si>
   <si>
     <t xml:space="preserve">9.94897079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0443525314331</t>
+    <t xml:space="preserve">10.0443534851074</t>
   </si>
   <si>
     <t xml:space="preserve">10.2848873138428</t>
@@ -2774,13 +2774,13 @@
     <t xml:space="preserve">9.87432193756104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98214626312256</t>
+    <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.065089225769</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96555995941162</t>
+    <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
     <t xml:space="preserve">9.95311737060547</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">10.7286319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6995992660522</t>
+    <t xml:space="preserve">10.6996011734009</t>
   </si>
   <si>
     <t xml:space="preserve">10.6747188568115</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">10.3388004302979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4093027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.401008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498346328735</t>
+    <t xml:space="preserve">10.4093017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4632139205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4010076522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
     <t xml:space="preserve">10.6415414810181</t>
@@ -2828,52 +2828,52 @@
     <t xml:space="preserve">10.9318408966064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7783966064453</t>
+    <t xml:space="preserve">10.778395652771</t>
   </si>
   <si>
     <t xml:space="preserve">10.6332473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042165756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024141311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.181209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5378618240356</t>
+    <t xml:space="preserve">10.6042175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53786277771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2309761047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4175958633423</t>
+    <t xml:space="preserve">10.3553886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.230975151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4175977706909</t>
   </si>
   <si>
     <t xml:space="preserve">11.064549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8654870986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8240156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6125106811523</t>
+    <t xml:space="preserve">10.8654861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8240146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.612512588501</t>
   </si>
   <si>
     <t xml:space="preserve">10.6000699996948</t>
@@ -2882,37 +2882,37 @@
     <t xml:space="preserve">10.7493667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6871604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6913070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7949867248535</t>
+    <t xml:space="preserve">10.687159538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6913080215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7949857711792</t>
   </si>
   <si>
     <t xml:space="preserve">10.6664237976074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5337171554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6249532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751867294312</t>
+    <t xml:space="preserve">10.5337162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6249523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751876831055</t>
   </si>
   <si>
     <t xml:space="preserve">10.0733842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4341840744019</t>
+    <t xml:space="preserve">10.4341850280762</t>
   </si>
   <si>
     <t xml:space="preserve">10.2392702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180656433105</t>
+    <t xml:space="preserve">10.3180646896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">10.1936511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0319128036499</t>
+    <t xml:space="preserve">10.0319137573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.81626224517822</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">9.46790218353271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44716644287109</t>
+    <t xml:space="preserve">9.44716739654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.72087860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55913925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71258354187012</t>
+    <t xml:space="preserve">9.5591402053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71258449554443</t>
   </si>
   <si>
     <t xml:space="preserve">9.67940711975098</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">9.74990749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82040882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.11070728302</t>
+    <t xml:space="preserve">9.82040977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0277662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
     <t xml:space="preserve">9.90335083007812</t>
@@ -2966,34 +2966,34 @@
     <t xml:space="preserve">10.1604738235474</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1729164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102394104004</t>
+    <t xml:space="preserve">10.1729154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102403640747</t>
   </si>
   <si>
     <t xml:space="preserve">10.0775318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1521787643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99044132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1065626144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96141147613525</t>
+    <t xml:space="preserve">10.1521797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99044227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1065607070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96141242980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.59646415710449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53425598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67111301422119</t>
+    <t xml:space="preserve">9.53425693511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67111110687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.74576091766357</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.96970653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2600059509277</t>
+    <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
     <t xml:space="preserve">10.3844194412231</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">10.3470945358276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3346538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1272983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2683010101318</t>
+    <t xml:space="preserve">10.3346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94482231140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1272974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2682991027832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5088319778442</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">10.4134483337402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5212745666504</t>
+    <t xml:space="preserve">10.5212755203247</t>
   </si>
   <si>
     <t xml:space="preserve">10.8074264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.757661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8779268264771</t>
+    <t xml:space="preserve">10.7576608657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8779277801514</t>
   </si>
   <si>
     <t xml:space="preserve">10.8945169448853</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8157215118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9733114242554</t>
+    <t xml:space="preserve">10.8157205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9733104705811</t>
   </si>
   <si>
     <t xml:space="preserve">10.898663520813</t>
@@ -3059,31 +3059,31 @@
     <t xml:space="preserve">10.8364562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9857540130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.873779296875</t>
+    <t xml:space="preserve">10.9857530593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
     <t xml:space="preserve">10.8447513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9774589538574</t>
+    <t xml:space="preserve">10.9774580001831</t>
   </si>
   <si>
     <t xml:space="preserve">11.1350498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1018724441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1474914550781</t>
+    <t xml:space="preserve">11.1018733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1474905014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">11.2843465805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6119699478149</t>
+    <t xml:space="preserve">11.6119709014893</t>
   </si>
   <si>
     <t xml:space="preserve">11.520733833313</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">11.4792623519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3507013320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1889629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1682281494141</t>
+    <t xml:space="preserve">11.350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1889619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1682271957397</t>
   </si>
   <si>
     <t xml:space="preserve">11.1226091384888</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">11.0355186462402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9442806243896</t>
+    <t xml:space="preserve">10.944281578064</t>
   </si>
   <si>
     <t xml:space="preserve">10.7452192306519</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">10.6788644790649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9935064315796</t>
+    <t xml:space="preserve">11.2926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9935054779053</t>
   </si>
   <si>
     <t xml:space="preserve">12.1096258163452</t>
@@ -3146,40 +3146,40 @@
     <t xml:space="preserve">12.4455442428589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2630701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5948419570923</t>
+    <t xml:space="preserve">12.263069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953088760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.594841003418</t>
   </si>
   <si>
     <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584537506104</t>
+    <t xml:space="preserve">12.358452796936</t>
   </si>
   <si>
     <t xml:space="preserve">12.1718339920044</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3169832229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1842737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0557126998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3377170562744</t>
+    <t xml:space="preserve">12.3169822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1842746734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0557136535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.337718963623</t>
   </si>
   <si>
     <t xml:space="preserve">12.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0847425460815</t>
+    <t xml:space="preserve">12.0847434997559</t>
   </si>
   <si>
     <t xml:space="preserve">12.2879524230957</t>
@@ -3200,49 +3200,49 @@
     <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1635389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2174501419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3543071746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1759796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9727716445923</t>
+    <t xml:space="preserve">12.163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2174510955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3543081283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1759805679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
     <t xml:space="preserve">11.97691822052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9437408447266</t>
+    <t xml:space="preserve">11.9437417984009</t>
   </si>
   <si>
     <t xml:space="preserve">12.1179208755493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244125366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5580587387085</t>
+    <t xml:space="preserve">11.7820043563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5580577850342</t>
   </si>
   <si>
     <t xml:space="preserve">11.5539112091064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4626741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5746469497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4834098815918</t>
+    <t xml:space="preserve">11.4626731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5746459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4834089279175</t>
   </si>
   <si>
     <t xml:space="preserve">11.5912342071533</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">11.5995283126831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5870876312256</t>
+    <t xml:space="preserve">11.5870885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7405309677124</t>
+    <t xml:space="preserve">11.7405300140381</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">11.8981227874756</t>
   </si>
   <si>
-    <t xml:space="preserve">11.952033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5456161499023</t>
+    <t xml:space="preserve">11.9520349502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.545615196228</t>
   </si>
   <si>
     <t xml:space="preserve">11.5331745147705</t>
@@ -3284,34 +3284,34 @@
     <t xml:space="preserve">11.4751148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6783246994019</t>
+    <t xml:space="preserve">11.6783227920532</t>
   </si>
   <si>
     <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064168930054</t>
+    <t xml:space="preserve">11.9064159393311</t>
   </si>
   <si>
     <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142412185669</t>
+    <t xml:space="preserve">12.0142421722412</t>
   </si>
   <si>
     <t xml:space="preserve">11.6949138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8732395172119</t>
+    <t xml:space="preserve">11.8732385635376</t>
   </si>
   <si>
     <t xml:space="preserve">11.6617364883423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7322378158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7446794509888</t>
+    <t xml:space="preserve">11.7322368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7446784973145</t>
   </si>
   <si>
     <t xml:space="preserve">11.6534423828125</t>
@@ -3323,16 +3323,16 @@
     <t xml:space="preserve">11.7654151916504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1640796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2055521011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.305082321167</t>
+    <t xml:space="preserve">11.5787935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.164080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2055511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050832748413</t>
   </si>
   <si>
     <t xml:space="preserve">11.4129085540771</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">11.4336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3631420135498</t>
+    <t xml:space="preserve">11.3299646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3631429672241</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382596969604</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">11.3880243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714361190796</t>
+    <t xml:space="preserve">11.3714370727539</t>
   </si>
   <si>
     <t xml:space="preserve">11.4917030334473</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">11.5124397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6451482772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5622043609619</t>
+    <t xml:space="preserve">11.6451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5622034072876</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248804092407</t>
@@ -3374,31 +3374,31 @@
     <t xml:space="preserve">11.5953817367554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5497627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6658821105957</t>
+    <t xml:space="preserve">11.5497636795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.66588306427</t>
   </si>
   <si>
     <t xml:space="preserve">11.9312992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8607978820801</t>
+    <t xml:space="preserve">11.8607988357544</t>
   </si>
   <si>
     <t xml:space="preserve">11.6410007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.026683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1013326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.213303565979</t>
+    <t xml:space="preserve">11.8068857192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1013317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2133054733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.2423343658447</t>
@@ -3407,34 +3407,34 @@
     <t xml:space="preserve">12.1967153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.308687210083</t>
+    <t xml:space="preserve">12.3086891174316</t>
   </si>
   <si>
     <t xml:space="preserve">12.1510972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4787197113037</t>
+    <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0391254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2215995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3335723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7151079177856</t>
+    <t xml:space="preserve">11.8690929412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2215986251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.333571434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7151069641113</t>
   </si>
   <si>
     <t xml:space="preserve">12.5367803573608</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">12.8975820541382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2293510437012</t>
+    <t xml:space="preserve">13.2293519973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.3827962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.453296661377</t>
+    <t xml:space="preserve">13.4532957077026</t>
   </si>
   <si>
     <t xml:space="preserve">13.5942993164062</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">13.4698848724365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201192855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3496179580688</t>
+    <t xml:space="preserve">13.4201202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3496170043945</t>
   </si>
   <si>
     <t xml:space="preserve">13.2252044677734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4781808853149</t>
+    <t xml:space="preserve">13.4781799316406</t>
   </si>
   <si>
     <t xml:space="preserve">13.2169103622437</t>
@@ -3488,34 +3488,34 @@
     <t xml:space="preserve">13.1837339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2583808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629981994629</t>
+    <t xml:space="preserve">13.2583818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629962921143</t>
   </si>
   <si>
     <t xml:space="preserve">13.2625293731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9514942169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8644037246704</t>
+    <t xml:space="preserve">12.9514951705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8644046783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.8685512542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7939023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9349050521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.831226348877</t>
+    <t xml:space="preserve">12.7607259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7939033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9349060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312273025513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482843399048</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">12.6611948013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9763765335083</t>
+    <t xml:space="preserve">12.9763774871826</t>
   </si>
   <si>
     <t xml:space="preserve">13.237645149231</t>
@@ -3545,49 +3545,49 @@
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9431991577148</t>
+    <t xml:space="preserve">12.9432001113892</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9971122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7690210342407</t>
+    <t xml:space="preserve">12.9971132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7690200805664</t>
   </si>
   <si>
     <t xml:space="preserve">12.644606590271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9722290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888191223145</t>
+    <t xml:space="preserve">12.9722309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888181686401</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9929647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2044687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1173791885376</t>
+    <t xml:space="preserve">13.1090850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9929656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2044696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1173782348633</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850666046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523580551147</t>
+    <t xml:space="preserve">13.7850685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523590087891</t>
   </si>
   <si>
     <t xml:space="preserve">13.8016548156738</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">13.7726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7975101470947</t>
+    <t xml:space="preserve">13.7975091934204</t>
   </si>
   <si>
     <t xml:space="preserve">13.9219226837158</t>
@@ -3608,28 +3608,28 @@
     <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7270078659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6979780197144</t>
+    <t xml:space="preserve">13.7270069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69797706604</t>
   </si>
   <si>
     <t xml:space="preserve">14.0048656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7643308639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173063278198</t>
+    <t xml:space="preserve">13.764331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878095626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173082351685</t>
   </si>
   <si>
     <t xml:space="preserve">14.2246627807617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3324890136719</t>
+    <t xml:space="preserve">14.3324899673462</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712203979492</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">14.1583089828491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2951641082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3532238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2619876861572</t>
+    <t xml:space="preserve">14.2951650619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3532257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2619867324829</t>
   </si>
   <si>
     <t xml:space="preserve">14.3076066970825</t>
@@ -3653,34 +3653,34 @@
     <t xml:space="preserve">14.2163686752319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.12513256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3006267547607</t>
+    <t xml:space="preserve">14.1251316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3006258010864</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255081176758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8597507476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6542940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2819042205811</t>
+    <t xml:space="preserve">13.8597526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6542949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605037689209</t>
+    <t xml:space="preserve">13.2605018615723</t>
   </si>
   <si>
     <t xml:space="preserve">13.4359970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1363735198975</t>
+    <t xml:space="preserve">13.1363725662231</t>
   </si>
   <si>
     <t xml:space="preserve">13.1834564208984</t>
@@ -3689,13 +3689,13 @@
     <t xml:space="preserve">13.5515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9068355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.645733833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4488372802734</t>
+    <t xml:space="preserve">13.906834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6457328796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4488382339478</t>
   </si>
   <si>
     <t xml:space="preserve">13.4188756942749</t>
@@ -3719,31 +3719,31 @@
     <t xml:space="preserve">12.965160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9523181915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9095134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2433815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2519416809082</t>
+    <t xml:space="preserve">12.9523191452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9095153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2433824539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2519426345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.2134199142456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4531192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4873609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6842575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562217712402</t>
+    <t xml:space="preserve">13.4531183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.487361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6842555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562227249146</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589506149292</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">13.0122423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741451263428</t>
+    <t xml:space="preserve">13.7741441726685</t>
   </si>
   <si>
     <t xml:space="preserve">13.8511905670166</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">13.6114912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2861862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0293655395508</t>
+    <t xml:space="preserve">13.2861852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0293645858765</t>
   </si>
   <si>
     <t xml:space="preserve">13.1920166015625</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">13.1320934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7597036361694</t>
+    <t xml:space="preserve">12.7597026824951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3616313934326</t>
@@ -3788,25 +3788,25 @@
     <t xml:space="preserve">12.4900417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857606887817</t>
+    <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8538703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.900954246521</t>
+    <t xml:space="preserve">12.85387134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009532928467</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.849591255188</t>
+    <t xml:space="preserve">12.7682638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8495903015137</t>
   </si>
   <si>
     <t xml:space="preserve">13.0550470352173</t>
@@ -3824,16 +3824,16 @@
     <t xml:space="preserve">13.6799764633179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5430068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4103145599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.277624130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4301166534424</t>
+    <t xml:space="preserve">13.5430059432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4103155136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2776250839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4301176071167</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
@@ -3842,13 +3842,13 @@
     <t xml:space="preserve">12.7768249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0234832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0363245010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8351488113403</t>
+    <t xml:space="preserve">12.0234851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0363254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.835147857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.9576787948608</t>
@@ -3857,43 +3857,43 @@
     <t xml:space="preserve">10.8720722198486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5339260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7837858200073</t>
+    <t xml:space="preserve">10.5339250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783784866333</t>
   </si>
   <si>
     <t xml:space="preserve">11.3172273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5954494476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.826587677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950729370117</t>
+    <t xml:space="preserve">11.5954504013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8265886306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.895073890686</t>
   </si>
   <si>
     <t xml:space="preserve">12.5157232284546</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9892406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106420516968</t>
+    <t xml:space="preserve">11.9892416000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0106430053711</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849615097046</t>
+    <t xml:space="preserve">11.9849605560303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8479900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9507188796997</t>
+    <t xml:space="preserve">11.9507179260254</t>
   </si>
   <si>
     <t xml:space="preserve">12.3145475387573</t>
@@ -3914,22 +3914,22 @@
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262111663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188276290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.946436882019</t>
+    <t xml:space="preserve">12.1262121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.318826675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9464378356934</t>
   </si>
   <si>
     <t xml:space="preserve">11.9079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9036331176758</t>
+    <t xml:space="preserve">11.9036340713501</t>
   </si>
   <si>
     <t xml:space="preserve">11.8009061813354</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">11.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771524429321</t>
+    <t xml:space="preserve">11.3771533966064</t>
   </si>
   <si>
     <t xml:space="preserve">11.0775279998779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0903692245483</t>
+    <t xml:space="preserve">11.090368270874</t>
   </si>
   <si>
     <t xml:space="preserve">10.5724477767944</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938491821289</t>
+    <t xml:space="preserve">10.5938501358032</t>
   </si>
   <si>
     <t xml:space="preserve">10.6109714508057</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">10.8292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8035869598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7693433761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1668996810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1403942108154</t>
+    <t xml:space="preserve">10.8035860061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7693424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.166898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1403951644897</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.5423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969728469849</t>
+    <t xml:space="preserve">11.6969738006592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6351318359375</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">11.560037612915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1580638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4893608093262</t>
+    <t xml:space="preserve">11.1580648422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4893617630005</t>
   </si>
   <si>
     <t xml:space="preserve">11.37451171875</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">9.62968349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14378261566162</t>
+    <t xml:space="preserve">9.14378356933594</t>
   </si>
   <si>
     <t xml:space="preserve">9.13052940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74453353881836</t>
+    <t xml:space="preserve">9.74453163146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">9.89030265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92122364044189</t>
+    <t xml:space="preserve">9.92122459411621</t>
   </si>
   <si>
     <t xml:space="preserve">10.1818437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4645500183105</t>
+    <t xml:space="preserve">10.4645509719849</t>
   </si>
   <si>
     <t xml:space="preserve">10.6191558837891</t>
@@ -4079,10 +4079,10 @@
     <t xml:space="preserve">10.4778022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3894567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890817642212</t>
+    <t xml:space="preserve">10.3894577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890808105469</t>
   </si>
   <si>
     <t xml:space="preserve">10.1244201660156</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">9.9786491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2171821594238</t>
+    <t xml:space="preserve">10.2171812057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.7384214401245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5970687866211</t>
+    <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
     <t xml:space="preserve">10.3585357666016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83287811279297</t>
+    <t xml:space="preserve">9.83287906646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.85054779052734</t>
@@ -4115,37 +4115,37 @@
     <t xml:space="preserve">10.0449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5661478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0934991836548</t>
+    <t xml:space="preserve">10.5661487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0007343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6809968948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6500768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.999041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8841924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8267679214478</t>
+    <t xml:space="preserve">10.0758285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0007352828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6809988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6500759124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9990425109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8841915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8267688751221</t>
   </si>
   <si>
     <t xml:space="preserve">10.707501411438</t>
@@ -4157,22 +4157,22 @@
     <t xml:space="preserve">10.9062795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9592866897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9902067184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7781772613525</t>
+    <t xml:space="preserve">10.959285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9902057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7781782150269</t>
   </si>
   <si>
     <t xml:space="preserve">10.5308094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6544942855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.146505355835</t>
+    <t xml:space="preserve">10.6544933319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1465063095093</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">10.0051517486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93447589874268</t>
+    <t xml:space="preserve">9.93447685241699</t>
   </si>
   <si>
     <t xml:space="preserve">9.4529914855957</t>
@@ -4193,61 +4193,61 @@
     <t xml:space="preserve">9.54133796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55458927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42648887634277</t>
+    <t xml:space="preserve">9.55458831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42648792266846</t>
   </si>
   <si>
     <t xml:space="preserve">9.84613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55017280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58109283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59876251220703</t>
+    <t xml:space="preserve">9.55017185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58109474182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59876155853271</t>
   </si>
   <si>
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.919529914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2287406921387</t>
+    <t xml:space="preserve">10.8797740936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9195308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.228741645813</t>
   </si>
   <si>
     <t xml:space="preserve">11.3082523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1183080673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9946250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5528964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8046808242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215036392212</t>
+    <t xml:space="preserve">11.1183090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9946241378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5528945922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8046817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215026855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.9372005462646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.02112865448</t>
+    <t xml:space="preserve">11.3259210586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0211296081543</t>
   </si>
   <si>
     <t xml:space="preserve">10.8488540649414</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8471612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5379505157471</t>
+    <t xml:space="preserve">11.8471603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5379514694214</t>
   </si>
   <si>
     <t xml:space="preserve">10.9460344314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9548683166504</t>
+    <t xml:space="preserve">10.9548692703247</t>
   </si>
   <si>
     <t xml:space="preserve">10.5352277755737</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">11.2331581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2110719680786</t>
+    <t xml:space="preserve">11.2110710144043</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.962010383606</t>
+    <t xml:space="preserve">11.9620094299316</t>
   </si>
   <si>
     <t xml:space="preserve">12.0591897964478</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">12.0503568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1961278915405</t>
+    <t xml:space="preserve">12.1961269378662</t>
   </si>
   <si>
     <t xml:space="preserve">12.3949041366577</t>
@@ -4319,64 +4319,64 @@
     <t xml:space="preserve">12.6201858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6246032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6908626556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527055740356</t>
+    <t xml:space="preserve">12.3772354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6246023178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6908617019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527046203613</t>
   </si>
   <si>
     <t xml:space="preserve">12.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9205617904663</t>
+    <t xml:space="preserve">12.920560836792</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0354118347168</t>
+    <t xml:space="preserve">13.0354108810425</t>
   </si>
   <si>
     <t xml:space="preserve">13.2518577575684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1811819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2827777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3843765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.441801071167</t>
+    <t xml:space="preserve">13.1811809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2827787399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3843755722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4418020248413</t>
   </si>
   <si>
     <t xml:space="preserve">13.5743198394775</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4285488128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3578720092773</t>
+    <t xml:space="preserve">13.4285497665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3578729629517</t>
   </si>
   <si>
     <t xml:space="preserve">13.6405792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6494131088257</t>
+    <t xml:space="preserve">13.6494140625</t>
   </si>
   <si>
     <t xml:space="preserve">13.9144506454468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8835296630859</t>
+    <t xml:space="preserve">13.8835306167603</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522336959839</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">13.6759166717529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.773097038269</t>
+    <t xml:space="preserve">13.7730979919434</t>
   </si>
   <si>
     <t xml:space="preserve">13.923285484314</t>
@@ -4403,16 +4403,16 @@
     <t xml:space="preserve">13.1414251327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3534555435181</t>
+    <t xml:space="preserve">13.3534545898438</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5345630645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5831546783447</t>
+    <t xml:space="preserve">13.5345640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5831537246704</t>
   </si>
   <si>
     <t xml:space="preserve">13.834939956665</t>
@@ -4421,10 +4421,10 @@
     <t xml:space="preserve">13.7112560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8658599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1883220672607</t>
+    <t xml:space="preserve">13.8658609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1883230209351</t>
   </si>
   <si>
     <t xml:space="preserve">14.5947132110596</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">14.5726270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6963109970093</t>
+    <t xml:space="preserve">14.696310043335</t>
   </si>
   <si>
     <t xml:space="preserve">14.8685846328735</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">14.7095613479614</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7934923171997</t>
+    <t xml:space="preserve">14.7934913635254</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">14.3429279327393</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5196180343628</t>
+    <t xml:space="preserve">14.5196189880371</t>
   </si>
   <si>
     <t xml:space="preserve">14.3385095596313</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">14.5107841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4312734603882</t>
+    <t xml:space="preserve">14.4312725067139</t>
   </si>
   <si>
     <t xml:space="preserve">14.5328712463379</t>
@@ -4496,37 +4496,37 @@
     <t xml:space="preserve">14.9392614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8553342819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.009937286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6918916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5682096481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9701824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7714023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6433029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453706741333</t>
+    <t xml:space="preserve">14.8553323745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0099382400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6609706878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6918926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9701814651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7714042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6433038711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453716278076</t>
   </si>
   <si>
     <t xml:space="preserve">14.1397314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.963041305542</t>
+    <t xml:space="preserve">13.9630422592163</t>
   </si>
   <si>
     <t xml:space="preserve">14.1927404403687</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">14.444525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2236614227295</t>
+    <t xml:space="preserve">14.2236604690552</t>
   </si>
   <si>
     <t xml:space="preserve">14.3473443984985</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402982711792</t>
+    <t xml:space="preserve">12.2402992248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.4523296356201</t>
@@ -4568,25 +4568,25 @@
     <t xml:space="preserve">11.502613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7455625534058</t>
+    <t xml:space="preserve">11.7455635070801</t>
   </si>
   <si>
     <t xml:space="preserve">11.2684965133667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4169912338257</t>
+    <t xml:space="preserve">11.6837224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.315393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169902801514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.023853302002</t>
+    <t xml:space="preserve">12.0238523483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4595,16 +4595,16 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500919342041</t>
+    <t xml:space="preserve">12.5009183883667</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2933073043823</t>
+    <t xml:space="preserve">12.4920854568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.293306350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579689025879</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">12.7438697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5892648696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5362567901611</t>
+    <t xml:space="preserve">12.3684005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5892658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5362577438354</t>
   </si>
   <si>
     <t xml:space="preserve">12.3065586090088</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">11.7588148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1121978759766</t>
+    <t xml:space="preserve">12.1121988296509</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632322311401</t>
@@ -4664,19 +4664,19 @@
     <t xml:space="preserve">11.9399242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8824996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2022380828857</t>
+    <t xml:space="preserve">11.8824987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2022371292114</t>
   </si>
   <si>
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2199058532715</t>
+    <t xml:space="preserve">11.0343809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2199068069458</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653009414673</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">11.2950000762939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0873880386353</t>
+    <t xml:space="preserve">11.0873870849609</t>
   </si>
   <si>
     <t xml:space="preserve">11.1448125839233</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.30748462677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638666152954</t>
+    <t xml:space="preserve">11.0638675689697</t>
   </si>
   <si>
     <t xml:space="preserve">11.2753086090088</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">11.3856248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4361867904663</t>
+    <t xml:space="preserve">11.436185836792</t>
   </si>
   <si>
     <t xml:space="preserve">11.6522245407104</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">11.5832767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913463592529</t>
+    <t xml:space="preserve">11.4913454055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.4959421157837</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">11.4499769210815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4591693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7533473968506</t>
+    <t xml:space="preserve">11.4591703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7533483505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6935930252075</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">11.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0041131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9949188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0960426330566</t>
+    <t xml:space="preserve">11.0041122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9949197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.096043586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.1833772659302</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">11.2890977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0868511199951</t>
+    <t xml:space="preserve">11.0868501663208</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4683628082275</t>
+    <t xml:space="preserve">11.4683637619019</t>
   </si>
   <si>
     <t xml:space="preserve">11.8131036758423</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">12.1486501693726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3279161453247</t>
+    <t xml:space="preserve">12.3187217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3279151916504</t>
   </si>
   <si>
     <t xml:space="preserve">12.5117769241333</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.3784770965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5301637649536</t>
+    <t xml:space="preserve">12.5301628112793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6358833312988</t>
@@ -4832,19 +4832,19 @@
     <t xml:space="preserve">12.9760274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4428281784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255661010742</t>
+    <t xml:space="preserve">12.7645864486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4428291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255670547485</t>
   </si>
   <si>
     <t xml:space="preserve">12.4750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2385368347168</t>
+    <t xml:space="preserve">11.2385358810425</t>
   </si>
   <si>
     <t xml:space="preserve">12.0383338928223</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">11.964789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9555959701538</t>
+    <t xml:space="preserve">11.9555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5005388259888</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">11.6016626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5510997772217</t>
+    <t xml:space="preserve">11.551100730896</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143280029297</t>
@@ -4877,19 +4877,19 @@
     <t xml:space="preserve">11.5786800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7073831558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625408172607</t>
+    <t xml:space="preserve">11.7073822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625417709351</t>
   </si>
   <si>
     <t xml:space="preserve">11.7441549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6384353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465040206909</t>
+    <t xml:space="preserve">11.6384344100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465049743652</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855243682861</t>
@@ -4898,19 +4898,19 @@
     <t xml:space="preserve">11.7487516403198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6154518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9489545822144</t>
+    <t xml:space="preserve">11.6154527664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.94895362854</t>
   </si>
   <si>
     <t xml:space="preserve">10.7558994293213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.870813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570232391357</t>
+    <t xml:space="preserve">10.8708124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570241928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.8478298187256</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">10.889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7283210754395</t>
+    <t xml:space="preserve">10.7283201217651</t>
   </si>
   <si>
     <t xml:space="preserve">10.8294439315796</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">10.6915483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6547765731812</t>
+    <t xml:space="preserve">10.6547756195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7329168319702</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">10.6271963119507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858287811279</t>
+    <t xml:space="preserve">10.5858278274536</t>
   </si>
   <si>
     <t xml:space="preserve">10.287052154541</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">10.1445598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1215772628784</t>
+    <t xml:space="preserve">10.1215782165527</t>
   </si>
   <si>
     <t xml:space="preserve">9.91932964324951</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">9.99747085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79522228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399631500244</t>
+    <t xml:space="preserve">9.79522323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399621963501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721391677856</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">9.90094375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96989154815674</t>
+    <t xml:space="preserve">9.96989250183105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1951217651367</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">10.043436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0848045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0388402938843</t>
+    <t xml:space="preserve">10.0848054885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.03883934021</t>
   </si>
   <si>
     <t xml:space="preserve">10.057225227356</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">10.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629457473755</t>
+    <t xml:space="preserve">10.1629467010498</t>
   </si>
   <si>
     <t xml:space="preserve">10.2181043624878</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">11.0454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3948183059692</t>
+    <t xml:space="preserve">11.3948192596436</t>
   </si>
   <si>
     <t xml:space="preserve">11.5097322463989</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">11.0592708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9995164871216</t>
+    <t xml:space="preserve">10.9995155334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9903221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477283477783</t>
+    <t xml:space="preserve">10.9903230667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477293014526</t>
   </si>
   <si>
     <t xml:space="preserve">11.3672389984131</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">11.5970659255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7763319015503</t>
+    <t xml:space="preserve">11.776330947876</t>
   </si>
   <si>
     <t xml:space="preserve">11.8866481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3646879196167</t>
+    <t xml:space="preserve">12.3646869659424</t>
   </si>
   <si>
     <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4290399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.401460647583</t>
+    <t xml:space="preserve">12.4290390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4014596939087</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3692836761475</t>
+    <t xml:space="preserve">12.3692846298218</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554944992065</t>
@@ -5099,7 +5099,7 @@
     <t xml:space="preserve">12.5485486984253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2497749328613</t>
+    <t xml:space="preserve">12.249773979187</t>
   </si>
   <si>
     <t xml:space="preserve">12.5393571853638</t>
@@ -5111,25 +5111,25 @@
     <t xml:space="preserve">12.6404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.456618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7507972717285</t>
+    <t xml:space="preserve">12.4566192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7507963180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.6680593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8473243713379</t>
+    <t xml:space="preserve">12.8473253250122</t>
   </si>
   <si>
     <t xml:space="preserve">12.870306968689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9024829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7783756256104</t>
+    <t xml:space="preserve">12.9024820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7783765792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.8105525970459</t>
@@ -5138,16 +5138,16 @@
     <t xml:space="preserve">12.7094278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6174983978271</t>
+    <t xml:space="preserve">12.6174974441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.5577421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8381319046021</t>
+    <t xml:space="preserve">12.6588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8381309509277</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819499969482</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">11.8544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8452796936035</t>
+    <t xml:space="preserve">11.8452787399292</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705099105835</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">12.1348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0888948440552</t>
+    <t xml:space="preserve">12.0888957977295</t>
   </si>
   <si>
     <t xml:space="preserve">11.9326124191284</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">11.8085069656372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8958396911621</t>
+    <t xml:space="preserve">11.8958406448364</t>
   </si>
   <si>
     <t xml:space="preserve">12.0107536315918</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">12.194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1532468795776</t>
+    <t xml:space="preserve">12.153247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.1854228973389</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">12.0934915542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808271408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1578435897827</t>
+    <t xml:space="preserve">12.1808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.157844543457</t>
   </si>
   <si>
     <t xml:space="preserve">12.2957391738892</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">12.3922672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6266899108887</t>
+    <t xml:space="preserve">12.626690864563</t>
   </si>
   <si>
     <t xml:space="preserve">12.6220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.833535194397</t>
+    <t xml:space="preserve">12.8335342407227</t>
   </si>
   <si>
     <t xml:space="preserve">12.9162721633911</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">12.4796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2242412567139</t>
+    <t xml:space="preserve">13.2242403030396</t>
   </si>
   <si>
     <t xml:space="preserve">13.136905670166</t>
@@ -5270,7 +5270,7 @@
     <t xml:space="preserve">13.2012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.270206451416</t>
+    <t xml:space="preserve">13.2702054977417</t>
   </si>
   <si>
     <t xml:space="preserve">13.1736783981323</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">12.6726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6818494796753</t>
+    <t xml:space="preserve">12.681848526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9990100860596</t>
+    <t xml:space="preserve">12.9990110397339</t>
   </si>
   <si>
     <t xml:space="preserve">13.0265893936157</t>
@@ -5309,16 +5309,16 @@
     <t xml:space="preserve">12.8611135482788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0541687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587644577026</t>
+    <t xml:space="preserve">13.0541677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.058765411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2748022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460990905762</t>
+    <t xml:space="preserve">13.1461000442505</t>
   </si>
   <si>
     <t xml:space="preserve">13.233434677124</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7804222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.92751121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9045276641846</t>
+    <t xml:space="preserve">13.780421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9275102615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9045286178589</t>
   </si>
   <si>
     <t xml:space="preserve">14.0102481842041</t>
@@ -6279,6 +6279,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.9150009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0149993896484</t>
   </si>
 </sst>
 </file>
@@ -71435,7 +71438,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6496296296</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>1110327</v>
@@ -71456,6 +71459,32 @@
         <v>2088</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495138889</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>1236334</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>19.1299991607666</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>18.7700004577637</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>18.8649997711182</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>19.0149993896484</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="2090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="2091">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13951969146729</t>
+    <t xml:space="preserve">5.32048892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209434509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951873779297</t>
   </si>
   <si>
     <t xml:space="preserve">5.2625789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1322808265686</t>
+    <t xml:space="preserve">5.13228130340576</t>
   </si>
   <si>
     <t xml:space="preserve">5.26619815826416</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">5.31325006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19381093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0454158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07437181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65814161300659</t>
+    <t xml:space="preserve">5.19381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04541540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07437086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65814208984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.82101392745972</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21190690994263</t>
+    <t xml:space="preserve">5.21190643310547</t>
   </si>
   <si>
     <t xml:space="preserve">5.04903507232666</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">5.14675855636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16485500335693</t>
+    <t xml:space="preserve">5.16485548019409</t>
   </si>
   <si>
     <t xml:space="preserve">5.12504148483276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88978290557861</t>
+    <t xml:space="preserve">4.88978242874146</t>
   </si>
   <si>
     <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138736724854</t>
+    <t xml:space="preserve">4.74138832092285</t>
   </si>
   <si>
     <t xml:space="preserve">4.56765747070312</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">4.3432559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441219329834</t>
+    <t xml:space="preserve">4.45545768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441171646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.58213520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78482103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73414945602417</t>
+    <t xml:space="preserve">4.78482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73414897918701</t>
   </si>
   <si>
     <t xml:space="preserve">4.81377553939819</t>
@@ -140,40 +140,40 @@
     <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71243238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84996938705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88616275787354</t>
+    <t xml:space="preserve">4.71243333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84996891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88616228103638</t>
   </si>
   <si>
     <t xml:space="preserve">5.00922155380249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09246778488159</t>
+    <t xml:space="preserve">5.09246730804443</t>
   </si>
   <si>
     <t xml:space="preserve">5.10332584381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95493078231812</t>
+    <t xml:space="preserve">5.16847467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95493125915527</t>
   </si>
   <si>
     <t xml:space="preserve">4.84273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78120183944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713199615479</t>
+    <t xml:space="preserve">4.78120136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713151931763</t>
   </si>
   <si>
     <t xml:space="preserve">5.08884859085083</t>
@@ -188,94 +188,94 @@
     <t xml:space="preserve">5.1901912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362302780151</t>
+    <t xml:space="preserve">5.23362350463867</t>
   </si>
   <si>
     <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02008008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026657104492</t>
+    <t xml:space="preserve">5.12866115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02007961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026704788208</t>
   </si>
   <si>
     <t xml:space="preserve">4.94769239425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9730281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787887573242</t>
+    <t xml:space="preserve">4.97302770614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787935256958</t>
   </si>
   <si>
     <t xml:space="preserve">5.02369976043701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11418342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.121422290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544111251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28287506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27161121368408</t>
+    <t xml:space="preserve">5.11418437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406362533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28287410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">5.23030948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16647958755493</t>
+    <t xml:space="preserve">5.16647863388062</t>
   </si>
   <si>
     <t xml:space="preserve">5.3316855430603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30164909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39176177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2641019821167</t>
+    <t xml:space="preserve">5.30164861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.391761302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26410150527954</t>
   </si>
   <si>
     <t xml:space="preserve">5.25659227371216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05759191513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0988941192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96747875213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88863039016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78725433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79100799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76472473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7008957862854</t>
+    <t xml:space="preserve">5.05759334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09889459609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96747922897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88863086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78725385665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79100847244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76472520828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70089483261108</t>
   </si>
   <si>
     <t xml:space="preserve">4.96372509002686</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">4.90364933013916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90740442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77598905563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73844242095947</t>
+    <t xml:space="preserve">4.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7759895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73844289779663</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91866827011108</t>
+    <t xml:space="preserve">4.91866779327393</t>
   </si>
   <si>
     <t xml:space="preserve">4.98625326156616</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">4.97874402999878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01629066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92617750167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95245981216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9712347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483837127686</t>
+    <t xml:space="preserve">5.01629018783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92617797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95246028900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97123336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85483884811401</t>
   </si>
   <si>
     <t xml:space="preserve">4.87736654281616</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">4.8022723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197071075439</t>
+    <t xml:space="preserve">4.62204694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197118759155</t>
   </si>
   <si>
     <t xml:space="preserve">4.44182062149048</t>
@@ -341,58 +341,58 @@
     <t xml:space="preserve">4.4568395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56948089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093271255493</t>
+    <t xml:space="preserve">4.56948041915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093318939209</t>
   </si>
   <si>
     <t xml:space="preserve">4.80602693557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97498941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063205718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13017892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39676332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33668899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39300966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17523622512817</t>
+    <t xml:space="preserve">4.97498893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13017988204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39676380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33668851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39300870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17523574829102</t>
   </si>
   <si>
     <t xml:space="preserve">4.10014200210571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87485933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244408607483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2653489112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3179144859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1902551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20151853561401</t>
+    <t xml:space="preserve">3.87485885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31791496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20151901245117</t>
   </si>
   <si>
     <t xml:space="preserve">4.23531150817871</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">4.25032997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24657583236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27661323547363</t>
+    <t xml:space="preserve">4.2465763092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27661275863647</t>
   </si>
   <si>
     <t xml:space="preserve">4.09638738632202</t>
@@ -419,88 +419,88 @@
     <t xml:space="preserve">3.98750042915344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8373122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9386887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93493413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97248196601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746350288391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99876475334167</t>
+    <t xml:space="preserve">3.83731245994568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93868970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623658180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93493437767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97248148918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9987645149231</t>
   </si>
   <si>
     <t xml:space="preserve">3.82980275154114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82604765892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470852851868</t>
+    <t xml:space="preserve">3.82604718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348208427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470924377441</t>
   </si>
   <si>
     <t xml:space="preserve">4.05133056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07010459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04382133483887</t>
+    <t xml:space="preserve">4.07010412216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04382181167603</t>
   </si>
   <si>
     <t xml:space="preserve">4.01378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05883979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09263181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13768911361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12266969680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05508613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385921478271</t>
+    <t xml:space="preserve">4.05884027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09263277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1376895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1226692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05508470535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385873794556</t>
   </si>
   <si>
     <t xml:space="preserve">4.03255701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91240692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229351997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90489721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114235877991</t>
+    <t xml:space="preserve">3.91240668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229375839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478381156921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90489673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114212036133</t>
   </si>
   <si>
     <t xml:space="preserve">3.88987827301025</t>
@@ -509,34 +509,34 @@
     <t xml:space="preserve">3.81102919578552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88612389564514</t>
+    <t xml:space="preserve">3.88612413406372</t>
   </si>
   <si>
     <t xml:space="preserve">3.89738750457764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88236856460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8523313999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850102424622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61202931404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550881385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601049423218</t>
+    <t xml:space="preserve">3.88236880302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233068466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221871376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6120297908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7960102558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.96121740341187</t>
@@ -548,148 +548,148 @@
     <t xml:space="preserve">4.02504730224609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96497225761414</t>
+    <t xml:space="preserve">3.96497297286987</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08887815475464</t>
+    <t xml:space="preserve">4.0888786315918</t>
   </si>
   <si>
     <t xml:space="preserve">4.14519834518433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99500942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474640846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727458000183</t>
+    <t xml:space="preserve">3.99501085281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742514610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727481842041</t>
   </si>
   <si>
     <t xml:space="preserve">3.79225564002991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75170516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056539535522</t>
+    <t xml:space="preserve">3.751704454422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64056611061096</t>
   </si>
   <si>
     <t xml:space="preserve">3.60452055931091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54444456100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843712806702</t>
+    <t xml:space="preserve">3.54444479942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843688964844</t>
   </si>
   <si>
     <t xml:space="preserve">3.5414412021637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55646014213562</t>
+    <t xml:space="preserve">3.55645966529846</t>
   </si>
   <si>
     <t xml:space="preserve">3.60001468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47085285186768</t>
+    <t xml:space="preserve">3.4708526134491</t>
   </si>
   <si>
     <t xml:space="preserve">3.58799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66459560394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64507126808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66910123825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748627662659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857606887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10389709472656</t>
+    <t xml:space="preserve">3.66459584236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64507102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66910171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748579978943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73969006538391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857678413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144420623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1038966178894</t>
   </si>
   <si>
     <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11516046524048</t>
+    <t xml:space="preserve">4.04006624221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11516094207764</t>
   </si>
   <si>
     <t xml:space="preserve">4.00251913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07761383056641</t>
+    <t xml:space="preserve">4.07761335372925</t>
   </si>
   <si>
     <t xml:space="preserve">4.16772651672363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15270805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895248413086</t>
+    <t xml:space="preserve">4.15270757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895343780518</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512306213379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18274593353271</t>
+    <t xml:space="preserve">4.18274545669556</t>
   </si>
   <si>
     <t xml:space="preserve">4.22029209136963</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23906707763672</t>
+    <t xml:space="preserve">4.2390661239624</t>
   </si>
   <si>
     <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06259536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03631162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28787755966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30289649963379</t>
+    <t xml:space="preserve">4.12642431259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06259489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03631210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13393449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28787660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30289602279663</t>
   </si>
   <si>
     <t xml:space="preserve">4.33293342590332</t>
@@ -698,37 +698,37 @@
     <t xml:space="preserve">4.46810340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44557476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69338607788086</t>
+    <t xml:space="preserve">4.44557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6933856010437</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085647583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8097825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83981943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81353616714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79851722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72717761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85108423233032</t>
+    <t xml:space="preserve">4.67085742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80978202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83981990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81353664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79851770401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7271785736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85108375549316</t>
   </si>
   <si>
     <t xml:space="preserve">4.82104587554932</t>
@@ -740,25 +740,25 @@
     <t xml:space="preserve">5.07056093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13733148574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198259353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07448959350586</t>
+    <t xml:space="preserve">5.13733100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0744891166687</t>
   </si>
   <si>
     <t xml:space="preserve">5.12947559356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16875171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371162414551</t>
+    <t xml:space="preserve">5.16875219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552179336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371210098267</t>
   </si>
   <si>
     <t xml:space="preserve">5.3415675163269</t>
@@ -770,25 +770,25 @@
     <t xml:space="preserve">5.20410060882568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28265190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20017337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373819351196</t>
+    <t xml:space="preserve">5.28265237808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20017194747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373914718628</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092287063599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15696859359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29050779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26694250106812</t>
+    <t xml:space="preserve">5.15696907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29050874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26694202423096</t>
   </si>
   <si>
     <t xml:space="preserve">5.36906099319458</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">5.34942245483398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3847713470459</t>
+    <t xml:space="preserve">5.38477087020874</t>
   </si>
   <si>
     <t xml:space="preserve">5.21588325500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.219810962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25515937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32585716247559</t>
+    <t xml:space="preserve">5.21981143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2551589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32585763931274</t>
   </si>
   <si>
     <t xml:space="preserve">5.25123167037964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37298822402954</t>
+    <t xml:space="preserve">5.37298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">5.43975782394409</t>
@@ -830,49 +830,49 @@
     <t xml:space="preserve">5.577223777771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54187631607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63221120834351</t>
+    <t xml:space="preserve">5.5418758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63221073150635</t>
   </si>
   <si>
     <t xml:space="preserve">5.62435579299927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065279006958</t>
+    <t xml:space="preserve">5.50652694702148</t>
   </si>
   <si>
     <t xml:space="preserve">5.5379490852356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62042856216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55365943908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50260019302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41226434707642</t>
+    <t xml:space="preserve">5.62042903900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55365896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50259971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41226387023926</t>
   </si>
   <si>
     <t xml:space="preserve">5.52223777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61257314682007</t>
+    <t xml:space="preserve">5.61257362365723</t>
   </si>
   <si>
     <t xml:space="preserve">5.69112586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75789499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87572431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076345443726</t>
+    <t xml:space="preserve">5.75789546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87572383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076393127441</t>
   </si>
   <si>
     <t xml:space="preserve">5.73432970046997</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">5.64006662368774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65970420837402</t>
+    <t xml:space="preserve">5.65970468521118</t>
   </si>
   <si>
     <t xml:space="preserve">5.72647380828857</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6832709312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67148780822754</t>
+    <t xml:space="preserve">5.68326997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67148733139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.65577697753906</t>
@@ -902,25 +902,25 @@
     <t xml:space="preserve">5.77360534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86786794662476</t>
+    <t xml:space="preserve">5.86786842346191</t>
   </si>
   <si>
     <t xml:space="preserve">5.83644723892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82466459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8403754234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8285927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179613113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93463802337646</t>
+    <t xml:space="preserve">5.82466506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84037494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82859230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93463850021362</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034885406494</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">5.90714502334595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7971715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70290899276733</t>
+    <t xml:space="preserve">5.79717206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70290946960449</t>
   </si>
   <si>
     <t xml:space="preserve">5.78931570053101</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">5.89143419265747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78538846969604</t>
+    <t xml:space="preserve">5.78538799285889</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70683622360229</t>
+    <t xml:space="preserve">5.70683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">5.56936931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46725130081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66755962371826</t>
+    <t xml:space="preserve">5.46725082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293603897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66756010055542</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903394699097</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">5.75396776199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80109930038452</t>
+    <t xml:space="preserve">5.80109977722168</t>
   </si>
   <si>
     <t xml:space="preserve">5.8089542388916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91499996185303</t>
+    <t xml:space="preserve">5.91500043869019</t>
   </si>
   <si>
     <t xml:space="preserve">5.87965202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85215759277344</t>
+    <t xml:space="preserve">5.85215902328491</t>
   </si>
   <si>
     <t xml:space="preserve">5.84430313110352</t>
@@ -1010,76 +1010,76 @@
     <t xml:space="preserve">5.86001348495483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84823131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69505262374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6636323928833</t>
+    <t xml:space="preserve">5.84823083877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254705429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6950535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363191604614</t>
   </si>
   <si>
     <t xml:space="preserve">5.64792203903198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71861934661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83252048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76575088500977</t>
+    <t xml:space="preserve">5.71861886978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83252096176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76575040817261</t>
   </si>
   <si>
     <t xml:space="preserve">6.11530923843384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08388805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26063108444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24492073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31169033050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776309967041</t>
+    <t xml:space="preserve">6.08388757705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26063060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24492025375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31168937683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776214599609</t>
   </si>
   <si>
     <t xml:space="preserve">6.29990720748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29205226898193</t>
+    <t xml:space="preserve">6.29205179214478</t>
   </si>
   <si>
     <t xml:space="preserve">6.25670337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23706483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2527756690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20171594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23313665390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032228469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00926351547241</t>
+    <t xml:space="preserve">6.23706531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25277614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26455879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20171642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23313808441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926399230957</t>
   </si>
   <si>
     <t xml:space="preserve">6.1270923614502</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">6.22528266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28026914596558</t>
+    <t xml:space="preserve">6.28026866912842</t>
   </si>
   <si>
     <t xml:space="preserve">6.37060451507568</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">6.58662414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65339326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53949213027954</t>
+    <t xml:space="preserve">6.65339422225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53949165344238</t>
   </si>
   <si>
     <t xml:space="preserve">6.60626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63768243789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5630578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8301362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874168395996</t>
+    <t xml:space="preserve">6.63768291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56305694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83013582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874263763428</t>
   </si>
   <si>
     <t xml:space="preserve">6.79086065292358</t>
@@ -1139,106 +1139,106 @@
     <t xml:space="preserve">6.68088626861572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77907705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75551128387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336622238159</t>
+    <t xml:space="preserve">6.72409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77907752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75551176071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336717605591</t>
   </si>
   <si>
     <t xml:space="preserve">6.85762929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81049823760986</t>
+    <t xml:space="preserve">6.86155652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81049776077271</t>
   </si>
   <si>
     <t xml:space="preserve">6.70445203781128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63375425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40356969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58031272888184</t>
+    <t xml:space="preserve">6.63375568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99902439117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3328709602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4035701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031225204468</t>
   </si>
   <si>
     <t xml:space="preserve">7.54103660583496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.552818775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641159057617</t>
+    <t xml:space="preserve">7.55281829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641063690186</t>
   </si>
   <si>
     <t xml:space="preserve">7.49783229827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60387849807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351560592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66671991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80418729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75705432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8866662979126</t>
+    <t xml:space="preserve">7.60387802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66672039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8041877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75705480575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88666725158691</t>
   </si>
   <si>
     <t xml:space="preserve">7.93379831314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91808795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310052871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488412857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74055862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951808929443</t>
+    <t xml:space="preserve">7.91808748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87488460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74056053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886354446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951713562012</t>
   </si>
   <si>
     <t xml:space="preserve">7.50804376602173</t>
@@ -1247,49 +1247,49 @@
     <t xml:space="preserve">7.53161001205444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23782348632812</t>
+    <t xml:space="preserve">7.23782396316528</t>
   </si>
   <si>
     <t xml:space="preserve">7.26610279083252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24410772323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076223373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59130954742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69656944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355098724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80025911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826547622681</t>
+    <t xml:space="preserve">7.24410724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066442489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69657039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80026006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826404571533</t>
   </si>
   <si>
     <t xml:space="preserve">7.83325099945068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94950866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52061367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83010911941528</t>
+    <t xml:space="preserve">7.94950914382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52061223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83010864257812</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">7.95343589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04377269744873</t>
+    <t xml:space="preserve">8.0437707901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.11054134368896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14589023590088</t>
+    <t xml:space="preserve">8.1458911895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.07126426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86702871322632</t>
+    <t xml:space="preserve">7.86702966690063</t>
   </si>
   <si>
     <t xml:space="preserve">7.83953523635864</t>
@@ -1328,46 +1328,46 @@
     <t xml:space="preserve">7.69499826431274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7107105255127</t>
+    <t xml:space="preserve">7.71070909500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.64158248901367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67300271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487674713135</t>
+    <t xml:space="preserve">7.67300462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487436294556</t>
   </si>
   <si>
     <t xml:space="preserve">7.65572357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85524559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59445285797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415287017822</t>
+    <t xml:space="preserve">7.85524654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59445142745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">7.59602308273315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5614595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7531270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83167934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554605484009</t>
+    <t xml:space="preserve">7.56146001815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75312805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83168125152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554557800293</t>
   </si>
   <si>
     <t xml:space="preserve">8.03897953033447</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">8.08750534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01633453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96942663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97428035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560094833374</t>
+    <t xml:space="preserve">8.01633548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96942853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97427940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98560190200806</t>
   </si>
   <si>
     <t xml:space="preserve">8.14816093444824</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">8.21690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9322247505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85943651199341</t>
+    <t xml:space="preserve">7.93222379684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85943698883057</t>
   </si>
   <si>
     <t xml:space="preserve">7.87884664535522</t>
@@ -1421,22 +1421,22 @@
     <t xml:space="preserve">7.4194769859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25125646591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626140594482</t>
+    <t xml:space="preserve">7.25125598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626188278198</t>
   </si>
   <si>
     <t xml:space="preserve">7.43079853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40491962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42594575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568237304688</t>
+    <t xml:space="preserve">7.40492010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42594623565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568141937256</t>
   </si>
   <si>
     <t xml:space="preserve">6.59293413162231</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">6.43441867828369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84849977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805171966553</t>
+    <t xml:space="preserve">6.84849882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805219650269</t>
   </si>
   <si>
     <t xml:space="preserve">7.10729932785034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92613983154297</t>
+    <t xml:space="preserve">6.92613935470581</t>
   </si>
   <si>
     <t xml:space="preserve">6.81776666641235</t>
@@ -1469,31 +1469,31 @@
     <t xml:space="preserve">7.1477370262146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26419734954834</t>
+    <t xml:space="preserve">7.26419639587402</t>
   </si>
   <si>
     <t xml:space="preserve">7.61681175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58607959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70415687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78179597854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70739221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282545089722</t>
+    <t xml:space="preserve">7.58607912063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70415735244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7817964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7073917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282497406006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62975168228149</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">7.65886688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69768667221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8222336769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032178878784</t>
+    <t xml:space="preserve">7.69768762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032274246216</t>
   </si>
   <si>
     <t xml:space="preserve">7.95163488388062</t>
@@ -1523,31 +1523,31 @@
     <t xml:space="preserve">8.03089237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95001745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294845581055</t>
+    <t xml:space="preserve">7.95001697540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294750213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.06809520721436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19264125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25329780578613</t>
+    <t xml:space="preserve">8.19264221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969287872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29778099060059</t>
+    <t xml:space="preserve">8.29777908325195</t>
   </si>
   <si>
     <t xml:space="preserve">8.31395530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27756118774414</t>
+    <t xml:space="preserve">8.27756023406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455505371094</t>
@@ -1559,22 +1559,22 @@
     <t xml:space="preserve">8.21286106109619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28564834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24925518035889</t>
+    <t xml:space="preserve">8.28564929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24925422668457</t>
   </si>
   <si>
     <t xml:space="preserve">8.12794208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24521064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13198566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06647682189941</t>
+    <t xml:space="preserve">8.24521255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13198661804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06647777557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.1764669418335</t>
@@ -1583,55 +1583,55 @@
     <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1400728225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08588790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12389945983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20881748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2249927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30991077423096</t>
+    <t xml:space="preserve">8.14007377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08588695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12389850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20881652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22499179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30990982055664</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33417415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31799793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60510540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77898597717285</t>
+    <t xml:space="preserve">8.18859767913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33417320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60510635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77898693084717</t>
   </si>
   <si>
     <t xml:space="preserve">8.77089977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89625453948975</t>
+    <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.95691108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03778743743896</t>
+    <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.04183101654053</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">9.32084941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22784423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41790103912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44620513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61604309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48260116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3127613067627</t>
+    <t xml:space="preserve">9.22784233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41790008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44620609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61604404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48259925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31276226043701</t>
   </si>
   <si>
     <t xml:space="preserve">9.39768123626709</t>
@@ -1676,37 +1676,37 @@
     <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19549369812012</t>
+    <t xml:space="preserve">9.1954927444458</t>
   </si>
   <si>
     <t xml:space="preserve">9.1146183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67789268493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65363025665283</t>
+    <t xml:space="preserve">8.67789077758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65362930297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.05192089080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89987373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531732559204</t>
+    <t xml:space="preserve">7.89987468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531637191772</t>
   </si>
   <si>
     <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4680027961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287532806396</t>
+    <t xml:space="preserve">7.83355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287485122681</t>
   </si>
   <si>
     <t xml:space="preserve">7.24155235290527</t>
@@ -1718,208 +1718,208 @@
     <t xml:space="preserve">7.05715656280518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59093189239502</t>
+    <t xml:space="preserve">7.32080841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595659255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47770643234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59093236923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.92251920700073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75106430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562070846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.987220287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0082483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9661922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78017902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78988361358643</t>
+    <t xml:space="preserve">7.75106477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562213897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98721981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00824737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9451642036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96619272232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88370037078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7898850440979</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7429780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84164381027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98074865341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9111967086792</t>
+    <t xml:space="preserve">7.74297714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84164571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98075103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91119718551636</t>
   </si>
   <si>
     <t xml:space="preserve">7.68474721908569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85134983062744</t>
+    <t xml:space="preserve">7.85134935379028</t>
   </si>
   <si>
     <t xml:space="preserve">7.74944686889648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32889652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39036178588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2496395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212102890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49388122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521408081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26581478118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35477685928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01833724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05230474472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09921169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07980155944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99245691299438</t>
+    <t xml:space="preserve">7.32889747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39036130905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24963998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212198257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49388265609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521551132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26581430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890640258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35477733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01833629608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05230379104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0992112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0798020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99245738983154</t>
   </si>
   <si>
     <t xml:space="preserve">7.23831701278687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27875375747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58446216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62328195571899</t>
+    <t xml:space="preserve">7.27875471115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62328100204468</t>
   </si>
   <si>
     <t xml:space="preserve">7.56828737258911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55534648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54078960418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92898845672607</t>
+    <t xml:space="preserve">7.55534696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54079055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92898988723755</t>
   </si>
   <si>
     <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046646118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781812667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67342472076416</t>
+    <t xml:space="preserve">7.88046455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781908035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67342519760132</t>
   </si>
   <si>
     <t xml:space="preserve">7.57152223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83193922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92575454711914</t>
+    <t xml:space="preserve">7.83193969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92575407028198</t>
   </si>
   <si>
     <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00339508056641</t>
+    <t xml:space="preserve">7.80767679214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00339317321777</t>
   </si>
   <si>
     <t xml:space="preserve">8.39887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23712348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45144176483154</t>
+    <t xml:space="preserve">8.2371244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45144081115723</t>
   </si>
   <si>
     <t xml:space="preserve">8.57679843902588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38674259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2694730758667</t>
+    <t xml:space="preserve">8.38674354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26947212219238</t>
   </si>
   <si>
     <t xml:space="preserve">8.18051147460938</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83559989929199</t>
+    <t xml:space="preserve">8.3503475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83559799194336</t>
   </si>
   <si>
     <t xml:space="preserve">8.92051792144775</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07418060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445529937744</t>
+    <t xml:space="preserve">9.07418155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445434570312</t>
   </si>
   <si>
     <t xml:space="preserve">9.17931842803955</t>
@@ -1961,25 +1961,25 @@
     <t xml:space="preserve">9.2318868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34915542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38150501251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36532974243164</t>
+    <t xml:space="preserve">9.34915637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38150596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32489204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36533069610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.5917797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40576839447021</t>
+    <t xml:space="preserve">9.4057674407959</t>
   </si>
   <si>
     <t xml:space="preserve">9.59582424163818</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">9.56751823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4664249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47451305389404</t>
+    <t xml:space="preserve">9.45833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46642398834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47451210021973</t>
   </si>
   <si>
     <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163745880127</t>
+    <t xml:space="preserve">10.0163736343384</t>
   </si>
   <si>
     <t xml:space="preserve">9.83036231994629</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">10.036060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84943866729736</t>
+    <t xml:space="preserve">9.84943962097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.79552745819092</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">9.73331928253174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4761962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50162029266357</t>
+    <t xml:space="preserve">9.47619724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50162124633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.44356155395508</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">8.27767562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17150974273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96912860870361</t>
+    <t xml:space="preserve">8.1715087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96912908554077</t>
   </si>
   <si>
     <t xml:space="preserve">8.12506103515625</t>
@@ -2063,58 +2063,58 @@
     <t xml:space="preserve">8.23620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11842632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2113208770752</t>
+    <t xml:space="preserve">8.11842727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21131992340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08690929412842</t>
+    <t xml:space="preserve">8.00728225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0869083404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.03880214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87955093383789</t>
+    <t xml:space="preserve">7.87955236434937</t>
   </si>
   <si>
     <t xml:space="preserve">7.67385339736938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69376039505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5909104347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77172660827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70868968963623</t>
+    <t xml:space="preserve">7.69375991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77172613143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70868873596191</t>
   </si>
   <si>
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70039558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73357248306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58925247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6257472038269</t>
+    <t xml:space="preserve">7.70039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73357200622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58925151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62574672698975</t>
   </si>
   <si>
     <t xml:space="preserve">7.50299119949341</t>
@@ -2123,34 +2123,34 @@
     <t xml:space="preserve">7.55109834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72859573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82978582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91936349868774</t>
+    <t xml:space="preserve">7.72859525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82978534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91936445236206</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12837886810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08359146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01557636260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96249437332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17814350128174</t>
+    <t xml:space="preserve">8.12837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08359050750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01557731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96249389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667297363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17814445495605</t>
   </si>
   <si>
     <t xml:space="preserve">8.2196159362793</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">8.87901020050049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86656856536865</t>
+    <t xml:space="preserve">8.86656761169434</t>
   </si>
   <si>
     <t xml:space="preserve">8.54724025726318</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">8.48088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29094696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32329368591309</t>
+    <t xml:space="preserve">8.2909460067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3232946395874</t>
   </si>
   <si>
     <t xml:space="preserve">8.05704784393311</t>
@@ -2204,130 +2204,130 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462116241455</t>
+    <t xml:space="preserve">7.86462259292603</t>
   </si>
   <si>
     <t xml:space="preserve">7.36530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45820236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5726637840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39184856414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22098731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38355493545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38853073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191261291504</t>
+    <t xml:space="preserve">7.45820283889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57266330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39184761047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38355445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38853120803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7319130897522</t>
   </si>
   <si>
     <t xml:space="preserve">7.41839027404785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25084590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42502546310425</t>
+    <t xml:space="preserve">7.25084543228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42502593994141</t>
   </si>
   <si>
     <t xml:space="preserve">7.06173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388282775879</t>
+    <t xml:space="preserve">7.17951583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388187408447</t>
   </si>
   <si>
     <t xml:space="preserve">7.25914001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.564368724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44493103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76509094238281</t>
+    <t xml:space="preserve">7.56436920166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44493246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76509189605713</t>
   </si>
   <si>
     <t xml:space="preserve">7.73854875564575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92765712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77836179733276</t>
+    <t xml:space="preserve">7.92765760421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77836132049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.82646799087524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258832931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989780426025</t>
+    <t xml:space="preserve">7.72030162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258737564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989685058594</t>
   </si>
   <si>
     <t xml:space="preserve">8.1897554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89116334915161</t>
+    <t xml:space="preserve">7.89116239547729</t>
   </si>
   <si>
     <t xml:space="preserve">7.81651496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16985034942627</t>
+    <t xml:space="preserve">8.16985130310059</t>
   </si>
   <si>
     <t xml:space="preserve">8.09851932525635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76343154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79660797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03216552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98903656005859</t>
+    <t xml:space="preserve">7.76343107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79660844802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03216457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98903560638428</t>
   </si>
   <si>
     <t xml:space="preserve">7.84969186782837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86130332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05539035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581220626831</t>
+    <t xml:space="preserve">7.86130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9774227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05538940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581172943115</t>
   </si>
   <si>
     <t xml:space="preserve">7.76840782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90443420410156</t>
+    <t xml:space="preserve">7.90443468093872</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">8.02718925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6539478302002</t>
+    <t xml:space="preserve">7.65394687652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.72361946105957</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">8.1267204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95917463302612</t>
+    <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
     <t xml:space="preserve">8.17482662200928</t>
@@ -2363,88 +2363,88 @@
     <t xml:space="preserve">8.5596809387207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46014881134033</t>
+    <t xml:space="preserve">8.46014976501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.44770812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42697143554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6260347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47673892974854</t>
+    <t xml:space="preserve">8.42697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62603569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47673797607422</t>
   </si>
   <si>
     <t xml:space="preserve">8.37720775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60944652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95780658721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99927711486816</t>
+    <t xml:space="preserve">8.60944557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95780563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99927806854248</t>
   </si>
   <si>
     <t xml:space="preserve">9.16516208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13198566436768</t>
+    <t xml:space="preserve">9.13198471069336</t>
   </si>
   <si>
     <t xml:space="preserve">9.23566436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48449230194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52596187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42643260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31445789337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38496017456055</t>
+    <t xml:space="preserve">9.48449325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52596282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50937557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42643070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3144588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38496112823486</t>
   </si>
   <si>
     <t xml:space="preserve">9.51766872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73746681213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7001428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57158184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33934116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23151683807373</t>
+    <t xml:space="preserve">9.73746585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">9.28957748413086</t>
@@ -2459,40 +2459,40 @@
     <t xml:space="preserve">9.19833946228027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31031322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078109741211</t>
+    <t xml:space="preserve">9.31031227111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
     <t xml:space="preserve">9.26884078979492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11539649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12369060516357</t>
+    <t xml:space="preserve">9.11539554595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
     <t xml:space="preserve">9.04074859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06148433685303</t>
+    <t xml:space="preserve">9.06148338317871</t>
   </si>
   <si>
     <t xml:space="preserve">9.01586532592773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05318927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93292331695557</t>
+    <t xml:space="preserve">9.05319023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93292236328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.12783813476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88315677642822</t>
+    <t xml:space="preserve">8.88315773010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.82509803771973</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">9.58817005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29372310638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1527214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2564001083374</t>
+    <t xml:space="preserve">9.29372215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25639915466309</t>
   </si>
   <si>
     <t xml:space="preserve">9.15686798095703</t>
@@ -2528,76 +2528,76 @@
     <t xml:space="preserve">9.08221912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0946626663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11124992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77533054351807</t>
+    <t xml:space="preserve">9.09466075897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11124897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77533149719238</t>
   </si>
   <si>
     <t xml:space="preserve">9.27298831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10710144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77118492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97024631500244</t>
+    <t xml:space="preserve">9.107102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77118301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97024536132812</t>
   </si>
   <si>
     <t xml:space="preserve">9.27713489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68770027160645</t>
+    <t xml:space="preserve">9.68770122528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.1444263458252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08636665344238</t>
+    <t xml:space="preserve">9.0863676071167</t>
   </si>
   <si>
     <t xml:space="preserve">9.05733680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99098205566406</t>
+    <t xml:space="preserve">8.99098300933838</t>
   </si>
   <si>
     <t xml:space="preserve">9.28128147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89559841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25279331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14994430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87457513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74186563491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35867118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327306747437</t>
+    <t xml:space="preserve">8.89559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25279235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14994335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87457466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74186611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042406082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35867071151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327259063721</t>
   </si>
   <si>
     <t xml:space="preserve">6.73328399658203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25055742263794</t>
+    <t xml:space="preserve">6.25055694580078</t>
   </si>
   <si>
     <t xml:space="preserve">6.53256273269653</t>
@@ -2615,67 +2615,67 @@
     <t xml:space="preserve">6.12946128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24060487747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2024507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19083881378174</t>
+    <t xml:space="preserve">6.24060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20245122909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1908392906189</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71503639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33047103881836</t>
+    <t xml:space="preserve">6.71503686904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33047151565552</t>
   </si>
   <si>
     <t xml:space="preserve">6.85769748687744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98542928695679</t>
+    <t xml:space="preserve">6.98542881011963</t>
   </si>
   <si>
     <t xml:space="preserve">6.87594509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096977233887</t>
+    <t xml:space="preserve">6.87096834182739</t>
   </si>
   <si>
     <t xml:space="preserve">7.09159660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42336654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59257030487061</t>
+    <t xml:space="preserve">7.4233660697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59256887435913</t>
   </si>
   <si>
     <t xml:space="preserve">7.83310317993164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83144378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92931652069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32715320587158</t>
+    <t xml:space="preserve">7.83144474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92931699752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32715368270874</t>
   </si>
   <si>
     <t xml:space="preserve">7.22264528274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21600961685181</t>
+    <t xml:space="preserve">7.21601009368896</t>
   </si>
   <si>
     <t xml:space="preserve">7.24255228042603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76977825164795</t>
+    <t xml:space="preserve">6.76977872848511</t>
   </si>
   <si>
     <t xml:space="preserve">7.26411724090576</t>
@@ -2684,28 +2684,28 @@
     <t xml:space="preserve">7.66224193572998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64067649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88286828994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07363605499268</t>
+    <t xml:space="preserve">7.64067697525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88286876678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07363796234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41038417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05207252502441</t>
+    <t xml:space="preserve">8.4103832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0520715713501</t>
   </si>
   <si>
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897769927979</t>
+    <t xml:space="preserve">8.70897674560547</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232448577881</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">8.22956848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48503112792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.294264793396</t>
+    <t xml:space="preserve">8.485032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29426383972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.20800399780273</t>
@@ -2726,25 +2726,25 @@
     <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47259140014648</t>
+    <t xml:space="preserve">8.47259044647217</t>
   </si>
   <si>
     <t xml:space="preserve">8.78777408599854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71312427520752</t>
+    <t xml:space="preserve">8.71312522888184</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91218662261963</t>
+    <t xml:space="preserve">8.91218757629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.0034236907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34763622283936</t>
+    <t xml:space="preserve">9.34763717651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.34348964691162</t>
@@ -2756,16 +2756,16 @@
     <t xml:space="preserve">9.60475826263428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2973299026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0443534851074</t>
+    <t xml:space="preserve">10.0402059555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2973289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94896984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0443544387817</t>
   </si>
   <si>
     <t xml:space="preserve">10.2848873138428</t>
@@ -2777,37 +2777,37 @@
     <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065089225769</t>
+    <t xml:space="preserve">10.0650901794434</t>
   </si>
   <si>
     <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95311737060547</t>
+    <t xml:space="preserve">9.95311641693115</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595361709595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3512420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7286319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6996011734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6747188568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3388004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4093017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4632139205933</t>
+    <t xml:space="preserve">10.3512411117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7286310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6996002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6747169494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387994766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4093027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4632148742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.4010076522827</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">10.6415414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8323087692261</t>
+    <t xml:space="preserve">10.8323097229004</t>
   </si>
   <si>
     <t xml:space="preserve">10.7659549713135</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">10.9318408966064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778395652771</t>
+    <t xml:space="preserve">10.7783966064453</t>
   </si>
   <si>
     <t xml:space="preserve">10.6332473754883</t>
@@ -2837,43 +2837,43 @@
     <t xml:space="preserve">10.6042175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812086105347</t>
+    <t xml:space="preserve">10.4300384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024141311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.181209564209</t>
   </si>
   <si>
     <t xml:space="preserve">10.53786277771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305063247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.230975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4175977706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.064549446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8654861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8240146636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.612512588501</t>
+    <t xml:space="preserve">10.3305072784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553895950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2309761047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4175968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0645484924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8654870986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8240156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
     <t xml:space="preserve">10.6000699996948</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">10.7493667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.687159538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6913080215454</t>
+    <t xml:space="preserve">10.6871604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6913070678711</t>
   </si>
   <si>
     <t xml:space="preserve">10.7949857711792</t>
@@ -2894,16 +2894,16 @@
     <t xml:space="preserve">10.6664237976074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5337162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6249523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733842849731</t>
+    <t xml:space="preserve">10.5337152481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6249532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751867294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733852386475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4341850280762</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">10.0319137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81626224517822</t>
+    <t xml:space="preserve">9.81626129150391</t>
   </si>
   <si>
     <t xml:space="preserve">9.83285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46790218353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44716739654541</t>
+    <t xml:space="preserve">9.46790313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44716835021973</t>
   </si>
   <si>
     <t xml:space="preserve">9.72087860107422</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">9.5591402053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71258449554443</t>
+    <t xml:space="preserve">9.71258354187012</t>
   </si>
   <si>
     <t xml:space="preserve">9.67940711975098</t>
@@ -2954,25 +2954,25 @@
     <t xml:space="preserve">9.82040977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0277662277222</t>
+    <t xml:space="preserve">10.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1604738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1729154586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102403640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0775318145752</t>
+    <t xml:space="preserve">9.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1604747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1729164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0775299072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.1521797180176</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">9.99044227600098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1065607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96141242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59646415710449</t>
+    <t xml:space="preserve">10.1065626144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96141147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59646320343018</t>
   </si>
   <si>
     <t xml:space="preserve">9.53425693511963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67111110687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74576091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970653533936</t>
+    <t xml:space="preserve">9.67111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74576187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970748901367</t>
   </si>
   <si>
     <t xml:space="preserve">10.2600049972534</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">10.3844194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3470945358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3346529006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94482231140137</t>
+    <t xml:space="preserve">10.347095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3346538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94482421875</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2682991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5088319778442</t>
+    <t xml:space="preserve">10.2683010101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5088329315186</t>
   </si>
   <si>
     <t xml:space="preserve">10.4134483337402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5212755203247</t>
+    <t xml:space="preserve">10.5212745666504</t>
   </si>
   <si>
     <t xml:space="preserve">10.8074264526367</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">10.8945169448853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9359884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8157205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9733104705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.898663520813</t>
+    <t xml:space="preserve">10.9359874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8157215118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9733114242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986625671387</t>
   </si>
   <si>
     <t xml:space="preserve">10.8364562988281</t>
@@ -3065,28 +3065,28 @@
     <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8447513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9774580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350498199463</t>
+    <t xml:space="preserve">10.8447504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9774589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.135048866272</t>
   </si>
   <si>
     <t xml:space="preserve">11.1018733978271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1143131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3548488616943</t>
+    <t xml:space="preserve">11.1143140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35484790802</t>
   </si>
   <si>
     <t xml:space="preserve">11.1474905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.15993309021</t>
+    <t xml:space="preserve">11.1599321365356</t>
   </si>
   <si>
     <t xml:space="preserve">11.3921718597412</t>
@@ -3098,40 +3098,40 @@
     <t xml:space="preserve">11.6119709014893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.520733833313</t>
+    <t xml:space="preserve">11.5207328796387</t>
   </si>
   <si>
     <t xml:space="preserve">11.4792623519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.350700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1889619827271</t>
+    <t xml:space="preserve">11.3507013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1889629364014</t>
   </si>
   <si>
     <t xml:space="preserve">11.1682271957397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1226091384888</t>
+    <t xml:space="preserve">11.1226081848145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0355186462402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6788644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9935054779053</t>
+    <t xml:space="preserve">10.9442825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6788654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2926416397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9935064315796</t>
   </si>
   <si>
     <t xml:space="preserve">12.1096258163452</t>
@@ -3140,16 +3140,16 @@
     <t xml:space="preserve">12.3999252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303615570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4455442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.263069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953088760376</t>
+    <t xml:space="preserve">12.1303625106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4455432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2630701065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953098297119</t>
   </si>
   <si>
     <t xml:space="preserve">12.594841003418</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">12.3169822692871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1842746734619</t>
+    <t xml:space="preserve">12.1842737197876</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.337718963623</t>
+    <t xml:space="preserve">12.3377180099487</t>
   </si>
   <si>
     <t xml:space="preserve">12.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0847434997559</t>
+    <t xml:space="preserve">12.0847425460815</t>
   </si>
   <si>
     <t xml:space="preserve">12.2879524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0640077590942</t>
+    <t xml:space="preserve">12.0640087127686</t>
   </si>
   <si>
     <t xml:space="preserve">12.0349779129028</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">11.9230051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9810647964478</t>
+    <t xml:space="preserve">11.9810638427734</t>
   </si>
   <si>
     <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.163537979126</t>
+    <t xml:space="preserve">12.1635389328003</t>
   </si>
   <si>
     <t xml:space="preserve">12.2174510955811</t>
@@ -3212,22 +3212,22 @@
     <t xml:space="preserve">12.1759805679321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.972770690918</t>
+    <t xml:space="preserve">11.9727716445923</t>
   </si>
   <si>
     <t xml:space="preserve">11.97691822052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9437417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1179208755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820043563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244106292725</t>
+    <t xml:space="preserve">11.9437408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.117919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244115829468</t>
   </si>
   <si>
     <t xml:space="preserve">11.5580577850342</t>
@@ -3242,112 +3242,112 @@
     <t xml:space="preserve">11.5746459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834089279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5912342071533</t>
+    <t xml:space="preserve">11.4834098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5912351608276</t>
   </si>
   <si>
     <t xml:space="preserve">11.5995283126831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5870885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7405300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9603300094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7985916137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981227874756</t>
+    <t xml:space="preserve">11.5870866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6824703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9603290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7985906600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981218338013</t>
   </si>
   <si>
     <t xml:space="preserve">11.9520349502563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.545615196228</t>
+    <t xml:space="preserve">11.5456161499023</t>
   </si>
   <si>
     <t xml:space="preserve">11.5331745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4543790817261</t>
+    <t xml:space="preserve">11.4543800354004</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6783227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8193273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.877387046814</t>
+    <t xml:space="preserve">11.6783246994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8193264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9064168930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">12.0142421722412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6949138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8732385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6617364883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322368621826</t>
+    <t xml:space="preserve">11.6949129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8732395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.661735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322378158569</t>
   </si>
   <si>
     <t xml:space="preserve">11.7446784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6534423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.711501121521</t>
+    <t xml:space="preserve">11.6534414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7115020751953</t>
   </si>
   <si>
     <t xml:space="preserve">11.7654151916504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.164080619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2055511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050832748413</t>
+    <t xml:space="preserve">11.5787925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1640796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2055521011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.305082321167</t>
   </si>
   <si>
     <t xml:space="preserve">11.4129085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4336442947388</t>
+    <t xml:space="preserve">11.4336433410645</t>
   </si>
   <si>
     <t xml:space="preserve">11.3299646377563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631429672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3382596969604</t>
+    <t xml:space="preserve">11.3631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3382587432861</t>
   </si>
   <si>
     <t xml:space="preserve">11.3880243301392</t>
@@ -3359,16 +3359,16 @@
     <t xml:space="preserve">11.4917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5124397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6451473236084</t>
+    <t xml:space="preserve">11.5124387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6451482772827</t>
   </si>
   <si>
     <t xml:space="preserve">11.5622034072876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248804092407</t>
+    <t xml:space="preserve">11.5248794555664</t>
   </si>
   <si>
     <t xml:space="preserve">11.5953817367554</t>
@@ -3380,34 +3380,34 @@
     <t xml:space="preserve">11.66588306427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9312992095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8607988357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6410007476807</t>
+    <t xml:space="preserve">11.931300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8607978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6409997940063</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068857192993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0266828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1013317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2133054733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2423343658447</t>
+    <t xml:space="preserve">12.026683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1013326644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2133045196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2423334121704</t>
   </si>
   <si>
     <t xml:space="preserve">12.1967153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3086891174316</t>
+    <t xml:space="preserve">12.3086881637573</t>
   </si>
   <si>
     <t xml:space="preserve">12.1510972976685</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">11.8690929412842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778549194336</t>
+    <t xml:space="preserve">11.7778558731079</t>
   </si>
   <si>
     <t xml:space="preserve">12.1220664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2215986251831</t>
+    <t xml:space="preserve">12.2215976715088</t>
   </si>
   <si>
     <t xml:space="preserve">12.333571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7151069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5367803573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3708953857422</t>
+    <t xml:space="preserve">12.7151079177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5367813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3708944320679</t>
   </si>
   <si>
     <t xml:space="preserve">12.7773141860962</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">12.8975820541382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2293519973755</t>
+    <t xml:space="preserve">13.2293510437012</t>
   </si>
   <si>
     <t xml:space="preserve">13.3827962875366</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">13.5942993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698848724365</t>
+    <t xml:space="preserve">13.4698858261108</t>
   </si>
   <si>
     <t xml:space="preserve">13.4201202392578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3496170043945</t>
+    <t xml:space="preserve">13.3496179580688</t>
   </si>
   <si>
     <t xml:space="preserve">13.2252044677734</t>
@@ -3476,34 +3476,34 @@
     <t xml:space="preserve">13.4781799316406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2169103622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.051025390625</t>
+    <t xml:space="preserve">13.216911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0510244369507</t>
   </si>
   <si>
     <t xml:space="preserve">13.1588506698608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1837339401245</t>
+    <t xml:space="preserve">13.1837348937988</t>
   </si>
   <si>
     <t xml:space="preserve">13.2583818435669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1629962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625293731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9514951705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8644046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8685512542725</t>
+    <t xml:space="preserve">13.1629972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9514942169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8644037246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8685503005981</t>
   </si>
   <si>
     <t xml:space="preserve">12.7607259750366</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">12.7939033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9349060058594</t>
+    <t xml:space="preserve">12.9349069595337</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312273025513</t>
@@ -3521,64 +3521,64 @@
     <t xml:space="preserve">12.7482843399048</t>
   </si>
   <si>
-    <t xml:space="preserve">12.574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6611948013306</t>
+    <t xml:space="preserve">12.5741052627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6611957550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.9763774871826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.237645149231</t>
+    <t xml:space="preserve">13.2376470565796</t>
   </si>
   <si>
     <t xml:space="preserve">13.1215267181396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0095539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2417936325073</t>
+    <t xml:space="preserve">13.0095548629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.241792678833</t>
   </si>
   <si>
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432001113892</t>
+    <t xml:space="preserve">12.9431982040405</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9971132278442</t>
+    <t xml:space="preserve">12.9971122741699</t>
   </si>
   <si>
     <t xml:space="preserve">12.7690200805664</t>
   </si>
   <si>
-    <t xml:space="preserve">12.644606590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9929656982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2044696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1173782348633</t>
+    <t xml:space="preserve">12.6446056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9929647445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2044687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1173801422119</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
@@ -3587,46 +3587,46 @@
     <t xml:space="preserve">13.7850685119629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6523590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8016548156738</t>
+    <t xml:space="preserve">13.6523580551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8016538619995</t>
   </si>
   <si>
     <t xml:space="preserve">13.7726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7975091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9219226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9799823760986</t>
+    <t xml:space="preserve">13.7975101470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9219217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9799833297729</t>
   </si>
   <si>
     <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7270069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.69797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0048656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.764331817627</t>
+    <t xml:space="preserve">13.7270059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6979780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0048666000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7643308639526</t>
   </si>
   <si>
     <t xml:space="preserve">14.0878095626831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0173082351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2246627807617</t>
+    <t xml:space="preserve">14.0173072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.224663734436</t>
   </si>
   <si>
     <t xml:space="preserve">14.3324899673462</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">14.2951650619507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3532257080078</t>
+    <t xml:space="preserve">14.3532238006592</t>
   </si>
   <si>
     <t xml:space="preserve">14.2619867324829</t>
@@ -3650,52 +3650,52 @@
     <t xml:space="preserve">14.3076066970825</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2163686752319</t>
+    <t xml:space="preserve">14.2163696289062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1251316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3006258010864</t>
+    <t xml:space="preserve">14.3006267547607</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255081176758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8597526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6542949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3161478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605018615723</t>
+    <t xml:space="preserve">13.8597507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6542940139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3161468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605028152466</t>
   </si>
   <si>
     <t xml:space="preserve">13.4359970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1363725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1834564208984</t>
+    <t xml:space="preserve">13.1363735198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1834573745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.5515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6457328796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4488382339478</t>
+    <t xml:space="preserve">13.9068365097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.645733833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4488372802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.4188756942749</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9951219558716</t>
+    <t xml:space="preserve">13.4445571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258836746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9951229095459</t>
   </si>
   <si>
     <t xml:space="preserve">12.7639837265015</t>
@@ -3722,37 +3722,37 @@
     <t xml:space="preserve">12.9523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2433824539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2519426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2134199142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4531183242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.487361907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6842555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3589506149292</t>
+    <t xml:space="preserve">12.9095144271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2433815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2519416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2134189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4531192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4873609542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6842575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3589496612549</t>
   </si>
   <si>
     <t xml:space="preserve">13.0122423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741441726685</t>
+    <t xml:space="preserve">13.7741451263428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8511905670166</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">13.6114912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2861852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0293645858765</t>
+    <t xml:space="preserve">13.2861862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0293655395508</t>
   </si>
   <si>
     <t xml:space="preserve">13.1920166015625</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">12.3616313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5499658584595</t>
+    <t xml:space="preserve">12.5499649047852</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857616424561</t>
+    <t xml:space="preserve">12.4857606887817</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740961074829</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">12.85387134552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9009532928467</t>
+    <t xml:space="preserve">12.900954246521</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682638168335</t>
+    <t xml:space="preserve">12.7682628631592</t>
   </si>
   <si>
     <t xml:space="preserve">12.8495903015137</t>
@@ -3827,37 +3827,37 @@
     <t xml:space="preserve">13.5430059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4103155136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2776250839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4301176071167</t>
+    <t xml:space="preserve">13.4103145599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.277624130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4301166534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0234851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0363254547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.835147857666</t>
+    <t xml:space="preserve">12.7768239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0234832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0363245010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8351488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.9576787948608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8720722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5339250564575</t>
+    <t xml:space="preserve">10.8720712661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5339260101318</t>
   </si>
   <si>
     <t xml:space="preserve">11.783784866333</t>
@@ -3866,28 +3866,28 @@
     <t xml:space="preserve">11.3172273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5954504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8265886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.895073890686</t>
+    <t xml:space="preserve">11.5954494476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8265867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950729370117</t>
   </si>
   <si>
     <t xml:space="preserve">12.5157232284546</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9892416000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106430053711</t>
+    <t xml:space="preserve">11.9892406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0106420516968</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849605560303</t>
+    <t xml:space="preserve">11.9849615097046</t>
   </si>
   <si>
     <t xml:space="preserve">11.8479900360107</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">12.3145475387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1989784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2332201004028</t>
+    <t xml:space="preserve">12.1989774703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
     <t xml:space="preserve">12.3102674484253</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318826675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203788757324</t>
+    <t xml:space="preserve">12.1262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188276290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.9464378356934</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834093093872</t>
+    <t xml:space="preserve">12.0834083557129</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705680847168</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">11.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771533966064</t>
+    <t xml:space="preserve">11.3771524429321</t>
   </si>
   <si>
     <t xml:space="preserve">11.0775279998779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090368270874</t>
+    <t xml:space="preserve">11.0903692245483</t>
   </si>
   <si>
     <t xml:space="preserve">10.5724477767944</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">10.080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4868402481079</t>
+    <t xml:space="preserve">10.4868412017822</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938501358032</t>
+    <t xml:space="preserve">10.5938491821289</t>
   </si>
   <si>
     <t xml:space="preserve">10.6109714508057</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">10.8292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8035860061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7693424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.166898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1403951644897</t>
+    <t xml:space="preserve">10.8035869598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7693433761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1668996810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1403942108154</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.5423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969738006592</t>
+    <t xml:space="preserve">11.6969728469849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6351318359375</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">11.560037612915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1580648422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4893617630005</t>
+    <t xml:space="preserve">11.1580638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4893608093262</t>
   </si>
   <si>
     <t xml:space="preserve">11.37451171875</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">9.62968349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14378356933594</t>
+    <t xml:space="preserve">9.14378261566162</t>
   </si>
   <si>
     <t xml:space="preserve">9.13052940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74453163146973</t>
+    <t xml:space="preserve">9.74453353881836</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">9.89030265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92122459411621</t>
+    <t xml:space="preserve">9.92122364044189</t>
   </si>
   <si>
     <t xml:space="preserve">10.1818437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4645509719849</t>
+    <t xml:space="preserve">10.4645500183105</t>
   </si>
   <si>
     <t xml:space="preserve">10.6191558837891</t>
@@ -4079,10 +4079,10 @@
     <t xml:space="preserve">10.4778022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3894577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890808105469</t>
+    <t xml:space="preserve">10.3894567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890817642212</t>
   </si>
   <si>
     <t xml:space="preserve">10.1244201660156</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">9.9786491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2171812057495</t>
+    <t xml:space="preserve">10.2171821594238</t>
   </si>
   <si>
     <t xml:space="preserve">10.7384214401245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5970697402954</t>
+    <t xml:space="preserve">10.5970687866211</t>
   </si>
   <si>
     <t xml:space="preserve">10.3585357666016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83287906646729</t>
+    <t xml:space="preserve">9.83287811279297</t>
   </si>
   <si>
     <t xml:space="preserve">9.85054779052734</t>
@@ -4115,37 +4115,37 @@
     <t xml:space="preserve">10.0449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5661487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0934982299805</t>
+    <t xml:space="preserve">10.5661478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0934991836548</t>
   </si>
   <si>
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0007352828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6809988021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6500759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9990425109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8841915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8267688751221</t>
+    <t xml:space="preserve">10.0758295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0007343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6809968948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6500768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.999041557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8841924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8267679214478</t>
   </si>
   <si>
     <t xml:space="preserve">10.707501411438</t>
@@ -4157,22 +4157,22 @@
     <t xml:space="preserve">10.9062795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.959285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9902057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7781782150269</t>
+    <t xml:space="preserve">10.9592866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9902067184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7781772613525</t>
   </si>
   <si>
     <t xml:space="preserve">10.5308094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6544933319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1465063095093</t>
+    <t xml:space="preserve">10.6544942855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.146505355835</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">10.0051517486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93447685241699</t>
+    <t xml:space="preserve">9.93447589874268</t>
   </si>
   <si>
     <t xml:space="preserve">9.4529914855957</t>
@@ -4193,61 +4193,61 @@
     <t xml:space="preserve">9.54133796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55458831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42648792266846</t>
+    <t xml:space="preserve">9.55458927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42648887634277</t>
   </si>
   <si>
     <t xml:space="preserve">9.84613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55017185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58109474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59876155853271</t>
+    <t xml:space="preserve">9.55017280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58109283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59876251220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797740936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9195308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.228741645813</t>
+    <t xml:space="preserve">10.8797750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.919529914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2287406921387</t>
   </si>
   <si>
     <t xml:space="preserve">11.3082523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1183090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9946241378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5528945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215026855469</t>
+    <t xml:space="preserve">11.1183080673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9946250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5528964996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215036392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.9372005462646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259210586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0211296081543</t>
+    <t xml:space="preserve">11.3259220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.02112865448</t>
   </si>
   <si>
     <t xml:space="preserve">10.8488540649414</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8471603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5379514694214</t>
+    <t xml:space="preserve">11.8471612930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5379505157471</t>
   </si>
   <si>
     <t xml:space="preserve">10.9460344314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9548692703247</t>
+    <t xml:space="preserve">10.9548683166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.5352277755737</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">11.2331581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2110710144043</t>
+    <t xml:space="preserve">11.2110719680786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9620094299316</t>
+    <t xml:space="preserve">11.962010383606</t>
   </si>
   <si>
     <t xml:space="preserve">12.0591897964478</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">12.0503568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1961269378662</t>
+    <t xml:space="preserve">12.1961278915405</t>
   </si>
   <si>
     <t xml:space="preserve">12.3949041366577</t>
@@ -4319,64 +4319,64 @@
     <t xml:space="preserve">12.6201858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6246023178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6908617019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527046203613</t>
+    <t xml:space="preserve">12.3772344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6246032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6908626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527055740356</t>
   </si>
   <si>
     <t xml:space="preserve">12.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.920560836792</t>
+    <t xml:space="preserve">12.9205617904663</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0354108810425</t>
+    <t xml:space="preserve">13.0354118347168</t>
   </si>
   <si>
     <t xml:space="preserve">13.2518577575684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1811809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2827787399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3843755722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4418020248413</t>
+    <t xml:space="preserve">13.1811819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2827777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3843765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.441801071167</t>
   </si>
   <si>
     <t xml:space="preserve">13.5743198394775</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4285497665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3578729629517</t>
+    <t xml:space="preserve">13.4285488128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3578720092773</t>
   </si>
   <si>
     <t xml:space="preserve">13.6405792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6494140625</t>
+    <t xml:space="preserve">13.6494131088257</t>
   </si>
   <si>
     <t xml:space="preserve">13.9144506454468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8835306167603</t>
+    <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522336959839</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">13.6759166717529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7730979919434</t>
+    <t xml:space="preserve">13.773097038269</t>
   </si>
   <si>
     <t xml:space="preserve">13.923285484314</t>
@@ -4403,16 +4403,16 @@
     <t xml:space="preserve">13.1414251327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3534545898438</t>
+    <t xml:space="preserve">13.3534555435181</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5345640182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5831537246704</t>
+    <t xml:space="preserve">13.5345630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5831546783447</t>
   </si>
   <si>
     <t xml:space="preserve">13.834939956665</t>
@@ -4421,10 +4421,10 @@
     <t xml:space="preserve">13.7112560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8658609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1883230209351</t>
+    <t xml:space="preserve">13.8658599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1883220672607</t>
   </si>
   <si>
     <t xml:space="preserve">14.5947132110596</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">14.5726270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.696310043335</t>
+    <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
     <t xml:space="preserve">14.8685846328735</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">14.7095613479614</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7934913635254</t>
+    <t xml:space="preserve">14.7934923171997</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">14.3429279327393</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5196189880371</t>
+    <t xml:space="preserve">14.5196180343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.3385095596313</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">14.5107841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4312725067139</t>
+    <t xml:space="preserve">14.4312734603882</t>
   </si>
   <si>
     <t xml:space="preserve">14.5328712463379</t>
@@ -4496,37 +4496,37 @@
     <t xml:space="preserve">14.9392614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8553323745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0099382400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6609706878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6918926239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.568208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9701814651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7714042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6433038711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453716278076</t>
+    <t xml:space="preserve">14.8553342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.009937286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6609716415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6918916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5682096481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9701824188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7714023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6433029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453706741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.1397314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9630422592163</t>
+    <t xml:space="preserve">13.963041305542</t>
   </si>
   <si>
     <t xml:space="preserve">14.1927404403687</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">14.444525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2236604690552</t>
+    <t xml:space="preserve">14.2236614227295</t>
   </si>
   <si>
     <t xml:space="preserve">14.3473443984985</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402992248535</t>
+    <t xml:space="preserve">12.2402982711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.4523296356201</t>
@@ -4568,25 +4568,25 @@
     <t xml:space="preserve">11.502613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7455635070801</t>
+    <t xml:space="preserve">11.7455625534058</t>
   </si>
   <si>
     <t xml:space="preserve">11.2684965133667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.315393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4169902801514</t>
+    <t xml:space="preserve">11.6837215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169912338257</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0238523483276</t>
+    <t xml:space="preserve">12.023853302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4595,16 +4595,16 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5009183883667</t>
+    <t xml:space="preserve">12.500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.293306350708</t>
+    <t xml:space="preserve">12.4920845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2933073043823</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579689025879</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">12.7438697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5892658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5362577438354</t>
+    <t xml:space="preserve">12.3684015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5892648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5362567901611</t>
   </si>
   <si>
     <t xml:space="preserve">12.3065586090088</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">11.7588148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1121988296509</t>
+    <t xml:space="preserve">12.1121978759766</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632322311401</t>
@@ -4664,19 +4664,19 @@
     <t xml:space="preserve">11.9399242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8824987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2022371292114</t>
+    <t xml:space="preserve">11.8824996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2022380828857</t>
   </si>
   <si>
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343809127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2199068069458</t>
+    <t xml:space="preserve">11.0343799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2199058532715</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653009414673</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">11.2950000762939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0873870849609</t>
+    <t xml:space="preserve">11.0873880386353</t>
   </si>
   <si>
     <t xml:space="preserve">11.1448125839233</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.30748462677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638675689697</t>
+    <t xml:space="preserve">11.0638666152954</t>
   </si>
   <si>
     <t xml:space="preserve">11.2753086090088</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">11.3856248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.436185836792</t>
+    <t xml:space="preserve">11.4361867904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.6522245407104</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">11.5832767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913454055786</t>
+    <t xml:space="preserve">11.4913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">11.4959421157837</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">11.4499769210815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4591703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7533483505249</t>
+    <t xml:space="preserve">11.4591693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7533473968506</t>
   </si>
   <si>
     <t xml:space="preserve">11.6935930252075</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">11.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0041122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9949197769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.096043586731</t>
+    <t xml:space="preserve">11.0041131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9949188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0960426330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.1833772659302</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">11.2890977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0868501663208</t>
+    <t xml:space="preserve">11.0868511199951</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4683637619019</t>
+    <t xml:space="preserve">11.4683628082275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8131036758423</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">12.1486501693726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3279151916504</t>
+    <t xml:space="preserve">12.3187227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3279161453247</t>
   </si>
   <si>
     <t xml:space="preserve">12.5117769241333</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.3784770965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5301628112793</t>
+    <t xml:space="preserve">12.5301637649536</t>
   </si>
   <si>
     <t xml:space="preserve">12.6358833312988</t>
@@ -4832,19 +4832,19 @@
     <t xml:space="preserve">12.9760274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645864486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4428291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255670547485</t>
+    <t xml:space="preserve">12.7645874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4428281784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255661010742</t>
   </si>
   <si>
     <t xml:space="preserve">12.4750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2385358810425</t>
+    <t xml:space="preserve">11.2385368347168</t>
   </si>
   <si>
     <t xml:space="preserve">12.0383338928223</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">11.964789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9555969238281</t>
+    <t xml:space="preserve">11.9555959701538</t>
   </si>
   <si>
     <t xml:space="preserve">11.5005388259888</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">11.6016626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.551100730896</t>
+    <t xml:space="preserve">11.5510997772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143280029297</t>
@@ -4877,19 +4877,19 @@
     <t xml:space="preserve">11.5786800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7073822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625417709351</t>
+    <t xml:space="preserve">11.7073831558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625408172607</t>
   </si>
   <si>
     <t xml:space="preserve">11.7441549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6384344100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
+    <t xml:space="preserve">11.6384353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465040206909</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855243682861</t>
@@ -4898,19 +4898,19 @@
     <t xml:space="preserve">11.7487516403198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6154527664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.94895362854</t>
+    <t xml:space="preserve">11.6154518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9489545822144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7558994293213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8708124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570241928101</t>
+    <t xml:space="preserve">10.870813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570232391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.8478298187256</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">10.889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7283201217651</t>
+    <t xml:space="preserve">10.7283210754395</t>
   </si>
   <si>
     <t xml:space="preserve">10.8294439315796</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">10.6915483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6547756195068</t>
+    <t xml:space="preserve">10.6547765731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7329168319702</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">10.6271963119507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858278274536</t>
+    <t xml:space="preserve">10.5858287811279</t>
   </si>
   <si>
     <t xml:space="preserve">10.287052154541</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">10.1445598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1215782165527</t>
+    <t xml:space="preserve">10.1215772628784</t>
   </si>
   <si>
     <t xml:space="preserve">9.91932964324951</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">9.99747085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79522323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399621963501</t>
+    <t xml:space="preserve">9.79522228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399631500244</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721391677856</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">9.90094375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96989250183105</t>
+    <t xml:space="preserve">9.96989154815674</t>
   </si>
   <si>
     <t xml:space="preserve">10.1951217651367</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">10.043436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0848054885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.03883934021</t>
+    <t xml:space="preserve">10.0848045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0388402938843</t>
   </si>
   <si>
     <t xml:space="preserve">10.057225227356</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">10.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629467010498</t>
+    <t xml:space="preserve">10.1629457473755</t>
   </si>
   <si>
     <t xml:space="preserve">10.2181043624878</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">11.0454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3948192596436</t>
+    <t xml:space="preserve">11.3948183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.5097322463989</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">11.0592708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9995155334473</t>
+    <t xml:space="preserve">10.9995164871216</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9903230667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477293014526</t>
+    <t xml:space="preserve">10.9903221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477283477783</t>
   </si>
   <si>
     <t xml:space="preserve">11.3672389984131</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">11.5970659255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.776330947876</t>
+    <t xml:space="preserve">11.7763319015503</t>
   </si>
   <si>
     <t xml:space="preserve">11.8866481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3646869659424</t>
+    <t xml:space="preserve">12.3646879196167</t>
   </si>
   <si>
     <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4290390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4014596939087</t>
+    <t xml:space="preserve">12.4290399551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.401460647583</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3692846298218</t>
+    <t xml:space="preserve">12.3692836761475</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554944992065</t>
@@ -5099,7 +5099,7 @@
     <t xml:space="preserve">12.5485486984253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.249773979187</t>
+    <t xml:space="preserve">12.2497749328613</t>
   </si>
   <si>
     <t xml:space="preserve">12.5393571853638</t>
@@ -5111,25 +5111,25 @@
     <t xml:space="preserve">12.6404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4566192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7507963180542</t>
+    <t xml:space="preserve">12.456618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7507972717285</t>
   </si>
   <si>
     <t xml:space="preserve">12.6680593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8473253250122</t>
+    <t xml:space="preserve">12.8473243713379</t>
   </si>
   <si>
     <t xml:space="preserve">12.870306968689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9024820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7783765792847</t>
+    <t xml:space="preserve">12.9024829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7783756256104</t>
   </si>
   <si>
     <t xml:space="preserve">12.8105525970459</t>
@@ -5138,16 +5138,16 @@
     <t xml:space="preserve">12.7094278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6174974441528</t>
+    <t xml:space="preserve">12.6174983978271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5577421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8381309509277</t>
+    <t xml:space="preserve">12.6588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8381319046021</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819499969482</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">11.8544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8452787399292</t>
+    <t xml:space="preserve">11.8452796936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705099105835</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">12.1348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0888957977295</t>
+    <t xml:space="preserve">12.0888948440552</t>
   </si>
   <si>
     <t xml:space="preserve">11.9326124191284</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">11.8085069656372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8958406448364</t>
+    <t xml:space="preserve">11.8958396911621</t>
   </si>
   <si>
     <t xml:space="preserve">12.0107536315918</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">12.194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.153247833252</t>
+    <t xml:space="preserve">12.1532468795776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1854228973389</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">12.0934915542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.157844543457</t>
+    <t xml:space="preserve">12.1808271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1578435897827</t>
   </si>
   <si>
     <t xml:space="preserve">12.2957391738892</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">12.3922672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.626690864563</t>
+    <t xml:space="preserve">12.6266899108887</t>
   </si>
   <si>
     <t xml:space="preserve">12.6220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8335342407227</t>
+    <t xml:space="preserve">12.833535194397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9162721633911</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">12.4796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2242403030396</t>
+    <t xml:space="preserve">13.2242412567139</t>
   </si>
   <si>
     <t xml:space="preserve">13.136905670166</t>
@@ -5270,7 +5270,7 @@
     <t xml:space="preserve">13.2012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2702054977417</t>
+    <t xml:space="preserve">13.270206451416</t>
   </si>
   <si>
     <t xml:space="preserve">13.1736783981323</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">12.6726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.681848526001</t>
+    <t xml:space="preserve">12.6818494796753</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9990110397339</t>
+    <t xml:space="preserve">12.9990100860596</t>
   </si>
   <si>
     <t xml:space="preserve">13.0265893936157</t>
@@ -5309,16 +5309,16 @@
     <t xml:space="preserve">12.8611135482788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0541677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058765411377</t>
+    <t xml:space="preserve">13.0541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587644577026</t>
   </si>
   <si>
     <t xml:space="preserve">13.2748022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1461000442505</t>
+    <t xml:space="preserve">13.1460990905762</t>
   </si>
   <si>
     <t xml:space="preserve">13.233434677124</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.780421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9275102615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9045286178589</t>
+    <t xml:space="preserve">13.7804222106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.92751121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9045276641846</t>
   </si>
   <si>
     <t xml:space="preserve">14.0102481842041</t>
@@ -6282,6 +6282,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.0149993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0550003051758</t>
   </si>
 </sst>
 </file>
@@ -71464,7 +71467,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495138889</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1236334</v>
@@ -71485,6 +71488,32 @@
         <v>2089</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6496064815</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>1116397</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>19.1499996185303</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>18.9699993133545</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>18.9950008392334</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>19.0550003051758</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="2091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="2092">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35306262969971</t>
+    <t xml:space="preserve">5.35306310653687</t>
   </si>
   <si>
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13951873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2625789642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13228130340576</t>
+    <t xml:space="preserve">5.32048845291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951969146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26257848739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1322808265686</t>
   </si>
   <si>
     <t xml:space="preserve">5.26619815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31325006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959594726562</t>
+    <t xml:space="preserve">5.3132495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1938099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0454158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959499359131</t>
   </si>
   <si>
     <t xml:space="preserve">5.07437086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65814208984375</t>
+    <t xml:space="preserve">4.65814256668091</t>
   </si>
   <si>
     <t xml:space="preserve">4.82101392745972</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21190643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04903507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14675855636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12504148483276</t>
+    <t xml:space="preserve">5.21190690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0490345954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14675807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12504196166992</t>
   </si>
   <si>
     <t xml:space="preserve">4.88978242874146</t>
@@ -113,52 +113,52 @@
     <t xml:space="preserve">4.74138832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56765747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3432559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45545768737793</t>
+    <t xml:space="preserve">4.56765651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34325551986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45545673370361</t>
   </si>
   <si>
     <t xml:space="preserve">4.48441171646118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58213520050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78482055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73414897918701</t>
+    <t xml:space="preserve">4.58213567733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78482103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73414850234985</t>
   </si>
   <si>
     <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672315597534</t>
+    <t xml:space="preserve">4.7667236328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.71243333816528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83187294006348</t>
+    <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88616228103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00922155380249</t>
+    <t xml:space="preserve">4.88616371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00922203063965</t>
   </si>
   <si>
     <t xml:space="preserve">5.09246730804443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10332584381104</t>
+    <t xml:space="preserve">5.10332536697388</t>
   </si>
   <si>
     <t xml:space="preserve">5.16847467422485</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">4.84273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78120136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713151931763</t>
+    <t xml:space="preserve">4.78120040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713199615479</t>
   </si>
   <si>
     <t xml:space="preserve">5.08884859085083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00560235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99112510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1901912689209</t>
+    <t xml:space="preserve">5.00560283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99112462997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19019079208374</t>
   </si>
   <si>
     <t xml:space="preserve">5.23362350463867</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12866115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02007961273193</t>
+    <t xml:space="preserve">5.12866163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02008008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.98026704788208</t>
@@ -206,46 +206,46 @@
     <t xml:space="preserve">4.94769239425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97302770614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11418437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406362533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28287410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27161026000977</t>
+    <t xml:space="preserve">4.9730281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0236988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11418390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.121422290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28287506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27161121368408</t>
   </si>
   <si>
     <t xml:space="preserve">5.23030948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3316855430603</t>
+    <t xml:space="preserve">5.16647911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33168649673462</t>
   </si>
   <si>
     <t xml:space="preserve">5.30164861679077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.391761302948</t>
+    <t xml:space="preserve">5.39176082611084</t>
   </si>
   <si>
     <t xml:space="preserve">5.26410150527954</t>
@@ -263,106 +263,106 @@
     <t xml:space="preserve">4.96747922897339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88863086700439</t>
+    <t xml:space="preserve">4.88863039016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.78725385665894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79100847244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76472520828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70089483261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96372509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90364933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90740394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7759895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73844289779663</t>
+    <t xml:space="preserve">4.79100799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76472473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70089530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9637246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90364980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90740442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77599000930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91866779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98625326156616</t>
+    <t xml:space="preserve">4.91866874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.986252784729</t>
   </si>
   <si>
     <t xml:space="preserve">4.97874402999878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01629018783569</t>
+    <t xml:space="preserve">5.01629066467285</t>
   </si>
   <si>
     <t xml:space="preserve">4.92617797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95246028900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97123336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483884811401</t>
+    <t xml:space="preserve">4.95246076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9712347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8548378944397</t>
   </si>
   <si>
     <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8022723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62204694747925</t>
+    <t xml:space="preserve">4.80227279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62204647064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.56197118759155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44182062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44932985305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4568395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56948041915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80602693557739</t>
+    <t xml:space="preserve">4.44182014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4493293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45683908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56947994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7534613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093271255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80602741241455</t>
   </si>
   <si>
     <t xml:space="preserve">4.97498893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49063158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13017988204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39676380157471</t>
+    <t xml:space="preserve">4.49063205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39676427841187</t>
   </si>
   <si>
     <t xml:space="preserve">4.33668851852417</t>
@@ -377,55 +377,55 @@
     <t xml:space="preserve">4.10014200210571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87485885620117</t>
+    <t xml:space="preserve">3.87485909461975</t>
   </si>
   <si>
     <t xml:space="preserve">3.94244432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26534938812256</t>
+    <t xml:space="preserve">4.2653489112854</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19025468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20151901245117</t>
+    <t xml:space="preserve">4.19025373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20151853561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.23531150817871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31040525436401</t>
+    <t xml:space="preserve">4.31040573120117</t>
   </si>
   <si>
     <t xml:space="preserve">4.25032997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2465763092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27661275863647</t>
+    <t xml:space="preserve">4.24657583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27661371231079</t>
   </si>
   <si>
     <t xml:space="preserve">4.09638738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9311797618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750042915344</t>
+    <t xml:space="preserve">3.93118071556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98750066757202</t>
   </si>
   <si>
     <t xml:space="preserve">3.83731245994568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93868970870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623658180237</t>
+    <t xml:space="preserve">3.93868947029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623586654663</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493437767029</t>
@@ -434,121 +434,121 @@
     <t xml:space="preserve">3.97248148918152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95746278762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9987645149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980275154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348208427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07010412216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04382181167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01378345489502</t>
+    <t xml:space="preserve">3.95746302604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99876427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604837417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348279953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470852851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07010459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04382133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01378297805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09263277053833</t>
+    <t xml:space="preserve">4.09263229370117</t>
   </si>
   <si>
     <t xml:space="preserve">4.1376895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05508470535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91240668296814</t>
+    <t xml:space="preserve">4.12267017364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0550856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91240692138672</t>
   </si>
   <si>
     <t xml:space="preserve">3.82229375839233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81478381156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90489673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987827301025</t>
+    <t xml:space="preserve">3.81478452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9048969745636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114235877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8898777961731</t>
   </si>
   <si>
     <t xml:space="preserve">3.81102919578552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88612413406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738750457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236880302429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233068466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6120297908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7960102558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96121740341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999119758606</t>
+    <t xml:space="preserve">3.88612365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738726615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236856460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110447883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221823692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61202955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79601001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96121764183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999095916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504730224609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96497297286987</t>
+    <t xml:space="preserve">3.96497273445129</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753807067871</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">4.14519834518433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99501085281372</t>
+    <t xml:space="preserve">3.99501013755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.92742514610291</t>
@@ -569,40 +569,40 @@
     <t xml:space="preserve">3.83355736732483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78474617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727481842041</t>
+    <t xml:space="preserve">3.78474640846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727505683899</t>
   </si>
   <si>
     <t xml:space="preserve">3.79225564002991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.751704454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056611061096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60452055931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54444479942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5414412021637</t>
+    <t xml:space="preserve">3.75170540809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518395423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64056515693665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60452079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54444456100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54144167900085</t>
   </si>
   <si>
     <t xml:space="preserve">3.55645966529846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60001468658447</t>
+    <t xml:space="preserve">3.60001516342163</t>
   </si>
   <si>
     <t xml:space="preserve">3.4708526134491</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">3.66459584236145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64507102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66910171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748579978943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73969006538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857678413391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144420623779</t>
+    <t xml:space="preserve">3.64507126808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66910123825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748603820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73968982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144372940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.1038966178894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01002931594849</t>
+    <t xml:space="preserve">4.01002883911133</t>
   </si>
   <si>
     <t xml:space="preserve">4.04006624221802</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">4.00251913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07761335372925</t>
+    <t xml:space="preserve">4.07761383056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.16772651672363</t>
@@ -656,40 +656,40 @@
     <t xml:space="preserve">4.15270757675171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14895343780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18274545669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22029209136963</t>
+    <t xml:space="preserve">4.14895296096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1827449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22029256820679</t>
   </si>
   <si>
     <t xml:space="preserve">4.2390661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16021728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12642431259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06259489059448</t>
+    <t xml:space="preserve">4.16021633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06259441375732</t>
   </si>
   <si>
     <t xml:space="preserve">4.03631210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13393449783325</t>
+    <t xml:space="preserve">4.13393497467041</t>
   </si>
   <si>
     <t xml:space="preserve">4.28787660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30289602279663</t>
+    <t xml:space="preserve">4.30289649963379</t>
   </si>
   <si>
     <t xml:space="preserve">4.33293342590332</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">4.46810340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6933856010437</t>
+    <t xml:space="preserve">4.44557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69338512420654</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085742950439</t>
+    <t xml:space="preserve">4.67085790634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.80978202819824</t>
@@ -722,43 +722,43 @@
     <t xml:space="preserve">4.81353664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79851770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7271785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85108375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82104587554932</t>
+    <t xml:space="preserve">4.79851722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85108327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82104539871216</t>
   </si>
   <si>
     <t xml:space="preserve">4.83606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07056093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0744891166687</t>
+    <t xml:space="preserve">5.07056140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07448863983154</t>
   </si>
   <si>
     <t xml:space="preserve">5.12947559356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16875219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552179336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371210098267</t>
+    <t xml:space="preserve">5.16875123977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552131652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371257781982</t>
   </si>
   <si>
     <t xml:space="preserve">5.3415675163269</t>
@@ -767,52 +767,52 @@
     <t xml:space="preserve">5.3769154548645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20410060882568</t>
+    <t xml:space="preserve">5.20410013198853</t>
   </si>
   <si>
     <t xml:space="preserve">5.28265237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20017194747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373914718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092287063599</t>
+    <t xml:space="preserve">5.20017290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373819351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092334747314</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29050874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26694202423096</t>
+    <t xml:space="preserve">5.29050827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26694250106812</t>
   </si>
   <si>
     <t xml:space="preserve">5.36906099319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34942245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38477087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21981143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2551589012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32585763931274</t>
+    <t xml:space="preserve">5.34942197799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3847713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.219810962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25515937805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32585668563843</t>
   </si>
   <si>
     <t xml:space="preserve">5.25123167037964</t>
@@ -821,73 +821,73 @@
     <t xml:space="preserve">5.37298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975782394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.577223777771</t>
+    <t xml:space="preserve">5.43975830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57722473144531</t>
   </si>
   <si>
     <t xml:space="preserve">5.5418758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63221073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62435579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50652694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5379490852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62042903900146</t>
+    <t xml:space="preserve">5.63221168518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62435626983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5065279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53794860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
     <t xml:space="preserve">5.55365896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50259971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41226387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52223777770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61257362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69112586975098</t>
+    <t xml:space="preserve">5.50260019302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41226434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52223825454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61257266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69112539291382</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572383880615</t>
+    <t xml:space="preserve">5.87572431564331</t>
   </si>
   <si>
     <t xml:space="preserve">5.71076393127441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73432970046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64006662368774</t>
+    <t xml:space="preserve">5.73432922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64006614685059</t>
   </si>
   <si>
     <t xml:space="preserve">5.65970468521118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72647380828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68326997756958</t>
+    <t xml:space="preserve">5.72647476196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6832709312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.67148733139038</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77360534667969</t>
+    <t xml:space="preserve">5.77360582351685</t>
   </si>
   <si>
     <t xml:space="preserve">5.86786842346191</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">5.83644723892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82466506958008</t>
+    <t xml:space="preserve">5.82466459274292</t>
   </si>
   <si>
     <t xml:space="preserve">5.84037494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82859230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93463850021362</t>
+    <t xml:space="preserve">5.8285927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93463802337646</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034885406494</t>
@@ -932,94 +932,94 @@
     <t xml:space="preserve">5.79717206954956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70290946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78931570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89143419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78538799285889</t>
+    <t xml:space="preserve">5.70290803909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78931617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89143466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70683574676514</t>
+    <t xml:space="preserve">5.70683622360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46725082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293603897095</t>
+    <t xml:space="preserve">5.56937026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46725130081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293460845947</t>
   </si>
   <si>
     <t xml:space="preserve">5.66756010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47903394699097</t>
+    <t xml:space="preserve">5.47903442382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39262580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45939540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75004053115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040246963501</t>
+    <t xml:space="preserve">5.39262676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45939588546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75004100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76182317733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040199279785</t>
   </si>
   <si>
     <t xml:space="preserve">5.75396776199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80109977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8089542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91500043869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87965202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85215902328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84430313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001348495483</t>
+    <t xml:space="preserve">5.80109930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80895471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91499948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87965154647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8521580696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84430360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001300811768</t>
   </si>
   <si>
     <t xml:space="preserve">5.84823083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72254705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6950535774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66363191604614</t>
+    <t xml:space="preserve">5.72254657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69505310058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363286972046</t>
   </si>
   <si>
     <t xml:space="preserve">5.64792203903198</t>
@@ -1028,73 +1028,73 @@
     <t xml:space="preserve">5.71861886978149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83252096176147</t>
+    <t xml:space="preserve">5.83252000808716</t>
   </si>
   <si>
     <t xml:space="preserve">5.76575040817261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11530923843384</t>
+    <t xml:space="preserve">6.11530876159668</t>
   </si>
   <si>
     <t xml:space="preserve">6.08388757705688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26063060760498</t>
+    <t xml:space="preserve">6.2606315612793</t>
   </si>
   <si>
     <t xml:space="preserve">6.24492025375366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31168937683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29205179214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25277614593506</t>
+    <t xml:space="preserve">6.31169033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29990768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29205226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670289993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2527756690979</t>
   </si>
   <si>
     <t xml:space="preserve">6.26455879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20171642303467</t>
+    <t xml:space="preserve">6.20171689987183</t>
   </si>
   <si>
     <t xml:space="preserve">6.23313808441162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06032276153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00926399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1270923614502</t>
+    <t xml:space="preserve">6.06032180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926303863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12709188461304</t>
   </si>
   <si>
     <t xml:space="preserve">6.22528266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28026866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37060451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3745322227478</t>
+    <t xml:space="preserve">6.28026914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37060403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37453174591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
@@ -1106,109 +1106,109 @@
     <t xml:space="preserve">6.45308446884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58662414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53949165344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60626220703125</t>
+    <t xml:space="preserve">6.58662366867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53949213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
     <t xml:space="preserve">6.63768291473389</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56305694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83013582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874263763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79086065292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409152984619</t>
+    <t xml:space="preserve">6.56305742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8301362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79085969924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.77907752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336717605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85762929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86155652999878</t>
+    <t xml:space="preserve">6.75551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86155700683594</t>
   </si>
   <si>
     <t xml:space="preserve">6.81049776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70445203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375568389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99902439117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3328709602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4035701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58031225204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54103660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55281829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641063690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783229827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351703643799</t>
+    <t xml:space="preserve">6.70445346832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99902391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40356922149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5803108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54103803634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641206741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351655960083</t>
   </si>
   <si>
     <t xml:space="preserve">7.66672039031982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8041877746582</t>
+    <t xml:space="preserve">7.80418682098389</t>
   </si>
   <si>
     <t xml:space="preserve">7.75705480575562</t>
@@ -1223,73 +1223,73 @@
     <t xml:space="preserve">7.91808748245239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78454732894897</t>
+    <t xml:space="preserve">7.78454923629761</t>
   </si>
   <si>
     <t xml:space="preserve">7.86310148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87488460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74056053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886354446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951713562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50804376602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53161001205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23782396316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69657039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80026006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826404571533</t>
+    <t xml:space="preserve">7.87488412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74056005477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951761245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50804328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53160953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23782348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610231399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410820007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076318740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59130907058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69656896591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355146408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80026054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826595306396</t>
   </si>
   <si>
     <t xml:space="preserve">7.83325099945068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94950914382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914672851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52061223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83010864257812</t>
+    <t xml:space="preserve">7.94950866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914720535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52061319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83010911941528</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">8.08304882049561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09090328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95343589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0437707901001</t>
+    <t xml:space="preserve">8.09090518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165229797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95343685150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04377174377441</t>
   </si>
   <si>
     <t xml:space="preserve">8.11054134368896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1458911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07126426696777</t>
+    <t xml:space="preserve">8.14589023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07126522064209</t>
   </si>
   <si>
     <t xml:space="preserve">7.86702966690063</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">7.69499826431274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71070909500122</t>
+    <t xml:space="preserve">7.71070957183838</t>
   </si>
   <si>
     <t xml:space="preserve">7.64158248901367</t>
@@ -1337,40 +1337,40 @@
     <t xml:space="preserve">7.67300462722778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61487436294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65572357177734</t>
+    <t xml:space="preserve">7.61487531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65572261810303</t>
   </si>
   <si>
     <t xml:space="preserve">7.85524654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59445142745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415143966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602308273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56146001815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75312805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83168125152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554557800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897953033447</t>
+    <t xml:space="preserve">7.59445095062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602403640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56145906448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7531270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83168029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7955470085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03897857666016</t>
   </si>
   <si>
     <t xml:space="preserve">8.08750534057617</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">8.01633548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942853927612</t>
+    <t xml:space="preserve">7.96942806243896</t>
   </si>
   <si>
     <t xml:space="preserve">7.97427940368652</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">8.14816093444824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21690464019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93222379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85943698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87884664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86752367019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726921081543</t>
+    <t xml:space="preserve">8.21690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93222427368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85943794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87884616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86752462387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726968765259</t>
   </si>
   <si>
     <t xml:space="preserve">7.4194769859314</t>
@@ -1427,40 +1427,40 @@
     <t xml:space="preserve">7.19626188278198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43079853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40492010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42594623565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568141937256</t>
+    <t xml:space="preserve">7.43079948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40491914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42594718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568284988403</t>
   </si>
   <si>
     <t xml:space="preserve">6.59293413162231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43441867828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84849882125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805219650269</t>
+    <t xml:space="preserve">6.43441915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8484992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805171966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.10729932785034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92613935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81776666641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22214126586914</t>
+    <t xml:space="preserve">6.92613983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81776714324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22214221954346</t>
   </si>
   <si>
     <t xml:space="preserve">7.20111465454102</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">7.1477370262146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58607912063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70415735244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63784027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7817964553833</t>
+    <t xml:space="preserve">7.2641978263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681270599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58607959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70415687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857194900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63783931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179693222046</t>
   </si>
   <si>
     <t xml:space="preserve">7.7073917388916</t>
@@ -1496,34 +1496,34 @@
     <t xml:space="preserve">7.80282497406006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62975168228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69445133209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032274246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95163488388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05353736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001697540283</t>
+    <t xml:space="preserve">7.62975120544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6944522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886735916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032178878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95163440704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001792907715</t>
   </si>
   <si>
     <t xml:space="preserve">8.07294750213623</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">8.19264221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29777908325195</t>
+    <t xml:space="preserve">8.25329971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969097137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29778099060059</t>
   </si>
   <si>
     <t xml:space="preserve">8.31395530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27756023406982</t>
+    <t xml:space="preserve">8.27756118774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455505371094</t>
@@ -1556,37 +1556,37 @@
     <t xml:space="preserve">8.23307991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28564929962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24925422668457</t>
+    <t xml:space="preserve">8.21286010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28564834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.12794208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24521255493164</t>
+    <t xml:space="preserve">8.24521160125732</t>
   </si>
   <si>
     <t xml:space="preserve">8.13198661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06647777557373</t>
+    <t xml:space="preserve">8.06647682189941</t>
   </si>
   <si>
     <t xml:space="preserve">8.1764669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07941722869873</t>
+    <t xml:space="preserve">8.07941627502441</t>
   </si>
   <si>
     <t xml:space="preserve">8.14007377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08588695526123</t>
+    <t xml:space="preserve">8.08588600158691</t>
   </si>
   <si>
     <t xml:space="preserve">8.12389850616455</t>
@@ -1595,19 +1595,19 @@
     <t xml:space="preserve">8.20881652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22499179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30990982055664</t>
+    <t xml:space="preserve">8.2249927520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30991077423096</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18859767913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33417320251465</t>
+    <t xml:space="preserve">8.1885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33417415618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.30182361602783</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">8.60510635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77898693084717</t>
+    <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
     <t xml:space="preserve">8.77089977264404</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95691108703613</t>
+    <t xml:space="preserve">8.95691204071045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04183101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11866092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22379875183105</t>
+    <t xml:space="preserve">9.04182910919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11866188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379970550537</t>
   </si>
   <si>
     <t xml:space="preserve">9.33298015594482</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">9.41790008544922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44620609283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61604404449463</t>
+    <t xml:space="preserve">9.44620513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61604309082031</t>
   </si>
   <si>
     <t xml:space="preserve">9.48259925842285</t>
@@ -1667,31 +1667,31 @@
     <t xml:space="preserve">9.31276226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39768123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30063056945801</t>
+    <t xml:space="preserve">9.39768028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30063152313232</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1146183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67789077758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65362930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05192089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89987468719482</t>
+    <t xml:space="preserve">9.19549369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11461925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67789173126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65363025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05191898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89987516403198</t>
   </si>
   <si>
     <t xml:space="preserve">7.88531637191772</t>
@@ -1700,46 +1700,46 @@
     <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800231933594</t>
+    <t xml:space="preserve">7.83355665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800184249878</t>
   </si>
   <si>
     <t xml:space="preserve">7.25287485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24155235290527</t>
+    <t xml:space="preserve">7.24155282974243</t>
   </si>
   <si>
     <t xml:space="preserve">7.1606764793396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05715656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595659255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860158920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770643234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59093236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92251920700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106477737427</t>
+    <t xml:space="preserve">7.05715608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32081031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3386025428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47770738601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59093189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92251873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106334686279</t>
   </si>
   <si>
     <t xml:space="preserve">7.76562213897705</t>
@@ -1748,136 +1748,136 @@
     <t xml:space="preserve">7.78503227233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721981048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00824737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9451642036438</t>
+    <t xml:space="preserve">7.98721933364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0082483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516468048096</t>
   </si>
   <si>
     <t xml:space="preserve">7.96619272232056</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88370037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78017950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7898850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76238632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74297714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84164571762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98075103759766</t>
+    <t xml:space="preserve">7.88369941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78988409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76238679885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74297666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84164428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98074960708618</t>
   </si>
   <si>
     <t xml:space="preserve">7.91119718551636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68474721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85134935379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74944686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39036130905151</t>
+    <t xml:space="preserve">7.68474626541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85134983062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74944591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889699935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39036178588867</t>
   </si>
   <si>
     <t xml:space="preserve">7.22537708282471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24963998794556</t>
+    <t xml:space="preserve">7.24963855743408</t>
   </si>
   <si>
     <t xml:space="preserve">7.44212198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49388265609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521551132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26581430435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890640258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35477733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01833629608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05230379104614</t>
+    <t xml:space="preserve">7.4938817024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26581478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890687942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35477685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0183367729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0523042678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.93099117279053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0992112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0798020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99245738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831701278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875471115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58446264266968</t>
+    <t xml:space="preserve">7.09921216964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07980155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99245691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446216583252</t>
   </si>
   <si>
     <t xml:space="preserve">7.62328100204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56828737258911</t>
+    <t xml:space="preserve">7.56828594207764</t>
   </si>
   <si>
     <t xml:space="preserve">7.55534696578979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54079055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634441375732</t>
+    <t xml:space="preserve">7.54078912734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634489059448</t>
   </si>
   <si>
     <t xml:space="preserve">7.92898988723755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78826713562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88046455383301</t>
+    <t xml:space="preserve">7.78826808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88046503067017</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781908035278</t>
@@ -1892,49 +1892,49 @@
     <t xml:space="preserve">7.83193969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92575407028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01795196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80767679214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00339317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39887428283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2371244430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45144081115723</t>
+    <t xml:space="preserve">7.92575454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01795291900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80767726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00339508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3988733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23712348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45144176483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.57679843902588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38674354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26947212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18051147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26138591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3503475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83559799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92051792144775</t>
+    <t xml:space="preserve">8.38674259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2694730758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18051052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35034942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92051696777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.08226680755615</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">9.15909862518311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18740558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02161121368408</t>
+    <t xml:space="preserve">9.18740653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0216121673584</t>
   </si>
   <si>
     <t xml:space="preserve">9.07418155670166</t>
@@ -1970,28 +1970,28 @@
     <t xml:space="preserve">9.32489204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26828002929688</t>
+    <t xml:space="preserve">9.26828098297119</t>
   </si>
   <si>
     <t xml:space="preserve">9.36533069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5917797088623</t>
+    <t xml:space="preserve">9.59178066253662</t>
   </si>
   <si>
     <t xml:space="preserve">9.4057674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59582424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65647983551025</t>
+    <t xml:space="preserve">9.5958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65648078918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.56751823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45833683013916</t>
+    <t xml:space="preserve">9.45833587646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.46642398834229</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">9.47451210021973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81014347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0163736343384</t>
+    <t xml:space="preserve">9.81014251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0163745880127</t>
   </si>
   <si>
     <t xml:space="preserve">9.83036231994629</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">9.84943962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79552745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629379272461</t>
+    <t xml:space="preserve">9.7955265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629474639893</t>
   </si>
   <si>
     <t xml:space="preserve">9.79967308044434</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">9.47619724273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40569591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50162124633789</t>
+    <t xml:space="preserve">9.40569686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50161933898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.44356155395508</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">8.27767562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1715087890625</t>
+    <t xml:space="preserve">8.17150974273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.96912908554077</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">8.12506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03050708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22625160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23620510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11842727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21131992340088</t>
+    <t xml:space="preserve">8.0305061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22625064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2362060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11842632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728225708008</t>
+    <t xml:space="preserve">8.00728321075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.0869083404541</t>
@@ -2081,37 +2081,37 @@
     <t xml:space="preserve">8.03880214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67385339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670240402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77172613143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70868873596191</t>
+    <t xml:space="preserve">7.87955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69376087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091138839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670335769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70868921279907</t>
   </si>
   <si>
     <t xml:space="preserve">7.7136664390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70039510726929</t>
+    <t xml:space="preserve">7.7003960609436</t>
   </si>
   <si>
     <t xml:space="preserve">7.73357200622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58925151824951</t>
+    <t xml:space="preserve">7.58925104141235</t>
   </si>
   <si>
     <t xml:space="preserve">7.62574672698975</t>
@@ -2120,22 +2120,22 @@
     <t xml:space="preserve">7.50299119949341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72859525680542</t>
+    <t xml:space="preserve">7.55109786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72859573364258</t>
   </si>
   <si>
     <t xml:space="preserve">7.82978534698486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91936445236206</t>
+    <t xml:space="preserve">7.91936302185059</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12837982177734</t>
+    <t xml:space="preserve">8.12837886810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.08359050750732</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">7.96249389648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13667297363281</t>
+    <t xml:space="preserve">8.13667488098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.17814445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2196159362793</t>
+    <t xml:space="preserve">8.21961688995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.60529899597168</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">8.87901020050049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86656761169434</t>
+    <t xml:space="preserve">8.86656856536865</t>
   </si>
   <si>
     <t xml:space="preserve">8.54724025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38550090789795</t>
+    <t xml:space="preserve">8.38549995422363</t>
   </si>
   <si>
     <t xml:space="preserve">8.55553340911865</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">8.51406288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4560022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30670547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48088550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2909460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3232946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704784393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06700229644775</t>
+    <t xml:space="preserve">8.45600318908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30670642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48088645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29094696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32329368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06700134277344</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283981323242</t>
@@ -2204,31 +2204,31 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462259292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45820283889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57266330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39184761047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22098636627197</t>
+    <t xml:space="preserve">7.86462116241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36530733108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45820188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5726637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39184856414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22098684310913</t>
   </si>
   <si>
     <t xml:space="preserve">7.38355445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38853120803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7319130897522</t>
+    <t xml:space="preserve">7.38853073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73191261291504</t>
   </si>
   <si>
     <t xml:space="preserve">7.41839027404785</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">7.25084543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42502593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06173706054688</t>
+    <t xml:space="preserve">7.42502546310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06173658370972</t>
   </si>
   <si>
     <t xml:space="preserve">7.17951583862305</t>
@@ -2252,82 +2252,82 @@
     <t xml:space="preserve">7.25914001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56436920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44493246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76509189605713</t>
+    <t xml:space="preserve">7.564368724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4449315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76509046554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.73854875564575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92765760421753</t>
+    <t xml:space="preserve">7.92765712738037</t>
   </si>
   <si>
     <t xml:space="preserve">7.77836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030162811279</t>
+    <t xml:space="preserve">7.82646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030067443848</t>
   </si>
   <si>
     <t xml:space="preserve">7.94258737564087</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15989685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116239547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16985130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09851932525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76343107223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79660844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03216457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98903560638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84969186782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9774227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840782165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90443468093872</t>
+    <t xml:space="preserve">8.15989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18975639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16985034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09852027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76343202590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79660797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03216648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98903512954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84969091415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86130380630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9044337272644</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">8.02718925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65394687652588</t>
+    <t xml:space="preserve">7.65394735336304</t>
   </si>
   <si>
     <t xml:space="preserve">7.72361946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89614009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1267204284668</t>
+    <t xml:space="preserve">7.89613962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12671947479248</t>
   </si>
   <si>
     <t xml:space="preserve">7.95917654037476</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">8.46014976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44770812988281</t>
+    <t xml:space="preserve">8.44770908355713</t>
   </si>
   <si>
     <t xml:space="preserve">8.42697334289551</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">8.37720775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60944557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412693023682</t>
+    <t xml:space="preserve">8.60944747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412788391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.95780563354492</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">9.16516208648682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13198471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23566436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48449325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255104064941</t>
+    <t xml:space="preserve">9.13198566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23566246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255199432373</t>
   </si>
   <si>
     <t xml:space="preserve">9.52596282958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50937557220459</t>
+    <t xml:space="preserve">9.50937461853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.42643070220947</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38496112823486</t>
+    <t xml:space="preserve">9.38496017456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.51766872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73746585845947</t>
+    <t xml:space="preserve">9.73746681213379</t>
   </si>
   <si>
     <t xml:space="preserve">9.70014190673828</t>
@@ -2441,22 +2441,22 @@
     <t xml:space="preserve">9.57158088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2315149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28957748413086</t>
+    <t xml:space="preserve">9.33934116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23151683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28957653045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.35178279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38910675048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19833946228027</t>
+    <t xml:space="preserve">9.3891077041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19834041595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.31031227111816</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">9.26884078979492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11539554595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12369155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04074859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06148338317871</t>
+    <t xml:space="preserve">9.11539745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12369060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04074764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06148433685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.01586532592773</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">9.05319023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93292236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12783813476562</t>
+    <t xml:space="preserve">8.93292427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12783908843994</t>
   </si>
   <si>
     <t xml:space="preserve">8.88315773010254</t>
@@ -2498,28 +2498,28 @@
     <t xml:space="preserve">8.82509803771973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09880828857422</t>
+    <t xml:space="preserve">9.09880924224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24395751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58817005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29372215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15272045135498</t>
+    <t xml:space="preserve">9.58817100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29372406005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1527214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.25639915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15686798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21492767333984</t>
+    <t xml:space="preserve">9.15686702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21492862701416</t>
   </si>
   <si>
     <t xml:space="preserve">9.11954402923584</t>
@@ -2531,40 +2531,40 @@
     <t xml:space="preserve">9.09466075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11124897003174</t>
+    <t xml:space="preserve">9.11124992370605</t>
   </si>
   <si>
     <t xml:space="preserve">8.77533149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27298831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.107102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77118301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97024536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27713489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68770122528076</t>
+    <t xml:space="preserve">9.27298736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10710144042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77118396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97024726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27713584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68770217895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.1444263458252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0863676071167</t>
+    <t xml:space="preserve">9.08636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">9.05733680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99098300933838</t>
+    <t xml:space="preserve">8.99098205566406</t>
   </si>
   <si>
     <t xml:space="preserve">9.28128147125244</t>
@@ -2573,37 +2573,37 @@
     <t xml:space="preserve">8.89559936523438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25279235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14994335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87457466125488</t>
+    <t xml:space="preserve">8.25279426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14994430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87457513809204</t>
   </si>
   <si>
     <t xml:space="preserve">7.74186611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34042406082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35867071151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73328399658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25055694580078</t>
+    <t xml:space="preserve">7.34042501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35867166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327211380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73328447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.53256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73797273635864</t>
+    <t xml:space="preserve">5.73797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">6.38990116119385</t>
@@ -2615,79 +2615,79 @@
     <t xml:space="preserve">6.12946128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24060440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20245122909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1908392906189</t>
+    <t xml:space="preserve">6.24060487747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2024507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19083976745605</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71503686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33047151565552</t>
+    <t xml:space="preserve">6.71503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3304705619812</t>
   </si>
   <si>
     <t xml:space="preserve">6.85769748687744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98542881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87594509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87096834182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09159660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4233660697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59256887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310317993164</t>
+    <t xml:space="preserve">6.98542928695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87594556808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87096881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0915961265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42336702346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59257030487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310270309448</t>
   </si>
   <si>
     <t xml:space="preserve">7.83144474029541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92931699752808</t>
+    <t xml:space="preserve">7.92931747436523</t>
   </si>
   <si>
     <t xml:space="preserve">7.32715368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22264528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21601009368896</t>
+    <t xml:space="preserve">7.22264575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21600961685181</t>
   </si>
   <si>
     <t xml:space="preserve">7.24255228042603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76977872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26411724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66224193572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067697525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88286876678467</t>
+    <t xml:space="preserve">6.76977825164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26411771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88286828994751</t>
   </si>
   <si>
     <t xml:space="preserve">8.07363796234131</t>
@@ -2696,58 +2696,58 @@
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4103832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0520715713501</t>
+    <t xml:space="preserve">8.41038513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05207252502441</t>
   </si>
   <si>
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35232448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22956848144531</t>
+    <t xml:space="preserve">8.7089786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35232353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22956943511963</t>
   </si>
   <si>
     <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29426383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20800399780273</t>
+    <t xml:space="preserve">8.294264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20800304412842</t>
   </si>
   <si>
     <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47259044647217</t>
+    <t xml:space="preserve">8.4725923538208</t>
   </si>
   <si>
     <t xml:space="preserve">8.78777408599854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71312522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91218757629395</t>
+    <t xml:space="preserve">8.71312427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874423980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91218566894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.0034236907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34763717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34348964691162</t>
+    <t xml:space="preserve">9.34763622283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34349060058594</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94896984100342</t>
+    <t xml:space="preserve">9.94897174835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0443544387817</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">10.2848873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87432193756104</t>
+    <t xml:space="preserve">9.87432098388672</t>
   </si>
   <si>
     <t xml:space="preserve">9.98214721679688</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">10.0650901794434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9655590057373</t>
+    <t xml:space="preserve">9.96555995941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.95311641693115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3595361709595</t>
+    <t xml:space="preserve">10.3595371246338</t>
   </si>
   <si>
     <t xml:space="preserve">10.3512411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7286310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6996002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6747169494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387994766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4093027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4632148742676</t>
+    <t xml:space="preserve">10.7286319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6996011734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6747188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3388013839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4093017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4632139205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.4010076522827</t>
@@ -2816,58 +2816,58 @@
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415414810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8323097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9318408966064</t>
+    <t xml:space="preserve">10.6415405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8323106765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7659559249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9318399429321</t>
   </si>
   <si>
     <t xml:space="preserve">10.7783966064453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6332473754883</t>
+    <t xml:space="preserve">10.633246421814</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024141311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.181209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.53786277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3305072784424</t>
+    <t xml:space="preserve">10.4300374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5378637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
     <t xml:space="preserve">10.3553895950317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2309761047363</t>
+    <t xml:space="preserve">10.230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4175968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0645484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8654870986938</t>
+    <t xml:space="preserve">11.064549446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8654880523682</t>
   </si>
   <si>
     <t xml:space="preserve">10.8240156173706</t>
@@ -2882,28 +2882,28 @@
     <t xml:space="preserve">10.7493667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6871604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6913070678711</t>
+    <t xml:space="preserve">10.687159538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6913080215454</t>
   </si>
   <si>
     <t xml:space="preserve">10.7949857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6664237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5337152481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6249532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733852386475</t>
+    <t xml:space="preserve">10.6664257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5337162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6249523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733842849731</t>
   </si>
   <si>
     <t xml:space="preserve">10.4341850280762</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">10.0319137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81626129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83285045623779</t>
+    <t xml:space="preserve">9.81626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83285140991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.46790313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44716835021973</t>
+    <t xml:space="preserve">9.44716739654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.72087860107422</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">9.5591402053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71258354187012</t>
+    <t xml:space="preserve">9.71258449554443</t>
   </si>
   <si>
     <t xml:space="preserve">9.67940711975098</t>
@@ -2954,58 +2954,58 @@
     <t xml:space="preserve">9.82040977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0277652740479</t>
+    <t xml:space="preserve">10.0277662277222</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1604747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1729164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102394104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0775299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1521797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99044227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1065626144409</t>
+    <t xml:space="preserve">9.90335083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1604738235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1729154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102403640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0775318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1521787643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1065616607666</t>
   </si>
   <si>
     <t xml:space="preserve">9.96141147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59646320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53425693511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970748901367</t>
+    <t xml:space="preserve">9.59646415710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67111206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74575996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970558166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3844194412231</t>
+    <t xml:space="preserve">10.3844203948975</t>
   </si>
   <si>
     <t xml:space="preserve">10.347095489502</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">10.3346538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94482421875</t>
+    <t xml:space="preserve">9.94482231140137</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2683010101318</t>
+    <t xml:space="preserve">10.2682991027832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5088329315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4134483337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5212745666504</t>
+    <t xml:space="preserve">10.4134492874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5212755203247</t>
   </si>
   <si>
     <t xml:space="preserve">10.8074264526367</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">10.7576608657837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8779277801514</t>
+    <t xml:space="preserve">10.8779268264771</t>
   </si>
   <si>
     <t xml:space="preserve">10.8945169448853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9359874725342</t>
+    <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
     <t xml:space="preserve">10.8157215118408</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">10.9733114242554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986625671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8364562988281</t>
+    <t xml:space="preserve">10.8986644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8364553451538</t>
   </si>
   <si>
     <t xml:space="preserve">10.9857530593872</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8447504043579</t>
+    <t xml:space="preserve">10.8447513580322</t>
   </si>
   <si>
     <t xml:space="preserve">10.9774589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.135048866272</t>
+    <t xml:space="preserve">11.1350507736206</t>
   </si>
   <si>
     <t xml:space="preserve">11.1018733978271</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">11.1143140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35484790802</t>
+    <t xml:space="preserve">11.3548488616943</t>
   </si>
   <si>
     <t xml:space="preserve">11.1474905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1599321365356</t>
+    <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
     <t xml:space="preserve">11.3921718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2843465805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6119709014893</t>
+    <t xml:space="preserve">11.2843456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6119699478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.5207328796387</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">10.6788654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926416397095</t>
+    <t xml:space="preserve">11.2926406860352</t>
   </si>
   <si>
     <t xml:space="preserve">11.9935064315796</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">12.1096258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3999252319336</t>
+    <t xml:space="preserve">12.3999261856079</t>
   </si>
   <si>
     <t xml:space="preserve">12.1303625106812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4455432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2630701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953098297119</t>
+    <t xml:space="preserve">12.4455442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.263069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
     <t xml:space="preserve">12.594841003418</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.358452796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1718339920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3169822692871</t>
+    <t xml:space="preserve">12.3584537506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1718330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3169832229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.1842737197876</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3377180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.192569732666</t>
+    <t xml:space="preserve">12.3377170562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1925687789917</t>
   </si>
   <si>
     <t xml:space="preserve">12.0847425460815</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">12.2879524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0640087127686</t>
+    <t xml:space="preserve">12.0640077590942</t>
   </si>
   <si>
     <t xml:space="preserve">12.0349779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9230051040649</t>
+    <t xml:space="preserve">11.9230060577393</t>
   </si>
   <si>
     <t xml:space="preserve">11.9810638427734</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1635389328003</t>
+    <t xml:space="preserve">12.163537979126</t>
   </si>
   <si>
     <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3543081283569</t>
+    <t xml:space="preserve">12.3543062210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.1759805679321</t>
@@ -3221,19 +3221,19 @@
     <t xml:space="preserve">11.9437408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.117919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244115829468</t>
+    <t xml:space="preserve">12.1179208755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820024490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244125366211</t>
   </si>
   <si>
     <t xml:space="preserve">11.5580577850342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5539112091064</t>
+    <t xml:space="preserve">11.5539102554321</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626731872559</t>
@@ -3242,31 +3242,31 @@
     <t xml:space="preserve">11.5746459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834098815918</t>
+    <t xml:space="preserve">11.4834089279175</t>
   </si>
   <si>
     <t xml:space="preserve">11.5912351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5995283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5870866775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6824703216553</t>
+    <t xml:space="preserve">11.5995292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5870876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
     <t xml:space="preserve">11.7405319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9603290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7985906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981218338013</t>
+    <t xml:space="preserve">11.9603300094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7985916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981237411499</t>
   </si>
   <si>
     <t xml:space="preserve">11.9520349502563</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">11.5331745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4543800354004</t>
+    <t xml:space="preserve">11.4543790817261</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751148223877</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8193264007568</t>
+    <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
     <t xml:space="preserve">11.9064168930054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8773860931396</t>
+    <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
     <t xml:space="preserve">12.0142421722412</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">11.8732395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.661735534668</t>
+    <t xml:space="preserve">11.6617374420166</t>
   </si>
   <si>
     <t xml:space="preserve">11.7322378158569</t>
@@ -3314,109 +3314,109 @@
     <t xml:space="preserve">11.7446784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6534414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7115020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7654151916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1640796661377</t>
+    <t xml:space="preserve">11.6534423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.711501121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7654142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5787935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.164080619812</t>
   </si>
   <si>
     <t xml:space="preserve">11.2055521011353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4129085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4336433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3299646377563</t>
+    <t xml:space="preserve">11.3050832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4129076004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4336442947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3299655914307</t>
   </si>
   <si>
     <t xml:space="preserve">11.3631420135498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3382587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3880243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3714370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4917030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5124387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6451482772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5622034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5953817367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5497636795044</t>
+    <t xml:space="preserve">11.3382596969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714380264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4917020797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5124397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5622043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.524881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5953807830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5497646331787</t>
   </si>
   <si>
     <t xml:space="preserve">11.66588306427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.931300163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8607978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6409997940063</t>
+    <t xml:space="preserve">11.9312992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8607997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6410007476807</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068857192993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.026683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1013326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2133045196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2423334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1967153549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3086881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1510972976685</t>
+    <t xml:space="preserve">12.0266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1013317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2133054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2423343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1967163085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3086891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1510982513428</t>
   </si>
   <si>
     <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391254425049</t>
+    <t xml:space="preserve">12.0391263961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690929412842</t>
@@ -3425,46 +3425,46 @@
     <t xml:space="preserve">11.7778558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1220664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2215976715088</t>
+    <t xml:space="preserve">12.1220674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2215986251831</t>
   </si>
   <si>
     <t xml:space="preserve">12.333571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7151079177856</t>
+    <t xml:space="preserve">12.7151069641113</t>
   </si>
   <si>
     <t xml:space="preserve">12.5367813110352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3708944320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7773141860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8975820541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2293510437012</t>
+    <t xml:space="preserve">12.3708953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7773132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8975811004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2293519973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.3827962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532957077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5942993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4201202392578</t>
+    <t xml:space="preserve">13.453296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5942983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698848724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4201211929321</t>
   </si>
   <si>
     <t xml:space="preserve">13.3496179580688</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">13.216911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0510244369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1588506698608</t>
+    <t xml:space="preserve">13.051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1588487625122</t>
   </si>
   <si>
     <t xml:space="preserve">13.1837348937988</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">13.2583818435669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1629972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625284194946</t>
+    <t xml:space="preserve">13.1629981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625293731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514942169189</t>
@@ -3503,43 +3503,43 @@
     <t xml:space="preserve">12.8644037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8685503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607259750366</t>
+    <t xml:space="preserve">12.8685522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9349069595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312273025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7482843399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5741052627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6611957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9763774871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2376470565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1215267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0095548629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.241792678833</t>
+    <t xml:space="preserve">12.9349060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7482833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6611948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9763765335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.237645149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1215257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2417936325073</t>
   </si>
   <si>
     <t xml:space="preserve">13.3081474304199</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">12.6446056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090860366821</t>
+    <t xml:space="preserve">12.9722309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090850830078</t>
   </si>
   <si>
     <t xml:space="preserve">12.9929647445679</t>
@@ -3578,52 +3578,52 @@
     <t xml:space="preserve">13.2044687271118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1173801422119</t>
+    <t xml:space="preserve">13.1173791885376</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523580551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8016538619995</t>
+    <t xml:space="preserve">13.7850694656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8016548156738</t>
   </si>
   <si>
     <t xml:space="preserve">13.7726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7975101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9219217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9799833297729</t>
+    <t xml:space="preserve">13.7975091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9219236373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9799823760986</t>
   </si>
   <si>
     <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7270059585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6979780197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0048666000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7643308639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878095626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173072814941</t>
+    <t xml:space="preserve">13.7270069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0048656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.764331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173063278198</t>
   </si>
   <si>
     <t xml:space="preserve">14.224663734436</t>
@@ -3632,85 +3632,85 @@
     <t xml:space="preserve">14.3324899673462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0712203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583089828491</t>
+    <t xml:space="preserve">14.0712184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583099365234</t>
   </si>
   <si>
     <t xml:space="preserve">14.2951650619507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3532238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2619867324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3076066970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3006267547607</t>
+    <t xml:space="preserve">14.3532257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2619876861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3076057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.12513256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3006258010864</t>
   </si>
   <si>
     <t xml:space="preserve">13.8255081176758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8597507476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6542940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3161468505859</t>
+    <t xml:space="preserve">13.859751701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6542949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2819051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2605028152466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4359970092773</t>
+    <t xml:space="preserve">13.435996055603</t>
   </si>
   <si>
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834573745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5515661239624</t>
+    <t xml:space="preserve">13.1834564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5515670776367</t>
   </si>
   <si>
     <t xml:space="preserve">13.9068365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.645733833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4488372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4188756942749</t>
+    <t xml:space="preserve">13.6457347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4488382339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4188766479492</t>
   </si>
   <si>
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258836746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9951229095459</t>
+    <t xml:space="preserve">13.4445581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9951219558716</t>
   </si>
   <si>
     <t xml:space="preserve">12.7639837265015</t>
@@ -3725,16 +3725,16 @@
     <t xml:space="preserve">12.9095144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433815002441</t>
+    <t xml:space="preserve">13.2433824539185</t>
   </si>
   <si>
     <t xml:space="preserve">13.2519416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2134189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4531192779541</t>
+    <t xml:space="preserve">13.2134199142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4531183242798</t>
   </si>
   <si>
     <t xml:space="preserve">13.4873609542847</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">13.7741451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8511905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5301656723022</t>
+    <t xml:space="preserve">13.8511915206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5301647186279</t>
   </si>
   <si>
     <t xml:space="preserve">13.6114912033081</t>
@@ -3767,34 +3767,34 @@
     <t xml:space="preserve">13.2861862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0293655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1920166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1320934295654</t>
+    <t xml:space="preserve">13.0293645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1920175552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1320924758911</t>
   </si>
   <si>
     <t xml:space="preserve">12.7597026824951</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3616313934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5499649047852</t>
+    <t xml:space="preserve">12.3616304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5499658584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857606887817</t>
+    <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.85387134552</t>
+    <t xml:space="preserve">12.8538703918457</t>
   </si>
   <si>
     <t xml:space="preserve">12.900954246521</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8495903015137</t>
+    <t xml:space="preserve">12.7682638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.849591255188</t>
   </si>
   <si>
     <t xml:space="preserve">13.0550470352173</t>
@@ -3824,16 +3824,16 @@
     <t xml:space="preserve">13.6799764633179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5430059432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4103145599365</t>
+    <t xml:space="preserve">13.543004989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4103155136108</t>
   </si>
   <si>
     <t xml:space="preserve">13.277624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4301166534424</t>
+    <t xml:space="preserve">12.4301156997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
@@ -3842,10 +3842,10 @@
     <t xml:space="preserve">12.7768239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0234832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0363245010376</t>
+    <t xml:space="preserve">12.0234842300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0363264083862</t>
   </si>
   <si>
     <t xml:space="preserve">11.8351488113403</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">10.8720712661743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5339260101318</t>
+    <t xml:space="preserve">10.5339250564575</t>
   </si>
   <si>
     <t xml:space="preserve">11.783784866333</t>
@@ -3869,43 +3869,43 @@
     <t xml:space="preserve">11.5954494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8265867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950729370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157232284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9892406463623</t>
+    <t xml:space="preserve">11.826587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9892416000366</t>
   </si>
   <si>
     <t xml:space="preserve">12.0106420516968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849615097046</t>
+    <t xml:space="preserve">12.0277652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849605560303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8479900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9507179260254</t>
+    <t xml:space="preserve">11.9507188796997</t>
   </si>
   <si>
     <t xml:space="preserve">12.3145475387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1989774703979</t>
+    <t xml:space="preserve">12.1989784240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3102674484253</t>
+    <t xml:space="preserve">12.310266494751</t>
   </si>
   <si>
     <t xml:space="preserve">12.2631826400757</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262111663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188276290894</t>
+    <t xml:space="preserve">12.1262121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188285827637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203798294067</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">12.0834083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0705680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8651103973389</t>
+    <t xml:space="preserve">12.0705671310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8651113510132</t>
   </si>
   <si>
     <t xml:space="preserve">11.4798803329468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2444620132446</t>
+    <t xml:space="preserve">11.2444610595703</t>
   </si>
   <si>
     <t xml:space="preserve">11.2530221939087</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">11.3771524429321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0775279998779</t>
+    <t xml:space="preserve">11.0775270462036</t>
   </si>
   <si>
     <t xml:space="preserve">11.0903692245483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5724477767944</t>
+    <t xml:space="preserve">10.5724487304688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0545263290405</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">10.8292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8035869598389</t>
+    <t xml:space="preserve">10.8035850524902</t>
   </si>
   <si>
     <t xml:space="preserve">10.7693433761597</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.5423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969728469849</t>
+    <t xml:space="preserve">11.6969738006592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6351318359375</t>
@@ -4025,31 +4025,31 @@
     <t xml:space="preserve">11.560037612915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1580638885498</t>
+    <t xml:space="preserve">11.1580648422241</t>
   </si>
   <si>
     <t xml:space="preserve">11.4893608093262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.37451171875</t>
+    <t xml:space="preserve">11.3745107650757</t>
   </si>
   <si>
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62968349456787</t>
+    <t xml:space="preserve">10.6368255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62968254089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13052940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74453353881836</t>
+    <t xml:space="preserve">9.13053035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74453258514404</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">9.57667636871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89030265808105</t>
+    <t xml:space="preserve">9.89030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.92122364044189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1818437576294</t>
+    <t xml:space="preserve">10.1818447113037</t>
   </si>
   <si>
     <t xml:space="preserve">10.4645500183105</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">10.6191558837891</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4689683914185</t>
+    <t xml:space="preserve">10.4689674377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.4778022766113</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">10.3894567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0890817642212</t>
+    <t xml:space="preserve">10.0890808105469</t>
   </si>
   <si>
     <t xml:space="preserve">10.1244201660156</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">9.9786491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2171821594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7384214401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5970687866211</t>
+    <t xml:space="preserve">10.2171812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7384223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
     <t xml:space="preserve">10.3585357666016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83287811279297</t>
+    <t xml:space="preserve">9.83287906646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.85054779052734</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">10.5661478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3408670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0934991836548</t>
+    <t xml:space="preserve">10.3408660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.92564105987549</t>
@@ -4130,13 +4130,13 @@
     <t xml:space="preserve">10.0758295059204</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0007343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6809968948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6500768661499</t>
+    <t xml:space="preserve">10.0007352828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6809978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6500759124756</t>
   </si>
   <si>
     <t xml:space="preserve">10.999041557312</t>
@@ -4148,19 +4148,19 @@
     <t xml:space="preserve">10.8267679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.707501411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5573129653931</t>
+    <t xml:space="preserve">10.7075004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5573139190674</t>
   </si>
   <si>
     <t xml:space="preserve">10.9062795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9592866897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9902067184448</t>
+    <t xml:space="preserve">10.959285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9902076721191</t>
   </si>
   <si>
     <t xml:space="preserve">10.7781772613525</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">9.95656299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0051517486572</t>
+    <t xml:space="preserve">10.0051527023315</t>
   </si>
   <si>
     <t xml:space="preserve">9.93447589874268</t>
@@ -4196,16 +4196,16 @@
     <t xml:space="preserve">9.55458927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42648887634277</t>
+    <t xml:space="preserve">9.42648792266846</t>
   </si>
   <si>
     <t xml:space="preserve">9.84613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55017280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58109283447266</t>
+    <t xml:space="preserve">9.55017185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58109378814697</t>
   </si>
   <si>
     <t xml:space="preserve">9.59876251220703</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797750473022</t>
+    <t xml:space="preserve">10.8797740936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.919529914856</t>
@@ -4226,31 +4226,31 @@
     <t xml:space="preserve">11.3082523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1183080673218</t>
+    <t xml:space="preserve">11.1183090209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.9946250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5528964996338</t>
+    <t xml:space="preserve">10.5528955459595</t>
   </si>
   <si>
     <t xml:space="preserve">10.8046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215036392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9372005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3259220123291</t>
+    <t xml:space="preserve">11.3215045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9371995925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3259210586548</t>
   </si>
   <si>
     <t xml:space="preserve">11.02112865448</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8488540649414</t>
+    <t xml:space="preserve">10.8488550186157</t>
   </si>
   <si>
     <t xml:space="preserve">11.2508268356323</t>
@@ -4259,37 +4259,37 @@
     <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8471612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5379505157471</t>
+    <t xml:space="preserve">11.8471603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5379514694214</t>
   </si>
   <si>
     <t xml:space="preserve">10.9460344314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9548683166504</t>
+    <t xml:space="preserve">10.9548692703247</t>
   </si>
   <si>
     <t xml:space="preserve">10.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239482879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.246410369873</t>
+    <t xml:space="preserve">10.9239473342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2464094161987</t>
   </si>
   <si>
     <t xml:space="preserve">11.2331581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2110719680786</t>
+    <t xml:space="preserve">11.2110710144043</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.962010383606</t>
+    <t xml:space="preserve">11.9620094299316</t>
   </si>
   <si>
     <t xml:space="preserve">12.0591897964478</t>
@@ -4304,10 +4304,10 @@
     <t xml:space="preserve">12.0503568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1961278915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3949041366577</t>
+    <t xml:space="preserve">12.1961269378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3949031829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.1607885360718</t>
@@ -4328,70 +4328,70 @@
     <t xml:space="preserve">12.6908626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7527055740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8277988433838</t>
+    <t xml:space="preserve">12.7527046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8277978897095</t>
   </si>
   <si>
     <t xml:space="preserve">12.9205617904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9514818191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0354118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2518577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1811819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2827777862549</t>
+    <t xml:space="preserve">12.9514827728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0354108810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2518587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1811809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2827787399292</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.441801071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743198394775</t>
+    <t xml:space="preserve">13.4418020248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743188858032</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285488128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6405792236328</t>
+    <t xml:space="preserve">13.3578729629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6405782699585</t>
   </si>
   <si>
     <t xml:space="preserve">13.6494131088257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9144506454468</t>
+    <t xml:space="preserve">13.9144515991211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5522336959839</t>
+    <t xml:space="preserve">13.5522327423096</t>
   </si>
   <si>
     <t xml:space="preserve">13.6008234024048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7465944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6759166717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.773097038269</t>
+    <t xml:space="preserve">13.7465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6759176254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7730979919434</t>
   </si>
   <si>
     <t xml:space="preserve">13.923285484314</t>
@@ -4424,10 +4424,10 @@
     <t xml:space="preserve">13.8658599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1883220672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5947132110596</t>
+    <t xml:space="preserve">14.1883230209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5947122573853</t>
   </si>
   <si>
     <t xml:space="preserve">14.4710273742676</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">14.7802381515503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7669868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7095613479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7934923171997</t>
+    <t xml:space="preserve">14.7669878005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7095623016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7934904098511</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">14.3429279327393</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5196180343628</t>
+    <t xml:space="preserve">14.5196189880371</t>
   </si>
   <si>
     <t xml:space="preserve">14.3385095596313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1485662460327</t>
+    <t xml:space="preserve">14.148567199707</t>
   </si>
   <si>
     <t xml:space="preserve">14.0955591201782</t>
@@ -4475,52 +4475,52 @@
     <t xml:space="preserve">14.4489421844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5107841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4312734603882</t>
+    <t xml:space="preserve">14.5107831954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4312725067139</t>
   </si>
   <si>
     <t xml:space="preserve">14.5328712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5814599990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9790163040161</t>
+    <t xml:space="preserve">14.52845287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5814609527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9790172576904</t>
   </si>
   <si>
     <t xml:space="preserve">14.9392614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8553342819214</t>
+    <t xml:space="preserve">14.8553333282471</t>
   </si>
   <si>
     <t xml:space="preserve">15.009937286377</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6609716415405</t>
+    <t xml:space="preserve">14.6609725952148</t>
   </si>
   <si>
     <t xml:space="preserve">14.6918916702271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5682096481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9701824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7714023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6433029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453706741333</t>
+    <t xml:space="preserve">14.568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9701814651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7714042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6433038711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453716278076</t>
   </si>
   <si>
     <t xml:space="preserve">14.1397314071655</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">14.444525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2236614227295</t>
+    <t xml:space="preserve">14.2236604690552</t>
   </si>
   <si>
     <t xml:space="preserve">14.3473443984985</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">12.2402982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4523296356201</t>
+    <t xml:space="preserve">12.4523286819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.502613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7455625534058</t>
+    <t xml:space="preserve">11.7455635070801</t>
   </si>
   <si>
     <t xml:space="preserve">11.2684965133667</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">12.3153924942017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4169912338257</t>
+    <t xml:space="preserve">12.4169902801514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.023853302002</t>
+    <t xml:space="preserve">12.0238513946533</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500919342041</t>
+    <t xml:space="preserve">12.5009183883667</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">12.4920845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2933073043823</t>
+    <t xml:space="preserve">12.293306350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579689025879</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">12.5141706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0795841217041</t>
+    <t xml:space="preserve">13.0795831680298</t>
   </si>
   <si>
     <t xml:space="preserve">12.5848474502563</t>
@@ -4634,28 +4634,28 @@
     <t xml:space="preserve">12.7438697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684015274048</t>
+    <t xml:space="preserve">12.3684005737305</t>
   </si>
   <si>
     <t xml:space="preserve">12.5892648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5362567901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3065586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.540675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1298666000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7588148117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1121978759766</t>
+    <t xml:space="preserve">12.5362577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3065595626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7588157653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1121988296509</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632322311401</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">11.9399242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8824996948242</t>
+    <t xml:space="preserve">11.8824987411499</t>
   </si>
   <si>
     <t xml:space="preserve">11.2022380828857</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.0653009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2950000762939</t>
+    <t xml:space="preserve">11.2949991226196</t>
   </si>
   <si>
     <t xml:space="preserve">11.0873880386353</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.30748462677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638666152954</t>
+    <t xml:space="preserve">11.0638675689697</t>
   </si>
   <si>
     <t xml:space="preserve">11.2753086090088</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">11.3856248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4361867904663</t>
+    <t xml:space="preserve">11.436185836792</t>
   </si>
   <si>
     <t xml:space="preserve">11.6522245407104</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">11.5832767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913463592529</t>
+    <t xml:space="preserve">11.4913454055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.4959421157837</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">11.4499769210815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4591693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7533473968506</t>
+    <t xml:space="preserve">11.4591703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7533483505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6935930252075</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">11.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0041131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9949188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0960426330566</t>
+    <t xml:space="preserve">11.0041122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9949197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.096043586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.1833772659302</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">11.2890977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0868511199951</t>
+    <t xml:space="preserve">11.0868501663208</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4683628082275</t>
+    <t xml:space="preserve">11.4683637619019</t>
   </si>
   <si>
     <t xml:space="preserve">11.8131036758423</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">12.1486501693726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3279161453247</t>
+    <t xml:space="preserve">12.3187217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3279151916504</t>
   </si>
   <si>
     <t xml:space="preserve">12.5117769241333</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.3784770965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5301637649536</t>
+    <t xml:space="preserve">12.5301628112793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6358833312988</t>
@@ -4832,19 +4832,19 @@
     <t xml:space="preserve">12.9760274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4428281784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255661010742</t>
+    <t xml:space="preserve">12.7645864486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4428291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255670547485</t>
   </si>
   <si>
     <t xml:space="preserve">12.4750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2385368347168</t>
+    <t xml:space="preserve">11.2385358810425</t>
   </si>
   <si>
     <t xml:space="preserve">12.0383338928223</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">11.964789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9555959701538</t>
+    <t xml:space="preserve">11.9555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5005388259888</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">11.6016626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5510997772217</t>
+    <t xml:space="preserve">11.551100730896</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143280029297</t>
@@ -4877,19 +4877,19 @@
     <t xml:space="preserve">11.5786800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7073831558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625408172607</t>
+    <t xml:space="preserve">11.7073822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625417709351</t>
   </si>
   <si>
     <t xml:space="preserve">11.7441549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6384353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465040206909</t>
+    <t xml:space="preserve">11.6384344100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465049743652</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855243682861</t>
@@ -4898,19 +4898,19 @@
     <t xml:space="preserve">11.7487516403198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6154518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9489545822144</t>
+    <t xml:space="preserve">11.6154527664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.94895362854</t>
   </si>
   <si>
     <t xml:space="preserve">10.7558994293213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.870813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570232391357</t>
+    <t xml:space="preserve">10.8708124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570241928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.8478298187256</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">10.889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7283210754395</t>
+    <t xml:space="preserve">10.7283201217651</t>
   </si>
   <si>
     <t xml:space="preserve">10.8294439315796</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">10.6915483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6547765731812</t>
+    <t xml:space="preserve">10.6547756195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7329168319702</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">10.6271963119507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858287811279</t>
+    <t xml:space="preserve">10.5858278274536</t>
   </si>
   <si>
     <t xml:space="preserve">10.287052154541</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">10.1445598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1215772628784</t>
+    <t xml:space="preserve">10.1215782165527</t>
   </si>
   <si>
     <t xml:space="preserve">9.91932964324951</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">9.99747085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79522228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399631500244</t>
+    <t xml:space="preserve">9.79522323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399621963501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721391677856</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">9.90094375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96989154815674</t>
+    <t xml:space="preserve">9.96989250183105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1951217651367</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">10.043436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0848045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0388402938843</t>
+    <t xml:space="preserve">10.0848054885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.03883934021</t>
   </si>
   <si>
     <t xml:space="preserve">10.057225227356</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">10.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629457473755</t>
+    <t xml:space="preserve">10.1629467010498</t>
   </si>
   <si>
     <t xml:space="preserve">10.2181043624878</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">11.0454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3948183059692</t>
+    <t xml:space="preserve">11.3948192596436</t>
   </si>
   <si>
     <t xml:space="preserve">11.5097322463989</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">11.0592708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9995164871216</t>
+    <t xml:space="preserve">10.9995155334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9903221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477283477783</t>
+    <t xml:space="preserve">10.9903230667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477293014526</t>
   </si>
   <si>
     <t xml:space="preserve">11.3672389984131</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">11.5970659255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7763319015503</t>
+    <t xml:space="preserve">11.776330947876</t>
   </si>
   <si>
     <t xml:space="preserve">11.8866481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3646879196167</t>
+    <t xml:space="preserve">12.3646869659424</t>
   </si>
   <si>
     <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4290399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.401460647583</t>
+    <t xml:space="preserve">12.4290390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4014596939087</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3692836761475</t>
+    <t xml:space="preserve">12.3692846298218</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554944992065</t>
@@ -5099,7 +5099,7 @@
     <t xml:space="preserve">12.5485486984253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2497749328613</t>
+    <t xml:space="preserve">12.249773979187</t>
   </si>
   <si>
     <t xml:space="preserve">12.5393571853638</t>
@@ -5111,25 +5111,25 @@
     <t xml:space="preserve">12.6404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.456618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7507972717285</t>
+    <t xml:space="preserve">12.4566192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7507963180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.6680593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8473243713379</t>
+    <t xml:space="preserve">12.8473253250122</t>
   </si>
   <si>
     <t xml:space="preserve">12.870306968689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9024829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7783756256104</t>
+    <t xml:space="preserve">12.9024820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7783765792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.8105525970459</t>
@@ -5138,16 +5138,16 @@
     <t xml:space="preserve">12.7094278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6174983978271</t>
+    <t xml:space="preserve">12.6174974441528</t>
   </si>
   <si>
     <t xml:space="preserve">12.5577421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8381319046021</t>
+    <t xml:space="preserve">12.6588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8381309509277</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819499969482</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">11.8544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8452796936035</t>
+    <t xml:space="preserve">11.8452787399292</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705099105835</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">12.1348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0888948440552</t>
+    <t xml:space="preserve">12.0888957977295</t>
   </si>
   <si>
     <t xml:space="preserve">11.9326124191284</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">11.8085069656372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8958396911621</t>
+    <t xml:space="preserve">11.8958406448364</t>
   </si>
   <si>
     <t xml:space="preserve">12.0107536315918</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">12.194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1532468795776</t>
+    <t xml:space="preserve">12.153247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.1854228973389</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">12.0934915542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808271408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1578435897827</t>
+    <t xml:space="preserve">12.1808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.157844543457</t>
   </si>
   <si>
     <t xml:space="preserve">12.2957391738892</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">12.3922672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6266899108887</t>
+    <t xml:space="preserve">12.626690864563</t>
   </si>
   <si>
     <t xml:space="preserve">12.6220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.833535194397</t>
+    <t xml:space="preserve">12.8335342407227</t>
   </si>
   <si>
     <t xml:space="preserve">12.9162721633911</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">12.4796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2242412567139</t>
+    <t xml:space="preserve">13.2242403030396</t>
   </si>
   <si>
     <t xml:space="preserve">13.136905670166</t>
@@ -5270,7 +5270,7 @@
     <t xml:space="preserve">13.2012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.270206451416</t>
+    <t xml:space="preserve">13.2702054977417</t>
   </si>
   <si>
     <t xml:space="preserve">13.1736783981323</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">12.6726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6818494796753</t>
+    <t xml:space="preserve">12.681848526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9990100860596</t>
+    <t xml:space="preserve">12.9990110397339</t>
   </si>
   <si>
     <t xml:space="preserve">13.0265893936157</t>
@@ -5309,16 +5309,16 @@
     <t xml:space="preserve">12.8611135482788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0541687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587644577026</t>
+    <t xml:space="preserve">13.0541677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.058765411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2748022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460990905762</t>
+    <t xml:space="preserve">13.1461000442505</t>
   </si>
   <si>
     <t xml:space="preserve">13.233434677124</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7804222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.92751121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9045276641846</t>
+    <t xml:space="preserve">13.780421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9275102615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9045286178589</t>
   </si>
   <si>
     <t xml:space="preserve">14.0102481842041</t>
@@ -6285,6 +6285,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.0550003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2150001525879</t>
   </si>
 </sst>
 </file>
@@ -71493,7 +71496,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6496064815</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>1116397</v>
@@ -71514,6 +71517,32 @@
         <v>2090</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.651099537</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>1167485</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>19.2150001525879</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>18.9349994659424</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>19.1499996185303</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>19.2150001525879</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2091</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="2092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">5.32048845291138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17209386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13951969146729</t>
+    <t xml:space="preserve">5.17209434509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951873779297</t>
   </si>
   <si>
     <t xml:space="preserve">5.26257848739624</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">5.1322808265686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26619815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3132495880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1938099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0454158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959499359131</t>
+    <t xml:space="preserve">5.266197681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31325006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19381093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04541540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959547042847</t>
   </si>
   <si>
     <t xml:space="preserve">5.07437086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65814256668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101392745972</t>
+    <t xml:space="preserve">4.65814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101345062256</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21190690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0490345954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485500335693</t>
+    <t xml:space="preserve">5.05265474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21190738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04903554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14675855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485452651978</t>
   </si>
   <si>
     <t xml:space="preserve">5.12504196166992</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56765651702881</t>
+    <t xml:space="preserve">4.74138784408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56765747070312</t>
   </si>
   <si>
     <t xml:space="preserve">4.34325551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545673370361</t>
+    <t xml:space="preserve">4.45545721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.48441171646118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58213567733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78482103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73414850234985</t>
+    <t xml:space="preserve">4.58213520050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73414945602417</t>
   </si>
   <si>
     <t xml:space="preserve">4.81377553939819</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">4.7667236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71243333816528</t>
+    <t xml:space="preserve">4.71243238449097</t>
   </si>
   <si>
     <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84996891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88616371154785</t>
+    <t xml:space="preserve">4.84996938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88616275787354</t>
   </si>
   <si>
     <t xml:space="preserve">5.00922203063965</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">5.09246730804443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10332536697388</t>
+    <t xml:space="preserve">5.10332584381104</t>
   </si>
   <si>
     <t xml:space="preserve">5.16847467422485</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">4.95493125915527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84273052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713199615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08884859085083</t>
+    <t xml:space="preserve">4.8427300453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120088577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">5.00560283660889</t>
@@ -188,31 +188,31 @@
     <t xml:space="preserve">5.19019079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35668230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12866163253784</t>
+    <t xml:space="preserve">5.23362302780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35668277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12866115570068</t>
   </si>
   <si>
     <t xml:space="preserve">5.02008008956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98026704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94769239425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9730281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0236988067627</t>
+    <t xml:space="preserve">4.98026752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94769334793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97302865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369976043701</t>
   </si>
   <si>
     <t xml:space="preserve">5.11418390274048</t>
@@ -221,31 +221,31 @@
     <t xml:space="preserve">5.121422290802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544158935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28287506103516</t>
+    <t xml:space="preserve">5.33544063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28287553787231</t>
   </si>
   <si>
     <t xml:space="preserve">5.27161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23030948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16647911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33168649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39176082611084</t>
+    <t xml:space="preserve">5.23030853271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16647958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3316855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.391761302948</t>
   </si>
   <si>
     <t xml:space="preserve">5.26410150527954</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">5.25659227371216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05759334564209</t>
+    <t xml:space="preserve">5.05759239196777</t>
   </si>
   <si>
     <t xml:space="preserve">5.09889459609985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96747922897339</t>
+    <t xml:space="preserve">4.96747970581055</t>
   </si>
   <si>
     <t xml:space="preserve">4.88863039016724</t>
@@ -272,100 +272,100 @@
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472473144531</t>
+    <t xml:space="preserve">4.76472520828247</t>
   </si>
   <si>
     <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9637246131897</t>
+    <t xml:space="preserve">4.96372509002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.90364980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90740442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77599000930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73844242095947</t>
+    <t xml:space="preserve">4.90740394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77598905563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73844194412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91866874694824</t>
+    <t xml:space="preserve">4.91866827011108</t>
   </si>
   <si>
     <t xml:space="preserve">4.986252784729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97874402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01629066467285</t>
+    <t xml:space="preserve">4.97874307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01629018783569</t>
   </si>
   <si>
     <t xml:space="preserve">4.92617797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95246076583862</t>
+    <t xml:space="preserve">4.95246028900146</t>
   </si>
   <si>
     <t xml:space="preserve">4.9712347984314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8548378944397</t>
+    <t xml:space="preserve">4.85483837127686</t>
   </si>
   <si>
     <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80227279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62204647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197118759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44182014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4493293762207</t>
+    <t xml:space="preserve">4.8022723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62204694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44182109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.45683908462524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56947994232178</t>
+    <t xml:space="preserve">4.56948041915894</t>
   </si>
   <si>
     <t xml:space="preserve">4.7534613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73093271255493</t>
+    <t xml:space="preserve">4.73093318939209</t>
   </si>
   <si>
     <t xml:space="preserve">4.80602741241455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97498893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063205718994</t>
+    <t xml:space="preserve">4.97498941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063158035278</t>
   </si>
   <si>
     <t xml:space="preserve">4.1301794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39676427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33668851852417</t>
+    <t xml:space="preserve">4.39676380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33668899536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.39300870895386</t>
@@ -374,31 +374,31 @@
     <t xml:space="preserve">4.17523574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10014200210571</t>
+    <t xml:space="preserve">4.10014152526855</t>
   </si>
   <si>
     <t xml:space="preserve">3.87485909461975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94244432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2653489112854</t>
+    <t xml:space="preserve">3.94244384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534938812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19025373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20151853561401</t>
+    <t xml:space="preserve">4.19025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20151901245117</t>
   </si>
   <si>
     <t xml:space="preserve">4.23531150817871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31040573120117</t>
+    <t xml:space="preserve">4.31040477752686</t>
   </si>
   <si>
     <t xml:space="preserve">4.25032997131348</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">4.24657583236694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27661371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93118071556091</t>
+    <t xml:space="preserve">4.27661323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93118023872375</t>
   </si>
   <si>
     <t xml:space="preserve">3.98750066757202</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">3.83731245994568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93868947029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623586654663</t>
+    <t xml:space="preserve">3.93868899345398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623634338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493437767029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97248148918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746302604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619846343994</t>
+    <t xml:space="preserve">3.97248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9461989402771</t>
   </si>
   <si>
     <t xml:space="preserve">3.99876427650452</t>
@@ -446,34 +446,34 @@
     <t xml:space="preserve">3.82980251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82604837417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348279953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470852851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07010459899902</t>
+    <t xml:space="preserve">3.82604742050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133104324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07010364532471</t>
   </si>
   <si>
     <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01378297805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05884027481079</t>
+    <t xml:space="preserve">4.01378393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05883979797363</t>
   </si>
   <si>
     <t xml:space="preserve">4.09263229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1376895904541</t>
+    <t xml:space="preserve">4.13768863677979</t>
   </si>
   <si>
     <t xml:space="preserve">4.12267017364502</t>
@@ -482,31 +482,31 @@
     <t xml:space="preserve">4.0550856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07385921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255653381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91240692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9048969745636</t>
+    <t xml:space="preserve">4.07385873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255605697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229351997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478357315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90489745140076</t>
   </si>
   <si>
     <t xml:space="preserve">3.90114235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8898777961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81102919578552</t>
+    <t xml:space="preserve">3.88987827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81102895736694</t>
   </si>
   <si>
     <t xml:space="preserve">3.88612365722656</t>
@@ -518,43 +518,43 @@
     <t xml:space="preserve">3.88236856460571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87110447883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233163833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221823692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61202955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96121764183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02504730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96497273445129</t>
+    <t xml:space="preserve">3.87110495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850102424622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61203002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550881385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79601049423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9612181186676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999143600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02504777908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96497225761414</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0888786315918</t>
+    <t xml:space="preserve">4.08887815475464</t>
   </si>
   <si>
     <t xml:space="preserve">4.14519834518433</t>
@@ -566,85 +566,85 @@
     <t xml:space="preserve">3.92742514610291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83355736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474640846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727505683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225564002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170540809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518395423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056515693665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60452079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54444456100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843784332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54144167900085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55645966529846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4708526134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66459584236145</t>
+    <t xml:space="preserve">3.83355784416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474593162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225587844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170493125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64056539535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60452055931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54444479942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843712806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5414412021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5564603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001492500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47085332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799982070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66459536552429</t>
   </si>
   <si>
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910123825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748603820801</t>
+    <t xml:space="preserve">3.66910171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748651504517</t>
   </si>
   <si>
     <t xml:space="preserve">3.73968982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84857559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14144372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1038966178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01002883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04006624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11516094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00251913070679</t>
+    <t xml:space="preserve">3.84857654571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14144325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10389614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01002931594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04006671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11516046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00251960754395</t>
   </si>
   <si>
     <t xml:space="preserve">4.07761383056641</t>
@@ -653,67 +653,67 @@
     <t xml:space="preserve">4.16772651672363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15270757675171</t>
+    <t xml:space="preserve">4.15270853042603</t>
   </si>
   <si>
     <t xml:space="preserve">4.14895296096802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1827449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22029256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2390661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16021633148193</t>
+    <t xml:space="preserve">4.08512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18274545669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22029209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23906564712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06259441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03631210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13393497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28787660598755</t>
+    <t xml:space="preserve">4.06259393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03631162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13393449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28787708282471</t>
   </si>
   <si>
     <t xml:space="preserve">4.30289649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33293342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557476043701</t>
+    <t xml:space="preserve">4.33293437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810388565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557523727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.63706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69338512420654</t>
+    <t xml:space="preserve">4.69338607788086</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80978202819824</t>
+    <t xml:space="preserve">4.67085695266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8097825050354</t>
   </si>
   <si>
     <t xml:space="preserve">4.83981990814209</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">4.81353664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79851722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72717809677124</t>
+    <t xml:space="preserve">4.79851818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7271785736084</t>
   </si>
   <si>
     <t xml:space="preserve">4.85108327865601</t>
@@ -737,49 +737,49 @@
     <t xml:space="preserve">4.83606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07056140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198163986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07448863983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12947559356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16875123977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371257781982</t>
+    <t xml:space="preserve">5.07056093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0744891166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12947511672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16875171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552083969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371210098267</t>
   </si>
   <si>
     <t xml:space="preserve">5.3415675163269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3769154548645</t>
+    <t xml:space="preserve">5.37691593170166</t>
   </si>
   <si>
     <t xml:space="preserve">5.20410013198853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28265237808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20017290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373819351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092334747314</t>
+    <t xml:space="preserve">5.28265285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20017337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092239379883</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">5.36906099319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34942197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3847713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588277816772</t>
+    <t xml:space="preserve">5.34942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38477087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588230133057</t>
   </si>
   <si>
     <t xml:space="preserve">5.219810962677</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">5.32585668563843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25123167037964</t>
+    <t xml:space="preserve">5.2512321472168</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975830078125</t>
+    <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
     <t xml:space="preserve">5.61650133132935</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">5.5418758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63221168518066</t>
+    <t xml:space="preserve">5.63221073150635</t>
   </si>
   <si>
     <t xml:space="preserve">5.62435626983643</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">5.5065279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53794860839844</t>
+    <t xml:space="preserve">5.53794813156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55365896224976</t>
+    <t xml:space="preserve">5.5536584854126</t>
   </si>
   <si>
     <t xml:space="preserve">5.50260019302368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41226434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52223825454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61257266998291</t>
+    <t xml:space="preserve">5.41226482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52223777770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61257314682007</t>
   </si>
   <si>
     <t xml:space="preserve">5.69112539291382</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076393127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73432922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64006614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65970468521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72647476196289</t>
+    <t xml:space="preserve">5.87572383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076345443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73432970046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64006662368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65970420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72647428512573</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">5.67148733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65577697753906</t>
+    <t xml:space="preserve">5.65577745437622</t>
   </si>
   <si>
     <t xml:space="preserve">5.77753353118896</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">5.83644723892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82466459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84037494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8285927772522</t>
+    <t xml:space="preserve">5.82466506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8403754234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82859230041504</t>
   </si>
   <si>
     <t xml:space="preserve">5.87179708480835</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90714502334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79717206954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70290803909302</t>
+    <t xml:space="preserve">5.90714454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7971715927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70290946960449</t>
   </si>
   <si>
     <t xml:space="preserve">5.78931617736816</t>
@@ -941,43 +941,43 @@
     <t xml:space="preserve">5.89143466949463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78538846969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79324340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70683622360229</t>
+    <t xml:space="preserve">5.7853889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79324388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70683526992798</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56937026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46725130081177</t>
+    <t xml:space="preserve">5.56936979293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46725082397461</t>
   </si>
   <si>
     <t xml:space="preserve">5.59293460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66756010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903442382812</t>
+    <t xml:space="preserve">5.66755962371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903394699097</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39262676239014</t>
+    <t xml:space="preserve">5.39262628555298</t>
   </si>
   <si>
     <t xml:space="preserve">5.45939588546753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75004100799561</t>
+    <t xml:space="preserve">5.75004005432129</t>
   </si>
   <si>
     <t xml:space="preserve">5.76182317733765</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">5.80895471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91499948501587</t>
+    <t xml:space="preserve">5.91499996185303</t>
   </si>
   <si>
     <t xml:space="preserve">5.87965154647827</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">5.8521580696106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84430360794067</t>
+    <t xml:space="preserve">5.84430265426636</t>
   </si>
   <si>
     <t xml:space="preserve">5.86001300811768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84823083877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254657745361</t>
+    <t xml:space="preserve">5.84823036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254610061646</t>
   </si>
   <si>
     <t xml:space="preserve">5.69505310058594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66363286972046</t>
+    <t xml:space="preserve">5.6636323928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.64792203903198</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">5.83252000808716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76575040817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11530876159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08388757705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2606315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24492025375366</t>
+    <t xml:space="preserve">5.76575088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11530923843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08388710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26063060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24492073059082</t>
   </si>
   <si>
     <t xml:space="preserve">6.31169033050537</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30776262283325</t>
+    <t xml:space="preserve">6.30776214599609</t>
   </si>
   <si>
     <t xml:space="preserve">6.29990768432617</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">6.29205226898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25670289993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2527756690979</t>
+    <t xml:space="preserve">6.25670337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25277614593506</t>
   </si>
   <si>
     <t xml:space="preserve">6.26455879211426</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">6.20171689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23313808441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00926303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12709188461304</t>
+    <t xml:space="preserve">6.23313760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1270923614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.22528266906738</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">6.28026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37060403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37453174591064</t>
+    <t xml:space="preserve">6.37060451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3745322227478</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">6.39809799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58662366867065</t>
+    <t xml:space="preserve">6.45308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">6.65339326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53949213027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60626173019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63768291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56305742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230792999268</t>
+    <t xml:space="preserve">6.5394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60626125335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63768339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5630578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230745315552</t>
   </si>
   <si>
     <t xml:space="preserve">6.8301362991333</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">6.68874168395996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79085969924927</t>
+    <t xml:space="preserve">6.79086065292358</t>
   </si>
   <si>
     <t xml:space="preserve">6.68088674545288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77907752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75551223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336669921875</t>
+    <t xml:space="preserve">6.72409009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77907705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75551176071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336574554443</t>
   </si>
   <si>
     <t xml:space="preserve">6.85762977600098</t>
@@ -1157,64 +1157,64 @@
     <t xml:space="preserve">6.86155700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81049776077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70445346832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99902391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40356922149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5803108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54103803634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55281925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46641206741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66672039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80418682098389</t>
+    <t xml:space="preserve">6.81049823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4035701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5410361289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.552818775177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46641111373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783277511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66671991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8041877746582</t>
   </si>
   <si>
     <t xml:space="preserve">7.75705480575562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88666725158691</t>
+    <t xml:space="preserve">7.88666820526123</t>
   </si>
   <si>
     <t xml:space="preserve">7.93379831314087</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">7.86310148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87488412857056</t>
+    <t xml:space="preserve">7.87488317489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.74056005477905</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">7.65886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31951761245728</t>
+    <t xml:space="preserve">7.31951808929443</t>
   </si>
   <si>
     <t xml:space="preserve">7.50804328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53160953521729</t>
+    <t xml:space="preserve">7.53161001205444</t>
   </si>
   <si>
     <t xml:space="preserve">7.23782348632812</t>
@@ -1253,28 +1253,28 @@
     <t xml:space="preserve">7.26610231399536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24410820007324</t>
+    <t xml:space="preserve">7.24410772323608</t>
   </si>
   <si>
     <t xml:space="preserve">7.30066537857056</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49076318740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59130907058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69656896591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355146408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80026054382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826595306396</t>
+    <t xml:space="preserve">7.49076366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59131002426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69656991958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355051040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826452255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.83325099945068</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">7.94950866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96914720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52061319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83010911941528</t>
+    <t xml:space="preserve">7.96914625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52061367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8301100730896</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08304882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165229797363</t>
+    <t xml:space="preserve">8.08304786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090328216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165372848511</t>
   </si>
   <si>
     <t xml:space="preserve">7.95343685150146</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">8.07126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86702966690063</t>
+    <t xml:space="preserve">7.86702871322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.83953523635864</t>
@@ -1331,28 +1331,28 @@
     <t xml:space="preserve">7.71070957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65572261810303</t>
+    <t xml:space="preserve">7.64158201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300271987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65572357177734</t>
   </si>
   <si>
     <t xml:space="preserve">7.85524654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59445095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602403640747</t>
+    <t xml:space="preserve">7.59445142745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602308273315</t>
   </si>
   <si>
     <t xml:space="preserve">7.56145906448364</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">7.82696628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7955470085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897857666016</t>
+    <t xml:space="preserve">7.79554605484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03898048400879</t>
   </si>
   <si>
     <t xml:space="preserve">8.08750534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01633548736572</t>
+    <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
     <t xml:space="preserve">7.96942806243896</t>
@@ -1388,91 +1388,91 @@
     <t xml:space="preserve">8.00986480712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07456493377686</t>
+    <t xml:space="preserve">8.07456588745117</t>
   </si>
   <si>
     <t xml:space="preserve">7.98560190200806</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14816093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21690559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93222427368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105442047119</t>
+    <t xml:space="preserve">8.14816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21690464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93222522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105537414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.85943794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87884616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86752462387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726968765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4194769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626188278198</t>
+    <t xml:space="preserve">7.87884712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86752367019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41947603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626140594482</t>
   </si>
   <si>
     <t xml:space="preserve">7.43079948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40491914749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42594718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568284988403</t>
+    <t xml:space="preserve">7.40491962432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42594766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568237304688</t>
   </si>
   <si>
     <t xml:space="preserve">6.59293413162231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43441915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8484992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81776714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22214221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20111465454102</t>
+    <t xml:space="preserve">6.43441867828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84849977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92613935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2221417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20111417770386</t>
   </si>
   <si>
     <t xml:space="preserve">7.1477370262146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2641978263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681270599365</t>
+    <t xml:space="preserve">7.26419639587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681222915649</t>
   </si>
   <si>
     <t xml:space="preserve">7.58607959747314</t>
@@ -1481,34 +1481,34 @@
     <t xml:space="preserve">7.70415687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66857194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63783931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78179693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7073917388916</t>
+    <t xml:space="preserve">7.66857290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63783979415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179597854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70739078521729</t>
   </si>
   <si>
     <t xml:space="preserve">7.80282497406006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62975120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6944522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886735916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223510742188</t>
+    <t xml:space="preserve">7.62975263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69445133209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223415374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.83032178878784</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">8.03089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95001792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294750213623</t>
+    <t xml:space="preserve">7.95001697540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294654846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.06809520721436</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">8.19264221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31395530700684</t>
+    <t xml:space="preserve">8.25329875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2977819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.27756118774414</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">8.18455505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23307991027832</t>
+    <t xml:space="preserve">8.233078956604</t>
   </si>
   <si>
     <t xml:space="preserve">8.21286010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28564834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24925518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12794208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24521160125732</t>
+    <t xml:space="preserve">8.28564739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24925422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12794303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24521064758301</t>
   </si>
   <si>
     <t xml:space="preserve">8.13198661804199</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">8.1764669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07941627502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14007377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08588600158691</t>
+    <t xml:space="preserve">8.07941722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1400728225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08588695526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.12389850616455</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">8.20881652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2249927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30991077423096</t>
+    <t xml:space="preserve">8.22499179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30991172790527</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903633117676</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">8.1885986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33417415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182361602783</t>
+    <t xml:space="preserve">8.33417510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182456970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.3179988861084</t>
@@ -1622,28 +1622,28 @@
     <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77089977264404</t>
+    <t xml:space="preserve">8.77089881896973</t>
   </si>
   <si>
     <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95691204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03778648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04182910919189</t>
+    <t xml:space="preserve">8.95691108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03778743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04183101654053</t>
   </si>
   <si>
     <t xml:space="preserve">9.11866188049316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22379970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298015594482</t>
+    <t xml:space="preserve">9.22379875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298110961914</t>
   </si>
   <si>
     <t xml:space="preserve">9.32084941864014</t>
@@ -1652,31 +1652,31 @@
     <t xml:space="preserve">9.22784233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41790008544922</t>
+    <t xml:space="preserve">9.4178991317749</t>
   </si>
   <si>
     <t xml:space="preserve">9.44620513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61604309082031</t>
+    <t xml:space="preserve">9.61604404449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.48259925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31276226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39768028259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30063152313232</t>
+    <t xml:space="preserve">9.3127613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39768123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30063056945801</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19549369812012</t>
+    <t xml:space="preserve">9.1954927444458</t>
   </si>
   <si>
     <t xml:space="preserve">9.11461925506592</t>
@@ -1685,52 +1685,52 @@
     <t xml:space="preserve">8.67789173126221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05191898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89987516403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11985492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83355665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800184249878</t>
+    <t xml:space="preserve">8.65362930297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05191993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89987325668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531732559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1198558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4680027961731</t>
   </si>
   <si>
     <t xml:space="preserve">7.25287485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24155282974243</t>
+    <t xml:space="preserve">7.24155187606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.1606764793396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05715608596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32081031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3386025428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770738601685</t>
+    <t xml:space="preserve">7.05715656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595659255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47770690917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.59093189239502</t>
@@ -1739,25 +1739,25 @@
     <t xml:space="preserve">7.92251873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75106334686279</t>
+    <t xml:space="preserve">7.75106525421143</t>
   </si>
   <si>
     <t xml:space="preserve">7.76562213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78503227233887</t>
+    <t xml:space="preserve">7.78503131866455</t>
   </si>
   <si>
     <t xml:space="preserve">7.98721933364868</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0082483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96619272232056</t>
+    <t xml:space="preserve">8.00824737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96619176864624</t>
   </si>
   <si>
     <t xml:space="preserve">7.88369941711426</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">7.78017997741699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78988409042358</t>
+    <t xml:space="preserve">7.78988456726074</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238679885864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74297666549683</t>
+    <t xml:space="preserve">7.74297857284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.84164428710938</t>
@@ -1781,37 +1781,37 @@
     <t xml:space="preserve">7.98074960708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91119718551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474626541138</t>
+    <t xml:space="preserve">7.91119623184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474721908569</t>
   </si>
   <si>
     <t xml:space="preserve">7.85134983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74944591522217</t>
+    <t xml:space="preserve">7.74944734573364</t>
   </si>
   <si>
     <t xml:space="preserve">7.32889699935913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39036178588867</t>
+    <t xml:space="preserve">7.39036083221436</t>
   </si>
   <si>
     <t xml:space="preserve">7.22537708282471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24963855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4938817024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521503448486</t>
+    <t xml:space="preserve">7.24963903427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49388122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521455764771</t>
   </si>
   <si>
     <t xml:space="preserve">7.26581478118896</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">7.21890687942505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35477685928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0183367729187</t>
+    <t xml:space="preserve">7.35477638244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
     <t xml:space="preserve">7.0523042678833</t>
@@ -1832,49 +1832,49 @@
     <t xml:space="preserve">6.93099117279053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09921216964722</t>
+    <t xml:space="preserve">7.0992112159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07980155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99245691299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875423431396</t>
+    <t xml:space="preserve">6.99245595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875471115112</t>
   </si>
   <si>
     <t xml:space="preserve">7.58446216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62328100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54078912734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707752227783</t>
+    <t xml:space="preserve">7.62328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54079008102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707656860352</t>
   </si>
   <si>
     <t xml:space="preserve">7.90634489059448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92898988723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78826808929443</t>
+    <t xml:space="preserve">7.92898893356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
     <t xml:space="preserve">7.88046503067017</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">7.85781908035278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67342519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57152223587036</t>
+    <t xml:space="preserve">7.67342472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57152271270752</t>
   </si>
   <si>
     <t xml:space="preserve">7.83193969726562</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">7.92575454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01795291900635</t>
+    <t xml:space="preserve">8.01795196533203</t>
   </si>
   <si>
     <t xml:space="preserve">7.80767726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00339508056641</t>
+    <t xml:space="preserve">8.00339412689209</t>
   </si>
   <si>
     <t xml:space="preserve">8.3988733291626</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">8.45144176483154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57679843902588</t>
+    <t xml:space="preserve">8.5767993927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.38674259185791</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">8.18051052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26138687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35034942626953</t>
+    <t xml:space="preserve">8.26138591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559989929199</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">9.08226680755615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15909862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18740653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0216121673584</t>
+    <t xml:space="preserve">9.15909957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18740463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
     <t xml:space="preserve">9.07418155670166</t>
@@ -1955,91 +1955,91 @@
     <t xml:space="preserve">9.28445434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17931842803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2318868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34915637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38150596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32489204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36533069610596</t>
+    <t xml:space="preserve">9.17931747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23188591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34915542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38150691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32489395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36532974243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4057674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5958251953125</t>
+    <t xml:space="preserve">9.40576839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59582424163818</t>
   </si>
   <si>
     <t xml:space="preserve">9.65648078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56751823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45833587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46642398834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47451210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81014251708984</t>
+    <t xml:space="preserve">9.56751918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4664249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47451114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">10.0163745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83036231994629</t>
+    <t xml:space="preserve">9.83036136627197</t>
   </si>
   <si>
     <t xml:space="preserve">10.036060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84943962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7955265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629474639893</t>
+    <t xml:space="preserve">9.84943866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79552745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629379272461</t>
   </si>
   <si>
     <t xml:space="preserve">9.79967308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73331928253174</t>
+    <t xml:space="preserve">9.73331737518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.47619724273682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40569686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50161933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44356155395508</t>
+    <t xml:space="preserve">9.40569591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50162124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44356060028076</t>
   </si>
   <si>
     <t xml:space="preserve">8.27767562866211</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">8.12506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0305061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22625064849854</t>
+    <t xml:space="preserve">8.03050708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22625255584717</t>
   </si>
   <si>
     <t xml:space="preserve">8.2362060546875</t>
@@ -2066,49 +2066,49 @@
     <t xml:space="preserve">8.11842632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21132183074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09520244598389</t>
+    <t xml:space="preserve">8.2113208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09520149230957</t>
   </si>
   <si>
     <t xml:space="preserve">8.00728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0869083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03880214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67385292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69376087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091138839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670335769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77172565460205</t>
+    <t xml:space="preserve">8.08690738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0388011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955141067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69375991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77172660827637</t>
   </si>
   <si>
     <t xml:space="preserve">7.70868921279907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7136664390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7003960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73357200622559</t>
+    <t xml:space="preserve">7.71366739273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73357248306274</t>
   </si>
   <si>
     <t xml:space="preserve">7.58925104141235</t>
@@ -2117,10 +2117,10 @@
     <t xml:space="preserve">7.62574672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50299119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109786987305</t>
+    <t xml:space="preserve">7.50299167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109834671021</t>
   </si>
   <si>
     <t xml:space="preserve">7.72859573364258</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">7.82978534698486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91936302185059</t>
+    <t xml:space="preserve">7.9193639755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17814445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21961688995361</t>
+    <t xml:space="preserve">7.96249485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17814350128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2196159362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.60529899597168</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">8.87901020050049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86656856536865</t>
+    <t xml:space="preserve">8.86656951904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.54724025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38549995422363</t>
+    <t xml:space="preserve">8.38550090789795</t>
   </si>
   <si>
     <t xml:space="preserve">8.55553340911865</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">8.30670642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48088645935059</t>
+    <t xml:space="preserve">8.48088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">8.29094696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32329368591309</t>
+    <t xml:space="preserve">8.3232946395874</t>
   </si>
   <si>
     <t xml:space="preserve">8.05704879760742</t>
@@ -2204,49 +2204,49 @@
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462116241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36530733108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45820188522339</t>
+    <t xml:space="preserve">7.86462211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45820140838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.5726637840271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39184856414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22098684310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38355445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38853073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41839027404785</t>
+    <t xml:space="preserve">7.39184808731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22098588943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38853168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73191165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41839122772217</t>
   </si>
   <si>
     <t xml:space="preserve">7.25084543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42502546310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06173658370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17951583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388187408447</t>
+    <t xml:space="preserve">7.42502593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388235092163</t>
   </si>
   <si>
     <t xml:space="preserve">7.25914001464844</t>
@@ -2273,34 +2273,34 @@
     <t xml:space="preserve">7.82646751403809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258737564087</t>
+    <t xml:space="preserve">7.72030162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258642196655</t>
   </si>
   <si>
     <t xml:space="preserve">8.15989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18975639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16985034942627</t>
+    <t xml:space="preserve">8.18975734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651449203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16984939575195</t>
   </si>
   <si>
     <t xml:space="preserve">8.09852027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76343202590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79660797119141</t>
+    <t xml:space="preserve">7.76343154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79660892486572</t>
   </si>
   <si>
     <t xml:space="preserve">8.03216648101807</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">7.98903512954712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84969091415405</t>
+    <t xml:space="preserve">7.84969186782837</t>
   </si>
   <si>
     <t xml:space="preserve">7.86130380630493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97742319107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05539035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581077575684</t>
+    <t xml:space="preserve">7.97742414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05538940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581172943115</t>
   </si>
   <si>
     <t xml:space="preserve">7.76840829849243</t>
@@ -2330,52 +2330,52 @@
     <t xml:space="preserve">7.9044337272644</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00064754486084</t>
+    <t xml:space="preserve">8.00064659118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.02718925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65394735336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89613962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12671947479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95917654037476</t>
+    <t xml:space="preserve">7.65394687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89614057540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1267204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95917510986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.17482662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33988285064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34403038024902</t>
+    <t xml:space="preserve">8.33988380432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34402942657471</t>
   </si>
   <si>
     <t xml:space="preserve">8.5596809387207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46014976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44770908355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62603569030762</t>
+    <t xml:space="preserve">8.46014881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44770812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6260347366333</t>
   </si>
   <si>
     <t xml:space="preserve">8.47673797607422</t>
@@ -2384,25 +2384,25 @@
     <t xml:space="preserve">8.37720775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60944747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95780563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16516208648682</t>
+    <t xml:space="preserve">8.60944652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95780658721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99927711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1651611328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.13198566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23566246032715</t>
+    <t xml:space="preserve">9.23566341400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.48449230194092</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">9.54255199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52596282958984</t>
+    <t xml:space="preserve">9.52596378326416</t>
   </si>
   <si>
     <t xml:space="preserve">9.50937461853027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42643070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3144588470459</t>
+    <t xml:space="preserve">9.42643165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31445789337158</t>
   </si>
   <si>
     <t xml:space="preserve">9.43057823181152</t>
@@ -2438,28 +2438,28 @@
     <t xml:space="preserve">9.70014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57158088684082</t>
+    <t xml:space="preserve">9.57158184051514</t>
   </si>
   <si>
     <t xml:space="preserve">9.33934116363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23151683807373</t>
+    <t xml:space="preserve">9.23151588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.28957653045654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35178279876709</t>
+    <t xml:space="preserve">9.35178375244141</t>
   </si>
   <si>
     <t xml:space="preserve">9.3891077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19834041595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31031227111816</t>
+    <t xml:space="preserve">9.19833946228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31031322479248</t>
   </si>
   <si>
     <t xml:space="preserve">9.21078014373779</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">9.26884078979492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11539745330811</t>
+    <t xml:space="preserve">9.11539649963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.12369060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04074764251709</t>
+    <t xml:space="preserve">9.04074954986572</t>
   </si>
   <si>
     <t xml:space="preserve">9.06148433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01586532592773</t>
+    <t xml:space="preserve">9.01586627960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.05319023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93292427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12783908843994</t>
+    <t xml:space="preserve">8.93292331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12783813476562</t>
   </si>
   <si>
     <t xml:space="preserve">8.88315773010254</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">8.82509803771973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09880924224854</t>
+    <t xml:space="preserve">9.09880828857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.24395751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58817100524902</t>
+    <t xml:space="preserve">9.58817005157471</t>
   </si>
   <si>
     <t xml:space="preserve">9.29372406005859</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">9.1527214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25639915466309</t>
+    <t xml:space="preserve">9.25639820098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.15686702728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21492862701416</t>
+    <t xml:space="preserve">9.21492767333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.11954402923584</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">9.11124992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77533149719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27298736572266</t>
+    <t xml:space="preserve">8.7753324508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27298831939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.10710144042969</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">8.77118396759033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97024726867676</t>
+    <t xml:space="preserve">8.97024631500244</t>
   </si>
   <si>
     <t xml:space="preserve">9.27713584899902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68770217895508</t>
+    <t xml:space="preserve">9.68770122528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.1444263458252</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">9.08636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05733680725098</t>
+    <t xml:space="preserve">9.05733776092529</t>
   </si>
   <si>
     <t xml:space="preserve">8.99098205566406</t>
@@ -2570,31 +2570,31 @@
     <t xml:space="preserve">9.28128147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89559936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25279426574707</t>
+    <t xml:space="preserve">8.89559841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25279331207275</t>
   </si>
   <si>
     <t xml:space="preserve">8.14994430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87457513809204</t>
+    <t xml:space="preserve">7.87457418441772</t>
   </si>
   <si>
     <t xml:space="preserve">7.74186611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34042501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35867166519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327211380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73328447341919</t>
+    <t xml:space="preserve">7.34042453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327259063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73328399658203</t>
   </si>
   <si>
     <t xml:space="preserve">6.25055742263794</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">5.73797225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38990116119385</t>
+    <t xml:space="preserve">6.38990068435669</t>
   </si>
   <si>
     <t xml:space="preserve">6.30861759185791</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">6.71503639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3304705619812</t>
+    <t xml:space="preserve">7.33047103881836</t>
   </si>
   <si>
     <t xml:space="preserve">6.85769748687744</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">7.0915961265564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42336702346802</t>
+    <t xml:space="preserve">7.4233660697937</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83310270309448</t>
+    <t xml:space="preserve">7.8331036567688</t>
   </si>
   <si>
     <t xml:space="preserve">7.83144474029541</t>
@@ -2663,34 +2663,34 @@
     <t xml:space="preserve">7.92931747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32715368270874</t>
+    <t xml:space="preserve">7.32715272903442</t>
   </si>
   <si>
     <t xml:space="preserve">7.22264575958252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21600961685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24255228042603</t>
+    <t xml:space="preserve">7.21601009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24255180358887</t>
   </si>
   <si>
     <t xml:space="preserve">6.76977825164795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26411771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64067602157593</t>
+    <t xml:space="preserve">7.2641167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66224145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64067649841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.88286828994751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07363796234131</t>
+    <t xml:space="preserve">8.07363700866699</t>
   </si>
   <si>
     <t xml:space="preserve">8.46844387054443</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7089786529541</t>
+    <t xml:space="preserve">8.70897769927979</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232353210449</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">8.75874423980713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91218566894531</t>
+    <t xml:space="preserve">8.91218662261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.0034236907959</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.34763622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34349060058594</t>
+    <t xml:space="preserve">9.34348964691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
@@ -2762,37 +2762,37 @@
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94897174835205</t>
+    <t xml:space="preserve">9.94897079467773</t>
   </si>
   <si>
     <t xml:space="preserve">10.0443544387817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98214721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0650901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96555995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95311641693115</t>
+    <t xml:space="preserve">10.2848863601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87432193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98214626312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065089225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9655590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95311737060547</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595371246338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3512411117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7286319732666</t>
+    <t xml:space="preserve">10.3512420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7286310195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.6996011734009</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">10.4093017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4632139205933</t>
+    <t xml:space="preserve">10.4632148742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.4010076522827</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">10.6415405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8323106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659559249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9318399429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7783966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.633246421814</t>
+    <t xml:space="preserve">10.8323097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7659540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9318408966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.778395652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6332473754883</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042175292969</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">10.1812086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5378637313843</t>
+    <t xml:space="preserve">10.53786277771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3305063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553895950317</t>
+    <t xml:space="preserve">10.3553886413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.230975151062</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">10.8654880523682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8240156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6125116348267</t>
+    <t xml:space="preserve">10.8240146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.612512588501</t>
   </si>
   <si>
     <t xml:space="preserve">10.6000699996948</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">10.6913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7949857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6664257049561</t>
+    <t xml:space="preserve">10.7949848175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6664237976074</t>
   </si>
   <si>
     <t xml:space="preserve">10.5337162017822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6249523162842</t>
+    <t xml:space="preserve">10.6249532699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.5751876831055</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">10.0733842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4341850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2392702102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3180646896362</t>
+    <t xml:space="preserve">10.4341840744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2392692565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180637359619</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">10.1936511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0319137573242</t>
+    <t xml:space="preserve">10.0319128036499</t>
   </si>
   <si>
     <t xml:space="preserve">9.81626224517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83285140991211</t>
+    <t xml:space="preserve">9.83285045623779</t>
   </si>
   <si>
     <t xml:space="preserve">9.46790313720703</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">9.5591402053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71258449554443</t>
+    <t xml:space="preserve">9.71258354187012</t>
   </si>
   <si>
     <t xml:space="preserve">9.67940711975098</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335083007812</t>
+    <t xml:space="preserve">9.90335178375244</t>
   </si>
   <si>
     <t xml:space="preserve">10.1604738235474</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">10.1729154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2102403640747</t>
+    <t xml:space="preserve">10.2102394104004</t>
   </si>
   <si>
     <t xml:space="preserve">10.0775318145752</t>
@@ -2981,31 +2981,31 @@
     <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1065616607666</t>
+    <t xml:space="preserve">10.1065626144409</t>
   </si>
   <si>
     <t xml:space="preserve">9.96141147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59646415710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53425598144531</t>
+    <t xml:space="preserve">9.59646320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53425693511963</t>
   </si>
   <si>
     <t xml:space="preserve">9.67111206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74575996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970558166504</t>
+    <t xml:space="preserve">9.74576091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970653533936</t>
   </si>
   <si>
     <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3844203948975</t>
+    <t xml:space="preserve">10.3844194412231</t>
   </si>
   <si>
     <t xml:space="preserve">10.347095489502</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">9.94482231140137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272974014282</t>
+    <t xml:space="preserve">10.1272964477539</t>
   </si>
   <si>
     <t xml:space="preserve">10.2682991027832</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">10.5088329315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4134492874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5212755203247</t>
+    <t xml:space="preserve">10.4134502410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5212745666504</t>
   </si>
   <si>
     <t xml:space="preserve">10.8074264526367</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8157215118408</t>
+    <t xml:space="preserve">10.8157205581665</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733114242554</t>
@@ -3056,46 +3056,46 @@
     <t xml:space="preserve">10.8986644744873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8364553451538</t>
+    <t xml:space="preserve">10.8364562988281</t>
   </si>
   <si>
     <t xml:space="preserve">10.9857530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8737802505493</t>
+    <t xml:space="preserve">10.8737812042236</t>
   </si>
   <si>
     <t xml:space="preserve">10.8447513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9774589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1018733978271</t>
+    <t xml:space="preserve">10.9774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1018743515015</t>
   </si>
   <si>
     <t xml:space="preserve">11.1143140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3548488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1474905014038</t>
+    <t xml:space="preserve">11.35484790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1474924087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3921718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2843456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6119699478149</t>
+    <t xml:space="preserve">11.3921728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2843465805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6119689941406</t>
   </si>
   <si>
     <t xml:space="preserve">11.5207328796387</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">11.4792623519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3507013320923</t>
+    <t xml:space="preserve">11.350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">11.1889629364014</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">11.1682271957397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1226081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0355186462402</t>
+    <t xml:space="preserve">11.1226091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0355176925659</t>
   </si>
   <si>
     <t xml:space="preserve">10.9442825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7452201843262</t>
+    <t xml:space="preserve">10.7452192306519</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">12.1096258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3999261856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1303625106812</t>
+    <t xml:space="preserve">12.3999252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1303615570068</t>
   </si>
   <si>
     <t xml:space="preserve">12.4455442428589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.263069152832</t>
+    <t xml:space="preserve">12.2630701065063</t>
   </si>
   <si>
     <t xml:space="preserve">12.4953088760376</t>
@@ -3158,25 +3158,25 @@
     <t xml:space="preserve">12.4870157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584537506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1718330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3169832229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1842737197876</t>
+    <t xml:space="preserve">12.358452796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1718339920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3169822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1842746734619</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3377170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1925687789917</t>
+    <t xml:space="preserve">12.3377180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.192569732666</t>
   </si>
   <si>
     <t xml:space="preserve">12.0847425460815</t>
@@ -3188,31 +3188,31 @@
     <t xml:space="preserve">12.0640077590942</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0349779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230060577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9810638427734</t>
+    <t xml:space="preserve">12.0349788665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9230051040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9810647964478</t>
   </si>
   <si>
     <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2174510955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3543062210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1759805679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9727716445923</t>
+    <t xml:space="preserve">12.1635389328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2174520492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3543071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1759815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
     <t xml:space="preserve">11.97691822052</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">11.6244125366211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5580577850342</t>
+    <t xml:space="preserve">11.5580587387085</t>
   </si>
   <si>
     <t xml:space="preserve">11.5539102554321</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">11.5912351608276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5995292663574</t>
+    <t xml:space="preserve">11.5995283126831</t>
   </si>
   <si>
     <t xml:space="preserve">11.5870876312256</t>
@@ -3263,16 +3263,16 @@
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985916137695</t>
+    <t xml:space="preserve">11.7985906600952</t>
   </si>
   <si>
     <t xml:space="preserve">11.8981237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9520349502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5456161499023</t>
+    <t xml:space="preserve">11.9520359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.545615196228</t>
   </si>
   <si>
     <t xml:space="preserve">11.5331745147705</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">11.877387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142421722412</t>
+    <t xml:space="preserve">12.0142412185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6949129104614</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">11.8732395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6617374420166</t>
+    <t xml:space="preserve">11.6617364883423</t>
   </si>
   <si>
     <t xml:space="preserve">11.7322378158569</t>
@@ -3323,25 +3323,25 @@
     <t xml:space="preserve">11.7654142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.164080619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2055521011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4129076004028</t>
+    <t xml:space="preserve">11.5787925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1640815734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2055511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.305082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">11.4336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3299655914307</t>
+    <t xml:space="preserve">11.3299646377563</t>
   </si>
   <si>
     <t xml:space="preserve">11.3631420135498</t>
@@ -3350,25 +3350,25 @@
     <t xml:space="preserve">11.3382596969604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3880252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3714380264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4917020797729</t>
+    <t xml:space="preserve">11.3880243301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4917030334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.5124397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5622043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.524881362915</t>
+    <t xml:space="preserve">11.6451482772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5622034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248804092407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5953807830811</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">11.9312992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8607997894287</t>
+    <t xml:space="preserve">11.8607988357544</t>
   </si>
   <si>
     <t xml:space="preserve">11.6410007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068857192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0266828536987</t>
+    <t xml:space="preserve">11.806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.026683807373</t>
   </si>
   <si>
     <t xml:space="preserve">12.1013317108154</t>
@@ -3416,34 +3416,34 @@
     <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391263961792</t>
+    <t xml:space="preserve">12.0391254425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690929412842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220674514771</t>
+    <t xml:space="preserve">11.7778549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220664978027</t>
   </si>
   <si>
     <t xml:space="preserve">12.2215986251831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.333571434021</t>
+    <t xml:space="preserve">12.3335704803467</t>
   </si>
   <si>
     <t xml:space="preserve">12.7151069641113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5367813110352</t>
+    <t xml:space="preserve">12.5367803573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7773132324219</t>
+    <t xml:space="preserve">12.7773151397705</t>
   </si>
   <si>
     <t xml:space="preserve">12.8975811004639</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">13.453296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5942983627319</t>
+    <t xml:space="preserve">13.5942993164062</t>
   </si>
   <si>
     <t xml:space="preserve">13.4698848724365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201211929321</t>
+    <t xml:space="preserve">13.4201202392578</t>
   </si>
   <si>
     <t xml:space="preserve">13.3496179580688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2252044677734</t>
+    <t xml:space="preserve">13.2252054214478</t>
   </si>
   <si>
     <t xml:space="preserve">13.4781799316406</t>
@@ -3485,16 +3485,16 @@
     <t xml:space="preserve">13.1588487625122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1837348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625293731689</t>
+    <t xml:space="preserve">13.1837339401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625303268433</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514942169189</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">12.8644037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8685522079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607250213623</t>
+    <t xml:space="preserve">12.8685512542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607269287109</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939033508301</t>
@@ -3515,22 +3515,22 @@
     <t xml:space="preserve">12.9349060058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7482833862305</t>
+    <t xml:space="preserve">12.8312273025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7482843399048</t>
   </si>
   <si>
     <t xml:space="preserve">12.574104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6611948013306</t>
+    <t xml:space="preserve">12.6611957550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.9763765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.237645149231</t>
+    <t xml:space="preserve">13.2376461029053</t>
   </si>
   <si>
     <t xml:space="preserve">13.1215257644653</t>
@@ -3545,16 +3545,16 @@
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9431982040405</t>
+    <t xml:space="preserve">12.9431991577148</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9971122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7690200805664</t>
+    <t xml:space="preserve">12.9971132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7690210342407</t>
   </si>
   <si>
     <t xml:space="preserve">12.6446056365967</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">12.9722309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9888181686401</t>
+    <t xml:space="preserve">12.9888191223145</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302896499634</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">12.9929647445679</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2044687271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1173791885376</t>
+    <t xml:space="preserve">13.2044696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1173782348633</t>
   </si>
   <si>
     <t xml:space="preserve">13.602593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850694656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8016548156738</t>
+    <t xml:space="preserve">13.7850685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523580551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8016557693481</t>
   </si>
   <si>
     <t xml:space="preserve">13.7726259231567</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">13.7975091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9219236373901</t>
+    <t xml:space="preserve">13.9219226837158</t>
   </si>
   <si>
     <t xml:space="preserve">13.9799823760986</t>
@@ -3611,19 +3611,19 @@
     <t xml:space="preserve">13.7270069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.69797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0048656463623</t>
+    <t xml:space="preserve">13.6979780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0048666000366</t>
   </si>
   <si>
     <t xml:space="preserve">13.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878076553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173063278198</t>
+    <t xml:space="preserve">14.0878086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173072814941</t>
   </si>
   <si>
     <t xml:space="preserve">14.224663734436</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">14.3324899673462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0712184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583099365234</t>
+    <t xml:space="preserve">14.0712203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583089828491</t>
   </si>
   <si>
     <t xml:space="preserve">14.2951650619507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3532257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2619876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3076057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163677215576</t>
+    <t xml:space="preserve">14.3532247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2619867324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3076066970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163686752319</t>
   </si>
   <si>
     <t xml:space="preserve">14.12513256073</t>
@@ -3668,43 +3668,43 @@
     <t xml:space="preserve">13.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819051742554</t>
+    <t xml:space="preserve">13.2819042205811</t>
   </si>
   <si>
     <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605028152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.435996055603</t>
+    <t xml:space="preserve">13.2605018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4359970092773</t>
   </si>
   <si>
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5515670776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9068365097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6457347869873</t>
+    <t xml:space="preserve">13.1834554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5515661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.906834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6457328796387</t>
   </si>
   <si>
     <t xml:space="preserve">13.4488382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4188766479492</t>
+    <t xml:space="preserve">13.4188756942749</t>
   </si>
   <si>
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445581436157</t>
+    <t xml:space="preserve">13.4445571899414</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258846282959</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">12.9523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9095144271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2433824539185</t>
+    <t xml:space="preserve">12.9095153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2433815002441</t>
   </si>
   <si>
     <t xml:space="preserve">13.2519416809082</t>
@@ -3737,25 +3737,25 @@
     <t xml:space="preserve">13.4531183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4873609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6842575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3589496612549</t>
+    <t xml:space="preserve">13.487361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6842565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3589506149292</t>
   </si>
   <si>
     <t xml:space="preserve">13.0122423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8511915206909</t>
+    <t xml:space="preserve">13.7741441726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8511905670166</t>
   </si>
   <si>
     <t xml:space="preserve">13.5301647186279</t>
@@ -3767,19 +3767,19 @@
     <t xml:space="preserve">13.2861862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0293645858765</t>
+    <t xml:space="preserve">13.0293655395508</t>
   </si>
   <si>
     <t xml:space="preserve">13.1920175552368</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1320924758911</t>
+    <t xml:space="preserve">13.1320934295654</t>
   </si>
   <si>
     <t xml:space="preserve">12.7597026824951</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3616304397583</t>
+    <t xml:space="preserve">12.3616313934326</t>
   </si>
   <si>
     <t xml:space="preserve">12.5499658584595</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740961074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8538703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.900954246521</t>
+    <t xml:space="preserve">12.6740970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.85387134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009532928467</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254600524902</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">12.7682638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.849591255188</t>
+    <t xml:space="preserve">12.8495903015137</t>
   </si>
   <si>
     <t xml:space="preserve">13.0550470352173</t>
@@ -3830,28 +3830,28 @@
     <t xml:space="preserve">13.4103155136108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.277624130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4301156997681</t>
+    <t xml:space="preserve">13.2776250839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4301166534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768239974976</t>
+    <t xml:space="preserve">12.7768249511719</t>
   </si>
   <si>
     <t xml:space="preserve">12.0234842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0363264083862</t>
+    <t xml:space="preserve">12.0363254547119</t>
   </si>
   <si>
     <t xml:space="preserve">11.8351488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576787948608</t>
+    <t xml:space="preserve">10.9576778411865</t>
   </si>
   <si>
     <t xml:space="preserve">10.8720712661743</t>
@@ -3869,19 +3869,19 @@
     <t xml:space="preserve">11.5954494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.826587677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950748443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9892416000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106420516968</t>
+    <t xml:space="preserve">11.8265886306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8950729370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157232284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9892406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0106430053711</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277652740479</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">11.9849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8479900360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9507188796997</t>
+    <t xml:space="preserve">11.8479909896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9507179260254</t>
   </si>
   <si>
     <t xml:space="preserve">12.3145475387573</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.310266494751</t>
+    <t xml:space="preserve">12.3102674484253</t>
   </si>
   <si>
     <t xml:space="preserve">12.2631826400757</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188285827637</t>
+    <t xml:space="preserve">12.1262130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188276290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203798294067</t>
@@ -3935,19 +3935,19 @@
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0705671310425</t>
+    <t xml:space="preserve">12.0834093093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0705680847168</t>
   </si>
   <si>
     <t xml:space="preserve">11.8651113510132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4798803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2444610595703</t>
+    <t xml:space="preserve">11.4798812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2444620132446</t>
   </si>
   <si>
     <t xml:space="preserve">11.2530221939087</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">11.0775270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0903692245483</t>
+    <t xml:space="preserve">11.090368270874</t>
   </si>
   <si>
     <t xml:space="preserve">10.5724487304688</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4868412017822</t>
+    <t xml:space="preserve">10.4868402481079</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771043777466</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">10.6109714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8292684555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035850524902</t>
+    <t xml:space="preserve">10.8292675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035860061646</t>
   </si>
   <si>
     <t xml:space="preserve">10.7693433761597</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">11.1668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1403942108154</t>
+    <t xml:space="preserve">11.1403951644897</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158643722534</t>
+    <t xml:space="preserve">11.5158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368255615234</t>
+    <t xml:space="preserve">10.6368246078491</t>
   </si>
   <si>
     <t xml:space="preserve">9.62968254089355</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.13053035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74453258514404</t>
+    <t xml:space="preserve">9.74453163146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">10.1818447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4645500183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191558837891</t>
+    <t xml:space="preserve">10.4645509719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191568374634</t>
   </si>
   <si>
     <t xml:space="preserve">10.4689674377441</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">10.2171812057495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7384223937988</t>
+    <t xml:space="preserve">10.7384214401245</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3585357666016</t>
+    <t xml:space="preserve">10.3585367202759</t>
   </si>
   <si>
     <t xml:space="preserve">9.83287906646729</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758295059204</t>
+    <t xml:space="preserve">10.0758285522461</t>
   </si>
   <si>
     <t xml:space="preserve">10.0007352828979</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">10.999041557312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8841924667358</t>
+    <t xml:space="preserve">10.8841915130615</t>
   </si>
   <si>
     <t xml:space="preserve">10.8267679214478</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">10.5573139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9062795639038</t>
+    <t xml:space="preserve">10.9062786102295</t>
   </si>
   <si>
     <t xml:space="preserve">10.959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902076721191</t>
+    <t xml:space="preserve">10.9902067184448</t>
   </si>
   <si>
     <t xml:space="preserve">10.7781772613525</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">10.6544942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.146505355835</t>
+    <t xml:space="preserve">10.1465063095093</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
@@ -4181,10 +4181,10 @@
     <t xml:space="preserve">10.0051527023315</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93447589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4529914855957</t>
+    <t xml:space="preserve">9.93447685241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45299053192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.58109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59876251220703</t>
+    <t xml:space="preserve">9.59876155853271</t>
   </si>
   <si>
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797740936279</t>
+    <t xml:space="preserve">10.8797750473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.919529914856</t>
@@ -4238,10 +4238,10 @@
     <t xml:space="preserve">10.8046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215045928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9371995925903</t>
+    <t xml:space="preserve">11.3215036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9372005462646</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259210586548</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1889848709106</t>
+    <t xml:space="preserve">11.188985824585</t>
   </si>
   <si>
     <t xml:space="preserve">11.8471603393555</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">10.9239473342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2464094161987</t>
+    <t xml:space="preserve">11.246410369873</t>
   </si>
   <si>
     <t xml:space="preserve">11.2331581115723</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">12.1961269378662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3949031829834</t>
+    <t xml:space="preserve">12.3949041366577</t>
   </si>
   <si>
     <t xml:space="preserve">12.1607885360718</t>
@@ -4325,16 +4325,16 @@
     <t xml:space="preserve">12.6246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908626556396</t>
+    <t xml:space="preserve">12.6908617019653</t>
   </si>
   <si>
     <t xml:space="preserve">12.7527046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8277978897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9205617904663</t>
+    <t xml:space="preserve">12.8277988433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.920560836792</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514827728271</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">13.0354108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2518587112427</t>
+    <t xml:space="preserve">13.2518577575684</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2827787399292</t>
+    <t xml:space="preserve">13.2827796936035</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
@@ -4370,19 +4370,19 @@
     <t xml:space="preserve">13.6405782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6494131088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9144515991211</t>
+    <t xml:space="preserve">13.6494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9144506454468</t>
   </si>
   <si>
     <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5522327423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6008234024048</t>
+    <t xml:space="preserve">13.5522336959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6008243560791</t>
   </si>
   <si>
     <t xml:space="preserve">13.7465934753418</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188680648804</t>
+    <t xml:space="preserve">13.9188690185547</t>
   </si>
   <si>
     <t xml:space="preserve">13.1414251327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3534555435181</t>
+    <t xml:space="preserve">13.3534545898438</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">13.5345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5831546783447</t>
+    <t xml:space="preserve">13.5831537246704</t>
   </si>
   <si>
     <t xml:space="preserve">13.834939956665</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">14.1883230209351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5947122573853</t>
+    <t xml:space="preserve">14.5947132110596</t>
   </si>
   <si>
     <t xml:space="preserve">14.4710273742676</t>
@@ -4439,19 +4439,19 @@
     <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8685846328735</t>
+    <t xml:space="preserve">14.8685836791992</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7669878005981</t>
+    <t xml:space="preserve">14.7669868469238</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095623016357</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7934904098511</t>
+    <t xml:space="preserve">14.7934913635254</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">14.5814609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9790172576904</t>
+    <t xml:space="preserve">14.9790163040161</t>
   </si>
   <si>
     <t xml:space="preserve">14.9392614364624</t>
@@ -4499,13 +4499,13 @@
     <t xml:space="preserve">14.8553333282471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.009937286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6609725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6918916702271</t>
+    <t xml:space="preserve">15.0099382400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6609716415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6918926239014</t>
   </si>
   <si>
     <t xml:space="preserve">14.568208694458</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">14.9701814651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7714042663574</t>
+    <t xml:space="preserve">14.7714033126831</t>
   </si>
   <si>
     <t xml:space="preserve">14.6433038711548</t>
@@ -4559,10 +4559,10 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4523286819458</t>
+    <t xml:space="preserve">12.2402992248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4523296356201</t>
   </si>
   <si>
     <t xml:space="preserve">11.502613067627</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5009183883667</t>
+    <t xml:space="preserve">12.500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">12.5141706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0795831680298</t>
+    <t xml:space="preserve">13.0795841217041</t>
   </si>
   <si>
     <t xml:space="preserve">12.5848474502563</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">12.5406742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7588157653809</t>
+    <t xml:space="preserve">12.1298666000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7588148117065</t>
   </si>
   <si>
     <t xml:space="preserve">12.1121988296509</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343799591064</t>
+    <t xml:space="preserve">11.0343809127808</t>
   </si>
   <si>
     <t xml:space="preserve">11.2199058532715</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.0653009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949991226196</t>
+    <t xml:space="preserve">11.2950000762939</t>
   </si>
   <si>
     <t xml:space="preserve">11.0873880386353</t>
@@ -6288,6 +6288,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.2150001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2199993133545</t>
   </si>
 </sst>
 </file>
@@ -71522,7 +71525,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.651099537</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>1167485</v>
@@ -71543,6 +71546,32 @@
         <v>2091</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912731481</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>1146338</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>19.2900009155273</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>19.1200008392334</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>19.2150001525879</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>19.2199993133545</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,28 +44,28 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048845291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13951873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26257848739624</t>
+    <t xml:space="preserve">5.32048892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951969146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26257801055908</t>
   </si>
   <si>
     <t xml:space="preserve">5.1322808265686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.266197681427</t>
+    <t xml:space="preserve">5.26619863510132</t>
   </si>
   <si>
     <t xml:space="preserve">5.31325006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19381093978882</t>
+    <t xml:space="preserve">5.19381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">5.04541540145874</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">5.07437086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101345062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96578931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05265474319458</t>
+    <t xml:space="preserve">4.65814161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101392745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96578884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.21190738677979</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">5.14675855636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16485452651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12504196166992</t>
+    <t xml:space="preserve">5.16485548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12504148483276</t>
   </si>
   <si>
     <t xml:space="preserve">4.88978242874146</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">4.74138784408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56765747070312</t>
+    <t xml:space="preserve">4.56765699386597</t>
   </si>
   <si>
     <t xml:space="preserve">4.34325551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545721054077</t>
+    <t xml:space="preserve">4.45545625686646</t>
   </si>
   <si>
     <t xml:space="preserve">4.48441171646118</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">4.58213520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78482055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73414945602417</t>
+    <t xml:space="preserve">4.78482103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73414897918701</t>
   </si>
   <si>
     <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7667236328125</t>
+    <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
     <t xml:space="preserve">4.71243238449097</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84996938705444</t>
+    <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
     <t xml:space="preserve">4.88616275787354</t>
@@ -155,115 +155,115 @@
     <t xml:space="preserve">5.00922203063965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09246730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332584381104</t>
+    <t xml:space="preserve">5.09246778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332536697388</t>
   </si>
   <si>
     <t xml:space="preserve">5.16847467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95493125915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8427300453186</t>
+    <t xml:space="preserve">4.95493078231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84273099899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.78120088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06713151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08884811401367</t>
+    <t xml:space="preserve">5.06713199615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08884859085083</t>
   </si>
   <si>
     <t xml:space="preserve">5.00560283660889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99112462997437</t>
+    <t xml:space="preserve">4.99112415313721</t>
   </si>
   <si>
     <t xml:space="preserve">5.19019079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362302780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35668277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12866115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02008008956909</t>
+    <t xml:space="preserve">5.23362350463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35668230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12866163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02007961273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.98026752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94769334793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97302865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787982940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369976043701</t>
+    <t xml:space="preserve">4.94769239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97302770614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369928359985</t>
   </si>
   <si>
     <t xml:space="preserve">5.11418390274048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.121422290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28287553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27161121368408</t>
+    <t xml:space="preserve">5.12142276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544111251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406362533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28287506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27161073684692</t>
   </si>
   <si>
     <t xml:space="preserve">5.23030853271484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16647958755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3316855430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.391761302948</t>
+    <t xml:space="preserve">5.16647911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33168649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39176177978516</t>
   </si>
   <si>
     <t xml:space="preserve">5.26410150527954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25659227371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05759239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09889459609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96747970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88863039016724</t>
+    <t xml:space="preserve">5.25659275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05759286880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09889507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96747922897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">4.78725385665894</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472520828247</t>
+    <t xml:space="preserve">4.76472473144531</t>
   </si>
   <si>
     <t xml:space="preserve">4.70089530944824</t>
@@ -281,106 +281,106 @@
     <t xml:space="preserve">4.96372509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90364980697632</t>
+    <t xml:space="preserve">4.90364933013916</t>
   </si>
   <si>
     <t xml:space="preserve">4.90740394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77598905563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73844194412231</t>
+    <t xml:space="preserve">4.7759895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91866827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.986252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97874307632446</t>
+    <t xml:space="preserve">4.91866779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98625373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97874402999878</t>
   </si>
   <si>
     <t xml:space="preserve">5.01629018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92617797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95246028900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9712347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87736654281616</t>
+    <t xml:space="preserve">4.92617750167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95246076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97123432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8548378944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.877366065979</t>
   </si>
   <si>
     <t xml:space="preserve">4.8022723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44182109832764</t>
+    <t xml:space="preserve">4.62204647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197118759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44182062149048</t>
   </si>
   <si>
     <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45683908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56948041915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7534613609314</t>
+    <t xml:space="preserve">4.4568395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56948089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346183776855</t>
   </si>
   <si>
     <t xml:space="preserve">4.73093318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97498941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1301794052124</t>
+    <t xml:space="preserve">4.80602645874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97498893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13017988204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.39676380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33668899536133</t>
+    <t xml:space="preserve">4.33668851852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.39300870895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17523574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10014152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87485909461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244384765625</t>
+    <t xml:space="preserve">4.17523622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10014200210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87485933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244408607483</t>
   </si>
   <si>
     <t xml:space="preserve">4.26534938812256</t>
@@ -395,46 +395,46 @@
     <t xml:space="preserve">4.20151901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23531150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31040477752686</t>
+    <t xml:space="preserve">4.23531103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31040525436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.25032997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24657583236694</t>
+    <t xml:space="preserve">4.24657535552979</t>
   </si>
   <si>
     <t xml:space="preserve">4.27661323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09638690948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93118023872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750066757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83731245994568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93868899345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93493437767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97248220443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746278762817</t>
+    <t xml:space="preserve">4.09638738632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93118047714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9875009059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8373122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93868923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623586654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93493413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97248244285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746302604675</t>
   </si>
   <si>
     <t xml:space="preserve">3.9461989402771</t>
@@ -443,91 +443,91 @@
     <t xml:space="preserve">3.99876427650452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82980251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604742050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133104324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07010364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04382133483887</t>
+    <t xml:space="preserve">3.82980275154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604837417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348208427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470852851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07010459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04382181167603</t>
   </si>
   <si>
     <t xml:space="preserve">4.01378393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05883979797363</t>
+    <t xml:space="preserve">4.05884027481079</t>
   </si>
   <si>
     <t xml:space="preserve">4.09263229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13768863677979</t>
+    <t xml:space="preserve">4.13768911361694</t>
   </si>
   <si>
     <t xml:space="preserve">4.12267017364502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0550856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255605697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124059677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229351997375</t>
+    <t xml:space="preserve">4.05508518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385969161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255701065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91240644454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229375839233</t>
   </si>
   <si>
     <t xml:space="preserve">3.81478357315063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90489745140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114235877991</t>
+    <t xml:space="preserve">3.90489673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114283561707</t>
   </si>
   <si>
     <t xml:space="preserve">3.88987827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81102895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88612365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738726615906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236856460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233116149902</t>
+    <t xml:space="preserve">3.81102919578552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88612389564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738750457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8523313999176</t>
   </si>
   <si>
     <t xml:space="preserve">3.78850102424622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7622184753418</t>
+    <t xml:space="preserve">3.76221871376038</t>
   </si>
   <si>
     <t xml:space="preserve">3.61203002929688</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">3.59550881385803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79601049423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9612181186676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999143600464</t>
+    <t xml:space="preserve">3.79601073265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96121788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999119758606</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504777908325</t>
@@ -551,94 +551,94 @@
     <t xml:space="preserve">3.96497225761414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01753807067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08887815475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14519834518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99501013755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742514610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355784416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474593162537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225587844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170493125916</t>
+    <t xml:space="preserve">4.01753854751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08887767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14519786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99501037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742538452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727458000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225611686707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170516967773</t>
   </si>
   <si>
     <t xml:space="preserve">3.73518419265747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64056539535522</t>
+    <t xml:space="preserve">3.64056515693665</t>
   </si>
   <si>
     <t xml:space="preserve">3.60452055931091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54444479942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843712806702</t>
+    <t xml:space="preserve">3.54444527626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843784332275</t>
   </si>
   <si>
     <t xml:space="preserve">3.5414412021637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5564603805542</t>
+    <t xml:space="preserve">3.55645990371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.60001492500305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47085332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799982070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66459536552429</t>
+    <t xml:space="preserve">3.47085285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799958229065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66459608078003</t>
   </si>
   <si>
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748651504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857654571533</t>
+    <t xml:space="preserve">3.66910123825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748627662659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73968958854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857606887817</t>
   </si>
   <si>
     <t xml:space="preserve">4.14144325256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10389614105225</t>
+    <t xml:space="preserve">4.1038966178894</t>
   </si>
   <si>
     <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006671905518</t>
+    <t xml:space="preserve">4.04006719589233</t>
   </si>
   <si>
     <t xml:space="preserve">4.11516046524048</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">4.00251960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07761383056641</t>
+    <t xml:space="preserve">4.07761335372925</t>
   </si>
   <si>
     <t xml:space="preserve">4.16772651672363</t>
@@ -659,43 +659,43 @@
     <t xml:space="preserve">4.14895296096802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512401580811</t>
+    <t xml:space="preserve">4.08512306213379</t>
   </si>
   <si>
     <t xml:space="preserve">4.18274545669556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22029209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23906564712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16021728515625</t>
+    <t xml:space="preserve">4.22029256820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2390661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16021680831909</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06259393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03631162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13393449783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28787708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810388565063</t>
+    <t xml:space="preserve">4.06259489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03631114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13393402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28787755966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30289554595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810293197632</t>
   </si>
   <si>
     <t xml:space="preserve">4.44557523727417</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">4.63706493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69338607788086</t>
+    <t xml:space="preserve">4.6933856010437</t>
   </si>
   <si>
     <t xml:space="preserve">4.72342348098755</t>
@@ -716,49 +716,49 @@
     <t xml:space="preserve">4.8097825050354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83981990814209</t>
+    <t xml:space="preserve">4.83981943130493</t>
   </si>
   <si>
     <t xml:space="preserve">4.81353664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79851818084717</t>
+    <t xml:space="preserve">4.79851722717285</t>
   </si>
   <si>
     <t xml:space="preserve">4.7271785736084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85108327865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82104539871216</t>
+    <t xml:space="preserve">4.85108375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82104587554932</t>
   </si>
   <si>
     <t xml:space="preserve">4.83606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07056093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198211669922</t>
+    <t xml:space="preserve">5.07056140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198163986206</t>
   </si>
   <si>
     <t xml:space="preserve">5.0744891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12947511672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16875171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33371210098267</t>
+    <t xml:space="preserve">5.12947607040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16875219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552131652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">5.3415675163269</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">5.28265285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20017337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092239379883</t>
+    <t xml:space="preserve">5.20017290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373819351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092334747314</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
@@ -794,40 +794,40 @@
     <t xml:space="preserve">5.36906099319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34942245483398</t>
+    <t xml:space="preserve">5.34942197799683</t>
   </si>
   <si>
     <t xml:space="preserve">5.38477087020874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21588230133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.219810962677</t>
+    <t xml:space="preserve">5.21588325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21981048583984</t>
   </si>
   <si>
     <t xml:space="preserve">5.25515937805176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32978391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32585668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37298774719238</t>
+    <t xml:space="preserve">5.32978439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32585716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25123167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
     <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61650133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57722473144531</t>
+    <t xml:space="preserve">5.61650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57722520828247</t>
   </si>
   <si>
     <t xml:space="preserve">5.5418758392334</t>
@@ -839,52 +839,52 @@
     <t xml:space="preserve">5.62435626983643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065279006958</t>
+    <t xml:space="preserve">5.50652742385864</t>
   </si>
   <si>
     <t xml:space="preserve">5.53794813156128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62042856216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5536584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50260019302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41226482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52223777770996</t>
+    <t xml:space="preserve">5.62042808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55365896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50259971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41226387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52223825454712</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257314682007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69112539291382</t>
+    <t xml:space="preserve">5.69112586975098</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076345443726</t>
+    <t xml:space="preserve">5.87572431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076440811157</t>
   </si>
   <si>
     <t xml:space="preserve">5.73432970046997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64006662368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65970420837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72647428512573</t>
+    <t xml:space="preserve">5.64006614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65970468521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72647380828857</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
@@ -893,61 +893,61 @@
     <t xml:space="preserve">5.67148733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65577745437622</t>
+    <t xml:space="preserve">5.65577697753906</t>
   </si>
   <si>
     <t xml:space="preserve">5.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77360582351685</t>
+    <t xml:space="preserve">5.77360534667969</t>
   </si>
   <si>
     <t xml:space="preserve">5.86786842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83644723892212</t>
+    <t xml:space="preserve">5.83644771575928</t>
   </si>
   <si>
     <t xml:space="preserve">5.82466506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8403754234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82859230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179708480835</t>
+    <t xml:space="preserve">5.84037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8285927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179613113403</t>
   </si>
   <si>
     <t xml:space="preserve">5.93463802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95034885406494</t>
+    <t xml:space="preserve">5.95034837722778</t>
   </si>
   <si>
     <t xml:space="preserve">5.90714454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7971715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70290946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78931617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89143466949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7853889465332</t>
+    <t xml:space="preserve">5.79717111587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70290899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78931570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89143419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324388504028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70683526992798</t>
+    <t xml:space="preserve">5.70683622360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">5.56936979293823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46725082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293460845947</t>
+    <t xml:space="preserve">5.46725177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293556213379</t>
   </si>
   <si>
     <t xml:space="preserve">5.66755962371826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47903394699097</t>
+    <t xml:space="preserve">5.47903347015381</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">5.45939588546753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75004005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75396776199341</t>
+    <t xml:space="preserve">5.75003957748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76182270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75396728515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80895471572876</t>
+    <t xml:space="preserve">5.8089542388916</t>
   </si>
   <si>
     <t xml:space="preserve">5.91499996185303</t>
@@ -1001,19 +1001,19 @@
     <t xml:space="preserve">5.87965154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8521580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84430265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84823036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254610061646</t>
+    <t xml:space="preserve">5.85215759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001348495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84823131561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254705429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.69505310058594</t>
@@ -1022,133 +1022,133 @@
     <t xml:space="preserve">5.6636323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64792203903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71861886978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83252000808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76575088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11530923843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08388710021973</t>
+    <t xml:space="preserve">5.64792156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71861934661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83252048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76575040817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11530876159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
     <t xml:space="preserve">6.26063060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24492073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31169033050537</t>
+    <t xml:space="preserve">6.24492025375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31168985366821</t>
   </si>
   <si>
     <t xml:space="preserve">6.30776214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29990768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29205226898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670337677002</t>
+    <t xml:space="preserve">6.29990720748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29205274581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670385360718</t>
   </si>
   <si>
     <t xml:space="preserve">6.23706531524658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25277614593506</t>
+    <t xml:space="preserve">6.2527756690979</t>
   </si>
   <si>
     <t xml:space="preserve">6.26455879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20171689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23313760757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032276153564</t>
+    <t xml:space="preserve">6.20171642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2331371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032180786133</t>
   </si>
   <si>
     <t xml:space="preserve">6.00926351547241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1270923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22528266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28026914596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37060451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3745322227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33132839202881</t>
+    <t xml:space="preserve">6.12709188461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22528314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28026866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37060403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37453126907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33132886886597</t>
   </si>
   <si>
     <t xml:space="preserve">6.39809799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45308494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5866231918335</t>
+    <t xml:space="preserve">6.45308446884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58662366867065</t>
   </si>
   <si>
     <t xml:space="preserve">6.65339326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5394926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60626125335693</t>
+    <t xml:space="preserve">6.53949213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
     <t xml:space="preserve">6.63768339157104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5630578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8301362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68874168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79086065292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409009933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77907705307007</t>
+    <t xml:space="preserve">6.56305837631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83013582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68874216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79086017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088722229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77907752990723</t>
   </si>
   <si>
     <t xml:space="preserve">6.75551176071167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76336574554443</t>
+    <t xml:space="preserve">6.76336622238159</t>
   </si>
   <si>
     <t xml:space="preserve">6.85762977600098</t>
@@ -1160,148 +1160,148 @@
     <t xml:space="preserve">6.81049823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70445203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375425338745</t>
+    <t xml:space="preserve">6.70445251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375473022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.64553785324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91261768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9990234375</t>
+    <t xml:space="preserve">6.91261672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99902391433716</t>
   </si>
   <si>
     <t xml:space="preserve">6.99116897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33287191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4035701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58031177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5410361289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.552818775177</t>
+    <t xml:space="preserve">7.33287239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40356969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54103660583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55281972885132</t>
   </si>
   <si>
     <t xml:space="preserve">7.46641111373901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49783277511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66671991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8041877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75705480575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88666820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93379831314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91808748245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454923629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310148239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488317489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74056005477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50804328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53161001205444</t>
+    <t xml:space="preserve">7.49783229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351560592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66672086715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80418729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75705528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8866662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93379926681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91808700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87488412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74055862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886354446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50804376602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5316104888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.23782348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26610231399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410772323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59131002426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69656991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355051040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80025959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83325099945068</t>
+    <t xml:space="preserve">7.26610279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2441086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076271057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59130907058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69657039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025911331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83325290679932</t>
   </si>
   <si>
     <t xml:space="preserve">7.94950866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96914625167847</t>
+    <t xml:space="preserve">7.96914720535278</t>
   </si>
   <si>
     <t xml:space="preserve">7.52061367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8301100730896</t>
+    <t xml:space="preserve">7.83010911941528</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08304786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165372848511</t>
+    <t xml:space="preserve">8.08304882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165277481079</t>
   </si>
   <si>
     <t xml:space="preserve">7.95343685150146</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">8.04377174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11054134368896</t>
+    <t xml:space="preserve">8.11054229736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
@@ -1322,22 +1322,22 @@
     <t xml:space="preserve">7.86702871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83953523635864</t>
+    <t xml:space="preserve">7.83953619003296</t>
   </si>
   <si>
     <t xml:space="preserve">7.69499826431274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71070957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158201217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487483978271</t>
+    <t xml:space="preserve">7.71070861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487674713135</t>
   </si>
   <si>
     <t xml:space="preserve">7.65572357177734</t>
@@ -1346,31 +1346,31 @@
     <t xml:space="preserve">7.85524654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59445142745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602308273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56145906448364</t>
+    <t xml:space="preserve">7.59445285797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59602355957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5614595413208</t>
   </si>
   <si>
     <t xml:space="preserve">7.7531270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83168029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82696628570557</t>
+    <t xml:space="preserve">7.8316798210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82696676254272</t>
   </si>
   <si>
     <t xml:space="preserve">7.79554605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03898048400879</t>
+    <t xml:space="preserve">8.03897953033447</t>
   </si>
   <si>
     <t xml:space="preserve">8.08750534057617</t>
@@ -1379,37 +1379,37 @@
     <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942806243896</t>
+    <t xml:space="preserve">7.96942663192749</t>
   </si>
   <si>
     <t xml:space="preserve">7.97427940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00986480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14816188812256</t>
+    <t xml:space="preserve">8.00986576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9856014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14815998077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.21690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93222522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85943794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87884712219238</t>
+    <t xml:space="preserve">7.9322247505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85943746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">7.86752367019653</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">7.41947603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25125551223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626140594482</t>
+    <t xml:space="preserve">7.25125694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626188278198</t>
   </si>
   <si>
     <t xml:space="preserve">7.43079948425293</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">7.40491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42594766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568237304688</t>
+    <t xml:space="preserve">7.4259467124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568284988403</t>
   </si>
   <si>
     <t xml:space="preserve">6.59293413162231</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">6.43441867828369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84849977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805124282837</t>
+    <t xml:space="preserve">6.8484992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805171966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.10729885101318</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">6.92613935470581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2221417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20111417770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1477370262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26419639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681222915649</t>
+    <t xml:space="preserve">6.8177661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22214221954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20111465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14773750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2641978263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681175231934</t>
   </si>
   <si>
     <t xml:space="preserve">7.58607959747314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415687561035</t>
+    <t xml:space="preserve">7.70415782928467</t>
   </si>
   <si>
     <t xml:space="preserve">7.66857290267944</t>
@@ -1487,91 +1487,91 @@
     <t xml:space="preserve">7.63783979415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78179597854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70739078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282497406006</t>
+    <t xml:space="preserve">7.78179693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70739126205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">7.62975263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69445133209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768810272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223415374756</t>
+    <t xml:space="preserve">7.6944522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768667221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8222336769104</t>
   </si>
   <si>
     <t xml:space="preserve">7.83032178878784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95163440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05353832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001697540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06809520721436</t>
+    <t xml:space="preserve">7.9516339302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05353736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001840591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
     <t xml:space="preserve">8.19264221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329875946045</t>
+    <t xml:space="preserve">8.25329780578613</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969287872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2977819442749</t>
+    <t xml:space="preserve">8.29778003692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.31395435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27756118774414</t>
+    <t xml:space="preserve">8.27756023406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.233078956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21286010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28564739227295</t>
+    <t xml:space="preserve">8.23307991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21286106109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28564929962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.24925422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794303894043</t>
+    <t xml:space="preserve">8.12794208526611</t>
   </si>
   <si>
     <t xml:space="preserve">8.24521064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13198661804199</t>
+    <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
     <t xml:space="preserve">8.06647682189941</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">8.07941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1400728225708</t>
+    <t xml:space="preserve">8.14007186889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.08588695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12389850616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20881652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22499179840088</t>
+    <t xml:space="preserve">8.12389945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20881748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2249927520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.30991172790527</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.1885986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33417510986328</t>
+    <t xml:space="preserve">8.33417415618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.30182456970215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3179988861084</t>
+    <t xml:space="preserve">8.31799793243408</t>
   </si>
   <si>
     <t xml:space="preserve">8.60510635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77898597717285</t>
+    <t xml:space="preserve">8.77898502349854</t>
   </si>
   <si>
     <t xml:space="preserve">8.77089881896973</t>
@@ -1628,49 +1628,49 @@
     <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95691108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03778743743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04183101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11866188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22379875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32084941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784233093262</t>
+    <t xml:space="preserve">8.95691204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03778648376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04183006286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32084846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22784423828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.4178991317749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44620513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61604404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3127613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39768123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30063056945801</t>
+    <t xml:space="preserve">9.44620609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61604309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48260021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31276035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39768028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30062961578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.28041172027588</t>
@@ -1679,55 +1679,55 @@
     <t xml:space="preserve">9.1954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11461925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67789173126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65362930297852</t>
+    <t xml:space="preserve">9.1146183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67789363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65363121032715</t>
   </si>
   <si>
     <t xml:space="preserve">8.05191993713379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89987325668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1198558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83355760574341</t>
+    <t xml:space="preserve">7.89987468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11985492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83355712890625</t>
   </si>
   <si>
     <t xml:space="preserve">7.4680027961731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25287485122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24155187606812</t>
+    <t xml:space="preserve">7.25287389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24155235290527</t>
   </si>
   <si>
     <t xml:space="preserve">7.1606764793396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05715656280518</t>
+    <t xml:space="preserve">7.05715703964233</t>
   </si>
   <si>
     <t xml:space="preserve">7.32080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09597730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595659255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860158920288</t>
+    <t xml:space="preserve">7.09597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860206604004</t>
   </si>
   <si>
     <t xml:space="preserve">7.47770690917969</t>
@@ -1736,31 +1736,31 @@
     <t xml:space="preserve">7.59093189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92251873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106525421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503131866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98721933364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00824737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96619176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369941711426</t>
+    <t xml:space="preserve">7.92251920700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.987220287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0082483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9661922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8836989402771</t>
   </si>
   <si>
     <t xml:space="preserve">7.78017997741699</t>
@@ -1769,130 +1769,130 @@
     <t xml:space="preserve">7.78988456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74297857284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84164428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98074960708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91119623184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474721908569</t>
+    <t xml:space="preserve">7.76238584518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7429780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84164381027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98074865341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9111967086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474626541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.85134983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74944734573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889699935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39036083221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24963903427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212055206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49388122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39521455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26581478118896</t>
+    <t xml:space="preserve">7.7494478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39036130905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24963998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212102890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49388217926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39521408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26581382751465</t>
   </si>
   <si>
     <t xml:space="preserve">7.21890687942505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35477638244629</t>
+    <t xml:space="preserve">7.35477733612061</t>
   </si>
   <si>
     <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0523042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0992112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07980155944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99245595932007</t>
+    <t xml:space="preserve">7.05230474472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09921169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0798020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99245643615723</t>
   </si>
   <si>
     <t xml:space="preserve">7.23831653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27875471115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58446216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62328147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54079008102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430904388428</t>
+    <t xml:space="preserve">7.27875423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62328195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828641891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54078912734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430952072144</t>
   </si>
   <si>
     <t xml:space="preserve">7.93707656860352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90634489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92898893356323</t>
+    <t xml:space="preserve">7.90634393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92898845672607</t>
   </si>
   <si>
     <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67342472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57152271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83193969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92575454711914</t>
+    <t xml:space="preserve">7.88046646118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8578200340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67342376708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57152223587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83193922042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9257550239563</t>
   </si>
   <si>
     <t xml:space="preserve">8.01795196533203</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">7.80767726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00339412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3988733291626</t>
+    <t xml:space="preserve">8.00339508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39887428283691</t>
   </si>
   <si>
     <t xml:space="preserve">8.23712348937988</t>
@@ -1928,46 +1928,46 @@
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92051696777344</t>
+    <t xml:space="preserve">8.35034942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83559894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92051792144775</t>
   </si>
   <si>
     <t xml:space="preserve">9.08226680755615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15909957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18740463256836</t>
+    <t xml:space="preserve">9.15909862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18740558624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.02161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07418155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445434570312</t>
+    <t xml:space="preserve">9.07417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17931747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23188591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34915542602539</t>
+    <t xml:space="preserve">9.23188781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34915637969971</t>
   </si>
   <si>
     <t xml:space="preserve">9.38150691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32489395141602</t>
+    <t xml:space="preserve">9.3248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">9.26828002929688</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">9.36532974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40576839447021</t>
+    <t xml:space="preserve">9.5917797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40576934814453</t>
   </si>
   <si>
     <t xml:space="preserve">9.59582424163818</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">9.65648078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56751918792725</t>
+    <t xml:space="preserve">9.56751728057861</t>
   </si>
   <si>
     <t xml:space="preserve">9.45833683013916</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">9.4664249420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47451114654541</t>
+    <t xml:space="preserve">9.47451210021973</t>
   </si>
   <si>
     <t xml:space="preserve">9.81014347076416</t>
@@ -2018,28 +2018,28 @@
     <t xml:space="preserve">9.79552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98629379272461</t>
+    <t xml:space="preserve">9.98629474639893</t>
   </si>
   <si>
     <t xml:space="preserve">9.79967308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73331737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47619724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589687347412</t>
+    <t xml:space="preserve">9.73331928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4761962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589782714844</t>
   </si>
   <si>
     <t xml:space="preserve">8.50162124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44356060028076</t>
+    <t xml:space="preserve">8.44356155395508</t>
   </si>
   <si>
     <t xml:space="preserve">8.27767562866211</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">8.17150974273682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96912908554077</t>
+    <t xml:space="preserve">7.96912860870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.12506103515625</t>
@@ -2057,67 +2057,67 @@
     <t xml:space="preserve">8.03050708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22625255584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2362060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11842632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2113208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09520149230957</t>
+    <t xml:space="preserve">8.22625160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23620510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1184253692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21132183074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0952033996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.00728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08690738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0388011932373</t>
+    <t xml:space="preserve">8.0869083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03880214691162</t>
   </si>
   <si>
     <t xml:space="preserve">7.87955141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67385339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670240402222</t>
+    <t xml:space="preserve">7.6738543510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69375944137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091138839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670192718506</t>
   </si>
   <si>
     <t xml:space="preserve">7.77172660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70868921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71366739273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70039510726929</t>
+    <t xml:space="preserve">7.70868968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7136664390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70039558410645</t>
   </si>
   <si>
     <t xml:space="preserve">7.73357248306274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58925104141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62574672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50299167633057</t>
+    <t xml:space="preserve">7.58925151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6257472038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50299072265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.55109834671021</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">7.72859573364258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82978534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9193639755249</t>
+    <t xml:space="preserve">7.82978582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91936254501343</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12837886810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08359050750732</t>
+    <t xml:space="preserve">8.12837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08359146118164</t>
   </si>
   <si>
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249485015869</t>
+    <t xml:space="preserve">7.96249437332153</t>
   </si>
   <si>
     <t xml:space="preserve">8.13667392730713</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">8.60529899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87901020050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86656951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54724025726318</t>
+    <t xml:space="preserve">8.87900924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86656856536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5472412109375</t>
   </si>
   <si>
     <t xml:space="preserve">8.38550090789795</t>
@@ -2177,22 +2177,22 @@
     <t xml:space="preserve">8.51406288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45600318908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30670642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48088550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29094696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3232946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704879760742</t>
+    <t xml:space="preserve">8.4560022354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30670547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48088455200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2909460067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32329368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704784393311</t>
   </si>
   <si>
     <t xml:space="preserve">8.06700134277344</t>
@@ -2216,31 +2216,31 @@
     <t xml:space="preserve">7.5726637840271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39184808731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22098588943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38853168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191165924072</t>
+    <t xml:space="preserve">7.39184856414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38355445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38853025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73191261291504</t>
   </si>
   <si>
     <t xml:space="preserve">7.41839122772217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25084543228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42502593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06173706054688</t>
+    <t xml:space="preserve">7.25084590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42502546310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06173658370972</t>
   </si>
   <si>
     <t xml:space="preserve">7.17951488494873</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">7.564368724823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4449315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76509046554565</t>
+    <t xml:space="preserve">7.44493103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76509094238281</t>
   </si>
   <si>
     <t xml:space="preserve">7.73854875564575</t>
@@ -2267,34 +2267,34 @@
     <t xml:space="preserve">7.92765712738037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77836132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18975734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16984939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09852027893066</t>
+    <t xml:space="preserve">7.77836179733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258737564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18975639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16985034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09851932525635</t>
   </si>
   <si>
     <t xml:space="preserve">7.76343154907227</t>
@@ -2303,61 +2303,61 @@
     <t xml:space="preserve">7.79660892486572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03216648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98903512954712</t>
+    <t xml:space="preserve">8.03216552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98903560638428</t>
   </si>
   <si>
     <t xml:space="preserve">7.84969186782837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86130380630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9044337272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00064659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02718925476074</t>
+    <t xml:space="preserve">7.86130332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840782165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90443325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00064754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02719020843506</t>
   </si>
   <si>
     <t xml:space="preserve">7.65394687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72361850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89614057540894</t>
+    <t xml:space="preserve">7.72362041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89614105224609</t>
   </si>
   <si>
     <t xml:space="preserve">8.1267204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95917510986328</t>
+    <t xml:space="preserve">7.95917558670044</t>
   </si>
   <si>
     <t xml:space="preserve">8.17482662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33988380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34402942657471</t>
+    <t xml:space="preserve">8.33988285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.5596809387207</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">8.46014881134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44770812988281</t>
+    <t xml:space="preserve">8.44770908355713</t>
   </si>
   <si>
     <t xml:space="preserve">8.42697238922119</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">8.6260347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47673797607422</t>
+    <t xml:space="preserve">8.47673892974854</t>
   </si>
   <si>
     <t xml:space="preserve">8.37720775604248</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">8.60944652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85412693023682</t>
+    <t xml:space="preserve">8.85412788391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.95780658721924</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">8.99927711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1651611328125</t>
+    <t xml:space="preserve">9.16516304016113</t>
   </si>
   <si>
     <t xml:space="preserve">9.13198566436768</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">9.23566341400146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48449230194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52596378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50937461853027</t>
+    <t xml:space="preserve">9.4844913482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52596187591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50937366485596</t>
   </si>
   <si>
     <t xml:space="preserve">9.42643165588379</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">9.73746681213379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70014190673828</t>
+    <t xml:space="preserve">9.7001428604126</t>
   </si>
   <si>
     <t xml:space="preserve">9.57158184051514</t>
@@ -2450,40 +2450,40 @@
     <t xml:space="preserve">9.28957653045654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35178375244141</t>
+    <t xml:space="preserve">9.35178279876709</t>
   </si>
   <si>
     <t xml:space="preserve">9.3891077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19833946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31031322479248</t>
+    <t xml:space="preserve">9.19834041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31031227111816</t>
   </si>
   <si>
     <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26884078979492</t>
+    <t xml:space="preserve">9.26883983612061</t>
   </si>
   <si>
     <t xml:space="preserve">9.11539649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12369060516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04074954986572</t>
+    <t xml:space="preserve">9.12369155883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04074859619141</t>
   </si>
   <si>
     <t xml:space="preserve">9.06148433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01586627960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05319023132324</t>
+    <t xml:space="preserve">9.01586532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05318927764893</t>
   </si>
   <si>
     <t xml:space="preserve">8.93292331695557</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">9.12783813476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88315773010254</t>
+    <t xml:space="preserve">8.88315677642822</t>
   </si>
   <si>
     <t xml:space="preserve">8.82509803771973</t>
@@ -2501,22 +2501,22 @@
     <t xml:space="preserve">9.09880828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24395751953125</t>
+    <t xml:space="preserve">9.24395847320557</t>
   </si>
   <si>
     <t xml:space="preserve">9.58817005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29372406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1527214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25639820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15686702728271</t>
+    <t xml:space="preserve">9.29372310638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25639915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15686798095703</t>
   </si>
   <si>
     <t xml:space="preserve">9.21492767333984</t>
@@ -2528,49 +2528,49 @@
     <t xml:space="preserve">9.08221912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09466075897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11124992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7753324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27298831939697</t>
+    <t xml:space="preserve">9.09466171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11124897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77533149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27298927307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.10710144042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77118396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97024631500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68770122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1444263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08636665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05733776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99098205566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28128147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89559841156006</t>
+    <t xml:space="preserve">8.77118492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97024726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27713394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68770027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14442729949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0863676071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05733585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99098300933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28128242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89559936523438</t>
   </si>
   <si>
     <t xml:space="preserve">8.25279331207275</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">7.87457418441772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74186611175537</t>
+    <t xml:space="preserve">7.74186658859253</t>
   </si>
   <si>
     <t xml:space="preserve">7.34042453765869</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">7.35867118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44327259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73328399658203</t>
+    <t xml:space="preserve">7.44327306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73328447341919</t>
   </si>
   <si>
     <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53256273269653</t>
+    <t xml:space="preserve">6.53256320953369</t>
   </si>
   <si>
     <t xml:space="preserve">5.73797225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38990068435669</t>
+    <t xml:space="preserve">6.38990116119385</t>
   </si>
   <si>
     <t xml:space="preserve">6.30861759185791</t>
@@ -2618,16 +2618,16 @@
     <t xml:space="preserve">6.24060487747192</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2024507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19083976745605</t>
+    <t xml:space="preserve">6.20245122909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1908392906189</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71503639221191</t>
+    <t xml:space="preserve">6.71503591537476</t>
   </si>
   <si>
     <t xml:space="preserve">7.33047103881836</t>
@@ -2636,28 +2636,28 @@
     <t xml:space="preserve">6.85769748687744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98542928695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87594556808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87096881866455</t>
+    <t xml:space="preserve">6.98542881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87594509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87096929550171</t>
   </si>
   <si>
     <t xml:space="preserve">7.0915961265564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4233660697937</t>
+    <t xml:space="preserve">7.42336750030518</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8331036567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144474029541</t>
+    <t xml:space="preserve">7.83310317993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144426345825</t>
   </si>
   <si>
     <t xml:space="preserve">7.92931747436523</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">7.32715272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22264575958252</t>
+    <t xml:space="preserve">7.22264528274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.21601009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24255180358887</t>
+    <t xml:space="preserve">7.24255228042603</t>
   </si>
   <si>
     <t xml:space="preserve">6.76977825164795</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">7.2641167640686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66224145889282</t>
+    <t xml:space="preserve">7.66224098205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.64067649841309</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">7.88286828994751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07363700866699</t>
+    <t xml:space="preserve">8.07363605499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41038513183594</t>
+    <t xml:space="preserve">8.41038417816162</t>
   </si>
   <si>
     <t xml:space="preserve">8.05207252502441</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">8.70897769927979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35232353210449</t>
+    <t xml:space="preserve">8.35232448577881</t>
   </si>
   <si>
     <t xml:space="preserve">8.22956943511963</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">8.294264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20800304412842</t>
+    <t xml:space="preserve">8.20800495147705</t>
   </si>
   <si>
     <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4725923538208</t>
+    <t xml:space="preserve">8.47259140014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.78777408599854</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">8.71312427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874423980713</t>
+    <t xml:space="preserve">8.75874328613281</t>
   </si>
   <si>
     <t xml:space="preserve">8.91218662261963</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">9.34763622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34348964691162</t>
+    <t xml:space="preserve">9.34349060058594</t>
   </si>
   <si>
     <t xml:space="preserve">9.36007690429688</t>
@@ -2756,22 +2756,22 @@
     <t xml:space="preserve">9.60475826263428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402059555054</t>
+    <t xml:space="preserve">10.040207862854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0443544387817</t>
+    <t xml:space="preserve">9.94896984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0443534851074</t>
   </si>
   <si>
     <t xml:space="preserve">10.2848863601685</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87432193756104</t>
+    <t xml:space="preserve">9.87432098388672</t>
   </si>
   <si>
     <t xml:space="preserve">9.98214626312256</t>
@@ -2780,49 +2780,49 @@
     <t xml:space="preserve">10.065089225769</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9655590057373</t>
+    <t xml:space="preserve">9.96555995941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.95311737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3595371246338</t>
+    <t xml:space="preserve">10.3595361709595</t>
   </si>
   <si>
     <t xml:space="preserve">10.3512420654297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7286310195923</t>
+    <t xml:space="preserve">10.7286319732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.6996011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6747188568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3388013839722</t>
+    <t xml:space="preserve">10.6747179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3388004302979</t>
   </si>
   <si>
     <t xml:space="preserve">10.4093017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4010076522827</t>
+    <t xml:space="preserve">10.4632139205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4010066986084</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8323097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659540176392</t>
+    <t xml:space="preserve">10.6415414810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8323087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7659559249878</t>
   </si>
   <si>
     <t xml:space="preserve">10.9318408966064</t>
@@ -2831,16 +2831,16 @@
     <t xml:space="preserve">10.778395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6332473754883</t>
+    <t xml:space="preserve">10.633246421814</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295677185059</t>
+    <t xml:space="preserve">10.4300365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295686721802</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024150848389</t>
@@ -2861,22 +2861,22 @@
     <t xml:space="preserve">10.230975151062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4175968170166</t>
+    <t xml:space="preserve">10.4175977706909</t>
   </si>
   <si>
     <t xml:space="preserve">11.064549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8654880523682</t>
+    <t xml:space="preserve">10.8654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">10.8240146636963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.612512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6000699996948</t>
+    <t xml:space="preserve">10.6125116348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6000690460205</t>
   </si>
   <si>
     <t xml:space="preserve">10.7493667602539</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">10.7949848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6664237976074</t>
+    <t xml:space="preserve">10.6664247512817</t>
   </si>
   <si>
     <t xml:space="preserve">10.5337162017822</t>
@@ -2900,19 +2900,19 @@
     <t xml:space="preserve">10.6249532699585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5751876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2392692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3180637359619</t>
+    <t xml:space="preserve">10.5751867294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4341850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2392702102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180646896362</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">10.1936511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0319128036499</t>
+    <t xml:space="preserve">10.0319137573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.81626224517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83285045623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46790313720703</t>
+    <t xml:space="preserve">9.83284950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46790218353271</t>
   </si>
   <si>
     <t xml:space="preserve">9.44716739654541</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">9.72087860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5591402053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71258354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67940711975098</t>
+    <t xml:space="preserve">9.55913925170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71258449554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67940616607666</t>
   </si>
   <si>
     <t xml:space="preserve">9.74990749359131</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">9.82040977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0277662277222</t>
+    <t xml:space="preserve">10.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335178375244</t>
+    <t xml:space="preserve">9.90335083007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.1604738235474</t>
@@ -2975,19 +2975,19 @@
     <t xml:space="preserve">10.0775318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1521787643433</t>
+    <t xml:space="preserve">10.1521797180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1065626144409</t>
+    <t xml:space="preserve">10.1065607070923</t>
   </si>
   <si>
     <t xml:space="preserve">9.96141147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59646320343018</t>
+    <t xml:space="preserve">9.59646415710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.53425693511963</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">9.67111206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74576091766357</t>
+    <t xml:space="preserve">9.74576187133789</t>
   </si>
   <si>
     <t xml:space="preserve">9.96970653533936</t>
@@ -3008,25 +3008,25 @@
     <t xml:space="preserve">10.3844194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.347095489502</t>
+    <t xml:space="preserve">10.3470945358276</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94482231140137</t>
+    <t xml:space="preserve">9.94482326507568</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272964477539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2682991027832</t>
+    <t xml:space="preserve">10.2683000564575</t>
   </si>
   <si>
     <t xml:space="preserve">10.5088329315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4134502410889</t>
+    <t xml:space="preserve">10.4134492874146</t>
   </si>
   <si>
     <t xml:space="preserve">10.5212745666504</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">10.7576608657837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8779268264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8945169448853</t>
+    <t xml:space="preserve">10.8779277801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8945159912109</t>
   </si>
   <si>
     <t xml:space="preserve">10.9359884262085</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">10.8986644744873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8364562988281</t>
+    <t xml:space="preserve">10.8364572525024</t>
   </si>
   <si>
     <t xml:space="preserve">10.9857530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8737812042236</t>
+    <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
     <t xml:space="preserve">10.8447513580322</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">11.1350498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1018743515015</t>
+    <t xml:space="preserve">11.1018733978271</t>
   </si>
   <si>
     <t xml:space="preserve">11.1143140792847</t>
@@ -3083,19 +3083,19 @@
     <t xml:space="preserve">11.35484790802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1474924087524</t>
+    <t xml:space="preserve">11.1474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3921728134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2843465805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6119689941406</t>
+    <t xml:space="preserve">11.3921718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2843475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6119709014893</t>
   </si>
   <si>
     <t xml:space="preserve">11.5207328796387</t>
@@ -3104,22 +3104,22 @@
     <t xml:space="preserve">11.4792623519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.350700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1889629364014</t>
+    <t xml:space="preserve">11.3507013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1889619827271</t>
   </si>
   <si>
     <t xml:space="preserve">11.1682271957397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1226091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0355176925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9442825317383</t>
+    <t xml:space="preserve">11.1226081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0355186462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.944281578064</t>
   </si>
   <si>
     <t xml:space="preserve">10.7452192306519</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">11.2926406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9935064315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1096258163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3999252319336</t>
+    <t xml:space="preserve">11.9935054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1096267700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3999261856079</t>
   </si>
   <si>
     <t xml:space="preserve">12.1303615570068</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">12.594841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4870157241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.358452796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1718339920044</t>
+    <t xml:space="preserve">12.4870147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584537506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1718330383301</t>
   </si>
   <si>
     <t xml:space="preserve">12.3169822692871</t>
@@ -3173,61 +3173,61 @@
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3377180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.192569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0847425460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2879524230957</t>
+    <t xml:space="preserve">12.337718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1925687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0847434997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2879514694214</t>
   </si>
   <si>
     <t xml:space="preserve">12.0640077590942</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0349788665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230051040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9810647964478</t>
+    <t xml:space="preserve">12.0349779129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9230041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9810657501221</t>
   </si>
   <si>
     <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1635389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2174520492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3543071746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1759815216064</t>
+    <t xml:space="preserve">12.163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2174510955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3543081283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1759805679321</t>
   </si>
   <si>
     <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.97691822052</t>
+    <t xml:space="preserve">11.9769172668457</t>
   </si>
   <si>
     <t xml:space="preserve">11.9437408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1179208755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820024490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6244125366211</t>
+    <t xml:space="preserve">12.117919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.78200340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6244115829468</t>
   </si>
   <si>
     <t xml:space="preserve">11.5580587387085</t>
@@ -3236,37 +3236,37 @@
     <t xml:space="preserve">11.5539102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4626731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5746459960938</t>
+    <t xml:space="preserve">11.4626741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5746450424194</t>
   </si>
   <si>
     <t xml:space="preserve">11.4834089279175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5912351608276</t>
+    <t xml:space="preserve">11.5912342071533</t>
   </si>
   <si>
     <t xml:space="preserve">11.5995283126831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5870876312256</t>
+    <t xml:space="preserve">11.5870885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7405319213867</t>
+    <t xml:space="preserve">11.7405309677124</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981237411499</t>
+    <t xml:space="preserve">11.7985925674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981227874756</t>
   </si>
   <si>
     <t xml:space="preserve">11.9520359039307</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">11.4751148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6783246994019</t>
+    <t xml:space="preserve">11.6783237457275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8193273544312</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">11.9064168930054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.877387046814</t>
+    <t xml:space="preserve">11.8773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">12.0142412185669</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">11.7322378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7446784973145</t>
+    <t xml:space="preserve">11.7446775436401</t>
   </si>
   <si>
     <t xml:space="preserve">11.6534423828125</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">11.7654142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1640815734863</t>
+    <t xml:space="preserve">11.5787944793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.164080619812</t>
   </si>
   <si>
     <t xml:space="preserve">11.2055511474609</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">11.4336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3299646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3631420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3382596969604</t>
+    <t xml:space="preserve">11.3299655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3631429672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3382606506348</t>
   </si>
   <si>
     <t xml:space="preserve">11.3880243301392</t>
@@ -3356,28 +3356,28 @@
     <t xml:space="preserve">11.3714370727539</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4917030334473</t>
+    <t xml:space="preserve">11.4917020797729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5124397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6451482772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5622034072876</t>
+    <t xml:space="preserve">11.6451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5622043609619</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248804092407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5953807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5497646331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.66588306427</t>
+    <t xml:space="preserve">11.5953817367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5497636795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">11.9312992095947</t>
@@ -3389,40 +3389,40 @@
     <t xml:space="preserve">11.6410007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.026683807373</t>
+    <t xml:space="preserve">11.8068857192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0266828536987</t>
   </si>
   <si>
     <t xml:space="preserve">12.1013317108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2133054733276</t>
+    <t xml:space="preserve">12.2133045196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.2423343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1967163085938</t>
+    <t xml:space="preserve">12.1967144012451</t>
   </si>
   <si>
     <t xml:space="preserve">12.3086891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1510982513428</t>
+    <t xml:space="preserve">12.1510972976685</t>
   </si>
   <si>
     <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391254425049</t>
+    <t xml:space="preserve">12.0391244888306</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690929412842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778549194336</t>
+    <t xml:space="preserve">11.7778558731079</t>
   </si>
   <si>
     <t xml:space="preserve">12.1220664978027</t>
@@ -3431,19 +3431,19 @@
     <t xml:space="preserve">12.2215986251831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3335704803467</t>
+    <t xml:space="preserve">12.333571434021</t>
   </si>
   <si>
     <t xml:space="preserve">12.7151069641113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5367803573608</t>
+    <t xml:space="preserve">12.5367794036865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7773151397705</t>
+    <t xml:space="preserve">12.7773141860962</t>
   </si>
   <si>
     <t xml:space="preserve">12.8975811004639</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">13.4201202392578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3496179580688</t>
+    <t xml:space="preserve">13.3496170043945</t>
   </si>
   <si>
     <t xml:space="preserve">13.2252054214478</t>
@@ -3482,19 +3482,19 @@
     <t xml:space="preserve">13.051025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1588487625122</t>
+    <t xml:space="preserve">13.1588506698608</t>
   </si>
   <si>
     <t xml:space="preserve">13.1837339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2583808898926</t>
+    <t xml:space="preserve">13.2583818435669</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2625303268433</t>
+    <t xml:space="preserve">13.2625284194946</t>
   </si>
   <si>
     <t xml:space="preserve">12.9514942169189</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">12.8644037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8685512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607269287109</t>
+    <t xml:space="preserve">12.8685522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939033508301</t>
@@ -3515,37 +3515,37 @@
     <t xml:space="preserve">12.9349060058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312273025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7482843399048</t>
+    <t xml:space="preserve">12.8312282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7482852935791</t>
   </si>
   <si>
     <t xml:space="preserve">12.574104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6611957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9763765335083</t>
+    <t xml:space="preserve">12.6611948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9763774871826</t>
   </si>
   <si>
     <t xml:space="preserve">13.2376461029053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1215257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0095539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2417936325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3081474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9431991577148</t>
+    <t xml:space="preserve">13.1215267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0095529556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.241792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3081464767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9432001113892</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
@@ -3554,22 +3554,22 @@
     <t xml:space="preserve">12.9971132278442</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7690210342407</t>
+    <t xml:space="preserve">12.7690200805664</t>
   </si>
   <si>
     <t xml:space="preserve">12.6446056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9722309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888191223145</t>
+    <t xml:space="preserve">12.9722299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888181686401</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090850830078</t>
+    <t xml:space="preserve">13.1090841293335</t>
   </si>
   <si>
     <t xml:space="preserve">12.9929647445679</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">13.7726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7975091934204</t>
+    <t xml:space="preserve">13.7975082397461</t>
   </si>
   <si>
     <t xml:space="preserve">13.9219226837158</t>
@@ -3605,40 +3605,40 @@
     <t xml:space="preserve">13.9799823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6274766921997</t>
+    <t xml:space="preserve">13.627477645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.7270069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6979780197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0048666000366</t>
+    <t xml:space="preserve">13.6979761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0048656463623</t>
   </si>
   <si>
     <t xml:space="preserve">13.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.224663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3324899673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2951650619507</t>
+    <t xml:space="preserve">14.0878105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173082351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3324890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2951641082764</t>
   </si>
   <si>
     <t xml:space="preserve">14.3532247543335</t>
@@ -3647,13 +3647,13 @@
     <t xml:space="preserve">14.2619867324829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076066970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.12513256073</t>
+    <t xml:space="preserve">14.3076076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251316070557</t>
   </si>
   <si>
     <t xml:space="preserve">14.3006258010864</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">13.8255081176758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.859751701355</t>
+    <t xml:space="preserve">13.8597526550293</t>
   </si>
   <si>
     <t xml:space="preserve">13.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819042205811</t>
+    <t xml:space="preserve">13.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">13.3161478042603</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">13.4359970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1363735198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1834554672241</t>
+    <t xml:space="preserve">13.1363725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1834564208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.5515661239624</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445571899414</t>
+    <t xml:space="preserve">13.4445581436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258846282959</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">12.9095153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2519416809082</t>
+    <t xml:space="preserve">13.2433824539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2519426345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.2134199142456</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">13.487361907959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6842565536499</t>
+    <t xml:space="preserve">13.6842555999756</t>
   </si>
   <si>
     <t xml:space="preserve">13.2562227249146</t>
@@ -3758,19 +3758,19 @@
     <t xml:space="preserve">13.8511905670166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5301647186279</t>
+    <t xml:space="preserve">13.5301656723022</t>
   </si>
   <si>
     <t xml:space="preserve">13.6114912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2861862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0293655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1920175552368</t>
+    <t xml:space="preserve">13.2861852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0293645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1920166015625</t>
   </si>
   <si>
     <t xml:space="preserve">13.1320934295654</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740970611572</t>
+    <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
     <t xml:space="preserve">12.85387134552</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">13.6799764633179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.543004989624</t>
+    <t xml:space="preserve">13.5430059432983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4103155136108</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">13.2776250839233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4301166534424</t>
+    <t xml:space="preserve">12.4301176071167</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
@@ -3842,19 +3842,19 @@
     <t xml:space="preserve">12.7768249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0234842300415</t>
+    <t xml:space="preserve">12.0234851837158</t>
   </si>
   <si>
     <t xml:space="preserve">12.0363254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8351488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9576778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8720712661743</t>
+    <t xml:space="preserve">11.835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9576787948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8720722198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.5339250564575</t>
@@ -3866,31 +3866,31 @@
     <t xml:space="preserve">11.3172273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5954494476318</t>
+    <t xml:space="preserve">11.5954504013062</t>
   </si>
   <si>
     <t xml:space="preserve">11.8265886306763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8950729370117</t>
+    <t xml:space="preserve">11.895073890686</t>
   </si>
   <si>
     <t xml:space="preserve">12.5157232284546</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9892406463623</t>
+    <t xml:space="preserve">11.9892416000366</t>
   </si>
   <si>
     <t xml:space="preserve">12.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277652740479</t>
+    <t xml:space="preserve">12.0277643203735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9849605560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8479909896851</t>
+    <t xml:space="preserve">11.8479900360107</t>
   </si>
   <si>
     <t xml:space="preserve">11.9507179260254</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">12.1989784240723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2332210540771</t>
+    <t xml:space="preserve">12.2332201004028</t>
   </si>
   <si>
     <t xml:space="preserve">12.3102674484253</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188276290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203798294067</t>
+    <t xml:space="preserve">12.1262121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.318826675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203788757324</t>
   </si>
   <si>
     <t xml:space="preserve">11.9464378356934</t>
@@ -3941,10 +3941,10 @@
     <t xml:space="preserve">12.0705680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8651113510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4798812866211</t>
+    <t xml:space="preserve">11.8651103973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4798803329468</t>
   </si>
   <si>
     <t xml:space="preserve">11.2444620132446</t>
@@ -3962,16 +3962,16 @@
     <t xml:space="preserve">11.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0775270462036</t>
+    <t xml:space="preserve">11.3771533966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0775279998779</t>
   </si>
   <si>
     <t xml:space="preserve">11.090368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5724487304688</t>
+    <t xml:space="preserve">10.5724477767944</t>
   </si>
   <si>
     <t xml:space="preserve">10.0545263290405</t>
@@ -3986,22 +3986,22 @@
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938491821289</t>
+    <t xml:space="preserve">10.5938501358032</t>
   </si>
   <si>
     <t xml:space="preserve">10.6109714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8292675018311</t>
+    <t xml:space="preserve">10.8292684555054</t>
   </si>
   <si>
     <t xml:space="preserve">10.8035860061646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7693433761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1668996810913</t>
+    <t xml:space="preserve">10.7693424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.166898727417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1403951644897</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158653259277</t>
+    <t xml:space="preserve">11.5158643722534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
@@ -4028,25 +4028,25 @@
     <t xml:space="preserve">11.1580648422241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4893608093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3745107650757</t>
+    <t xml:space="preserve">11.4893617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37451171875</t>
   </si>
   <si>
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62968254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14378261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13053035736084</t>
+    <t xml:space="preserve">10.6368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62968349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14378356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13052940368652</t>
   </si>
   <si>
     <t xml:space="preserve">9.74453163146973</t>
@@ -4058,28 +4058,28 @@
     <t xml:space="preserve">9.57667636871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89030361175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92122364044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1818447113037</t>
+    <t xml:space="preserve">9.89030265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92122459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1818437576294</t>
   </si>
   <si>
     <t xml:space="preserve">10.4645509719849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6191568374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4689674377441</t>
+    <t xml:space="preserve">10.6191558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4689683914185</t>
   </si>
   <si>
     <t xml:space="preserve">10.4778022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3894567489624</t>
+    <t xml:space="preserve">10.3894577026367</t>
   </si>
   <si>
     <t xml:space="preserve">10.0890808105469</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3585367202759</t>
+    <t xml:space="preserve">10.3585357666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.83287906646729</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">10.0449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5661478042603</t>
+    <t xml:space="preserve">10.5661487579346</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408660888672</t>
@@ -4133,43 +4133,43 @@
     <t xml:space="preserve">10.0007352828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6809978485107</t>
+    <t xml:space="preserve">10.6809988021851</t>
   </si>
   <si>
     <t xml:space="preserve">10.6500759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.999041557312</t>
+    <t xml:space="preserve">10.9990425109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.8841915130615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8267679214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5573139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062786102295</t>
+    <t xml:space="preserve">10.8267688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.707501411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5573129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062795639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902067184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7781772613525</t>
+    <t xml:space="preserve">10.9902057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7781782150269</t>
   </si>
   <si>
     <t xml:space="preserve">10.5308094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6544942855835</t>
+    <t xml:space="preserve">10.6544933319092</t>
   </si>
   <si>
     <t xml:space="preserve">10.1465063095093</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">9.95656299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0051527023315</t>
+    <t xml:space="preserve">10.0051517486572</t>
   </si>
   <si>
     <t xml:space="preserve">9.93447685241699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45299053192139</t>
+    <t xml:space="preserve">9.4529914855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">9.54133796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55458927154541</t>
+    <t xml:space="preserve">9.55458831787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.42648792266846</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">9.55017185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58109378814697</t>
+    <t xml:space="preserve">9.58109474182129</t>
   </si>
   <si>
     <t xml:space="preserve">9.59876155853271</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.919529914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2287406921387</t>
+    <t xml:space="preserve">10.8797740936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9195308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.228741645813</t>
   </si>
   <si>
     <t xml:space="preserve">11.3082523345947</t>
@@ -4229,16 +4229,16 @@
     <t xml:space="preserve">11.1183090209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9946250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5528955459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8046808242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215036392212</t>
+    <t xml:space="preserve">10.9946241378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5528945922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8046817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215026855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.9372005462646</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">11.3259210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.02112865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8488550186157</t>
+    <t xml:space="preserve">11.0211296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8488540649414</t>
   </si>
   <si>
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.188985824585</t>
+    <t xml:space="preserve">11.1889848709106</t>
   </si>
   <si>
     <t xml:space="preserve">11.8471603393555</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">10.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239473342896</t>
+    <t xml:space="preserve">10.9239482879639</t>
   </si>
   <si>
     <t xml:space="preserve">11.246410369873</t>
@@ -4319,10 +4319,10 @@
     <t xml:space="preserve">12.6201858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6246032714844</t>
+    <t xml:space="preserve">12.3772354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6246023178101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6908617019653</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">12.920560836792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9514827728271</t>
+    <t xml:space="preserve">12.9514818191528</t>
   </si>
   <si>
     <t xml:space="preserve">13.0354108810425</t>
@@ -4349,25 +4349,25 @@
     <t xml:space="preserve">13.1811809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2827796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3843765258789</t>
+    <t xml:space="preserve">13.2827787399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3843755722046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4418020248413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5743188858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285488128662</t>
+    <t xml:space="preserve">13.5743198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285497665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.3578729629517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6405782699585</t>
+    <t xml:space="preserve">13.6405792236328</t>
   </si>
   <si>
     <t xml:space="preserve">13.6494140625</t>
@@ -4376,19 +4376,19 @@
     <t xml:space="preserve">13.9144506454468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8835296630859</t>
+    <t xml:space="preserve">13.8835306167603</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6759176254272</t>
+    <t xml:space="preserve">13.6008234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7465944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6759166717529</t>
   </si>
   <si>
     <t xml:space="preserve">13.7730979919434</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188690185547</t>
+    <t xml:space="preserve">13.9188680648804</t>
   </si>
   <si>
     <t xml:space="preserve">13.1414251327515</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">13.4903917312622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5345630645752</t>
+    <t xml:space="preserve">13.5345640182495</t>
   </si>
   <si>
     <t xml:space="preserve">13.5831537246704</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">13.7112560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8658599853516</t>
+    <t xml:space="preserve">13.8658609390259</t>
   </si>
   <si>
     <t xml:space="preserve">14.1883230209351</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">14.5726270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6963109970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8685836791992</t>
+    <t xml:space="preserve">14.696310043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8685846328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">14.7669868469238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7095623016357</t>
+    <t xml:space="preserve">14.7095613479614</t>
   </si>
   <si>
     <t xml:space="preserve">14.7934913635254</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.3385095596313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.148567199707</t>
+    <t xml:space="preserve">14.1485662460327</t>
   </si>
   <si>
     <t xml:space="preserve">14.0955591201782</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">14.4489421844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5107831954956</t>
+    <t xml:space="preserve">14.5107841491699</t>
   </si>
   <si>
     <t xml:space="preserve">14.4312725067139</t>
@@ -4484,10 +4484,10 @@
     <t xml:space="preserve">14.5328712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.52845287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5814609527588</t>
+    <t xml:space="preserve">14.5284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5814599990845</t>
   </si>
   <si>
     <t xml:space="preserve">14.9790163040161</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">14.9392614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8553333282471</t>
+    <t xml:space="preserve">14.8553323745728</t>
   </si>
   <si>
     <t xml:space="preserve">15.0099382400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6609716415405</t>
+    <t xml:space="preserve">14.6609706878662</t>
   </si>
   <si>
     <t xml:space="preserve">14.6918926239014</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">14.9701814651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7714033126831</t>
+    <t xml:space="preserve">14.7714042663574</t>
   </si>
   <si>
     <t xml:space="preserve">14.6433038711548</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">14.1397314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.963041305542</t>
+    <t xml:space="preserve">13.9630422592163</t>
   </si>
   <si>
     <t xml:space="preserve">14.1927404403687</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">11.2684965133667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153924942017</t>
+    <t xml:space="preserve">11.6837224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.315393447876</t>
   </si>
   <si>
     <t xml:space="preserve">12.4169902801514</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0238513946533</t>
+    <t xml:space="preserve">12.0238523483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500919342041</t>
+    <t xml:space="preserve">12.5009183883667</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920845031738</t>
+    <t xml:space="preserve">12.4920854568481</t>
   </si>
   <si>
     <t xml:space="preserve">12.293306350708</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">12.3684005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5892648696899</t>
+    <t xml:space="preserve">12.5892658233643</t>
   </si>
   <si>
     <t xml:space="preserve">12.5362577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3065595626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406742095947</t>
+    <t xml:space="preserve">12.3065586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.540675163269</t>
   </si>
   <si>
     <t xml:space="preserve">12.1298666000366</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">11.8824987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2022380828857</t>
+    <t xml:space="preserve">11.2022371292114</t>
   </si>
   <si>
     <t xml:space="preserve">11.0255451202393</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">11.0343809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2199058532715</t>
+    <t xml:space="preserve">11.2199068069458</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653009414673</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">11.2950000762939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0873880386353</t>
+    <t xml:space="preserve">11.0873870849609</t>
   </si>
   <si>
     <t xml:space="preserve">11.1448125839233</t>
@@ -6291,6 +6291,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.2199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299995422363</t>
   </si>
 </sst>
 </file>
@@ -71551,7 +71554,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912731481</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>1146338</v>
@@ -71572,6 +71575,32 @@
         <v>2092</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.691087963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>1432916</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>19.3700008392334</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>19.2350006103516</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>19.2299995422363</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="2095">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048892974854</t>
+    <t xml:space="preserve">5.32048797607422</t>
   </si>
   <si>
     <t xml:space="preserve">5.17209386825562</t>
@@ -53,55 +53,55 @@
     <t xml:space="preserve">5.13951969146729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26257801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1322808265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26619863510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31325006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959547042847</t>
+    <t xml:space="preserve">5.26257848739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13228034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26619720458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3132495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1938099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04541635513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959594726562</t>
   </si>
   <si>
     <t xml:space="preserve">5.07437086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65814161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101392745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96578884124756</t>
+    <t xml:space="preserve">4.65814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96578931808472</t>
   </si>
   <si>
     <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21190738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04903554916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14675855636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12504148483276</t>
+    <t xml:space="preserve">5.21190690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04903507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14675807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12504196166992</t>
   </si>
   <si>
     <t xml:space="preserve">4.88978242874146</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74138784408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56765699386597</t>
+    <t xml:space="preserve">4.74138736724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56765747070312</t>
   </si>
   <si>
     <t xml:space="preserve">4.34325551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545625686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441171646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213520050049</t>
+    <t xml:space="preserve">4.45545673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213472366333</t>
   </si>
   <si>
     <t xml:space="preserve">4.78482103347778</t>
@@ -140,82 +140,82 @@
     <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71243238449097</t>
+    <t xml:space="preserve">4.71243286132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84996891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88616275787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00922203063965</t>
+    <t xml:space="preserve">4.84996938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88616371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00922250747681</t>
   </si>
   <si>
     <t xml:space="preserve">5.09246778488159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10332536697388</t>
+    <t xml:space="preserve">5.10332632064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.16847467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95493078231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84273099899292</t>
+    <t xml:space="preserve">4.95493173599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84273052215576</t>
   </si>
   <si>
     <t xml:space="preserve">4.78120088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06713199615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08884859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00560283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99112415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19019079208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23362350463867</t>
+    <t xml:space="preserve">5.06713247299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00560235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99112510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1901912689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23362398147583</t>
   </si>
   <si>
     <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02007961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026752471924</t>
+    <t xml:space="preserve">5.12866115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02008008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026704788208</t>
   </si>
   <si>
     <t xml:space="preserve">4.94769239425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97302770614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369928359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11418390274048</t>
+    <t xml:space="preserve">4.9730281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11418485641479</t>
   </si>
   <si>
     <t xml:space="preserve">5.12142276763916</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">5.23406362533569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28287506103516</t>
+    <t xml:space="preserve">5.282874584198</t>
   </si>
   <si>
     <t xml:space="preserve">5.27161073684692</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39176177978516</t>
+    <t xml:space="preserve">5.33168601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.391761302948</t>
   </si>
   <si>
     <t xml:space="preserve">5.26410150527954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25659275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05759286880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09889507293701</t>
+    <t xml:space="preserve">5.25659227371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05759334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.96747922897339</t>
@@ -269,22 +269,22 @@
     <t xml:space="preserve">4.78725385665894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79100799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76472473144531</t>
+    <t xml:space="preserve">4.79100847244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76472520828247</t>
   </si>
   <si>
     <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96372509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90364933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90740394592285</t>
+    <t xml:space="preserve">4.96372556686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90364980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90740346908569</t>
   </si>
   <si>
     <t xml:space="preserve">4.7759895324707</t>
@@ -293,64 +293,64 @@
     <t xml:space="preserve">4.73844242095947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84357452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91866779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98625373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97874402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01629018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92617750167847</t>
+    <t xml:space="preserve">4.84357357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91866827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.986252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97874355316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01629066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92617797851562</t>
   </si>
   <si>
     <t xml:space="preserve">4.95246076583862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97123432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8548378944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.877366065979</t>
+    <t xml:space="preserve">4.9712347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85483837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87736701965332</t>
   </si>
   <si>
     <t xml:space="preserve">4.8022723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204647064209</t>
+    <t xml:space="preserve">4.62204694747925</t>
   </si>
   <si>
     <t xml:space="preserve">4.56197118759155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44182062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44932985305786</t>
+    <t xml:space="preserve">4.44182014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44932889938354</t>
   </si>
   <si>
     <t xml:space="preserve">4.4568395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56948089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346183776855</t>
+    <t xml:space="preserve">4.56947994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346088409424</t>
   </si>
   <si>
     <t xml:space="preserve">4.73093318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80602645874023</t>
+    <t xml:space="preserve">4.80602693557739</t>
   </si>
   <si>
     <t xml:space="preserve">4.97498893737793</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">4.49063205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13017988204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39676380157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33668851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39300870895386</t>
+    <t xml:space="preserve">4.13017892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39676427841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33668899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39300918579102</t>
   </si>
   <si>
     <t xml:space="preserve">4.17523622512817</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">4.10014200210571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87485933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244408607483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26534938812256</t>
+    <t xml:space="preserve">3.87485909461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244360923767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534795761108</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
@@ -395,76 +395,76 @@
     <t xml:space="preserve">4.20151901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23531103134155</t>
+    <t xml:space="preserve">4.23531150817871</t>
   </si>
   <si>
     <t xml:space="preserve">4.31040525436401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25032997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24657535552979</t>
+    <t xml:space="preserve">4.25033044815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24657583236694</t>
   </si>
   <si>
     <t xml:space="preserve">4.27661323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09638738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93118047714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9875009059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8373122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93868923187256</t>
+    <t xml:space="preserve">4.09638690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93118023872375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98750042915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83731293678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93868947029114</t>
   </si>
   <si>
     <t xml:space="preserve">3.97623586654663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93493413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97248244285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746302604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9461989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99876427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980275154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604837417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348208427429</t>
+    <t xml:space="preserve">3.93493437767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9724817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619917869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99876475334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604789733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348232269287</t>
   </si>
   <si>
     <t xml:space="preserve">3.75470852851868</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05133056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07010459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04382181167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01378393173218</t>
+    <t xml:space="preserve">4.05133104324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07010412216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04382228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01378297805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">4.09263229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13768911361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12267017364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05508518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385969161987</t>
+    <t xml:space="preserve">4.1376895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12266969680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0550856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385873794556</t>
   </si>
   <si>
     <t xml:space="preserve">4.03255701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91240644454956</t>
+    <t xml:space="preserve">3.9124059677124</t>
   </si>
   <si>
     <t xml:space="preserve">3.82229375839233</t>
@@ -497,172 +497,172 @@
     <t xml:space="preserve">3.81478357315063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90489673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114283561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81102919578552</t>
+    <t xml:space="preserve">3.90489625930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114235877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987851142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81102991104126</t>
   </si>
   <si>
     <t xml:space="preserve">3.88612389564514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89738750457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8523313999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850102424622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61203002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550881385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601073265076</t>
+    <t xml:space="preserve">3.89738726615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236880302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233068466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850054740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221799850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61202931404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79600977897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.96121788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97999119758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02504777908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96497225761414</t>
+    <t xml:space="preserve">3.9799919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02504730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96497201919556</t>
   </si>
   <si>
     <t xml:space="preserve">4.01753854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08887767791748</t>
+    <t xml:space="preserve">4.08887815475464</t>
   </si>
   <si>
     <t xml:space="preserve">4.14519786834717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99501037597656</t>
+    <t xml:space="preserve">3.99501013755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.92742538452148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83355736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727458000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225611686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518419265747</t>
+    <t xml:space="preserve">3.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474593162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727505683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225564002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.751704454422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518371582031</t>
   </si>
   <si>
     <t xml:space="preserve">3.64056515693665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60452055931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54444527626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843784332275</t>
+    <t xml:space="preserve">3.60452032089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5444450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5384373664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.5414412021637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55645990371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001492500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47085285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799958229065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66459608078003</t>
+    <t xml:space="preserve">3.55646014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4708526134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58800005912781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66459560394287</t>
   </si>
   <si>
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910123825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57748627662659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73968958854675</t>
+    <t xml:space="preserve">3.66910171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57748651504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73969054222107</t>
   </si>
   <si>
     <t xml:space="preserve">3.84857606887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14144325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1038966178894</t>
+    <t xml:space="preserve">4.14144372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10389709472656</t>
   </si>
   <si>
     <t xml:space="preserve">4.01002931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04006719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11516046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00251960754395</t>
+    <t xml:space="preserve">4.04006671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11516094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00251913070679</t>
   </si>
   <si>
     <t xml:space="preserve">4.07761335372925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16772651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270853042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18274545669556</t>
+    <t xml:space="preserve">4.16772699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895343780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512258529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1827449798584</t>
   </si>
   <si>
     <t xml:space="preserve">4.22029256820679</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">4.2390661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16021680831909</t>
+    <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642478942871</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">4.06259489059448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631114959717</t>
+    <t xml:space="preserve">4.03631162643433</t>
   </si>
   <si>
     <t xml:space="preserve">4.13393402099609</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.28787755966187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30289554595947</t>
+    <t xml:space="preserve">4.30289602279663</t>
   </si>
   <si>
     <t xml:space="preserve">4.33293342590332</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.46810293197632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44557523727417</t>
+    <t xml:space="preserve">4.44557476043701</t>
   </si>
   <si>
     <t xml:space="preserve">4.63706493377686</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">4.72342348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67085695266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8097825050354</t>
+    <t xml:space="preserve">4.67085742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80978107452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.83981943130493</t>
@@ -725,76 +725,76 @@
     <t xml:space="preserve">4.79851722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7271785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85108375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82104587554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83606481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07056140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13733148574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10198163986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0744891166687</t>
+    <t xml:space="preserve">4.72717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85108327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82104635238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83606433868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07056093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13733100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10198211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07448863983154</t>
   </si>
   <si>
     <t xml:space="preserve">5.12947607040405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16875219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23552131652832</t>
+    <t xml:space="preserve">5.16875123977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23552083969116</t>
   </si>
   <si>
     <t xml:space="preserve">5.33371162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3415675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37691593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20410013198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28265285491943</t>
+    <t xml:space="preserve">5.34156703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37691640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20410060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28265237808228</t>
   </si>
   <si>
     <t xml:space="preserve">5.20017290115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22373819351196</t>
+    <t xml:space="preserve">5.22373867034912</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29050827026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26694250106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36906099319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34942197799683</t>
+    <t xml:space="preserve">5.15696859359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29050874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26694202423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36906051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34942293167114</t>
   </si>
   <si>
     <t xml:space="preserve">5.38477087020874</t>
@@ -803,37 +803,37 @@
     <t xml:space="preserve">5.21588325500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21981048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25515937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32978439331055</t>
+    <t xml:space="preserve">5.219810962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25515985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32978391647339</t>
   </si>
   <si>
     <t xml:space="preserve">5.32585716247559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25123167037964</t>
+    <t xml:space="preserve">5.2512321472168</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43975782394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57722520828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5418758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63221073150635</t>
+    <t xml:space="preserve">5.43975830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6165018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57722425460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54187631607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63221168518066</t>
   </si>
   <si>
     <t xml:space="preserve">5.62435626983643</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">5.50652742385864</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53794813156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62042808532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55365896224976</t>
+    <t xml:space="preserve">5.5379490852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62042903900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55365943908691</t>
   </si>
   <si>
     <t xml:space="preserve">5.50259971618652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41226387023926</t>
+    <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
     <t xml:space="preserve">5.52223825454712</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076440811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73432970046997</t>
+    <t xml:space="preserve">5.87572383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73433017730713</t>
   </si>
   <si>
     <t xml:space="preserve">5.64006614685059</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">5.65970468521118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72647380828857</t>
+    <t xml:space="preserve">5.72647476196289</t>
   </si>
   <si>
     <t xml:space="preserve">5.6832709312439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67148733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65577697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77753353118896</t>
+    <t xml:space="preserve">5.67148780822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6557765007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77753305435181</t>
   </si>
   <si>
     <t xml:space="preserve">5.77360534667969</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">5.86786842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83644771575928</t>
+    <t xml:space="preserve">5.83644676208496</t>
   </si>
   <si>
     <t xml:space="preserve">5.82466506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8285927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179613113403</t>
+    <t xml:space="preserve">5.84037494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82859230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179660797119</t>
   </si>
   <si>
     <t xml:space="preserve">5.93463802337646</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">5.95034837722778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90714454650879</t>
+    <t xml:space="preserve">5.90714550018311</t>
   </si>
   <si>
     <t xml:space="preserve">5.79717111587524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70290899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78931570053101</t>
+    <t xml:space="preserve">5.70290851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78931665420532</t>
   </si>
   <si>
     <t xml:space="preserve">5.89143419265747</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324388504028</t>
+    <t xml:space="preserve">5.7932448387146</t>
   </si>
   <si>
     <t xml:space="preserve">5.70683622360229</t>
@@ -953,37 +953,37 @@
     <t xml:space="preserve">5.6871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936979293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46725177764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66755962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903347015381</t>
+    <t xml:space="preserve">5.56936931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46725130081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66756057739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903394699097</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39262628555298</t>
+    <t xml:space="preserve">5.39262580871582</t>
   </si>
   <si>
     <t xml:space="preserve">5.45939588546753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75003957748413</t>
+    <t xml:space="preserve">5.75004005432129</t>
   </si>
   <si>
     <t xml:space="preserve">5.76182270050049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73040246963501</t>
+    <t xml:space="preserve">5.73040199279785</t>
   </si>
   <si>
     <t xml:space="preserve">5.75396728515625</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8089542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91499996185303</t>
+    <t xml:space="preserve">5.80895471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91500043869019</t>
   </si>
   <si>
     <t xml:space="preserve">5.87965154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85215759277344</t>
+    <t xml:space="preserve">5.8521580696106</t>
   </si>
   <si>
     <t xml:space="preserve">5.84430313110352</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">5.86001348495483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84823131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69505310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6636323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64792156219482</t>
+    <t xml:space="preserve">5.84823036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6950535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363191604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64792108535767</t>
   </si>
   <si>
     <t xml:space="preserve">5.71861934661865</t>
@@ -1040,52 +1040,52 @@
     <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26063060760498</t>
+    <t xml:space="preserve">6.2606315612793</t>
   </si>
   <si>
     <t xml:space="preserve">6.24492025375366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31168985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29205274581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2527756690979</t>
+    <t xml:space="preserve">6.31169033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776166915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29990768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29205226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25277614593506</t>
   </si>
   <si>
     <t xml:space="preserve">6.26455879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20171642303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2331371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00926351547241</t>
+    <t xml:space="preserve">6.20171689987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23313760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926303863525</t>
   </si>
   <si>
     <t xml:space="preserve">6.12709188461304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528314590454</t>
+    <t xml:space="preserve">6.22528219223022</t>
   </si>
   <si>
     <t xml:space="preserve">6.28026866912842</t>
@@ -1094,121 +1094,121 @@
     <t xml:space="preserve">6.37060403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37453126907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33132886886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39809799194336</t>
+    <t xml:space="preserve">6.3745322227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33132791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3980975151062</t>
   </si>
   <si>
     <t xml:space="preserve">6.45308446884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58662366867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339326858521</t>
+    <t xml:space="preserve">6.5866231918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339374542236</t>
   </si>
   <si>
     <t xml:space="preserve">6.53949213027954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60626173019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63768339157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56305837631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71230792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83013582229614</t>
+    <t xml:space="preserve">6.60626220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63768196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5630578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71230697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8301362991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.68874216079712</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79086017608643</t>
+    <t xml:space="preserve">6.79086065292358</t>
   </si>
   <si>
     <t xml:space="preserve">6.68088722229004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409057617188</t>
+    <t xml:space="preserve">6.72409105300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.77907752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76336622238159</t>
+    <t xml:space="preserve">6.75551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76336669921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.85762977600098</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86155700683594</t>
+    <t xml:space="preserve">6.8615574836731</t>
   </si>
   <si>
     <t xml:space="preserve">6.81049823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70445251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261672973633</t>
+    <t xml:space="preserve">6.70445156097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261625289917</t>
   </si>
   <si>
     <t xml:space="preserve">6.99902391433716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99116897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40356969833374</t>
+    <t xml:space="preserve">6.99116802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40357065200806</t>
   </si>
   <si>
     <t xml:space="preserve">7.58031225204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54103660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55281972885132</t>
+    <t xml:space="preserve">7.54103565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55281925201416</t>
   </si>
   <si>
     <t xml:space="preserve">7.46641111373901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49783229827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62351560592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66672086715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80418729782104</t>
+    <t xml:space="preserve">7.49783277511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62351655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66672039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80418682098389</t>
   </si>
   <si>
     <t xml:space="preserve">7.75705528259277</t>
@@ -1217,58 +1217,58 @@
     <t xml:space="preserve">7.8866662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93379926681519</t>
+    <t xml:space="preserve">7.93379831314087</t>
   </si>
   <si>
     <t xml:space="preserve">7.91808700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78454875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310243606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488412857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74055862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886354446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31951713562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50804376602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5316104888916</t>
+    <t xml:space="preserve">7.78454828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8748836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31951904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50804424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53160953521729</t>
   </si>
   <si>
     <t xml:space="preserve">7.23782348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26610279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30066585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076271057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59130907058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69657039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355194091797</t>
+    <t xml:space="preserve">7.26610231399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410772323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59130954742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355146408081</t>
   </si>
   <si>
     <t xml:space="preserve">7.80025911331177</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">7.77826547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83325290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94950866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96914720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52061367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83010911941528</t>
+    <t xml:space="preserve">7.83325099945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94950914382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96914672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5206127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83010864257812</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129179000854</t>
@@ -1301,55 +1301,55 @@
     <t xml:space="preserve">8.09090423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94165277481079</t>
+    <t xml:space="preserve">7.94165229797363</t>
   </si>
   <si>
     <t xml:space="preserve">7.95343685150146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04377174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11054229736328</t>
+    <t xml:space="preserve">8.0437707901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11054134368896</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07126522064209</t>
+    <t xml:space="preserve">8.07126331329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.86702871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83953619003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69499826431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71070861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61487674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65572357177734</t>
+    <t xml:space="preserve">7.8395357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71070909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64158296585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300367355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61487531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6557240486145</t>
   </si>
   <si>
     <t xml:space="preserve">7.85524654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59445285797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415287017822</t>
+    <t xml:space="preserve">7.59445142745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">7.59602355957031</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.7531270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8316798210144</t>
+    <t xml:space="preserve">7.83168077468872</t>
   </si>
   <si>
     <t xml:space="preserve">7.82696676254272</t>
@@ -1370,40 +1370,40 @@
     <t xml:space="preserve">7.79554605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03897953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08750534057617</t>
+    <t xml:space="preserve">8.03897857666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08750438690186</t>
   </si>
   <si>
     <t xml:space="preserve">8.01633453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96942663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97427940368652</t>
+    <t xml:space="preserve">7.96942758560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97427988052368</t>
   </si>
   <si>
     <t xml:space="preserve">8.00986576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07456493377686</t>
+    <t xml:space="preserve">8.07456398010254</t>
   </si>
   <si>
     <t xml:space="preserve">7.9856014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14815998077393</t>
+    <t xml:space="preserve">8.14816093444824</t>
   </si>
   <si>
     <t xml:space="preserve">8.21690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9322247505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105442047119</t>
+    <t xml:space="preserve">7.93222379684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105537414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.85943746566772</t>
@@ -1412,34 +1412,34 @@
     <t xml:space="preserve">7.87884616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86752367019653</t>
+    <t xml:space="preserve">7.86752414703369</t>
   </si>
   <si>
     <t xml:space="preserve">7.43726921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41947603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19626188278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43079948425293</t>
+    <t xml:space="preserve">7.4194769859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19626140594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43079853057861</t>
   </si>
   <si>
     <t xml:space="preserve">7.40491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4259467124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10568284988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59293413162231</t>
+    <t xml:space="preserve">7.42594623565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10568237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59293460845947</t>
   </si>
   <si>
     <t xml:space="preserve">6.43441867828369</t>
@@ -1448,70 +1448,70 @@
     <t xml:space="preserve">6.8484992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91805171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10729885101318</t>
+    <t xml:space="preserve">6.91805124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10729837417603</t>
   </si>
   <si>
     <t xml:space="preserve">6.92613935470581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8177661895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22214221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20111465454102</t>
+    <t xml:space="preserve">6.81776714324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2221417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20111417770386</t>
   </si>
   <si>
     <t xml:space="preserve">7.14773750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2641978263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58607959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70415782928467</t>
+    <t xml:space="preserve">7.26419734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61681318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58607912063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70415735244751</t>
   </si>
   <si>
     <t xml:space="preserve">7.66857290267944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63783979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78179693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70739126205444</t>
+    <t xml:space="preserve">7.63783931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78179740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70739269256592</t>
   </si>
   <si>
     <t xml:space="preserve">7.8028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62975263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6944522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886783599854</t>
+    <t xml:space="preserve">7.62975120544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69445180892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886735916138</t>
   </si>
   <si>
     <t xml:space="preserve">7.69768667221069</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8222336769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032178878784</t>
+    <t xml:space="preserve">7.82223463058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032321929932</t>
   </si>
   <si>
     <t xml:space="preserve">7.9516339302063</t>
@@ -1523,31 +1523,31 @@
     <t xml:space="preserve">8.03089237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95001840591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07294750213623</t>
+    <t xml:space="preserve">7.95001554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07294654846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19264221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25329780578613</t>
+    <t xml:space="preserve">8.19264316558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969287872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29778003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27756023406982</t>
+    <t xml:space="preserve">8.29778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31395530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27756118774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455505371094</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">8.23307991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28564929962158</t>
+    <t xml:space="preserve">8.21286010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28564834594727</t>
   </si>
   <si>
     <t xml:space="preserve">8.24925422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24521064758301</t>
+    <t xml:space="preserve">8.12794303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24521255493164</t>
   </si>
   <si>
     <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06647682189941</t>
+    <t xml:space="preserve">8.06647777557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.1764669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07941722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14007186889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08588695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12389945983887</t>
+    <t xml:space="preserve">8.07941818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14007377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08588790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12389850616455</t>
   </si>
   <si>
     <t xml:space="preserve">8.20881748199463</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">8.2249927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30991172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22903633117676</t>
+    <t xml:space="preserve">8.30990982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22903537750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.1885986328125</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">8.33417415618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30182456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31799793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60510635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77898502349854</t>
+    <t xml:space="preserve">8.30182361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60510540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
     <t xml:space="preserve">8.77089881896973</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">8.89625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95691204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03778648376465</t>
+    <t xml:space="preserve">8.95691108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03778743743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.04183006286621</t>
@@ -1640,52 +1640,52 @@
     <t xml:space="preserve">9.11866092681885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22379970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32084846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4178991317749</t>
+    <t xml:space="preserve">9.22379875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32084941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22784233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41790008544922</t>
   </si>
   <si>
     <t xml:space="preserve">9.44620609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61604309082031</t>
+    <t xml:space="preserve">9.61604404449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.48260021209717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31276035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39768028259277</t>
+    <t xml:space="preserve">9.31276226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39768123626709</t>
   </si>
   <si>
     <t xml:space="preserve">9.30062961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28041172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1954927444458</t>
+    <t xml:space="preserve">9.28041076660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19549369812012</t>
   </si>
   <si>
     <t xml:space="preserve">9.1146183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67789363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65363121032715</t>
+    <t xml:space="preserve">8.67789268493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6536283493042</t>
   </si>
   <si>
     <t xml:space="preserve">8.05191993713379</t>
@@ -1694,49 +1694,49 @@
     <t xml:space="preserve">7.89987468719482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88531637191772</t>
+    <t xml:space="preserve">7.88531684875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4680027961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24155235290527</t>
+    <t xml:space="preserve">7.83355665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287485122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24155187606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.1606764793396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05715703964233</t>
+    <t xml:space="preserve">7.05715608596802</t>
   </si>
   <si>
     <t xml:space="preserve">7.32080936431885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09597587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770690917969</t>
+    <t xml:space="preserve">7.09597730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595659255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47770738601685</t>
   </si>
   <si>
     <t xml:space="preserve">7.59093189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92251920700073</t>
+    <t xml:space="preserve">7.92251968383789</t>
   </si>
   <si>
     <t xml:space="preserve">7.75106430053711</t>
@@ -1748,64 +1748,64 @@
     <t xml:space="preserve">7.78503179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.987220287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0082483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516468048096</t>
+    <t xml:space="preserve">7.98721933364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00824737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516515731812</t>
   </si>
   <si>
     <t xml:space="preserve">7.9661922454834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8836989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78017997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78988456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76238584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7429780960083</t>
+    <t xml:space="preserve">7.88370084762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78017902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78988409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76238632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74297761917114</t>
   </si>
   <si>
     <t xml:space="preserve">7.84164381027222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98074865341187</t>
+    <t xml:space="preserve">7.98074960708618</t>
   </si>
   <si>
     <t xml:space="preserve">7.9111967086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68474626541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85134983062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7494478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32889747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39036130905151</t>
+    <t xml:space="preserve">7.68474721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8513503074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74944639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32889652252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3903603553772</t>
   </si>
   <si>
     <t xml:space="preserve">7.22537660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24963998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212102890015</t>
+    <t xml:space="preserve">7.24963903427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4421215057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.49388217926025</t>
@@ -1814,40 +1814,40 @@
     <t xml:space="preserve">7.39521408081055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26581382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890687942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35477733612061</t>
+    <t xml:space="preserve">7.26581430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890640258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35477590560913</t>
   </si>
   <si>
     <t xml:space="preserve">7.01833724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05230474472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09921169281006</t>
+    <t xml:space="preserve">7.0523042678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0992112159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.0798020362854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99245643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58446311950684</t>
+    <t xml:space="preserve">6.99245691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831701278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875471115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58446216583252</t>
   </si>
   <si>
     <t xml:space="preserve">7.62328195571899</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">7.55534744262695</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54078912734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707656860352</t>
+    <t xml:space="preserve">7.54078960418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707799911499</t>
   </si>
   <si>
     <t xml:space="preserve">7.90634393692017</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">7.78826713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046646118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8578200340271</t>
+    <t xml:space="preserve">7.88046455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781908035278</t>
   </si>
   <si>
     <t xml:space="preserve">7.67342376708984</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">7.57152223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83193922042847</t>
+    <t xml:space="preserve">7.83193969726562</t>
   </si>
   <si>
     <t xml:space="preserve">7.9257550239563</t>
@@ -1901,61 +1901,61 @@
     <t xml:space="preserve">7.80767726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00339508056641</t>
+    <t xml:space="preserve">8.00339412689209</t>
   </si>
   <si>
     <t xml:space="preserve">8.39887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23712348937988</t>
+    <t xml:space="preserve">8.2371244430542</t>
   </si>
   <si>
     <t xml:space="preserve">8.45144176483154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5767993927002</t>
+    <t xml:space="preserve">8.57679843902588</t>
   </si>
   <si>
     <t xml:space="preserve">8.38674259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18051052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26138591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35034942626953</t>
+    <t xml:space="preserve">8.26947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18051147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559894561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92051792144775</t>
+    <t xml:space="preserve">8.92051696777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.08226680755615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15909862518311</t>
+    <t xml:space="preserve">9.15909957885742</t>
   </si>
   <si>
     <t xml:space="preserve">9.18740558624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02161121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07417964935303</t>
+    <t xml:space="preserve">9.0216121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07418155670166</t>
   </si>
   <si>
     <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17931747436523</t>
+    <t xml:space="preserve">9.17931938171387</t>
   </si>
   <si>
     <t xml:space="preserve">9.23188781738281</t>
@@ -1964,28 +1964,28 @@
     <t xml:space="preserve">9.34915637969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38150691986084</t>
+    <t xml:space="preserve">9.38150596618652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3248929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26828002929688</t>
+    <t xml:space="preserve">9.26828098297119</t>
   </si>
   <si>
     <t xml:space="preserve">9.36532974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5917797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40576934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59582424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65648078918457</t>
+    <t xml:space="preserve">9.59178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40576839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65647983551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.56751728057861</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">9.45833683013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4664249420166</t>
+    <t xml:space="preserve">9.46642398834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.47451210021973</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">9.83036136627197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.036060333252</t>
+    <t xml:space="preserve">10.0360593795776</t>
   </si>
   <si>
     <t xml:space="preserve">9.84943866729736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79552745819092</t>
+    <t xml:space="preserve">9.7955265045166</t>
   </si>
   <si>
     <t xml:space="preserve">9.98629474639893</t>
@@ -2024,91 +2024,91 @@
     <t xml:space="preserve">9.79967308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73331928253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4761962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589782714844</t>
+    <t xml:space="preserve">9.73331832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47619724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589687347412</t>
   </si>
   <si>
     <t xml:space="preserve">8.50162124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44356155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27767562866211</t>
+    <t xml:space="preserve">8.44356060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27767467498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.17150974273682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96912860870361</t>
+    <t xml:space="preserve">7.96912813186646</t>
   </si>
   <si>
     <t xml:space="preserve">8.12506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03050708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22625160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23620510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1184253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21132183074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0952033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00728321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0869083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03880214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87955141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6738543510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091138839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77670192718506</t>
+    <t xml:space="preserve">8.03050804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22625255584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2362060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11842632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2113208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09520149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00728225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08690738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0388011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385244369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69375991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77670383453369</t>
   </si>
   <si>
     <t xml:space="preserve">7.77172660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70868968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7136664390564</t>
+    <t xml:space="preserve">7.70868873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71366596221924</t>
   </si>
   <si>
     <t xml:space="preserve">7.70039558410645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73357248306274</t>
+    <t xml:space="preserve">7.7335729598999</t>
   </si>
   <si>
     <t xml:space="preserve">7.58925151824951</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">7.6257472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50299072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72859573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82978582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91936254501343</t>
+    <t xml:space="preserve">7.50299119949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72859525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82978630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91936492919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.12340259552002</t>
@@ -2138,19 +2138,19 @@
     <t xml:space="preserve">8.12837982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08359146118164</t>
+    <t xml:space="preserve">8.08359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.01557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96249437332153</t>
+    <t xml:space="preserve">7.96249485015869</t>
   </si>
   <si>
     <t xml:space="preserve">8.13667392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17814350128174</t>
+    <t xml:space="preserve">8.17814445495605</t>
   </si>
   <si>
     <t xml:space="preserve">8.2196159362793</t>
@@ -2159,16 +2159,16 @@
     <t xml:space="preserve">8.60529899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87900924682617</t>
+    <t xml:space="preserve">8.87901020050049</t>
   </si>
   <si>
     <t xml:space="preserve">8.86656856536865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5472412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38550090789795</t>
+    <t xml:space="preserve">8.54724025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38549995422363</t>
   </si>
   <si>
     <t xml:space="preserve">8.55553340911865</t>
@@ -2177,64 +2177,64 @@
     <t xml:space="preserve">8.51406288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4560022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30670547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48088455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2909460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32329368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704784393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06700134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24283981323242</t>
+    <t xml:space="preserve">8.45600318908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30670642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48088550567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29094696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3232946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06700229644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24283885955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.08027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86462211608887</t>
+    <t xml:space="preserve">7.86462259292603</t>
   </si>
   <si>
     <t xml:space="preserve">7.36530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45820140838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5726637840271</t>
+    <t xml:space="preserve">7.45820236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57266426086426</t>
   </si>
   <si>
     <t xml:space="preserve">7.39184856414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22098636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38355445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38853025436401</t>
+    <t xml:space="preserve">7.22098684310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38853073120117</t>
   </si>
   <si>
     <t xml:space="preserve">7.73191261291504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41839122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25084590911865</t>
+    <t xml:space="preserve">7.41839075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25084638595581</t>
   </si>
   <si>
     <t xml:space="preserve">7.42502546310425</t>
@@ -2243,76 +2243,76 @@
     <t xml:space="preserve">7.06173658370972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388235092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25914001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.564368724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44493103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76509094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73854875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92765712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77836179733276</t>
+    <t xml:space="preserve">7.17951536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388330459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2591404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4449315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76509046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73854923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92765760421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77836132049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.82646799087524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258737564087</t>
+    <t xml:space="preserve">7.72030162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258785247803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15989780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18975639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81651496887207</t>
+    <t xml:space="preserve">8.1897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81651449203491</t>
   </si>
   <si>
     <t xml:space="preserve">8.16985034942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09851932525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76343154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79660892486572</t>
+    <t xml:space="preserve">8.09852027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76343059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79660797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.03216552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98903560638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84969186782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86130332946777</t>
+    <t xml:space="preserve">7.98903512954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84969234466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86130285263062</t>
   </si>
   <si>
     <t xml:space="preserve">7.97742366790771</t>
@@ -2321,34 +2321,34 @@
     <t xml:space="preserve">8.05539035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96581220626831</t>
+    <t xml:space="preserve">7.96581125259399</t>
   </si>
   <si>
     <t xml:space="preserve">7.76840782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90443325042725</t>
+    <t xml:space="preserve">7.90443515777588</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02719020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65394687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72362041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89614105224609</t>
+    <t xml:space="preserve">8.02718925476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65394639968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361898422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89613914489746</t>
   </si>
   <si>
     <t xml:space="preserve">8.1267204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95917558670044</t>
+    <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
     <t xml:space="preserve">8.17482662200928</t>
@@ -2360,67 +2360,67 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5596809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46014881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44770908355713</t>
+    <t xml:space="preserve">8.55967998504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46014976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44770812988281</t>
   </si>
   <si>
     <t xml:space="preserve">8.42697238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6260347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47673892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37720775604248</t>
+    <t xml:space="preserve">8.63018131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62603569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47673797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37720680236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.60944652557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85412788391113</t>
+    <t xml:space="preserve">8.85412693023682</t>
   </si>
   <si>
     <t xml:space="preserve">8.95780658721924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99927711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16516304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13198566436768</t>
+    <t xml:space="preserve">8.99927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16516208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13198471069336</t>
   </si>
   <si>
     <t xml:space="preserve">9.23566341400146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4844913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52596187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42643165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31445789337158</t>
+    <t xml:space="preserve">9.48449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52596282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50937461853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42643260955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3144588470459</t>
   </si>
   <si>
     <t xml:space="preserve">9.43057823181152</t>
@@ -2429,22 +2429,22 @@
     <t xml:space="preserve">9.38496017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51766872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73746681213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7001428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57158184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33934116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23151588439941</t>
+    <t xml:space="preserve">9.51766777038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73746585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.28957653045654</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">9.3891077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19834041595459</t>
+    <t xml:space="preserve">9.19833946228027</t>
   </si>
   <si>
     <t xml:space="preserve">9.31031227111816</t>
@@ -2465,25 +2465,25 @@
     <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26883983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11539649963379</t>
+    <t xml:space="preserve">9.26884078979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11539745330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04074859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06148433685303</t>
+    <t xml:space="preserve">9.04074764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06148529052734</t>
   </si>
   <si>
     <t xml:space="preserve">9.01586532592773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05318927764893</t>
+    <t xml:space="preserve">9.05319023132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.93292331695557</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">9.09880828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24395847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58817005157471</t>
+    <t xml:space="preserve">9.24395751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58817100524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.29372310638428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15272045135498</t>
+    <t xml:space="preserve">9.1527214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.25639915466309</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">9.11954402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08221912384033</t>
+    <t xml:space="preserve">9.08222007751465</t>
   </si>
   <si>
     <t xml:space="preserve">9.09466171264648</t>
@@ -2534,34 +2534,34 @@
     <t xml:space="preserve">9.11124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77533149719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27298927307129</t>
+    <t xml:space="preserve">8.77533054351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27298736572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.10710144042969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77118492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97024726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27713394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68770027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14442729949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0863676071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05733585357666</t>
+    <t xml:space="preserve">8.77118396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97024631500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27713489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1444263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08636665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05733680725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.99098300933838</t>
@@ -2579,19 +2579,19 @@
     <t xml:space="preserve">8.14994430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87457418441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74186658859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042453765869</t>
+    <t xml:space="preserve">7.87457513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74186611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042501449585</t>
   </si>
   <si>
     <t xml:space="preserve">7.35867118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44327306747437</t>
+    <t xml:space="preserve">7.44327259063721</t>
   </si>
   <si>
     <t xml:space="preserve">6.73328447341919</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53256320953369</t>
+    <t xml:space="preserve">6.53256273269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.73797225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38990116119385</t>
+    <t xml:space="preserve">6.38990068435669</t>
   </si>
   <si>
     <t xml:space="preserve">6.30861759185791</t>
@@ -2615,40 +2615,40 @@
     <t xml:space="preserve">6.12946128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24060487747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20245122909546</t>
+    <t xml:space="preserve">6.24060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2024507522583</t>
   </si>
   <si>
     <t xml:space="preserve">6.1908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8178858757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71503591537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33047103881836</t>
+    <t xml:space="preserve">6.81788635253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33047151565552</t>
   </si>
   <si>
     <t xml:space="preserve">6.85769748687744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98542881011963</t>
+    <t xml:space="preserve">6.98542928695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.87594509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096929550171</t>
+    <t xml:space="preserve">6.87096881866455</t>
   </si>
   <si>
     <t xml:space="preserve">7.0915961265564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42336750030518</t>
+    <t xml:space="preserve">7.42336702346802</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
@@ -2657,37 +2657,37 @@
     <t xml:space="preserve">7.83310317993164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83144426345825</t>
+    <t xml:space="preserve">7.83144521713257</t>
   </si>
   <si>
     <t xml:space="preserve">7.92931747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32715272903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264528274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21601009368896</t>
+    <t xml:space="preserve">7.32715225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21600961685181</t>
   </si>
   <si>
     <t xml:space="preserve">7.24255228042603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76977825164795</t>
+    <t xml:space="preserve">6.76977872848511</t>
   </si>
   <si>
     <t xml:space="preserve">7.2641167640686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66224098205566</t>
+    <t xml:space="preserve">7.66224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">7.64067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88286828994751</t>
+    <t xml:space="preserve">7.88286876678467</t>
   </si>
   <si>
     <t xml:space="preserve">8.07363605499268</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">8.35232448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22956943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.485032081604</t>
+    <t xml:space="preserve">8.22956848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48503112792969</t>
   </si>
   <si>
     <t xml:space="preserve">8.294264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20800495147705</t>
+    <t xml:space="preserve">8.20800399780273</t>
   </si>
   <si>
     <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47259140014648</t>
+    <t xml:space="preserve">8.4725923538208</t>
   </si>
   <si>
     <t xml:space="preserve">8.78777408599854</t>
@@ -2741,88 +2741,88 @@
     <t xml:space="preserve">8.91218662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0034236907959</t>
+    <t xml:space="preserve">9.00342273712158</t>
   </si>
   <si>
     <t xml:space="preserve">9.34763622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34349060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36007690429688</t>
+    <t xml:space="preserve">9.34348964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36007785797119</t>
   </si>
   <si>
     <t xml:space="preserve">9.60475826263428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.040207862854</t>
+    <t xml:space="preserve">10.0402069091797</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94896984100342</t>
+    <t xml:space="preserve">9.94897174835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0443534851074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98214626312256</t>
+    <t xml:space="preserve">10.2848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87432193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.065089225769</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96555995941162</t>
+    <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
     <t xml:space="preserve">9.95311737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3595361709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3512420654297</t>
+    <t xml:space="preserve">10.3595371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3512411117554</t>
   </si>
   <si>
     <t xml:space="preserve">10.7286319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6996011734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6747179031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3388004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4093017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4632139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4010066986084</t>
+    <t xml:space="preserve">10.6996002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6747188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3388013839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4093027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415414810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8323087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659559249878</t>
+    <t xml:space="preserve">10.6415405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8323097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7659549713135</t>
   </si>
   <si>
     <t xml:space="preserve">10.9318408966064</t>
@@ -2831,25 +2831,25 @@
     <t xml:space="preserve">10.778395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.633246421814</t>
+    <t xml:space="preserve">10.6332473754883</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5295686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024150848389</t>
+    <t xml:space="preserve">10.4300374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5295677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024141311646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.53786277771</t>
+    <t xml:space="preserve">10.5378637313843</t>
   </si>
   <si>
     <t xml:space="preserve">10.3305063247681</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">10.230975151062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4175977706909</t>
+    <t xml:space="preserve">10.4175958633423</t>
   </si>
   <si>
     <t xml:space="preserve">11.064549446106</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6000690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7493667602539</t>
+    <t xml:space="preserve">10.6000699996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7493658065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.687159538269</t>
@@ -2888,31 +2888,31 @@
     <t xml:space="preserve">10.6913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7949848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6664247512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5337162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6249532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2392702102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3180646896362</t>
+    <t xml:space="preserve">10.7949857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6664237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5337152481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6249523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4341840744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2392692565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180637359619</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895036697388</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">9.81626224517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83284950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46790218353271</t>
+    <t xml:space="preserve">9.83285045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46790313720703</t>
   </si>
   <si>
     <t xml:space="preserve">9.44716739654541</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">9.72087860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55913925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71258449554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67940616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74990749359131</t>
+    <t xml:space="preserve">9.5591402053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71258354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67940711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74990844726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.82040977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1107082366943</t>
+    <t xml:space="preserve">10.0277662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1107091903687</t>
   </si>
   <si>
     <t xml:space="preserve">9.90335083007812</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">10.1729154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2102394104004</t>
+    <t xml:space="preserve">10.2102403640747</t>
   </si>
   <si>
     <t xml:space="preserve">10.0775318145752</t>
@@ -2981,34 +2981,34 @@
     <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1065607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96141147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59646415710449</t>
+    <t xml:space="preserve">10.1065616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96141052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59646320343018</t>
   </si>
   <si>
     <t xml:space="preserve">9.53425693511963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67111206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96970653533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2600049972534</t>
+    <t xml:space="preserve">9.67111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74576091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96970748901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2600059509277</t>
   </si>
   <si>
     <t xml:space="preserve">10.3844194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3470945358276</t>
+    <t xml:space="preserve">10.347095489502</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346538543701</t>
@@ -3026,19 +3026,19 @@
     <t xml:space="preserve">10.5088329315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4134492874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5212745666504</t>
+    <t xml:space="preserve">10.4134502410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5212755203247</t>
   </si>
   <si>
     <t xml:space="preserve">10.8074264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7576608657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8779277801514</t>
+    <t xml:space="preserve">10.757661819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8779268264771</t>
   </si>
   <si>
     <t xml:space="preserve">10.8945159912109</t>
@@ -3053,19 +3053,19 @@
     <t xml:space="preserve">10.9733114242554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8364572525024</t>
+    <t xml:space="preserve">10.898663520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8364562988281</t>
   </si>
   <si>
     <t xml:space="preserve">10.9857530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8737802505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8447513580322</t>
+    <t xml:space="preserve">10.8737812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8447504043579</t>
   </si>
   <si>
     <t xml:space="preserve">10.9774580001831</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">11.1350498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1018733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143140792847</t>
+    <t xml:space="preserve">11.1018743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143131256104</t>
   </si>
   <si>
     <t xml:space="preserve">11.35484790802</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">11.15993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3921718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2843475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6119709014893</t>
+    <t xml:space="preserve">11.3921728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2843456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6119699478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.5207328796387</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">11.1226081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0355186462402</t>
+    <t xml:space="preserve">11.0355195999146</t>
   </si>
   <si>
     <t xml:space="preserve">10.944281578064</t>
@@ -3128,70 +3128,70 @@
     <t xml:space="preserve">10.6788654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9935054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1096267700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3999261856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1303615570068</t>
+    <t xml:space="preserve">11.2926416397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9935064315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1096258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3999252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1303606033325</t>
   </si>
   <si>
     <t xml:space="preserve">12.4455442428589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2630701065063</t>
+    <t xml:space="preserve">12.2630681991577</t>
   </si>
   <si>
     <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.594841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4870147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584537506104</t>
+    <t xml:space="preserve">12.5948400497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4870157241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.358452796936</t>
   </si>
   <si>
     <t xml:space="preserve">12.1718330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3169822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1842746734619</t>
+    <t xml:space="preserve">12.3169832229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1842737197876</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.337718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1925687789917</t>
+    <t xml:space="preserve">12.3377180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1925678253174</t>
   </si>
   <si>
     <t xml:space="preserve">12.0847434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2879514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0640077590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0349779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230041503906</t>
+    <t xml:space="preserve">12.2879543304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0640068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0349788665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9230060577393</t>
   </si>
   <si>
     <t xml:space="preserve">11.9810657501221</t>
@@ -3206,16 +3206,16 @@
     <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3543081283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1759805679321</t>
+    <t xml:space="preserve">12.3543071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1759815216064</t>
   </si>
   <si>
     <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9769172668457</t>
+    <t xml:space="preserve">11.97691822052</t>
   </si>
   <si>
     <t xml:space="preserve">11.9437408447266</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">11.78200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6244115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5580587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5539102554321</t>
+    <t xml:space="preserve">11.6244125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5580577850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5539112091064</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626741409302</t>
@@ -3245,73 +3245,73 @@
     <t xml:space="preserve">11.4834089279175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5912342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5995283126831</t>
+    <t xml:space="preserve">11.591236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5995292663574</t>
   </si>
   <si>
     <t xml:space="preserve">11.5870885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7405309677124</t>
+    <t xml:space="preserve">11.6824722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405300140381</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985925674438</t>
+    <t xml:space="preserve">11.7985906600952</t>
   </si>
   <si>
     <t xml:space="preserve">11.8981227874756</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9520359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.545615196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5331745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543790817261</t>
+    <t xml:space="preserve">11.9520349502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5456161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5331754684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543800354004</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6783237457275</t>
+    <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
     <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064168930054</t>
+    <t xml:space="preserve">11.9064159393311</t>
   </si>
   <si>
     <t xml:space="preserve">11.8773860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142412185669</t>
+    <t xml:space="preserve">12.0142421722412</t>
   </si>
   <si>
     <t xml:space="preserve">11.6949129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8732395172119</t>
+    <t xml:space="preserve">11.8732385635376</t>
   </si>
   <si>
     <t xml:space="preserve">11.6617364883423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7322378158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7446775436401</t>
+    <t xml:space="preserve">11.7322368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7446784973145</t>
   </si>
   <si>
     <t xml:space="preserve">11.6534423828125</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">11.7654142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5787944793701</t>
+    <t xml:space="preserve">11.5787925720215</t>
   </si>
   <si>
     <t xml:space="preserve">11.164080619812</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">11.2055511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4129085540771</t>
+    <t xml:space="preserve">11.3050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4129076004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.4336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3631429672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3382606506348</t>
+    <t xml:space="preserve">11.3299646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3382587432861</t>
   </si>
   <si>
     <t xml:space="preserve">11.3880243301392</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">11.3714370727539</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4917020797729</t>
+    <t xml:space="preserve">11.4917030334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.5124397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6451473236084</t>
+    <t xml:space="preserve">11.6451482772827</t>
   </si>
   <si>
     <t xml:space="preserve">11.5622043609619</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">11.5497636795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6658821105957</t>
+    <t xml:space="preserve">11.66588306427</t>
   </si>
   <si>
     <t xml:space="preserve">11.9312992095947</t>
@@ -3386,46 +3386,46 @@
     <t xml:space="preserve">11.8607988357544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6410007476807</t>
+    <t xml:space="preserve">11.6409997940063</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068857192993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0266828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1013317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2133045196533</t>
+    <t xml:space="preserve">12.026683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1013307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2133054733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.2423343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1967144012451</t>
+    <t xml:space="preserve">12.1967163085938</t>
   </si>
   <si>
     <t xml:space="preserve">12.3086891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1510972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.478720664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391244888306</t>
+    <t xml:space="preserve">12.1510982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4787216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391254425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690929412842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220664978027</t>
+    <t xml:space="preserve">11.7778549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220684051514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2215986251831</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">12.333571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7151069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5367794036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3708953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7773141860962</t>
+    <t xml:space="preserve">12.7151079177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5367803573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3708963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7773151397705</t>
   </si>
   <si>
     <t xml:space="preserve">12.8975811004639</t>
@@ -3455,31 +3455,31 @@
     <t xml:space="preserve">13.3827962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.453296661377</t>
+    <t xml:space="preserve">13.4532957077026</t>
   </si>
   <si>
     <t xml:space="preserve">13.5942993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698848724365</t>
+    <t xml:space="preserve">13.4698858261108</t>
   </si>
   <si>
     <t xml:space="preserve">13.4201202392578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3496170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2252054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4781799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.216911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.051025390625</t>
+    <t xml:space="preserve">13.3496179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2252044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4781789779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2169103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0510244369507</t>
   </si>
   <si>
     <t xml:space="preserve">13.1588506698608</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">13.1837339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2583818435669</t>
+    <t xml:space="preserve">13.2583808898926</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629972457886</t>
@@ -3497,13 +3497,13 @@
     <t xml:space="preserve">13.2625284194946</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9514942169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8644037246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8685522079468</t>
+    <t xml:space="preserve">12.9514932632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8644046783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8685512542725</t>
   </si>
   <si>
     <t xml:space="preserve">12.7607250213623</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">12.9349060058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312282562256</t>
+    <t xml:space="preserve">12.8312273025513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482852935791</t>
@@ -3527,52 +3527,52 @@
     <t xml:space="preserve">12.6611948013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9763774871826</t>
+    <t xml:space="preserve">12.9763784408569</t>
   </si>
   <si>
     <t xml:space="preserve">13.2376461029053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1215267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.241792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3081464767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9432001113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8768453598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9971132278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7690200805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6446056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722299575806</t>
+    <t xml:space="preserve">13.1215257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0095548629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2417936325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3081474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9431991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8768463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9971122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7690210342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.644606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722309112549</t>
   </si>
   <si>
     <t xml:space="preserve">12.9888181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9929647445679</t>
+    <t xml:space="preserve">13.0302906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9929656982422</t>
   </si>
   <si>
     <t xml:space="preserve">13.2044696807861</t>
@@ -3581,37 +3581,37 @@
     <t xml:space="preserve">13.1173782348633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.602593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7850685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523580551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8016557693481</t>
+    <t xml:space="preserve">13.6025943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7850675582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8016567230225</t>
   </si>
   <si>
     <t xml:space="preserve">13.7726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7975082397461</t>
+    <t xml:space="preserve">13.7975101470947</t>
   </si>
   <si>
     <t xml:space="preserve">13.9219226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9799823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.627477645874</t>
+    <t xml:space="preserve">13.9799814224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6274766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.7270069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6979761123657</t>
+    <t xml:space="preserve">13.69797706604</t>
   </si>
   <si>
     <t xml:space="preserve">14.0048656463623</t>
@@ -3620,49 +3620,49 @@
     <t xml:space="preserve">13.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173082351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2246627807617</t>
+    <t xml:space="preserve">14.0878086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.224663734436</t>
   </si>
   <si>
     <t xml:space="preserve">14.3324890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0712194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2951641082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3532247543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2619867324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3076076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3006258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8255081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8597526550293</t>
+    <t xml:space="preserve">14.0712203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.295166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3532257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2619876861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3076057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.12513256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3006267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8255071640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.859751701355</t>
   </si>
   <si>
     <t xml:space="preserve">13.6542949676514</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">13.3161478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605018615723</t>
+    <t xml:space="preserve">13.2605028152466</t>
   </si>
   <si>
     <t xml:space="preserve">13.4359970092773</t>
@@ -3689,13 +3689,13 @@
     <t xml:space="preserve">13.5515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.906834602356</t>
+    <t xml:space="preserve">13.9068355560303</t>
   </si>
   <si>
     <t xml:space="preserve">13.6457328796387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4488382339478</t>
+    <t xml:space="preserve">13.4488391876221</t>
   </si>
   <si>
     <t xml:space="preserve">13.4188756942749</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445581436157</t>
+    <t xml:space="preserve">13.4445571899414</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258846282959</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">12.7639837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.965160369873</t>
+    <t xml:space="preserve">12.9651594161987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9523191452026</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">12.9095153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2433824539185</t>
+    <t xml:space="preserve">13.2433815002441</t>
   </si>
   <si>
     <t xml:space="preserve">13.2519426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2134199142456</t>
+    <t xml:space="preserve">13.2134189605713</t>
   </si>
   <si>
     <t xml:space="preserve">13.4531183242798</t>
@@ -3740,34 +3740,34 @@
     <t xml:space="preserve">13.487361907959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6842555999756</t>
+    <t xml:space="preserve">13.6842565536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.2562227249146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3589506149292</t>
+    <t xml:space="preserve">13.3589496612549</t>
   </si>
   <si>
     <t xml:space="preserve">13.0122423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8511905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5301656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6114912033081</t>
+    <t xml:space="preserve">13.7741451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8511915206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5301647186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6114902496338</t>
   </si>
   <si>
     <t xml:space="preserve">13.2861852645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0293645858765</t>
+    <t xml:space="preserve">13.0293655395508</t>
   </si>
   <si>
     <t xml:space="preserve">13.1920166015625</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">12.3616313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5499658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4900417327881</t>
+    <t xml:space="preserve">12.5499668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4900407791138</t>
   </si>
   <si>
     <t xml:space="preserve">12.4857616424561</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.85387134552</t>
+    <t xml:space="preserve">12.8538703918457</t>
   </si>
   <si>
     <t xml:space="preserve">12.9009532928467</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">12.8495903015137</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0550470352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6157712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286125183105</t>
+    <t xml:space="preserve">13.055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6157722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286134719849</t>
   </si>
   <si>
     <t xml:space="preserve">13.7784242630005</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">13.2776250839233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4301176071167</t>
+    <t xml:space="preserve">12.4301166534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">12.7768249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0234851837158</t>
+    <t xml:space="preserve">12.0234842300415</t>
   </si>
   <si>
     <t xml:space="preserve">12.0363254547119</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">10.9576787948608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8720722198486</t>
+    <t xml:space="preserve">10.8720712661743</t>
   </si>
   <si>
     <t xml:space="preserve">10.5339250564575</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">11.783784866333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3172273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8265886306763</t>
+    <t xml:space="preserve">11.3172283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954494476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.826587677002</t>
   </si>
   <si>
     <t xml:space="preserve">11.895073890686</t>
@@ -3896,40 +3896,40 @@
     <t xml:space="preserve">11.9507179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3145475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1989784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2332201004028</t>
+    <t xml:space="preserve">12.314546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1989774703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2332210540771</t>
   </si>
   <si>
     <t xml:space="preserve">12.3102674484253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2631826400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9549989700317</t>
+    <t xml:space="preserve">12.2631845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9549980163574</t>
   </si>
   <si>
     <t xml:space="preserve">12.1262121200562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.318826675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203788757324</t>
+    <t xml:space="preserve">12.3188276290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.9464378356934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9079141616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9036340713501</t>
+    <t xml:space="preserve">11.9079151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9036350250244</t>
   </si>
   <si>
     <t xml:space="preserve">11.8009061813354</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">12.0834093093872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0705680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8651103973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4798803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2444620132446</t>
+    <t xml:space="preserve">12.0705671310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8651113510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4798793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2444610595703</t>
   </si>
   <si>
     <t xml:space="preserve">11.2530221939087</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">11.407114982605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1716957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3771533966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0775279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5724477767944</t>
+    <t xml:space="preserve">11.1716947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3771524429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0775270462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0903692245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5724487304688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0545263290405</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">10.6109714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8292684555054</t>
+    <t xml:space="preserve">10.8292675018311</t>
   </si>
   <si>
     <t xml:space="preserve">10.8035860061646</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">10.7693424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.166898727417</t>
+    <t xml:space="preserve">11.1668996810913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1403951644897</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158643722534</t>
+    <t xml:space="preserve">11.5158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
@@ -4028,25 +4028,25 @@
     <t xml:space="preserve">11.1580648422241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4893617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.37451171875</t>
+    <t xml:space="preserve">11.4893608093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3745107650757</t>
   </si>
   <si>
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62968349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14378356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13052940368652</t>
+    <t xml:space="preserve">10.6368246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62968254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14378261566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13053035736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.74453163146973</t>
@@ -4058,28 +4058,28 @@
     <t xml:space="preserve">9.57667636871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89030265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92122459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1818437576294</t>
+    <t xml:space="preserve">9.89030361175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92122364044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1818447113037</t>
   </si>
   <si>
     <t xml:space="preserve">10.4645509719849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6191558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4689683914185</t>
+    <t xml:space="preserve">10.6191568374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4689674377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.4778022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3894577026367</t>
+    <t xml:space="preserve">10.3894567489624</t>
   </si>
   <si>
     <t xml:space="preserve">10.0890808105469</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">10.5970697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3585357666016</t>
+    <t xml:space="preserve">10.3585367202759</t>
   </si>
   <si>
     <t xml:space="preserve">9.83287906646729</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">10.0449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5661487579346</t>
+    <t xml:space="preserve">10.5661478042603</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408660888672</t>
@@ -4133,43 +4133,43 @@
     <t xml:space="preserve">10.0007352828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6809988021851</t>
+    <t xml:space="preserve">10.6809978485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.6500759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9990425109863</t>
+    <t xml:space="preserve">10.999041557312</t>
   </si>
   <si>
     <t xml:space="preserve">10.8841915130615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8267688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.707501411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5573129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062795639038</t>
+    <t xml:space="preserve">10.8267679214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7075004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5573139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062786102295</t>
   </si>
   <si>
     <t xml:space="preserve">10.959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7781782150269</t>
+    <t xml:space="preserve">10.9902067184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7781772613525</t>
   </si>
   <si>
     <t xml:space="preserve">10.5308094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6544933319092</t>
+    <t xml:space="preserve">10.6544942855835</t>
   </si>
   <si>
     <t xml:space="preserve">10.1465063095093</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">9.95656299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0051517486572</t>
+    <t xml:space="preserve">10.0051527023315</t>
   </si>
   <si>
     <t xml:space="preserve">9.93447685241699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4529914855957</t>
+    <t xml:space="preserve">9.45299053192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">9.54133796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55458831787109</t>
+    <t xml:space="preserve">9.55458927154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.42648792266846</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">9.55017185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58109474182129</t>
+    <t xml:space="preserve">9.58109378814697</t>
   </si>
   <si>
     <t xml:space="preserve">9.59876155853271</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">9.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8797740936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9195308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.228741645813</t>
+    <t xml:space="preserve">10.8797750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.919529914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2287406921387</t>
   </si>
   <si>
     <t xml:space="preserve">11.3082523345947</t>
@@ -4229,16 +4229,16 @@
     <t xml:space="preserve">11.1183090209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9946241378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5528945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215026855469</t>
+    <t xml:space="preserve">10.9946250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5528955459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215036392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.9372005462646</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">11.3259210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0211296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8488540649414</t>
+    <t xml:space="preserve">11.02112865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8488550186157</t>
   </si>
   <si>
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1889848709106</t>
+    <t xml:space="preserve">11.188985824585</t>
   </si>
   <si>
     <t xml:space="preserve">11.8471603393555</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">10.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239482879639</t>
+    <t xml:space="preserve">10.9239473342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.246410369873</t>
@@ -4319,10 +4319,10 @@
     <t xml:space="preserve">12.6201858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6246023178101</t>
+    <t xml:space="preserve">12.3772344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6246032714844</t>
   </si>
   <si>
     <t xml:space="preserve">12.6908617019653</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">12.920560836792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9514818191528</t>
+    <t xml:space="preserve">12.9514827728271</t>
   </si>
   <si>
     <t xml:space="preserve">13.0354108810425</t>
@@ -4349,25 +4349,25 @@
     <t xml:space="preserve">13.1811809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2827787399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3843755722046</t>
+    <t xml:space="preserve">13.2827796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3843765258789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4418020248413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5743198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285497665405</t>
+    <t xml:space="preserve">13.5743188858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285488128662</t>
   </si>
   <si>
     <t xml:space="preserve">13.3578729629517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6405792236328</t>
+    <t xml:space="preserve">13.6405782699585</t>
   </si>
   <si>
     <t xml:space="preserve">13.6494140625</t>
@@ -4376,19 +4376,19 @@
     <t xml:space="preserve">13.9144506454468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8835306167603</t>
+    <t xml:space="preserve">13.8835296630859</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6008234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7465944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6759166717529</t>
+    <t xml:space="preserve">13.6008243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6759176254272</t>
   </si>
   <si>
     <t xml:space="preserve">13.7730979919434</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188680648804</t>
+    <t xml:space="preserve">13.9188690185547</t>
   </si>
   <si>
     <t xml:space="preserve">13.1414251327515</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">13.4903917312622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5345640182495</t>
+    <t xml:space="preserve">13.5345630645752</t>
   </si>
   <si>
     <t xml:space="preserve">13.5831537246704</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">13.7112560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8658609390259</t>
+    <t xml:space="preserve">13.8658599853516</t>
   </si>
   <si>
     <t xml:space="preserve">14.1883230209351</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">14.5726270675659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.696310043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8685846328735</t>
+    <t xml:space="preserve">14.6963109970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8685836791992</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">14.7669868469238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7095613479614</t>
+    <t xml:space="preserve">14.7095623016357</t>
   </si>
   <si>
     <t xml:space="preserve">14.7934913635254</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">14.3385095596313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1485662460327</t>
+    <t xml:space="preserve">14.148567199707</t>
   </si>
   <si>
     <t xml:space="preserve">14.0955591201782</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">14.4489421844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5107841491699</t>
+    <t xml:space="preserve">14.5107831954956</t>
   </si>
   <si>
     <t xml:space="preserve">14.4312725067139</t>
@@ -4484,10 +4484,10 @@
     <t xml:space="preserve">14.5328712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5814599990845</t>
+    <t xml:space="preserve">14.52845287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5814609527588</t>
   </si>
   <si>
     <t xml:space="preserve">14.9790163040161</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">14.9392614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8553323745728</t>
+    <t xml:space="preserve">14.8553333282471</t>
   </si>
   <si>
     <t xml:space="preserve">15.0099382400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6609706878662</t>
+    <t xml:space="preserve">14.6609716415405</t>
   </si>
   <si>
     <t xml:space="preserve">14.6918926239014</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">14.9701814651489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7714042663574</t>
+    <t xml:space="preserve">14.7714033126831</t>
   </si>
   <si>
     <t xml:space="preserve">14.6433038711548</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">14.1397314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9630422592163</t>
+    <t xml:space="preserve">13.963041305542</t>
   </si>
   <si>
     <t xml:space="preserve">14.1927404403687</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">11.2684965133667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.315393447876</t>
+    <t xml:space="preserve">11.6837215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153924942017</t>
   </si>
   <si>
     <t xml:space="preserve">12.4169902801514</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0238523483276</t>
+    <t xml:space="preserve">12.0238513946533</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">12.2712202072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5009183883667</t>
+    <t xml:space="preserve">12.500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7350358963013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920854568481</t>
+    <t xml:space="preserve">12.4920845031738</t>
   </si>
   <si>
     <t xml:space="preserve">12.293306350708</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">12.3684005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5892658233643</t>
+    <t xml:space="preserve">12.5892648696899</t>
   </si>
   <si>
     <t xml:space="preserve">12.5362577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3065586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.540675163269</t>
+    <t xml:space="preserve">12.3065595626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406742095947</t>
   </si>
   <si>
     <t xml:space="preserve">12.1298666000366</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">11.8824987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2022371292114</t>
+    <t xml:space="preserve">11.2022380828857</t>
   </si>
   <si>
     <t xml:space="preserve">11.0255451202393</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">11.0343809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2199068069458</t>
+    <t xml:space="preserve">11.2199058532715</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653009414673</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">11.2950000762939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0873870849609</t>
+    <t xml:space="preserve">11.0873880386353</t>
   </si>
   <si>
     <t xml:space="preserve">11.1448125839233</t>
@@ -6294,6 +6294,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.2299995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9099998474121</t>
   </si>
 </sst>
 </file>
@@ -71580,7 +71583,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.691087963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>1432916</v>
@@ -71601,6 +71604,32 @@
         <v>2093</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6910185185</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>3397487</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>20.0400009155273</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>19.5249996185303</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>19.5450000762939</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>19.9099998474121</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>2094</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="2098">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">5.32048845291138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17209434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13952016830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26257848739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13228034973145</t>
+    <t xml:space="preserve">5.17209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951969146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2625789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1322808265686</t>
   </si>
   <si>
     <t xml:space="preserve">5.26619815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3132495880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07437086105347</t>
+    <t xml:space="preserve">5.31324911117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1938099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0454158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07437133789062</t>
   </si>
   <si>
     <t xml:space="preserve">4.65814208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82101392745972</t>
+    <t xml:space="preserve">4.82101440429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">5.05265474319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21190738677979</t>
+    <t xml:space="preserve">5.21190690994263</t>
   </si>
   <si>
     <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485595703125</t>
+    <t xml:space="preserve">5.14675855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485500335693</t>
   </si>
   <si>
     <t xml:space="preserve">5.12504196166992</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">4.88978242874146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79205894470215</t>
+    <t xml:space="preserve">4.79205942153931</t>
   </si>
   <si>
     <t xml:space="preserve">4.74138784408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56765699386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3432559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45545673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78482055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73414897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81377553939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71243238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187294006348</t>
+    <t xml:space="preserve">4.56765747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34325647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45545721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441171646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213520050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78482007980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73414850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81377506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71243286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996938705444</t>
@@ -158,70 +158,70 @@
     <t xml:space="preserve">5.09246730804443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10332536697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16847467422485</t>
+    <t xml:space="preserve">5.10332584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1684741973877</t>
   </si>
   <si>
     <t xml:space="preserve">4.95493078231812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84273052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120088577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713199615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08884811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00560235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99112510681152</t>
+    <t xml:space="preserve">4.8427300453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713247299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08884859085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00560283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99112462997437</t>
   </si>
   <si>
     <t xml:space="preserve">5.19019079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362302780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35668277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02008056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9730281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787982940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369928359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11418342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12142276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544063568115</t>
+    <t xml:space="preserve">5.23362350463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35668182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12866115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02007961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94769239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97302722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11418437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.121422290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544111251831</t>
   </si>
   <si>
     <t xml:space="preserve">5.23406362533569</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">5.27161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.230309009552</t>
+    <t xml:space="preserve">5.23030948638916</t>
   </si>
   <si>
     <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164861679077</t>
+    <t xml:space="preserve">5.33168601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164909362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.39176177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26410245895386</t>
+    <t xml:space="preserve">5.2641019821167</t>
   </si>
   <si>
     <t xml:space="preserve">5.25659227371216</t>
@@ -260,103 +260,103 @@
     <t xml:space="preserve">5.09889459609985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96747922897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88863086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78725385665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79100847244263</t>
+    <t xml:space="preserve">4.96747970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88862991333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78725337982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
     <t xml:space="preserve">4.76472520828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7008957862854</t>
+    <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
     <t xml:space="preserve">4.96372509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90364933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90740442276001</t>
+    <t xml:space="preserve">4.90364980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90740394592285</t>
   </si>
   <si>
     <t xml:space="preserve">4.7759895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73844194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84357452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91866827011108</t>
+    <t xml:space="preserve">4.73844289779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84357404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91866874694824</t>
   </si>
   <si>
     <t xml:space="preserve">4.986252784729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97874402999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01629066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92617750167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95246124267578</t>
+    <t xml:space="preserve">4.97874355316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01629114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92617797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95246076583862</t>
   </si>
   <si>
     <t xml:space="preserve">4.97123432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85483837127686</t>
+    <t xml:space="preserve">4.8548378944397</t>
   </si>
   <si>
     <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80227184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62204694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197071075439</t>
+    <t xml:space="preserve">4.80227279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62204647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197118759155</t>
   </si>
   <si>
     <t xml:space="preserve">4.44182062149048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44932985305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45683908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56948041915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093366622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97498846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063110351562</t>
+    <t xml:space="preserve">4.4493293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4568395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56947994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7534613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093271255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80602693557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97498941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063205718994</t>
   </si>
   <si>
     <t xml:space="preserve">4.13017988204956</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">4.39676380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33668851852417</t>
+    <t xml:space="preserve">4.33668804168701</t>
   </si>
   <si>
     <t xml:space="preserve">4.39300918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17523574829102</t>
+    <t xml:space="preserve">4.17523622512817</t>
   </si>
   <si>
     <t xml:space="preserve">4.10014200210571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87485933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244432449341</t>
+    <t xml:space="preserve">3.87485909461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244408607483</t>
   </si>
   <si>
     <t xml:space="preserve">4.2653489112854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31791543960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1902551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20151853561401</t>
+    <t xml:space="preserve">4.3179144859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20151901245117</t>
   </si>
   <si>
     <t xml:space="preserve">4.23531103134155</t>
@@ -407,58 +407,58 @@
     <t xml:space="preserve">4.24657583236694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27661275863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09638643264771</t>
+    <t xml:space="preserve">4.27661323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09638738632202</t>
   </si>
   <si>
     <t xml:space="preserve">3.9311797618866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98750019073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83731245994568</t>
+    <t xml:space="preserve">3.98750042915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8373122215271</t>
   </si>
   <si>
     <t xml:space="preserve">3.93868947029114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97623658180237</t>
+    <t xml:space="preserve">3.97623586654663</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493485450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97248196601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746254920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9461989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99876475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980298995972</t>
+    <t xml:space="preserve">3.9724817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619870185852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99876427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980251312256</t>
   </si>
   <si>
     <t xml:space="preserve">3.82604813575745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77348256111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07010364532471</t>
+    <t xml:space="preserve">3.77348160743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7547082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133104324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07010412216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.04382133483887</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">4.01378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05884075164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09263229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13768911361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12267065048218</t>
+    <t xml:space="preserve">4.05884027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09263277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1376895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12266969680786</t>
   </si>
   <si>
     <t xml:space="preserve">4.05508518218994</t>
@@ -485,64 +485,64 @@
     <t xml:space="preserve">4.07385921478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03255605697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91240620613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82229375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81478357315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90489673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987851142883</t>
+    <t xml:space="preserve">4.03255653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229351997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81478404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9048969745636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114283561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987803459167</t>
   </si>
   <si>
     <t xml:space="preserve">3.8110294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88612365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738750457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236880302429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110543251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8523313999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850150108337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221823692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61202907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79601049423218</t>
+    <t xml:space="preserve">3.88612389564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738774299622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85233116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61203002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7960102558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.96121788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97999119758606</t>
+    <t xml:space="preserve">3.97999167442322</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504777908325</t>
@@ -554,61 +554,61 @@
     <t xml:space="preserve">4.01753854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08887815475464</t>
+    <t xml:space="preserve">4.08887767791748</t>
   </si>
   <si>
     <t xml:space="preserve">4.14519834518433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99501013755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80727505683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225587844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170469284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518395423889</t>
+    <t xml:space="preserve">3.99500966072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742538452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474593162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80727434158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225635528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170516967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518419265747</t>
   </si>
   <si>
     <t xml:space="preserve">3.6405656337738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60452032089233</t>
+    <t xml:space="preserve">3.60452079772949</t>
   </si>
   <si>
     <t xml:space="preserve">3.54444479942322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53843712806702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54144191741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646014213562</t>
+    <t xml:space="preserve">3.53843784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54144167900085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55645990371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.60001492500305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4708526134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58799934387207</t>
+    <t xml:space="preserve">3.47085332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799910545349</t>
   </si>
   <si>
     <t xml:space="preserve">3.66459560394287</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910171508789</t>
+    <t xml:space="preserve">3.66910123825073</t>
   </si>
   <si>
     <t xml:space="preserve">3.57748651504517</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.73968935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84857654571533</t>
+    <t xml:space="preserve">3.84857630729675</t>
   </si>
   <si>
     <t xml:space="preserve">4.14144372940063</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">4.1038966178894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01002931594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04006671905518</t>
+    <t xml:space="preserve">4.01002883911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04006624221802</t>
   </si>
   <si>
     <t xml:space="preserve">4.11516046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00251960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07761383056641</t>
+    <t xml:space="preserve">4.0025200843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07761335372925</t>
   </si>
   <si>
     <t xml:space="preserve">4.16772651672363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15270805358887</t>
+    <t xml:space="preserve">4.15270853042603</t>
   </si>
   <si>
     <t xml:space="preserve">4.14895343780518</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">4.18274545669556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22029209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23906517028809</t>
+    <t xml:space="preserve">4.22029256820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2390661239624</t>
   </si>
   <si>
     <t xml:space="preserve">4.16021728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642478942871</t>
+    <t xml:space="preserve">4.12642431259155</t>
   </si>
   <si>
     <t xml:space="preserve">4.06259489059448</t>
@@ -683,34 +683,34 @@
     <t xml:space="preserve">4.03631162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13393354415894</t>
+    <t xml:space="preserve">4.13393402099609</t>
   </si>
   <si>
     <t xml:space="preserve">4.28787755966187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30289554595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33293390274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706541061401</t>
+    <t xml:space="preserve">4.30289602279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33293437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706588745117</t>
   </si>
   <si>
     <t xml:space="preserve">4.69338607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72342395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67085647583008</t>
+    <t xml:space="preserve">4.72342348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67085838317871</t>
   </si>
   <si>
     <t xml:space="preserve">4.80978155136108</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">4.79851722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72717809677124</t>
+    <t xml:space="preserve">4.7271785736084</t>
   </si>
   <si>
     <t xml:space="preserve">4.85108375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82104539871216</t>
+    <t xml:space="preserve">4.82104635238647</t>
   </si>
   <si>
     <t xml:space="preserve">4.83606481552124</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">5.07056093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13733053207397</t>
+    <t xml:space="preserve">5.13733100891113</t>
   </si>
   <si>
     <t xml:space="preserve">5.10198211669922</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">5.0744891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12947559356689</t>
+    <t xml:space="preserve">5.12947607040405</t>
   </si>
   <si>
     <t xml:space="preserve">5.16875171661377</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">5.23552131652832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33371162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34156799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3769154548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20410060882568</t>
+    <t xml:space="preserve">5.33371210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3415675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37691593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20410108566284</t>
   </si>
   <si>
     <t xml:space="preserve">5.28265285491943</t>
@@ -779,28 +779,28 @@
     <t xml:space="preserve">5.22373867034912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05092287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15696954727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29050874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2669415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34942245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38477039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21588277816772</t>
+    <t xml:space="preserve">5.05092334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15696907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29050827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26694202423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36906099319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34942197799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3847713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21588325500488</t>
   </si>
   <si>
     <t xml:space="preserve">5.219810962677</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">5.32978439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32585668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25123262405396</t>
+    <t xml:space="preserve">5.32585620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25123167037964</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298774719238</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61650133132935</t>
+    <t xml:space="preserve">5.61650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">5.57722473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5418758392334</t>
+    <t xml:space="preserve">5.54187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">5.63221120834351</t>
@@ -839,61 +839,61 @@
     <t xml:space="preserve">5.62435626983643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5065279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53794860839844</t>
+    <t xml:space="preserve">5.50652742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53794813156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5536584854126</t>
+    <t xml:space="preserve">5.55365896224976</t>
   </si>
   <si>
     <t xml:space="preserve">5.50259971618652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41226387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52223825454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61257314682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69112539291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789546966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87572431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076393127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73432970046997</t>
+    <t xml:space="preserve">5.41226434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52223777770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61257362365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69112586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789594650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87572383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076345443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73433017730713</t>
   </si>
   <si>
     <t xml:space="preserve">5.64006662368774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65970420837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72647476196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6832709312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67148780822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65577697753906</t>
+    <t xml:space="preserve">5.65970468521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72647428512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68327045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67148733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6557765007019</t>
   </si>
   <si>
     <t xml:space="preserve">5.77753305435181</t>
@@ -902,25 +902,25 @@
     <t xml:space="preserve">5.77360582351685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86786890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83644819259644</t>
+    <t xml:space="preserve">5.86786842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83644723892212</t>
   </si>
   <si>
     <t xml:space="preserve">5.82466506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84037494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82859230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87179613113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93463802337646</t>
+    <t xml:space="preserve">5.8403754234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8285927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87179660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93463754653931</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034837722778</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">5.90714502334595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7971715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70290851593018</t>
+    <t xml:space="preserve">5.79717111587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70290803909302</t>
   </si>
   <si>
     <t xml:space="preserve">5.78931617736816</t>
@@ -944,22 +944,22 @@
     <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70683622360229</t>
+    <t xml:space="preserve">5.79324436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70683670043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936931610107</t>
+    <t xml:space="preserve">5.56936979293823</t>
   </si>
   <si>
     <t xml:space="preserve">5.46725130081177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59293508529663</t>
+    <t xml:space="preserve">5.59293556213379</t>
   </si>
   <si>
     <t xml:space="preserve">5.66756010055542</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">5.41619205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39262628555298</t>
+    <t xml:space="preserve">5.39262580871582</t>
   </si>
   <si>
     <t xml:space="preserve">5.45939588546753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75003957748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75396728515625</t>
+    <t xml:space="preserve">5.75004005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76182270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75396680831909</t>
   </si>
   <si>
     <t xml:space="preserve">5.80109930038452</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">5.80895471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91499996185303</t>
+    <t xml:space="preserve">5.91500043869019</t>
   </si>
   <si>
     <t xml:space="preserve">5.87965154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8521580696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84430265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001300811768</t>
+    <t xml:space="preserve">5.85215854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84430313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001348495483</t>
   </si>
   <si>
     <t xml:space="preserve">5.84823083877563</t>
@@ -1016,64 +1016,64 @@
     <t xml:space="preserve">5.72254657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69505262374878</t>
+    <t xml:space="preserve">5.69505310058594</t>
   </si>
   <si>
     <t xml:space="preserve">5.6636323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64792156219482</t>
+    <t xml:space="preserve">5.64792203903198</t>
   </si>
   <si>
     <t xml:space="preserve">5.71861934661865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83252048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76575040817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11530923843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08388757705688</t>
+    <t xml:space="preserve">5.83252000808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76575088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11530828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
     <t xml:space="preserve">6.26063060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24492073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31169033050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29990720748901</t>
+    <t xml:space="preserve">6.2449197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31168985366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776166915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29990768432617</t>
   </si>
   <si>
     <t xml:space="preserve">6.29205179214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25670385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706579208374</t>
+    <t xml:space="preserve">6.25670337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23706531524658</t>
   </si>
   <si>
     <t xml:space="preserve">6.25277614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2645583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20171689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23313808441162</t>
+    <t xml:space="preserve">6.26455879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20171642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">6.06032228469849</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">6.00926303863525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1270923614502</t>
+    <t xml:space="preserve">6.12709140777588</t>
   </si>
   <si>
     <t xml:space="preserve">6.22528219223022</t>
@@ -1091,37 +1091,37 @@
     <t xml:space="preserve">6.28026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37060403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3745322227478</t>
+    <t xml:space="preserve">6.37060451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37453174591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39809894561768</t>
+    <t xml:space="preserve">6.39809799194336</t>
   </si>
   <si>
     <t xml:space="preserve">6.45308494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58662414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339279174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53949213027954</t>
+    <t xml:space="preserve">6.58662366867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53949165344238</t>
   </si>
   <si>
     <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63768339157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5630578994751</t>
+    <t xml:space="preserve">6.63768291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.71230697631836</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">6.83013582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68874311447144</t>
+    <t xml:space="preserve">6.68874216079712</t>
   </si>
   <si>
     <t xml:space="preserve">6.79086065292358</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">6.72409152984619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77907657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75551128387451</t>
+    <t xml:space="preserve">6.77907752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75551271438599</t>
   </si>
   <si>
     <t xml:space="preserve">6.76336622238159</t>
@@ -1154,88 +1154,88 @@
     <t xml:space="preserve">6.85762929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8615574836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81049823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70445156097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91261720657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99902391433716</t>
+    <t xml:space="preserve">6.86155700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81049776077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91261625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9990234375</t>
   </si>
   <si>
     <t xml:space="preserve">6.99116897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33287143707275</t>
+    <t xml:space="preserve">7.33287191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.40356874465942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58031225204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5410361289978</t>
+    <t xml:space="preserve">7.58031272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54103708267212</t>
   </si>
   <si>
     <t xml:space="preserve">7.55281925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46641063690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783372879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60387849807739</t>
+    <t xml:space="preserve">7.46641111373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60387802124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.62351608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66672039031982</t>
+    <t xml:space="preserve">7.66671991348267</t>
   </si>
   <si>
     <t xml:space="preserve">7.8041877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7570538520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88666772842407</t>
+    <t xml:space="preserve">7.75705528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88666820526123</t>
   </si>
   <si>
     <t xml:space="preserve">7.93379926681519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91808748245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310052871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87488269805908</t>
+    <t xml:space="preserve">7.91808700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8748836517334</t>
   </si>
   <si>
     <t xml:space="preserve">7.74055910110474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65886497497559</t>
+    <t xml:space="preserve">7.65886449813843</t>
   </si>
   <si>
     <t xml:space="preserve">7.31951856613159</t>
@@ -1247,13 +1247,13 @@
     <t xml:space="preserve">7.53161001205444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23782300949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610326766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24410772323608</t>
+    <t xml:space="preserve">7.23782348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24410820007324</t>
   </si>
   <si>
     <t xml:space="preserve">7.30066585540771</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">7.49076223373413</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59131002426147</t>
+    <t xml:space="preserve">7.59130954742432</t>
   </si>
   <si>
     <t xml:space="preserve">7.69657135009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77355194091797</t>
+    <t xml:space="preserve">7.77355241775513</t>
   </si>
   <si>
     <t xml:space="preserve">7.80026006698608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77826547622681</t>
+    <t xml:space="preserve">7.77826452255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.83325099945068</t>
@@ -1283,34 +1283,34 @@
     <t xml:space="preserve">7.94950914382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96914625167847</t>
+    <t xml:space="preserve">7.96914768218994</t>
   </si>
   <si>
     <t xml:space="preserve">7.52061319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83010911941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9612922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08304691314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090423583984</t>
+    <t xml:space="preserve">7.83010959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96129083633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08304786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090232849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.94165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95343637466431</t>
+    <t xml:space="preserve">7.95343685150146</t>
   </si>
   <si>
     <t xml:space="preserve">8.04377174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11054229736328</t>
+    <t xml:space="preserve">8.11054039001465</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">8.07126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.867027759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83953475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6949987411499</t>
+    <t xml:space="preserve">7.86702871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8395357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499778747559</t>
   </si>
   <si>
     <t xml:space="preserve">7.71070909500122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64158344268799</t>
+    <t xml:space="preserve">7.64158248901367</t>
   </si>
   <si>
     <t xml:space="preserve">7.67300367355347</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">7.61487531661987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6557240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85524654388428</t>
+    <t xml:space="preserve">7.65572309494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85524559020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.59445190429688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65415191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59602212905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56146001815796</t>
+    <t xml:space="preserve">7.65415143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.596022605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56146097183228</t>
   </si>
   <si>
     <t xml:space="preserve">7.75312757492065</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">7.83168077468872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82696580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554653167725</t>
+    <t xml:space="preserve">7.82696676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554605484009</t>
   </si>
   <si>
     <t xml:space="preserve">8.03897857666016</t>
@@ -1376,64 +1376,64 @@
     <t xml:space="preserve">8.08750534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01633453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96942710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97427940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98560190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14816093444824</t>
+    <t xml:space="preserve">8.01633548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96942663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97427892684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9856014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14815998077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.21690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93222427368164</t>
+    <t xml:space="preserve">7.9322247505188</t>
   </si>
   <si>
     <t xml:space="preserve">7.86105442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85943794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86752462387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43727016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41947603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125551223755</t>
+    <t xml:space="preserve">7.85943746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87884616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86752414703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43726825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4194769859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125694274902</t>
   </si>
   <si>
     <t xml:space="preserve">7.19626140594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43079948425293</t>
+    <t xml:space="preserve">7.43079900741577</t>
   </si>
   <si>
     <t xml:space="preserve">7.40491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4259467124939</t>
+    <t xml:space="preserve">7.42594766616821</t>
   </si>
   <si>
     <t xml:space="preserve">7.10568189620972</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">6.59293460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43441915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84849882125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805219650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10729932785034</t>
+    <t xml:space="preserve">6.43441867828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8484992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10729885101318</t>
   </si>
   <si>
     <t xml:space="preserve">6.92613887786865</t>
@@ -1460,25 +1460,25 @@
     <t xml:space="preserve">6.81776714324951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22214221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20111465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1477370262146</t>
+    <t xml:space="preserve">7.2221417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20111417770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14773750305176</t>
   </si>
   <si>
     <t xml:space="preserve">7.2641978263855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61681222915649</t>
+    <t xml:space="preserve">7.61681175231934</t>
   </si>
   <si>
     <t xml:space="preserve">7.5860800743103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415782928467</t>
+    <t xml:space="preserve">7.70415735244751</t>
   </si>
   <si>
     <t xml:space="preserve">7.66857290267944</t>
@@ -1487,79 +1487,79 @@
     <t xml:space="preserve">7.63783979415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78179693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70739269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282592773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62975263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6944522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82223510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95163440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05353736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001697540283</t>
+    <t xml:space="preserve">7.78179740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70739221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282354354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62975168228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69445276260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886831283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82223463058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95163488388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001745223999</t>
   </si>
   <si>
     <t xml:space="preserve">8.07294750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06809520721436</t>
+    <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
     <t xml:space="preserve">8.19264316558838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29778003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31395435333252</t>
+    <t xml:space="preserve">8.25329780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969192504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31395530700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.27756118774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18455505371094</t>
+    <t xml:space="preserve">8.18455410003662</t>
   </si>
   <si>
     <t xml:space="preserve">8.23307991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21286010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28564739227295</t>
+    <t xml:space="preserve">8.21286106109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28564929962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.24925518035889</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">8.12794303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24521160125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13198661804199</t>
+    <t xml:space="preserve">8.24521064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13198566436768</t>
   </si>
   <si>
     <t xml:space="preserve">8.06647682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1764669418335</t>
+    <t xml:space="preserve">8.17646789550781</t>
   </si>
   <si>
     <t xml:space="preserve">8.07941722869873</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">8.14007377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08588790893555</t>
+    <t xml:space="preserve">8.08588695526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.12389850616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20881652832031</t>
+    <t xml:space="preserve">8.20881748199463</t>
   </si>
   <si>
     <t xml:space="preserve">8.2249927520752</t>
@@ -1601,28 +1601,28 @@
     <t xml:space="preserve">8.30991077423096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22903633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33417415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182552337646</t>
+    <t xml:space="preserve">8.22903537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18859958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33417510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182456970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.3179988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60510540008545</t>
+    <t xml:space="preserve">8.60510635375977</t>
   </si>
   <si>
     <t xml:space="preserve">8.77898597717285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77089786529541</t>
+    <t xml:space="preserve">8.77089977264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.89625549316406</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">8.95691108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03778648376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04183006286621</t>
+    <t xml:space="preserve">9.03778743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04183101654053</t>
   </si>
   <si>
     <t xml:space="preserve">9.11866188049316</t>
@@ -1643,28 +1643,28 @@
     <t xml:space="preserve">9.22379970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33298110961914</t>
+    <t xml:space="preserve">9.33298206329346</t>
   </si>
   <si>
     <t xml:space="preserve">9.32084941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22784233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4178991317749</t>
+    <t xml:space="preserve">9.22784328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41790008544922</t>
   </si>
   <si>
     <t xml:space="preserve">9.44620513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61604499816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48260021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3127613067627</t>
+    <t xml:space="preserve">9.61604404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48259830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31276226043701</t>
   </si>
   <si>
     <t xml:space="preserve">9.39768028259277</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">9.30063056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28041172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19549369812012</t>
+    <t xml:space="preserve">9.2804126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1954927444458</t>
   </si>
   <si>
     <t xml:space="preserve">9.1146183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67789268493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65363121032715</t>
+    <t xml:space="preserve">8.67789173126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65363025665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.05191993713379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89987421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88531732559204</t>
+    <t xml:space="preserve">7.89987468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88531684875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.1198558807373</t>
@@ -1703,73 +1703,73 @@
     <t xml:space="preserve">7.83355665206909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4680027961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287437438965</t>
+    <t xml:space="preserve">7.46800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287389755249</t>
   </si>
   <si>
     <t xml:space="preserve">7.24155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16067695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05715656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080888748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595659255981</t>
+    <t xml:space="preserve">7.1606764793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05715703964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595611572266</t>
   </si>
   <si>
     <t xml:space="preserve">7.33860206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47770690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59093189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.987220287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0082483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94516468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96619272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369941711426</t>
+    <t xml:space="preserve">7.47770738601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59093141555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92251873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98721933364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00824737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94516515731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96619319915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88369989395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.78017997741699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78988456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76238679885864</t>
+    <t xml:space="preserve">7.78988409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76238536834717</t>
   </si>
   <si>
     <t xml:space="preserve">7.74297761917114</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">7.84164428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9807505607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91119718551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85134887695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74944734573364</t>
+    <t xml:space="preserve">7.98074960708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91119766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474674224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8513503074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7494478225708</t>
   </si>
   <si>
     <t xml:space="preserve">7.32889747619629</t>
@@ -1802,109 +1802,109 @@
     <t xml:space="preserve">7.22537660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2496395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4421215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49388217926025</t>
+    <t xml:space="preserve">7.24963855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212102890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49388265609741</t>
   </si>
   <si>
     <t xml:space="preserve">7.39521455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26581478118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890592575073</t>
+    <t xml:space="preserve">7.26581430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890640258789</t>
   </si>
   <si>
     <t xml:space="preserve">7.35477685928345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0183367729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0523042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0992112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07980108261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99245595932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875375747681</t>
+    <t xml:space="preserve">7.01833629608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05230522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09921169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0798020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99245643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875423431396</t>
   </si>
   <si>
     <t xml:space="preserve">7.58446216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62328147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55534648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54079008102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64430904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93707656860352</t>
+    <t xml:space="preserve">7.62328100204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56828641891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55534791946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54078960418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93707799911499</t>
   </si>
   <si>
     <t xml:space="preserve">7.90634489059448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92898988723755</t>
+    <t xml:space="preserve">7.92898941040039</t>
   </si>
   <si>
     <t xml:space="preserve">7.78826808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88046503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781812667847</t>
+    <t xml:space="preserve">7.88046550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781908035278</t>
   </si>
   <si>
     <t xml:space="preserve">7.673424243927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5715217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83193969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92575454711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01795196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00339508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3988733291626</t>
+    <t xml:space="preserve">7.57152318954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83194065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9257550239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01795101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80767726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00339603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39887523651123</t>
   </si>
   <si>
     <t xml:space="preserve">8.2371244430542</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">8.26947402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18051147460938</t>
+    <t xml:space="preserve">8.18051052093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034942626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92051696777344</t>
+    <t xml:space="preserve">8.35034847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83559894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92051887512207</t>
   </si>
   <si>
     <t xml:space="preserve">9.08226680755615</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">9.18740463256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02161121368408</t>
+    <t xml:space="preserve">9.02161026000977</t>
   </si>
   <si>
     <t xml:space="preserve">9.07418060302734</t>
@@ -1955,58 +1955,58 @@
     <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17931747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23188591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34915542602539</t>
+    <t xml:space="preserve">9.17931842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2318868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34915637969971</t>
   </si>
   <si>
     <t xml:space="preserve">9.38150596618652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32489395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36532974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5917797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40576839447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59582424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65648078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56751823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4664249420166</t>
+    <t xml:space="preserve">9.3248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26827907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36533069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40576934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65647983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56751728057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45833587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46642398834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.47451210021973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81014442443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.016375541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83036041259766</t>
+    <t xml:space="preserve">9.81014347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0163745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83036231994629</t>
   </si>
   <si>
     <t xml:space="preserve">10.036060333252</t>
@@ -2015,49 +2015,49 @@
     <t xml:space="preserve">9.84943866729736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7955265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79967308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73331737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47619819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18589687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50162029266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44356155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27767467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17150974273682</t>
+    <t xml:space="preserve">9.79552745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629570007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79967212677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73331928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4761962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18589782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50162124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44356060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27767562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17151069641113</t>
   </si>
   <si>
     <t xml:space="preserve">7.96912908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12506198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0305061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22625255584717</t>
+    <t xml:space="preserve">8.12506008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03050708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22625160217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.23620510101318</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">8.11842632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21132183074951</t>
+    <t xml:space="preserve">8.2113208770752</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728321075439</t>
+    <t xml:space="preserve">8.00728225708008</t>
   </si>
   <si>
     <t xml:space="preserve">8.08690738677979</t>
@@ -2081,19 +2081,19 @@
     <t xml:space="preserve">8.0388011932373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6738543510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375991821289</t>
+    <t xml:space="preserve">7.87955141067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385387420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69375944137573</t>
   </si>
   <si>
     <t xml:space="preserve">7.59091091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77670240402222</t>
+    <t xml:space="preserve">7.77670288085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77172565460205</t>
@@ -2102,43 +2102,43 @@
     <t xml:space="preserve">7.70868921279907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7136664390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70039510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73357248306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58925104141235</t>
+    <t xml:space="preserve">7.71366548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70039558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7335729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58925151824951</t>
   </si>
   <si>
     <t xml:space="preserve">7.62574672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50299167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72859573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82978534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9193639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12340354919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12837886810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08359050750732</t>
+    <t xml:space="preserve">7.50299119949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55109882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72859621047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82978630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91936492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1234016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08359146118164</t>
   </si>
   <si>
     <t xml:space="preserve">8.01557731628418</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">7.96249485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13667297363281</t>
+    <t xml:space="preserve">8.13667488098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.17814445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21961688995361</t>
+    <t xml:space="preserve">8.2196159362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.60529899597168</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">8.86656951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54723930358887</t>
+    <t xml:space="preserve">8.54724025726318</t>
   </si>
   <si>
     <t xml:space="preserve">8.38550090789795</t>
@@ -2177,22 +2177,22 @@
     <t xml:space="preserve">8.51406288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45600318908691</t>
+    <t xml:space="preserve">8.4560022354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.30670642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48088645935059</t>
+    <t xml:space="preserve">8.48088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">8.29094696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3232946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704879760742</t>
+    <t xml:space="preserve">8.32329559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704784393311</t>
   </si>
   <si>
     <t xml:space="preserve">8.06700038909912</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">8.24283981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08027172088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86462211608887</t>
+    <t xml:space="preserve">8.08027267456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86462163925171</t>
   </si>
   <si>
     <t xml:space="preserve">7.36530685424805</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">7.45820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57266473770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39184761047363</t>
+    <t xml:space="preserve">7.57266330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39184904098511</t>
   </si>
   <si>
     <t xml:space="preserve">7.22098684310913</t>
@@ -2225,19 +2225,19 @@
     <t xml:space="preserve">7.38355398178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38853120803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73191261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41839027404785</t>
+    <t xml:space="preserve">7.38853025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7319130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41839170455933</t>
   </si>
   <si>
     <t xml:space="preserve">7.25084543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42502498626709</t>
+    <t xml:space="preserve">7.42502593994141</t>
   </si>
   <si>
     <t xml:space="preserve">7.06173658370972</t>
@@ -2249,58 +2249,58 @@
     <t xml:space="preserve">7.31388187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25914001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56436967849731</t>
+    <t xml:space="preserve">7.25913953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56436824798584</t>
   </si>
   <si>
     <t xml:space="preserve">7.4449315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76509046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73854875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92765712738037</t>
+    <t xml:space="preserve">7.76509141921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73854827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92765760421753</t>
   </si>
   <si>
     <t xml:space="preserve">7.77836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15989780426025</t>
+    <t xml:space="preserve">7.82646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030115127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15989685058594</t>
   </si>
   <si>
     <t xml:space="preserve">8.18975734710693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89116334915161</t>
+    <t xml:space="preserve">7.89116382598877</t>
   </si>
   <si>
     <t xml:space="preserve">7.81651449203491</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16985034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09852027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76343202590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79660892486572</t>
+    <t xml:space="preserve">8.16985130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09851932525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76343059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79660797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.03216552734375</t>
@@ -2309,49 +2309,49 @@
     <t xml:space="preserve">7.98903512954712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84969186782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86130332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90443468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00064754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02718925476074</t>
+    <t xml:space="preserve">7.84969091415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86130380630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581125259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840782165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90443420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00064659118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02719020843506</t>
   </si>
   <si>
     <t xml:space="preserve">7.65394735336304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72361850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89614057540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1267204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9591760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17482662200928</t>
+    <t xml:space="preserve">7.72361898422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89614105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12672138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95917654037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17482757568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.33988380432129</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55968189239502</t>
+    <t xml:space="preserve">8.55967998504639</t>
   </si>
   <si>
     <t xml:space="preserve">8.46014976501465</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">8.44770908355713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42697238922119</t>
+    <t xml:space="preserve">8.42697334289551</t>
   </si>
   <si>
     <t xml:space="preserve">8.63018131256104</t>
@@ -2381,43 +2381,43 @@
     <t xml:space="preserve">8.47673797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37720775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60944652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95780563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99927711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1651611328125</t>
+    <t xml:space="preserve">8.37720680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60944557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95780658721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16516208648682</t>
   </si>
   <si>
     <t xml:space="preserve">9.13198471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23566341400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48449325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54255104064941</t>
+    <t xml:space="preserve">9.23566436767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48449230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54255199432373</t>
   </si>
   <si>
     <t xml:space="preserve">9.52596282958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50937557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42643070220947</t>
+    <t xml:space="preserve">9.50937461853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42643165588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.31445789337158</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">9.43057823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38496017456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51766872406006</t>
+    <t xml:space="preserve">9.38496112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51766967773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.73746681213379</t>
@@ -2438,22 +2438,22 @@
     <t xml:space="preserve">9.70014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33934116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23151683807373</t>
+    <t xml:space="preserve">9.57158184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23151588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.28957557678223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35178279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38910675048828</t>
+    <t xml:space="preserve">9.35178375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">9.19833946228027</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">9.11539649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12369060516357</t>
+    <t xml:space="preserve">9.12369155883789</t>
   </si>
   <si>
     <t xml:space="preserve">9.04074859619141</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">9.06148433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01586532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05319023132324</t>
+    <t xml:space="preserve">9.01586627960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05318927764893</t>
   </si>
   <si>
     <t xml:space="preserve">8.93292331695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12783908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88315773010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82509803771973</t>
+    <t xml:space="preserve">9.12783718109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88315677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82509899139404</t>
   </si>
   <si>
     <t xml:space="preserve">9.09880828857422</t>
@@ -2507,16 +2507,16 @@
     <t xml:space="preserve">9.58817005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29372406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1527214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25639915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15686702728271</t>
+    <t xml:space="preserve">9.29372501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25639820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15686798095703</t>
   </si>
   <si>
     <t xml:space="preserve">9.21492767333984</t>
@@ -2537,61 +2537,61 @@
     <t xml:space="preserve">8.7753324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27298736572266</t>
+    <t xml:space="preserve">9.27298831939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.107102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77118301391602</t>
+    <t xml:space="preserve">8.77118396759033</t>
   </si>
   <si>
     <t xml:space="preserve">8.97024631500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68770122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14442729949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08636569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05733776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9909839630127</t>
+    <t xml:space="preserve">9.27713489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1444263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08636665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05733680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99098300933838</t>
   </si>
   <si>
     <t xml:space="preserve">9.28128147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89559841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25279235839844</t>
+    <t xml:space="preserve">8.89559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25279331207275</t>
   </si>
   <si>
     <t xml:space="preserve">8.14994430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87457513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74186706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34042501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35867071151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327259063721</t>
+    <t xml:space="preserve">7.87457418441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74186658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34042406082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35867166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327306747437</t>
   </si>
   <si>
     <t xml:space="preserve">6.73328399658203</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53256273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73797178268433</t>
+    <t xml:space="preserve">6.53256225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73797225952148</t>
   </si>
   <si>
     <t xml:space="preserve">6.38990116119385</t>
@@ -2618,16 +2618,16 @@
     <t xml:space="preserve">6.24060487747192</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20245122909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1908392906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81788539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71503639221191</t>
+    <t xml:space="preserve">6.2024507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19083881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8178858757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71503591537476</t>
   </si>
   <si>
     <t xml:space="preserve">7.33047151565552</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">6.98542928695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87594556808472</t>
+    <t xml:space="preserve">6.87594509124756</t>
   </si>
   <si>
     <t xml:space="preserve">6.87096929550171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09159660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4233660697937</t>
+    <t xml:space="preserve">7.09159564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42336702346802</t>
   </si>
   <si>
     <t xml:space="preserve">7.59257030487061</t>
@@ -2657,28 +2657,28 @@
     <t xml:space="preserve">7.8331036567688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83144474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92931747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32715368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22264623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21601009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24255180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76977872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2641167640686</t>
+    <t xml:space="preserve">7.83144426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92931842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32715272903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22264528274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21600961685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24255228042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76977825164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26411724090576</t>
   </si>
   <si>
     <t xml:space="preserve">7.66224145889282</t>
@@ -2687,28 +2687,28 @@
     <t xml:space="preserve">7.64067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88286924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07363796234131</t>
+    <t xml:space="preserve">7.88286828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07363700866699</t>
   </si>
   <si>
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41038513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0520715713501</t>
+    <t xml:space="preserve">8.4103832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05207252502441</t>
   </si>
   <si>
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897769927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35232257843018</t>
+    <t xml:space="preserve">8.70897674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35232353210449</t>
   </si>
   <si>
     <t xml:space="preserve">8.22956943511963</t>
@@ -2729,19 +2729,19 @@
     <t xml:space="preserve">8.4725923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78777408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71312522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874423980713</t>
+    <t xml:space="preserve">8.78777313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71312427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874328613281</t>
   </si>
   <si>
     <t xml:space="preserve">8.91218662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0034236907959</t>
+    <t xml:space="preserve">9.00342273712158</t>
   </si>
   <si>
     <t xml:space="preserve">9.34763622283936</t>
@@ -2762,13 +2762,13 @@
     <t xml:space="preserve">10.2973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94897079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0443544387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2848873138428</t>
+    <t xml:space="preserve">9.94896984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0443553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2848863601685</t>
   </si>
   <si>
     <t xml:space="preserve">9.87432098388672</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0650901794434</t>
+    <t xml:space="preserve">10.065089225769</t>
   </si>
   <si>
     <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95311737060547</t>
+    <t xml:space="preserve">9.95311832427979</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595361709595</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">10.3512411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7286310195923</t>
+    <t xml:space="preserve">10.7286319732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.6996011734009</t>
@@ -2801,37 +2801,37 @@
     <t xml:space="preserve">10.6747188568115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3388004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4093027114868</t>
+    <t xml:space="preserve">10.3388013839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4093017578125</t>
   </si>
   <si>
     <t xml:space="preserve">10.4632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4010076522827</t>
+    <t xml:space="preserve">10.4010066986084</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415405273438</t>
+    <t xml:space="preserve">10.6415424346924</t>
   </si>
   <si>
     <t xml:space="preserve">10.8323106765747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7659549713135</t>
+    <t xml:space="preserve">10.7659559249878</t>
   </si>
   <si>
     <t xml:space="preserve">10.9318408966064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7783966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.633246421814</t>
+    <t xml:space="preserve">10.778395652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6332473754883</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042175292969</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">10.4300374984741</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5295677185059</t>
+    <t xml:space="preserve">10.5295686721802</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024150848389</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">10.3553886413574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.230975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4175958633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0645484924316</t>
+    <t xml:space="preserve">10.2309761047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4175968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.064549446106</t>
   </si>
   <si>
     <t xml:space="preserve">10.8654880523682</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">10.8240156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.612512588501</t>
+    <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
     <t xml:space="preserve">10.6000699996948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7493677139282</t>
+    <t xml:space="preserve">10.7493667602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.687159538269</t>
@@ -2894,40 +2894,40 @@
     <t xml:space="preserve">10.6664247512817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5337162017822</t>
+    <t xml:space="preserve">10.5337152481079</t>
   </si>
   <si>
     <t xml:space="preserve">10.6249532699585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5751867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2392692565918</t>
+    <t xml:space="preserve">10.5751876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4341840744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2392702102661</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1895027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1936511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0319128036499</t>
+    <t xml:space="preserve">10.1895036697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1936502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0319118499756</t>
   </si>
   <si>
     <t xml:space="preserve">9.81626224517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83285045623779</t>
+    <t xml:space="preserve">9.83284950256348</t>
   </si>
   <si>
     <t xml:space="preserve">9.46790313720703</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">9.44716835021973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72087860107422</t>
+    <t xml:space="preserve">9.72087955474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.5591402053833</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">9.74990749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82040882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0277671813965</t>
+    <t xml:space="preserve">9.82040977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">10.1107082366943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90335178375244</t>
+    <t xml:space="preserve">9.90335083007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.1604738235474</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">10.2102403640747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0775318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1521787643433</t>
+    <t xml:space="preserve">10.0775308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1521797180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.99044132232666</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">9.96141147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59646415710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53425693511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67111206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74576091766357</t>
+    <t xml:space="preserve">9.59646320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74576187133789</t>
   </si>
   <si>
     <t xml:space="preserve">9.96970653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2600040435791</t>
+    <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
     <t xml:space="preserve">10.3844194412231</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">10.1272964477539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2682991027832</t>
+    <t xml:space="preserve">10.2683000564575</t>
   </si>
   <si>
     <t xml:space="preserve">10.5088338851929</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">10.4134492874146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5212755203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8074254989624</t>
+    <t xml:space="preserve">10.5212745666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.807427406311</t>
   </si>
   <si>
     <t xml:space="preserve">10.7576608657837</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">10.8779268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8945169448853</t>
+    <t xml:space="preserve">10.8945159912109</t>
   </si>
   <si>
     <t xml:space="preserve">10.9359884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8157215118408</t>
+    <t xml:space="preserve">10.8157205581665</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733114242554</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">10.898663520813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8364553451538</t>
+    <t xml:space="preserve">10.8364562988281</t>
   </si>
   <si>
     <t xml:space="preserve">10.9857530593872</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">10.8447494506836</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9774589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1018724441528</t>
+    <t xml:space="preserve">10.9774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1018743515015</t>
   </si>
   <si>
     <t xml:space="preserve">11.1143140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1474914550781</t>
+    <t xml:space="preserve">11.35484790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1474905014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.15993309021</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">11.2843465805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6119699478149</t>
+    <t xml:space="preserve">11.6119709014893</t>
   </si>
   <si>
     <t xml:space="preserve">11.520733833313</t>
@@ -3116,43 +3116,43 @@
     <t xml:space="preserve">11.1226081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0355186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9442825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452192306519</t>
+    <t xml:space="preserve">11.0355195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9442806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452182769775</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9935073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1096258163452</t>
+    <t xml:space="preserve">11.2926416397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9935064315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1096267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.3999252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1303625106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4455432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2630701065063</t>
+    <t xml:space="preserve">12.1303615570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4455442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.263069152832</t>
   </si>
   <si>
     <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5948419570923</t>
+    <t xml:space="preserve">12.5948400497437</t>
   </si>
   <si>
     <t xml:space="preserve">12.4870157241821</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">12.1718330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3169832229614</t>
+    <t xml:space="preserve">12.3169822692871</t>
   </si>
   <si>
     <t xml:space="preserve">12.1842746734619</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">12.3377180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1925687789917</t>
+    <t xml:space="preserve">12.1925678253174</t>
   </si>
   <si>
     <t xml:space="preserve">12.0847434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2879524230957</t>
+    <t xml:space="preserve">12.28795337677</t>
   </si>
   <si>
     <t xml:space="preserve">12.0640068054199</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">11.9230051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9810647964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2755117416382</t>
+    <t xml:space="preserve">11.9810657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2755107879639</t>
   </si>
   <si>
     <t xml:space="preserve">12.1635389328003</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3543071746826</t>
+    <t xml:space="preserve">12.3543081283569</t>
   </si>
   <si>
     <t xml:space="preserve">12.1759805679321</t>
@@ -3221,16 +3221,16 @@
     <t xml:space="preserve">11.9437408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1179208755493</t>
+    <t xml:space="preserve">12.117919921875</t>
   </si>
   <si>
     <t xml:space="preserve">11.7820024490356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6244125366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5580587387085</t>
+    <t xml:space="preserve">11.6244115829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5580577850342</t>
   </si>
   <si>
     <t xml:space="preserve">11.5539112091064</t>
@@ -3239,25 +3239,25 @@
     <t xml:space="preserve">11.4626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5746469497681</t>
+    <t xml:space="preserve">11.5746459960938</t>
   </si>
   <si>
     <t xml:space="preserve">11.4834098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.591236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5995302200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5870876312256</t>
+    <t xml:space="preserve">11.5912342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5995283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5870885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7405319213867</t>
+    <t xml:space="preserve">11.7405300140381</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
@@ -3266,49 +3266,49 @@
     <t xml:space="preserve">11.7985906600952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8981227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9520349502563</t>
+    <t xml:space="preserve">11.8981218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9520359039307</t>
   </si>
   <si>
     <t xml:space="preserve">11.5456161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5331735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.475115776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6783237457275</t>
+    <t xml:space="preserve">11.5331745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543790817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4751138687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6783246994019</t>
   </si>
   <si>
     <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.877387046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0142412185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6949129104614</t>
+    <t xml:space="preserve">11.9064159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0142421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6949138641357</t>
   </si>
   <si>
     <t xml:space="preserve">11.8732385635376</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6617374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322378158569</t>
+    <t xml:space="preserve">11.6617364883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322368621826</t>
   </si>
   <si>
     <t xml:space="preserve">11.7446784973145</t>
@@ -3317,19 +3317,19 @@
     <t xml:space="preserve">11.6534423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.711501121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7654142379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5787925720215</t>
+    <t xml:space="preserve">11.7115020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7654132843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5787935256958</t>
   </si>
   <si>
     <t xml:space="preserve">11.164080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2055521011353</t>
+    <t xml:space="preserve">11.2055511474609</t>
   </si>
   <si>
     <t xml:space="preserve">11.305082321167</t>
@@ -3344,46 +3344,46 @@
     <t xml:space="preserve">11.3299655914307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631420135498</t>
+    <t xml:space="preserve">11.3631429672241</t>
   </si>
   <si>
     <t xml:space="preserve">11.3382587432861</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3880243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3714361190796</t>
+    <t xml:space="preserve">11.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714351654053</t>
   </si>
   <si>
     <t xml:space="preserve">11.4917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5124397277832</t>
+    <t xml:space="preserve">11.5124387741089</t>
   </si>
   <si>
     <t xml:space="preserve">11.6451473236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5622043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5248804092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5953807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5497646331787</t>
+    <t xml:space="preserve">11.5622053146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.524881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5953817367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5497636795044</t>
   </si>
   <si>
     <t xml:space="preserve">11.66588306427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.931300163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8607988357544</t>
+    <t xml:space="preserve">11.9312992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8607997894287</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409997940063</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">11.806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0266828536987</t>
+    <t xml:space="preserve">12.026683807373</t>
   </si>
   <si>
     <t xml:space="preserve">12.1013317108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2133054733276</t>
+    <t xml:space="preserve">12.2133045196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.2423343658447</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">12.1967163085938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3086891174316</t>
+    <t xml:space="preserve">12.3086881637573</t>
   </si>
   <si>
     <t xml:space="preserve">12.1510972976685</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">12.0391254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690929412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778558731079</t>
+    <t xml:space="preserve">11.8690919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778549194336</t>
   </si>
   <si>
     <t xml:space="preserve">12.1220674514771</t>
@@ -3431,46 +3431,46 @@
     <t xml:space="preserve">12.2215986251831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3335704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7151069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5367813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3708963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7773151397705</t>
+    <t xml:space="preserve">12.333571434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7151079177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5367803573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3708953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7773141860962</t>
   </si>
   <si>
     <t xml:space="preserve">12.8975811004639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2293510437012</t>
+    <t xml:space="preserve">13.2293519973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.3827953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4532957077026</t>
+    <t xml:space="preserve">13.453296661377</t>
   </si>
   <si>
     <t xml:space="preserve">13.5942993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4698848724365</t>
+    <t xml:space="preserve">13.4698858261108</t>
   </si>
   <si>
     <t xml:space="preserve">13.4201202392578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3496189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2252044677734</t>
+    <t xml:space="preserve">13.3496179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2252054214478</t>
   </si>
   <si>
     <t xml:space="preserve">13.4781799316406</t>
@@ -3479,64 +3479,64 @@
     <t xml:space="preserve">13.2169103622437</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0510244369507</t>
+    <t xml:space="preserve">13.051025390625</t>
   </si>
   <si>
     <t xml:space="preserve">13.1588506698608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1837339401245</t>
+    <t xml:space="preserve">13.1837329864502</t>
   </si>
   <si>
     <t xml:space="preserve">13.2583818435669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1629981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2625293731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8644046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8685512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7939033508301</t>
+    <t xml:space="preserve">13.1629972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2625284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9514942169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8644037246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8685522079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7939023971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.9349060058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312273025513</t>
+    <t xml:space="preserve">12.8312282562256</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482843399048</t>
   </si>
   <si>
-    <t xml:space="preserve">12.574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6611948013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9763765335083</t>
+    <t xml:space="preserve">12.5741052627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6611938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9763784408569</t>
   </si>
   <si>
     <t xml:space="preserve">13.2376461029053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1215267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0095539093018</t>
+    <t xml:space="preserve">13.1215257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0095548629761</t>
   </si>
   <si>
     <t xml:space="preserve">13.2417936325073</t>
@@ -3545,34 +3545,34 @@
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9431991577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8768444061279</t>
+    <t xml:space="preserve">12.9432001113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8768453598022</t>
   </si>
   <si>
     <t xml:space="preserve">12.9971122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7690210342407</t>
+    <t xml:space="preserve">12.7690200805664</t>
   </si>
   <si>
     <t xml:space="preserve">12.6446056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9722309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888181686401</t>
+    <t xml:space="preserve">12.9722299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888172149658</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9929647445679</t>
+    <t xml:space="preserve">13.1090860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9929656982422</t>
   </si>
   <si>
     <t xml:space="preserve">13.2044696807861</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">13.1173782348633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.602593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7850685119629</t>
+    <t xml:space="preserve">13.6025943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7850675582886</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523590087891</t>
@@ -3593,22 +3593,22 @@
     <t xml:space="preserve">13.8016557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7726249694824</t>
+    <t xml:space="preserve">13.7726259231567</t>
   </si>
   <si>
     <t xml:space="preserve">13.7975091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9219226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9799823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.627477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7270059585571</t>
+    <t xml:space="preserve">13.9219236373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6274766921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7270069122314</t>
   </si>
   <si>
     <t xml:space="preserve">13.69797706604</t>
@@ -3620,58 +3620,58 @@
     <t xml:space="preserve">13.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0173063278198</t>
+    <t xml:space="preserve">14.0878095626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0173072814941</t>
   </si>
   <si>
     <t xml:space="preserve">14.224663734436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3324890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.295166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3532257080078</t>
+    <t xml:space="preserve">14.3324880599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1583089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2951641082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3532238006592</t>
   </si>
   <si>
     <t xml:space="preserve">14.2619876861572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251344680786</t>
+    <t xml:space="preserve">14.3076066970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251316070557</t>
   </si>
   <si>
     <t xml:space="preserve">14.3006258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8255081176758</t>
+    <t xml:space="preserve">13.8255071640015</t>
   </si>
   <si>
     <t xml:space="preserve">13.859751701355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6542949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3161487579346</t>
+    <t xml:space="preserve">13.6542940139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3161468505859</t>
   </si>
   <si>
     <t xml:space="preserve">13.2605028152466</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">13.1363735198975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1834564208984</t>
+    <t xml:space="preserve">13.1834573745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.5515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9068355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6457328796387</t>
+    <t xml:space="preserve">13.9068365097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.645733833313</t>
   </si>
   <si>
     <t xml:space="preserve">13.4488382339478</t>
@@ -3704,16 +3704,16 @@
     <t xml:space="preserve">13.3974742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4445581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9951219558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7639827728271</t>
+    <t xml:space="preserve">13.4445571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258836746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9951229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7639837265015</t>
   </si>
   <si>
     <t xml:space="preserve">12.965160369873</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">13.2519416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2134208679199</t>
+    <t xml:space="preserve">13.2134189605713</t>
   </si>
   <si>
     <t xml:space="preserve">13.4531183242798</t>
@@ -3740,10 +3740,10 @@
     <t xml:space="preserve">13.4873609542847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6842575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562217712402</t>
+    <t xml:space="preserve">13.6842565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562227249146</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589496612549</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">13.0122423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7741441726685</t>
+    <t xml:space="preserve">13.7741451263428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8511905670166</t>
@@ -3764,19 +3764,19 @@
     <t xml:space="preserve">13.6114912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2861862182617</t>
+    <t xml:space="preserve">13.2861852645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.0293655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1920175552368</t>
+    <t xml:space="preserve">13.1920166015625</t>
   </si>
   <si>
     <t xml:space="preserve">13.1320934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7597036361694</t>
+    <t xml:space="preserve">12.7597026824951</t>
   </si>
   <si>
     <t xml:space="preserve">12.3616313934326</t>
@@ -3785,16 +3785,16 @@
     <t xml:space="preserve">12.5499658584595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4900426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4857606887817</t>
+    <t xml:space="preserve">12.4900417327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4857616424561</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.85387134552</t>
+    <t xml:space="preserve">12.8538703918457</t>
   </si>
   <si>
     <t xml:space="preserve">12.900954246521</t>
@@ -3803,19 +3803,19 @@
     <t xml:space="preserve">12.7254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7682638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8495893478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0550470352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6157703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286125183105</t>
+    <t xml:space="preserve">12.7682628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8495903015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6157722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286134719849</t>
   </si>
   <si>
     <t xml:space="preserve">13.7784242630005</t>
@@ -3824,34 +3824,34 @@
     <t xml:space="preserve">13.6799764633179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.543004989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4103155136108</t>
+    <t xml:space="preserve">13.5430059432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4103145599365</t>
   </si>
   <si>
     <t xml:space="preserve">13.2776250839233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4301156997681</t>
+    <t xml:space="preserve">12.4301166534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.7168989181519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7768249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0234842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0363264083862</t>
+    <t xml:space="preserve">12.7768239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0234832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0363254547119</t>
   </si>
   <si>
     <t xml:space="preserve">11.8351488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576778411865</t>
+    <t xml:space="preserve">10.9576787948608</t>
   </si>
   <si>
     <t xml:space="preserve">10.8720712661743</t>
@@ -3863,31 +3863,31 @@
     <t xml:space="preserve">11.783784866333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3172273635864</t>
+    <t xml:space="preserve">11.3172264099121</t>
   </si>
   <si>
     <t xml:space="preserve">11.5954494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8265886306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8950729370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157232284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9892406463623</t>
+    <t xml:space="preserve">11.8265867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.895073890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9892416000366</t>
   </si>
   <si>
     <t xml:space="preserve">12.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849605560303</t>
+    <t xml:space="preserve">12.0277633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849615097046</t>
   </si>
   <si>
     <t xml:space="preserve">11.8479900360107</t>
@@ -3896,10 +3896,10 @@
     <t xml:space="preserve">11.9507179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3145475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1989784240723</t>
+    <t xml:space="preserve">12.314546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1989774703979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2332210540771</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">12.3102674484253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2631826400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9549999237061</t>
+    <t xml:space="preserve">12.26318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
     <t xml:space="preserve">12.1262121200562</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">12.3188285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2203788757324</t>
+    <t xml:space="preserve">12.2203798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.9464378356934</t>
@@ -3929,16 +3929,16 @@
     <t xml:space="preserve">11.9079151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9036331176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8009052276611</t>
+    <t xml:space="preserve">11.9036340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
     <t xml:space="preserve">12.0834093093872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0705680847168</t>
+    <t xml:space="preserve">12.0705671310425</t>
   </si>
   <si>
     <t xml:space="preserve">11.8651113510132</t>
@@ -3950,10 +3950,10 @@
     <t xml:space="preserve">11.2444620132446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2530221939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2787055969238</t>
+    <t xml:space="preserve">11.253023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2787046432495</t>
   </si>
   <si>
     <t xml:space="preserve">11.407114982605</t>
@@ -3962,19 +3962,19 @@
     <t xml:space="preserve">11.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771514892578</t>
+    <t xml:space="preserve">11.3771524429321</t>
   </si>
   <si>
     <t xml:space="preserve">11.0775270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090368270874</t>
+    <t xml:space="preserve">11.0903692245483</t>
   </si>
   <si>
     <t xml:space="preserve">10.5724477767944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0545253753662</t>
+    <t xml:space="preserve">10.0545272827148</t>
   </si>
   <si>
     <t xml:space="preserve">10.080207824707</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6109714508057</t>
+    <t xml:space="preserve">10.5938501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6109704971313</t>
   </si>
   <si>
     <t xml:space="preserve">10.8292675018311</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">11.1668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1403951644897</t>
+    <t xml:space="preserve">11.1403942108154</t>
   </si>
   <si>
     <t xml:space="preserve">11.3435907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5158653259277</t>
+    <t xml:space="preserve">11.5158643722534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969738006592</t>
+    <t xml:space="preserve">11.6969728469849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6351318359375</t>
@@ -4025,31 +4025,31 @@
     <t xml:space="preserve">11.560037612915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1580648422241</t>
+    <t xml:space="preserve">11.1580638885498</t>
   </si>
   <si>
     <t xml:space="preserve">11.4893608093262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3745107650757</t>
+    <t xml:space="preserve">11.37451171875</t>
   </si>
   <si>
     <t xml:space="preserve">11.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62968254089355</t>
+    <t xml:space="preserve">10.6368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62968349456787</t>
   </si>
   <si>
     <t xml:space="preserve">9.14378261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13053035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74453163146973</t>
+    <t xml:space="preserve">9.13052940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74453353881836</t>
   </si>
   <si>
     <t xml:space="preserve">9.44415664672852</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">9.57667636871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89030361175537</t>
+    <t xml:space="preserve">9.89030265808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.92122364044189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1818447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4645509719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191568374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4689674377441</t>
+    <t xml:space="preserve">10.1818437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4645500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4689683914185</t>
   </si>
   <si>
     <t xml:space="preserve">10.4778022766113</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">10.3894567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0890808105469</t>
+    <t xml:space="preserve">10.0890817642212</t>
   </si>
   <si>
     <t xml:space="preserve">10.1244201660156</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">9.9786491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2171812057495</t>
+    <t xml:space="preserve">10.2171821594238</t>
   </si>
   <si>
     <t xml:space="preserve">10.7384214401245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5970697402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3585367202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83287906646729</t>
+    <t xml:space="preserve">10.5970687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3585357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83287811279297</t>
   </si>
   <si>
     <t xml:space="preserve">9.85054779052734</t>
@@ -4118,46 +4118,46 @@
     <t xml:space="preserve">10.5661478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3408660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0934982299805</t>
+    <t xml:space="preserve">10.3408670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0934991836548</t>
   </si>
   <si>
     <t xml:space="preserve">9.92564105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0007352828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6809978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6500759124756</t>
+    <t xml:space="preserve">10.0758295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0007343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6809968948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6500768661499</t>
   </si>
   <si>
     <t xml:space="preserve">10.999041557312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8841915130615</t>
+    <t xml:space="preserve">10.8841924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.8267679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5573139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.959285736084</t>
+    <t xml:space="preserve">10.707501411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5573129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9592866897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9902067184448</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">10.6544942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1465063095093</t>
+    <t xml:space="preserve">10.146505355835</t>
   </si>
   <si>
     <t xml:space="preserve">9.95656299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0051527023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93447685241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45299053192139</t>
+    <t xml:space="preserve">10.0051517486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93447589874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4529914855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.46624374389648</t>
@@ -4196,19 +4196,19 @@
     <t xml:space="preserve">9.55458927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42648792266846</t>
+    <t xml:space="preserve">9.42648887634277</t>
   </si>
   <si>
     <t xml:space="preserve">9.84613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55017185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58109378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59876155853271</t>
+    <t xml:space="preserve">9.55017280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58109283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59876251220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.86379909515381</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">11.3082523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1183090209961</t>
+    <t xml:space="preserve">11.1183080673218</t>
   </si>
   <si>
     <t xml:space="preserve">10.9946250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5528955459595</t>
+    <t xml:space="preserve">10.5528964996338</t>
   </si>
   <si>
     <t xml:space="preserve">10.8046808242798</t>
@@ -4244,37 +4244,37 @@
     <t xml:space="preserve">10.9372005462646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259210586548</t>
+    <t xml:space="preserve">11.3259220123291</t>
   </si>
   <si>
     <t xml:space="preserve">11.02112865448</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8488550186157</t>
+    <t xml:space="preserve">10.8488540649414</t>
   </si>
   <si>
     <t xml:space="preserve">11.2508268356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.188985824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8471603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5379514694214</t>
+    <t xml:space="preserve">11.1889848709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8471612930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5379505157471</t>
   </si>
   <si>
     <t xml:space="preserve">10.9460344314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9548692703247</t>
+    <t xml:space="preserve">10.9548683166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239473342896</t>
+    <t xml:space="preserve">10.9239482879639</t>
   </si>
   <si>
     <t xml:space="preserve">11.246410369873</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">11.2331581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2110710144043</t>
+    <t xml:space="preserve">11.2110719680786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9620094299316</t>
+    <t xml:space="preserve">11.962010383606</t>
   </si>
   <si>
     <t xml:space="preserve">12.0591897964478</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">12.0503568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1961269378662</t>
+    <t xml:space="preserve">12.1961278915405</t>
   </si>
   <si>
     <t xml:space="preserve">12.3949041366577</t>
@@ -4325,52 +4325,52 @@
     <t xml:space="preserve">12.6246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908617019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7527046203613</t>
+    <t xml:space="preserve">12.6908626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7527055740356</t>
   </si>
   <si>
     <t xml:space="preserve">12.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.920560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9514827728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0354108810425</t>
+    <t xml:space="preserve">12.9205617904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9514818191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0354118347168</t>
   </si>
   <si>
     <t xml:space="preserve">13.2518577575684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1811809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2827796936035</t>
+    <t xml:space="preserve">13.1811819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2827777862549</t>
   </si>
   <si>
     <t xml:space="preserve">13.3843765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4418020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743188858032</t>
+    <t xml:space="preserve">13.441801071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743198394775</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285488128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3578729629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6405782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6494140625</t>
+    <t xml:space="preserve">13.3578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6405792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6494131088257</t>
   </si>
   <si>
     <t xml:space="preserve">13.9144506454468</t>
@@ -4382,28 +4382,28 @@
     <t xml:space="preserve">13.5522336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6759176254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7730979919434</t>
+    <t xml:space="preserve">13.6008234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7465944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6759166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.773097038269</t>
   </si>
   <si>
     <t xml:space="preserve">13.923285484314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188690185547</t>
+    <t xml:space="preserve">13.9188680648804</t>
   </si>
   <si>
     <t xml:space="preserve">13.1414251327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3534545898438</t>
+    <t xml:space="preserve">13.3534555435181</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903917312622</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">13.5345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5831537246704</t>
+    <t xml:space="preserve">13.5831546783447</t>
   </si>
   <si>
     <t xml:space="preserve">13.834939956665</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">13.8658599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1883230209351</t>
+    <t xml:space="preserve">14.1883220672607</t>
   </si>
   <si>
     <t xml:space="preserve">14.5947132110596</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">14.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8685836791992</t>
+    <t xml:space="preserve">14.8685846328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.7802381515503</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">14.7669868469238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7095623016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7934913635254</t>
+    <t xml:space="preserve">14.7095613479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7934923171997</t>
   </si>
   <si>
     <t xml:space="preserve">14.6653900146484</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">14.3429279327393</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5196189880371</t>
+    <t xml:space="preserve">14.5196180343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.3385095596313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.148567199707</t>
+    <t xml:space="preserve">14.1485662460327</t>
   </si>
   <si>
     <t xml:space="preserve">14.0955591201782</t>
@@ -4475,19 +4475,19 @@
     <t xml:space="preserve">14.4489421844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5107831954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4312725067139</t>
+    <t xml:space="preserve">14.5107841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4312734603882</t>
   </si>
   <si>
     <t xml:space="preserve">14.5328712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.52845287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5814609527588</t>
+    <t xml:space="preserve">14.5284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5814599990845</t>
   </si>
   <si>
     <t xml:space="preserve">14.9790163040161</t>
@@ -4496,31 +4496,31 @@
     <t xml:space="preserve">14.9392614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8553333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0099382400513</t>
+    <t xml:space="preserve">14.8553342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.009937286377</t>
   </si>
   <si>
     <t xml:space="preserve">14.6609716415405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6918926239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.568208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9701814651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7714033126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6433038711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453716278076</t>
+    <t xml:space="preserve">14.6918916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5682096481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9701824188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7714023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6433029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453706741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.1397314071655</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">14.444525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2236604690552</t>
+    <t xml:space="preserve">14.2236614227295</t>
   </si>
   <si>
     <t xml:space="preserve">14.3473443984985</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">13.0663318634033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2402992248535</t>
+    <t xml:space="preserve">12.2402982711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.4523296356201</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">11.502613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7455635070801</t>
+    <t xml:space="preserve">11.7455625534058</t>
   </si>
   <si>
     <t xml:space="preserve">11.2684965133667</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">12.3153924942017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4169902801514</t>
+    <t xml:space="preserve">12.4169912338257</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0238513946533</t>
+    <t xml:space="preserve">12.023853302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1828746795654</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">12.4920845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.293306350708</t>
+    <t xml:space="preserve">12.2933073043823</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579689025879</t>
@@ -4634,19 +4634,19 @@
     <t xml:space="preserve">12.7438697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684005737305</t>
+    <t xml:space="preserve">12.3684015274048</t>
   </si>
   <si>
     <t xml:space="preserve">12.5892648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5362577438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3065595626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406742095947</t>
+    <t xml:space="preserve">12.5362567901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3065586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.540675163269</t>
   </si>
   <si>
     <t xml:space="preserve">12.1298666000366</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">11.7588148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1121988296509</t>
+    <t xml:space="preserve">12.1121978759766</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632322311401</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">11.9399242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8824987411499</t>
+    <t xml:space="preserve">11.8824996948242</t>
   </si>
   <si>
     <t xml:space="preserve">11.2022380828857</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">11.0255451202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343809127808</t>
+    <t xml:space="preserve">11.0343799591064</t>
   </si>
   <si>
     <t xml:space="preserve">11.2199058532715</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.30748462677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638675689697</t>
+    <t xml:space="preserve">11.0638666152954</t>
   </si>
   <si>
     <t xml:space="preserve">11.2753086090088</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">11.3856248855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.436185836792</t>
+    <t xml:space="preserve">11.4361867904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.6522245407104</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">11.5832767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4913454055786</t>
+    <t xml:space="preserve">11.4913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">11.4959421157837</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">11.4499769210815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4591703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7533483505249</t>
+    <t xml:space="preserve">11.4591693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7533473968506</t>
   </si>
   <si>
     <t xml:space="preserve">11.6935930252075</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">11.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0041122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9949197769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.096043586731</t>
+    <t xml:space="preserve">11.0041131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9949188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0960426330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.1833772659302</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">11.2890977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0868501663208</t>
+    <t xml:space="preserve">11.0868511199951</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156547546387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4683637619019</t>
+    <t xml:space="preserve">11.4683628082275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8131036758423</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">12.1486501693726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3279151916504</t>
+    <t xml:space="preserve">12.3187227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3279161453247</t>
   </si>
   <si>
     <t xml:space="preserve">12.5117769241333</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.3784770965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5301628112793</t>
+    <t xml:space="preserve">12.5301637649536</t>
   </si>
   <si>
     <t xml:space="preserve">12.6358833312988</t>
@@ -4832,19 +4832,19 @@
     <t xml:space="preserve">12.9760274887085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645864486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4428291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5255670547485</t>
+    <t xml:space="preserve">12.7645874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4428281784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5255661010742</t>
   </si>
   <si>
     <t xml:space="preserve">12.4750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2385358810425</t>
+    <t xml:space="preserve">11.2385368347168</t>
   </si>
   <si>
     <t xml:space="preserve">12.0383338928223</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">11.964789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9555969238281</t>
+    <t xml:space="preserve">11.9555959701538</t>
   </si>
   <si>
     <t xml:space="preserve">11.5005388259888</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">11.6016626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.551100730896</t>
+    <t xml:space="preserve">11.5510997772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143280029297</t>
@@ -4877,19 +4877,19 @@
     <t xml:space="preserve">11.5786800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7073822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625417709351</t>
+    <t xml:space="preserve">11.7073831558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625408172607</t>
   </si>
   <si>
     <t xml:space="preserve">11.7441549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6384344100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
+    <t xml:space="preserve">11.6384353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465040206909</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855243682861</t>
@@ -4898,19 +4898,19 @@
     <t xml:space="preserve">11.7487516403198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6154527664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.94895362854</t>
+    <t xml:space="preserve">11.6154518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9489545822144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7558994293213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8708124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570241928101</t>
+    <t xml:space="preserve">10.870813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570232391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.8478298187256</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">10.889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7283201217651</t>
+    <t xml:space="preserve">10.7283210754395</t>
   </si>
   <si>
     <t xml:space="preserve">10.8294439315796</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">10.6915483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6547756195068</t>
+    <t xml:space="preserve">10.6547765731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7329168319702</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">10.6271963119507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858278274536</t>
+    <t xml:space="preserve">10.5858287811279</t>
   </si>
   <si>
     <t xml:space="preserve">10.287052154541</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">10.1445598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1215782165527</t>
+    <t xml:space="preserve">10.1215772628784</t>
   </si>
   <si>
     <t xml:space="preserve">9.91932964324951</t>
@@ -4964,10 +4964,10 @@
     <t xml:space="preserve">9.99747085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79522323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1399621963501</t>
+    <t xml:space="preserve">9.79522228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1399631500244</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721391677856</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">9.90094375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96989250183105</t>
+    <t xml:space="preserve">9.96989154815674</t>
   </si>
   <si>
     <t xml:space="preserve">10.1951217651367</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">10.043436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0848054885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.03883934021</t>
+    <t xml:space="preserve">10.0848045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0388402938843</t>
   </si>
   <si>
     <t xml:space="preserve">10.057225227356</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">10.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629467010498</t>
+    <t xml:space="preserve">10.1629457473755</t>
   </si>
   <si>
     <t xml:space="preserve">10.2181043624878</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">11.0454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3948192596436</t>
+    <t xml:space="preserve">11.3948183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.5097322463989</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">11.0592708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9995155334473</t>
+    <t xml:space="preserve">10.9995164871216</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9903230667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477293014526</t>
+    <t xml:space="preserve">10.9903221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477283477783</t>
   </si>
   <si>
     <t xml:space="preserve">11.3672389984131</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">11.5970659255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.776330947876</t>
+    <t xml:space="preserve">11.7763319015503</t>
   </si>
   <si>
     <t xml:space="preserve">11.8866481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3646869659424</t>
+    <t xml:space="preserve">12.3646879196167</t>
   </si>
   <si>
     <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4290390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4014596939087</t>
+    <t xml:space="preserve">12.4290399551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.401460647583</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3692846298218</t>
+    <t xml:space="preserve">12.3692836761475</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554944992065</t>
@@ -5099,7 +5099,7 @@
     <t xml:space="preserve">12.5485486984253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.249773979187</t>
+    <t xml:space="preserve">12.2497749328613</t>
   </si>
   <si>
     <t xml:space="preserve">12.5393571853638</t>
@@ -5111,25 +5111,25 @@
     <t xml:space="preserve">12.6404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4566192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7507963180542</t>
+    <t xml:space="preserve">12.456618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7507972717285</t>
   </si>
   <si>
     <t xml:space="preserve">12.6680593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8473253250122</t>
+    <t xml:space="preserve">12.8473243713379</t>
   </si>
   <si>
     <t xml:space="preserve">12.870306968689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9024820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7783765792847</t>
+    <t xml:space="preserve">12.9024829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7783756256104</t>
   </si>
   <si>
     <t xml:space="preserve">12.8105525970459</t>
@@ -5138,16 +5138,16 @@
     <t xml:space="preserve">12.7094278335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6174974441528</t>
+    <t xml:space="preserve">12.6174983978271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5577421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8381309509277</t>
+    <t xml:space="preserve">12.6588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8381319046021</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819499969482</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">11.8544731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8452787399292</t>
+    <t xml:space="preserve">11.8452796936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0705099105835</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">12.1348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0888957977295</t>
+    <t xml:space="preserve">12.0888948440552</t>
   </si>
   <si>
     <t xml:space="preserve">11.9326124191284</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">11.8085069656372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8958406448364</t>
+    <t xml:space="preserve">11.8958396911621</t>
   </si>
   <si>
     <t xml:space="preserve">12.0107536315918</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">12.194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.153247833252</t>
+    <t xml:space="preserve">12.1532468795776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1854228973389</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">12.0934915542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.157844543457</t>
+    <t xml:space="preserve">12.1808271408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1578435897827</t>
   </si>
   <si>
     <t xml:space="preserve">12.2957391738892</t>
@@ -5240,13 +5240,13 @@
     <t xml:space="preserve">12.3922672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.626690864563</t>
+    <t xml:space="preserve">12.6266899108887</t>
   </si>
   <si>
     <t xml:space="preserve">12.6220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8335342407227</t>
+    <t xml:space="preserve">12.833535194397</t>
   </si>
   <si>
     <t xml:space="preserve">12.9162721633911</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">12.4796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2242403030396</t>
+    <t xml:space="preserve">13.2242412567139</t>
   </si>
   <si>
     <t xml:space="preserve">13.136905670166</t>
@@ -5270,7 +5270,7 @@
     <t xml:space="preserve">13.2012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2702054977417</t>
+    <t xml:space="preserve">13.270206451416</t>
   </si>
   <si>
     <t xml:space="preserve">13.1736783981323</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">12.6726560592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.681848526001</t>
+    <t xml:space="preserve">12.6818494796753</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9990110397339</t>
+    <t xml:space="preserve">12.9990100860596</t>
   </si>
   <si>
     <t xml:space="preserve">13.0265893936157</t>
@@ -5309,16 +5309,16 @@
     <t xml:space="preserve">12.8611135482788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0541677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058765411377</t>
+    <t xml:space="preserve">13.0541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587644577026</t>
   </si>
   <si>
     <t xml:space="preserve">13.2748022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1461000442505</t>
+    <t xml:space="preserve">13.1460990905762</t>
   </si>
   <si>
     <t xml:space="preserve">13.233434677124</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.780421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9275102615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9045286178589</t>
+    <t xml:space="preserve">13.7804222106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.92751121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9045276641846</t>
   </si>
   <si>
     <t xml:space="preserve">14.0102481842041</t>
@@ -6303,6 +6303,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.8099994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
   </si>
 </sst>
 </file>
@@ -71667,7 +71670,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6909722222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>1462176</v>
@@ -71688,6 +71691,32 @@
         <v>2096</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6941550926</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>1607971</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>20.1299991607666</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>19.8050003051758</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>19.8050003051758</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>2097</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="2098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="2099">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">5.32048845291138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17209386825562</t>
+    <t xml:space="preserve">5.17209434509277</t>
   </si>
   <si>
     <t xml:space="preserve">5.13951969146729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2625789642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1322808265686</t>
+    <t xml:space="preserve">5.26257801055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13228034973145</t>
   </si>
   <si>
     <t xml:space="preserve">5.26619815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31324911117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1938099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0454158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92959499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07437133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82101440429688</t>
+    <t xml:space="preserve">5.31325006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04541540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92959547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07437086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65814161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82101345062256</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">5.16485500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12504196166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88978242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79205942153931</t>
+    <t xml:space="preserve">5.12504148483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8897819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
     <t xml:space="preserve">4.74138784408569</t>
@@ -119,34 +119,34 @@
     <t xml:space="preserve">4.34325647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545721054077</t>
+    <t xml:space="preserve">4.45545673370361</t>
   </si>
   <si>
     <t xml:space="preserve">4.48441171646118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58213520050049</t>
+    <t xml:space="preserve">4.58213472366333</t>
   </si>
   <si>
     <t xml:space="preserve">4.78482007980347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73414850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81377506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672315597534</t>
+    <t xml:space="preserve">4.73414897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81377553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667236328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.71243286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83187246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84996938705444</t>
+    <t xml:space="preserve">4.83187294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
     <t xml:space="preserve">4.88616275787354</t>
@@ -155,76 +155,76 @@
     <t xml:space="preserve">5.00922203063965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09246730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95493078231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8427300453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713247299194</t>
+    <t xml:space="preserve">5.09246683120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332536697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16847467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95493173599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84273052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120088577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713151931763</t>
   </si>
   <si>
     <t xml:space="preserve">5.08884859085083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00560283660889</t>
+    <t xml:space="preserve">5.00560235977173</t>
   </si>
   <si>
     <t xml:space="preserve">4.99112462997437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19019079208374</t>
+    <t xml:space="preserve">5.1901912689209</t>
   </si>
   <si>
     <t xml:space="preserve">5.23362350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35668182373047</t>
+    <t xml:space="preserve">5.35668277740479</t>
   </si>
   <si>
     <t xml:space="preserve">5.12866115570068</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02007961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026752471924</t>
+    <t xml:space="preserve">5.02008056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026704788208</t>
   </si>
   <si>
     <t xml:space="preserve">4.94769239425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97302722930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11418437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.121422290802</t>
+    <t xml:space="preserve">4.9730281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369928359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11418390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12142276763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.33544111251831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23406362533569</t>
+    <t xml:space="preserve">5.23406314849854</t>
   </si>
   <si>
     <t xml:space="preserve">5.28287506103516</t>
@@ -233,28 +233,28 @@
     <t xml:space="preserve">5.27161121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23030948638916</t>
+    <t xml:space="preserve">5.230309009552</t>
   </si>
   <si>
     <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168601989746</t>
+    <t xml:space="preserve">5.33168649673462</t>
   </si>
   <si>
     <t xml:space="preserve">5.30164909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39176177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2641019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25659227371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05759286880493</t>
+    <t xml:space="preserve">5.391761302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26410150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25659132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05759334564209</t>
   </si>
   <si>
     <t xml:space="preserve">5.09889459609985</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.96747970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88862991333008</t>
+    <t xml:space="preserve">4.88863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">4.78725337982178</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472520828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70089530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96372509002686</t>
+    <t xml:space="preserve">4.76472568511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96372413635254</t>
   </si>
   <si>
     <t xml:space="preserve">4.90364980697632</t>
@@ -293,31 +293,31 @@
     <t xml:space="preserve">4.73844289779663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84357404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91866874694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.986252784729</t>
+    <t xml:space="preserve">4.84357357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91866827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98625326156616</t>
   </si>
   <si>
     <t xml:space="preserve">4.97874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01629114151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92617797851562</t>
+    <t xml:space="preserve">5.01629066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92617750167847</t>
   </si>
   <si>
     <t xml:space="preserve">4.95246076583862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97123432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8548378944397</t>
+    <t xml:space="preserve">4.97123384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85483837127686</t>
   </si>
   <si>
     <t xml:space="preserve">4.87736654281616</t>
@@ -326,37 +326,37 @@
     <t xml:space="preserve">4.80227279663086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197118759155</t>
+    <t xml:space="preserve">4.62204599380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197071075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.44182062149048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4493293762207</t>
+    <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.4568395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56947994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7534613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73093271255493</t>
+    <t xml:space="preserve">4.56948041915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73093318939209</t>
   </si>
   <si>
     <t xml:space="preserve">4.80602693557739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97498941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49063205718994</t>
+    <t xml:space="preserve">4.97498846054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49063158035278</t>
   </si>
   <si>
     <t xml:space="preserve">4.13017988204956</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">3.87485909461975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94244408607483</t>
+    <t xml:space="preserve">3.94244432449341</t>
   </si>
   <si>
     <t xml:space="preserve">4.2653489112854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3179144859314</t>
+    <t xml:space="preserve">4.31791496276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.19025468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20151901245117</t>
+    <t xml:space="preserve">4.20151948928833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23531103134155</t>
@@ -410,61 +410,61 @@
     <t xml:space="preserve">4.27661323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09638738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9311797618866</t>
+    <t xml:space="preserve">4.09638643264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117952346802</t>
   </si>
   <si>
     <t xml:space="preserve">3.98750042915344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8373122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93868947029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623586654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93493485450745</t>
+    <t xml:space="preserve">3.83731198310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93868899345398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623610496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93493437767029</t>
   </si>
   <si>
     <t xml:space="preserve">3.9724817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95746231079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619870185852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99876427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980251312256</t>
+    <t xml:space="preserve">3.95746302604675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94619917869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99876475334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980298995972</t>
   </si>
   <si>
     <t xml:space="preserve">3.82604813575745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77348160743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7547082901001</t>
+    <t xml:space="preserve">3.77348232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470852851868</t>
   </si>
   <si>
     <t xml:space="preserve">4.05133104324341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07010412216187</t>
+    <t xml:space="preserve">4.07010459899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01378345489502</t>
+    <t xml:space="preserve">4.01378297805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
@@ -473,37 +473,37 @@
     <t xml:space="preserve">4.09263277053833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1376895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12266969680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05508518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07385921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03255653381348</t>
+    <t xml:space="preserve">4.13768911361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12267017364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0550856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07385873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03255701065063</t>
   </si>
   <si>
     <t xml:space="preserve">3.9124059677124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82229351997375</t>
+    <t xml:space="preserve">3.8222930431366</t>
   </si>
   <si>
     <t xml:space="preserve">3.81478404998779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9048969745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90114283561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88987803459167</t>
+    <t xml:space="preserve">3.90489649772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90114212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88987827301025</t>
   </si>
   <si>
     <t xml:space="preserve">3.8110294342041</t>
@@ -518,22 +518,22 @@
     <t xml:space="preserve">3.88236904144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87110495567322</t>
+    <t xml:space="preserve">3.87110471725464</t>
   </si>
   <si>
     <t xml:space="preserve">3.85233116149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78850126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7622184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61203002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550857543945</t>
+    <t xml:space="preserve">3.78850078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221799850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61202955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550929069519</t>
   </si>
   <si>
     <t xml:space="preserve">3.7960102558136</t>
@@ -542,49 +542,49 @@
     <t xml:space="preserve">3.96121788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97999167442322</t>
+    <t xml:space="preserve">3.97999119758606</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504777908325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96497297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01753854751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08887767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14519834518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99500966072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355760574341</t>
+    <t xml:space="preserve">3.96497249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01753759384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08887815475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14519786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9950098991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742562294006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355808258057</t>
   </si>
   <si>
     <t xml:space="preserve">3.78474593162537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80727434158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79225635528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6405656337738</t>
+    <t xml:space="preserve">3.80727481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79225516319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170493125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518395423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64056539535522</t>
   </si>
   <si>
     <t xml:space="preserve">3.60452079772949</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">3.54444479942322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53843784332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54144167900085</t>
+    <t xml:space="preserve">3.53843760490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54144144058228</t>
   </si>
   <si>
     <t xml:space="preserve">3.55645990371704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60001492500305</t>
+    <t xml:space="preserve">3.60001468658447</t>
   </si>
   <si>
     <t xml:space="preserve">3.47085332870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58799910545349</t>
+    <t xml:space="preserve">3.58800005912781</t>
   </si>
   <si>
     <t xml:space="preserve">3.66459560394287</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">3.64507126808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66910123825073</t>
+    <t xml:space="preserve">3.66910147666931</t>
   </si>
   <si>
     <t xml:space="preserve">3.57748651504517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73968935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84857630729675</t>
+    <t xml:space="preserve">3.73968982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84857583045959</t>
   </si>
   <si>
     <t xml:space="preserve">4.14144372940063</t>
@@ -641,22 +641,22 @@
     <t xml:space="preserve">4.04006624221802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11516046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0025200843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07761335372925</t>
+    <t xml:space="preserve">4.11516094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00251960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07761287689209</t>
   </si>
   <si>
     <t xml:space="preserve">4.16772651672363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15270853042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895343780518</t>
+    <t xml:space="preserve">4.15270757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895296096802</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512306213379</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.22029256820679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2390661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16021728515625</t>
+    <t xml:space="preserve">4.23906564712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16021680831909</t>
   </si>
   <si>
     <t xml:space="preserve">4.12642431259155</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.03631162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13393402099609</t>
+    <t xml:space="preserve">4.13393449783325</t>
   </si>
   <si>
     <t xml:space="preserve">4.28787755966187</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">4.30289602279663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33293437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557476043701</t>
+    <t xml:space="preserve">4.33293390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557523727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.63706588745117</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">4.69338607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72342348098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67085838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80978155136108</t>
+    <t xml:space="preserve">4.72342300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67085742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80978202819824</t>
   </si>
   <si>
     <t xml:space="preserve">4.83981943130493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81353664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79851722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7271785736084</t>
+    <t xml:space="preserve">4.81353616714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79851770401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72717809677124</t>
   </si>
   <si>
     <t xml:space="preserve">4.85108375549316</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.82104635238647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83606481552124</t>
+    <t xml:space="preserve">4.83606433868408</t>
   </si>
   <si>
     <t xml:space="preserve">5.07056093215942</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">5.16875171661377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23552131652832</t>
+    <t xml:space="preserve">5.23552083969116</t>
   </si>
   <si>
     <t xml:space="preserve">5.33371210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3415675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37691593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20410108566284</t>
+    <t xml:space="preserve">5.34156703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37691640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20410013198853</t>
   </si>
   <si>
     <t xml:space="preserve">5.28265285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20017290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373867034912</t>
+    <t xml:space="preserve">5.20017242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373914718628</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092334747314</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">5.15696907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29050827026367</t>
+    <t xml:space="preserve">5.29050874710083</t>
   </si>
   <si>
     <t xml:space="preserve">5.26694202423096</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">5.36906099319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34942197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3847713470459</t>
+    <t xml:space="preserve">5.34942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38477087020874</t>
   </si>
   <si>
     <t xml:space="preserve">5.21588325500488</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">5.32585620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25123167037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37298774719238</t>
+    <t xml:space="preserve">5.2512321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37298822402954</t>
   </si>
   <si>
     <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61650085449219</t>
+    <t xml:space="preserve">5.61650133132935</t>
   </si>
   <si>
     <t xml:space="preserve">5.57722473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54187631607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63221120834351</t>
+    <t xml:space="preserve">5.5418758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63221168518066</t>
   </si>
   <si>
     <t xml:space="preserve">5.62435626983643</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55365896224976</t>
+    <t xml:space="preserve">5.55365943908691</t>
   </si>
   <si>
     <t xml:space="preserve">5.50259971618652</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">5.41226434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52223777770996</t>
+    <t xml:space="preserve">5.52223825454712</t>
   </si>
   <si>
     <t xml:space="preserve">5.61257362365723</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">5.69112586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75789594650269</t>
+    <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
     <t xml:space="preserve">5.87572383880615</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">5.73433017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64006662368774</t>
+    <t xml:space="preserve">5.64006614685059</t>
   </si>
   <si>
     <t xml:space="preserve">5.65970468521118</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">5.83644723892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82466506958008</t>
+    <t xml:space="preserve">5.82466554641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.8403754234314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8285927772522</t>
+    <t xml:space="preserve">5.82859230041504</t>
   </si>
   <si>
     <t xml:space="preserve">5.87179660797119</t>
@@ -923,52 +923,52 @@
     <t xml:space="preserve">5.93463754653931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95034837722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90714502334595</t>
+    <t xml:space="preserve">5.95034885406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90714454650879</t>
   </si>
   <si>
     <t xml:space="preserve">5.79717111587524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70290803909302</t>
+    <t xml:space="preserve">5.70290899276733</t>
   </si>
   <si>
     <t xml:space="preserve">5.78931617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89143466949463</t>
+    <t xml:space="preserve">5.89143514633179</t>
   </si>
   <si>
     <t xml:space="preserve">5.78538846969604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79324436187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70683670043945</t>
+    <t xml:space="preserve">5.79324388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70683622360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.6871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56936979293823</t>
+    <t xml:space="preserve">5.56936931610107</t>
   </si>
   <si>
     <t xml:space="preserve">5.46725130081177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59293556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66756010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41619205474854</t>
+    <t xml:space="preserve">5.59293508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66756057739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41619157791138</t>
   </si>
   <si>
     <t xml:space="preserve">5.39262580871582</t>
@@ -980,85 +980,85 @@
     <t xml:space="preserve">5.75004005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76182270050049</t>
+    <t xml:space="preserve">5.76182317733765</t>
   </si>
   <si>
     <t xml:space="preserve">5.73040151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75396680831909</t>
+    <t xml:space="preserve">5.75396728515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.80109930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80895471572876</t>
+    <t xml:space="preserve">5.8089542388916</t>
   </si>
   <si>
     <t xml:space="preserve">5.91500043869019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87965154647827</t>
+    <t xml:space="preserve">5.87965202331543</t>
   </si>
   <si>
     <t xml:space="preserve">5.85215854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84430313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86001348495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84823083877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69505310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6636323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64792203903198</t>
+    <t xml:space="preserve">5.84430265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86001300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84823131561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6950535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66363191604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64792156219482</t>
   </si>
   <si>
     <t xml:space="preserve">5.71861934661865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83252000808716</t>
+    <t xml:space="preserve">5.83252048492432</t>
   </si>
   <si>
     <t xml:space="preserve">5.76575088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11530828475952</t>
+    <t xml:space="preserve">6.11530876159668</t>
   </si>
   <si>
     <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26063060760498</t>
+    <t xml:space="preserve">6.26063108444214</t>
   </si>
   <si>
     <t xml:space="preserve">6.2449197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31168985366821</t>
+    <t xml:space="preserve">6.31168937683105</t>
   </si>
   <si>
     <t xml:space="preserve">6.30776166915894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29990768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29205179214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670337677002</t>
+    <t xml:space="preserve">6.29990720748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29205226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670385360718</t>
   </si>
   <si>
     <t xml:space="preserve">6.23706531524658</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">6.20171642303467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23313760757446</t>
+    <t xml:space="preserve">6.2331371307373</t>
   </si>
   <si>
     <t xml:space="preserve">6.06032228469849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00926303863525</t>
+    <t xml:space="preserve">6.0092625617981</t>
   </si>
   <si>
     <t xml:space="preserve">6.12709140777588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528219223022</t>
+    <t xml:space="preserve">6.22528266906738</t>
   </si>
   <si>
     <t xml:space="preserve">6.28026914596558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37060451507568</t>
+    <t xml:space="preserve">6.37060403823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.37453174591064</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">6.39809799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45308494567871</t>
+    <t xml:space="preserve">6.45308446884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.58662366867065</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">6.65339326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53949165344238</t>
+    <t xml:space="preserve">6.53949117660522</t>
   </si>
   <si>
     <t xml:space="preserve">6.60626173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63768291473389</t>
+    <t xml:space="preserve">6.63768243789673</t>
   </si>
   <si>
     <t xml:space="preserve">6.56305742263794</t>
@@ -1127,46 +1127,46 @@
     <t xml:space="preserve">6.71230697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83013582229614</t>
+    <t xml:space="preserve">6.83013534545898</t>
   </si>
   <si>
     <t xml:space="preserve">6.68874216079712</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79086065292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68088722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409152984619</t>
+    <t xml:space="preserve">6.79086017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6808876991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409105300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.77907752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75551271438599</t>
+    <t xml:space="preserve">6.75551176071167</t>
   </si>
   <si>
     <t xml:space="preserve">6.76336622238159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85762929916382</t>
+    <t xml:space="preserve">6.8576283454895</t>
   </si>
   <si>
     <t xml:space="preserve">6.86155700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81049776077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70445203781128</t>
+    <t xml:space="preserve">6.81049823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445156097412</t>
   </si>
   <si>
     <t xml:space="preserve">6.63375568389893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64553785324097</t>
+    <t xml:space="preserve">6.64553737640381</t>
   </si>
   <si>
     <t xml:space="preserve">6.91261625289917</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">6.9990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99116897583008</t>
+    <t xml:space="preserve">6.99116802215576</t>
   </si>
   <si>
     <t xml:space="preserve">7.33287191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40356874465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58031272888184</t>
+    <t xml:space="preserve">7.40357065200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58031177520752</t>
   </si>
   <si>
     <t xml:space="preserve">7.54103708267212</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">7.88666820526123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93379926681519</t>
+    <t xml:space="preserve">7.93379735946655</t>
   </si>
   <si>
     <t xml:space="preserve">7.91808700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78454828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86310148239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8748836517334</t>
+    <t xml:space="preserve">7.78454732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86310052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87488460540771</t>
   </si>
   <si>
     <t xml:space="preserve">7.74055910110474</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">7.23782348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26610279083252</t>
+    <t xml:space="preserve">7.26610136032104</t>
   </si>
   <si>
     <t xml:space="preserve">7.24410820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30066585540771</t>
+    <t xml:space="preserve">7.30066442489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.49076223373413</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">7.59130954742432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69657135009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355241775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80026006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826452255249</t>
+    <t xml:space="preserve">7.69657039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355146408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77826547622681</t>
   </si>
   <si>
     <t xml:space="preserve">7.83325099945068</t>
@@ -1283,31 +1283,31 @@
     <t xml:space="preserve">7.94950914382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96914768218994</t>
+    <t xml:space="preserve">7.96914672851562</t>
   </si>
   <si>
     <t xml:space="preserve">7.52061319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83010959625244</t>
+    <t xml:space="preserve">7.83011054992676</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129083633423</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08304786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090232849121</t>
+    <t xml:space="preserve">8.08304882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090328216553</t>
   </si>
   <si>
     <t xml:space="preserve">7.94165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95343685150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04377174377441</t>
+    <t xml:space="preserve">7.95343780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0437707901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.11054039001465</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">7.8395357131958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69499778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71070909500122</t>
+    <t xml:space="preserve">7.6949987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71071004867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.64158248901367</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">7.596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56146097183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75312757492065</t>
+    <t xml:space="preserve">7.56146001815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75312852859497</t>
   </si>
   <si>
     <t xml:space="preserve">7.83168077468872</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">7.97427892684937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00986576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456398010254</t>
+    <t xml:space="preserve">8.00986480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456493377686</t>
   </si>
   <si>
     <t xml:space="preserve">7.9856014251709</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">8.21690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9322247505188</t>
+    <t xml:space="preserve">7.93222379684448</t>
   </si>
   <si>
     <t xml:space="preserve">7.86105442047119</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">7.4194769859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25125694274902</t>
+    <t xml:space="preserve">7.25125646591187</t>
   </si>
   <si>
     <t xml:space="preserve">7.19626140594482</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">7.43079900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40491962432861</t>
+    <t xml:space="preserve">7.40492010116577</t>
   </si>
   <si>
     <t xml:space="preserve">7.42594766616821</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10568189620972</t>
+    <t xml:space="preserve">7.10568141937256</t>
   </si>
   <si>
     <t xml:space="preserve">6.59293460845947</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">6.43441867828369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8484992980957</t>
+    <t xml:space="preserve">6.84849882125854</t>
   </si>
   <si>
     <t xml:space="preserve">6.91805171966553</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">6.92613887786865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81776714324951</t>
+    <t xml:space="preserve">6.81776762008667</t>
   </si>
   <si>
     <t xml:space="preserve">7.2221417427063</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">7.20111417770386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14773750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2641978263855</t>
+    <t xml:space="preserve">7.14773654937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26419687271118</t>
   </si>
   <si>
     <t xml:space="preserve">7.61681175231934</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">7.5860800743103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415735244751</t>
+    <t xml:space="preserve">7.70415639877319</t>
   </si>
   <si>
     <t xml:space="preserve">7.66857290267944</t>
@@ -1493,37 +1493,37 @@
     <t xml:space="preserve">7.70739221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80282354354858</t>
+    <t xml:space="preserve">7.8028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">7.62975168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69445276260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886831283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768619537354</t>
+    <t xml:space="preserve">7.69445180892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886735916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768667221069</t>
   </si>
   <si>
     <t xml:space="preserve">7.82223463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83032131195068</t>
+    <t xml:space="preserve">7.830322265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.95163488388062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05353832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03089237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001745223999</t>
+    <t xml:space="preserve">8.05353736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03089141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001649856567</t>
   </si>
   <si>
     <t xml:space="preserve">8.07294750213623</t>
@@ -1535,25 +1535,25 @@
     <t xml:space="preserve">8.19264316558838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329780578613</t>
+    <t xml:space="preserve">8.25329875946045</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31395530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27756118774414</t>
+    <t xml:space="preserve">8.29778003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31395435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27756023406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.18455410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23307991027832</t>
+    <t xml:space="preserve">8.23308086395264</t>
   </si>
   <si>
     <t xml:space="preserve">8.21286106109619</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24521064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13198566436768</t>
+    <t xml:space="preserve">8.12794399261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24521160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13198661804199</t>
   </si>
   <si>
     <t xml:space="preserve">8.06647682189941</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">8.17646789550781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07941722869873</t>
+    <t xml:space="preserve">8.07941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">8.14007377624512</t>
@@ -1598,19 +1598,19 @@
     <t xml:space="preserve">8.2249927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30991077423096</t>
+    <t xml:space="preserve">8.30990982055664</t>
   </si>
   <si>
     <t xml:space="preserve">8.22903537750244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18859958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33417510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30182456970215</t>
+    <t xml:space="preserve">8.1885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33417415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30182361602783</t>
   </si>
   <si>
     <t xml:space="preserve">8.3179988861084</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">8.60510635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77898597717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77089977264404</t>
+    <t xml:space="preserve">8.77898693084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77089881896973</t>
   </si>
   <si>
     <t xml:space="preserve">8.89625549316406</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">8.95691108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03778743743896</t>
+    <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.04183101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11866188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22379970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33298206329346</t>
+    <t xml:space="preserve">9.11866092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22379875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33298110961914</t>
   </si>
   <si>
     <t xml:space="preserve">9.32084941864014</t>
@@ -1658,22 +1658,22 @@
     <t xml:space="preserve">9.44620513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61604404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48259830474854</t>
+    <t xml:space="preserve">9.61604309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48260021209717</t>
   </si>
   <si>
     <t xml:space="preserve">9.31276226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39768028259277</t>
+    <t xml:space="preserve">9.39768123626709</t>
   </si>
   <si>
     <t xml:space="preserve">9.30063056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2804126739502</t>
+    <t xml:space="preserve">9.28041172027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.1954927444458</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">8.65363025665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05191993713379</t>
+    <t xml:space="preserve">8.05192089080811</t>
   </si>
   <si>
     <t xml:space="preserve">7.89987468719482</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">7.88531684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1198558807373</t>
+    <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
     <t xml:space="preserve">7.83355665206909</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">7.46800231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25287389755249</t>
+    <t xml:space="preserve">7.25287485122681</t>
   </si>
   <si>
     <t xml:space="preserve">7.24155235290527</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">7.05715703964233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595611572266</t>
+    <t xml:space="preserve">7.32080936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595659255981</t>
   </si>
   <si>
     <t xml:space="preserve">7.33860206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47770738601685</t>
+    <t xml:space="preserve">7.47770690917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.59093141555786</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">7.94516515731812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96619319915771</t>
+    <t xml:space="preserve">7.9661922454834</t>
   </si>
   <si>
     <t xml:space="preserve">7.88369989395142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78017997741699</t>
+    <t xml:space="preserve">7.78017902374268</t>
   </si>
   <si>
     <t xml:space="preserve">7.78988409042358</t>
@@ -1781,40 +1781,40 @@
     <t xml:space="preserve">7.98074960708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91119766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68474674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8513503074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7494478225708</t>
+    <t xml:space="preserve">7.9111967086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68474721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85134935379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74944686889648</t>
   </si>
   <si>
     <t xml:space="preserve">7.32889747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39036178588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22537660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24963855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44212102890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49388265609741</t>
+    <t xml:space="preserve">7.39036083221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22537708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2496395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44212198257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4938817024231</t>
   </si>
   <si>
     <t xml:space="preserve">7.39521455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26581430435181</t>
+    <t xml:space="preserve">7.26581525802612</t>
   </si>
   <si>
     <t xml:space="preserve">7.21890640258789</t>
@@ -1823,28 +1823,28 @@
     <t xml:space="preserve">7.35477685928345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01833629608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05230522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93099164962769</t>
+    <t xml:space="preserve">7.01833724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05230379104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93099117279053</t>
   </si>
   <si>
     <t xml:space="preserve">7.09921169281006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0798020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99245643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23831653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875423431396</t>
+    <t xml:space="preserve">7.07980155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99245691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23831748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875518798828</t>
   </si>
   <si>
     <t xml:space="preserve">7.58446216583252</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">7.56828641891479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55534791946411</t>
+    <t xml:space="preserve">7.55534696578979</t>
   </si>
   <si>
     <t xml:space="preserve">7.54078960418701</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">7.64430952072144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93707799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90634489059448</t>
+    <t xml:space="preserve">7.93707609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90634393692017</t>
   </si>
   <si>
     <t xml:space="preserve">7.92898941040039</t>
@@ -1886,37 +1886,37 @@
     <t xml:space="preserve">7.673424243927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57152318954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83194065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9257550239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01795101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80767726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00339603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39887523651123</t>
+    <t xml:space="preserve">7.57152223587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8319411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92575407028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01795196533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80767774581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00339508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39887428283691</t>
   </si>
   <si>
     <t xml:space="preserve">8.2371244430542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45144271850586</t>
+    <t xml:space="preserve">8.45144176483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.5767993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38674259185791</t>
+    <t xml:space="preserve">8.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">8.26947402954102</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35034847259521</t>
+    <t xml:space="preserve">8.3503475189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559894561768</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">8.92051887512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08226680755615</t>
+    <t xml:space="preserve">9.08226776123047</t>
   </si>
   <si>
     <t xml:space="preserve">9.15909957885742</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">9.18740463256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02161026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07418060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445529937744</t>
+    <t xml:space="preserve">9.02161121368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07418155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445434570312</t>
   </si>
   <si>
     <t xml:space="preserve">9.17931842803955</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">9.3248929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26827907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36533069610596</t>
+    <t xml:space="preserve">9.26828002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36532974243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40576934814453</t>
+    <t xml:space="preserve">9.40576839447021</t>
   </si>
   <si>
     <t xml:space="preserve">9.5958251953125</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">9.65647983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56751728057861</t>
+    <t xml:space="preserve">9.5675163269043</t>
   </si>
   <si>
     <t xml:space="preserve">9.45833587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46642398834229</t>
+    <t xml:space="preserve">9.4664249420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.47451210021973</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">9.81014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163745880127</t>
+    <t xml:space="preserve">10.0163736343384</t>
   </si>
   <si>
     <t xml:space="preserve">9.83036231994629</t>
@@ -6306,6 +6306,9 @@
   </si>
   <si>
     <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2099990844727</t>
   </si>
 </sst>
 </file>
@@ -71696,7 +71699,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6941550926</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>1607971</v>
@@ -71717,6 +71720,32 @@
         <v>2097</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6938078704</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>2137366</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>20.2600002288818</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>19.7299995422363</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>19.8700008392334</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>20.2099990844727</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="2099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="2100">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35306310653687</t>
+    <t xml:space="preserve">5.35306262969971</t>
   </si>
   <si>
     <t xml:space="preserve">FBK.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32048845291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17209434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13951969146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26257801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13228034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26619815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31325006484985</t>
+    <t xml:space="preserve">5.32048892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13951921463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26257848739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1322808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26619720458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3132495880127</t>
   </si>
   <si>
     <t xml:space="preserve">5.19381046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04541540145874</t>
+    <t xml:space="preserve">5.0454158782959</t>
   </si>
   <si>
     <t xml:space="preserve">4.92959547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07437086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65814161300659</t>
+    <t xml:space="preserve">5.07437038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65814208984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.82101345062256</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">4.96578931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05265474319458</t>
+    <t xml:space="preserve">5.05265426635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.21190690994263</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14675855636597</t>
+    <t xml:space="preserve">5.14675807952881</t>
   </si>
   <si>
     <t xml:space="preserve">5.16485500335693</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">5.12504148483276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8897819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79205894470215</t>
+    <t xml:space="preserve">4.88978242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79205942153931</t>
   </si>
   <si>
     <t xml:space="preserve">4.74138784408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56765747070312</t>
+    <t xml:space="preserve">4.56765651702881</t>
   </si>
   <si>
     <t xml:space="preserve">4.34325647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45545673370361</t>
+    <t xml:space="preserve">4.45545768737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.48441171646118</t>
@@ -131,55 +131,55 @@
     <t xml:space="preserve">4.78482007980347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73414897918701</t>
+    <t xml:space="preserve">4.73414850234985</t>
   </si>
   <si>
     <t xml:space="preserve">4.81377553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7667236328125</t>
+    <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
     <t xml:space="preserve">4.71243286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83187294006348</t>
+    <t xml:space="preserve">4.83187246322632</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88616275787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00922203063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09246683120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332536697388</t>
+    <t xml:space="preserve">4.88616323471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00922155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09246826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332632064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.16847467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95493173599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84273052215576</t>
+    <t xml:space="preserve">4.95493125915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8427300453186</t>
   </si>
   <si>
     <t xml:space="preserve">4.78120088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06713151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08884859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00560235977173</t>
+    <t xml:space="preserve">5.06713199615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08884906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00560188293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.99112462997437</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">5.1901912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23362350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35668277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12866115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02008056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98026704788208</t>
+    <t xml:space="preserve">5.23362398147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35668230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12866163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02007961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98026657104492</t>
   </si>
   <si>
     <t xml:space="preserve">4.94769239425659</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">4.9730281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90787887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02369928359985</t>
+    <t xml:space="preserve">4.90787982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02369976043701</t>
   </si>
   <si>
     <t xml:space="preserve">5.11418390274048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12142276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544111251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406314849854</t>
+    <t xml:space="preserve">5.121422290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544206619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406362533569</t>
   </si>
   <si>
     <t xml:space="preserve">5.28287506103516</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">5.16647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33168649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30164909362793</t>
+    <t xml:space="preserve">5.33168601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30164813995361</t>
   </si>
   <si>
     <t xml:space="preserve">5.391761302948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26410150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25659132003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05759334564209</t>
+    <t xml:space="preserve">5.2641019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25659227371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05759239196777</t>
   </si>
   <si>
     <t xml:space="preserve">5.09889459609985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96747970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88863086700439</t>
+    <t xml:space="preserve">4.96747922897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88863039016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.78725337982178</t>
@@ -272,61 +272,61 @@
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472568511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7008957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96372413635254</t>
+    <t xml:space="preserve">4.76472473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70089530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9637246131897</t>
   </si>
   <si>
     <t xml:space="preserve">4.90364980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90740394592285</t>
+    <t xml:space="preserve">4.90740442276001</t>
   </si>
   <si>
     <t xml:space="preserve">4.7759895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73844289779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84357357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91866827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98625326156616</t>
+    <t xml:space="preserve">4.73844242095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84357404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9186692237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98625230789185</t>
   </si>
   <si>
     <t xml:space="preserve">4.97874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01629066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92617750167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95246076583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97123384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87736654281616</t>
+    <t xml:space="preserve">5.01629018783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92617797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95246028900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97123432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85483884811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.877366065979</t>
   </si>
   <si>
     <t xml:space="preserve">4.80227279663086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204599380493</t>
+    <t xml:space="preserve">4.62204647064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.56197071075439</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">4.4568395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56948041915894</t>
+    <t xml:space="preserve">4.56948089599609</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73093318939209</t>
+    <t xml:space="preserve">4.73093366622925</t>
   </si>
   <si>
     <t xml:space="preserve">4.80602693557739</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">4.49063158035278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13017988204956</t>
+    <t xml:space="preserve">4.13017892837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39676380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33668804168701</t>
+    <t xml:space="preserve">4.33668851852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.39300918579102</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">4.17523622512817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10014200210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87485909461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94244432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2653489112854</t>
+    <t xml:space="preserve">4.10014152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87485933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94244360923767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534938812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
@@ -392,25 +392,25 @@
     <t xml:space="preserve">4.19025468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20151948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23531103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31040573120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25033044815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24657583236694</t>
+    <t xml:space="preserve">4.20151901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23531150817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31040477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25032949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24657535552979</t>
   </si>
   <si>
     <t xml:space="preserve">4.27661323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09638643264771</t>
+    <t xml:space="preserve">4.09638738632202</t>
   </si>
   <si>
     <t xml:space="preserve">3.93117952346802</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">3.83731198310852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93868899345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623610496521</t>
+    <t xml:space="preserve">3.93868923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623682022095</t>
   </si>
   <si>
     <t xml:space="preserve">3.93493437767029</t>
@@ -434,37 +434,37 @@
     <t xml:space="preserve">3.9724817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95746302604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94619917869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99876475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82980298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82604813575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470852851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133104324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07010459899902</t>
+    <t xml:space="preserve">3.95746231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9461989402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9987645149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82980251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8260486125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348208427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07010412216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01378297805786</t>
+    <t xml:space="preserve">4.01378393173218</t>
   </si>
   <si>
     <t xml:space="preserve">4.05884027481079</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">4.09263277053833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13768911361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12267017364502</t>
+    <t xml:space="preserve">4.13768863677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12266969680786</t>
   </si>
   <si>
     <t xml:space="preserve">4.0550856590271</t>
@@ -485,136 +485,136 @@
     <t xml:space="preserve">4.07385873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03255701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124059677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8222930431366</t>
+    <t xml:space="preserve">4.03255748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91240644454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82229328155518</t>
   </si>
   <si>
     <t xml:space="preserve">3.81478404998779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90489649772644</t>
+    <t xml:space="preserve">3.90489721298218</t>
   </si>
   <si>
     <t xml:space="preserve">3.90114212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88987827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8110294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88612389564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89738774299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88236904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87110471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85233116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76221799850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61202955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59550929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7960102558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96121788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97999119758606</t>
+    <t xml:space="preserve">3.88987803459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81102919578552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8861231803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89738726615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88236880302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87110447883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8523313999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76221776008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61203026771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59550976753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79601049423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96121764183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97999167442322</t>
   </si>
   <si>
     <t xml:space="preserve">4.02504777908325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96497249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01753759384155</t>
+    <t xml:space="preserve">3.96497297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01753807067871</t>
   </si>
   <si>
     <t xml:space="preserve">4.08887815475464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14519786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9950098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92742562294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83355808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78474593162537</t>
+    <t xml:space="preserve">4.14519834518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99501013755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92742538452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78474617004395</t>
   </si>
   <si>
     <t xml:space="preserve">3.80727481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79225516319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75170493125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73518395423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64056539535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60452079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54444479942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53843760490417</t>
+    <t xml:space="preserve">3.79225587844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75170469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73518443107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64056515693665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60452032089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54444432258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53843712806702</t>
   </si>
   <si>
     <t xml:space="preserve">3.54144144058228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55645990371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47085332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58800005912781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66459560394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64507126808167</t>
+    <t xml:space="preserve">3.55646014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60001492500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47085285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58799958229065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66459608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64507150650024</t>
   </si>
   <si>
     <t xml:space="preserve">3.66910147666931</t>
@@ -626,55 +626,55 @@
     <t xml:space="preserve">3.73968982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84857583045959</t>
+    <t xml:space="preserve">3.84857654571533</t>
   </si>
   <si>
     <t xml:space="preserve">4.14144372940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1038966178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01002883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04006624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11516094207764</t>
+    <t xml:space="preserve">4.10389709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01002836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04006671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11516046524048</t>
   </si>
   <si>
     <t xml:space="preserve">4.00251960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07761287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16772651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15270757675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14895296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18274545669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22029256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23906564712524</t>
+    <t xml:space="preserve">4.07761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16772699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15270805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14895343780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18274593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22029209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23906517028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.16021680831909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12642431259155</t>
+    <t xml:space="preserve">4.12642383575439</t>
   </si>
   <si>
     <t xml:space="preserve">4.06259489059448</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.03631162643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13393449783325</t>
+    <t xml:space="preserve">4.13393402099609</t>
   </si>
   <si>
     <t xml:space="preserve">4.28787755966187</t>
@@ -695,28 +695,28 @@
     <t xml:space="preserve">4.33293390274048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46810245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63706588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69338607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72342300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67085742950439</t>
+    <t xml:space="preserve">4.46810293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44557476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63706493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6933856010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72342348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67085790634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.80978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83981943130493</t>
+    <t xml:space="preserve">4.83981990814209</t>
   </si>
   <si>
     <t xml:space="preserve">4.81353616714478</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">5.0744891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12947607040405</t>
+    <t xml:space="preserve">5.12947559356689</t>
   </si>
   <si>
     <t xml:space="preserve">5.16875171661377</t>
@@ -761,25 +761,25 @@
     <t xml:space="preserve">5.33371210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34156703948975</t>
+    <t xml:space="preserve">5.3415675163269</t>
   </si>
   <si>
     <t xml:space="preserve">5.37691640853882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20410013198853</t>
+    <t xml:space="preserve">5.20410060882568</t>
   </si>
   <si>
     <t xml:space="preserve">5.28265285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20017242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22373914718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092334747314</t>
+    <t xml:space="preserve">5.20017290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22373819351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092287063599</t>
   </si>
   <si>
     <t xml:space="preserve">5.15696907043457</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">5.26694202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36906099319458</t>
+    <t xml:space="preserve">5.36906051635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.34942245483398</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">5.32978439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32585620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2512321472168</t>
+    <t xml:space="preserve">5.32585668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25123262405396</t>
   </si>
   <si>
     <t xml:space="preserve">5.37298822402954</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">5.43975782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61650133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57722473144531</t>
+    <t xml:space="preserve">5.61650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57722425460815</t>
   </si>
   <si>
     <t xml:space="preserve">5.5418758392334</t>
@@ -848,40 +848,40 @@
     <t xml:space="preserve">5.62042856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55365943908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50259971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41226434707642</t>
+    <t xml:space="preserve">5.55365896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50260019302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41226387023926</t>
   </si>
   <si>
     <t xml:space="preserve">5.52223825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61257362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69112586975098</t>
+    <t xml:space="preserve">5.61257314682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69112539291382</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87572383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71076345443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73433017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64006614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65970468521118</t>
+    <t xml:space="preserve">5.87572431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71076393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73432970046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64006662368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65970420837402</t>
   </si>
   <si>
     <t xml:space="preserve">5.72647428512573</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">5.68327045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67148733139038</t>
+    <t xml:space="preserve">5.67148685455322</t>
   </si>
   <si>
     <t xml:space="preserve">5.6557765007019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77753305435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77360582351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86786842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83644723892212</t>
+    <t xml:space="preserve">5.77753353118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77360534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86786890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83644771575928</t>
   </si>
   <si>
     <t xml:space="preserve">5.82466554641724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8403754234314</t>
+    <t xml:space="preserve">5.84037494659424</t>
   </si>
   <si>
     <t xml:space="preserve">5.82859230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87179660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93463754653931</t>
+    <t xml:space="preserve">5.87179613113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93463850021362</t>
   </si>
   <si>
     <t xml:space="preserve">5.95034885406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90714454650879</t>
+    <t xml:space="preserve">5.90714502334595</t>
   </si>
   <si>
     <t xml:space="preserve">5.79717111587524</t>
@@ -935,37 +935,37 @@
     <t xml:space="preserve">5.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78931617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89143514633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78538846969604</t>
+    <t xml:space="preserve">5.78931665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89143419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78538799285889</t>
   </si>
   <si>
     <t xml:space="preserve">5.79324388504028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70683622360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6871976852417</t>
+    <t xml:space="preserve">5.70683574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68719816207886</t>
   </si>
   <si>
     <t xml:space="preserve">5.56936931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46725130081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59293508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66756057739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903394699097</t>
+    <t xml:space="preserve">5.46725177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59293556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66756010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903442382812</t>
   </si>
   <si>
     <t xml:space="preserve">5.41619157791138</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">5.45939588546753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75004005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76182317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75396728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80109930038452</t>
+    <t xml:space="preserve">5.75004053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76182270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75396823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80109882354736</t>
   </si>
   <si>
     <t xml:space="preserve">5.8089542388916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91500043869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87965202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85215854644775</t>
+    <t xml:space="preserve">5.91499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87965154647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8521580696106</t>
   </si>
   <si>
     <t xml:space="preserve">5.84430265426636</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">5.86001300811768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84823131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72254610061646</t>
+    <t xml:space="preserve">5.84823083877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72254657745361</t>
   </si>
   <si>
     <t xml:space="preserve">5.6950535774231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66363191604614</t>
+    <t xml:space="preserve">5.6636323928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.64792156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71861934661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83252048492432</t>
+    <t xml:space="preserve">5.71861886978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83252000808716</t>
   </si>
   <si>
     <t xml:space="preserve">5.76575088500977</t>
@@ -1040,28 +1040,28 @@
     <t xml:space="preserve">6.08388805389404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26063108444214</t>
+    <t xml:space="preserve">6.26063060760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.2449197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31168937683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30776166915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29205226898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25670385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23706531524658</t>
+    <t xml:space="preserve">6.31168985366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30776214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29990768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29205179214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25670337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2370662689209</t>
   </si>
   <si>
     <t xml:space="preserve">6.25277614593506</t>
@@ -1070,61 +1070,61 @@
     <t xml:space="preserve">6.26455879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20171642303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2331371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06032228469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0092625617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12709140777588</t>
+    <t xml:space="preserve">6.20171689987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23313760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06032276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00926351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12709188461304</t>
   </si>
   <si>
     <t xml:space="preserve">6.22528266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28026914596558</t>
+    <t xml:space="preserve">6.28026866912842</t>
   </si>
   <si>
     <t xml:space="preserve">6.37060403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37453174591064</t>
+    <t xml:space="preserve">6.3745322227478</t>
   </si>
   <si>
     <t xml:space="preserve">6.33132839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39809799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58662366867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65339326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53949117660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60626173019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63768243789673</t>
+    <t xml:space="preserve">6.39809846878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45308399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5866231918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65339374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60626220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63768196105957</t>
   </si>
   <si>
     <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71230697631836</t>
+    <t xml:space="preserve">6.71230745315552</t>
   </si>
   <si>
     <t xml:space="preserve">6.83013534545898</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">6.68874216079712</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79086017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6808876991272</t>
+    <t xml:space="preserve">6.79086065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68088674545288</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409105300903</t>
@@ -1148,169 +1148,169 @@
     <t xml:space="preserve">6.75551176071167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76336622238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8576283454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86155700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81049823760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70445156097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63375568389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64553737640381</t>
+    <t xml:space="preserve">6.76336574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85762929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8615574836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81049776077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70445203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63375520706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64553833007812</t>
   </si>
   <si>
     <t xml:space="preserve">6.91261625289917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99116802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33287191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40357065200806</t>
+    <t xml:space="preserve">6.99902391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99116849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33287239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40356922149658</t>
   </si>
   <si>
     <t xml:space="preserve">7.58031177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54103708267212</t>
+    <t xml:space="preserve">7.5410361289978</t>
   </si>
   <si>
     <t xml:space="preserve">7.55281925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46641111373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49783325195312</t>
+    <t xml:space="preserve">7.46641159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49783182144165</t>
   </si>
   <si>
     <t xml:space="preserve">7.60387802124023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62351608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66671991348267</t>
+    <t xml:space="preserve">7.62351655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66672039031982</t>
   </si>
   <si>
     <t xml:space="preserve">7.8041877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75705528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88666820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93379735946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91808700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454732894897</t>
+    <t xml:space="preserve">7.75705480575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88666677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93379878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91808748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454875946045</t>
   </si>
   <si>
     <t xml:space="preserve">7.86310052871704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87488460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886449813843</t>
+    <t xml:space="preserve">7.87488412857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74055862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886354446411</t>
   </si>
   <si>
     <t xml:space="preserve">7.31951856613159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50804328918457</t>
+    <t xml:space="preserve">7.50804471969604</t>
   </si>
   <si>
     <t xml:space="preserve">7.53161001205444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23782348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26610136032104</t>
+    <t xml:space="preserve">7.23782396316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26610088348389</t>
   </si>
   <si>
     <t xml:space="preserve">7.24410820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30066442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49076223373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59130954742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69657039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77355146408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80025815963745</t>
+    <t xml:space="preserve">7.3006649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49076271057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59131002426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77355098724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80025911331177</t>
   </si>
   <si>
     <t xml:space="preserve">7.77826547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83325099945068</t>
+    <t xml:space="preserve">7.83325242996216</t>
   </si>
   <si>
     <t xml:space="preserve">7.94950914382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96914672851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52061319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83011054992676</t>
+    <t xml:space="preserve">7.96914863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52061176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83010911941528</t>
   </si>
   <si>
     <t xml:space="preserve">7.96129083633423</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08304882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09090328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95343780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0437707901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11054039001465</t>
+    <t xml:space="preserve">8.08304977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09090423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94165277481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95343685150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11054134368896</t>
   </si>
   <si>
     <t xml:space="preserve">8.14589023590088</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">8.07126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86702871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8395357131958</t>
+    <t xml:space="preserve">7.86702966690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83953523635864</t>
   </si>
   <si>
     <t xml:space="preserve">7.6949987411499</t>
@@ -1331,49 +1331,49 @@
     <t xml:space="preserve">7.71071004867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67300367355347</t>
+    <t xml:space="preserve">7.64158296585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67300415039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.61487531661987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65572309494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85524559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59445190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65415143966675</t>
+    <t xml:space="preserve">7.65572261810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85524702072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59445095062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65415287017822</t>
   </si>
   <si>
     <t xml:space="preserve">7.596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56146001815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75312852859497</t>
+    <t xml:space="preserve">7.5614595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75312757492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.83168077468872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82696676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79554605484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897857666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08750534057617</t>
+    <t xml:space="preserve">7.82696628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79554653167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03897953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08750438690186</t>
   </si>
   <si>
     <t xml:space="preserve">8.01633548736572</t>
@@ -1385,25 +1385,25 @@
     <t xml:space="preserve">7.97427892684937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00986480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07456493377686</t>
+    <t xml:space="preserve">8.00986385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07456398010254</t>
   </si>
   <si>
     <t xml:space="preserve">7.9856014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14815998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21690464019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93222379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86105442047119</t>
+    <t xml:space="preserve">8.14816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21690368652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93222332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86105537414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.85943746566772</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">7.87884616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86752414703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43726825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4194769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25125646591187</t>
+    <t xml:space="preserve">7.86752510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43727016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41947650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25125694274902</t>
   </si>
   <si>
     <t xml:space="preserve">7.19626140594482</t>
@@ -1430,22 +1430,22 @@
     <t xml:space="preserve">7.43079900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40492010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42594766616821</t>
+    <t xml:space="preserve">7.40491962432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4259467124939</t>
   </si>
   <si>
     <t xml:space="preserve">7.10568141937256</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43441867828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84849882125854</t>
+    <t xml:space="preserve">6.59293413162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43441820144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8484992980957</t>
   </si>
   <si>
     <t xml:space="preserve">6.91805171966553</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">6.92613887786865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81776762008667</t>
+    <t xml:space="preserve">6.81776714324951</t>
   </si>
   <si>
     <t xml:space="preserve">7.2221417427063</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">7.20111417770386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14773654937744</t>
+    <t xml:space="preserve">7.1477370262146</t>
   </si>
   <si>
     <t xml:space="preserve">7.26419687271118</t>
@@ -1478,34 +1478,34 @@
     <t xml:space="preserve">7.5860800743103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70415639877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66857290267944</t>
+    <t xml:space="preserve">7.70415735244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66857242584229</t>
   </si>
   <si>
     <t xml:space="preserve">7.63783979415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78179740905762</t>
+    <t xml:space="preserve">7.7817964553833</t>
   </si>
   <si>
     <t xml:space="preserve">7.70739221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8028244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62975168228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69445180892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65886735916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69768667221069</t>
+    <t xml:space="preserve">7.80282402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62975215911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69445085525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65886640548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69768714904785</t>
   </si>
   <si>
     <t xml:space="preserve">7.82223463058472</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">7.830322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95163488388062</t>
+    <t xml:space="preserve">7.95163440704346</t>
   </si>
   <si>
     <t xml:space="preserve">8.05353736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03089141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95001649856567</t>
+    <t xml:space="preserve">8.03089332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95001697540283</t>
   </si>
   <si>
     <t xml:space="preserve">8.07294750213623</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">8.06809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19264316558838</t>
+    <t xml:space="preserve">8.19264221191406</t>
   </si>
   <si>
     <t xml:space="preserve">8.25329875946045</t>
@@ -1544,19 +1544,19 @@
     <t xml:space="preserve">8.29778003692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27756023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18455410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23308086395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21286106109619</t>
+    <t xml:space="preserve">8.31395626068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27756118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18455505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23307991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21286010742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.28564929962158</t>
@@ -1565,43 +1565,43 @@
     <t xml:space="preserve">8.24925518035889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12794399261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24521160125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13198661804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06647682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17646789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07941818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14007377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08588695526123</t>
+    <t xml:space="preserve">8.12794303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24521064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13198566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06647777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1764669418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07941627502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14007186889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08588790893555</t>
   </si>
   <si>
     <t xml:space="preserve">8.12389850616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20881748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2249927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30990982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22903537750244</t>
+    <t xml:space="preserve">8.20881652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22499179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30991077423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">8.1885986328125</t>
@@ -1610,34 +1610,34 @@
     <t xml:space="preserve">8.33417415618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30182361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3179988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60510635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77898693084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77089881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95691108703613</t>
+    <t xml:space="preserve">8.30182456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31799983978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60510444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77898597717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77089786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89625453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95691204071045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03778648376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04183101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11866092681885</t>
+    <t xml:space="preserve">9.04183006286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11866188049316</t>
   </si>
   <si>
     <t xml:space="preserve">9.22379875183105</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">9.33298110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32084941864014</t>
+    <t xml:space="preserve">9.32084846496582</t>
   </si>
   <si>
     <t xml:space="preserve">9.22784328460693</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">9.61604309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48260021209717</t>
+    <t xml:space="preserve">9.48259925842285</t>
   </si>
   <si>
     <t xml:space="preserve">9.31276226043701</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">9.39768123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30063056945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28041172027588</t>
+    <t xml:space="preserve">9.30062961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2804126739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.1954927444458</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">8.67789173126221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05192089080811</t>
+    <t xml:space="preserve">8.65362930297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05191993713379</t>
   </si>
   <si>
     <t xml:space="preserve">7.89987468719482</t>
@@ -1700,73 +1700,73 @@
     <t xml:space="preserve">8.11985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83355665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46800231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25287485122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24155235290527</t>
+    <t xml:space="preserve">7.83355808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46800136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25287389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24155282974243</t>
   </si>
   <si>
     <t xml:space="preserve">7.1606764793396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05715703964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09597730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31595659255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33860206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47770690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59093141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92251873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75106477737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76562261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78503274917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98721933364868</t>
+    <t xml:space="preserve">7.05715608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080888748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09597682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31595611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33860158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.477707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59093046188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92251920700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75106430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76562309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78503322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.987220287323</t>
   </si>
   <si>
     <t xml:space="preserve">8.00824737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94516515731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9661922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88369989395142</t>
+    <t xml:space="preserve">7.94516563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96619319915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88369941711426</t>
   </si>
   <si>
     <t xml:space="preserve">7.78017902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78988409042358</t>
+    <t xml:space="preserve">7.7898850440979</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238536834717</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">7.74297761917114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84164428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98074960708618</t>
+    <t xml:space="preserve">7.84164476394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98075008392334</t>
   </si>
   <si>
     <t xml:space="preserve">7.9111967086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68474721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85134935379028</t>
+    <t xml:space="preserve">7.68474674224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85134983062744</t>
   </si>
   <si>
     <t xml:space="preserve">7.74944686889648</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">7.39036083221436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22537708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2496395111084</t>
+    <t xml:space="preserve">7.22537660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24963903427124</t>
   </si>
   <si>
     <t xml:space="preserve">7.44212198257446</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">7.4938817024231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39521455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26581525802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21890640258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35477685928345</t>
+    <t xml:space="preserve">7.39521503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26581430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21890687942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35477733612061</t>
   </si>
   <si>
     <t xml:space="preserve">7.01833724975586</t>
@@ -1829,22 +1829,22 @@
     <t xml:space="preserve">7.05230379104614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93099117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09921169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07980155944824</t>
+    <t xml:space="preserve">6.93099164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0992112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0798020362854</t>
   </si>
   <si>
     <t xml:space="preserve">6.99245691299438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23831748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27875518798828</t>
+    <t xml:space="preserve">7.23831605911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27875375747681</t>
   </si>
   <si>
     <t xml:space="preserve">7.58446216583252</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">7.62328100204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56828641891479</t>
+    <t xml:space="preserve">7.56828737258911</t>
   </si>
   <si>
     <t xml:space="preserve">7.55534696578979</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">7.64430952072144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93707609176636</t>
+    <t xml:space="preserve">7.93707704544067</t>
   </si>
   <si>
     <t xml:space="preserve">7.90634393692017</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">7.92898941040039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78826808929443</t>
+    <t xml:space="preserve">7.78826665878296</t>
   </si>
   <si>
     <t xml:space="preserve">7.88046550750732</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">7.85781908035278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.673424243927</t>
+    <t xml:space="preserve">7.67342329025269</t>
   </si>
   <si>
     <t xml:space="preserve">7.57152223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8319411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92575407028198</t>
+    <t xml:space="preserve">7.83193969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9257550239563</t>
   </si>
   <si>
     <t xml:space="preserve">8.01795196533203</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">8.2371244430542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45144176483154</t>
+    <t xml:space="preserve">8.45144271850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.5767993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38674163818359</t>
+    <t xml:space="preserve">8.38674354553223</t>
   </si>
   <si>
     <t xml:space="preserve">8.26947402954102</t>
@@ -1928,31 +1928,31 @@
     <t xml:space="preserve">8.26138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3503475189209</t>
+    <t xml:space="preserve">8.35034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83559894561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92051887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15909957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02161121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07418155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28445434570312</t>
+    <t xml:space="preserve">8.92051792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08226871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15909862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18740367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02161026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07418060302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28445529937744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17931842803955</t>
@@ -1961,19 +1961,19 @@
     <t xml:space="preserve">9.2318868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34915637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38150596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26828002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36532974243164</t>
+    <t xml:space="preserve">9.34915542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38150691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32489204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26828098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36533069610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.59178066253662</t>
@@ -1985,19 +1985,19 @@
     <t xml:space="preserve">9.5958251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65647983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5675163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45833587646484</t>
+    <t xml:space="preserve">9.65648078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56751728057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45833683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.4664249420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47451210021973</t>
+    <t xml:space="preserve">9.47451114654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.81014347076416</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">10.0163736343384</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83036231994629</t>
+    <t xml:space="preserve">9.83036136627197</t>
   </si>
   <si>
     <t xml:space="preserve">10.036060333252</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">9.84943866729736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79552745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98629570007324</t>
+    <t xml:space="preserve">9.7955265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98629379272461</t>
   </si>
   <si>
     <t xml:space="preserve">9.79967212677002</t>
@@ -2027,10 +2027,10 @@
     <t xml:space="preserve">9.73331928253174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4761962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40569496154785</t>
+    <t xml:space="preserve">9.47619819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40569591522217</t>
   </si>
   <si>
     <t xml:space="preserve">9.18589782714844</t>
@@ -2042,37 +2042,37 @@
     <t xml:space="preserve">8.44356060028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27767562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17151069641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96912908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12506008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03050708770752</t>
+    <t xml:space="preserve">8.27767658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17150974273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96912860870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12506103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03050804138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.22625160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23620510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11842632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2113208770752</t>
+    <t xml:space="preserve">8.2362060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11842727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21131992340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.09520244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00728225708008</t>
+    <t xml:space="preserve">8.00728321075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.08690738677979</t>
@@ -2081,37 +2081,37 @@
     <t xml:space="preserve">8.0388011932373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87955141067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67385387420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69375944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59091091156006</t>
+    <t xml:space="preserve">7.87955188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67385292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69376039505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59091138839722</t>
   </si>
   <si>
     <t xml:space="preserve">7.77670288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70868921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71366548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70039558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7335729598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58925151824951</t>
+    <t xml:space="preserve">7.77172660827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70868968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7136664390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70039510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73357248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58925199508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.62574672698975</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">7.55109882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72859621047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82978630065918</t>
+    <t xml:space="preserve">7.72859525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82978534698486</t>
   </si>
   <si>
     <t xml:space="preserve">7.91936492919922</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">8.08359146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01557731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96249485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13667488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17814445495605</t>
+    <t xml:space="preserve">8.01557636260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96249437332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13667392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17814350128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.2196159362793</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">8.87900924682617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86656951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54724025726318</t>
+    <t xml:space="preserve">8.86656761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54723930358887</t>
   </si>
   <si>
     <t xml:space="preserve">8.38550090789795</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">8.4560022354126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30670642852783</t>
+    <t xml:space="preserve">8.30670547485352</t>
   </si>
   <si>
     <t xml:space="preserve">8.48088550567627</t>
@@ -2189,49 +2189,49 @@
     <t xml:space="preserve">8.29094696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32329559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05704784393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06700038909912</t>
+    <t xml:space="preserve">8.3232946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05704879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06700229644775</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08027267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86462163925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36530685424805</t>
+    <t xml:space="preserve">8.08027172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86462211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36530733108521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57266330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39184904098511</t>
+    <t xml:space="preserve">7.5726637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39184808731079</t>
   </si>
   <si>
     <t xml:space="preserve">7.22098684310913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38853025436401</t>
+    <t xml:space="preserve">7.38355493545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38853120803833</t>
   </si>
   <si>
     <t xml:space="preserve">7.7319130897522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41839170455933</t>
+    <t xml:space="preserve">7.41839075088501</t>
   </si>
   <si>
     <t xml:space="preserve">7.25084543228149</t>
@@ -2240,25 +2240,25 @@
     <t xml:space="preserve">7.42502593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06173658370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17951536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31388187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25913953781128</t>
+    <t xml:space="preserve">7.06173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17951583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31388235092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2591404914856</t>
   </si>
   <si>
     <t xml:space="preserve">7.56436824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4449315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76509141921997</t>
+    <t xml:space="preserve">7.44493246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76509046554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.73854827880859</t>
@@ -2267,25 +2267,25 @@
     <t xml:space="preserve">7.92765760421753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77836132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72030115127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258689880371</t>
+    <t xml:space="preserve">7.77836227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72030162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258737564087</t>
   </si>
   <si>
     <t xml:space="preserve">8.15989685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18975734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89116382598877</t>
+    <t xml:space="preserve">8.18975639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89116239547729</t>
   </si>
   <si>
     <t xml:space="preserve">7.81651449203491</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">8.16985130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09851932525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76343059539795</t>
+    <t xml:space="preserve">8.09852027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76343154907227</t>
   </si>
   <si>
     <t xml:space="preserve">7.79660797119141</t>
@@ -2306,73 +2306,73 @@
     <t xml:space="preserve">8.03216552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98903512954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84969091415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86130380630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97742366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05539035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96581125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76840782165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90443420410156</t>
+    <t xml:space="preserve">7.98903656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84969234466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05538940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96581172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76840829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90443468093872</t>
   </si>
   <si>
     <t xml:space="preserve">8.00064659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02719020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65394735336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361898422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89614105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12672138214111</t>
+    <t xml:space="preserve">8.02718925476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65394687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89614009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12671947479248</t>
   </si>
   <si>
     <t xml:space="preserve">7.95917654037476</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17482757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33988380432129</t>
+    <t xml:space="preserve">8.17482662200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33988285064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.34403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55967998504639</t>
+    <t xml:space="preserve">8.5596809387207</t>
   </si>
   <si>
     <t xml:space="preserve">8.46014976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44770908355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63018131256104</t>
+    <t xml:space="preserve">8.44770812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63018226623535</t>
   </si>
   <si>
     <t xml:space="preserve">8.6260347366333</t>
@@ -2381,19 +2381,19 @@
     <t xml:space="preserve">8.47673797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37720680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60944557189941</t>
+    <t xml:space="preserve">8.37720775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60944652557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.85412788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95780658721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99927806854248</t>
+    <t xml:space="preserve">8.95780563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99927711486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.16516208648682</t>
@@ -2408,31 +2408,31 @@
     <t xml:space="preserve">9.48449230194092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54255199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52596282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50937461853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42643165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31445789337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057823181152</t>
+    <t xml:space="preserve">9.54255104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52596187591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50937557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42642974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31445980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057918548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.38496112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51766967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73746681213379</t>
+    <t xml:space="preserve">9.51766872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73746585845947</t>
   </si>
   <si>
     <t xml:space="preserve">9.70014190673828</t>
@@ -2441,19 +2441,19 @@
     <t xml:space="preserve">9.57158184051514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33934211730957</t>
+    <t xml:space="preserve">9.33934116363525</t>
   </si>
   <si>
     <t xml:space="preserve">9.23151588439941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28957557678223</t>
+    <t xml:space="preserve">9.28957653045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.35178375244141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3891077041626</t>
+    <t xml:space="preserve">9.38910675048828</t>
   </si>
   <si>
     <t xml:space="preserve">9.19833946228027</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26884078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11539649963379</t>
+    <t xml:space="preserve">9.26883983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11539554595947</t>
   </si>
   <si>
     <t xml:space="preserve">9.12369155883789</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">9.04074859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06148433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01586627960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05318927764893</t>
+    <t xml:space="preserve">9.06148338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01586532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05319023132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.93292331695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12783718109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88315677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82509899139404</t>
+    <t xml:space="preserve">9.12783813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88315773010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82509803771973</t>
   </si>
   <si>
     <t xml:space="preserve">9.09880828857422</t>
@@ -2504,25 +2504,25 @@
     <t xml:space="preserve">9.24395847320557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58817005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29372501373291</t>
+    <t xml:space="preserve">9.58816909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29372310638428</t>
   </si>
   <si>
     <t xml:space="preserve">9.15272045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25639820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15686798095703</t>
+    <t xml:space="preserve">9.2564001083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15686893463135</t>
   </si>
   <si>
     <t xml:space="preserve">9.21492767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11954402923584</t>
+    <t xml:space="preserve">9.11954498291016</t>
   </si>
   <si>
     <t xml:space="preserve">9.08221912384033</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">9.11124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7753324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27298831939697</t>
+    <t xml:space="preserve">8.77533149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27298736572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.107102394104</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">9.68770217895508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1444263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08636665344238</t>
+    <t xml:space="preserve">9.14442539215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0863676071167</t>
   </si>
   <si>
     <t xml:space="preserve">9.05733680725098</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">8.99098300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28128147125244</t>
+    <t xml:space="preserve">9.28128242492676</t>
   </si>
   <si>
     <t xml:space="preserve">8.89559936523438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25279331207275</t>
+    <t xml:space="preserve">8.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">8.14994430541992</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">7.87457418441772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74186658859253</t>
+    <t xml:space="preserve">7.74186611175537</t>
   </si>
   <si>
     <t xml:space="preserve">7.34042406082153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35867166519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44327306747437</t>
+    <t xml:space="preserve">7.35867071151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44327259063721</t>
   </si>
   <si>
     <t xml:space="preserve">6.73328399658203</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">6.25055742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53256225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73797225952148</t>
+    <t xml:space="preserve">6.53256273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73797273635864</t>
   </si>
   <si>
     <t xml:space="preserve">6.38990116119385</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">6.30861759185791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24060487747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2024507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19083881378174</t>
+    <t xml:space="preserve">6.12946176528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24060440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20245122909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19083976745605</t>
   </si>
   <si>
     <t xml:space="preserve">6.8178858757019</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">6.71503591537476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33047151565552</t>
+    <t xml:space="preserve">7.33047103881836</t>
   </si>
   <si>
     <t xml:space="preserve">6.85769748687744</t>
@@ -2642,37 +2642,37 @@
     <t xml:space="preserve">6.87594509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87096929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09159564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42336702346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59257030487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8331036567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92931842803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32715272903442</t>
+    <t xml:space="preserve">6.87096881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09159708023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4233660697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59256935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92931699752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32715368270874</t>
   </si>
   <si>
     <t xml:space="preserve">7.22264528274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21600961685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24255228042603</t>
+    <t xml:space="preserve">7.21601057052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24255275726318</t>
   </si>
   <si>
     <t xml:space="preserve">6.76977825164795</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">7.26411724090576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66224145889282</t>
+    <t xml:space="preserve">7.66224241256714</t>
   </si>
   <si>
     <t xml:space="preserve">7.64067649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88286828994751</t>
+    <t xml:space="preserve">7.88286876678467</t>
   </si>
   <si>
     <t xml:space="preserve">8.07363700866699</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">8.46844387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4103832244873</t>
+    <t xml:space="preserve">8.41038417816162</t>
   </si>
   <si>
     <t xml:space="preserve">8.05207252502441</t>
@@ -2705,43 +2705,43 @@
     <t xml:space="preserve">8.28596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70897674560547</t>
+    <t xml:space="preserve">8.70897769927979</t>
   </si>
   <si>
     <t xml:space="preserve">8.35232353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22956943511963</t>
+    <t xml:space="preserve">8.22956848144531</t>
   </si>
   <si>
     <t xml:space="preserve">8.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.294264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20800399780273</t>
+    <t xml:space="preserve">8.29426574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20800495147705</t>
   </si>
   <si>
     <t xml:space="preserve">8.43111991882324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4725923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78777313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71312427520752</t>
+    <t xml:space="preserve">8.47259140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78777408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71312522888184</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91218662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00342273712158</t>
+    <t xml:space="preserve">8.91218757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0034236907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.34763622283936</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">9.34348964691162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36007785797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60475826263428</t>
+    <t xml:space="preserve">9.36007690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60475730895996</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402069091797</t>
@@ -2765,85 +2765,85 @@
     <t xml:space="preserve">9.94896984100342</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0443553924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87432098388672</t>
+    <t xml:space="preserve">10.0443534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87432193756104</t>
   </si>
   <si>
     <t xml:space="preserve">9.98214721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065089225769</t>
+    <t xml:space="preserve">10.0650901794434</t>
   </si>
   <si>
     <t xml:space="preserve">9.9655590057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95311832427979</t>
+    <t xml:space="preserve">9.95311737060547</t>
   </si>
   <si>
     <t xml:space="preserve">10.3595361709595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3512411117554</t>
+    <t xml:space="preserve">10.3512420654297</t>
   </si>
   <si>
     <t xml:space="preserve">10.7286319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6996011734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6747188568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3388013839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4093017578125</t>
+    <t xml:space="preserve">10.6996002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6747179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3388004302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4093027114868</t>
   </si>
   <si>
     <t xml:space="preserve">10.4632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4010066986084</t>
+    <t xml:space="preserve">10.4010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6415424346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8323106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659559249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9318408966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.778395652771</t>
+    <t xml:space="preserve">10.6415405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8323097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7659549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9318399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7783966064453</t>
   </si>
   <si>
     <t xml:space="preserve">10.6332473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042175292969</t>
+    <t xml:space="preserve">10.6042165756226</t>
   </si>
   <si>
     <t xml:space="preserve">10.4300374984741</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5295686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024150848389</t>
+    <t xml:space="preserve">10.5295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024141311646</t>
   </si>
   <si>
     <t xml:space="preserve">10.181209564209</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">10.53786277771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305063247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2309761047363</t>
+    <t xml:space="preserve">10.3305053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553895950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4175968170166</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">11.064549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8654880523682</t>
+    <t xml:space="preserve">10.8654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">10.8240156173706</t>
@@ -2876,73 +2876,73 @@
     <t xml:space="preserve">10.6125116348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6000699996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7493667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.687159538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6913070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7949848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6664247512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5337152481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6249532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5751876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0733842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4341840744019</t>
+    <t xml:space="preserve">10.6000709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7493658065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6871604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6913080215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7949867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6664237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5337162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6249523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5751867294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0733852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4341850280762</t>
   </si>
   <si>
     <t xml:space="preserve">10.2392702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1895036697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1936502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0319118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81626224517822</t>
+    <t xml:space="preserve">10.3180646896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1895027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1936511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0319137573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81626129150391</t>
   </si>
   <si>
     <t xml:space="preserve">9.83284950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46790313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44716835021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72087955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5591402053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71258449554443</t>
+    <t xml:space="preserve">9.46790218353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44716739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7208776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55913925170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71258354187012</t>
   </si>
   <si>
     <t xml:space="preserve">9.67940711975098</t>
@@ -2951,40 +2951,40 @@
     <t xml:space="preserve">9.74990749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82040977478027</t>
+    <t xml:space="preserve">9.82040882110596</t>
   </si>
   <si>
     <t xml:space="preserve">10.0277652740479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1107082366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90335083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1604738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1729164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2102403640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0775308609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1521797180176</t>
+    <t xml:space="preserve">10.11070728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1604747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1729154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2102394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0775318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1521787643433</t>
   </si>
   <si>
     <t xml:space="preserve">9.99044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1065616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96141147613525</t>
+    <t xml:space="preserve">10.1065626144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96141242980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.59646320343018</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">9.67111301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74576187133789</t>
+    <t xml:space="preserve">9.74576091766357</t>
   </si>
   <si>
     <t xml:space="preserve">9.96970653533936</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">10.2600049972534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3844194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.347095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3346538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94482326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1272964477539</t>
+    <t xml:space="preserve">10.3844184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3470945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3346548080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1272974014282</t>
   </si>
   <si>
     <t xml:space="preserve">10.2683000564575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5088338851929</t>
+    <t xml:space="preserve">10.5088329315186</t>
   </si>
   <si>
     <t xml:space="preserve">10.4134492874146</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">10.5212745666504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.807427406311</t>
+    <t xml:space="preserve">10.8074264526367</t>
   </si>
   <si>
     <t xml:space="preserve">10.7576608657837</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">10.8779268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8945159912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9359884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8157205581665</t>
+    <t xml:space="preserve">10.8945169448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9359874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8157215118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733114242554</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">10.8737802505493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8447494506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9774580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1018743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143140792847</t>
+    <t xml:space="preserve">10.8447504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9774589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350507736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1018724441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.114315032959</t>
   </si>
   <si>
     <t xml:space="preserve">11.35484790802</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">11.6119709014893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.520733833313</t>
+    <t xml:space="preserve">11.5207328796387</t>
   </si>
   <si>
     <t xml:space="preserve">11.4792623519897</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">11.3507013320923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1889629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1226081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0355195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9442806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452182769775</t>
+    <t xml:space="preserve">11.1889619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1682271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1226091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0355186462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.944281578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452201843262</t>
   </si>
   <si>
     <t xml:space="preserve">10.6788654327393</t>
@@ -3134,25 +3134,25 @@
     <t xml:space="preserve">11.9935064315796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1096267700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3999252319336</t>
+    <t xml:space="preserve">12.1096258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3999261856079</t>
   </si>
   <si>
     <t xml:space="preserve">12.1303615570068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4455442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.263069152832</t>
+    <t xml:space="preserve">12.4455432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2630701065063</t>
   </si>
   <si>
     <t xml:space="preserve">12.4953088760376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5948400497437</t>
+    <t xml:space="preserve">12.5948419570923</t>
   </si>
   <si>
     <t xml:space="preserve">12.4870157241821</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">12.3584537506104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1718330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3169822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1842746734619</t>
+    <t xml:space="preserve">12.1718339920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3169832229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1842737197876</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557136535645</t>
@@ -3176,28 +3176,28 @@
     <t xml:space="preserve">12.3377180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1925678253174</t>
+    <t xml:space="preserve">12.192569732666</t>
   </si>
   <si>
     <t xml:space="preserve">12.0847434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.28795337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0640068054199</t>
+    <t xml:space="preserve">12.2879514694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0640087127686</t>
   </si>
   <si>
     <t xml:space="preserve">12.0349779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9230051040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9810657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2755107879639</t>
+    <t xml:space="preserve">11.9230060577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9810647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2755117416382</t>
   </si>
   <si>
     <t xml:space="preserve">12.1635389328003</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">12.2174510955811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3543081283569</t>
+    <t xml:space="preserve">12.3543071746826</t>
   </si>
   <si>
     <t xml:space="preserve">12.1759805679321</t>
@@ -3215,61 +3215,61 @@
     <t xml:space="preserve">11.972770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.97691822052</t>
+    <t xml:space="preserve">11.9769191741943</t>
   </si>
   <si>
     <t xml:space="preserve">11.9437408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.117919921875</t>
+    <t xml:space="preserve">12.1179208755493</t>
   </si>
   <si>
     <t xml:space="preserve">11.7820024490356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6244115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5580577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5539112091064</t>
+    <t xml:space="preserve">11.6244125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5580587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5539102554321</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5746459960938</t>
+    <t xml:space="preserve">11.5746469497681</t>
   </si>
   <si>
     <t xml:space="preserve">11.4834098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5912342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5995283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5870885848999</t>
+    <t xml:space="preserve">11.5912351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5995273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5870876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.6824712753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7405300140381</t>
+    <t xml:space="preserve">11.7405309677124</t>
   </si>
   <si>
     <t xml:space="preserve">11.9603300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7985906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8981218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9520359039307</t>
+    <t xml:space="preserve">11.7985916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8981227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.952033996582</t>
   </si>
   <si>
     <t xml:space="preserve">11.5456161499023</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">11.4543790817261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4751138687134</t>
+    <t xml:space="preserve">11.4751148223877</t>
   </si>
   <si>
     <t xml:space="preserve">11.6783246994019</t>
@@ -3290,91 +3290,91 @@
     <t xml:space="preserve">11.8193273544312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064159393311</t>
+    <t xml:space="preserve">11.9064168930054</t>
   </si>
   <si>
     <t xml:space="preserve">11.8773860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0142421722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6949138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8732385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6617364883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7446784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6534423828125</t>
+    <t xml:space="preserve">12.0142412185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6949129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8732395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.661735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7446794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6534404754639</t>
   </si>
   <si>
     <t xml:space="preserve">11.7115020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7654132843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5787935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.164080619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2055511474609</t>
+    <t xml:space="preserve">11.7654151916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5787925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1640796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2055521011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.305082321167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4129076004028</t>
+    <t xml:space="preserve">11.4129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">11.4336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3631429672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3382587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3880252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3714351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4917030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5124387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5622053146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.524881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5953817367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5497636795044</t>
+    <t xml:space="preserve">11.3299646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3382596969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3880243301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4917020797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5124397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6451482772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5622034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5953807830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5497646331787</t>
   </si>
   <si>
     <t xml:space="preserve">11.66588306427</t>
@@ -3383,19 +3383,19 @@
     <t xml:space="preserve">11.9312992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8607997894287</t>
+    <t xml:space="preserve">11.8607988357544</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409997940063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.806884765625</t>
+    <t xml:space="preserve">11.8068857192993</t>
   </si>
   <si>
     <t xml:space="preserve">12.026683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1013317108154</t>
+    <t xml:space="preserve">12.1013326644897</t>
   </si>
   <si>
     <t xml:space="preserve">12.2133045196533</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">12.1510972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4787216186523</t>
+    <t xml:space="preserve">12.478720664978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0391254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690919876099</t>
+    <t xml:space="preserve">11.8690929412842</t>
   </si>
   <si>
     <t xml:space="preserve">11.7778549194336</t>
@@ -3431,22 +3431,22 @@
     <t xml:space="preserve">12.2215986251831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.333571434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7151079177856</t>
+    <t xml:space="preserve">12.3335723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7151069641113</t>
   </si>
   <si>
     <t xml:space="preserve">12.5367803573608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3708953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7773141860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8975811004639</t>
+    <t xml:space="preserve">12.3708944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7773132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8975820541382</t>
   </si>
   <si>
     <t xml:space="preserve">13.2293519973755</t>
@@ -3455,43 +3455,43 @@
     <t xml:space="preserve">13.3827953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.453296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5942993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4698858261108</t>
+    <t xml:space="preserve">13.4532957077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5942983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4698848724365</t>
   </si>
   <si>
     <t xml:space="preserve">13.4201202392578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3496179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2252054214478</t>
+    <t xml:space="preserve">13.3496189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2252044677734</t>
   </si>
   <si>
     <t xml:space="preserve">13.4781799316406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2169103622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.051025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1588506698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1837329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2583818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629972457886</t>
+    <t xml:space="preserve">13.216911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0510244369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1588497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1837339401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2583808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629981994629</t>
   </si>
   <si>
     <t xml:space="preserve">13.2625284194946</t>
@@ -3503,40 +3503,40 @@
     <t xml:space="preserve">12.8644037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8685522079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607250213623</t>
+    <t xml:space="preserve">12.8685503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607259750366</t>
   </si>
   <si>
     <t xml:space="preserve">12.7939023971558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9349060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312282562256</t>
+    <t xml:space="preserve">12.9349050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.831226348877</t>
   </si>
   <si>
     <t xml:space="preserve">12.7482843399048</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5741052627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6611938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9763784408569</t>
+    <t xml:space="preserve">12.574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6611948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9763774871826</t>
   </si>
   <si>
     <t xml:space="preserve">13.2376461029053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1215257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0095548629761</t>
+    <t xml:space="preserve">13.1215267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0095539093018</t>
   </si>
   <si>
     <t xml:space="preserve">13.2417936325073</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">13.3081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9432001113892</t>
+    <t xml:space="preserve">12.9431991577148</t>
   </si>
   <si>
     <t xml:space="preserve">12.8768453598022</t>
@@ -3557,52 +3557,52 @@
     <t xml:space="preserve">12.7690200805664</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6446056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9888172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302896499634</t>
+    <t xml:space="preserve">12.644606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9888181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302886962891</t>
   </si>
   <si>
     <t xml:space="preserve">13.1090860366821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9929656982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2044696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1173782348633</t>
+    <t xml:space="preserve">12.9929647445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2044687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1173801422119</t>
   </si>
   <si>
     <t xml:space="preserve">13.6025943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7850675582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8016557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7726259231567</t>
+    <t xml:space="preserve">13.7850685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523580551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8016548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">13.7975091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9219236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9799833297729</t>
+    <t xml:space="preserve">13.9219226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9799823760986</t>
   </si>
   <si>
     <t xml:space="preserve">13.6274766921997</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">13.69797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0048656463623</t>
+    <t xml:space="preserve">14.0048666000366</t>
   </si>
   <si>
     <t xml:space="preserve">13.764331817627</t>
@@ -3623,16 +3623,16 @@
     <t xml:space="preserve">14.0878095626831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0173072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.224663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3324880599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712203979492</t>
+    <t xml:space="preserve">14.0173063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3324899673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712194442749</t>
   </si>
   <si>
     <t xml:space="preserve">14.1583089828491</t>
@@ -3647,22 +3647,22 @@
     <t xml:space="preserve">14.2619876861572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076066970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2163686752319</t>
+    <t xml:space="preserve">14.3076076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2163696289062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1251316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3006258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8255071640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.859751701355</t>
+    <t xml:space="preserve">14.3006267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8255081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8597507476807</t>
   </si>
   <si>
     <t xml:space="preserve">13.6542940139771</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">13.645733833313</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4488382339478</t>
+    <t xml:space="preserve">13.4488372802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.4188756942749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3974742889404</t>
+    <t xml:space="preserve">13.3974733352661</t>
   </si>
   <si>
     <t xml:space="preserve">13.4445571899414</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">12.9523191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9095153808594</t>
+    <t xml:space="preserve">12.9095144271851</t>
   </si>
   <si>
     <t xml:space="preserve">13.2433815002441</t>
@@ -3734,16 +3734,16 @@
     <t xml:space="preserve">13.2134189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4531183242798</t>
+    <t xml:space="preserve">13.4531192779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.4873609542847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6842565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2562227249146</t>
+    <t xml:space="preserve">13.6842575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2562217712402</t>
   </si>
   <si>
     <t xml:space="preserve">13.3589496612549</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">13.8511905670166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5301647186279</t>
+    <t xml:space="preserve">13.5301656723022</t>
   </si>
   <si>
     <t xml:space="preserve">13.6114912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2861852645874</t>
+    <t xml:space="preserve">13.2861862182617</t>
   </si>
   <si>
     <t xml:space="preserve">13.0293655395508</t>
@@ -3782,19 +3782,19 @@
     <t xml:space="preserve">12.3616313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5499658584595</t>
+    <t xml:space="preserve">12.5499649047852</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4857616424561</t>
+    <t xml:space="preserve">12.4857606887817</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740961074829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8538703918457</t>
+    <t xml:space="preserve">12.85387134552</t>
   </si>
   <si>
     <t xml:space="preserve">12.900954246521</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">12.8495903015137</t>
   </si>
   <si>
-    <t xml:space="preserve">13.055046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6157722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286134719849</t>
+    <t xml:space="preserve">13.0550470352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6157712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286125183105</t>
   </si>
   <si>
     <t xml:space="preserve">13.7784242630005</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">13.4103145599365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2776250839233</t>
+    <t xml:space="preserve">13.277624130249</t>
   </si>
   <si>
     <t xml:space="preserve">12.4301166534424</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">12.0234832763672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0363254547119</t>
+    <t xml:space="preserve">12.0363245010376</t>
   </si>
   <si>
     <t xml:space="preserve">11.8351488113403</t>
@@ -3857,13 +3857,13 @@
     <t xml:space="preserve">10.8720712661743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5339250564575</t>
+    <t xml:space="preserve">10.5339260101318</t>
   </si>
   <si>
     <t xml:space="preserve">11.783784866333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3172264099121</t>
+    <t xml:space="preserve">11.3172273635864</t>
   </si>
   <si>
     <t xml:space="preserve">11.5954494476318</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">11.8265867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.895073890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5157222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9892416000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0277633666992</t>
+    <t xml:space="preserve">11.8950729370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5157232284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9892406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0106420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0277643203735</t>
   </si>
   <si>
     <t xml:space="preserve">11.9849615097046</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">11.9507179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.314546585083</t>
+    <t xml:space="preserve">12.3145475387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.1989774703979</t>
@@ -3908,16 +3908,16 @@
     <t xml:space="preserve">12.3102674484253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.26318359375</t>
+    <t xml:space="preserve">12.2631826400757</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549989700317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1262121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188285827637</t>
+    <t xml:space="preserve">12.1262111663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188276290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203798294067</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">11.9464378356934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9079151153564</t>
+    <t xml:space="preserve">11.9079141616821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9036340713501</t>
@@ -3935,13 +3935,13 @@
     <t xml:space="preserve">11.8009061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0834093093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0705671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8651113510132</t>
+    <t xml:space="preserve">12.0834083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0705680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8651103973389</t>
   </si>
   <si>
     <t xml:space="preserve">11.4798803329468</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">11.2444620132446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.253023147583</t>
+    <t xml:space="preserve">11.2530221939087</t>
   </si>
   <si>
     <t xml:space="preserve">11.2787046432495</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">11.3771524429321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0775270462036</t>
+    <t xml:space="preserve">11.0775279998779</t>
   </si>
   <si>
     <t xml:space="preserve">11.0903692245483</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">10.5724477767944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0545272827148</t>
+    <t xml:space="preserve">10.0545263290405</t>
   </si>
   <si>
     <t xml:space="preserve">10.080207824707</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">10.2771043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5938501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6109704971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8292675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035860061646</t>
+    <t xml:space="preserve">10.5938491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6109714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8292684555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035869598389</t>
   </si>
   <si>
     <t xml:space="preserve">10.7693433761597</t>
@@ -6309,6 +6309,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.2099990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1499996185303</t>
   </si>
 </sst>
 </file>
@@ -71725,7 +71728,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6938078704</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>2137366</v>
@@ -71746,6 +71749,32 @@
         <v>2098</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.691712963</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>4373642</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>20.2900009155273</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>20.5799999237061</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>2099</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35306262969971</t>
+    <t xml:space="preserve">5.35306215286255</t>
   </si>
   <si>
     <t xml:space="preserve">FBK.MI</t>
@@ -50,130 +50,130 @@
     <t xml:space="preserve">5.17209386825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13951921463013</t>
+    <t xml:space="preserve">5.13951969146729</t>
   </si>
   <si>
     <t xml:space="preserve">5.26257848739624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1322808265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26619720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3132495880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0454158782959</t>
+    <t xml:space="preserve">5.13228130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.266197681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31325006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1938099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04541540145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.92959547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07437038421631</t>
+    <t xml:space="preserve">5.07437133789062</t>
   </si>
   <si>
     <t xml:space="preserve">4.65814208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82101345062256</t>
+    <t xml:space="preserve">4.82101440429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.96578931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21190690994263</t>
+    <t xml:space="preserve">5.05265474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21190643310547</t>
   </si>
   <si>
     <t xml:space="preserve">5.04903507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12504148483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88978242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79205942153931</t>
+    <t xml:space="preserve">5.14675855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16485548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12504196166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8897819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79205894470215</t>
   </si>
   <si>
     <t xml:space="preserve">4.74138784408569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56765651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34325647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45545768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48441171646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58213472366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78482007980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73414850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81377553939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71243286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83187246322632</t>
+    <t xml:space="preserve">4.56765747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3432559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45545673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48441219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58213520050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73414993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81377506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71243238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83187198638916</t>
   </si>
   <si>
     <t xml:space="preserve">4.84996891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88616323471069</t>
+    <t xml:space="preserve">4.88616275787354</t>
   </si>
   <si>
     <t xml:space="preserve">5.00922155380249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09246826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10332632064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16847467422485</t>
+    <t xml:space="preserve">5.09246730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10332536697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16847515106201</t>
   </si>
   <si>
     <t xml:space="preserve">4.95493125915527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8427300453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78120088577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06713199615479</t>
+    <t xml:space="preserve">4.84273099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78120136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06713151931763</t>
   </si>
   <si>
     <t xml:space="preserve">5.08884906768799</t>
@@ -182,58 +182,58 @@
     <t xml:space="preserve">5.00560188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99112462997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1901912689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23362398147583</t>
+    <t xml:space="preserve">4.99112510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19019079208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23362350463867</t>
   </si>
   <si>
     <t xml:space="preserve">5.35668230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02007961273193</t>
+    <t xml:space="preserve">5.128662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02008008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.98026657104492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94769239425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9730281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90787982940674</t>
+    <t xml:space="preserve">4.94769191741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97302770614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90787887573242</t>
   </si>
   <si>
     <t xml:space="preserve">5.02369976043701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11418390274048</t>
+    <t xml:space="preserve">5.11418342590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.121422290802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544206619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23406362533569</t>
+    <t xml:space="preserve">5.33544111251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23406314849854</t>
   </si>
   <si>
     <t xml:space="preserve">5.28287506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27161121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.230309009552</t>
+    <t xml:space="preserve">5.27161073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23030996322632</t>
   </si>
   <si>
     <t xml:space="preserve">5.16647911071777</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">5.33168601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30164813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.391761302948</t>
+    <t xml:space="preserve">5.30164909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39176177978516</t>
   </si>
   <si>
     <t xml:space="preserve">5.2641019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25659227371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05759239196777</t>
+    <t xml:space="preserve">5.256591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05759286880493</t>
   </si>
   <si>
     <t xml:space="preserve">5.09889459609985</t>
@@ -266,46 +266,46 @@
     <t xml:space="preserve">4.88863039016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78725337982178</t>
+    <t xml:space="preserve">4.78725385665894</t>
   </si>
   <si>
     <t xml:space="preserve">4.79100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76472473144531</t>
+    <t xml:space="preserve">4.76472520828247</t>
   </si>
   <si>
     <t xml:space="preserve">4.70089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9637246131897</t>
+    <t xml:space="preserve">4.96372509002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.90364980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90740442276001</t>
+    <t xml:space="preserve">4.90740394592285</t>
   </si>
   <si>
     <t xml:space="preserve">4.7759895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73844242095947</t>
+    <t xml:space="preserve">4.73844194412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.84357404708862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9186692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98625230789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97874355316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01629018783569</t>
+    <t xml:space="preserve">4.91866827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.986252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97874402999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01629066467285</t>
   </si>
   <si>
     <t xml:space="preserve">4.92617797851562</t>
@@ -314,52 +314,52 @@
     <t xml:space="preserve">4.95246028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97123432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85483884811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.877366065979</t>
+    <t xml:space="preserve">4.97123384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85483837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87736654281616</t>
   </si>
   <si>
     <t xml:space="preserve">4.80227279663086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62204647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44182062149048</t>
+    <t xml:space="preserve">4.62204694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56197118759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44181966781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.44932985305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4568395614624</t>
+    <t xml:space="preserve">4.45683908462524</t>
   </si>
   <si>
     <t xml:space="preserve">4.56948089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75346088409424</t>
+    <t xml:space="preserve">4.7534613609314</t>
   </si>
   <si>
     <t xml:space="preserve">4.73093366622925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80602693557739</t>
+    <t xml:space="preserve">4.80602741241455</t>
   </si>
   <si>
     <t xml:space="preserve">4.97498846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49063158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13017892837524</t>
+    <t xml:space="preserve">4.49063110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1301794052124</t>
   </si>
   <si>
     <t xml:space="preserve">4.39676380157471</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">4.39300918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17523622512817</t>
+    <t xml:space="preserve">4.17523574829102</t>
   </si>
   <si>
     <t xml:space="preserve">4.10014152526855</t>
@@ -380,61 +380,61 @@
     <t xml:space="preserve">3.87485933303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94244360923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26534938812256</t>
+    <t xml:space="preserve">3.94244384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26534843444824</t>
   </si>
   <si>
     <t xml:space="preserve">4.31791496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19025468826294</t>
+    <t xml:space="preserve">4.1902551651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.20151901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23531150817871</t>
+    <t xml:space="preserve">4.23531103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.31040477752686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25032949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24657535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27661323547363</t>
+    <t xml:space="preserve">4.25032997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24657583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27661371231079</t>
   </si>
   <si>
     <t xml:space="preserve">4.09638738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93117952346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98750042915344</t>
+    <t xml:space="preserve">3.9311797618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9875009059906</t>
   </si>
   <si>
     <t xml:space="preserve">3.83731198310852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93868923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93493437767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9724817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95746231079102</t>
+    <t xml:space="preserve">3.93868970870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97623658180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93493413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97248244285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95746326446533</t>
   </si>
   <si>
     <t xml:space="preserve">3.9461989402771</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">3.9987645149231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82980251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8260486125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77348208427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75470900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05133008956909</t>
+    <t xml:space="preserve">3.82980275154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82604813575745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77348232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75470876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05133056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.07010412216187</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">4.04382133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01378393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05884027481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09263277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13768863677979</t>
+    <t xml:space="preserve